--- a/ReportesUnificados/loja_ReporteUnificado.xlsx
+++ b/ReportesUnificados/loja_ReporteUnificado.xlsx
@@ -218,10 +218,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3524250" cy="666750"/>
+    <ext cx="4762500" cy="952500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -243,10 +243,10 @@
     <from>
       <col>33</col>
       <colOff>0</colOff>
-      <row>1</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2476500" cy="1333500"/>
+    <ext cx="2476500" cy="1143000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -268,10 +268,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>53</row>
+      <row>56</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3524250" cy="666750"/>
+    <ext cx="4762500" cy="952500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -293,10 +293,10 @@
     <from>
       <col>33</col>
       <colOff>0</colOff>
-      <row>52</row>
+      <row>55</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2476500" cy="1333500"/>
+    <ext cx="2476500" cy="1143000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -606,7 +606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK75"/>
+  <dimension ref="A1:AK77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="59" customWidth="1" min="1" max="1"/>
@@ -642,519 +642,311 @@
     <col width="8" customWidth="1" min="31" max="31"/>
     <col width="8" customWidth="1" min="32" max="32"/>
     <col width="8" customWidth="1" min="33" max="33"/>
-    <col width="19" customWidth="1" min="34" max="34"/>
-    <col width="22" customWidth="1" min="35" max="35"/>
-    <col width="42" customWidth="1" min="36" max="36"/>
+    <col width="15" customWidth="1" min="34" max="34"/>
+    <col width="23" customWidth="1" min="35" max="35"/>
+    <col width="23" customWidth="1" min="36" max="36"/>
     <col width="15" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AGENCIA DE REGULACIÓN Y CONTROL DE LAS TELECOMUNICACIONES</t>
+          <t>INFORME DE CONTROL TÉCNICO</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>COORDINACIÓN ZONAL 6</t>
+          <t>No. IT-CZ06-R-2025-00XX</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ESTACIÓN DE COMPROBACIÓN TÉCNICA</t>
+          <t>AGENCIA DE REGULACIÓN Y CONTROL DE LAS TELECOMUNICACIONES</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>FORMULARIO DE CONTROL MENSUAL DE FM</t>
+          <t>COORDINACIÓN ZONAL 6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>CIUDAD:LOJA</t>
+          <t>ESTACIÓN DE COMPROBACIÓN TÉCNICA</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>PERIODO: JULIO</t>
+          <t>FORMULARIO DE CONTROL MENSUAL DE FM</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
+          <t>CIUDAD:LOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>PERIODO: JULIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
           <t>FECHA PRESENTACIÓN: 27/08/2025</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="10" ht="45" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>ESTACION</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>FRECUENCIA (MHz)</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="n">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Frecuencia (MHz)</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G10" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H10" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="I8" s="3" t="n">
+      <c r="I10" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="J10" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L10" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M10" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="N8" s="3" t="n">
+      <c r="N10" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="O8" s="3" t="n">
+      <c r="O10" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="P8" s="3" t="n">
+      <c r="P10" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q10" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R10" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="S8" s="3" t="n">
+      <c r="S10" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="T8" s="3" t="n">
+      <c r="T10" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="U8" s="3" t="n">
+      <c r="U10" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V10" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="W8" s="3" t="n">
+      <c r="W10" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="X8" s="3" t="n">
+      <c r="X10" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="Y8" s="3" t="n">
+      <c r="Y10" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="Z8" s="3" t="n">
+      <c r="Z10" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="AA8" s="3" t="n">
+      <c r="AA10" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="AB8" s="3" t="n">
+      <c r="AB10" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="AC8" s="3" t="n">
+      <c r="AC10" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="AD8" s="3" t="n">
+      <c r="AD10" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="AE8" s="3" t="n">
+      <c r="AE10" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="AF8" s="3" t="n">
+      <c r="AF10" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="AG8" s="3" t="n">
+      <c r="AG10" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="AH8" s="3" t="inlineStr">
+      <c r="AH10" s="3" t="inlineStr">
         <is>
           <t>Promedio
 (dBuV/m)</t>
         </is>
       </c>
-      <c r="AI8" s="3" t="inlineStr">
+      <c r="AI10" s="3" t="inlineStr">
         <is>
           <t>Ancho de Banda
 (KHz)</t>
         </is>
       </c>
-      <c r="AJ8" s="3" t="inlineStr">
+      <c r="AJ10" s="3" t="inlineStr">
         <is>
           <t>Medición Manual
 AB(KHz) o NIVEL
 (dBµV/m)</t>
         </is>
       </c>
-      <c r="AK8" s="4" t="inlineStr">
+      <c r="AK10" s="4" t="inlineStr">
         <is>
           <t>OBSERVACIONES</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>RADIO LUZ Y VIDA</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>88.09999999999999</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>100.73</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>100.21</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>99.67</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>98.14</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>99.37</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>99.87</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>99.3</v>
-      </c>
-      <c r="J9" s="6" t="n">
-        <v>98.27</v>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>103.04</v>
-      </c>
-      <c r="L9" s="6" t="n">
-        <v>104.62</v>
-      </c>
-      <c r="M9" s="6" t="n">
-        <v>103.65</v>
-      </c>
-      <c r="N9" s="6" t="n">
-        <v>104.35</v>
-      </c>
-      <c r="O9" s="6" t="n">
-        <v>99.56999999999999</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v>100.89</v>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v>99.98999999999999</v>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v>100.87</v>
-      </c>
-      <c r="S9" s="6" t="n">
-        <v>101.26</v>
-      </c>
-      <c r="T9" s="6" t="n">
-        <v>99.95999999999999</v>
-      </c>
-      <c r="U9" s="6" t="n">
-        <v>103.34</v>
-      </c>
-      <c r="V9" s="6" t="n">
-        <v>100.12</v>
-      </c>
-      <c r="W9" s="6" t="n">
-        <v>102.4</v>
-      </c>
-      <c r="X9" s="6" t="n">
-        <v>104.77</v>
-      </c>
-      <c r="Y9" s="6" t="n">
-        <v>104.69</v>
-      </c>
-      <c r="Z9" s="6" t="n">
-        <v>104.73</v>
-      </c>
-      <c r="AA9" s="6" t="n">
-        <v>104.57</v>
-      </c>
-      <c r="AB9" s="6" t="n">
-        <v>104.87</v>
-      </c>
-      <c r="AC9" s="6" t="n">
-        <v>104.49</v>
-      </c>
-      <c r="AD9" s="6" t="n">
-        <v>104.43</v>
-      </c>
-      <c r="AE9" s="6" t="n">
-        <v>104.15</v>
-      </c>
-      <c r="AF9" s="6" t="n">
-        <v>103.92</v>
-      </c>
-      <c r="AG9" s="6" t="n">
-        <v>103.78</v>
-      </c>
-      <c r="AH9" s="6" t="n">
-        <v>102.07</v>
-      </c>
-      <c r="AI9" s="6" t="n">
-        <v>261.08</v>
-      </c>
-      <c r="AJ9" s="6" t="inlineStr"/>
-      <c r="AK9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>RADIO CHASKI STEREO</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>102.64</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>102.54</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>100.03</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>98.68000000000001</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>98.81999999999999</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>99.39</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>98.18000000000001</v>
-      </c>
-      <c r="J10" s="6" t="n">
-        <v>98.54000000000001</v>
-      </c>
-      <c r="K10" s="6" t="n">
-        <v>103.48</v>
-      </c>
-      <c r="L10" s="6" t="n">
-        <v>106.07</v>
-      </c>
-      <c r="M10" s="6" t="n">
-        <v>103.61</v>
-      </c>
-      <c r="N10" s="6" t="n">
-        <v>102.12</v>
-      </c>
-      <c r="O10" s="6" t="n">
-        <v>98.91</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v>100.43</v>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v>99.17</v>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v>100.68</v>
-      </c>
-      <c r="S10" s="6" t="n">
-        <v>100.48</v>
-      </c>
-      <c r="T10" s="6" t="n">
-        <v>100.5</v>
-      </c>
-      <c r="U10" s="6" t="n">
-        <v>102.11</v>
-      </c>
-      <c r="V10" s="6" t="n">
-        <v>99.84</v>
-      </c>
-      <c r="W10" s="6" t="n">
-        <v>102.52</v>
-      </c>
-      <c r="X10" s="6" t="n">
-        <v>105.26</v>
-      </c>
-      <c r="Y10" s="6" t="n">
-        <v>105.26</v>
-      </c>
-      <c r="Z10" s="6" t="n">
-        <v>105.57</v>
-      </c>
-      <c r="AA10" s="6" t="n">
-        <v>105.29</v>
-      </c>
-      <c r="AB10" s="6" t="n">
-        <v>104.97</v>
-      </c>
-      <c r="AC10" s="6" t="n">
-        <v>104.81</v>
-      </c>
-      <c r="AD10" s="6" t="n">
-        <v>105.28</v>
-      </c>
-      <c r="AE10" s="6" t="n">
-        <v>105.18</v>
-      </c>
-      <c r="AF10" s="6" t="n">
-        <v>103.21</v>
-      </c>
-      <c r="AG10" s="6" t="n">
-        <v>102.45</v>
-      </c>
-      <c r="AH10" s="6" t="n">
-        <v>102.13</v>
-      </c>
-      <c r="AI10" s="6" t="n">
-        <v>400.33</v>
-      </c>
-      <c r="AJ10" s="6" t="inlineStr"/>
-      <c r="AK10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>LA HECHICERA 88.9 FM</t>
+          <t>RADIO LUZ Y VIDA</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>88.90000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>106.04</v>
+        <v>100.73</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>106.46</v>
+        <v>100.21</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>105.83</v>
+        <v>99.67</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>104.99</v>
+        <v>98.14</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>105.07</v>
+        <v>99.37</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>106.63</v>
+        <v>99.87</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>105.73</v>
+        <v>99.3</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>104.88</v>
+        <v>98.27</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>108.41</v>
+        <v>103.04</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>109.61</v>
+        <v>104.62</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>109.16</v>
+        <v>103.65</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>109.38</v>
+        <v>104.35</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>105.76</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>107.38</v>
+        <v>100.89</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>106.48</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>107.36</v>
+        <v>100.87</v>
       </c>
       <c r="S11" s="6" t="n">
-        <v>107.12</v>
+        <v>101.26</v>
       </c>
       <c r="T11" s="6" t="n">
-        <v>106.32</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>108.66</v>
+        <v>103.34</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>106.53</v>
+        <v>100.12</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>107.33</v>
+        <v>102.4</v>
       </c>
       <c r="X11" s="6" t="n">
-        <v>109.04</v>
+        <v>104.77</v>
       </c>
       <c r="Y11" s="6" t="n">
-        <v>109.38</v>
+        <v>104.69</v>
       </c>
       <c r="Z11" s="6" t="n">
-        <v>109.66</v>
+        <v>104.73</v>
       </c>
       <c r="AA11" s="6" t="n">
-        <v>109.31</v>
+        <v>104.57</v>
       </c>
       <c r="AB11" s="6" t="n">
-        <v>109.43</v>
+        <v>104.87</v>
       </c>
       <c r="AC11" s="6" t="n">
-        <v>106.55</v>
+        <v>104.49</v>
       </c>
       <c r="AD11" s="6" t="n">
-        <v>103.29</v>
+        <v>104.43</v>
       </c>
       <c r="AE11" s="6" t="n">
-        <v>103.96</v>
+        <v>104.15</v>
       </c>
       <c r="AF11" s="6" t="n">
-        <v>103.71</v>
+        <v>103.92</v>
       </c>
       <c r="AG11" s="6" t="n">
-        <v>104.82</v>
+        <v>103.78</v>
       </c>
       <c r="AH11" s="6" t="n">
-        <v>106.91</v>
+        <v>102.07</v>
       </c>
       <c r="AI11" s="6" t="n">
-        <v>485.39</v>
+        <v>261.08</v>
       </c>
       <c r="AJ11" s="6" t="inlineStr"/>
       <c r="AK11" s="7" t="inlineStr"/>
@@ -1162,110 +954,110 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>LATIDOS FM</t>
+          <t>RADIO CHASKI STEREO</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>89.3</v>
+        <v>88.5</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>105.66</v>
+        <v>102.64</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>107.57</v>
+        <v>102.54</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>107.51</v>
+        <v>100.03</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>106.14</v>
+        <v>98.68000000000001</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>106.72</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>108.46</v>
+        <v>99.39</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>107.72</v>
+        <v>98.18000000000001</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>106.02</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>110.23</v>
+        <v>103.48</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>111.67</v>
+        <v>106.07</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>111.27</v>
+        <v>103.61</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>111.21</v>
+        <v>102.12</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>108.06</v>
+        <v>98.91</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>109.28</v>
+        <v>100.43</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>107.56</v>
+        <v>99.17</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>109.17</v>
+        <v>100.68</v>
       </c>
       <c r="S12" s="6" t="n">
-        <v>108.37</v>
+        <v>100.48</v>
       </c>
       <c r="T12" s="6" t="n">
-        <v>106.98</v>
+        <v>100.5</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>110.21</v>
+        <v>102.11</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>108.43</v>
+        <v>99.84</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>109.52</v>
+        <v>102.52</v>
       </c>
       <c r="X12" s="6" t="n">
-        <v>111.48</v>
+        <v>105.26</v>
       </c>
       <c r="Y12" s="6" t="n">
-        <v>111.49</v>
+        <v>105.26</v>
       </c>
       <c r="Z12" s="6" t="n">
-        <v>111.6</v>
+        <v>105.57</v>
       </c>
       <c r="AA12" s="6" t="n">
-        <v>111.47</v>
+        <v>105.29</v>
       </c>
       <c r="AB12" s="6" t="n">
-        <v>111.8</v>
+        <v>104.97</v>
       </c>
       <c r="AC12" s="6" t="n">
-        <v>111.7</v>
+        <v>104.81</v>
       </c>
       <c r="AD12" s="6" t="n">
-        <v>111.21</v>
+        <v>105.28</v>
       </c>
       <c r="AE12" s="6" t="n">
-        <v>111.61</v>
+        <v>105.18</v>
       </c>
       <c r="AF12" s="6" t="n">
-        <v>111.38</v>
+        <v>103.21</v>
       </c>
       <c r="AG12" s="6" t="n">
-        <v>111.67</v>
+        <v>102.45</v>
       </c>
       <c r="AH12" s="6" t="n">
-        <v>109.46</v>
+        <v>102.13</v>
       </c>
       <c r="AI12" s="6" t="n">
-        <v>372.17</v>
+        <v>400.33</v>
       </c>
       <c r="AJ12" s="6" t="inlineStr"/>
       <c r="AK12" s="7" t="inlineStr"/>
@@ -1273,110 +1065,110 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>SEMILLAS DE AMOR</t>
+          <t>LA HECHICERA 88.9 FM</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>89.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>101.81</v>
+        <v>106.04</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>101.63</v>
+        <v>106.46</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>101.45</v>
+        <v>105.83</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>100.81</v>
+        <v>104.99</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>100.7</v>
+        <v>105.07</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>102.51</v>
+        <v>106.63</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>101.59</v>
+        <v>105.73</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>100.62</v>
+        <v>104.88</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>104.52</v>
+        <v>108.41</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>105.85</v>
+        <v>109.61</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>104.58</v>
+        <v>109.16</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>104.78</v>
+        <v>109.38</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>101.78</v>
+        <v>105.76</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>102.56</v>
+        <v>107.38</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>101.9</v>
+        <v>106.48</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>103.48</v>
+        <v>107.36</v>
       </c>
       <c r="S13" s="6" t="n">
-        <v>101.89</v>
+        <v>107.12</v>
       </c>
       <c r="T13" s="6" t="n">
-        <v>101.72</v>
+        <v>106.32</v>
       </c>
       <c r="U13" s="6" t="n">
+        <v>108.66</v>
+      </c>
+      <c r="V13" s="6" t="n">
+        <v>106.53</v>
+      </c>
+      <c r="W13" s="6" t="n">
+        <v>107.33</v>
+      </c>
+      <c r="X13" s="6" t="n">
+        <v>109.04</v>
+      </c>
+      <c r="Y13" s="6" t="n">
+        <v>109.38</v>
+      </c>
+      <c r="Z13" s="6" t="n">
+        <v>109.66</v>
+      </c>
+      <c r="AA13" s="6" t="n">
+        <v>109.31</v>
+      </c>
+      <c r="AB13" s="6" t="n">
+        <v>109.43</v>
+      </c>
+      <c r="AC13" s="6" t="n">
+        <v>106.55</v>
+      </c>
+      <c r="AD13" s="6" t="n">
+        <v>103.29</v>
+      </c>
+      <c r="AE13" s="6" t="n">
+        <v>103.96</v>
+      </c>
+      <c r="AF13" s="6" t="n">
         <v>103.71</v>
       </c>
-      <c r="V13" s="6" t="n">
-        <v>102.37</v>
-      </c>
-      <c r="W13" s="6" t="n">
-        <v>103.49</v>
-      </c>
-      <c r="X13" s="6" t="n">
-        <v>104.3</v>
-      </c>
-      <c r="Y13" s="6" t="n">
-        <v>104.96</v>
-      </c>
-      <c r="Z13" s="6" t="n">
-        <v>105.19</v>
-      </c>
-      <c r="AA13" s="6" t="n">
-        <v>104.56</v>
-      </c>
-      <c r="AB13" s="6" t="n">
-        <v>104.47</v>
-      </c>
-      <c r="AC13" s="6" t="n">
-        <v>104.6</v>
-      </c>
-      <c r="AD13" s="6" t="n">
+      <c r="AG13" s="6" t="n">
         <v>104.82</v>
       </c>
-      <c r="AE13" s="6" t="n">
-        <v>104.94</v>
-      </c>
-      <c r="AF13" s="6" t="n">
-        <v>104.81</v>
-      </c>
-      <c r="AG13" s="6" t="n">
-        <v>105.46</v>
-      </c>
       <c r="AH13" s="6" t="n">
-        <v>103.29</v>
+        <v>106.91</v>
       </c>
       <c r="AI13" s="6" t="n">
-        <v>388.41</v>
+        <v>485.39</v>
       </c>
       <c r="AJ13" s="6" t="inlineStr"/>
       <c r="AK13" s="7" t="inlineStr"/>
@@ -1384,110 +1176,110 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>RADIO MUNICIPAL</t>
+          <t>LATIDOS FM</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>90.09999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>81.18000000000001</v>
+        <v>105.66</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>81.19</v>
+        <v>107.57</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>82.01000000000001</v>
+        <v>107.51</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>81.12</v>
+        <v>106.14</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>82.13</v>
+        <v>106.72</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>83.72</v>
+        <v>108.46</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>83.38</v>
+        <v>107.72</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>81.62</v>
+        <v>106.02</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>82.89</v>
+        <v>110.23</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>84.88</v>
+        <v>111.67</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>86.56</v>
+        <v>111.27</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>85.36</v>
+        <v>111.21</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>83.48</v>
+        <v>108.06</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>83.94</v>
+        <v>109.28</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>83.54000000000001</v>
+        <v>107.56</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>84.23</v>
+        <v>109.17</v>
       </c>
       <c r="S14" s="6" t="n">
-        <v>83.56</v>
+        <v>108.37</v>
       </c>
       <c r="T14" s="6" t="n">
-        <v>81.23</v>
+        <v>106.98</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>83.98999999999999</v>
+        <v>110.21</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>83.53</v>
+        <v>108.43</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>84.95</v>
+        <v>109.52</v>
       </c>
       <c r="X14" s="6" t="n">
-        <v>86.98</v>
+        <v>111.48</v>
       </c>
       <c r="Y14" s="6" t="n">
-        <v>87.2</v>
+        <v>111.49</v>
       </c>
       <c r="Z14" s="6" t="n">
-        <v>85.37</v>
+        <v>111.6</v>
       </c>
       <c r="AA14" s="6" t="n">
-        <v>87.22</v>
+        <v>111.47</v>
       </c>
       <c r="AB14" s="6" t="n">
-        <v>87.34</v>
+        <v>111.8</v>
       </c>
       <c r="AC14" s="6" t="n">
-        <v>87.25</v>
+        <v>111.7</v>
       </c>
       <c r="AD14" s="6" t="n">
-        <v>86.56</v>
+        <v>111.21</v>
       </c>
       <c r="AE14" s="6" t="n">
-        <v>87.37</v>
+        <v>111.61</v>
       </c>
       <c r="AF14" s="6" t="n">
-        <v>86.66</v>
+        <v>111.38</v>
       </c>
       <c r="AG14" s="6" t="n">
-        <v>87.37</v>
+        <v>111.67</v>
       </c>
       <c r="AH14" s="6" t="n">
-        <v>84.44</v>
+        <v>109.46</v>
       </c>
       <c r="AI14" s="6" t="n">
-        <v>444.57</v>
+        <v>372.17</v>
       </c>
       <c r="AJ14" s="6" t="inlineStr"/>
       <c r="AK14" s="7" t="inlineStr"/>
@@ -1495,110 +1287,110 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>PUBLICA FM</t>
+          <t>SEMILLAS DE AMOR</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>90.5</v>
+        <v>89.7</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>86.59</v>
+        <v>101.81</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>86.89</v>
+        <v>101.63</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>87.52</v>
+        <v>101.45</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>87.31999999999999</v>
+        <v>100.81</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>86.2</v>
+        <v>100.7</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>87.95999999999999</v>
+        <v>102.51</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>86.48999999999999</v>
+        <v>101.59</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>85.58</v>
+        <v>100.62</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>87.87</v>
+        <v>104.52</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>89.41</v>
+        <v>105.85</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>88.76000000000001</v>
+        <v>104.58</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>89.28</v>
+        <v>104.78</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>86.09</v>
+        <v>101.78</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>87.20999999999999</v>
+        <v>102.56</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>86.89</v>
+        <v>101.9</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>87.84999999999999</v>
+        <v>103.48</v>
       </c>
       <c r="S15" s="6" t="n">
-        <v>87.41</v>
+        <v>101.89</v>
       </c>
       <c r="T15" s="6" t="n">
-        <v>87.53</v>
+        <v>101.72</v>
       </c>
       <c r="U15" s="6" t="n">
-        <v>88.09</v>
+        <v>103.71</v>
       </c>
       <c r="V15" s="6" t="n">
-        <v>86.47</v>
+        <v>102.37</v>
       </c>
       <c r="W15" s="6" t="n">
-        <v>88.48999999999999</v>
+        <v>103.49</v>
       </c>
       <c r="X15" s="6" t="n">
-        <v>90.56999999999999</v>
+        <v>104.3</v>
       </c>
       <c r="Y15" s="6" t="n">
-        <v>89.93000000000001</v>
+        <v>104.96</v>
       </c>
       <c r="Z15" s="6" t="n">
-        <v>89.88</v>
+        <v>105.19</v>
       </c>
       <c r="AA15" s="6" t="n">
-        <v>88.79000000000001</v>
+        <v>104.56</v>
       </c>
       <c r="AB15" s="6" t="n">
-        <v>88.62</v>
+        <v>104.47</v>
       </c>
       <c r="AC15" s="6" t="n">
-        <v>88.70999999999999</v>
+        <v>104.6</v>
       </c>
       <c r="AD15" s="6" t="n">
-        <v>88.98999999999999</v>
+        <v>104.82</v>
       </c>
       <c r="AE15" s="6" t="n">
-        <v>88.67</v>
+        <v>104.94</v>
       </c>
       <c r="AF15" s="6" t="n">
-        <v>88.98</v>
+        <v>104.81</v>
       </c>
       <c r="AG15" s="6" t="n">
-        <v>89.48</v>
+        <v>105.46</v>
       </c>
       <c r="AH15" s="6" t="n">
-        <v>88.02</v>
+        <v>103.29</v>
       </c>
       <c r="AI15" s="6" t="n">
-        <v>364.81</v>
+        <v>388.41</v>
       </c>
       <c r="AJ15" s="6" t="inlineStr"/>
       <c r="AK15" s="7" t="inlineStr"/>
@@ -1606,110 +1398,110 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>RADIOACTIVA</t>
+          <t>RADIO MUNICIPAL</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>90.90000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>100.28</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>100.14</v>
+        <v>81.19</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>101.43</v>
+        <v>82.01000000000001</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>101.02</v>
+        <v>81.12</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>101.46</v>
+        <v>82.13</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>102.67</v>
+        <v>83.72</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>102.67</v>
+        <v>83.38</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>101.48</v>
+        <v>81.62</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>103.87</v>
+        <v>82.89</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>106.03</v>
+        <v>84.88</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>105.71</v>
+        <v>86.56</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>105.21</v>
+        <v>85.36</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>102.61</v>
+        <v>83.48</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>103.77</v>
+        <v>83.94</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>102.62</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>103.92</v>
+        <v>84.23</v>
       </c>
       <c r="S16" s="6" t="n">
-        <v>103.29</v>
+        <v>83.56</v>
       </c>
       <c r="T16" s="6" t="n">
-        <v>101.73</v>
+        <v>81.23</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>103.4</v>
+        <v>83.98999999999999</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>102.62</v>
+        <v>83.53</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>104.21</v>
+        <v>84.95</v>
       </c>
       <c r="X16" s="6" t="n">
-        <v>105.88</v>
+        <v>86.98</v>
       </c>
       <c r="Y16" s="6" t="n">
-        <v>106.01</v>
+        <v>87.2</v>
       </c>
       <c r="Z16" s="6" t="n">
-        <v>106.29</v>
+        <v>85.37</v>
       </c>
       <c r="AA16" s="6" t="n">
-        <v>106.23</v>
+        <v>87.22</v>
       </c>
       <c r="AB16" s="6" t="n">
-        <v>106.02</v>
+        <v>87.34</v>
       </c>
       <c r="AC16" s="6" t="n">
-        <v>106.35</v>
+        <v>87.25</v>
       </c>
       <c r="AD16" s="6" t="n">
-        <v>106.12</v>
+        <v>86.56</v>
       </c>
       <c r="AE16" s="6" t="n">
-        <v>105.89</v>
+        <v>87.37</v>
       </c>
       <c r="AF16" s="6" t="n">
-        <v>106</v>
+        <v>86.66</v>
       </c>
       <c r="AG16" s="6" t="n">
-        <v>106.29</v>
+        <v>87.37</v>
       </c>
       <c r="AH16" s="6" t="n">
-        <v>103.91</v>
+        <v>84.44</v>
       </c>
       <c r="AI16" s="6" t="n">
-        <v>415.88</v>
+        <v>444.57</v>
       </c>
       <c r="AJ16" s="6" t="inlineStr"/>
       <c r="AK16" s="7" t="inlineStr"/>
@@ -1717,110 +1509,110 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>AMAZONAS FM</t>
+          <t>PUBLICA FM</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>92.09999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>97.68000000000001</v>
+        <v>86.59</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>100.49</v>
+        <v>86.89</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>101.6</v>
+        <v>87.52</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>101.09</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>102.04</v>
+        <v>86.2</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>103.13</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>103.39</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>101.37</v>
+        <v>85.58</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>104.29</v>
+        <v>87.87</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>106.73</v>
+        <v>89.41</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>105.76</v>
+        <v>88.76000000000001</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>104.57</v>
+        <v>89.28</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>102.94</v>
+        <v>86.09</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>103.63</v>
+        <v>87.20999999999999</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>102.59</v>
+        <v>86.89</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>103.54</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="S17" s="6" t="n">
-        <v>103.07</v>
+        <v>87.41</v>
       </c>
       <c r="T17" s="6" t="n">
-        <v>102.02</v>
+        <v>87.53</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>103.72</v>
+        <v>88.09</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>102.81</v>
+        <v>86.47</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>104.56</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="X17" s="6" t="n">
-        <v>106.92</v>
+        <v>90.56999999999999</v>
       </c>
       <c r="Y17" s="6" t="n">
-        <v>107.14</v>
+        <v>89.93000000000001</v>
       </c>
       <c r="Z17" s="6" t="n">
-        <v>107.26</v>
+        <v>89.88</v>
       </c>
       <c r="AA17" s="6" t="n">
-        <v>107.2</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="AB17" s="6" t="n">
-        <v>107.29</v>
+        <v>88.62</v>
       </c>
       <c r="AC17" s="6" t="n">
-        <v>107.32</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="AD17" s="6" t="n">
-        <v>106.9</v>
+        <v>88.98999999999999</v>
       </c>
       <c r="AE17" s="6" t="n">
-        <v>106.57</v>
+        <v>88.67</v>
       </c>
       <c r="AF17" s="6" t="n">
-        <v>106.03</v>
+        <v>88.98</v>
       </c>
       <c r="AG17" s="6" t="n">
-        <v>105.72</v>
+        <v>89.48</v>
       </c>
       <c r="AH17" s="6" t="n">
-        <v>104.17</v>
+        <v>88.02</v>
       </c>
       <c r="AI17" s="6" t="n">
-        <v>418.76</v>
+        <v>364.81</v>
       </c>
       <c r="AJ17" s="6" t="inlineStr"/>
       <c r="AK17" s="7" t="inlineStr"/>
@@ -1828,110 +1620,110 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>WG MILENIO</t>
+          <t>RADIOACTIVA</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>92.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>95.48999999999999</v>
+        <v>100.28</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>95.12</v>
+        <v>100.14</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>94.48999999999999</v>
+        <v>101.43</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>94.18000000000001</v>
+        <v>101.02</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>94.04000000000001</v>
+        <v>101.46</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>94.16</v>
+        <v>102.67</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>93.19</v>
+        <v>102.67</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>94.19</v>
+        <v>101.48</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>95.20999999999999</v>
+        <v>103.87</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>96.98</v>
+        <v>106.03</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>95.88</v>
+        <v>105.71</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>91.90000000000001</v>
+        <v>105.21</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>93.38</v>
+        <v>102.61</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>92.69</v>
+        <v>103.77</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>93.16</v>
+        <v>102.62</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>93.67</v>
+        <v>103.92</v>
       </c>
       <c r="S18" s="6" t="n">
-        <v>93.63</v>
+        <v>103.29</v>
       </c>
       <c r="T18" s="6" t="n">
-        <v>94.48</v>
+        <v>101.73</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>93.19</v>
+        <v>103.4</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>94.34</v>
+        <v>102.62</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>96.26000000000001</v>
+        <v>104.21</v>
       </c>
       <c r="X18" s="6" t="n">
-        <v>98.88</v>
+        <v>105.88</v>
       </c>
       <c r="Y18" s="6" t="n">
-        <v>98.8</v>
+        <v>106.01</v>
       </c>
       <c r="Z18" s="6" t="n">
-        <v>98.48</v>
+        <v>106.29</v>
       </c>
       <c r="AA18" s="6" t="n">
-        <v>98.22</v>
+        <v>106.23</v>
       </c>
       <c r="AB18" s="6" t="n">
-        <v>98.26000000000001</v>
+        <v>106.02</v>
       </c>
       <c r="AC18" s="6" t="n">
-        <v>98.23</v>
+        <v>106.35</v>
       </c>
       <c r="AD18" s="6" t="n">
-        <v>98.13</v>
+        <v>106.12</v>
       </c>
       <c r="AE18" s="6" t="n">
-        <v>98.22</v>
+        <v>105.89</v>
       </c>
       <c r="AF18" s="6" t="n">
-        <v>96.83</v>
+        <v>106</v>
       </c>
       <c r="AG18" s="6" t="n">
-        <v>94.88</v>
+        <v>106.29</v>
       </c>
       <c r="AH18" s="6" t="n">
-        <v>95.44</v>
+        <v>103.91</v>
       </c>
       <c r="AI18" s="6" t="n">
-        <v>400.73</v>
+        <v>415.88</v>
       </c>
       <c r="AJ18" s="6" t="inlineStr"/>
       <c r="AK18" s="7" t="inlineStr"/>
@@ -1939,110 +1731,110 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>RADIO VIGIA FM</t>
+          <t>AMAZONAS FM</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>93.3</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>93.22</v>
+        <v>97.68000000000001</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>93.84</v>
+        <v>100.49</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>94.18000000000001</v>
+        <v>101.6</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>93.56999999999999</v>
+        <v>101.09</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>94.23</v>
+        <v>102.04</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>94.87</v>
+        <v>103.13</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>94.42</v>
+        <v>103.39</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>93.37</v>
+        <v>101.37</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>97.06999999999999</v>
+        <v>104.29</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>99.90000000000001</v>
+        <v>106.73</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>97.95999999999999</v>
+        <v>105.76</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>95.68000000000001</v>
+        <v>104.57</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>94.81</v>
+        <v>102.94</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>95.19</v>
+        <v>103.63</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>94.36</v>
+        <v>102.59</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>95.29000000000001</v>
+        <v>103.54</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>94.77</v>
+        <v>103.07</v>
       </c>
       <c r="T19" s="6" t="n">
-        <v>94.45</v>
+        <v>102.02</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>95.59</v>
+        <v>103.72</v>
       </c>
       <c r="V19" s="6" t="n">
-        <v>94.97</v>
+        <v>102.81</v>
       </c>
       <c r="W19" s="6" t="n">
-        <v>97.58</v>
+        <v>104.56</v>
       </c>
       <c r="X19" s="6" t="n">
-        <v>100.17</v>
+        <v>106.92</v>
       </c>
       <c r="Y19" s="6" t="n">
-        <v>100.55</v>
+        <v>107.14</v>
       </c>
       <c r="Z19" s="6" t="n">
-        <v>100.31</v>
+        <v>107.26</v>
       </c>
       <c r="AA19" s="6" t="n">
-        <v>99.81999999999999</v>
+        <v>107.2</v>
       </c>
       <c r="AB19" s="6" t="n">
-        <v>100.36</v>
+        <v>107.29</v>
       </c>
       <c r="AC19" s="6" t="n">
-        <v>100.22</v>
+        <v>107.32</v>
       </c>
       <c r="AD19" s="6" t="n">
-        <v>99.83</v>
+        <v>106.9</v>
       </c>
       <c r="AE19" s="6" t="n">
-        <v>99.89</v>
+        <v>106.57</v>
       </c>
       <c r="AF19" s="6" t="n">
-        <v>98.43000000000001</v>
+        <v>106.03</v>
       </c>
       <c r="AG19" s="6" t="n">
-        <v>96.98999999999999</v>
+        <v>105.72</v>
       </c>
       <c r="AH19" s="6" t="n">
-        <v>96.64</v>
+        <v>104.17</v>
       </c>
       <c r="AI19" s="6" t="n">
-        <v>406.58</v>
+        <v>418.76</v>
       </c>
       <c r="AJ19" s="6" t="inlineStr"/>
       <c r="AK19" s="7" t="inlineStr"/>
@@ -2050,110 +1842,110 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>BOQUERON FM</t>
+          <t>WG MILENIO</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>93.7</v>
+        <v>92.5</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>102.88</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>103.28</v>
+        <v>95.12</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>104.64</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>104.51</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>104.54</v>
+        <v>94.04000000000001</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>105.73</v>
+        <v>94.16</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>105.16</v>
+        <v>93.19</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>104.57</v>
+        <v>94.19</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>106.33</v>
+        <v>95.20999999999999</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>108.18</v>
+        <v>96.98</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>107.34</v>
+        <v>95.88</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>106.42</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>105.42</v>
+        <v>93.38</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>105.52</v>
+        <v>92.69</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>105.13</v>
+        <v>93.16</v>
       </c>
       <c r="R20" s="6" t="n">
-        <v>106.53</v>
+        <v>93.67</v>
       </c>
       <c r="S20" s="6" t="n">
-        <v>106.49</v>
+        <v>93.63</v>
       </c>
       <c r="T20" s="6" t="n">
-        <v>105.56</v>
+        <v>94.48</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>106.56</v>
+        <v>93.19</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>105.78</v>
+        <v>94.34</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>100.33</v>
+        <v>96.26000000000001</v>
       </c>
       <c r="X20" s="6" t="n">
+        <v>98.88</v>
+      </c>
+      <c r="Y20" s="6" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="Z20" s="6" t="n">
+        <v>98.48</v>
+      </c>
+      <c r="AA20" s="6" t="n">
+        <v>98.22</v>
+      </c>
+      <c r="AB20" s="6" t="n">
+        <v>98.26000000000001</v>
+      </c>
+      <c r="AC20" s="6" t="n">
+        <v>98.23</v>
+      </c>
+      <c r="AD20" s="6" t="n">
+        <v>98.13</v>
+      </c>
+      <c r="AE20" s="6" t="n">
+        <v>98.22</v>
+      </c>
+      <c r="AF20" s="6" t="n">
+        <v>96.83</v>
+      </c>
+      <c r="AG20" s="6" t="n">
         <v>94.88</v>
       </c>
-      <c r="Y20" s="6" t="n">
-        <v>102.51</v>
-      </c>
-      <c r="Z20" s="6" t="n">
-        <v>109.74</v>
-      </c>
-      <c r="AA20" s="6" t="n">
-        <v>109.78</v>
-      </c>
-      <c r="AB20" s="6" t="n">
-        <v>109.71</v>
-      </c>
-      <c r="AC20" s="6" t="n">
-        <v>109.88</v>
-      </c>
-      <c r="AD20" s="6" t="n">
-        <v>108.75</v>
-      </c>
-      <c r="AE20" s="6" t="n">
-        <v>108.75</v>
-      </c>
-      <c r="AF20" s="6" t="n">
-        <v>109.07</v>
-      </c>
-      <c r="AG20" s="6" t="n">
-        <v>109.51</v>
-      </c>
       <c r="AH20" s="6" t="n">
-        <v>105.92</v>
+        <v>95.44</v>
       </c>
       <c r="AI20" s="6" t="n">
-        <v>387.36</v>
+        <v>400.73</v>
       </c>
       <c r="AJ20" s="6" t="inlineStr"/>
       <c r="AK20" s="7" t="inlineStr"/>
@@ -2161,110 +1953,110 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>ONDAS DE ESPERANZA</t>
+          <t>RADIO VIGIA FM</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>94.09999999999999</v>
+        <v>93.3</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>101.84</v>
+        <v>93.22</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>102.64</v>
+        <v>93.84</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>102.76</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>102.78</v>
+        <v>93.56999999999999</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>102.92</v>
+        <v>94.23</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>103.32</v>
+        <v>94.87</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>103.29</v>
+        <v>94.42</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>102.96</v>
+        <v>93.37</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>103.86</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>105.12</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>104.86</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>104.06</v>
+        <v>95.68000000000001</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>100.32</v>
+        <v>94.81</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>100.72</v>
+        <v>95.19</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>100.56</v>
+        <v>94.36</v>
       </c>
       <c r="R21" s="6" t="n">
-        <v>100.99</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="S21" s="6" t="n">
-        <v>101.06</v>
+        <v>94.77</v>
       </c>
       <c r="T21" s="6" t="n">
-        <v>100.81</v>
+        <v>94.45</v>
       </c>
       <c r="U21" s="6" t="n">
-        <v>102.33</v>
+        <v>95.59</v>
       </c>
       <c r="V21" s="6" t="n">
-        <v>101.98</v>
+        <v>94.97</v>
       </c>
       <c r="W21" s="6" t="n">
-        <v>103.28</v>
+        <v>97.58</v>
       </c>
       <c r="X21" s="6" t="n">
-        <v>103.92</v>
+        <v>100.17</v>
       </c>
       <c r="Y21" s="6" t="n">
-        <v>104.17</v>
+        <v>100.55</v>
       </c>
       <c r="Z21" s="6" t="n">
-        <v>103.63</v>
+        <v>100.31</v>
       </c>
       <c r="AA21" s="6" t="n">
-        <v>104.24</v>
+        <v>99.81999999999999</v>
       </c>
       <c r="AB21" s="6" t="n">
-        <v>104.07</v>
+        <v>100.36</v>
       </c>
       <c r="AC21" s="6" t="n">
-        <v>103.92</v>
+        <v>100.22</v>
       </c>
       <c r="AD21" s="6" t="n">
-        <v>103.71</v>
+        <v>99.83</v>
       </c>
       <c r="AE21" s="6" t="n">
-        <v>103.58</v>
+        <v>99.89</v>
       </c>
       <c r="AF21" s="6" t="n">
-        <v>103.91</v>
+        <v>98.43000000000001</v>
       </c>
       <c r="AG21" s="6" t="n">
-        <v>104.5</v>
+        <v>96.98999999999999</v>
       </c>
       <c r="AH21" s="6" t="n">
-        <v>102.97</v>
+        <v>96.64</v>
       </c>
       <c r="AI21" s="6" t="n">
-        <v>419.3</v>
+        <v>406.58</v>
       </c>
       <c r="AJ21" s="6" t="inlineStr"/>
       <c r="AK21" s="7" t="inlineStr"/>
@@ -2272,110 +2064,110 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>RADIO BUENISIMA FM 94.5</t>
+          <t>BOQUERON FM</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>94.5</v>
+        <v>93.7</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>101.41</v>
+        <v>102.88</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>101.64</v>
+        <v>103.28</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>102.16</v>
+        <v>104.64</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>102.58</v>
+        <v>104.51</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>102.74</v>
+        <v>104.54</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>103.05</v>
+        <v>105.73</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>103.12</v>
+        <v>105.16</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>103.12</v>
+        <v>104.57</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>103.72</v>
+        <v>106.33</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>106.07</v>
+        <v>108.18</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>105.31</v>
+        <v>107.34</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>103.62</v>
+        <v>106.42</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>102.91</v>
+        <v>105.42</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>103.32</v>
+        <v>105.52</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>103.08</v>
+        <v>105.13</v>
       </c>
       <c r="R22" s="6" t="n">
-        <v>103.9</v>
+        <v>106.53</v>
       </c>
       <c r="S22" s="6" t="n">
-        <v>103.98</v>
+        <v>106.49</v>
       </c>
       <c r="T22" s="6" t="n">
-        <v>103.54</v>
+        <v>105.56</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>104.47</v>
+        <v>106.56</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>104.17</v>
+        <v>105.78</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>104.95</v>
+        <v>100.33</v>
       </c>
       <c r="X22" s="6" t="n">
-        <v>105.45</v>
+        <v>94.88</v>
       </c>
       <c r="Y22" s="6" t="n">
-        <v>105.52</v>
+        <v>102.51</v>
       </c>
       <c r="Z22" s="6" t="n">
-        <v>105.91</v>
+        <v>109.74</v>
       </c>
       <c r="AA22" s="6" t="n">
-        <v>105.18</v>
+        <v>109.78</v>
       </c>
       <c r="AB22" s="6" t="n">
-        <v>105.34</v>
+        <v>109.71</v>
       </c>
       <c r="AC22" s="6" t="n">
-        <v>105.46</v>
+        <v>109.88</v>
       </c>
       <c r="AD22" s="6" t="n">
-        <v>105.41</v>
+        <v>108.75</v>
       </c>
       <c r="AE22" s="6" t="n">
-        <v>105.26</v>
+        <v>108.75</v>
       </c>
       <c r="AF22" s="6" t="n">
-        <v>105.79</v>
+        <v>109.07</v>
       </c>
       <c r="AG22" s="6" t="n">
-        <v>106.08</v>
+        <v>109.51</v>
       </c>
       <c r="AH22" s="6" t="n">
-        <v>104.14</v>
+        <v>105.92</v>
       </c>
       <c r="AI22" s="6" t="n">
-        <v>408.72</v>
+        <v>387.36</v>
       </c>
       <c r="AJ22" s="6" t="inlineStr"/>
       <c r="AK22" s="7" t="inlineStr"/>
@@ -2383,110 +2175,110 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>MISION SAN ANTONIO</t>
+          <t>ONDAS DE ESPERANZA</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>94.90000000000001</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>89.14</v>
+        <v>101.84</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>88.89</v>
+        <v>102.64</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>89.68000000000001</v>
+        <v>102.76</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>89.27</v>
+        <v>102.78</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>89.5</v>
+        <v>102.92</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>90.97</v>
+        <v>103.32</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>89.84</v>
+        <v>103.29</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>89.01000000000001</v>
+        <v>102.96</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>92.48</v>
+        <v>103.86</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>95.73999999999999</v>
+        <v>105.12</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>93.39</v>
+        <v>104.86</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>91.67</v>
+        <v>104.06</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>90.26000000000001</v>
+        <v>100.32</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>90.45999999999999</v>
+        <v>100.72</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>90.36</v>
+        <v>100.56</v>
       </c>
       <c r="R23" s="6" t="n">
-        <v>91.18000000000001</v>
+        <v>100.99</v>
       </c>
       <c r="S23" s="6" t="n">
-        <v>90.94</v>
+        <v>101.06</v>
       </c>
       <c r="T23" s="6" t="n">
-        <v>90.26000000000001</v>
+        <v>100.81</v>
       </c>
       <c r="U23" s="6" t="n">
-        <v>91.06999999999999</v>
+        <v>102.33</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>90.27</v>
+        <v>101.98</v>
       </c>
       <c r="W23" s="6" t="n">
-        <v>93.14</v>
+        <v>103.28</v>
       </c>
       <c r="X23" s="6" t="n">
-        <v>95.72</v>
+        <v>103.92</v>
       </c>
       <c r="Y23" s="6" t="n">
-        <v>95.84</v>
+        <v>104.17</v>
       </c>
       <c r="Z23" s="6" t="n">
-        <v>95.25</v>
+        <v>103.63</v>
       </c>
       <c r="AA23" s="6" t="n">
-        <v>94.88</v>
+        <v>104.24</v>
       </c>
       <c r="AB23" s="6" t="n">
-        <v>94.68000000000001</v>
+        <v>104.07</v>
       </c>
       <c r="AC23" s="6" t="n">
-        <v>95.34999999999999</v>
+        <v>103.92</v>
       </c>
       <c r="AD23" s="6" t="n">
-        <v>94.42</v>
+        <v>103.71</v>
       </c>
       <c r="AE23" s="6" t="n">
-        <v>95.36</v>
+        <v>103.58</v>
       </c>
       <c r="AF23" s="6" t="n">
-        <v>93.76000000000001</v>
+        <v>103.91</v>
       </c>
       <c r="AG23" s="6" t="n">
-        <v>92.5</v>
+        <v>104.5</v>
       </c>
       <c r="AH23" s="6" t="n">
-        <v>92.11</v>
+        <v>102.97</v>
       </c>
       <c r="AI23" s="6" t="n">
-        <v>439.51</v>
+        <v>419.3</v>
       </c>
       <c r="AJ23" s="6" t="inlineStr"/>
       <c r="AK23" s="7" t="inlineStr"/>
@@ -2494,110 +2286,110 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>SONICA PODER</t>
+          <t>RADIO BUENISIMA FM 94.5</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>95.3</v>
+        <v>94.5</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>103.11</v>
+        <v>101.41</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>102.57</v>
+        <v>101.64</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>102.42</v>
+        <v>102.16</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>102.64</v>
+        <v>102.58</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>102.87</v>
+        <v>102.74</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>103.36</v>
+        <v>103.05</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>102.36</v>
+        <v>103.12</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>102.6</v>
+        <v>103.12</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>103.14</v>
+        <v>103.72</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>103.19</v>
+        <v>106.07</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>103.63</v>
+        <v>105.31</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>103.47</v>
+        <v>103.62</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>103.23</v>
+        <v>102.91</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>102.84</v>
+        <v>103.32</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>102.82</v>
+        <v>103.08</v>
       </c>
       <c r="R24" s="6" t="n">
-        <v>103.34</v>
+        <v>103.9</v>
       </c>
       <c r="S24" s="6" t="n">
-        <v>103.46</v>
+        <v>103.98</v>
       </c>
       <c r="T24" s="6" t="n">
-        <v>102.74</v>
+        <v>103.54</v>
       </c>
       <c r="U24" s="6" t="n">
-        <v>103.27</v>
+        <v>104.47</v>
       </c>
       <c r="V24" s="6" t="n">
-        <v>103.25</v>
+        <v>104.17</v>
       </c>
       <c r="W24" s="6" t="n">
-        <v>103.32</v>
+        <v>104.95</v>
       </c>
       <c r="X24" s="6" t="n">
-        <v>103.94</v>
+        <v>105.45</v>
       </c>
       <c r="Y24" s="6" t="n">
-        <v>103.06</v>
+        <v>105.52</v>
       </c>
       <c r="Z24" s="6" t="n">
-        <v>103.75</v>
+        <v>105.91</v>
       </c>
       <c r="AA24" s="6" t="n">
-        <v>103.18</v>
+        <v>105.18</v>
       </c>
       <c r="AB24" s="6" t="n">
-        <v>103.56</v>
+        <v>105.34</v>
       </c>
       <c r="AC24" s="6" t="n">
-        <v>103.35</v>
+        <v>105.46</v>
       </c>
       <c r="AD24" s="6" t="n">
-        <v>103.36</v>
+        <v>105.41</v>
       </c>
       <c r="AE24" s="6" t="n">
-        <v>103.43</v>
+        <v>105.26</v>
       </c>
       <c r="AF24" s="6" t="n">
-        <v>104.72</v>
+        <v>105.79</v>
       </c>
       <c r="AG24" s="6" t="n">
-        <v>105.59</v>
+        <v>106.08</v>
       </c>
       <c r="AH24" s="6" t="n">
-        <v>103.28</v>
+        <v>104.14</v>
       </c>
       <c r="AI24" s="6" t="n">
-        <v>412.36</v>
+        <v>408.72</v>
       </c>
       <c r="AJ24" s="6" t="inlineStr"/>
       <c r="AK24" s="7" t="inlineStr"/>
@@ -2605,110 +2397,110 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>LA RADIO DE LA ASAMBLEA NACIONA</t>
+          <t>MISION SAN ANTONIO</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>95.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>91.16</v>
+        <v>89.14</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>91.37</v>
+        <v>88.89</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>92.98999999999999</v>
+        <v>89.68000000000001</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>93.13</v>
+        <v>89.27</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>93.72</v>
+        <v>89.5</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>94.86</v>
+        <v>90.97</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>93.77</v>
+        <v>89.84</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>93.08</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>96.44</v>
+        <v>92.48</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>99.08</v>
+        <v>95.73999999999999</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>97.33</v>
+        <v>93.39</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>95.83</v>
+        <v>91.67</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>94.39</v>
+        <v>90.26000000000001</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>94.2</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>93.86</v>
+        <v>90.36</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>94.94</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="S25" s="6" t="n">
-        <v>94.95</v>
+        <v>90.94</v>
       </c>
       <c r="T25" s="6" t="n">
-        <v>93.73999999999999</v>
+        <v>90.26000000000001</v>
       </c>
       <c r="U25" s="6" t="n">
-        <v>95.06999999999999</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>94.11</v>
+        <v>90.27</v>
       </c>
       <c r="W25" s="6" t="n">
-        <v>96.31999999999999</v>
+        <v>93.14</v>
       </c>
       <c r="X25" s="6" t="n">
-        <v>99.06999999999999</v>
+        <v>95.72</v>
       </c>
       <c r="Y25" s="6" t="n">
-        <v>99.26000000000001</v>
+        <v>95.84</v>
       </c>
       <c r="Z25" s="6" t="n">
-        <v>99.39</v>
+        <v>95.25</v>
       </c>
       <c r="AA25" s="6" t="n">
-        <v>99.06999999999999</v>
+        <v>94.88</v>
       </c>
       <c r="AB25" s="6" t="n">
-        <v>99.31</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="AC25" s="6" t="n">
-        <v>99.2</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="AD25" s="6" t="n">
-        <v>99.47</v>
+        <v>94.42</v>
       </c>
       <c r="AE25" s="6" t="n">
-        <v>98.97</v>
+        <v>95.36</v>
       </c>
       <c r="AF25" s="6" t="n">
-        <v>97.64</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="AG25" s="6" t="n">
-        <v>96.20999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="AH25" s="6" t="n">
-        <v>95.87</v>
+        <v>92.11</v>
       </c>
       <c r="AI25" s="6" t="n">
-        <v>398.86</v>
+        <v>439.51</v>
       </c>
       <c r="AJ25" s="6" t="inlineStr"/>
       <c r="AK25" s="7" t="inlineStr"/>
@@ -2716,110 +2508,110 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>ZAPOTILLO FM</t>
+          <t>SONICA PODER</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>96.09999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>52.79</v>
+        <v>103.11</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>53.24</v>
+        <v>102.57</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>53.39</v>
+        <v>102.42</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>52.91</v>
+        <v>102.64</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>52.24</v>
+        <v>102.87</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>54.92</v>
+        <v>103.36</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>54.52</v>
+        <v>102.36</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>53.58</v>
+        <v>102.6</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>54.41</v>
+        <v>103.14</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>75.14</v>
+        <v>103.19</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>97.26000000000001</v>
+        <v>103.63</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>95.93000000000001</v>
+        <v>103.47</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>95.95</v>
+        <v>103.23</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>71.93000000000001</v>
+        <v>102.84</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>72.12</v>
+        <v>102.82</v>
       </c>
       <c r="R26" s="6" t="n">
-        <v>84.53</v>
+        <v>103.34</v>
       </c>
       <c r="S26" s="6" t="n">
-        <v>96.76000000000001</v>
+        <v>103.46</v>
       </c>
       <c r="T26" s="6" t="n">
-        <v>96.43000000000001</v>
+        <v>102.74</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>96.91</v>
+        <v>103.27</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>97.02</v>
+        <v>103.25</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>97.68000000000001</v>
+        <v>103.32</v>
       </c>
       <c r="X26" s="6" t="n">
-        <v>98.02</v>
+        <v>103.94</v>
       </c>
       <c r="Y26" s="6" t="n">
-        <v>97.98999999999999</v>
+        <v>103.06</v>
       </c>
       <c r="Z26" s="6" t="n">
-        <v>98.39</v>
+        <v>103.75</v>
       </c>
       <c r="AA26" s="6" t="n">
-        <v>97.87</v>
+        <v>103.18</v>
       </c>
       <c r="AB26" s="6" t="n">
-        <v>97.86</v>
+        <v>103.56</v>
       </c>
       <c r="AC26" s="6" t="n">
-        <v>97.76000000000001</v>
+        <v>103.35</v>
       </c>
       <c r="AD26" s="6" t="n">
-        <v>97.93000000000001</v>
+        <v>103.36</v>
       </c>
       <c r="AE26" s="6" t="n">
-        <v>98.01000000000001</v>
+        <v>103.43</v>
       </c>
       <c r="AF26" s="6" t="n">
-        <v>98.28</v>
+        <v>104.72</v>
       </c>
       <c r="AG26" s="6" t="n">
-        <v>98.55</v>
+        <v>105.59</v>
       </c>
       <c r="AH26" s="6" t="n">
-        <v>81.95</v>
+        <v>103.28</v>
       </c>
       <c r="AI26" s="6" t="n">
-        <v>546.02</v>
+        <v>412.36</v>
       </c>
       <c r="AJ26" s="6" t="inlineStr"/>
       <c r="AK26" s="7" t="inlineStr"/>
@@ -2827,110 +2619,110 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>CAÑAVERAL FM</t>
+          <t>LA RADIO DE LA ASAMBLEA NACIONA</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>96.5</v>
+        <v>95.7</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>95.69</v>
+        <v>91.16</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>95.77</v>
+        <v>91.37</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>96.58</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>96.54000000000001</v>
+        <v>93.13</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>96.73</v>
+        <v>93.72</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>97.01000000000001</v>
+        <v>94.86</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>96.31</v>
+        <v>93.77</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>96.36</v>
+        <v>93.08</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>98.44</v>
+        <v>96.44</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>101.3</v>
+        <v>99.08</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>99.37</v>
+        <v>97.33</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>97.51000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>96.90000000000001</v>
+        <v>94.39</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>97.31999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>96.98</v>
+        <v>93.86</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>97.51000000000001</v>
+        <v>94.94</v>
       </c>
       <c r="S27" s="6" t="n">
-        <v>97.73</v>
+        <v>94.95</v>
       </c>
       <c r="T27" s="6" t="n">
-        <v>96.93000000000001</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="U27" s="6" t="n">
-        <v>97.73</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="V27" s="6" t="n">
-        <v>96.91</v>
+        <v>94.11</v>
       </c>
       <c r="W27" s="6" t="n">
-        <v>98.98999999999999</v>
+        <v>96.31999999999999</v>
       </c>
       <c r="X27" s="6" t="n">
-        <v>101.66</v>
+        <v>99.06999999999999</v>
       </c>
       <c r="Y27" s="6" t="n">
-        <v>101.8</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="Z27" s="6" t="n">
-        <v>101.18</v>
+        <v>99.39</v>
       </c>
       <c r="AA27" s="6" t="n">
-        <v>101.54</v>
+        <v>99.06999999999999</v>
       </c>
       <c r="AB27" s="6" t="n">
-        <v>101.34</v>
+        <v>99.31</v>
       </c>
       <c r="AC27" s="6" t="n">
-        <v>101.57</v>
+        <v>99.2</v>
       </c>
       <c r="AD27" s="6" t="n">
-        <v>101.68</v>
+        <v>99.47</v>
       </c>
       <c r="AE27" s="6" t="n">
-        <v>101.66</v>
+        <v>98.97</v>
       </c>
       <c r="AF27" s="6" t="n">
-        <v>100.26</v>
+        <v>97.64</v>
       </c>
       <c r="AG27" s="6" t="n">
-        <v>98.88</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="AH27" s="6" t="n">
-        <v>98.59</v>
+        <v>95.87</v>
       </c>
       <c r="AI27" s="6" t="n">
-        <v>391.54</v>
+        <v>398.86</v>
       </c>
       <c r="AJ27" s="6" t="inlineStr"/>
       <c r="AK27" s="7" t="inlineStr"/>
@@ -2938,110 +2730,110 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>RADIO CLIP</t>
+          <t>ZAPOTILLO FM</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>96.90000000000001</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>106.13</v>
+        <v>52.79</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>105.07</v>
+        <v>53.24</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>105.17</v>
+        <v>53.39</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>104.98</v>
+        <v>52.91</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>105.09</v>
+        <v>52.24</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>105.69</v>
+        <v>54.92</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>105.12</v>
+        <v>54.52</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>104.79</v>
+        <v>53.58</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>107.12</v>
+        <v>54.41</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>108.92</v>
+        <v>75.14</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>107.68</v>
+        <v>97.26000000000001</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>106.08</v>
+        <v>95.93000000000001</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>105.24</v>
+        <v>95.95</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>105.14</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>105.33</v>
+        <v>72.12</v>
       </c>
       <c r="R28" s="6" t="n">
-        <v>105.77</v>
+        <v>84.53</v>
       </c>
       <c r="S28" s="6" t="n">
-        <v>105.61</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="T28" s="6" t="n">
-        <v>105.26</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="U28" s="6" t="n">
-        <v>105.96</v>
+        <v>96.91</v>
       </c>
       <c r="V28" s="6" t="n">
-        <v>105.32</v>
+        <v>97.02</v>
       </c>
       <c r="W28" s="6" t="n">
-        <v>107.3</v>
+        <v>97.68000000000001</v>
       </c>
       <c r="X28" s="6" t="n">
-        <v>108.94</v>
+        <v>98.02</v>
       </c>
       <c r="Y28" s="6" t="n">
-        <v>108.86</v>
+        <v>97.98999999999999</v>
       </c>
       <c r="Z28" s="6" t="n">
-        <v>109.09</v>
+        <v>98.39</v>
       </c>
       <c r="AA28" s="6" t="n">
-        <v>108.56</v>
+        <v>97.87</v>
       </c>
       <c r="AB28" s="6" t="n">
-        <v>108.91</v>
+        <v>97.86</v>
       </c>
       <c r="AC28" s="6" t="n">
-        <v>108.65</v>
+        <v>97.76000000000001</v>
       </c>
       <c r="AD28" s="6" t="n">
-        <v>108.59</v>
+        <v>97.93000000000001</v>
       </c>
       <c r="AE28" s="6" t="n">
-        <v>108.64</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="AF28" s="6" t="n">
-        <v>107.97</v>
+        <v>98.28</v>
       </c>
       <c r="AG28" s="6" t="n">
-        <v>106.94</v>
+        <v>98.55</v>
       </c>
       <c r="AH28" s="6" t="n">
-        <v>106.71</v>
+        <v>81.95</v>
       </c>
       <c r="AI28" s="6" t="n">
-        <v>476.01</v>
+        <v>546.02</v>
       </c>
       <c r="AJ28" s="6" t="inlineStr"/>
       <c r="AK28" s="7" t="inlineStr"/>
@@ -3049,110 +2841,110 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>RADIO CORPORACIÓN 97.3 FM</t>
+          <t>CAÑAVERAL FM</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>97.3</v>
+        <v>96.5</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>50.96</v>
+        <v>95.69</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>51.09</v>
+        <v>95.77</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>51.49</v>
+        <v>96.58</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>51.17</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>50.6</v>
+        <v>96.73</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>53.72</v>
+        <v>97.01000000000001</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>54.82</v>
+        <v>96.31</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>51.84</v>
+        <v>96.36</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>51.62</v>
+        <v>98.44</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>50.18</v>
+        <v>101.3</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>54.43</v>
+        <v>99.37</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>58.57</v>
+        <v>97.51000000000001</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>53.3</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>55.63</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>53.83</v>
+        <v>96.98</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>55.09</v>
+        <v>97.51000000000001</v>
       </c>
       <c r="S29" s="6" t="n">
-        <v>55.61</v>
+        <v>97.73</v>
       </c>
       <c r="T29" s="6" t="n">
-        <v>53.61</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="U29" s="6" t="n">
-        <v>56.99</v>
+        <v>97.73</v>
       </c>
       <c r="V29" s="6" t="n">
-        <v>53.82</v>
+        <v>96.91</v>
       </c>
       <c r="W29" s="6" t="n">
-        <v>51.9</v>
+        <v>98.98999999999999</v>
       </c>
       <c r="X29" s="6" t="n">
-        <v>49.27</v>
+        <v>101.66</v>
       </c>
       <c r="Y29" s="6" t="n">
-        <v>49.44</v>
+        <v>101.8</v>
       </c>
       <c r="Z29" s="6" t="n">
-        <v>50.36</v>
+        <v>101.18</v>
       </c>
       <c r="AA29" s="6" t="n">
-        <v>49.75</v>
+        <v>101.54</v>
       </c>
       <c r="AB29" s="6" t="n">
-        <v>49.7</v>
+        <v>101.34</v>
       </c>
       <c r="AC29" s="6" t="n">
-        <v>49.16</v>
+        <v>101.57</v>
       </c>
       <c r="AD29" s="6" t="n">
-        <v>50.04</v>
+        <v>101.68</v>
       </c>
       <c r="AE29" s="6" t="n">
-        <v>49.68</v>
+        <v>101.66</v>
       </c>
       <c r="AF29" s="6" t="n">
-        <v>55.52</v>
+        <v>100.26</v>
       </c>
       <c r="AG29" s="6" t="n">
-        <v>61.41</v>
+        <v>98.88</v>
       </c>
       <c r="AH29" s="6" t="n">
-        <v>52.73</v>
+        <v>98.59</v>
       </c>
       <c r="AI29" s="6" t="n">
-        <v>703.75</v>
+        <v>391.54</v>
       </c>
       <c r="AJ29" s="6" t="inlineStr"/>
       <c r="AK29" s="7" t="inlineStr"/>
@@ -3160,110 +2952,110 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>LOJA 97.9 FM</t>
+          <t>RADIO CLIP</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>87.5</v>
+        <v>106.13</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>86.09</v>
+        <v>105.07</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>88.16</v>
+        <v>105.17</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>88.63</v>
+        <v>104.98</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>88.90000000000001</v>
+        <v>105.09</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>89.79000000000001</v>
+        <v>105.69</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>89.31999999999999</v>
+        <v>105.12</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>88.58</v>
+        <v>104.79</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>92.53</v>
+        <v>107.12</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>95.92</v>
+        <v>108.92</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>93.44</v>
+        <v>107.68</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>90.87</v>
+        <v>106.08</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>88.67</v>
+        <v>105.24</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>89.11</v>
+        <v>105.14</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>88.59</v>
+        <v>105.33</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>89.87</v>
+        <v>105.77</v>
       </c>
       <c r="S30" s="6" t="n">
-        <v>90.02</v>
+        <v>105.61</v>
       </c>
       <c r="T30" s="6" t="n">
-        <v>87.84</v>
+        <v>105.26</v>
       </c>
       <c r="U30" s="6" t="n">
-        <v>89.95999999999999</v>
+        <v>105.96</v>
       </c>
       <c r="V30" s="6" t="n">
-        <v>88.63</v>
+        <v>105.32</v>
       </c>
       <c r="W30" s="6" t="n">
-        <v>92.45999999999999</v>
+        <v>107.3</v>
       </c>
       <c r="X30" s="6" t="n">
-        <v>96.26000000000001</v>
+        <v>108.94</v>
       </c>
       <c r="Y30" s="6" t="n">
-        <v>96.79000000000001</v>
+        <v>108.86</v>
       </c>
       <c r="Z30" s="6" t="n">
-        <v>96.63</v>
+        <v>109.09</v>
       </c>
       <c r="AA30" s="6" t="n">
-        <v>96.48</v>
+        <v>108.56</v>
       </c>
       <c r="AB30" s="6" t="n">
-        <v>96.76000000000001</v>
+        <v>108.91</v>
       </c>
       <c r="AC30" s="6" t="n">
-        <v>96.38</v>
+        <v>108.65</v>
       </c>
       <c r="AD30" s="6" t="n">
-        <v>96.31</v>
+        <v>108.59</v>
       </c>
       <c r="AE30" s="6" t="n">
-        <v>96.16</v>
+        <v>108.64</v>
       </c>
       <c r="AF30" s="6" t="n">
-        <v>93.79000000000001</v>
+        <v>107.97</v>
       </c>
       <c r="AG30" s="6" t="n">
-        <v>91.77</v>
+        <v>106.94</v>
       </c>
       <c r="AH30" s="6" t="n">
-        <v>91.68000000000001</v>
+        <v>106.71</v>
       </c>
       <c r="AI30" s="6" t="n">
-        <v>413.77</v>
+        <v>476.01</v>
       </c>
       <c r="AJ30" s="6" t="inlineStr"/>
       <c r="AK30" s="7" t="inlineStr"/>
@@ -3271,110 +3063,110 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>EKOOS FM 98.1</t>
+          <t>RADIO CORPORACIÓN 97.3 FM</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>98.09999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>93</v>
+        <v>50.96</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>90.98</v>
+        <v>51.09</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>89.84</v>
+        <v>51.49</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>91.18000000000001</v>
+        <v>51.17</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>91.06999999999999</v>
+        <v>50.6</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>90.76000000000001</v>
+        <v>53.72</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>90.42</v>
+        <v>54.82</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>90.91</v>
+        <v>51.84</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>92.01000000000001</v>
+        <v>51.62</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>95.33</v>
+        <v>50.18</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>92.98</v>
+        <v>54.43</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>90.56</v>
+        <v>58.57</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>90.81999999999999</v>
+        <v>53.3</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>90.56</v>
+        <v>55.63</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>91.73</v>
+        <v>53.83</v>
       </c>
       <c r="R31" s="6" t="n">
-        <v>91.59999999999999</v>
+        <v>55.09</v>
       </c>
       <c r="S31" s="6" t="n">
-        <v>91.7</v>
+        <v>55.61</v>
       </c>
       <c r="T31" s="6" t="n">
-        <v>91.56</v>
+        <v>53.61</v>
       </c>
       <c r="U31" s="6" t="n">
-        <v>91.42</v>
+        <v>56.99</v>
       </c>
       <c r="V31" s="6" t="n">
-        <v>91.79000000000001</v>
+        <v>53.82</v>
       </c>
       <c r="W31" s="6" t="n">
-        <v>93.86</v>
+        <v>51.9</v>
       </c>
       <c r="X31" s="6" t="n">
-        <v>95.48</v>
+        <v>49.27</v>
       </c>
       <c r="Y31" s="6" t="n">
-        <v>95.56</v>
+        <v>49.44</v>
       </c>
       <c r="Z31" s="6" t="n">
-        <v>95.55</v>
+        <v>50.36</v>
       </c>
       <c r="AA31" s="6" t="n">
-        <v>95.70999999999999</v>
+        <v>49.75</v>
       </c>
       <c r="AB31" s="6" t="n">
-        <v>95.95999999999999</v>
+        <v>49.7</v>
       </c>
       <c r="AC31" s="6" t="n">
-        <v>95.77</v>
+        <v>49.16</v>
       </c>
       <c r="AD31" s="6" t="n">
-        <v>95.66</v>
+        <v>50.04</v>
       </c>
       <c r="AE31" s="6" t="n">
-        <v>95.66</v>
+        <v>49.68</v>
       </c>
       <c r="AF31" s="6" t="n">
-        <v>93.38</v>
+        <v>55.52</v>
       </c>
       <c r="AG31" s="6" t="n">
-        <v>91.63</v>
+        <v>61.41</v>
       </c>
       <c r="AH31" s="6" t="n">
-        <v>92.72</v>
+        <v>52.73</v>
       </c>
       <c r="AI31" s="6" t="n">
-        <v>438.53</v>
+        <v>703.75</v>
       </c>
       <c r="AJ31" s="6" t="inlineStr"/>
       <c r="AK31" s="7" t="inlineStr"/>
@@ -3382,110 +3174,110 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>ESTACION RADIO Y TELEVISION UNI</t>
+          <t>LOJA 97.9 FM</t>
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>98.5</v>
+        <v>97.7</v>
       </c>
       <c r="C32" s="6" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>86.09</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>88.16</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>88.63</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>89.79000000000001</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>89.31999999999999</v>
+      </c>
+      <c r="J32" s="6" t="n">
+        <v>88.58</v>
+      </c>
+      <c r="K32" s="6" t="n">
+        <v>92.53</v>
+      </c>
+      <c r="L32" s="6" t="n">
+        <v>95.92</v>
+      </c>
+      <c r="M32" s="6" t="n">
+        <v>93.44</v>
+      </c>
+      <c r="N32" s="6" t="n">
+        <v>90.87</v>
+      </c>
+      <c r="O32" s="6" t="n">
         <v>88.67</v>
       </c>
-      <c r="D32" s="6" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="E32" s="6" t="n">
-        <v>87.81999999999999</v>
-      </c>
-      <c r="F32" s="6" t="n">
-        <v>87.62</v>
-      </c>
-      <c r="G32" s="6" t="n">
-        <v>87.64</v>
-      </c>
-      <c r="H32" s="6" t="n">
-        <v>88.52</v>
-      </c>
-      <c r="I32" s="6" t="n">
-        <v>88.34999999999999</v>
-      </c>
-      <c r="J32" s="6" t="n">
-        <v>87.61</v>
-      </c>
-      <c r="K32" s="6" t="n">
-        <v>89.45</v>
-      </c>
-      <c r="L32" s="6" t="n">
-        <v>90.98</v>
-      </c>
-      <c r="M32" s="6" t="n">
-        <v>90.31</v>
-      </c>
-      <c r="N32" s="6" t="n">
-        <v>88.88</v>
-      </c>
-      <c r="O32" s="6" t="n">
-        <v>88.42</v>
-      </c>
       <c r="P32" s="6" t="n">
-        <v>88.13</v>
+        <v>89.11</v>
       </c>
       <c r="Q32" s="6" t="n">
-        <v>88.22</v>
+        <v>88.59</v>
       </c>
       <c r="R32" s="6" t="n">
-        <v>88.58</v>
+        <v>89.87</v>
       </c>
       <c r="S32" s="6" t="n">
-        <v>88.66</v>
+        <v>90.02</v>
       </c>
       <c r="T32" s="6" t="n">
-        <v>88.23</v>
+        <v>87.84</v>
       </c>
       <c r="U32" s="6" t="n">
-        <v>88.87</v>
+        <v>89.95999999999999</v>
       </c>
       <c r="V32" s="6" t="n">
-        <v>88.36</v>
+        <v>88.63</v>
       </c>
       <c r="W32" s="6" t="n">
-        <v>89.94</v>
+        <v>92.45999999999999</v>
       </c>
       <c r="X32" s="6" t="n">
-        <v>91.51000000000001</v>
+        <v>96.26000000000001</v>
       </c>
       <c r="Y32" s="6" t="n">
-        <v>91.56999999999999</v>
+        <v>96.79000000000001</v>
       </c>
       <c r="Z32" s="6" t="n">
-        <v>91.45</v>
+        <v>96.63</v>
       </c>
       <c r="AA32" s="6" t="n">
-        <v>91.41</v>
+        <v>96.48</v>
       </c>
       <c r="AB32" s="6" t="n">
-        <v>91.34</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="AC32" s="6" t="n">
-        <v>91.48999999999999</v>
+        <v>96.38</v>
       </c>
       <c r="AD32" s="6" t="n">
-        <v>91.63</v>
+        <v>96.31</v>
       </c>
       <c r="AE32" s="6" t="n">
-        <v>91.52</v>
+        <v>96.16</v>
       </c>
       <c r="AF32" s="6" t="n">
-        <v>91.20999999999999</v>
+        <v>93.79000000000001</v>
       </c>
       <c r="AG32" s="6" t="n">
-        <v>90.66</v>
+        <v>91.77</v>
       </c>
       <c r="AH32" s="6" t="n">
-        <v>89.5</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="AI32" s="6" t="n">
-        <v>496.73</v>
+        <v>413.77</v>
       </c>
       <c r="AJ32" s="6" t="inlineStr"/>
       <c r="AK32" s="7" t="inlineStr"/>
@@ -3493,110 +3285,110 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>RADIO MARIA</t>
+          <t>EKOOS FM 98.1</t>
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>98.90000000000001</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>96.28</v>
+        <v>93</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>95.2</v>
+        <v>90.98</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>93.51000000000001</v>
+        <v>89.84</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>93.5</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>93.28</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>94.70999999999999</v>
+        <v>90.76000000000001</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>94.20999999999999</v>
+        <v>90.42</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>93.73999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>97.06</v>
+        <v>92.01000000000001</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>99.94</v>
+        <v>95.33</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>97.87</v>
+        <v>92.98</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>95</v>
+        <v>90.56</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>94.31999999999999</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>94.08</v>
+        <v>90.56</v>
       </c>
       <c r="Q33" s="6" t="n">
-        <v>94.43000000000001</v>
+        <v>91.73</v>
       </c>
       <c r="R33" s="6" t="n">
-        <v>94.98</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="S33" s="6" t="n">
-        <v>95.19</v>
+        <v>91.7</v>
       </c>
       <c r="T33" s="6" t="n">
-        <v>94.83</v>
+        <v>91.56</v>
       </c>
       <c r="U33" s="6" t="n">
-        <v>95.59</v>
+        <v>91.42</v>
       </c>
       <c r="V33" s="6" t="n">
-        <v>94.31</v>
+        <v>91.79000000000001</v>
       </c>
       <c r="W33" s="6" t="n">
-        <v>96.84</v>
+        <v>93.86</v>
       </c>
       <c r="X33" s="6" t="n">
-        <v>99.69</v>
+        <v>95.48</v>
       </c>
       <c r="Y33" s="6" t="n">
-        <v>99.31999999999999</v>
+        <v>95.56</v>
       </c>
       <c r="Z33" s="6" t="n">
-        <v>99.48</v>
+        <v>95.55</v>
       </c>
       <c r="AA33" s="6" t="n">
-        <v>99.34</v>
+        <v>95.70999999999999</v>
       </c>
       <c r="AB33" s="6" t="n">
-        <v>99.56</v>
+        <v>95.95999999999999</v>
       </c>
       <c r="AC33" s="6" t="n">
-        <v>99.34</v>
+        <v>95.77</v>
       </c>
       <c r="AD33" s="6" t="n">
-        <v>99.19</v>
+        <v>95.66</v>
       </c>
       <c r="AE33" s="6" t="n">
-        <v>99.31999999999999</v>
+        <v>95.66</v>
       </c>
       <c r="AF33" s="6" t="n">
-        <v>97.73</v>
+        <v>93.38</v>
       </c>
       <c r="AG33" s="6" t="n">
-        <v>96.22</v>
+        <v>91.63</v>
       </c>
       <c r="AH33" s="6" t="n">
-        <v>96.39</v>
+        <v>92.72</v>
       </c>
       <c r="AI33" s="6" t="n">
-        <v>387.7</v>
+        <v>438.53</v>
       </c>
       <c r="AJ33" s="6" t="inlineStr"/>
       <c r="AK33" s="7" t="inlineStr"/>
@@ -3604,110 +3396,110 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>SOCIEDAD FM</t>
+          <t>ESTACION RADIO Y TELEVISION UNI</t>
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>99.3</v>
+        <v>98.5</v>
       </c>
       <c r="C34" s="6" t="n">
-        <v>100.73</v>
+        <v>88.67</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>100.51</v>
+        <v>87.5</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>100.67</v>
+        <v>87.81999999999999</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>100.09</v>
+        <v>87.62</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>100.42</v>
+        <v>87.64</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>101.41</v>
+        <v>88.52</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>101.02</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>100.88</v>
+        <v>87.61</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>101.19</v>
+        <v>89.45</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>100.89</v>
+        <v>90.98</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>100.48</v>
+        <v>90.31</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>101.38</v>
+        <v>88.88</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>101.37</v>
+        <v>88.42</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>100.68</v>
+        <v>88.13</v>
       </c>
       <c r="Q34" s="6" t="n">
-        <v>101.06</v>
+        <v>88.22</v>
       </c>
       <c r="R34" s="6" t="n">
-        <v>100.97</v>
+        <v>88.58</v>
       </c>
       <c r="S34" s="6" t="n">
-        <v>100.17</v>
+        <v>88.66</v>
       </c>
       <c r="T34" s="6" t="n">
-        <v>101.12</v>
+        <v>88.23</v>
       </c>
       <c r="U34" s="6" t="n">
-        <v>101.11</v>
+        <v>88.87</v>
       </c>
       <c r="V34" s="6" t="n">
-        <v>101.01</v>
+        <v>88.36</v>
       </c>
       <c r="W34" s="6" t="n">
-        <v>99.90000000000001</v>
+        <v>89.94</v>
       </c>
       <c r="X34" s="6" t="n">
-        <v>99.19</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="Y34" s="6" t="n">
-        <v>99.81999999999999</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="Z34" s="6" t="n">
-        <v>100.26</v>
+        <v>91.45</v>
       </c>
       <c r="AA34" s="6" t="n">
-        <v>99.18000000000001</v>
+        <v>91.41</v>
       </c>
       <c r="AB34" s="6" t="n">
-        <v>99.89</v>
+        <v>91.34</v>
       </c>
       <c r="AC34" s="6" t="n">
-        <v>99.97</v>
+        <v>91.48999999999999</v>
       </c>
       <c r="AD34" s="6" t="n">
-        <v>99.77</v>
+        <v>91.63</v>
       </c>
       <c r="AE34" s="6" t="n">
-        <v>99.69</v>
+        <v>91.52</v>
       </c>
       <c r="AF34" s="6" t="n">
-        <v>100.54</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="AG34" s="6" t="n">
-        <v>101.43</v>
+        <v>90.66</v>
       </c>
       <c r="AH34" s="6" t="n">
-        <v>100.54</v>
+        <v>89.5</v>
       </c>
       <c r="AI34" s="6" t="n">
-        <v>400.46</v>
+        <v>496.73</v>
       </c>
       <c r="AJ34" s="6" t="inlineStr"/>
       <c r="AK34" s="7" t="inlineStr"/>
@@ -3715,110 +3507,110 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>MATOVELLE FM</t>
+          <t>RADIO MARIA</t>
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>100.1</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>104.58</v>
+        <v>96.28</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>104.67</v>
+        <v>95.2</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>103.33</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>104.4</v>
+        <v>93.5</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>104.63</v>
+        <v>93.28</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>105.15</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>103.98</v>
+        <v>94.20999999999999</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>104.01</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>103.93</v>
+        <v>97.06</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>104.06</v>
+        <v>99.94</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>104.12</v>
+        <v>97.87</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>104.99</v>
+        <v>95</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>105.4</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>104.18</v>
+        <v>94.08</v>
       </c>
       <c r="Q35" s="6" t="n">
-        <v>104.56</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="R35" s="6" t="n">
-        <v>104.82</v>
+        <v>94.98</v>
       </c>
       <c r="S35" s="6" t="n">
-        <v>104.64</v>
+        <v>95.19</v>
       </c>
       <c r="T35" s="6" t="n">
-        <v>104.56</v>
+        <v>94.83</v>
       </c>
       <c r="U35" s="6" t="n">
-        <v>105.75</v>
+        <v>95.59</v>
       </c>
       <c r="V35" s="6" t="n">
-        <v>105.66</v>
+        <v>94.31</v>
       </c>
       <c r="W35" s="6" t="n">
-        <v>104.31</v>
+        <v>96.84</v>
       </c>
       <c r="X35" s="6" t="n">
-        <v>103.87</v>
+        <v>99.69</v>
       </c>
       <c r="Y35" s="6" t="n">
-        <v>103.78</v>
+        <v>99.31999999999999</v>
       </c>
       <c r="Z35" s="6" t="n">
-        <v>103.2</v>
+        <v>99.48</v>
       </c>
       <c r="AA35" s="6" t="n">
-        <v>103.45</v>
+        <v>99.34</v>
       </c>
       <c r="AB35" s="6" t="n">
-        <v>104.43</v>
+        <v>99.56</v>
       </c>
       <c r="AC35" s="6" t="n">
-        <v>104.42</v>
+        <v>99.34</v>
       </c>
       <c r="AD35" s="6" t="n">
-        <v>103.52</v>
+        <v>99.19</v>
       </c>
       <c r="AE35" s="6" t="n">
-        <v>103.88</v>
+        <v>99.31999999999999</v>
       </c>
       <c r="AF35" s="6" t="n">
-        <v>104.63</v>
+        <v>97.73</v>
       </c>
       <c r="AG35" s="6" t="n">
-        <v>105.94</v>
+        <v>96.22</v>
       </c>
       <c r="AH35" s="6" t="n">
-        <v>104.41</v>
+        <v>96.39</v>
       </c>
       <c r="AI35" s="6" t="n">
-        <v>422.94</v>
+        <v>387.7</v>
       </c>
       <c r="AJ35" s="6" t="inlineStr"/>
       <c r="AK35" s="7" t="inlineStr"/>
@@ -3826,110 +3618,110 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>BAKANA</t>
+          <t>SOCIEDAD FM</t>
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>100.5</v>
+        <v>99.3</v>
       </c>
       <c r="C36" s="6" t="n">
-        <v>85.64</v>
+        <v>100.73</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>89.26000000000001</v>
+        <v>100.51</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>84.69</v>
+        <v>100.67</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>85.5</v>
+        <v>100.09</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>85.12</v>
+        <v>100.42</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>85.45999999999999</v>
+        <v>101.41</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>86.08</v>
+        <v>101.02</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>84.76000000000001</v>
+        <v>100.88</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>87.98</v>
+        <v>101.19</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>91.37</v>
+        <v>100.89</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>87.83</v>
+        <v>100.48</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>84.98</v>
+        <v>101.38</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>84.48999999999999</v>
+        <v>101.37</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>86.59</v>
+        <v>100.68</v>
       </c>
       <c r="Q36" s="6" t="n">
-        <v>87.42</v>
+        <v>101.06</v>
       </c>
       <c r="R36" s="6" t="n">
-        <v>87.05</v>
+        <v>100.97</v>
       </c>
       <c r="S36" s="6" t="n">
-        <v>87.66</v>
+        <v>100.17</v>
       </c>
       <c r="T36" s="6" t="n">
-        <v>88.83</v>
+        <v>101.12</v>
       </c>
       <c r="U36" s="6" t="n">
-        <v>87.95999999999999</v>
+        <v>101.11</v>
       </c>
       <c r="V36" s="6" t="n">
-        <v>88.23</v>
+        <v>101.01</v>
       </c>
       <c r="W36" s="6" t="n">
-        <v>89.31</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="X36" s="6" t="n">
-        <v>91.02</v>
+        <v>99.19</v>
       </c>
       <c r="Y36" s="6" t="n">
-        <v>91.7</v>
+        <v>99.81999999999999</v>
       </c>
       <c r="Z36" s="6" t="n">
-        <v>93.03</v>
+        <v>100.26</v>
       </c>
       <c r="AA36" s="6" t="n">
-        <v>91.01000000000001</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="AB36" s="6" t="n">
-        <v>90.93000000000001</v>
+        <v>99.89</v>
       </c>
       <c r="AC36" s="6" t="n">
-        <v>91.25</v>
+        <v>99.97</v>
       </c>
       <c r="AD36" s="6" t="n">
-        <v>91.53</v>
+        <v>99.77</v>
       </c>
       <c r="AE36" s="6" t="n">
-        <v>90.98999999999999</v>
+        <v>99.69</v>
       </c>
       <c r="AF36" s="6" t="n">
-        <v>89.48999999999999</v>
+        <v>100.54</v>
       </c>
       <c r="AG36" s="6" t="n">
-        <v>88.09</v>
+        <v>101.43</v>
       </c>
       <c r="AH36" s="6" t="n">
-        <v>88.23</v>
+        <v>100.54</v>
       </c>
       <c r="AI36" s="6" t="n">
-        <v>419.65</v>
+        <v>400.46</v>
       </c>
       <c r="AJ36" s="6" t="inlineStr"/>
       <c r="AK36" s="7" t="inlineStr"/>
@@ -3937,110 +3729,110 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>SATELITAL 100.9 FM</t>
+          <t>MATOVELLE FM</t>
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>100.9</v>
+        <v>100.1</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>98.81999999999999</v>
+        <v>104.58</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>101.34</v>
+        <v>104.67</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>97.12</v>
+        <v>103.33</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>97.89</v>
+        <v>104.4</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>97.7</v>
+        <v>104.63</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>98.11</v>
+        <v>105.15</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>98.68000000000001</v>
+        <v>103.98</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>97.28</v>
+        <v>104.01</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>101.19</v>
+        <v>103.93</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>103.54</v>
+        <v>104.06</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>101.93</v>
+        <v>104.12</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>98.64</v>
+        <v>104.99</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>98.05</v>
+        <v>105.4</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>98.52</v>
+        <v>104.18</v>
       </c>
       <c r="Q37" s="6" t="n">
-        <v>98.81999999999999</v>
+        <v>104.56</v>
       </c>
       <c r="R37" s="6" t="n">
-        <v>98.98</v>
+        <v>104.82</v>
       </c>
       <c r="S37" s="6" t="n">
-        <v>99.04000000000001</v>
+        <v>104.64</v>
       </c>
       <c r="T37" s="6" t="n">
-        <v>99.51000000000001</v>
+        <v>104.56</v>
       </c>
       <c r="U37" s="6" t="n">
-        <v>100.46</v>
+        <v>105.75</v>
       </c>
       <c r="V37" s="6" t="n">
-        <v>99.43000000000001</v>
+        <v>105.66</v>
       </c>
       <c r="W37" s="6" t="n">
-        <v>100.68</v>
+        <v>104.31</v>
       </c>
       <c r="X37" s="6" t="n">
-        <v>103.7</v>
+        <v>103.87</v>
       </c>
       <c r="Y37" s="6" t="n">
-        <v>104.14</v>
+        <v>103.78</v>
       </c>
       <c r="Z37" s="6" t="n">
-        <v>104.82</v>
+        <v>103.2</v>
       </c>
       <c r="AA37" s="6" t="n">
-        <v>104.1</v>
+        <v>103.45</v>
       </c>
       <c r="AB37" s="6" t="n">
-        <v>103.98</v>
+        <v>104.43</v>
       </c>
       <c r="AC37" s="6" t="n">
-        <v>104.17</v>
+        <v>104.42</v>
       </c>
       <c r="AD37" s="6" t="n">
-        <v>103.9</v>
+        <v>103.52</v>
       </c>
       <c r="AE37" s="6" t="n">
-        <v>104.06</v>
+        <v>103.88</v>
       </c>
       <c r="AF37" s="6" t="n">
-        <v>101.71</v>
+        <v>104.63</v>
       </c>
       <c r="AG37" s="6" t="n">
-        <v>100.18</v>
+        <v>105.94</v>
       </c>
       <c r="AH37" s="6" t="n">
-        <v>100.66</v>
+        <v>104.41</v>
       </c>
       <c r="AI37" s="6" t="n">
-        <v>399.91</v>
+        <v>422.94</v>
       </c>
       <c r="AJ37" s="6" t="inlineStr"/>
       <c r="AK37" s="7" t="inlineStr"/>
@@ -4048,110 +3840,110 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>DI BLU</t>
+          <t>BAKANA</t>
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>101.3</v>
+        <v>100.5</v>
       </c>
       <c r="C38" s="6" t="n">
-        <v>98.51000000000001</v>
+        <v>85.64</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>100.48</v>
+        <v>89.26000000000001</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>98.58</v>
+        <v>84.69</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>99.27</v>
+        <v>85.5</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>98.88</v>
+        <v>85.12</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>99.08</v>
+        <v>85.45999999999999</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>99.51000000000001</v>
+        <v>86.08</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>99.31</v>
+        <v>84.76000000000001</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>100.52</v>
+        <v>87.98</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>102.21</v>
+        <v>91.37</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>101.19</v>
+        <v>87.83</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>99.40000000000001</v>
+        <v>84.98</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>99.41</v>
+        <v>84.48999999999999</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>99.53</v>
+        <v>86.59</v>
       </c>
       <c r="Q38" s="6" t="n">
-        <v>99.78</v>
+        <v>87.42</v>
       </c>
       <c r="R38" s="6" t="n">
-        <v>99.94</v>
+        <v>87.05</v>
       </c>
       <c r="S38" s="6" t="n">
-        <v>99.69</v>
+        <v>87.66</v>
       </c>
       <c r="T38" s="6" t="n">
-        <v>100.28</v>
+        <v>88.83</v>
       </c>
       <c r="U38" s="6" t="n">
-        <v>100.74</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="V38" s="6" t="n">
-        <v>99.73</v>
+        <v>88.23</v>
       </c>
       <c r="W38" s="6" t="n">
-        <v>100.94</v>
+        <v>89.31</v>
       </c>
       <c r="X38" s="6" t="n">
-        <v>102</v>
+        <v>91.02</v>
       </c>
       <c r="Y38" s="6" t="n">
-        <v>101.42</v>
+        <v>91.7</v>
       </c>
       <c r="Z38" s="6" t="n">
-        <v>101.85</v>
+        <v>93.03</v>
       </c>
       <c r="AA38" s="6" t="n">
-        <v>101.92</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="AB38" s="6" t="n">
-        <v>101.72</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="AC38" s="6" t="n">
-        <v>101.67</v>
+        <v>91.25</v>
       </c>
       <c r="AD38" s="6" t="n">
-        <v>102.04</v>
+        <v>91.53</v>
       </c>
       <c r="AE38" s="6" t="n">
-        <v>101.97</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="AF38" s="6" t="n">
-        <v>101.61</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="AG38" s="6" t="n">
-        <v>100.71</v>
+        <v>88.09</v>
       </c>
       <c r="AH38" s="6" t="n">
-        <v>100.45</v>
+        <v>88.23</v>
       </c>
       <c r="AI38" s="6" t="n">
-        <v>407.04</v>
+        <v>419.65</v>
       </c>
       <c r="AJ38" s="6" t="inlineStr"/>
       <c r="AK38" s="7" t="inlineStr"/>
@@ -4159,110 +3951,110 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>RADIO ECUASUR</t>
+          <t>SATELITAL 100.9 FM</t>
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>102.1</v>
+        <v>100.9</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>102.57</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>105.03</v>
+        <v>101.34</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>103.34</v>
+        <v>97.12</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>103.44</v>
+        <v>97.89</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>103.11</v>
+        <v>97.7</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>103.53</v>
+        <v>98.11</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>103.46</v>
+        <v>98.68000000000001</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>103.53</v>
+        <v>97.28</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>106.06</v>
+        <v>101.19</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>108.66</v>
+        <v>103.54</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>106.24</v>
+        <v>101.93</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>103.67</v>
+        <v>98.64</v>
       </c>
       <c r="O39" s="6" t="n">
+        <v>98.05</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v>98.52</v>
+      </c>
+      <c r="Q39" s="6" t="n">
+        <v>98.81999999999999</v>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v>98.98</v>
+      </c>
+      <c r="S39" s="6" t="n">
+        <v>99.04000000000001</v>
+      </c>
+      <c r="T39" s="6" t="n">
+        <v>99.51000000000001</v>
+      </c>
+      <c r="U39" s="6" t="n">
+        <v>100.46</v>
+      </c>
+      <c r="V39" s="6" t="n">
+        <v>99.43000000000001</v>
+      </c>
+      <c r="W39" s="6" t="n">
+        <v>100.68</v>
+      </c>
+      <c r="X39" s="6" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="Y39" s="6" t="n">
         <v>104.14</v>
       </c>
-      <c r="P39" s="6" t="n">
-        <v>103.64</v>
-      </c>
-      <c r="Q39" s="6" t="n">
-        <v>103.54</v>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v>103.82</v>
-      </c>
-      <c r="S39" s="6" t="n">
-        <v>103.42</v>
-      </c>
-      <c r="T39" s="6" t="n">
-        <v>104.5</v>
-      </c>
-      <c r="U39" s="6" t="n">
-        <v>104.66</v>
-      </c>
-      <c r="V39" s="6" t="n">
-        <v>104.32</v>
-      </c>
-      <c r="W39" s="6" t="n">
-        <v>105.61</v>
-      </c>
-      <c r="X39" s="6" t="n">
-        <v>107.35</v>
-      </c>
-      <c r="Y39" s="6" t="n">
-        <v>107.55</v>
-      </c>
       <c r="Z39" s="6" t="n">
-        <v>108.24</v>
+        <v>104.82</v>
       </c>
       <c r="AA39" s="6" t="n">
-        <v>107.6</v>
+        <v>104.1</v>
       </c>
       <c r="AB39" s="6" t="n">
-        <v>107.67</v>
+        <v>103.98</v>
       </c>
       <c r="AC39" s="6" t="n">
-        <v>108.09</v>
+        <v>104.17</v>
       </c>
       <c r="AD39" s="6" t="n">
-        <v>108.48</v>
+        <v>103.9</v>
       </c>
       <c r="AE39" s="6" t="n">
-        <v>107.73</v>
+        <v>104.06</v>
       </c>
       <c r="AF39" s="6" t="n">
-        <v>106.29</v>
+        <v>101.71</v>
       </c>
       <c r="AG39" s="6" t="n">
-        <v>103.92</v>
+        <v>100.18</v>
       </c>
       <c r="AH39" s="6" t="n">
-        <v>105.27</v>
+        <v>100.66</v>
       </c>
       <c r="AI39" s="6" t="n">
-        <v>316.68</v>
+        <v>399.91</v>
       </c>
       <c r="AJ39" s="6" t="inlineStr"/>
       <c r="AK39" s="7" t="inlineStr"/>
@@ -4270,110 +4062,110 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>RADIO SONORAMA FM</t>
+          <t>DI BLU</t>
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>103.7</v>
+        <v>101.3</v>
       </c>
       <c r="C40" s="6" t="n">
-        <v>50.32</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>50.59</v>
+        <v>100.48</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>51.34</v>
+        <v>98.58</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>51.32</v>
+        <v>99.27</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>50.85</v>
+        <v>98.88</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>52.08</v>
+        <v>99.08</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>53.42</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>51.71</v>
+        <v>99.31</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>52.18</v>
+        <v>100.52</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>50.53</v>
+        <v>102.21</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>53.58</v>
+        <v>101.19</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>56.22</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>52.72</v>
+        <v>99.41</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>54.54</v>
+        <v>99.53</v>
       </c>
       <c r="Q40" s="6" t="n">
-        <v>52.73</v>
+        <v>99.78</v>
       </c>
       <c r="R40" s="6" t="n">
-        <v>54.53</v>
+        <v>99.94</v>
       </c>
       <c r="S40" s="6" t="n">
-        <v>54.02</v>
+        <v>99.69</v>
       </c>
       <c r="T40" s="6" t="n">
-        <v>52.69</v>
+        <v>100.28</v>
       </c>
       <c r="U40" s="6" t="n">
-        <v>55.21</v>
+        <v>100.74</v>
       </c>
       <c r="V40" s="6" t="n">
-        <v>53.4</v>
+        <v>99.73</v>
       </c>
       <c r="W40" s="6" t="n">
-        <v>51.93</v>
+        <v>100.94</v>
       </c>
       <c r="X40" s="6" t="n">
-        <v>50.58</v>
+        <v>102</v>
       </c>
       <c r="Y40" s="6" t="n">
-        <v>50.59</v>
+        <v>101.42</v>
       </c>
       <c r="Z40" s="6" t="n">
-        <v>51.81</v>
+        <v>101.85</v>
       </c>
       <c r="AA40" s="6" t="n">
-        <v>50.61</v>
+        <v>101.92</v>
       </c>
       <c r="AB40" s="6" t="n">
-        <v>50.29</v>
+        <v>101.72</v>
       </c>
       <c r="AC40" s="6" t="n">
-        <v>50.64</v>
+        <v>101.67</v>
       </c>
       <c r="AD40" s="6" t="n">
-        <v>50.85</v>
+        <v>102.04</v>
       </c>
       <c r="AE40" s="6" t="n">
-        <v>50.63</v>
+        <v>101.97</v>
       </c>
       <c r="AF40" s="6" t="n">
-        <v>54.85</v>
+        <v>101.61</v>
       </c>
       <c r="AG40" s="6" t="n">
-        <v>59.83</v>
+        <v>100.71</v>
       </c>
       <c r="AH40" s="6" t="n">
-        <v>52.47</v>
+        <v>100.45</v>
       </c>
       <c r="AI40" s="6" t="n">
-        <v>504.72</v>
+        <v>407.04</v>
       </c>
       <c r="AJ40" s="6" t="inlineStr"/>
       <c r="AK40" s="7" t="inlineStr"/>
@@ -4381,110 +4173,110 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>LA LUNA FM</t>
+          <t>RADIO ECUASUR</t>
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>104.1</v>
+        <v>102.1</v>
       </c>
       <c r="C41" s="6" t="n">
-        <v>94.04000000000001</v>
+        <v>102.57</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>95.83</v>
+        <v>105.03</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>95.92</v>
+        <v>103.34</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>96.47</v>
+        <v>103.44</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>95.53</v>
+        <v>103.11</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>96.39</v>
+        <v>103.53</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>96.56999999999999</v>
+        <v>103.46</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>96.41</v>
+        <v>103.53</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>98.69</v>
+        <v>106.06</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>100.37</v>
+        <v>108.66</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>98.08</v>
+        <v>106.24</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>97.19</v>
+        <v>103.67</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>96.73</v>
+        <v>104.14</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>96.40000000000001</v>
+        <v>103.64</v>
       </c>
       <c r="Q41" s="6" t="n">
-        <v>95.81</v>
+        <v>103.54</v>
       </c>
       <c r="R41" s="6" t="n">
-        <v>97.40000000000001</v>
+        <v>103.82</v>
       </c>
       <c r="S41" s="6" t="n">
-        <v>97.02</v>
+        <v>103.42</v>
       </c>
       <c r="T41" s="6" t="n">
-        <v>97.20999999999999</v>
+        <v>104.5</v>
       </c>
       <c r="U41" s="6" t="n">
-        <v>98.29000000000001</v>
+        <v>104.66</v>
       </c>
       <c r="V41" s="6" t="n">
-        <v>96.59</v>
+        <v>104.32</v>
       </c>
       <c r="W41" s="6" t="n">
-        <v>98.28</v>
+        <v>105.61</v>
       </c>
       <c r="X41" s="6" t="n">
-        <v>99.27</v>
+        <v>107.35</v>
       </c>
       <c r="Y41" s="6" t="n">
-        <v>99.29000000000001</v>
+        <v>107.55</v>
       </c>
       <c r="Z41" s="6" t="n">
-        <v>100.11</v>
+        <v>108.24</v>
       </c>
       <c r="AA41" s="6" t="n">
-        <v>99.68000000000001</v>
+        <v>107.6</v>
       </c>
       <c r="AB41" s="6" t="n">
-        <v>99.3</v>
+        <v>107.67</v>
       </c>
       <c r="AC41" s="6" t="n">
-        <v>98.88</v>
+        <v>108.09</v>
       </c>
       <c r="AD41" s="6" t="n">
-        <v>99.84</v>
+        <v>108.48</v>
       </c>
       <c r="AE41" s="6" t="n">
-        <v>98.58</v>
+        <v>107.73</v>
       </c>
       <c r="AF41" s="6" t="n">
-        <v>98.22</v>
+        <v>106.29</v>
       </c>
       <c r="AG41" s="6" t="n">
-        <v>98.54000000000001</v>
+        <v>103.92</v>
       </c>
       <c r="AH41" s="6" t="n">
-        <v>97.64</v>
+        <v>105.27</v>
       </c>
       <c r="AI41" s="6" t="n">
-        <v>265.12</v>
+        <v>316.68</v>
       </c>
       <c r="AJ41" s="6" t="inlineStr"/>
       <c r="AK41" s="7" t="inlineStr"/>
@@ -4492,110 +4284,110 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>KOCODRILO RADIO</t>
+          <t>RADIO SONORAMA FM</t>
         </is>
       </c>
       <c r="B42" s="6" t="n">
-        <v>104.5</v>
+        <v>103.7</v>
       </c>
       <c r="C42" s="6" t="n">
-        <v>96.89</v>
+        <v>50.32</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>98.95999999999999</v>
+        <v>50.59</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>100.69</v>
+        <v>51.34</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>99.98999999999999</v>
+        <v>51.32</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>100.05</v>
+        <v>50.85</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>100.15</v>
+        <v>52.08</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>99.63</v>
+        <v>53.42</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>99.47</v>
+        <v>51.71</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>103.17</v>
+        <v>52.18</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>105.8</v>
+        <v>50.53</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>103.22</v>
+        <v>53.58</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>100.21</v>
+        <v>56.22</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>100.55</v>
+        <v>52.72</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>100.05</v>
+        <v>54.54</v>
       </c>
       <c r="Q42" s="6" t="n">
-        <v>99.7</v>
+        <v>52.73</v>
       </c>
       <c r="R42" s="6" t="n">
-        <v>100.71</v>
+        <v>54.53</v>
       </c>
       <c r="S42" s="6" t="n">
-        <v>100.57</v>
+        <v>54.02</v>
       </c>
       <c r="T42" s="6" t="n">
-        <v>99.79000000000001</v>
+        <v>52.69</v>
       </c>
       <c r="U42" s="6" t="n">
-        <v>101.17</v>
+        <v>55.21</v>
       </c>
       <c r="V42" s="6" t="n">
-        <v>101.09</v>
+        <v>53.4</v>
       </c>
       <c r="W42" s="6" t="n">
-        <v>102.88</v>
+        <v>51.93</v>
       </c>
       <c r="X42" s="6" t="n">
-        <v>105.57</v>
+        <v>50.58</v>
       </c>
       <c r="Y42" s="6" t="n">
-        <v>106.06</v>
+        <v>50.59</v>
       </c>
       <c r="Z42" s="6" t="n">
-        <v>105.97</v>
+        <v>51.81</v>
       </c>
       <c r="AA42" s="6" t="n">
-        <v>106.17</v>
+        <v>50.61</v>
       </c>
       <c r="AB42" s="6" t="n">
-        <v>105.77</v>
+        <v>50.29</v>
       </c>
       <c r="AC42" s="6" t="n">
-        <v>105.69</v>
+        <v>50.64</v>
       </c>
       <c r="AD42" s="6" t="n">
-        <v>106.16</v>
+        <v>50.85</v>
       </c>
       <c r="AE42" s="6" t="n">
-        <v>105.9</v>
+        <v>50.63</v>
       </c>
       <c r="AF42" s="6" t="n">
-        <v>103.81</v>
+        <v>54.85</v>
       </c>
       <c r="AG42" s="6" t="n">
-        <v>100.94</v>
+        <v>59.83</v>
       </c>
       <c r="AH42" s="6" t="n">
-        <v>102.15</v>
+        <v>52.47</v>
       </c>
       <c r="AI42" s="6" t="n">
-        <v>348.54</v>
+        <v>504.72</v>
       </c>
       <c r="AJ42" s="6" t="inlineStr"/>
       <c r="AK42" s="7" t="inlineStr"/>
@@ -4603,110 +4395,110 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>SUPER LASER PANAMERICANA</t>
+          <t>LA LUNA FM</t>
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>104.9</v>
+        <v>104.1</v>
       </c>
       <c r="C43" s="6" t="n">
-        <v>99.90000000000001</v>
+        <v>94.04000000000001</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>99.70999999999999</v>
+        <v>95.83</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>100.45</v>
+        <v>95.92</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>100.85</v>
+        <v>96.47</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>100.75</v>
+        <v>95.53</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>101.45</v>
+        <v>96.39</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>101.65</v>
+        <v>96.56999999999999</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>100.51</v>
+        <v>96.41</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>101.33</v>
+        <v>98.69</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>101.65</v>
+        <v>100.37</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>101.78</v>
+        <v>98.08</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>102.15</v>
+        <v>97.19</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>101.4</v>
+        <v>96.73</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>101.39</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="Q43" s="6" t="n">
-        <v>101.01</v>
+        <v>95.81</v>
       </c>
       <c r="R43" s="6" t="n">
-        <v>62.75</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="S43" s="6" t="n">
-        <v>101.98</v>
+        <v>97.02</v>
       </c>
       <c r="T43" s="6" t="n">
-        <v>101.33</v>
+        <v>97.20999999999999</v>
       </c>
       <c r="U43" s="6" t="n">
-        <v>102.57</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="V43" s="6" t="n">
-        <v>101.05</v>
+        <v>96.59</v>
       </c>
       <c r="W43" s="6" t="n">
-        <v>101.24</v>
+        <v>98.28</v>
       </c>
       <c r="X43" s="6" t="n">
-        <v>100.69</v>
+        <v>99.27</v>
       </c>
       <c r="Y43" s="6" t="n">
-        <v>100.94</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="Z43" s="6" t="n">
-        <v>101.27</v>
+        <v>100.11</v>
       </c>
       <c r="AA43" s="6" t="n">
-        <v>100.94</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="AB43" s="6" t="n">
-        <v>101.06</v>
+        <v>99.3</v>
       </c>
       <c r="AC43" s="6" t="n">
-        <v>101.25</v>
+        <v>98.88</v>
       </c>
       <c r="AD43" s="6" t="n">
-        <v>101.16</v>
+        <v>99.84</v>
       </c>
       <c r="AE43" s="6" t="n">
-        <v>101.06</v>
+        <v>98.58</v>
       </c>
       <c r="AF43" s="6" t="n">
-        <v>102.18</v>
+        <v>98.22</v>
       </c>
       <c r="AG43" s="6" t="n">
-        <v>104.17</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="AH43" s="6" t="n">
-        <v>100.05</v>
+        <v>97.64</v>
       </c>
       <c r="AI43" s="6" t="n">
-        <v>456.27</v>
+        <v>265.12</v>
       </c>
       <c r="AJ43" s="6" t="inlineStr"/>
       <c r="AK43" s="7" t="inlineStr"/>
@@ -4714,110 +4506,110 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>RADIO MIX</t>
+          <t>KOCODRILO RADIO</t>
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>105.7</v>
+        <v>104.5</v>
       </c>
       <c r="C44" s="6" t="n">
-        <v>99.2</v>
+        <v>96.89</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>100.34</v>
+        <v>98.95999999999999</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>98.93000000000001</v>
+        <v>100.69</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>99.94</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>99.59999999999999</v>
+        <v>100.05</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>99.78</v>
+        <v>100.15</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>100.31</v>
+        <v>99.63</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>100.54</v>
+        <v>99.47</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>100.59</v>
+        <v>103.17</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>101.39</v>
+        <v>105.8</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>101.34</v>
+        <v>103.22</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>100.27</v>
+        <v>100.21</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>99.64</v>
+        <v>100.55</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>100.25</v>
+        <v>100.05</v>
       </c>
       <c r="Q44" s="6" t="n">
-        <v>100.02</v>
+        <v>99.7</v>
       </c>
       <c r="R44" s="6" t="n">
-        <v>101.94</v>
+        <v>100.71</v>
       </c>
       <c r="S44" s="6" t="n">
-        <v>101.76</v>
+        <v>100.57</v>
       </c>
       <c r="T44" s="6" t="n">
-        <v>99.89</v>
+        <v>99.79000000000001</v>
       </c>
       <c r="U44" s="6" t="n">
-        <v>100.34</v>
+        <v>101.17</v>
       </c>
       <c r="V44" s="6" t="n">
-        <v>100.52</v>
+        <v>101.09</v>
       </c>
       <c r="W44" s="6" t="n">
-        <v>100.96</v>
+        <v>102.88</v>
       </c>
       <c r="X44" s="6" t="n">
-        <v>101.15</v>
+        <v>105.57</v>
       </c>
       <c r="Y44" s="6" t="n">
-        <v>101.05</v>
+        <v>106.06</v>
       </c>
       <c r="Z44" s="6" t="n">
-        <v>101.21</v>
+        <v>105.97</v>
       </c>
       <c r="AA44" s="6" t="n">
-        <v>101.4</v>
+        <v>106.17</v>
       </c>
       <c r="AB44" s="6" t="n">
-        <v>100.88</v>
+        <v>105.77</v>
       </c>
       <c r="AC44" s="6" t="n">
-        <v>101.17</v>
+        <v>105.69</v>
       </c>
       <c r="AD44" s="6" t="n">
-        <v>101.41</v>
+        <v>106.16</v>
       </c>
       <c r="AE44" s="6" t="n">
-        <v>101.22</v>
+        <v>105.9</v>
       </c>
       <c r="AF44" s="6" t="n">
-        <v>101.94</v>
+        <v>103.81</v>
       </c>
       <c r="AG44" s="6" t="n">
-        <v>102.45</v>
+        <v>100.94</v>
       </c>
       <c r="AH44" s="6" t="n">
-        <v>100.69</v>
+        <v>102.15</v>
       </c>
       <c r="AI44" s="6" t="n">
-        <v>420.89</v>
+        <v>348.54</v>
       </c>
       <c r="AJ44" s="6" t="inlineStr"/>
       <c r="AK44" s="7" t="inlineStr"/>
@@ -4825,110 +4617,110 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>PLANETA F.M. STEREO</t>
+          <t>SUPER LASER PANAMERICANA</t>
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>106.1</v>
+        <v>104.9</v>
       </c>
       <c r="C45" s="6" t="n">
-        <v>96.41</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>98.17</v>
+        <v>99.70999999999999</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>99.8</v>
+        <v>100.45</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>99.06</v>
+        <v>100.85</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>99.08</v>
+        <v>100.75</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>99.69</v>
+        <v>101.45</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>98.59</v>
+        <v>101.65</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>98.34999999999999</v>
+        <v>100.51</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>100.83</v>
+        <v>101.33</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>102.82</v>
+        <v>101.65</v>
       </c>
       <c r="M45" s="6" t="n">
+        <v>101.78</v>
+      </c>
+      <c r="N45" s="6" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="O45" s="6" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v>101.39</v>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v>101.01</v>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v>62.75</v>
+      </c>
+      <c r="S45" s="6" t="n">
+        <v>101.98</v>
+      </c>
+      <c r="T45" s="6" t="n">
+        <v>101.33</v>
+      </c>
+      <c r="U45" s="6" t="n">
+        <v>102.57</v>
+      </c>
+      <c r="V45" s="6" t="n">
+        <v>101.05</v>
+      </c>
+      <c r="W45" s="6" t="n">
         <v>101.24</v>
       </c>
-      <c r="N45" s="6" t="n">
-        <v>100.28</v>
-      </c>
-      <c r="O45" s="6" t="n">
-        <v>99.76000000000001</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v>98.73</v>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v>99.03</v>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v>100.07</v>
-      </c>
-      <c r="S45" s="6" t="n">
-        <v>100.01</v>
-      </c>
-      <c r="T45" s="6" t="n">
-        <v>98.98</v>
-      </c>
-      <c r="U45" s="6" t="n">
-        <v>101.22</v>
-      </c>
-      <c r="V45" s="6" t="n">
-        <v>99.81</v>
-      </c>
-      <c r="W45" s="6" t="n">
-        <v>100.56</v>
-      </c>
       <c r="X45" s="6" t="n">
-        <v>102.19</v>
+        <v>100.69</v>
       </c>
       <c r="Y45" s="6" t="n">
-        <v>101.98</v>
+        <v>100.94</v>
       </c>
       <c r="Z45" s="6" t="n">
-        <v>101.83</v>
+        <v>101.27</v>
       </c>
       <c r="AA45" s="6" t="n">
-        <v>101.79</v>
+        <v>100.94</v>
       </c>
       <c r="AB45" s="6" t="n">
-        <v>102.13</v>
+        <v>101.06</v>
       </c>
       <c r="AC45" s="6" t="n">
-        <v>102.53</v>
+        <v>101.25</v>
       </c>
       <c r="AD45" s="6" t="n">
-        <v>102.13</v>
+        <v>101.16</v>
       </c>
       <c r="AE45" s="6" t="n">
-        <v>101.58</v>
+        <v>101.06</v>
       </c>
       <c r="AF45" s="6" t="n">
-        <v>101.42</v>
+        <v>102.18</v>
       </c>
       <c r="AG45" s="6" t="n">
-        <v>100.83</v>
+        <v>104.17</v>
       </c>
       <c r="AH45" s="6" t="n">
-        <v>100.35</v>
+        <v>100.05</v>
       </c>
       <c r="AI45" s="6" t="n">
-        <v>416.29</v>
+        <v>456.27</v>
       </c>
       <c r="AJ45" s="6" t="inlineStr"/>
       <c r="AK45" s="7" t="inlineStr"/>
@@ -4936,110 +4728,110 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>RADIO NACIONAL DEL ECUADOR</t>
+          <t>RADIO MIX</t>
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>106.5</v>
+        <v>105.7</v>
       </c>
       <c r="C46" s="6" t="n">
-        <v>89.23999999999999</v>
+        <v>99.2</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>89.87</v>
+        <v>100.34</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>91.44</v>
+        <v>98.93000000000001</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>91.03</v>
+        <v>99.94</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>90.90000000000001</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>91.18000000000001</v>
+        <v>99.78</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>91.34</v>
+        <v>100.31</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>90.97</v>
+        <v>100.54</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>93.91</v>
+        <v>100.59</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>96.01000000000001</v>
+        <v>101.39</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>94.14</v>
+        <v>101.34</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>91.38</v>
+        <v>100.27</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>91.3</v>
+        <v>99.64</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>91.44</v>
+        <v>100.25</v>
       </c>
       <c r="Q46" s="6" t="n">
-        <v>91.08</v>
+        <v>100.02</v>
       </c>
       <c r="R46" s="6" t="n">
-        <v>92.5</v>
+        <v>101.94</v>
       </c>
       <c r="S46" s="6" t="n">
-        <v>91.73999999999999</v>
+        <v>101.76</v>
       </c>
       <c r="T46" s="6" t="n">
-        <v>90.98</v>
+        <v>99.89</v>
       </c>
       <c r="U46" s="6" t="n">
-        <v>91.73999999999999</v>
+        <v>100.34</v>
       </c>
       <c r="V46" s="6" t="n">
-        <v>92.16</v>
+        <v>100.52</v>
       </c>
       <c r="W46" s="6" t="n">
-        <v>94.69</v>
+        <v>100.96</v>
       </c>
       <c r="X46" s="6" t="n">
-        <v>96.97</v>
+        <v>101.15</v>
       </c>
       <c r="Y46" s="6" t="n">
-        <v>96.66</v>
+        <v>101.05</v>
       </c>
       <c r="Z46" s="6" t="n">
-        <v>96.54000000000001</v>
+        <v>101.21</v>
       </c>
       <c r="AA46" s="6" t="n">
-        <v>96.87</v>
+        <v>101.4</v>
       </c>
       <c r="AB46" s="6" t="n">
-        <v>96.81999999999999</v>
+        <v>100.88</v>
       </c>
       <c r="AC46" s="6" t="n">
-        <v>96.98999999999999</v>
+        <v>101.17</v>
       </c>
       <c r="AD46" s="6" t="n">
-        <v>96.38</v>
+        <v>101.41</v>
       </c>
       <c r="AE46" s="6" t="n">
-        <v>96.38</v>
+        <v>101.22</v>
       </c>
       <c r="AF46" s="6" t="n">
-        <v>94.83</v>
+        <v>101.94</v>
       </c>
       <c r="AG46" s="6" t="n">
-        <v>92.87</v>
+        <v>102.45</v>
       </c>
       <c r="AH46" s="6" t="n">
-        <v>93.23999999999999</v>
+        <v>100.69</v>
       </c>
       <c r="AI46" s="6" t="n">
-        <v>389.74</v>
+        <v>420.89</v>
       </c>
       <c r="AJ46" s="6" t="inlineStr"/>
       <c r="AK46" s="7" t="inlineStr"/>
@@ -5047,110 +4839,110 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>RUMBA STEREO</t>
+          <t>PLANETA F.M. STEREO</t>
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>106.9</v>
+        <v>106.1</v>
       </c>
       <c r="C47" s="6" t="n">
-        <v>82.94</v>
+        <v>96.41</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>81.58</v>
+        <v>98.17</v>
       </c>
       <c r="E47" s="6" t="n">
-        <v>75.23999999999999</v>
+        <v>99.8</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>80.34999999999999</v>
+        <v>99.06</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>81.51000000000001</v>
+        <v>99.08</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>79.69</v>
+        <v>99.69</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>83.08</v>
+        <v>98.59</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>83.83</v>
+        <v>98.34999999999999</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>85.68000000000001</v>
+        <v>100.83</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>92.92</v>
+        <v>102.82</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>88.45999999999999</v>
+        <v>101.24</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>84.20999999999999</v>
+        <v>100.28</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>84.55</v>
+        <v>99.76000000000001</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>84.43000000000001</v>
+        <v>98.73</v>
       </c>
       <c r="Q47" s="6" t="n">
-        <v>85.41</v>
+        <v>99.03</v>
       </c>
       <c r="R47" s="6" t="n">
-        <v>86.06</v>
+        <v>100.07</v>
       </c>
       <c r="S47" s="6" t="n">
-        <v>86.41</v>
+        <v>100.01</v>
       </c>
       <c r="T47" s="6" t="n">
-        <v>81.58</v>
+        <v>98.98</v>
       </c>
       <c r="U47" s="6" t="n">
-        <v>79.8</v>
+        <v>101.22</v>
       </c>
       <c r="V47" s="6" t="n">
-        <v>81.06</v>
+        <v>99.81</v>
       </c>
       <c r="W47" s="6" t="n">
-        <v>84.2</v>
+        <v>100.56</v>
       </c>
       <c r="X47" s="6" t="n">
-        <v>93.41</v>
+        <v>102.19</v>
       </c>
       <c r="Y47" s="6" t="n">
-        <v>92.89</v>
+        <v>101.98</v>
       </c>
       <c r="Z47" s="6" t="n">
-        <v>92.38</v>
+        <v>101.83</v>
       </c>
       <c r="AA47" s="6" t="n">
-        <v>92.73999999999999</v>
+        <v>101.79</v>
       </c>
       <c r="AB47" s="6" t="n">
-        <v>93.53</v>
+        <v>102.13</v>
       </c>
       <c r="AC47" s="6" t="n">
-        <v>93.33</v>
+        <v>102.53</v>
       </c>
       <c r="AD47" s="6" t="n">
-        <v>91.56999999999999</v>
+        <v>102.13</v>
       </c>
       <c r="AE47" s="6" t="n">
-        <v>93.27</v>
+        <v>101.58</v>
       </c>
       <c r="AF47" s="6" t="n">
-        <v>87.43000000000001</v>
+        <v>101.42</v>
       </c>
       <c r="AG47" s="6" t="n">
-        <v>83.7</v>
+        <v>100.83</v>
       </c>
       <c r="AH47" s="6" t="n">
-        <v>86.04000000000001</v>
+        <v>100.35</v>
       </c>
       <c r="AI47" s="6" t="n">
-        <v>363.9</v>
+        <v>416.29</v>
       </c>
       <c r="AJ47" s="6" t="inlineStr"/>
       <c r="AK47" s="7" t="inlineStr"/>
@@ -5158,722 +4950,726 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>JC RADIO</t>
+          <t>RADIO NACIONAL DEL ECUADOR</t>
         </is>
       </c>
       <c r="B48" s="6" t="n">
-        <v>107.3</v>
+        <v>106.5</v>
       </c>
       <c r="C48" s="6" t="n">
-        <v>97.02</v>
+        <v>89.23999999999999</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>97.38</v>
+        <v>89.87</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>100.17</v>
+        <v>91.44</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>100.19</v>
+        <v>91.03</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>99.47</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>99.84999999999999</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>100.17</v>
+        <v>91.34</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>99.97</v>
+        <v>90.97</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>101.72</v>
+        <v>93.91</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>103.51</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>102.89</v>
+        <v>94.14</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>101.01</v>
+        <v>91.38</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>100.34</v>
+        <v>91.3</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>100.96</v>
+        <v>91.44</v>
       </c>
       <c r="Q48" s="6" t="n">
-        <v>100.27</v>
+        <v>91.08</v>
       </c>
       <c r="R48" s="6" t="n">
-        <v>101.63</v>
+        <v>92.5</v>
       </c>
       <c r="S48" s="6" t="n">
-        <v>101.48</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="T48" s="6" t="n">
-        <v>100.31</v>
+        <v>90.98</v>
       </c>
       <c r="U48" s="6" t="n">
-        <v>101.41</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="V48" s="6" t="n">
-        <v>101.11</v>
+        <v>92.16</v>
       </c>
       <c r="W48" s="6" t="n">
-        <v>102.63</v>
+        <v>94.69</v>
       </c>
       <c r="X48" s="6" t="n">
-        <v>103.98</v>
+        <v>96.97</v>
       </c>
       <c r="Y48" s="6" t="n">
-        <v>103.92</v>
+        <v>96.66</v>
       </c>
       <c r="Z48" s="6" t="n">
-        <v>104.27</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="AA48" s="6" t="n">
-        <v>103.99</v>
+        <v>96.87</v>
       </c>
       <c r="AB48" s="6" t="n">
-        <v>104.23</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="AC48" s="6" t="n">
-        <v>103.94</v>
+        <v>96.98999999999999</v>
       </c>
       <c r="AD48" s="6" t="n">
-        <v>103.89</v>
+        <v>96.38</v>
       </c>
       <c r="AE48" s="6" t="n">
-        <v>103.47</v>
+        <v>96.38</v>
       </c>
       <c r="AF48" s="6" t="n">
-        <v>103.17</v>
+        <v>94.83</v>
       </c>
       <c r="AG48" s="6" t="n">
-        <v>102.71</v>
+        <v>92.87</v>
       </c>
       <c r="AH48" s="6" t="n">
-        <v>101.65</v>
+        <v>93.23999999999999</v>
       </c>
       <c r="AI48" s="6" t="n">
-        <v>310.71</v>
+        <v>389.74</v>
       </c>
       <c r="AJ48" s="6" t="inlineStr"/>
       <c r="AK48" s="7" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>RUMBA STEREO</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>82.94</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>81.58</v>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>75.23999999999999</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>80.34999999999999</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>81.51000000000001</v>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>79.69</v>
+      </c>
+      <c r="I49" s="6" t="n">
+        <v>83.08</v>
+      </c>
+      <c r="J49" s="6" t="n">
+        <v>83.83</v>
+      </c>
+      <c r="K49" s="6" t="n">
+        <v>85.68000000000001</v>
+      </c>
+      <c r="L49" s="6" t="n">
+        <v>92.92</v>
+      </c>
+      <c r="M49" s="6" t="n">
+        <v>88.45999999999999</v>
+      </c>
+      <c r="N49" s="6" t="n">
+        <v>84.20999999999999</v>
+      </c>
+      <c r="O49" s="6" t="n">
+        <v>84.55</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v>84.43000000000001</v>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v>85.41</v>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v>86.06</v>
+      </c>
+      <c r="S49" s="6" t="n">
+        <v>86.41</v>
+      </c>
+      <c r="T49" s="6" t="n">
+        <v>81.58</v>
+      </c>
+      <c r="U49" s="6" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="V49" s="6" t="n">
+        <v>81.06</v>
+      </c>
+      <c r="W49" s="6" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="X49" s="6" t="n">
+        <v>93.41</v>
+      </c>
+      <c r="Y49" s="6" t="n">
+        <v>92.89</v>
+      </c>
+      <c r="Z49" s="6" t="n">
+        <v>92.38</v>
+      </c>
+      <c r="AA49" s="6" t="n">
+        <v>92.73999999999999</v>
+      </c>
+      <c r="AB49" s="6" t="n">
+        <v>93.53</v>
+      </c>
+      <c r="AC49" s="6" t="n">
+        <v>93.33</v>
+      </c>
+      <c r="AD49" s="6" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="AE49" s="6" t="n">
+        <v>93.27</v>
+      </c>
+      <c r="AF49" s="6" t="n">
+        <v>87.43000000000001</v>
+      </c>
+      <c r="AG49" s="6" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="AH49" s="6" t="n">
+        <v>86.04000000000001</v>
+      </c>
+      <c r="AI49" s="6" t="n">
+        <v>363.9</v>
+      </c>
+      <c r="AJ49" s="6" t="inlineStr"/>
+      <c r="AK49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>JC RADIO</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>97.02</v>
+      </c>
+      <c r="D50" s="6" t="n">
+        <v>97.38</v>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>100.17</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>100.19</v>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>99.47</v>
+      </c>
+      <c r="H50" s="6" t="n">
+        <v>99.84999999999999</v>
+      </c>
+      <c r="I50" s="6" t="n">
+        <v>100.17</v>
+      </c>
+      <c r="J50" s="6" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="K50" s="6" t="n">
+        <v>101.72</v>
+      </c>
+      <c r="L50" s="6" t="n">
+        <v>103.51</v>
+      </c>
+      <c r="M50" s="6" t="n">
+        <v>102.89</v>
+      </c>
+      <c r="N50" s="6" t="n">
+        <v>101.01</v>
+      </c>
+      <c r="O50" s="6" t="n">
+        <v>100.34</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v>100.96</v>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v>100.27</v>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v>101.63</v>
+      </c>
+      <c r="S50" s="6" t="n">
+        <v>101.48</v>
+      </c>
+      <c r="T50" s="6" t="n">
+        <v>100.31</v>
+      </c>
+      <c r="U50" s="6" t="n">
+        <v>101.41</v>
+      </c>
+      <c r="V50" s="6" t="n">
+        <v>101.11</v>
+      </c>
+      <c r="W50" s="6" t="n">
+        <v>102.63</v>
+      </c>
+      <c r="X50" s="6" t="n">
+        <v>103.98</v>
+      </c>
+      <c r="Y50" s="6" t="n">
+        <v>103.92</v>
+      </c>
+      <c r="Z50" s="6" t="n">
+        <v>104.27</v>
+      </c>
+      <c r="AA50" s="6" t="n">
+        <v>103.99</v>
+      </c>
+      <c r="AB50" s="6" t="n">
+        <v>104.23</v>
+      </c>
+      <c r="AC50" s="6" t="n">
+        <v>103.94</v>
+      </c>
+      <c r="AD50" s="6" t="n">
+        <v>103.89</v>
+      </c>
+      <c r="AE50" s="6" t="n">
+        <v>103.47</v>
+      </c>
+      <c r="AF50" s="6" t="n">
+        <v>103.17</v>
+      </c>
+      <c r="AG50" s="6" t="n">
+        <v>102.71</v>
+      </c>
+      <c r="AH50" s="6" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="AI50" s="6" t="n">
+        <v>310.71</v>
+      </c>
+      <c r="AJ50" s="6" t="inlineStr"/>
+      <c r="AK50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>RADIO POSITIVA FM</t>
         </is>
       </c>
-      <c r="B49" s="9" t="n">
+      <c r="B51" s="9" t="n">
         <v>107.7</v>
       </c>
-      <c r="C49" s="9" t="n">
+      <c r="C51" s="9" t="n">
         <v>76.42</v>
       </c>
-      <c r="D49" s="9" t="n">
+      <c r="D51" s="9" t="n">
         <v>76.77</v>
       </c>
-      <c r="E49" s="9" t="n">
+      <c r="E51" s="9" t="n">
         <v>81.34999999999999</v>
       </c>
-      <c r="F49" s="9" t="n">
+      <c r="F51" s="9" t="n">
         <v>79.69</v>
       </c>
-      <c r="G49" s="9" t="n">
+      <c r="G51" s="9" t="n">
         <v>79.67</v>
       </c>
-      <c r="H49" s="9" t="n">
+      <c r="H51" s="9" t="n">
         <v>79.69</v>
       </c>
-      <c r="I49" s="9" t="n">
+      <c r="I51" s="9" t="n">
         <v>79.95999999999999</v>
       </c>
-      <c r="J49" s="9" t="n">
+      <c r="J51" s="9" t="n">
         <v>79.01000000000001</v>
       </c>
-      <c r="K49" s="9" t="n">
+      <c r="K51" s="9" t="n">
         <v>82.05</v>
       </c>
-      <c r="L49" s="9" t="n">
+      <c r="L51" s="9" t="n">
         <v>84.64</v>
       </c>
-      <c r="M49" s="9" t="n">
+      <c r="M51" s="9" t="n">
         <v>81.73</v>
       </c>
-      <c r="N49" s="9" t="n">
+      <c r="N51" s="9" t="n">
         <v>79.73</v>
       </c>
-      <c r="O49" s="9" t="n">
+      <c r="O51" s="9" t="n">
         <v>78.31999999999999</v>
       </c>
-      <c r="P49" s="9" t="n">
+      <c r="P51" s="9" t="n">
         <v>79.45999999999999</v>
       </c>
-      <c r="Q49" s="9" t="n">
+      <c r="Q51" s="9" t="n">
         <v>79.41</v>
       </c>
-      <c r="R49" s="9" t="n">
+      <c r="R51" s="9" t="n">
         <v>79.73999999999999</v>
       </c>
-      <c r="S49" s="9" t="n">
+      <c r="S51" s="9" t="n">
         <v>79.73</v>
       </c>
-      <c r="T49" s="9" t="n">
+      <c r="T51" s="9" t="n">
         <v>79.68000000000001</v>
       </c>
-      <c r="U49" s="9" t="n">
+      <c r="U51" s="9" t="n">
         <v>80.61</v>
       </c>
-      <c r="V49" s="9" t="n">
+      <c r="V51" s="9" t="n">
         <v>79.16</v>
       </c>
-      <c r="W49" s="9" t="n">
+      <c r="W51" s="9" t="n">
         <v>81.95999999999999</v>
       </c>
-      <c r="X49" s="9" t="n">
+      <c r="X51" s="9" t="n">
         <v>84.26000000000001</v>
       </c>
-      <c r="Y49" s="9" t="n">
+      <c r="Y51" s="9" t="n">
         <v>83.81</v>
       </c>
-      <c r="Z49" s="9" t="n">
+      <c r="Z51" s="9" t="n">
         <v>84.69</v>
       </c>
-      <c r="AA49" s="9" t="n">
+      <c r="AA51" s="9" t="n">
         <v>84.03</v>
       </c>
-      <c r="AB49" s="9" t="n">
+      <c r="AB51" s="9" t="n">
         <v>83.94</v>
       </c>
-      <c r="AC49" s="9" t="n">
+      <c r="AC51" s="9" t="n">
         <v>83.68000000000001</v>
       </c>
-      <c r="AD49" s="9" t="n">
+      <c r="AD51" s="9" t="n">
         <v>83.81999999999999</v>
       </c>
-      <c r="AE49" s="9" t="n">
+      <c r="AE51" s="9" t="n">
         <v>84.41</v>
       </c>
-      <c r="AF49" s="9" t="n">
+      <c r="AF51" s="9" t="n">
         <v>82.03</v>
       </c>
-      <c r="AG49" s="9" t="n">
+      <c r="AG51" s="9" t="n">
         <v>79.73</v>
       </c>
-      <c r="AH49" s="9" t="n">
+      <c r="AH51" s="9" t="n">
         <v>81.06999999999999</v>
       </c>
-      <c r="AI49" s="9" t="n">
+      <c r="AI51" s="9" t="n">
         <v>264.88</v>
       </c>
-      <c r="AJ49" s="9" t="inlineStr"/>
-      <c r="AK49" s="10" t="inlineStr"/>
-    </row>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>AGENCIA DE REGULACIÓN Y CONTROL DE LAS TELECOMUNICACIONES</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>COORDINACIÓN ZONAL 6</t>
-        </is>
-      </c>
-    </row>
+      <c r="AJ51" s="9" t="inlineStr"/>
+      <c r="AK51" s="10" t="inlineStr"/>
+    </row>
+    <row r="52"/>
+    <row r="53"/>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>ESTACIÓN DE COMPROBACIÓN TÉCNICA</t>
+          <t>AGENCIA DE REGULACIÓN Y CONTROL DE LAS TELECOMUNICACIONES</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>FORMULARIO DE CONTROL MENSUAL DE TV</t>
+          <t>COORDINACIÓN ZONAL 6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>CIUDAD:LOJA</t>
+          <t>ESTACIÓN DE COMPROBACIÓN TÉCNICA</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>PERIODO: JULIO</t>
+          <t>FORMULARIO DE CONTROL MENSUAL DE TV</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
+          <t>CIUDAD:LOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>PERIODO: JULIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
           <t>FECHA PRESENTACIÓN: 27/08/2025</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="45" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="61" ht="45" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>ESTACION</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>Frecuencia (MHz)</t>
         </is>
       </c>
-      <c r="C59" s="3" t="n">
+      <c r="C61" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D59" s="3" t="n">
+      <c r="D61" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E59" s="3" t="n">
+      <c r="E61" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F59" s="3" t="n">
+      <c r="F61" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G59" s="3" t="n">
+      <c r="G61" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H59" s="3" t="n">
+      <c r="H61" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="I59" s="3" t="n">
+      <c r="I61" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="J59" s="3" t="n">
+      <c r="J61" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="K59" s="3" t="n">
+      <c r="K61" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="L59" s="3" t="n">
+      <c r="L61" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M59" s="3" t="n">
+      <c r="M61" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="N59" s="3" t="n">
+      <c r="N61" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="O59" s="3" t="n">
+      <c r="O61" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="P59" s="3" t="n">
+      <c r="P61" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="Q59" s="3" t="n">
+      <c r="Q61" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="R59" s="3" t="n">
+      <c r="R61" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="S59" s="3" t="n">
+      <c r="S61" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="T59" s="3" t="n">
+      <c r="T61" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="U59" s="3" t="n">
+      <c r="U61" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="V59" s="3" t="n">
+      <c r="V61" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="W59" s="3" t="n">
+      <c r="W61" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="X59" s="3" t="n">
+      <c r="X61" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="Y59" s="3" t="n">
+      <c r="Y61" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="Z59" s="3" t="n">
+      <c r="Z61" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="AA59" s="3" t="n">
+      <c r="AA61" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="AB59" s="3" t="n">
+      <c r="AB61" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="AC59" s="3" t="n">
+      <c r="AC61" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="AD59" s="3" t="n">
+      <c r="AD61" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="AE59" s="3" t="n">
+      <c r="AE61" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="AF59" s="3" t="n">
+      <c r="AF61" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="AG59" s="3" t="n">
+      <c r="AG61" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="AH59" s="3" t="inlineStr">
+      <c r="AH61" s="3" t="inlineStr">
         <is>
           <t>Promedio
 (dBuV/m)</t>
         </is>
       </c>
-      <c r="AI59" s="3" t="inlineStr">
+      <c r="AI61" s="3" t="inlineStr">
         <is>
           <t>Medición Manual
 AB(KHz) o NIVEL
 (dBµV/m)</t>
         </is>
       </c>
-      <c r="AJ59" s="3" t="inlineStr">
+      <c r="AJ61" s="3" t="inlineStr">
         <is>
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK59" s="4" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>CORPORACION ECUATORIANA DE</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="n">
-        <v>55.25</v>
-      </c>
-      <c r="C60" s="6" t="n">
-        <v>92.58</v>
-      </c>
-      <c r="D60" s="6" t="n">
-        <v>92.59999999999999</v>
-      </c>
-      <c r="E60" s="6" t="n">
-        <v>92.47</v>
-      </c>
-      <c r="F60" s="6" t="n">
-        <v>92.73</v>
-      </c>
-      <c r="G60" s="6" t="n">
-        <v>91.95</v>
-      </c>
-      <c r="H60" s="6" t="n">
-        <v>91.48</v>
-      </c>
-      <c r="I60" s="6" t="n">
-        <v>91.53</v>
-      </c>
-      <c r="J60" s="6" t="n">
-        <v>92.33</v>
-      </c>
-      <c r="K60" s="6" t="n">
-        <v>88.68000000000001</v>
-      </c>
-      <c r="L60" s="6" t="n">
-        <v>84.98</v>
-      </c>
-      <c r="M60" s="6" t="n">
-        <v>88.31999999999999</v>
-      </c>
-      <c r="N60" s="6" t="n">
-        <v>92.38</v>
-      </c>
-      <c r="O60" s="6" t="n">
-        <v>91.84999999999999</v>
-      </c>
-      <c r="P60" s="6" t="n">
-        <v>91.28</v>
-      </c>
-      <c r="Q60" s="6" t="n">
-        <v>91.65000000000001</v>
-      </c>
-      <c r="R60" s="6" t="n">
-        <v>92.25</v>
-      </c>
-      <c r="S60" s="6" t="n">
-        <v>92.17</v>
-      </c>
-      <c r="T60" s="6" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="U60" s="6" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="V60" s="6" t="n">
-        <v>92.02</v>
-      </c>
-      <c r="W60" s="6" t="n">
-        <v>88.45</v>
-      </c>
-      <c r="X60" s="6" t="n">
-        <v>84.58</v>
-      </c>
-      <c r="Y60" s="6" t="n">
-        <v>84.7</v>
-      </c>
-      <c r="Z60" s="6" t="n">
-        <v>84.90000000000001</v>
-      </c>
-      <c r="AA60" s="6" t="n">
-        <v>84.73</v>
-      </c>
-      <c r="AB60" s="6" t="n">
-        <v>84.53</v>
-      </c>
-      <c r="AC60" s="6" t="n">
-        <v>84.45</v>
-      </c>
-      <c r="AD60" s="6" t="n">
-        <v>84.92</v>
-      </c>
-      <c r="AE60" s="6" t="n">
-        <v>85.40000000000001</v>
-      </c>
-      <c r="AF60" s="6" t="n">
-        <v>89.3</v>
-      </c>
-      <c r="AG60" s="6" t="n">
-        <v>92.92</v>
-      </c>
-      <c r="AH60" s="6" t="n">
-        <v>89.59999999999999</v>
-      </c>
-      <c r="AI60" s="6" t="inlineStr"/>
-      <c r="AJ60" s="6" t="inlineStr"/>
-      <c r="AK60" s="7" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>UV TELEVISION</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="n">
-        <v>67.25</v>
-      </c>
-      <c r="C61" s="6" t="n">
-        <v>93.25</v>
-      </c>
-      <c r="D61" s="6" t="n">
-        <v>93.33</v>
-      </c>
-      <c r="E61" s="6" t="n">
-        <v>92.05</v>
-      </c>
-      <c r="F61" s="6" t="n">
-        <v>93.31999999999999</v>
-      </c>
-      <c r="G61" s="6" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="H61" s="6" t="n">
-        <v>93.18000000000001</v>
-      </c>
-      <c r="I61" s="6" t="n">
-        <v>92.56999999999999</v>
-      </c>
-      <c r="J61" s="6" t="n">
-        <v>93.27</v>
-      </c>
-      <c r="K61" s="6" t="n">
-        <v>84.75</v>
-      </c>
-      <c r="L61" s="6" t="n">
-        <v>79.81999999999999</v>
-      </c>
-      <c r="M61" s="6" t="n">
-        <v>87.84999999999999</v>
-      </c>
-      <c r="N61" s="6" t="n">
-        <v>91.63</v>
-      </c>
-      <c r="O61" s="6" t="n">
-        <v>91.15000000000001</v>
-      </c>
-      <c r="P61" s="6" t="n">
-        <v>89.13</v>
-      </c>
-      <c r="Q61" s="6" t="n">
-        <v>89.98</v>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v>94.06999999999999</v>
-      </c>
-      <c r="S61" s="6" t="n">
-        <v>94.25</v>
-      </c>
-      <c r="T61" s="6" t="n">
-        <v>92.77</v>
-      </c>
-      <c r="U61" s="6" t="n">
-        <v>93.7</v>
-      </c>
-      <c r="V61" s="6" t="n">
-        <v>91.33</v>
-      </c>
-      <c r="W61" s="6" t="n">
-        <v>87.59999999999999</v>
-      </c>
-      <c r="X61" s="6" t="n">
-        <v>86.08</v>
-      </c>
-      <c r="Y61" s="6" t="n">
-        <v>85.33</v>
-      </c>
-      <c r="Z61" s="6" t="n">
-        <v>81.62</v>
-      </c>
-      <c r="AA61" s="6" t="n">
-        <v>84.37</v>
-      </c>
-      <c r="AB61" s="6" t="n">
-        <v>86.25</v>
-      </c>
-      <c r="AC61" s="6" t="n">
-        <v>83.97</v>
-      </c>
-      <c r="AD61" s="6" t="n">
-        <v>79.47</v>
-      </c>
-      <c r="AE61" s="6" t="n">
-        <v>83.92</v>
-      </c>
-      <c r="AF61" s="6" t="n">
-        <v>89.75</v>
-      </c>
-      <c r="AG61" s="6" t="n">
-        <v>93.13</v>
-      </c>
-      <c r="AH61" s="6" t="n">
-        <v>89.2</v>
-      </c>
-      <c r="AI61" s="6" t="inlineStr"/>
-      <c r="AJ61" s="6" t="inlineStr"/>
-      <c r="AK61" s="7" t="n"/>
+      <c r="AK61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>TELEAMAZONAS</t>
+          <t>CORPORACION ECUATORIANA DE</t>
         </is>
       </c>
       <c r="B62" s="6" t="n">
-        <v>77.25</v>
+        <v>55.25</v>
       </c>
       <c r="C62" s="6" t="n">
-        <v>78.43000000000001</v>
+        <v>92.58</v>
       </c>
       <c r="D62" s="6" t="n">
-        <v>77.95</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>82.13</v>
+        <v>92.47</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>81</v>
+        <v>92.73</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>88.90000000000001</v>
+        <v>91.95</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>86.87</v>
+        <v>91.48</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>88.59999999999999</v>
+        <v>91.53</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>85.5</v>
+        <v>92.33</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>84.95</v>
+        <v>88.68000000000001</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>85.81999999999999</v>
+        <v>84.98</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>88.28</v>
+        <v>88.31999999999999</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>86.15000000000001</v>
+        <v>92.38</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>88.15000000000001</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="P62" s="6" t="n">
-        <v>88.84999999999999</v>
+        <v>91.28</v>
       </c>
       <c r="Q62" s="6" t="n">
-        <v>83.38</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="R62" s="6" t="n">
-        <v>86.23</v>
+        <v>92.25</v>
       </c>
       <c r="S62" s="6" t="n">
-        <v>86.43000000000001</v>
+        <v>92.17</v>
       </c>
       <c r="T62" s="6" t="n">
-        <v>81.55</v>
+        <v>92.7</v>
       </c>
       <c r="U62" s="6" t="n">
-        <v>82.25</v>
+        <v>92.8</v>
       </c>
       <c r="V62" s="6" t="n">
-        <v>88.13</v>
+        <v>92.02</v>
       </c>
       <c r="W62" s="6" t="n">
-        <v>87.98</v>
+        <v>88.45</v>
       </c>
       <c r="X62" s="6" t="n">
-        <v>85.22</v>
+        <v>84.58</v>
       </c>
       <c r="Y62" s="6" t="n">
-        <v>82.53</v>
+        <v>84.7</v>
       </c>
       <c r="Z62" s="6" t="n">
-        <v>84.78</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="AA62" s="6" t="n">
-        <v>75.37</v>
+        <v>84.73</v>
       </c>
       <c r="AB62" s="6" t="n">
-        <v>75.09999999999999</v>
+        <v>84.53</v>
       </c>
       <c r="AC62" s="6" t="n">
-        <v>77.83</v>
+        <v>84.45</v>
       </c>
       <c r="AD62" s="6" t="n">
-        <v>80.78</v>
+        <v>84.92</v>
       </c>
       <c r="AE62" s="6" t="n">
-        <v>73.13</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="AF62" s="6" t="n">
-        <v>71</v>
+        <v>89.3</v>
       </c>
       <c r="AG62" s="6" t="n">
-        <v>81.65000000000001</v>
+        <v>92.92</v>
       </c>
       <c r="AH62" s="6" t="n">
-        <v>83.06</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="AI62" s="6" t="inlineStr"/>
       <c r="AJ62" s="6" t="inlineStr"/>
@@ -5882,107 +5678,107 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>ECUADOR TV</t>
+          <t>UV TELEVISION</t>
         </is>
       </c>
       <c r="B63" s="6" t="n">
-        <v>175.25</v>
+        <v>67.25</v>
       </c>
       <c r="C63" s="6" t="n">
-        <v>91.97</v>
+        <v>93.25</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>92.06999999999999</v>
+        <v>93.33</v>
       </c>
       <c r="E63" s="6" t="n">
-        <v>92.53</v>
+        <v>92.05</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>94.15000000000001</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="G63" s="6" t="n">
-        <v>94.17</v>
+        <v>92.2</v>
       </c>
       <c r="H63" s="6" t="n">
-        <v>94.52</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="I63" s="6" t="n">
-        <v>94.59999999999999</v>
+        <v>92.56999999999999</v>
       </c>
       <c r="J63" s="6" t="n">
-        <v>94.53</v>
+        <v>93.27</v>
       </c>
       <c r="K63" s="6" t="n">
-        <v>92.12</v>
+        <v>84.75</v>
       </c>
       <c r="L63" s="6" t="n">
-        <v>88.5</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="M63" s="6" t="n">
-        <v>89.97</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="N63" s="6" t="n">
-        <v>94.43000000000001</v>
+        <v>91.63</v>
       </c>
       <c r="O63" s="6" t="n">
-        <v>93.95</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="P63" s="6" t="n">
-        <v>93.98</v>
+        <v>89.13</v>
       </c>
       <c r="Q63" s="6" t="n">
-        <v>94.02</v>
+        <v>89.98</v>
       </c>
       <c r="R63" s="6" t="n">
-        <v>95</v>
+        <v>94.06999999999999</v>
       </c>
       <c r="S63" s="6" t="n">
-        <v>95.06999999999999</v>
+        <v>94.25</v>
       </c>
       <c r="T63" s="6" t="n">
-        <v>91.95</v>
+        <v>92.77</v>
       </c>
       <c r="U63" s="6" t="n">
-        <v>95.92</v>
+        <v>93.7</v>
       </c>
       <c r="V63" s="6" t="n">
-        <v>94.37</v>
+        <v>91.33</v>
       </c>
       <c r="W63" s="6" t="n">
-        <v>92.59999999999999</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="X63" s="6" t="n">
-        <v>90.56999999999999</v>
+        <v>86.08</v>
       </c>
       <c r="Y63" s="6" t="n">
-        <v>90.02</v>
+        <v>85.33</v>
       </c>
       <c r="Z63" s="6" t="n">
-        <v>90.7</v>
+        <v>81.62</v>
       </c>
       <c r="AA63" s="6" t="n">
-        <v>89.25</v>
+        <v>84.37</v>
       </c>
       <c r="AB63" s="6" t="n">
-        <v>90.03</v>
+        <v>86.25</v>
       </c>
       <c r="AC63" s="6" t="n">
-        <v>90.34999999999999</v>
+        <v>83.97</v>
       </c>
       <c r="AD63" s="6" t="n">
-        <v>89.88</v>
+        <v>79.47</v>
       </c>
       <c r="AE63" s="6" t="n">
-        <v>89.15000000000001</v>
+        <v>83.92</v>
       </c>
       <c r="AF63" s="6" t="n">
-        <v>91.33</v>
+        <v>89.75</v>
       </c>
       <c r="AG63" s="6" t="n">
-        <v>95.03</v>
+        <v>93.13</v>
       </c>
       <c r="AH63" s="6" t="n">
-        <v>92.47</v>
+        <v>89.2</v>
       </c>
       <c r="AI63" s="6" t="inlineStr"/>
       <c r="AJ63" s="6" t="inlineStr"/>
@@ -5991,107 +5787,107 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>CADENA ECUATORIANA DE TELE</t>
+          <t>TELEAMAZONAS</t>
         </is>
       </c>
       <c r="B64" s="6" t="n">
-        <v>181.25</v>
+        <v>77.25</v>
       </c>
       <c r="C64" s="6" t="n">
-        <v>80.13</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>79.77</v>
+        <v>77.95</v>
       </c>
       <c r="E64" s="6" t="n">
-        <v>77.02</v>
+        <v>82.13</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>78.45</v>
+        <v>81</v>
       </c>
       <c r="G64" s="6" t="n">
-        <v>78.38</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H64" s="6" t="n">
-        <v>79.77</v>
+        <v>86.87</v>
       </c>
       <c r="I64" s="6" t="n">
-        <v>79.95</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>80.28</v>
+        <v>85.5</v>
       </c>
       <c r="K64" s="6" t="n">
-        <v>79.28</v>
+        <v>84.95</v>
       </c>
       <c r="L64" s="6" t="n">
-        <v>78.72</v>
+        <v>85.81999999999999</v>
       </c>
       <c r="M64" s="6" t="n">
-        <v>77.90000000000001</v>
+        <v>88.28</v>
       </c>
       <c r="N64" s="6" t="n">
-        <v>81.45</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="O64" s="6" t="n">
-        <v>80.13</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="P64" s="6" t="n">
-        <v>81</v>
+        <v>88.84999999999999</v>
       </c>
       <c r="Q64" s="6" t="n">
-        <v>81.15000000000001</v>
+        <v>83.38</v>
       </c>
       <c r="R64" s="6" t="n">
-        <v>82.13</v>
+        <v>86.23</v>
       </c>
       <c r="S64" s="6" t="n">
-        <v>81.15000000000001</v>
+        <v>86.43000000000001</v>
       </c>
       <c r="T64" s="6" t="n">
-        <v>80.42</v>
+        <v>81.55</v>
       </c>
       <c r="U64" s="6" t="n">
-        <v>79.87</v>
+        <v>82.25</v>
       </c>
       <c r="V64" s="6" t="n">
-        <v>84.87</v>
+        <v>88.13</v>
       </c>
       <c r="W64" s="6" t="n">
-        <v>82.87</v>
+        <v>87.98</v>
       </c>
       <c r="X64" s="6" t="n">
-        <v>80.48</v>
+        <v>85.22</v>
       </c>
       <c r="Y64" s="6" t="n">
-        <v>82.17</v>
+        <v>82.53</v>
       </c>
       <c r="Z64" s="6" t="n">
-        <v>83.45</v>
+        <v>84.78</v>
       </c>
       <c r="AA64" s="6" t="n">
-        <v>80.7</v>
+        <v>75.37</v>
       </c>
       <c r="AB64" s="6" t="n">
-        <v>81.31999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="AC64" s="6" t="n">
+        <v>77.83</v>
+      </c>
+      <c r="AD64" s="6" t="n">
+        <v>80.78</v>
+      </c>
+      <c r="AE64" s="6" t="n">
+        <v>73.13</v>
+      </c>
+      <c r="AF64" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="AG64" s="6" t="n">
         <v>81.65000000000001</v>
       </c>
-      <c r="AD64" s="6" t="n">
-        <v>82.7</v>
-      </c>
-      <c r="AE64" s="6" t="n">
-        <v>83.06999999999999</v>
-      </c>
-      <c r="AF64" s="6" t="n">
-        <v>84.22</v>
-      </c>
-      <c r="AG64" s="6" t="n">
-        <v>86.5</v>
-      </c>
       <c r="AH64" s="6" t="n">
-        <v>81</v>
+        <v>83.06</v>
       </c>
       <c r="AI64" s="6" t="inlineStr"/>
       <c r="AJ64" s="6" t="inlineStr"/>
@@ -6100,107 +5896,107 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>RED TELESISTEMA (R.T.S)</t>
+          <t>ECUADOR TV</t>
         </is>
       </c>
       <c r="B65" s="6" t="n">
-        <v>187.25</v>
+        <v>175.25</v>
       </c>
       <c r="C65" s="6" t="n">
-        <v>88</v>
+        <v>91.97</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>87.87</v>
+        <v>92.06999999999999</v>
       </c>
       <c r="E65" s="6" t="n">
-        <v>90.37</v>
+        <v>92.53</v>
       </c>
       <c r="F65" s="6" t="n">
+        <v>94.15000000000001</v>
+      </c>
+      <c r="G65" s="6" t="n">
+        <v>94.17</v>
+      </c>
+      <c r="H65" s="6" t="n">
+        <v>94.52</v>
+      </c>
+      <c r="I65" s="6" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="J65" s="6" t="n">
+        <v>94.53</v>
+      </c>
+      <c r="K65" s="6" t="n">
+        <v>92.12</v>
+      </c>
+      <c r="L65" s="6" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="M65" s="6" t="n">
+        <v>89.97</v>
+      </c>
+      <c r="N65" s="6" t="n">
+        <v>94.43000000000001</v>
+      </c>
+      <c r="O65" s="6" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="P65" s="6" t="n">
+        <v>93.98</v>
+      </c>
+      <c r="Q65" s="6" t="n">
+        <v>94.02</v>
+      </c>
+      <c r="R65" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="S65" s="6" t="n">
+        <v>95.06999999999999</v>
+      </c>
+      <c r="T65" s="6" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="U65" s="6" t="n">
+        <v>95.92</v>
+      </c>
+      <c r="V65" s="6" t="n">
+        <v>94.37</v>
+      </c>
+      <c r="W65" s="6" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="X65" s="6" t="n">
+        <v>90.56999999999999</v>
+      </c>
+      <c r="Y65" s="6" t="n">
+        <v>90.02</v>
+      </c>
+      <c r="Z65" s="6" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="AA65" s="6" t="n">
+        <v>89.25</v>
+      </c>
+      <c r="AB65" s="6" t="n">
+        <v>90.03</v>
+      </c>
+      <c r="AC65" s="6" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="AD65" s="6" t="n">
+        <v>89.88</v>
+      </c>
+      <c r="AE65" s="6" t="n">
         <v>89.15000000000001</v>
       </c>
-      <c r="G65" s="6" t="n">
-        <v>89.31999999999999</v>
-      </c>
-      <c r="H65" s="6" t="n">
-        <v>89.45</v>
-      </c>
-      <c r="I65" s="6" t="n">
-        <v>89.03</v>
-      </c>
-      <c r="J65" s="6" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="K65" s="6" t="n">
-        <v>91.17</v>
-      </c>
-      <c r="L65" s="6" t="n">
-        <v>93.93000000000001</v>
-      </c>
-      <c r="M65" s="6" t="n">
-        <v>92.55</v>
-      </c>
-      <c r="N65" s="6" t="n">
-        <v>89.2</v>
-      </c>
-      <c r="O65" s="6" t="n">
-        <v>89.72</v>
-      </c>
-      <c r="P65" s="6" t="n">
-        <v>90.22</v>
-      </c>
-      <c r="Q65" s="6" t="n">
-        <v>90.2</v>
-      </c>
-      <c r="R65" s="6" t="n">
-        <v>89.56999999999999</v>
-      </c>
-      <c r="S65" s="6" t="n">
-        <v>89.03</v>
-      </c>
-      <c r="T65" s="6" t="n">
-        <v>89.34999999999999</v>
-      </c>
-      <c r="U65" s="6" t="n">
-        <v>89.78</v>
-      </c>
-      <c r="V65" s="6" t="n">
-        <v>89.78</v>
-      </c>
-      <c r="W65" s="6" t="n">
-        <v>91.87</v>
-      </c>
-      <c r="X65" s="6" t="n">
-        <v>94.08</v>
-      </c>
-      <c r="Y65" s="6" t="n">
-        <v>94.45</v>
-      </c>
-      <c r="Z65" s="6" t="n">
-        <v>94.65000000000001</v>
-      </c>
-      <c r="AA65" s="6" t="n">
-        <v>94</v>
-      </c>
-      <c r="AB65" s="6" t="n">
-        <v>93.73</v>
-      </c>
-      <c r="AC65" s="6" t="n">
-        <v>93.92</v>
-      </c>
-      <c r="AD65" s="6" t="n">
-        <v>94.31999999999999</v>
-      </c>
-      <c r="AE65" s="6" t="n">
-        <v>94.02</v>
-      </c>
       <c r="AF65" s="6" t="n">
-        <v>92.17</v>
+        <v>91.33</v>
       </c>
       <c r="AG65" s="6" t="n">
-        <v>90.22</v>
+        <v>95.03</v>
       </c>
       <c r="AH65" s="6" t="n">
-        <v>91.06999999999999</v>
+        <v>92.47</v>
       </c>
       <c r="AI65" s="6" t="inlineStr"/>
       <c r="AJ65" s="6" t="inlineStr"/>
@@ -6209,107 +6005,107 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>TELEVISION DEL PACIFICO</t>
+          <t>CADENA ECUATORIANA DE TELE</t>
         </is>
       </c>
       <c r="B66" s="6" t="n">
-        <v>199.25</v>
+        <v>181.25</v>
       </c>
       <c r="C66" s="6" t="n">
-        <v>67.97</v>
+        <v>80.13</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>67.75</v>
+        <v>79.77</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>70.25</v>
+        <v>77.02</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>70.18000000000001</v>
+        <v>78.45</v>
       </c>
       <c r="G66" s="6" t="n">
-        <v>69.31999999999999</v>
+        <v>78.38</v>
       </c>
       <c r="H66" s="6" t="n">
-        <v>70.72</v>
+        <v>79.77</v>
       </c>
       <c r="I66" s="6" t="n">
-        <v>71.78</v>
+        <v>79.95</v>
       </c>
       <c r="J66" s="6" t="n">
-        <v>69.59999999999999</v>
+        <v>80.28</v>
       </c>
       <c r="K66" s="6" t="n">
-        <v>68.25</v>
+        <v>79.28</v>
       </c>
       <c r="L66" s="6" t="n">
-        <v>65.83</v>
+        <v>78.72</v>
       </c>
       <c r="M66" s="6" t="n">
-        <v>67.34999999999999</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="N66" s="6" t="n">
-        <v>72.52</v>
+        <v>81.45</v>
       </c>
       <c r="O66" s="6" t="n">
-        <v>71.33</v>
+        <v>80.13</v>
       </c>
       <c r="P66" s="6" t="n">
-        <v>72.13</v>
+        <v>81</v>
       </c>
       <c r="Q66" s="6" t="n">
-        <v>70.43000000000001</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="R66" s="6" t="n">
-        <v>70.83</v>
+        <v>82.13</v>
       </c>
       <c r="S66" s="6" t="n">
-        <v>72.3</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="T66" s="6" t="n">
-        <v>69.37</v>
+        <v>80.42</v>
       </c>
       <c r="U66" s="6" t="n">
-        <v>71.59999999999999</v>
+        <v>79.87</v>
       </c>
       <c r="V66" s="6" t="n">
-        <v>70.43000000000001</v>
+        <v>84.87</v>
       </c>
       <c r="W66" s="6" t="n">
-        <v>68.2</v>
+        <v>82.87</v>
       </c>
       <c r="X66" s="6" t="n">
-        <v>65.47</v>
+        <v>80.48</v>
       </c>
       <c r="Y66" s="6" t="n">
-        <v>64.65000000000001</v>
+        <v>82.17</v>
       </c>
       <c r="Z66" s="6" t="n">
-        <v>65.03</v>
+        <v>83.45</v>
       </c>
       <c r="AA66" s="6" t="n">
-        <v>64.8</v>
+        <v>80.7</v>
       </c>
       <c r="AB66" s="6" t="n">
-        <v>65.42</v>
+        <v>81.31999999999999</v>
       </c>
       <c r="AC66" s="6" t="n">
-        <v>65.77</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="AD66" s="6" t="n">
-        <v>65.05</v>
+        <v>82.7</v>
       </c>
       <c r="AE66" s="6" t="n">
-        <v>66.34999999999999</v>
+        <v>83.06999999999999</v>
       </c>
       <c r="AF66" s="6" t="n">
-        <v>69.90000000000001</v>
+        <v>84.22</v>
       </c>
       <c r="AG66" s="6" t="n">
-        <v>74.7</v>
+        <v>86.5</v>
       </c>
       <c r="AH66" s="6" t="n">
-        <v>68.88</v>
+        <v>81</v>
       </c>
       <c r="AI66" s="6" t="inlineStr"/>
       <c r="AJ66" s="6" t="inlineStr"/>
@@ -6318,107 +6114,107 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>ECOTEL</t>
+          <t>RED TELESISTEMA (R.T.S)</t>
         </is>
       </c>
       <c r="B67" s="6" t="n">
-        <v>519.25</v>
+        <v>187.25</v>
       </c>
       <c r="C67" s="6" t="n">
-        <v>84.31999999999999</v>
+        <v>88</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>83.48</v>
+        <v>87.87</v>
       </c>
       <c r="E67" s="6" t="n">
-        <v>83.25</v>
+        <v>90.37</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>83.02</v>
+        <v>89.15000000000001</v>
       </c>
       <c r="G67" s="6" t="n">
-        <v>83.56999999999999</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="H67" s="6" t="n">
-        <v>83.67</v>
+        <v>89.45</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>84.25</v>
+        <v>89.03</v>
       </c>
       <c r="J67" s="6" t="n">
-        <v>83.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="K67" s="6" t="n">
-        <v>81.27</v>
+        <v>91.17</v>
       </c>
       <c r="L67" s="6" t="n">
-        <v>79.15000000000001</v>
+        <v>93.93000000000001</v>
       </c>
       <c r="M67" s="6" t="n">
-        <v>82</v>
+        <v>92.55</v>
       </c>
       <c r="N67" s="6" t="n">
-        <v>82.68000000000001</v>
+        <v>89.2</v>
       </c>
       <c r="O67" s="6" t="n">
-        <v>83.15000000000001</v>
+        <v>89.72</v>
       </c>
       <c r="P67" s="6" t="n">
-        <v>83.65000000000001</v>
+        <v>90.22</v>
       </c>
       <c r="Q67" s="6" t="n">
-        <v>83.8</v>
+        <v>90.2</v>
       </c>
       <c r="R67" s="6" t="n">
-        <v>83.75</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="S67" s="6" t="n">
-        <v>83.84999999999999</v>
+        <v>89.03</v>
       </c>
       <c r="T67" s="6" t="n">
-        <v>83.2</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="U67" s="6" t="n">
-        <v>83.33</v>
+        <v>89.78</v>
       </c>
       <c r="V67" s="6" t="n">
-        <v>83.95</v>
+        <v>89.78</v>
       </c>
       <c r="W67" s="6" t="n">
-        <v>82.31999999999999</v>
+        <v>91.87</v>
       </c>
       <c r="X67" s="6" t="n">
-        <v>78.5</v>
+        <v>94.08</v>
       </c>
       <c r="Y67" s="6" t="n">
-        <v>77.97</v>
+        <v>94.45</v>
       </c>
       <c r="Z67" s="6" t="n">
-        <v>75.37</v>
+        <v>94.65000000000001</v>
       </c>
       <c r="AA67" s="6" t="n">
-        <v>80.13</v>
+        <v>94</v>
       </c>
       <c r="AB67" s="6" t="n">
-        <v>79.25</v>
+        <v>93.73</v>
       </c>
       <c r="AC67" s="6" t="n">
-        <v>79.8</v>
+        <v>93.92</v>
       </c>
       <c r="AD67" s="6" t="n">
-        <v>77.13</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="AE67" s="6" t="n">
-        <v>78.34999999999999</v>
+        <v>94.02</v>
       </c>
       <c r="AF67" s="6" t="n">
-        <v>81.37</v>
+        <v>92.17</v>
       </c>
       <c r="AG67" s="6" t="n">
-        <v>84.68000000000001</v>
+        <v>90.22</v>
       </c>
       <c r="AH67" s="6" t="n">
-        <v>81.86</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="AI67" s="6" t="inlineStr"/>
       <c r="AJ67" s="6" t="inlineStr"/>
@@ -6427,107 +6223,107 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>TELERAMA</t>
+          <t>TELEVISION DEL PACIFICO</t>
         </is>
       </c>
       <c r="B68" s="6" t="n">
-        <v>531.25</v>
+        <v>199.25</v>
       </c>
       <c r="C68" s="6" t="n">
-        <v>28.37</v>
+        <v>67.97</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>29.4</v>
+        <v>67.75</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>27.83</v>
+        <v>70.25</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>28.55</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="G68" s="6" t="n">
-        <v>28.55</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="H68" s="6" t="n">
-        <v>27.95</v>
+        <v>70.72</v>
       </c>
       <c r="I68" s="6" t="n">
-        <v>28</v>
+        <v>71.78</v>
       </c>
       <c r="J68" s="6" t="n">
-        <v>28.12</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K68" s="6" t="n">
-        <v>33.42</v>
+        <v>68.25</v>
       </c>
       <c r="L68" s="6" t="n">
-        <v>38.92</v>
+        <v>65.83</v>
       </c>
       <c r="M68" s="6" t="n">
-        <v>34.12</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="N68" s="6" t="n">
-        <v>28.75</v>
+        <v>72.52</v>
       </c>
       <c r="O68" s="6" t="n">
-        <v>28.63</v>
+        <v>71.33</v>
       </c>
       <c r="P68" s="6" t="n">
-        <v>27.68</v>
+        <v>72.13</v>
       </c>
       <c r="Q68" s="6" t="n">
-        <v>28.35</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="R68" s="6" t="n">
-        <v>27.93</v>
+        <v>70.83</v>
       </c>
       <c r="S68" s="6" t="n">
-        <v>28.22</v>
+        <v>72.3</v>
       </c>
       <c r="T68" s="6" t="n">
-        <v>29</v>
+        <v>69.37</v>
       </c>
       <c r="U68" s="6" t="n">
-        <v>28.68</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="V68" s="6" t="n">
-        <v>27.77</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="W68" s="6" t="n">
-        <v>33.18</v>
+        <v>68.2</v>
       </c>
       <c r="X68" s="6" t="n">
-        <v>39.05</v>
+        <v>65.47</v>
       </c>
       <c r="Y68" s="6" t="n">
-        <v>39.05</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="Z68" s="6" t="n">
-        <v>38.88</v>
+        <v>65.03</v>
       </c>
       <c r="AA68" s="6" t="n">
-        <v>38.68</v>
+        <v>64.8</v>
       </c>
       <c r="AB68" s="6" t="n">
-        <v>38.78</v>
+        <v>65.42</v>
       </c>
       <c r="AC68" s="6" t="n">
-        <v>39.45</v>
+        <v>65.77</v>
       </c>
       <c r="AD68" s="6" t="n">
-        <v>38.48</v>
+        <v>65.05</v>
       </c>
       <c r="AE68" s="6" t="n">
-        <v>39.23</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="AF68" s="6" t="n">
-        <v>33.83</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="AG68" s="6" t="n">
-        <v>28.65</v>
+        <v>74.7</v>
       </c>
       <c r="AH68" s="6" t="n">
-        <v>32.11</v>
+        <v>68.88</v>
       </c>
       <c r="AI68" s="6" t="inlineStr"/>
       <c r="AJ68" s="6" t="inlineStr"/>
@@ -6536,107 +6332,107 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>PLUS TV</t>
+          <t>ECOTEL</t>
         </is>
       </c>
       <c r="B69" s="6" t="n">
-        <v>537.25</v>
+        <v>519.25</v>
       </c>
       <c r="C69" s="6" t="n">
-        <v>67.88</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>67.90000000000001</v>
+        <v>83.48</v>
       </c>
       <c r="E69" s="6" t="n">
-        <v>68.84999999999999</v>
+        <v>83.25</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>68.3</v>
+        <v>83.02</v>
       </c>
       <c r="G69" s="6" t="n">
-        <v>67.59999999999999</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="H69" s="6" t="n">
-        <v>66.7</v>
+        <v>83.67</v>
       </c>
       <c r="I69" s="6" t="n">
-        <v>67.18000000000001</v>
+        <v>84.25</v>
       </c>
       <c r="J69" s="6" t="n">
-        <v>66.09999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K69" s="6" t="n">
-        <v>66.88</v>
+        <v>81.27</v>
       </c>
       <c r="L69" s="6" t="n">
-        <v>68.42</v>
+        <v>79.15000000000001</v>
       </c>
       <c r="M69" s="6" t="n">
-        <v>68.22</v>
+        <v>82</v>
       </c>
       <c r="N69" s="6" t="n">
-        <v>68.06999999999999</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="O69" s="6" t="n">
-        <v>68</v>
+        <v>83.15000000000001</v>
       </c>
       <c r="P69" s="6" t="n">
-        <v>68.68000000000001</v>
+        <v>83.65000000000001</v>
       </c>
       <c r="Q69" s="6" t="n">
-        <v>68.65000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="R69" s="6" t="n">
-        <v>70.63</v>
+        <v>83.75</v>
       </c>
       <c r="S69" s="6" t="n">
-        <v>70.2</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="T69" s="6" t="n">
-        <v>67.40000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="U69" s="6" t="n">
-        <v>69.95</v>
+        <v>83.33</v>
       </c>
       <c r="V69" s="6" t="n">
-        <v>70.65000000000001</v>
+        <v>83.95</v>
       </c>
       <c r="W69" s="6" t="n">
-        <v>70.73</v>
+        <v>82.31999999999999</v>
       </c>
       <c r="X69" s="6" t="n">
-        <v>68.55</v>
+        <v>78.5</v>
       </c>
       <c r="Y69" s="6" t="n">
-        <v>68.7</v>
+        <v>77.97</v>
       </c>
       <c r="Z69" s="6" t="n">
-        <v>66.93000000000001</v>
+        <v>75.37</v>
       </c>
       <c r="AA69" s="6" t="n">
-        <v>68.27</v>
+        <v>80.13</v>
       </c>
       <c r="AB69" s="6" t="n">
-        <v>68.40000000000001</v>
+        <v>79.25</v>
       </c>
       <c r="AC69" s="6" t="n">
-        <v>69.8</v>
+        <v>79.8</v>
       </c>
       <c r="AD69" s="6" t="n">
-        <v>70.15000000000001</v>
+        <v>77.13</v>
       </c>
       <c r="AE69" s="6" t="n">
-        <v>69.95</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="AF69" s="6" t="n">
-        <v>69.75</v>
+        <v>81.37</v>
       </c>
       <c r="AG69" s="6" t="n">
-        <v>72</v>
+        <v>84.68000000000001</v>
       </c>
       <c r="AH69" s="6" t="n">
-        <v>68.69</v>
+        <v>81.86</v>
       </c>
       <c r="AI69" s="6" t="inlineStr"/>
       <c r="AJ69" s="6" t="inlineStr"/>
@@ -6645,107 +6441,107 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>CANAL UNO</t>
+          <t>TELERAMA</t>
         </is>
       </c>
       <c r="B70" s="6" t="n">
-        <v>543.25</v>
+        <v>531.25</v>
       </c>
       <c r="C70" s="6" t="n">
-        <v>30.25</v>
+        <v>28.37</v>
       </c>
       <c r="D70" s="6" t="n">
-        <v>28.95</v>
+        <v>29.4</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>29.82</v>
+        <v>27.83</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>30.2</v>
+        <v>28.55</v>
       </c>
       <c r="G70" s="6" t="n">
-        <v>30.07</v>
+        <v>28.55</v>
       </c>
       <c r="H70" s="6" t="n">
-        <v>29.28</v>
+        <v>27.95</v>
       </c>
       <c r="I70" s="6" t="n">
-        <v>29.25</v>
+        <v>28</v>
       </c>
       <c r="J70" s="6" t="n">
-        <v>30.22</v>
+        <v>28.12</v>
       </c>
       <c r="K70" s="6" t="n">
-        <v>35.05</v>
+        <v>33.42</v>
       </c>
       <c r="L70" s="6" t="n">
-        <v>39.5</v>
+        <v>38.92</v>
       </c>
       <c r="M70" s="6" t="n">
-        <v>34.93</v>
+        <v>34.12</v>
       </c>
       <c r="N70" s="6" t="n">
-        <v>31.55</v>
+        <v>28.75</v>
       </c>
       <c r="O70" s="6" t="n">
+        <v>28.63</v>
+      </c>
+      <c r="P70" s="6" t="n">
+        <v>27.68</v>
+      </c>
+      <c r="Q70" s="6" t="n">
+        <v>28.35</v>
+      </c>
+      <c r="R70" s="6" t="n">
+        <v>27.93</v>
+      </c>
+      <c r="S70" s="6" t="n">
+        <v>28.22</v>
+      </c>
+      <c r="T70" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="P70" s="6" t="n">
-        <v>29.75</v>
-      </c>
-      <c r="Q70" s="6" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="R70" s="6" t="n">
-        <v>30.48</v>
-      </c>
-      <c r="S70" s="6" t="n">
-        <v>30.13</v>
-      </c>
-      <c r="T70" s="6" t="n">
-        <v>29.78</v>
-      </c>
       <c r="U70" s="6" t="n">
-        <v>33.47</v>
+        <v>28.68</v>
       </c>
       <c r="V70" s="6" t="n">
-        <v>29.87</v>
+        <v>27.77</v>
       </c>
       <c r="W70" s="6" t="n">
-        <v>34.4</v>
+        <v>33.18</v>
       </c>
       <c r="X70" s="6" t="n">
-        <v>38.93</v>
+        <v>39.05</v>
       </c>
       <c r="Y70" s="6" t="n">
-        <v>39.37</v>
+        <v>39.05</v>
       </c>
       <c r="Z70" s="6" t="n">
-        <v>39.2</v>
+        <v>38.88</v>
       </c>
       <c r="AA70" s="6" t="n">
-        <v>38.98</v>
+        <v>38.68</v>
       </c>
       <c r="AB70" s="6" t="n">
-        <v>40.15</v>
+        <v>38.78</v>
       </c>
       <c r="AC70" s="6" t="n">
-        <v>39.25</v>
+        <v>39.45</v>
       </c>
       <c r="AD70" s="6" t="n">
-        <v>39.2</v>
+        <v>38.48</v>
       </c>
       <c r="AE70" s="6" t="n">
-        <v>39.17</v>
+        <v>39.23</v>
       </c>
       <c r="AF70" s="6" t="n">
-        <v>34</v>
+        <v>33.83</v>
       </c>
       <c r="AG70" s="6" t="n">
-        <v>30.6</v>
+        <v>28.65</v>
       </c>
       <c r="AH70" s="6" t="n">
-        <v>33.36</v>
+        <v>32.11</v>
       </c>
       <c r="AI70" s="6" t="inlineStr"/>
       <c r="AJ70" s="6" t="inlineStr"/>
@@ -6754,107 +6550,107 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>TELEATAHUALPA (RTU)</t>
+          <t>PLUS TV</t>
         </is>
       </c>
       <c r="B71" s="6" t="n">
-        <v>567.25</v>
+        <v>537.25</v>
       </c>
       <c r="C71" s="6" t="n">
-        <v>38.72</v>
+        <v>67.88</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>40.58</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="E71" s="6" t="n">
-        <v>39.1</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>39.9</v>
+        <v>68.3</v>
       </c>
       <c r="G71" s="6" t="n">
-        <v>39.67</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H71" s="6" t="n">
-        <v>40.1</v>
+        <v>66.7</v>
       </c>
       <c r="I71" s="6" t="n">
-        <v>39.85</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="J71" s="6" t="n">
-        <v>39.65</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="K71" s="6" t="n">
-        <v>39.85</v>
+        <v>66.88</v>
       </c>
       <c r="L71" s="6" t="n">
-        <v>41.55</v>
+        <v>68.42</v>
       </c>
       <c r="M71" s="6" t="n">
-        <v>39.78</v>
+        <v>68.22</v>
       </c>
       <c r="N71" s="6" t="n">
-        <v>40.37</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="O71" s="6" t="n">
-        <v>39.98</v>
+        <v>68</v>
       </c>
       <c r="P71" s="6" t="n">
-        <v>40</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="Q71" s="6" t="n">
-        <v>40.37</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="R71" s="6" t="n">
-        <v>41.43</v>
+        <v>70.63</v>
       </c>
       <c r="S71" s="6" t="n">
-        <v>41.08</v>
+        <v>70.2</v>
       </c>
       <c r="T71" s="6" t="n">
-        <v>41.43</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="U71" s="6" t="n">
-        <v>41.27</v>
+        <v>69.95</v>
       </c>
       <c r="V71" s="6" t="n">
-        <v>41.17</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="W71" s="6" t="n">
-        <v>42.6</v>
+        <v>70.73</v>
       </c>
       <c r="X71" s="6" t="n">
-        <v>41.62</v>
+        <v>68.55</v>
       </c>
       <c r="Y71" s="6" t="n">
-        <v>40.92</v>
+        <v>68.7</v>
       </c>
       <c r="Z71" s="6" t="n">
-        <v>40.37</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="AA71" s="6" t="n">
-        <v>41.32</v>
+        <v>68.27</v>
       </c>
       <c r="AB71" s="6" t="n">
-        <v>41.38</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="AC71" s="6" t="n">
-        <v>41.15</v>
+        <v>69.8</v>
       </c>
       <c r="AD71" s="6" t="n">
-        <v>41.08</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="AE71" s="6" t="n">
-        <v>41.33</v>
+        <v>69.95</v>
       </c>
       <c r="AF71" s="6" t="n">
-        <v>41.33</v>
+        <v>69.75</v>
       </c>
       <c r="AG71" s="6" t="n">
-        <v>41.08</v>
+        <v>72</v>
       </c>
       <c r="AH71" s="6" t="n">
-        <v>40.65</v>
+        <v>68.69</v>
       </c>
       <c r="AI71" s="6" t="inlineStr"/>
       <c r="AJ71" s="6" t="inlineStr"/>
@@ -6863,107 +6659,107 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>TELEVICENTRO TVC</t>
+          <t>CANAL UNO</t>
         </is>
       </c>
       <c r="B72" s="6" t="n">
-        <v>579.25</v>
+        <v>543.25</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>79.78</v>
+        <v>30.25</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>80.72</v>
+        <v>28.95</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>79.93000000000001</v>
+        <v>29.82</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>80.12</v>
+        <v>30.2</v>
       </c>
       <c r="G72" s="6" t="n">
-        <v>79.88</v>
+        <v>30.07</v>
       </c>
       <c r="H72" s="6" t="n">
-        <v>79.08</v>
+        <v>29.28</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>78.75</v>
+        <v>29.25</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>77.95</v>
+        <v>30.22</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>80.68000000000001</v>
+        <v>35.05</v>
       </c>
       <c r="L72" s="6" t="n">
-        <v>81.78</v>
+        <v>39.5</v>
       </c>
       <c r="M72" s="6" t="n">
-        <v>79.17</v>
+        <v>34.93</v>
       </c>
       <c r="N72" s="6" t="n">
-        <v>77.7</v>
+        <v>31.55</v>
       </c>
       <c r="O72" s="6" t="n">
-        <v>78.22</v>
+        <v>29</v>
       </c>
       <c r="P72" s="6" t="n">
-        <v>78.63</v>
+        <v>29.75</v>
       </c>
       <c r="Q72" s="6" t="n">
-        <v>80.17</v>
+        <v>29.25</v>
       </c>
       <c r="R72" s="6" t="n">
-        <v>81.37</v>
+        <v>30.48</v>
       </c>
       <c r="S72" s="6" t="n">
-        <v>81.08</v>
+        <v>30.13</v>
       </c>
       <c r="T72" s="6" t="n">
-        <v>80.27</v>
+        <v>29.78</v>
       </c>
       <c r="U72" s="6" t="n">
-        <v>81.02</v>
+        <v>33.47</v>
       </c>
       <c r="V72" s="6" t="n">
-        <v>81.15000000000001</v>
+        <v>29.87</v>
       </c>
       <c r="W72" s="6" t="n">
-        <v>80.2</v>
+        <v>34.4</v>
       </c>
       <c r="X72" s="6" t="n">
-        <v>80.59999999999999</v>
+        <v>38.93</v>
       </c>
       <c r="Y72" s="6" t="n">
-        <v>78.77</v>
+        <v>39.37</v>
       </c>
       <c r="Z72" s="6" t="n">
-        <v>82.28</v>
+        <v>39.2</v>
       </c>
       <c r="AA72" s="6" t="n">
-        <v>81.15000000000001</v>
+        <v>38.98</v>
       </c>
       <c r="AB72" s="6" t="n">
-        <v>80.33</v>
+        <v>40.15</v>
       </c>
       <c r="AC72" s="6" t="n">
-        <v>80.15000000000001</v>
+        <v>39.25</v>
       </c>
       <c r="AD72" s="6" t="n">
-        <v>83</v>
+        <v>39.2</v>
       </c>
       <c r="AE72" s="6" t="n">
-        <v>79.43000000000001</v>
+        <v>39.17</v>
       </c>
       <c r="AF72" s="6" t="n">
-        <v>79.03</v>
+        <v>34</v>
       </c>
       <c r="AG72" s="6" t="n">
-        <v>81.13</v>
+        <v>30.6</v>
       </c>
       <c r="AH72" s="6" t="n">
-        <v>80.11</v>
+        <v>33.36</v>
       </c>
       <c r="AI72" s="6" t="inlineStr"/>
       <c r="AJ72" s="6" t="inlineStr"/>
@@ -6972,107 +6768,107 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>UCSG TELEVISION</t>
+          <t>TELEATAHUALPA (RTU)</t>
         </is>
       </c>
       <c r="B73" s="6" t="n">
-        <v>591.25</v>
+        <v>567.25</v>
       </c>
       <c r="C73" s="6" t="n">
-        <v>32.83</v>
+        <v>38.72</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>34.15</v>
+        <v>40.58</v>
       </c>
       <c r="E73" s="6" t="n">
-        <v>32.67</v>
+        <v>39.1</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>32.47</v>
+        <v>39.9</v>
       </c>
       <c r="G73" s="6" t="n">
-        <v>32.32</v>
+        <v>39.67</v>
       </c>
       <c r="H73" s="6" t="n">
-        <v>32.23</v>
+        <v>40.1</v>
       </c>
       <c r="I73" s="6" t="n">
-        <v>32.47</v>
+        <v>39.85</v>
       </c>
       <c r="J73" s="6" t="n">
-        <v>34.17</v>
+        <v>39.65</v>
       </c>
       <c r="K73" s="6" t="n">
-        <v>37.27</v>
+        <v>39.85</v>
       </c>
       <c r="L73" s="6" t="n">
-        <v>45.08</v>
+        <v>41.55</v>
       </c>
       <c r="M73" s="6" t="n">
-        <v>39.83</v>
+        <v>39.78</v>
       </c>
       <c r="N73" s="6" t="n">
-        <v>32.48</v>
+        <v>40.37</v>
       </c>
       <c r="O73" s="6" t="n">
-        <v>32.45</v>
+        <v>39.98</v>
       </c>
       <c r="P73" s="6" t="n">
-        <v>32.08</v>
+        <v>40</v>
       </c>
       <c r="Q73" s="6" t="n">
-        <v>31.9</v>
+        <v>40.37</v>
       </c>
       <c r="R73" s="6" t="n">
-        <v>31.83</v>
+        <v>41.43</v>
       </c>
       <c r="S73" s="6" t="n">
-        <v>32.6</v>
+        <v>41.08</v>
       </c>
       <c r="T73" s="6" t="n">
-        <v>34.5</v>
+        <v>41.43</v>
       </c>
       <c r="U73" s="6" t="n">
-        <v>31.85</v>
+        <v>41.27</v>
       </c>
       <c r="V73" s="6" t="n">
-        <v>32.28</v>
+        <v>41.17</v>
       </c>
       <c r="W73" s="6" t="n">
-        <v>37.38</v>
+        <v>42.6</v>
       </c>
       <c r="X73" s="6" t="n">
-        <v>43.55</v>
+        <v>41.62</v>
       </c>
       <c r="Y73" s="6" t="n">
-        <v>42.93</v>
+        <v>40.92</v>
       </c>
       <c r="Z73" s="6" t="n">
-        <v>43.05</v>
+        <v>40.37</v>
       </c>
       <c r="AA73" s="6" t="n">
-        <v>43.25</v>
+        <v>41.32</v>
       </c>
       <c r="AB73" s="6" t="n">
-        <v>43.55</v>
+        <v>41.38</v>
       </c>
       <c r="AC73" s="6" t="n">
-        <v>43</v>
+        <v>41.15</v>
       </c>
       <c r="AD73" s="6" t="n">
-        <v>43.15</v>
+        <v>41.08</v>
       </c>
       <c r="AE73" s="6" t="n">
-        <v>43.18</v>
+        <v>41.33</v>
       </c>
       <c r="AF73" s="6" t="n">
-        <v>39.02</v>
+        <v>41.33</v>
       </c>
       <c r="AG73" s="6" t="n">
-        <v>32.98</v>
+        <v>41.08</v>
       </c>
       <c r="AH73" s="6" t="n">
-        <v>36.53</v>
+        <v>40.65</v>
       </c>
       <c r="AI73" s="6" t="inlineStr"/>
       <c r="AJ73" s="6" t="inlineStr"/>
@@ -7081,236 +6877,456 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>OROMAR</t>
+          <t>TELEVICENTRO TVC</t>
         </is>
       </c>
       <c r="B74" s="6" t="n">
-        <v>603.25</v>
+        <v>579.25</v>
       </c>
       <c r="C74" s="6" t="n">
-        <v>32.45</v>
+        <v>79.78</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>32.73</v>
+        <v>80.72</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>32.25</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>32.4</v>
+        <v>80.12</v>
       </c>
       <c r="G74" s="6" t="n">
-        <v>32.48</v>
+        <v>79.88</v>
       </c>
       <c r="H74" s="6" t="n">
-        <v>32.68</v>
+        <v>79.08</v>
       </c>
       <c r="I74" s="6" t="n">
-        <v>33.48</v>
+        <v>78.75</v>
       </c>
       <c r="J74" s="6" t="n">
-        <v>32.9</v>
+        <v>77.95</v>
       </c>
       <c r="K74" s="6" t="n">
-        <v>39.47</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="L74" s="6" t="n">
-        <v>46.07</v>
+        <v>81.78</v>
       </c>
       <c r="M74" s="6" t="n">
-        <v>39.98</v>
+        <v>79.17</v>
       </c>
       <c r="N74" s="6" t="n">
-        <v>32.65</v>
+        <v>77.7</v>
       </c>
       <c r="O74" s="6" t="n">
-        <v>32.73</v>
+        <v>78.22</v>
       </c>
       <c r="P74" s="6" t="n">
-        <v>33.17</v>
+        <v>78.63</v>
       </c>
       <c r="Q74" s="6" t="n">
-        <v>32.58</v>
+        <v>80.17</v>
       </c>
       <c r="R74" s="6" t="n">
-        <v>32.58</v>
+        <v>81.37</v>
       </c>
       <c r="S74" s="6" t="n">
-        <v>33</v>
+        <v>81.08</v>
       </c>
       <c r="T74" s="6" t="n">
-        <v>33.23</v>
+        <v>80.27</v>
       </c>
       <c r="U74" s="6" t="n">
-        <v>32.78</v>
+        <v>81.02</v>
       </c>
       <c r="V74" s="6" t="n">
-        <v>32.85</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="W74" s="6" t="n">
-        <v>44.6</v>
+        <v>80.2</v>
       </c>
       <c r="X74" s="6" t="n">
-        <v>46.48</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="Y74" s="6" t="n">
-        <v>46.78</v>
+        <v>78.77</v>
       </c>
       <c r="Z74" s="6" t="n">
-        <v>46.05</v>
+        <v>82.28</v>
       </c>
       <c r="AA74" s="6" t="n">
-        <v>46.18</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="AB74" s="6" t="n">
-        <v>48.7</v>
+        <v>80.33</v>
       </c>
       <c r="AC74" s="6" t="n">
-        <v>47.2</v>
+        <v>80.15000000000001</v>
       </c>
       <c r="AD74" s="6" t="n">
-        <v>46.2</v>
+        <v>83</v>
       </c>
       <c r="AE74" s="6" t="n">
-        <v>46.93</v>
+        <v>79.43000000000001</v>
       </c>
       <c r="AF74" s="6" t="n">
-        <v>39.97</v>
+        <v>79.03</v>
       </c>
       <c r="AG74" s="6" t="n">
-        <v>33.45</v>
+        <v>81.13</v>
       </c>
       <c r="AH74" s="6" t="n">
-        <v>37.9</v>
+        <v>80.11</v>
       </c>
       <c r="AI74" s="6" t="inlineStr"/>
       <c r="AJ74" s="6" t="inlineStr"/>
       <c r="AK74" s="7" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="8" t="inlineStr">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>UCSG TELEVISION</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="n">
+        <v>591.25</v>
+      </c>
+      <c r="C75" s="6" t="n">
+        <v>32.83</v>
+      </c>
+      <c r="D75" s="6" t="n">
+        <v>34.15</v>
+      </c>
+      <c r="E75" s="6" t="n">
+        <v>32.67</v>
+      </c>
+      <c r="F75" s="6" t="n">
+        <v>32.47</v>
+      </c>
+      <c r="G75" s="6" t="n">
+        <v>32.32</v>
+      </c>
+      <c r="H75" s="6" t="n">
+        <v>32.23</v>
+      </c>
+      <c r="I75" s="6" t="n">
+        <v>32.47</v>
+      </c>
+      <c r="J75" s="6" t="n">
+        <v>34.17</v>
+      </c>
+      <c r="K75" s="6" t="n">
+        <v>37.27</v>
+      </c>
+      <c r="L75" s="6" t="n">
+        <v>45.08</v>
+      </c>
+      <c r="M75" s="6" t="n">
+        <v>39.83</v>
+      </c>
+      <c r="N75" s="6" t="n">
+        <v>32.48</v>
+      </c>
+      <c r="O75" s="6" t="n">
+        <v>32.45</v>
+      </c>
+      <c r="P75" s="6" t="n">
+        <v>32.08</v>
+      </c>
+      <c r="Q75" s="6" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="R75" s="6" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="S75" s="6" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="T75" s="6" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="U75" s="6" t="n">
+        <v>31.85</v>
+      </c>
+      <c r="V75" s="6" t="n">
+        <v>32.28</v>
+      </c>
+      <c r="W75" s="6" t="n">
+        <v>37.38</v>
+      </c>
+      <c r="X75" s="6" t="n">
+        <v>43.55</v>
+      </c>
+      <c r="Y75" s="6" t="n">
+        <v>42.93</v>
+      </c>
+      <c r="Z75" s="6" t="n">
+        <v>43.05</v>
+      </c>
+      <c r="AA75" s="6" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="AB75" s="6" t="n">
+        <v>43.55</v>
+      </c>
+      <c r="AC75" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="AD75" s="6" t="n">
+        <v>43.15</v>
+      </c>
+      <c r="AE75" s="6" t="n">
+        <v>43.18</v>
+      </c>
+      <c r="AF75" s="6" t="n">
+        <v>39.02</v>
+      </c>
+      <c r="AG75" s="6" t="n">
+        <v>32.98</v>
+      </c>
+      <c r="AH75" s="6" t="n">
+        <v>36.53</v>
+      </c>
+      <c r="AI75" s="6" t="inlineStr"/>
+      <c r="AJ75" s="6" t="inlineStr"/>
+      <c r="AK75" s="7" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>OROMAR</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="n">
+        <v>603.25</v>
+      </c>
+      <c r="C76" s="6" t="n">
+        <v>32.45</v>
+      </c>
+      <c r="D76" s="6" t="n">
+        <v>32.73</v>
+      </c>
+      <c r="E76" s="6" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="F76" s="6" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="G76" s="6" t="n">
+        <v>32.48</v>
+      </c>
+      <c r="H76" s="6" t="n">
+        <v>32.68</v>
+      </c>
+      <c r="I76" s="6" t="n">
+        <v>33.48</v>
+      </c>
+      <c r="J76" s="6" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="K76" s="6" t="n">
+        <v>39.47</v>
+      </c>
+      <c r="L76" s="6" t="n">
+        <v>46.07</v>
+      </c>
+      <c r="M76" s="6" t="n">
+        <v>39.98</v>
+      </c>
+      <c r="N76" s="6" t="n">
+        <v>32.65</v>
+      </c>
+      <c r="O76" s="6" t="n">
+        <v>32.73</v>
+      </c>
+      <c r="P76" s="6" t="n">
+        <v>33.17</v>
+      </c>
+      <c r="Q76" s="6" t="n">
+        <v>32.58</v>
+      </c>
+      <c r="R76" s="6" t="n">
+        <v>32.58</v>
+      </c>
+      <c r="S76" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="T76" s="6" t="n">
+        <v>33.23</v>
+      </c>
+      <c r="U76" s="6" t="n">
+        <v>32.78</v>
+      </c>
+      <c r="V76" s="6" t="n">
+        <v>32.85</v>
+      </c>
+      <c r="W76" s="6" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="X76" s="6" t="n">
+        <v>46.48</v>
+      </c>
+      <c r="Y76" s="6" t="n">
+        <v>46.78</v>
+      </c>
+      <c r="Z76" s="6" t="n">
+        <v>46.05</v>
+      </c>
+      <c r="AA76" s="6" t="n">
+        <v>46.18</v>
+      </c>
+      <c r="AB76" s="6" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="AC76" s="6" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="AD76" s="6" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="AE76" s="6" t="n">
+        <v>46.93</v>
+      </c>
+      <c r="AF76" s="6" t="n">
+        <v>39.97</v>
+      </c>
+      <c r="AG76" s="6" t="n">
+        <v>33.45</v>
+      </c>
+      <c r="AH76" s="6" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="AI76" s="6" t="inlineStr"/>
+      <c r="AJ76" s="6" t="inlineStr"/>
+      <c r="AK76" s="7" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="inlineStr">
         <is>
           <t>CANAL SUR - TELEVISION MUN</t>
         </is>
       </c>
-      <c r="B75" s="9" t="n">
+      <c r="B77" s="9" t="n">
         <v>621.25</v>
       </c>
-      <c r="C75" s="9" t="n">
+      <c r="C77" s="9" t="n">
         <v>75.28</v>
       </c>
-      <c r="D75" s="9" t="n">
+      <c r="D77" s="9" t="n">
         <v>75.62</v>
       </c>
-      <c r="E75" s="9" t="n">
+      <c r="E77" s="9" t="n">
         <v>69.09999999999999</v>
       </c>
-      <c r="F75" s="9" t="n">
+      <c r="F77" s="9" t="n">
         <v>70.23</v>
       </c>
-      <c r="G75" s="9" t="n">
+      <c r="G77" s="9" t="n">
         <v>70.78</v>
       </c>
-      <c r="H75" s="9" t="n">
+      <c r="H77" s="9" t="n">
         <v>69.77</v>
       </c>
-      <c r="I75" s="9" t="n">
+      <c r="I77" s="9" t="n">
         <v>70.2</v>
       </c>
-      <c r="J75" s="9" t="n">
+      <c r="J77" s="9" t="n">
         <v>68.48</v>
       </c>
-      <c r="K75" s="9" t="n">
+      <c r="K77" s="9" t="n">
         <v>83.56999999999999</v>
       </c>
-      <c r="L75" s="9" t="n">
+      <c r="L77" s="9" t="n">
         <v>99.27</v>
       </c>
-      <c r="M75" s="9" t="n">
+      <c r="M77" s="9" t="n">
         <v>84.33</v>
       </c>
-      <c r="N75" s="9" t="n">
+      <c r="N77" s="9" t="n">
         <v>69.23</v>
       </c>
-      <c r="O75" s="9" t="n">
+      <c r="O77" s="9" t="n">
         <v>68.53</v>
       </c>
-      <c r="P75" s="9" t="n">
+      <c r="P77" s="9" t="n">
         <v>70.05</v>
       </c>
-      <c r="Q75" s="9" t="n">
+      <c r="Q77" s="9" t="n">
         <v>68.92</v>
       </c>
-      <c r="R75" s="9" t="n">
+      <c r="R77" s="9" t="n">
         <v>71.08</v>
       </c>
-      <c r="S75" s="9" t="n">
+      <c r="S77" s="9" t="n">
         <v>72.17</v>
       </c>
-      <c r="T75" s="9" t="n">
+      <c r="T77" s="9" t="n">
         <v>71.13</v>
       </c>
-      <c r="U75" s="9" t="n">
+      <c r="U77" s="9" t="n">
         <v>72.59999999999999</v>
       </c>
-      <c r="V75" s="9" t="n">
+      <c r="V77" s="9" t="n">
         <v>69.81999999999999</v>
       </c>
-      <c r="W75" s="9" t="n">
+      <c r="W77" s="9" t="n">
         <v>85.8</v>
       </c>
-      <c r="X75" s="9" t="n">
+      <c r="X77" s="9" t="n">
         <v>99.72</v>
       </c>
-      <c r="Y75" s="9" t="n">
+      <c r="Y77" s="9" t="n">
         <v>99.43000000000001</v>
       </c>
-      <c r="Z75" s="9" t="n">
+      <c r="Z77" s="9" t="n">
         <v>99.73</v>
       </c>
-      <c r="AA75" s="9" t="n">
+      <c r="AA77" s="9" t="n">
         <v>99.73</v>
       </c>
-      <c r="AB75" s="9" t="n">
+      <c r="AB77" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="AC75" s="9" t="n">
+      <c r="AC77" s="9" t="n">
         <v>99.05</v>
       </c>
-      <c r="AD75" s="9" t="n">
+      <c r="AD77" s="9" t="n">
         <v>99.48</v>
       </c>
-      <c r="AE75" s="9" t="n">
+      <c r="AE77" s="9" t="n">
         <v>99.78</v>
       </c>
-      <c r="AF75" s="9" t="n">
+      <c r="AF77" s="9" t="n">
         <v>85.68000000000001</v>
       </c>
-      <c r="AG75" s="9" t="n">
+      <c r="AG77" s="9" t="n">
         <v>73.12</v>
       </c>
-      <c r="AH75" s="9" t="n">
+      <c r="AH77" s="9" t="n">
         <v>81.02</v>
       </c>
-      <c r="AI75" s="9" t="inlineStr"/>
-      <c r="AJ75" s="9" t="inlineStr"/>
-      <c r="AK75" s="10" t="n"/>
+      <c r="AI77" s="9" t="inlineStr"/>
+      <c r="AJ77" s="9" t="inlineStr"/>
+      <c r="AK77" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="16">
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="A4:AK4"/>
     <mergeCell ref="A3:AK3"/>
-    <mergeCell ref="A53:AK53"/>
     <mergeCell ref="A55:AK55"/>
     <mergeCell ref="A7:AK7"/>
+    <mergeCell ref="A59:AK59"/>
     <mergeCell ref="A57:AK57"/>
     <mergeCell ref="A2:AK2"/>
     <mergeCell ref="A54:AK54"/>
-    <mergeCell ref="A52:AK52"/>
+    <mergeCell ref="A56:AK56"/>
     <mergeCell ref="A58:AK58"/>
+    <mergeCell ref="A60:AK60"/>
     <mergeCell ref="A1:AK1"/>
-    <mergeCell ref="A56:AK56"/>
+    <mergeCell ref="A9:AK9"/>
+    <mergeCell ref="A8:AK8"/>
     <mergeCell ref="A6:AK6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ReportesUnificados/loja_ReporteUnificado.xlsx
+++ b/ReportesUnificados/loja_ReporteUnificado.xlsx
@@ -218,7 +218,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4762500" cy="952500"/>
@@ -268,7 +268,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>56</row>
+      <row>55</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4762500" cy="952500"/>

--- a/ReportesUnificados/loja_ReporteUnificado.xlsx
+++ b/ReportesUnificados/loja_ReporteUnificado.xlsx
@@ -38,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -100,11 +100,60 @@
       <top style="thin"/>
       <bottom style="medium"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="medium"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -136,6 +185,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -644,7 +696,7 @@
     <col width="8" customWidth="1" min="33" max="33"/>
     <col width="15" customWidth="1" min="34" max="34"/>
     <col width="23" customWidth="1" min="35" max="35"/>
-    <col width="23" customWidth="1" min="36" max="36"/>
+    <col width="38" customWidth="1" min="36" max="36"/>
     <col width="15" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
@@ -5564,7 +5616,7 @@
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK61" s="4" t="n"/>
+      <c r="AK61" s="11" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -5673,7 +5725,7 @@
       </c>
       <c r="AI62" s="6" t="inlineStr"/>
       <c r="AJ62" s="6" t="inlineStr"/>
-      <c r="AK62" s="7" t="n"/>
+      <c r="AK62" s="12" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -5782,7 +5834,7 @@
       </c>
       <c r="AI63" s="6" t="inlineStr"/>
       <c r="AJ63" s="6" t="inlineStr"/>
-      <c r="AK63" s="7" t="n"/>
+      <c r="AK63" s="12" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -5891,7 +5943,7 @@
       </c>
       <c r="AI64" s="6" t="inlineStr"/>
       <c r="AJ64" s="6" t="inlineStr"/>
-      <c r="AK64" s="7" t="n"/>
+      <c r="AK64" s="12" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -6000,7 +6052,7 @@
       </c>
       <c r="AI65" s="6" t="inlineStr"/>
       <c r="AJ65" s="6" t="inlineStr"/>
-      <c r="AK65" s="7" t="n"/>
+      <c r="AK65" s="12" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -6109,7 +6161,7 @@
       </c>
       <c r="AI66" s="6" t="inlineStr"/>
       <c r="AJ66" s="6" t="inlineStr"/>
-      <c r="AK66" s="7" t="n"/>
+      <c r="AK66" s="12" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -6218,7 +6270,7 @@
       </c>
       <c r="AI67" s="6" t="inlineStr"/>
       <c r="AJ67" s="6" t="inlineStr"/>
-      <c r="AK67" s="7" t="n"/>
+      <c r="AK67" s="12" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -6327,7 +6379,7 @@
       </c>
       <c r="AI68" s="6" t="inlineStr"/>
       <c r="AJ68" s="6" t="inlineStr"/>
-      <c r="AK68" s="7" t="n"/>
+      <c r="AK68" s="12" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -6436,7 +6488,7 @@
       </c>
       <c r="AI69" s="6" t="inlineStr"/>
       <c r="AJ69" s="6" t="inlineStr"/>
-      <c r="AK69" s="7" t="n"/>
+      <c r="AK69" s="12" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -6545,7 +6597,7 @@
       </c>
       <c r="AI70" s="6" t="inlineStr"/>
       <c r="AJ70" s="6" t="inlineStr"/>
-      <c r="AK70" s="7" t="n"/>
+      <c r="AK70" s="12" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -6654,7 +6706,7 @@
       </c>
       <c r="AI71" s="6" t="inlineStr"/>
       <c r="AJ71" s="6" t="inlineStr"/>
-      <c r="AK71" s="7" t="n"/>
+      <c r="AK71" s="12" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -6763,7 +6815,7 @@
       </c>
       <c r="AI72" s="6" t="inlineStr"/>
       <c r="AJ72" s="6" t="inlineStr"/>
-      <c r="AK72" s="7" t="n"/>
+      <c r="AK72" s="12" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -6872,7 +6924,7 @@
       </c>
       <c r="AI73" s="6" t="inlineStr"/>
       <c r="AJ73" s="6" t="inlineStr"/>
-      <c r="AK73" s="7" t="n"/>
+      <c r="AK73" s="12" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -6981,7 +7033,7 @@
       </c>
       <c r="AI74" s="6" t="inlineStr"/>
       <c r="AJ74" s="6" t="inlineStr"/>
-      <c r="AK74" s="7" t="n"/>
+      <c r="AK74" s="12" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
@@ -7090,7 +7142,7 @@
       </c>
       <c r="AI75" s="6" t="inlineStr"/>
       <c r="AJ75" s="6" t="inlineStr"/>
-      <c r="AK75" s="7" t="n"/>
+      <c r="AK75" s="12" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -7199,7 +7251,7 @@
       </c>
       <c r="AI76" s="6" t="inlineStr"/>
       <c r="AJ76" s="6" t="inlineStr"/>
-      <c r="AK76" s="7" t="n"/>
+      <c r="AK76" s="12" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
@@ -7308,26 +7360,43 @@
       </c>
       <c r="AI77" s="9" t="inlineStr"/>
       <c r="AJ77" s="9" t="inlineStr"/>
-      <c r="AK77" s="10" t="n"/>
+      <c r="AK77" s="13" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A5:AK5"/>
-    <mergeCell ref="A4:AK4"/>
+  <mergeCells count="33">
     <mergeCell ref="A3:AK3"/>
     <mergeCell ref="A55:AK55"/>
-    <mergeCell ref="A7:AK7"/>
-    <mergeCell ref="A59:AK59"/>
     <mergeCell ref="A57:AK57"/>
     <mergeCell ref="A2:AK2"/>
-    <mergeCell ref="A54:AK54"/>
-    <mergeCell ref="A56:AK56"/>
+    <mergeCell ref="AJ71:AK71"/>
+    <mergeCell ref="A5:AK5"/>
+    <mergeCell ref="AJ70:AK70"/>
+    <mergeCell ref="A8:AK8"/>
+    <mergeCell ref="AJ61:AK61"/>
+    <mergeCell ref="A4:AK4"/>
+    <mergeCell ref="AJ73:AK73"/>
+    <mergeCell ref="AJ72:AK72"/>
+    <mergeCell ref="AJ67:AK67"/>
+    <mergeCell ref="AJ66:AK66"/>
+    <mergeCell ref="A9:AK9"/>
     <mergeCell ref="A58:AK58"/>
+    <mergeCell ref="AJ69:AK69"/>
+    <mergeCell ref="A59:AK59"/>
+    <mergeCell ref="AJ68:AK68"/>
+    <mergeCell ref="AJ77:AK77"/>
+    <mergeCell ref="AJ62:AK62"/>
     <mergeCell ref="A60:AK60"/>
     <mergeCell ref="A1:AK1"/>
-    <mergeCell ref="A9:AK9"/>
-    <mergeCell ref="A8:AK8"/>
+    <mergeCell ref="AJ74:AK74"/>
+    <mergeCell ref="AJ65:AK65"/>
     <mergeCell ref="A6:AK6"/>
+    <mergeCell ref="AJ64:AK64"/>
+    <mergeCell ref="A7:AK7"/>
+    <mergeCell ref="A54:AK54"/>
+    <mergeCell ref="AJ76:AK76"/>
+    <mergeCell ref="AJ63:AK63"/>
+    <mergeCell ref="A56:AK56"/>
+    <mergeCell ref="AJ75:AK75"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/ReportesUnificados/loja_ReporteUnificado.xlsx
+++ b/ReportesUnificados/loja_ReporteUnificado.xlsx
@@ -30,12 +30,30 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDFECE"/>
+        <bgColor rgb="FFCDFECE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFE9F"/>
+        <bgColor rgb="FFFFFE9F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFD9BCB"/>
+        <bgColor rgb="FFFD9BCB"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="17">
@@ -153,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -173,7 +191,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -182,11 +206,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -759,7 +789,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 27/08/2025</t>
+          <t>FECHA PRESENTACIÓN: 28/08/2025</t>
         </is>
       </c>
     </row>
@@ -901,97 +931,97 @@
       <c r="B11" s="6" t="n">
         <v>88.09999999999999</v>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C11" s="7" t="n">
         <v>100.73</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="7" t="n">
         <v>100.21</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="7" t="n">
         <v>99.67</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="7" t="n">
         <v>98.14</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G11" s="7" t="n">
         <v>99.37</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="7" t="n">
         <v>99.87</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="I11" s="7" t="n">
         <v>99.3</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="7" t="n">
         <v>98.27</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="K11" s="7" t="n">
         <v>103.04</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="L11" s="7" t="n">
         <v>104.62</v>
       </c>
-      <c r="M11" s="6" t="n">
+      <c r="M11" s="7" t="n">
         <v>103.65</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="N11" s="7" t="n">
         <v>104.35</v>
       </c>
-      <c r="O11" s="6" t="n">
+      <c r="O11" s="7" t="n">
         <v>99.56999999999999</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="P11" s="7" t="n">
         <v>100.89</v>
       </c>
-      <c r="Q11" s="6" t="n">
+      <c r="Q11" s="7" t="n">
         <v>99.98999999999999</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="R11" s="7" t="n">
         <v>100.87</v>
       </c>
-      <c r="S11" s="6" t="n">
+      <c r="S11" s="7" t="n">
         <v>101.26</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="T11" s="7" t="n">
         <v>99.95999999999999</v>
       </c>
-      <c r="U11" s="6" t="n">
+      <c r="U11" s="7" t="n">
         <v>103.34</v>
       </c>
-      <c r="V11" s="6" t="n">
+      <c r="V11" s="7" t="n">
         <v>100.12</v>
       </c>
-      <c r="W11" s="6" t="n">
+      <c r="W11" s="7" t="n">
         <v>102.4</v>
       </c>
-      <c r="X11" s="6" t="n">
+      <c r="X11" s="7" t="n">
         <v>104.77</v>
       </c>
-      <c r="Y11" s="6" t="n">
+      <c r="Y11" s="7" t="n">
         <v>104.69</v>
       </c>
-      <c r="Z11" s="6" t="n">
+      <c r="Z11" s="7" t="n">
         <v>104.73</v>
       </c>
-      <c r="AA11" s="6" t="n">
+      <c r="AA11" s="7" t="n">
         <v>104.57</v>
       </c>
-      <c r="AB11" s="6" t="n">
+      <c r="AB11" s="7" t="n">
         <v>104.87</v>
       </c>
-      <c r="AC11" s="6" t="n">
+      <c r="AC11" s="7" t="n">
         <v>104.49</v>
       </c>
-      <c r="AD11" s="6" t="n">
+      <c r="AD11" s="7" t="n">
         <v>104.43</v>
       </c>
-      <c r="AE11" s="6" t="n">
+      <c r="AE11" s="7" t="n">
         <v>104.15</v>
       </c>
-      <c r="AF11" s="6" t="n">
+      <c r="AF11" s="7" t="n">
         <v>103.92</v>
       </c>
-      <c r="AG11" s="6" t="n">
+      <c r="AG11" s="7" t="n">
         <v>103.78</v>
       </c>
       <c r="AH11" s="6" t="n">
@@ -1001,7 +1031,7 @@
         <v>261.08</v>
       </c>
       <c r="AJ11" s="6" t="inlineStr"/>
-      <c r="AK11" s="7" t="inlineStr"/>
+      <c r="AK11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1012,97 +1042,97 @@
       <c r="B12" s="6" t="n">
         <v>88.5</v>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C12" s="7" t="n">
         <v>102.64</v>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="7" t="n">
         <v>102.54</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="7" t="n">
         <v>100.03</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="7" t="n">
         <v>98.68000000000001</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="G12" s="7" t="n">
         <v>98.81999999999999</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H12" s="7" t="n">
         <v>99.39</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="I12" s="7" t="n">
         <v>98.18000000000001</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="J12" s="7" t="n">
         <v>98.54000000000001</v>
       </c>
-      <c r="K12" s="6" t="n">
+      <c r="K12" s="7" t="n">
         <v>103.48</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="L12" s="7" t="n">
         <v>106.07</v>
       </c>
-      <c r="M12" s="6" t="n">
+      <c r="M12" s="7" t="n">
         <v>103.61</v>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="N12" s="7" t="n">
         <v>102.12</v>
       </c>
-      <c r="O12" s="6" t="n">
+      <c r="O12" s="7" t="n">
         <v>98.91</v>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="P12" s="7" t="n">
         <v>100.43</v>
       </c>
-      <c r="Q12" s="6" t="n">
+      <c r="Q12" s="7" t="n">
         <v>99.17</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="R12" s="7" t="n">
         <v>100.68</v>
       </c>
-      <c r="S12" s="6" t="n">
+      <c r="S12" s="7" t="n">
         <v>100.48</v>
       </c>
-      <c r="T12" s="6" t="n">
+      <c r="T12" s="7" t="n">
         <v>100.5</v>
       </c>
-      <c r="U12" s="6" t="n">
+      <c r="U12" s="7" t="n">
         <v>102.11</v>
       </c>
-      <c r="V12" s="6" t="n">
+      <c r="V12" s="7" t="n">
         <v>99.84</v>
       </c>
-      <c r="W12" s="6" t="n">
+      <c r="W12" s="7" t="n">
         <v>102.52</v>
       </c>
-      <c r="X12" s="6" t="n">
+      <c r="X12" s="7" t="n">
         <v>105.26</v>
       </c>
-      <c r="Y12" s="6" t="n">
+      <c r="Y12" s="7" t="n">
         <v>105.26</v>
       </c>
-      <c r="Z12" s="6" t="n">
+      <c r="Z12" s="7" t="n">
         <v>105.57</v>
       </c>
-      <c r="AA12" s="6" t="n">
+      <c r="AA12" s="7" t="n">
         <v>105.29</v>
       </c>
-      <c r="AB12" s="6" t="n">
+      <c r="AB12" s="7" t="n">
         <v>104.97</v>
       </c>
-      <c r="AC12" s="6" t="n">
+      <c r="AC12" s="7" t="n">
         <v>104.81</v>
       </c>
-      <c r="AD12" s="6" t="n">
+      <c r="AD12" s="7" t="n">
         <v>105.28</v>
       </c>
-      <c r="AE12" s="6" t="n">
+      <c r="AE12" s="7" t="n">
         <v>105.18</v>
       </c>
-      <c r="AF12" s="6" t="n">
+      <c r="AF12" s="7" t="n">
         <v>103.21</v>
       </c>
-      <c r="AG12" s="6" t="n">
+      <c r="AG12" s="7" t="n">
         <v>102.45</v>
       </c>
       <c r="AH12" s="6" t="n">
@@ -1112,7 +1142,7 @@
         <v>400.33</v>
       </c>
       <c r="AJ12" s="6" t="inlineStr"/>
-      <c r="AK12" s="7" t="inlineStr"/>
+      <c r="AK12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1123,97 +1153,97 @@
       <c r="B13" s="6" t="n">
         <v>88.90000000000001</v>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C13" s="7" t="n">
         <v>106.04</v>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="7" t="n">
         <v>106.46</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E13" s="7" t="n">
         <v>105.83</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F13" s="7" t="n">
         <v>104.99</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="G13" s="7" t="n">
         <v>105.07</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="H13" s="7" t="n">
         <v>106.63</v>
       </c>
-      <c r="I13" s="6" t="n">
+      <c r="I13" s="7" t="n">
         <v>105.73</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="J13" s="7" t="n">
         <v>104.88</v>
       </c>
-      <c r="K13" s="6" t="n">
+      <c r="K13" s="7" t="n">
         <v>108.41</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="L13" s="7" t="n">
         <v>109.61</v>
       </c>
-      <c r="M13" s="6" t="n">
+      <c r="M13" s="7" t="n">
         <v>109.16</v>
       </c>
-      <c r="N13" s="6" t="n">
+      <c r="N13" s="7" t="n">
         <v>109.38</v>
       </c>
-      <c r="O13" s="6" t="n">
+      <c r="O13" s="7" t="n">
         <v>105.76</v>
       </c>
-      <c r="P13" s="6" t="n">
+      <c r="P13" s="7" t="n">
         <v>107.38</v>
       </c>
-      <c r="Q13" s="6" t="n">
+      <c r="Q13" s="7" t="n">
         <v>106.48</v>
       </c>
-      <c r="R13" s="6" t="n">
+      <c r="R13" s="7" t="n">
         <v>107.36</v>
       </c>
-      <c r="S13" s="6" t="n">
+      <c r="S13" s="7" t="n">
         <v>107.12</v>
       </c>
-      <c r="T13" s="6" t="n">
+      <c r="T13" s="7" t="n">
         <v>106.32</v>
       </c>
-      <c r="U13" s="6" t="n">
+      <c r="U13" s="7" t="n">
         <v>108.66</v>
       </c>
-      <c r="V13" s="6" t="n">
+      <c r="V13" s="7" t="n">
         <v>106.53</v>
       </c>
-      <c r="W13" s="6" t="n">
+      <c r="W13" s="7" t="n">
         <v>107.33</v>
       </c>
-      <c r="X13" s="6" t="n">
+      <c r="X13" s="7" t="n">
         <v>109.04</v>
       </c>
-      <c r="Y13" s="6" t="n">
+      <c r="Y13" s="7" t="n">
         <v>109.38</v>
       </c>
-      <c r="Z13" s="6" t="n">
+      <c r="Z13" s="7" t="n">
         <v>109.66</v>
       </c>
-      <c r="AA13" s="6" t="n">
+      <c r="AA13" s="7" t="n">
         <v>109.31</v>
       </c>
-      <c r="AB13" s="6" t="n">
+      <c r="AB13" s="7" t="n">
         <v>109.43</v>
       </c>
-      <c r="AC13" s="6" t="n">
+      <c r="AC13" s="7" t="n">
         <v>106.55</v>
       </c>
-      <c r="AD13" s="6" t="n">
+      <c r="AD13" s="7" t="n">
         <v>103.29</v>
       </c>
-      <c r="AE13" s="6" t="n">
+      <c r="AE13" s="7" t="n">
         <v>103.96</v>
       </c>
-      <c r="AF13" s="6" t="n">
+      <c r="AF13" s="7" t="n">
         <v>103.71</v>
       </c>
-      <c r="AG13" s="6" t="n">
+      <c r="AG13" s="7" t="n">
         <v>104.82</v>
       </c>
       <c r="AH13" s="6" t="n">
@@ -1223,7 +1253,7 @@
         <v>485.39</v>
       </c>
       <c r="AJ13" s="6" t="inlineStr"/>
-      <c r="AK13" s="7" t="inlineStr"/>
+      <c r="AK13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1234,97 +1264,97 @@
       <c r="B14" s="6" t="n">
         <v>89.3</v>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C14" s="7" t="n">
         <v>105.66</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="7" t="n">
         <v>107.57</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E14" s="7" t="n">
         <v>107.51</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="F14" s="7" t="n">
         <v>106.14</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="G14" s="7" t="n">
         <v>106.72</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="H14" s="7" t="n">
         <v>108.46</v>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="I14" s="7" t="n">
         <v>107.72</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="J14" s="7" t="n">
         <v>106.02</v>
       </c>
-      <c r="K14" s="6" t="n">
+      <c r="K14" s="7" t="n">
         <v>110.23</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="L14" s="7" t="n">
         <v>111.67</v>
       </c>
-      <c r="M14" s="6" t="n">
+      <c r="M14" s="7" t="n">
         <v>111.27</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="N14" s="7" t="n">
         <v>111.21</v>
       </c>
-      <c r="O14" s="6" t="n">
+      <c r="O14" s="7" t="n">
         <v>108.06</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="P14" s="7" t="n">
         <v>109.28</v>
       </c>
-      <c r="Q14" s="6" t="n">
+      <c r="Q14" s="7" t="n">
         <v>107.56</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="R14" s="7" t="n">
         <v>109.17</v>
       </c>
-      <c r="S14" s="6" t="n">
+      <c r="S14" s="7" t="n">
         <v>108.37</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="T14" s="7" t="n">
         <v>106.98</v>
       </c>
-      <c r="U14" s="6" t="n">
+      <c r="U14" s="7" t="n">
         <v>110.21</v>
       </c>
-      <c r="V14" s="6" t="n">
+      <c r="V14" s="7" t="n">
         <v>108.43</v>
       </c>
-      <c r="W14" s="6" t="n">
+      <c r="W14" s="7" t="n">
         <v>109.52</v>
       </c>
-      <c r="X14" s="6" t="n">
+      <c r="X14" s="7" t="n">
         <v>111.48</v>
       </c>
-      <c r="Y14" s="6" t="n">
+      <c r="Y14" s="7" t="n">
         <v>111.49</v>
       </c>
-      <c r="Z14" s="6" t="n">
+      <c r="Z14" s="7" t="n">
         <v>111.6</v>
       </c>
-      <c r="AA14" s="6" t="n">
+      <c r="AA14" s="7" t="n">
         <v>111.47</v>
       </c>
-      <c r="AB14" s="6" t="n">
+      <c r="AB14" s="7" t="n">
         <v>111.8</v>
       </c>
-      <c r="AC14" s="6" t="n">
+      <c r="AC14" s="7" t="n">
         <v>111.7</v>
       </c>
-      <c r="AD14" s="6" t="n">
+      <c r="AD14" s="7" t="n">
         <v>111.21</v>
       </c>
-      <c r="AE14" s="6" t="n">
+      <c r="AE14" s="7" t="n">
         <v>111.61</v>
       </c>
-      <c r="AF14" s="6" t="n">
+      <c r="AF14" s="7" t="n">
         <v>111.38</v>
       </c>
-      <c r="AG14" s="6" t="n">
+      <c r="AG14" s="7" t="n">
         <v>111.67</v>
       </c>
       <c r="AH14" s="6" t="n">
@@ -1334,7 +1364,7 @@
         <v>372.17</v>
       </c>
       <c r="AJ14" s="6" t="inlineStr"/>
-      <c r="AK14" s="7" t="inlineStr"/>
+      <c r="AK14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1345,97 +1375,97 @@
       <c r="B15" s="6" t="n">
         <v>89.7</v>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C15" s="7" t="n">
         <v>101.81</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="7" t="n">
         <v>101.63</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="7" t="n">
         <v>101.45</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F15" s="7" t="n">
         <v>100.81</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="G15" s="7" t="n">
         <v>100.7</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="H15" s="7" t="n">
         <v>102.51</v>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="I15" s="7" t="n">
         <v>101.59</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="J15" s="7" t="n">
         <v>100.62</v>
       </c>
-      <c r="K15" s="6" t="n">
+      <c r="K15" s="7" t="n">
         <v>104.52</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="L15" s="7" t="n">
         <v>105.85</v>
       </c>
-      <c r="M15" s="6" t="n">
+      <c r="M15" s="7" t="n">
         <v>104.58</v>
       </c>
-      <c r="N15" s="6" t="n">
+      <c r="N15" s="7" t="n">
         <v>104.78</v>
       </c>
-      <c r="O15" s="6" t="n">
+      <c r="O15" s="7" t="n">
         <v>101.78</v>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="P15" s="7" t="n">
         <v>102.56</v>
       </c>
-      <c r="Q15" s="6" t="n">
+      <c r="Q15" s="7" t="n">
         <v>101.9</v>
       </c>
-      <c r="R15" s="6" t="n">
+      <c r="R15" s="7" t="n">
         <v>103.48</v>
       </c>
-      <c r="S15" s="6" t="n">
+      <c r="S15" s="7" t="n">
         <v>101.89</v>
       </c>
-      <c r="T15" s="6" t="n">
+      <c r="T15" s="7" t="n">
         <v>101.72</v>
       </c>
-      <c r="U15" s="6" t="n">
+      <c r="U15" s="7" t="n">
         <v>103.71</v>
       </c>
-      <c r="V15" s="6" t="n">
+      <c r="V15" s="7" t="n">
         <v>102.37</v>
       </c>
-      <c r="W15" s="6" t="n">
+      <c r="W15" s="7" t="n">
         <v>103.49</v>
       </c>
-      <c r="X15" s="6" t="n">
+      <c r="X15" s="7" t="n">
         <v>104.3</v>
       </c>
-      <c r="Y15" s="6" t="n">
+      <c r="Y15" s="7" t="n">
         <v>104.96</v>
       </c>
-      <c r="Z15" s="6" t="n">
+      <c r="Z15" s="7" t="n">
         <v>105.19</v>
       </c>
-      <c r="AA15" s="6" t="n">
+      <c r="AA15" s="7" t="n">
         <v>104.56</v>
       </c>
-      <c r="AB15" s="6" t="n">
+      <c r="AB15" s="7" t="n">
         <v>104.47</v>
       </c>
-      <c r="AC15" s="6" t="n">
+      <c r="AC15" s="7" t="n">
         <v>104.6</v>
       </c>
-      <c r="AD15" s="6" t="n">
+      <c r="AD15" s="7" t="n">
         <v>104.82</v>
       </c>
-      <c r="AE15" s="6" t="n">
+      <c r="AE15" s="7" t="n">
         <v>104.94</v>
       </c>
-      <c r="AF15" s="6" t="n">
+      <c r="AF15" s="7" t="n">
         <v>104.81</v>
       </c>
-      <c r="AG15" s="6" t="n">
+      <c r="AG15" s="7" t="n">
         <v>105.46</v>
       </c>
       <c r="AH15" s="6" t="n">
@@ -1445,7 +1475,7 @@
         <v>388.41</v>
       </c>
       <c r="AJ15" s="6" t="inlineStr"/>
-      <c r="AK15" s="7" t="inlineStr"/>
+      <c r="AK15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1456,97 +1486,97 @@
       <c r="B16" s="6" t="n">
         <v>90.09999999999999</v>
       </c>
-      <c r="C16" s="6" t="n">
+      <c r="C16" s="7" t="n">
         <v>81.18000000000001</v>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="7" t="n">
         <v>81.19</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E16" s="7" t="n">
         <v>82.01000000000001</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F16" s="7" t="n">
         <v>81.12</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="G16" s="7" t="n">
         <v>82.13</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="H16" s="7" t="n">
         <v>83.72</v>
       </c>
-      <c r="I16" s="6" t="n">
+      <c r="I16" s="7" t="n">
         <v>83.38</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="J16" s="7" t="n">
         <v>81.62</v>
       </c>
-      <c r="K16" s="6" t="n">
+      <c r="K16" s="7" t="n">
         <v>82.89</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="L16" s="7" t="n">
         <v>84.88</v>
       </c>
-      <c r="M16" s="6" t="n">
+      <c r="M16" s="7" t="n">
         <v>86.56</v>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="N16" s="7" t="n">
         <v>85.36</v>
       </c>
-      <c r="O16" s="6" t="n">
+      <c r="O16" s="7" t="n">
         <v>83.48</v>
       </c>
-      <c r="P16" s="6" t="n">
+      <c r="P16" s="7" t="n">
         <v>83.94</v>
       </c>
-      <c r="Q16" s="6" t="n">
+      <c r="Q16" s="7" t="n">
         <v>83.54000000000001</v>
       </c>
-      <c r="R16" s="6" t="n">
+      <c r="R16" s="7" t="n">
         <v>84.23</v>
       </c>
-      <c r="S16" s="6" t="n">
+      <c r="S16" s="7" t="n">
         <v>83.56</v>
       </c>
-      <c r="T16" s="6" t="n">
+      <c r="T16" s="7" t="n">
         <v>81.23</v>
       </c>
-      <c r="U16" s="6" t="n">
+      <c r="U16" s="7" t="n">
         <v>83.98999999999999</v>
       </c>
-      <c r="V16" s="6" t="n">
+      <c r="V16" s="7" t="n">
         <v>83.53</v>
       </c>
-      <c r="W16" s="6" t="n">
+      <c r="W16" s="7" t="n">
         <v>84.95</v>
       </c>
-      <c r="X16" s="6" t="n">
+      <c r="X16" s="7" t="n">
         <v>86.98</v>
       </c>
-      <c r="Y16" s="6" t="n">
+      <c r="Y16" s="7" t="n">
         <v>87.2</v>
       </c>
-      <c r="Z16" s="6" t="n">
+      <c r="Z16" s="7" t="n">
         <v>85.37</v>
       </c>
-      <c r="AA16" s="6" t="n">
+      <c r="AA16" s="7" t="n">
         <v>87.22</v>
       </c>
-      <c r="AB16" s="6" t="n">
+      <c r="AB16" s="7" t="n">
         <v>87.34</v>
       </c>
-      <c r="AC16" s="6" t="n">
+      <c r="AC16" s="7" t="n">
         <v>87.25</v>
       </c>
-      <c r="AD16" s="6" t="n">
+      <c r="AD16" s="7" t="n">
         <v>86.56</v>
       </c>
-      <c r="AE16" s="6" t="n">
+      <c r="AE16" s="7" t="n">
         <v>87.37</v>
       </c>
-      <c r="AF16" s="6" t="n">
+      <c r="AF16" s="7" t="n">
         <v>86.66</v>
       </c>
-      <c r="AG16" s="6" t="n">
+      <c r="AG16" s="7" t="n">
         <v>87.37</v>
       </c>
       <c r="AH16" s="6" t="n">
@@ -1556,7 +1586,7 @@
         <v>444.57</v>
       </c>
       <c r="AJ16" s="6" t="inlineStr"/>
-      <c r="AK16" s="7" t="inlineStr"/>
+      <c r="AK16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1567,97 +1597,97 @@
       <c r="B17" s="6" t="n">
         <v>90.5</v>
       </c>
-      <c r="C17" s="6" t="n">
+      <c r="C17" s="7" t="n">
         <v>86.59</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="7" t="n">
         <v>86.89</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="E17" s="7" t="n">
         <v>87.52</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="F17" s="7" t="n">
         <v>87.31999999999999</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="G17" s="7" t="n">
         <v>86.2</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="H17" s="7" t="n">
         <v>87.95999999999999</v>
       </c>
-      <c r="I17" s="6" t="n">
+      <c r="I17" s="7" t="n">
         <v>86.48999999999999</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="J17" s="7" t="n">
         <v>85.58</v>
       </c>
-      <c r="K17" s="6" t="n">
+      <c r="K17" s="7" t="n">
         <v>87.87</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="L17" s="7" t="n">
         <v>89.41</v>
       </c>
-      <c r="M17" s="6" t="n">
+      <c r="M17" s="7" t="n">
         <v>88.76000000000001</v>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="N17" s="7" t="n">
         <v>89.28</v>
       </c>
-      <c r="O17" s="6" t="n">
+      <c r="O17" s="7" t="n">
         <v>86.09</v>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="P17" s="7" t="n">
         <v>87.20999999999999</v>
       </c>
-      <c r="Q17" s="6" t="n">
+      <c r="Q17" s="7" t="n">
         <v>86.89</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="R17" s="7" t="n">
         <v>87.84999999999999</v>
       </c>
-      <c r="S17" s="6" t="n">
+      <c r="S17" s="7" t="n">
         <v>87.41</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="T17" s="7" t="n">
         <v>87.53</v>
       </c>
-      <c r="U17" s="6" t="n">
+      <c r="U17" s="7" t="n">
         <v>88.09</v>
       </c>
-      <c r="V17" s="6" t="n">
+      <c r="V17" s="7" t="n">
         <v>86.47</v>
       </c>
-      <c r="W17" s="6" t="n">
+      <c r="W17" s="7" t="n">
         <v>88.48999999999999</v>
       </c>
-      <c r="X17" s="6" t="n">
+      <c r="X17" s="7" t="n">
         <v>90.56999999999999</v>
       </c>
-      <c r="Y17" s="6" t="n">
+      <c r="Y17" s="7" t="n">
         <v>89.93000000000001</v>
       </c>
-      <c r="Z17" s="6" t="n">
+      <c r="Z17" s="7" t="n">
         <v>89.88</v>
       </c>
-      <c r="AA17" s="6" t="n">
+      <c r="AA17" s="7" t="n">
         <v>88.79000000000001</v>
       </c>
-      <c r="AB17" s="6" t="n">
+      <c r="AB17" s="7" t="n">
         <v>88.62</v>
       </c>
-      <c r="AC17" s="6" t="n">
+      <c r="AC17" s="7" t="n">
         <v>88.70999999999999</v>
       </c>
-      <c r="AD17" s="6" t="n">
+      <c r="AD17" s="7" t="n">
         <v>88.98999999999999</v>
       </c>
-      <c r="AE17" s="6" t="n">
+      <c r="AE17" s="7" t="n">
         <v>88.67</v>
       </c>
-      <c r="AF17" s="6" t="n">
+      <c r="AF17" s="7" t="n">
         <v>88.98</v>
       </c>
-      <c r="AG17" s="6" t="n">
+      <c r="AG17" s="7" t="n">
         <v>89.48</v>
       </c>
       <c r="AH17" s="6" t="n">
@@ -1667,7 +1697,7 @@
         <v>364.81</v>
       </c>
       <c r="AJ17" s="6" t="inlineStr"/>
-      <c r="AK17" s="7" t="inlineStr"/>
+      <c r="AK17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1678,97 +1708,97 @@
       <c r="B18" s="6" t="n">
         <v>90.90000000000001</v>
       </c>
-      <c r="C18" s="6" t="n">
+      <c r="C18" s="7" t="n">
         <v>100.28</v>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="7" t="n">
         <v>100.14</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E18" s="7" t="n">
         <v>101.43</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="F18" s="7" t="n">
         <v>101.02</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="G18" s="7" t="n">
         <v>101.46</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="H18" s="7" t="n">
         <v>102.67</v>
       </c>
-      <c r="I18" s="6" t="n">
+      <c r="I18" s="7" t="n">
         <v>102.67</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="J18" s="7" t="n">
         <v>101.48</v>
       </c>
-      <c r="K18" s="6" t="n">
+      <c r="K18" s="7" t="n">
         <v>103.87</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="L18" s="7" t="n">
         <v>106.03</v>
       </c>
-      <c r="M18" s="6" t="n">
+      <c r="M18" s="7" t="n">
         <v>105.71</v>
       </c>
-      <c r="N18" s="6" t="n">
+      <c r="N18" s="7" t="n">
         <v>105.21</v>
       </c>
-      <c r="O18" s="6" t="n">
+      <c r="O18" s="7" t="n">
         <v>102.61</v>
       </c>
-      <c r="P18" s="6" t="n">
+      <c r="P18" s="7" t="n">
         <v>103.77</v>
       </c>
-      <c r="Q18" s="6" t="n">
+      <c r="Q18" s="7" t="n">
         <v>102.62</v>
       </c>
-      <c r="R18" s="6" t="n">
+      <c r="R18" s="7" t="n">
         <v>103.92</v>
       </c>
-      <c r="S18" s="6" t="n">
+      <c r="S18" s="7" t="n">
         <v>103.29</v>
       </c>
-      <c r="T18" s="6" t="n">
+      <c r="T18" s="7" t="n">
         <v>101.73</v>
       </c>
-      <c r="U18" s="6" t="n">
+      <c r="U18" s="7" t="n">
         <v>103.4</v>
       </c>
-      <c r="V18" s="6" t="n">
+      <c r="V18" s="7" t="n">
         <v>102.62</v>
       </c>
-      <c r="W18" s="6" t="n">
+      <c r="W18" s="7" t="n">
         <v>104.21</v>
       </c>
-      <c r="X18" s="6" t="n">
+      <c r="X18" s="7" t="n">
         <v>105.88</v>
       </c>
-      <c r="Y18" s="6" t="n">
+      <c r="Y18" s="7" t="n">
         <v>106.01</v>
       </c>
-      <c r="Z18" s="6" t="n">
+      <c r="Z18" s="7" t="n">
         <v>106.29</v>
       </c>
-      <c r="AA18" s="6" t="n">
+      <c r="AA18" s="7" t="n">
         <v>106.23</v>
       </c>
-      <c r="AB18" s="6" t="n">
+      <c r="AB18" s="7" t="n">
         <v>106.02</v>
       </c>
-      <c r="AC18" s="6" t="n">
+      <c r="AC18" s="7" t="n">
         <v>106.35</v>
       </c>
-      <c r="AD18" s="6" t="n">
+      <c r="AD18" s="7" t="n">
         <v>106.12</v>
       </c>
-      <c r="AE18" s="6" t="n">
+      <c r="AE18" s="7" t="n">
         <v>105.89</v>
       </c>
-      <c r="AF18" s="6" t="n">
+      <c r="AF18" s="7" t="n">
         <v>106</v>
       </c>
-      <c r="AG18" s="6" t="n">
+      <c r="AG18" s="7" t="n">
         <v>106.29</v>
       </c>
       <c r="AH18" s="6" t="n">
@@ -1778,7 +1808,7 @@
         <v>415.88</v>
       </c>
       <c r="AJ18" s="6" t="inlineStr"/>
-      <c r="AK18" s="7" t="inlineStr"/>
+      <c r="AK18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1789,97 +1819,97 @@
       <c r="B19" s="6" t="n">
         <v>92.09999999999999</v>
       </c>
-      <c r="C19" s="6" t="n">
+      <c r="C19" s="7" t="n">
         <v>97.68000000000001</v>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="7" t="n">
         <v>100.49</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="E19" s="7" t="n">
         <v>101.6</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="F19" s="7" t="n">
         <v>101.09</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="G19" s="7" t="n">
         <v>102.04</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="H19" s="7" t="n">
         <v>103.13</v>
       </c>
-      <c r="I19" s="6" t="n">
+      <c r="I19" s="7" t="n">
         <v>103.39</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="J19" s="7" t="n">
         <v>101.37</v>
       </c>
-      <c r="K19" s="6" t="n">
+      <c r="K19" s="7" t="n">
         <v>104.29</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="L19" s="7" t="n">
         <v>106.73</v>
       </c>
-      <c r="M19" s="6" t="n">
+      <c r="M19" s="7" t="n">
         <v>105.76</v>
       </c>
-      <c r="N19" s="6" t="n">
+      <c r="N19" s="7" t="n">
         <v>104.57</v>
       </c>
-      <c r="O19" s="6" t="n">
+      <c r="O19" s="7" t="n">
         <v>102.94</v>
       </c>
-      <c r="P19" s="6" t="n">
+      <c r="P19" s="7" t="n">
         <v>103.63</v>
       </c>
-      <c r="Q19" s="6" t="n">
+      <c r="Q19" s="7" t="n">
         <v>102.59</v>
       </c>
-      <c r="R19" s="6" t="n">
+      <c r="R19" s="7" t="n">
         <v>103.54</v>
       </c>
-      <c r="S19" s="6" t="n">
+      <c r="S19" s="7" t="n">
         <v>103.07</v>
       </c>
-      <c r="T19" s="6" t="n">
+      <c r="T19" s="7" t="n">
         <v>102.02</v>
       </c>
-      <c r="U19" s="6" t="n">
+      <c r="U19" s="7" t="n">
         <v>103.72</v>
       </c>
-      <c r="V19" s="6" t="n">
+      <c r="V19" s="7" t="n">
         <v>102.81</v>
       </c>
-      <c r="W19" s="6" t="n">
+      <c r="W19" s="7" t="n">
         <v>104.56</v>
       </c>
-      <c r="X19" s="6" t="n">
+      <c r="X19" s="7" t="n">
         <v>106.92</v>
       </c>
-      <c r="Y19" s="6" t="n">
+      <c r="Y19" s="7" t="n">
         <v>107.14</v>
       </c>
-      <c r="Z19" s="6" t="n">
+      <c r="Z19" s="7" t="n">
         <v>107.26</v>
       </c>
-      <c r="AA19" s="6" t="n">
+      <c r="AA19" s="7" t="n">
         <v>107.2</v>
       </c>
-      <c r="AB19" s="6" t="n">
+      <c r="AB19" s="7" t="n">
         <v>107.29</v>
       </c>
-      <c r="AC19" s="6" t="n">
+      <c r="AC19" s="7" t="n">
         <v>107.32</v>
       </c>
-      <c r="AD19" s="6" t="n">
+      <c r="AD19" s="7" t="n">
         <v>106.9</v>
       </c>
-      <c r="AE19" s="6" t="n">
+      <c r="AE19" s="7" t="n">
         <v>106.57</v>
       </c>
-      <c r="AF19" s="6" t="n">
+      <c r="AF19" s="7" t="n">
         <v>106.03</v>
       </c>
-      <c r="AG19" s="6" t="n">
+      <c r="AG19" s="7" t="n">
         <v>105.72</v>
       </c>
       <c r="AH19" s="6" t="n">
@@ -1889,7 +1919,7 @@
         <v>418.76</v>
       </c>
       <c r="AJ19" s="6" t="inlineStr"/>
-      <c r="AK19" s="7" t="inlineStr"/>
+      <c r="AK19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -1900,97 +1930,97 @@
       <c r="B20" s="6" t="n">
         <v>92.5</v>
       </c>
-      <c r="C20" s="6" t="n">
+      <c r="C20" s="7" t="n">
         <v>95.48999999999999</v>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="7" t="n">
         <v>95.12</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="E20" s="7" t="n">
         <v>94.48999999999999</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="F20" s="7" t="n">
         <v>94.18000000000001</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="G20" s="7" t="n">
         <v>94.04000000000001</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="H20" s="7" t="n">
         <v>94.16</v>
       </c>
-      <c r="I20" s="6" t="n">
+      <c r="I20" s="7" t="n">
         <v>93.19</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="J20" s="7" t="n">
         <v>94.19</v>
       </c>
-      <c r="K20" s="6" t="n">
+      <c r="K20" s="7" t="n">
         <v>95.20999999999999</v>
       </c>
-      <c r="L20" s="6" t="n">
+      <c r="L20" s="7" t="n">
         <v>96.98</v>
       </c>
-      <c r="M20" s="6" t="n">
+      <c r="M20" s="7" t="n">
         <v>95.88</v>
       </c>
-      <c r="N20" s="6" t="n">
+      <c r="N20" s="7" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="O20" s="6" t="n">
+      <c r="O20" s="7" t="n">
         <v>93.38</v>
       </c>
-      <c r="P20" s="6" t="n">
+      <c r="P20" s="7" t="n">
         <v>92.69</v>
       </c>
-      <c r="Q20" s="6" t="n">
+      <c r="Q20" s="7" t="n">
         <v>93.16</v>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="R20" s="7" t="n">
         <v>93.67</v>
       </c>
-      <c r="S20" s="6" t="n">
+      <c r="S20" s="7" t="n">
         <v>93.63</v>
       </c>
-      <c r="T20" s="6" t="n">
+      <c r="T20" s="7" t="n">
         <v>94.48</v>
       </c>
-      <c r="U20" s="6" t="n">
+      <c r="U20" s="7" t="n">
         <v>93.19</v>
       </c>
-      <c r="V20" s="6" t="n">
+      <c r="V20" s="7" t="n">
         <v>94.34</v>
       </c>
-      <c r="W20" s="6" t="n">
+      <c r="W20" s="7" t="n">
         <v>96.26000000000001</v>
       </c>
-      <c r="X20" s="6" t="n">
+      <c r="X20" s="7" t="n">
         <v>98.88</v>
       </c>
-      <c r="Y20" s="6" t="n">
+      <c r="Y20" s="7" t="n">
         <v>98.8</v>
       </c>
-      <c r="Z20" s="6" t="n">
+      <c r="Z20" s="7" t="n">
         <v>98.48</v>
       </c>
-      <c r="AA20" s="6" t="n">
+      <c r="AA20" s="7" t="n">
         <v>98.22</v>
       </c>
-      <c r="AB20" s="6" t="n">
+      <c r="AB20" s="7" t="n">
         <v>98.26000000000001</v>
       </c>
-      <c r="AC20" s="6" t="n">
+      <c r="AC20" s="7" t="n">
         <v>98.23</v>
       </c>
-      <c r="AD20" s="6" t="n">
+      <c r="AD20" s="7" t="n">
         <v>98.13</v>
       </c>
-      <c r="AE20" s="6" t="n">
+      <c r="AE20" s="7" t="n">
         <v>98.22</v>
       </c>
-      <c r="AF20" s="6" t="n">
+      <c r="AF20" s="7" t="n">
         <v>96.83</v>
       </c>
-      <c r="AG20" s="6" t="n">
+      <c r="AG20" s="7" t="n">
         <v>94.88</v>
       </c>
       <c r="AH20" s="6" t="n">
@@ -2000,7 +2030,7 @@
         <v>400.73</v>
       </c>
       <c r="AJ20" s="6" t="inlineStr"/>
-      <c r="AK20" s="7" t="inlineStr"/>
+      <c r="AK20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2011,97 +2041,97 @@
       <c r="B21" s="6" t="n">
         <v>93.3</v>
       </c>
-      <c r="C21" s="6" t="n">
+      <c r="C21" s="7" t="n">
         <v>93.22</v>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="7" t="n">
         <v>93.84</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="E21" s="7" t="n">
         <v>94.18000000000001</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="F21" s="7" t="n">
         <v>93.56999999999999</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="G21" s="7" t="n">
         <v>94.23</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="H21" s="7" t="n">
         <v>94.87</v>
       </c>
-      <c r="I21" s="6" t="n">
+      <c r="I21" s="7" t="n">
         <v>94.42</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="J21" s="7" t="n">
         <v>93.37</v>
       </c>
-      <c r="K21" s="6" t="n">
+      <c r="K21" s="7" t="n">
         <v>97.06999999999999</v>
       </c>
-      <c r="L21" s="6" t="n">
+      <c r="L21" s="7" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="M21" s="6" t="n">
+      <c r="M21" s="7" t="n">
         <v>97.95999999999999</v>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="N21" s="7" t="n">
         <v>95.68000000000001</v>
       </c>
-      <c r="O21" s="6" t="n">
+      <c r="O21" s="7" t="n">
         <v>94.81</v>
       </c>
-      <c r="P21" s="6" t="n">
+      <c r="P21" s="7" t="n">
         <v>95.19</v>
       </c>
-      <c r="Q21" s="6" t="n">
+      <c r="Q21" s="7" t="n">
         <v>94.36</v>
       </c>
-      <c r="R21" s="6" t="n">
+      <c r="R21" s="7" t="n">
         <v>95.29000000000001</v>
       </c>
-      <c r="S21" s="6" t="n">
+      <c r="S21" s="7" t="n">
         <v>94.77</v>
       </c>
-      <c r="T21" s="6" t="n">
+      <c r="T21" s="7" t="n">
         <v>94.45</v>
       </c>
-      <c r="U21" s="6" t="n">
+      <c r="U21" s="7" t="n">
         <v>95.59</v>
       </c>
-      <c r="V21" s="6" t="n">
+      <c r="V21" s="7" t="n">
         <v>94.97</v>
       </c>
-      <c r="W21" s="6" t="n">
+      <c r="W21" s="7" t="n">
         <v>97.58</v>
       </c>
-      <c r="X21" s="6" t="n">
+      <c r="X21" s="7" t="n">
         <v>100.17</v>
       </c>
-      <c r="Y21" s="6" t="n">
+      <c r="Y21" s="7" t="n">
         <v>100.55</v>
       </c>
-      <c r="Z21" s="6" t="n">
+      <c r="Z21" s="7" t="n">
         <v>100.31</v>
       </c>
-      <c r="AA21" s="6" t="n">
+      <c r="AA21" s="7" t="n">
         <v>99.81999999999999</v>
       </c>
-      <c r="AB21" s="6" t="n">
+      <c r="AB21" s="7" t="n">
         <v>100.36</v>
       </c>
-      <c r="AC21" s="6" t="n">
+      <c r="AC21" s="7" t="n">
         <v>100.22</v>
       </c>
-      <c r="AD21" s="6" t="n">
+      <c r="AD21" s="7" t="n">
         <v>99.83</v>
       </c>
-      <c r="AE21" s="6" t="n">
+      <c r="AE21" s="7" t="n">
         <v>99.89</v>
       </c>
-      <c r="AF21" s="6" t="n">
+      <c r="AF21" s="7" t="n">
         <v>98.43000000000001</v>
       </c>
-      <c r="AG21" s="6" t="n">
+      <c r="AG21" s="7" t="n">
         <v>96.98999999999999</v>
       </c>
       <c r="AH21" s="6" t="n">
@@ -2111,7 +2141,7 @@
         <v>406.58</v>
       </c>
       <c r="AJ21" s="6" t="inlineStr"/>
-      <c r="AK21" s="7" t="inlineStr"/>
+      <c r="AK21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2122,97 +2152,97 @@
       <c r="B22" s="6" t="n">
         <v>93.7</v>
       </c>
-      <c r="C22" s="6" t="n">
+      <c r="C22" s="7" t="n">
         <v>102.88</v>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="7" t="n">
         <v>103.28</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E22" s="7" t="n">
         <v>104.64</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="F22" s="7" t="n">
         <v>104.51</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="G22" s="7" t="n">
         <v>104.54</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="H22" s="7" t="n">
         <v>105.73</v>
       </c>
-      <c r="I22" s="6" t="n">
+      <c r="I22" s="7" t="n">
         <v>105.16</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="J22" s="7" t="n">
         <v>104.57</v>
       </c>
-      <c r="K22" s="6" t="n">
+      <c r="K22" s="7" t="n">
         <v>106.33</v>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="L22" s="7" t="n">
         <v>108.18</v>
       </c>
-      <c r="M22" s="6" t="n">
+      <c r="M22" s="7" t="n">
         <v>107.34</v>
       </c>
-      <c r="N22" s="6" t="n">
+      <c r="N22" s="7" t="n">
         <v>106.42</v>
       </c>
-      <c r="O22" s="6" t="n">
+      <c r="O22" s="7" t="n">
         <v>105.42</v>
       </c>
-      <c r="P22" s="6" t="n">
+      <c r="P22" s="7" t="n">
         <v>105.52</v>
       </c>
-      <c r="Q22" s="6" t="n">
+      <c r="Q22" s="7" t="n">
         <v>105.13</v>
       </c>
-      <c r="R22" s="6" t="n">
+      <c r="R22" s="7" t="n">
         <v>106.53</v>
       </c>
-      <c r="S22" s="6" t="n">
+      <c r="S22" s="7" t="n">
         <v>106.49</v>
       </c>
-      <c r="T22" s="6" t="n">
+      <c r="T22" s="7" t="n">
         <v>105.56</v>
       </c>
-      <c r="U22" s="6" t="n">
+      <c r="U22" s="7" t="n">
         <v>106.56</v>
       </c>
-      <c r="V22" s="6" t="n">
+      <c r="V22" s="7" t="n">
         <v>105.78</v>
       </c>
-      <c r="W22" s="6" t="n">
+      <c r="W22" s="7" t="n">
         <v>100.33</v>
       </c>
-      <c r="X22" s="6" t="n">
+      <c r="X22" s="7" t="n">
         <v>94.88</v>
       </c>
-      <c r="Y22" s="6" t="n">
+      <c r="Y22" s="7" t="n">
         <v>102.51</v>
       </c>
-      <c r="Z22" s="6" t="n">
+      <c r="Z22" s="7" t="n">
         <v>109.74</v>
       </c>
-      <c r="AA22" s="6" t="n">
+      <c r="AA22" s="7" t="n">
         <v>109.78</v>
       </c>
-      <c r="AB22" s="6" t="n">
+      <c r="AB22" s="7" t="n">
         <v>109.71</v>
       </c>
-      <c r="AC22" s="6" t="n">
+      <c r="AC22" s="7" t="n">
         <v>109.88</v>
       </c>
-      <c r="AD22" s="6" t="n">
+      <c r="AD22" s="7" t="n">
         <v>108.75</v>
       </c>
-      <c r="AE22" s="6" t="n">
+      <c r="AE22" s="7" t="n">
         <v>108.75</v>
       </c>
-      <c r="AF22" s="6" t="n">
+      <c r="AF22" s="7" t="n">
         <v>109.07</v>
       </c>
-      <c r="AG22" s="6" t="n">
+      <c r="AG22" s="7" t="n">
         <v>109.51</v>
       </c>
       <c r="AH22" s="6" t="n">
@@ -2222,7 +2252,7 @@
         <v>387.36</v>
       </c>
       <c r="AJ22" s="6" t="inlineStr"/>
-      <c r="AK22" s="7" t="inlineStr"/>
+      <c r="AK22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -2233,97 +2263,97 @@
       <c r="B23" s="6" t="n">
         <v>94.09999999999999</v>
       </c>
-      <c r="C23" s="6" t="n">
+      <c r="C23" s="7" t="n">
         <v>101.84</v>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="7" t="n">
         <v>102.64</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="E23" s="7" t="n">
         <v>102.76</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="F23" s="7" t="n">
         <v>102.78</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="G23" s="7" t="n">
         <v>102.92</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="H23" s="7" t="n">
         <v>103.32</v>
       </c>
-      <c r="I23" s="6" t="n">
+      <c r="I23" s="7" t="n">
         <v>103.29</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="J23" s="7" t="n">
         <v>102.96</v>
       </c>
-      <c r="K23" s="6" t="n">
+      <c r="K23" s="7" t="n">
         <v>103.86</v>
       </c>
-      <c r="L23" s="6" t="n">
+      <c r="L23" s="7" t="n">
         <v>105.12</v>
       </c>
-      <c r="M23" s="6" t="n">
+      <c r="M23" s="7" t="n">
         <v>104.86</v>
       </c>
-      <c r="N23" s="6" t="n">
+      <c r="N23" s="7" t="n">
         <v>104.06</v>
       </c>
-      <c r="O23" s="6" t="n">
+      <c r="O23" s="7" t="n">
         <v>100.32</v>
       </c>
-      <c r="P23" s="6" t="n">
+      <c r="P23" s="7" t="n">
         <v>100.72</v>
       </c>
-      <c r="Q23" s="6" t="n">
+      <c r="Q23" s="7" t="n">
         <v>100.56</v>
       </c>
-      <c r="R23" s="6" t="n">
+      <c r="R23" s="7" t="n">
         <v>100.99</v>
       </c>
-      <c r="S23" s="6" t="n">
+      <c r="S23" s="7" t="n">
         <v>101.06</v>
       </c>
-      <c r="T23" s="6" t="n">
+      <c r="T23" s="7" t="n">
         <v>100.81</v>
       </c>
-      <c r="U23" s="6" t="n">
+      <c r="U23" s="7" t="n">
         <v>102.33</v>
       </c>
-      <c r="V23" s="6" t="n">
+      <c r="V23" s="7" t="n">
         <v>101.98</v>
       </c>
-      <c r="W23" s="6" t="n">
+      <c r="W23" s="7" t="n">
         <v>103.28</v>
       </c>
-      <c r="X23" s="6" t="n">
+      <c r="X23" s="7" t="n">
         <v>103.92</v>
       </c>
-      <c r="Y23" s="6" t="n">
+      <c r="Y23" s="7" t="n">
         <v>104.17</v>
       </c>
-      <c r="Z23" s="6" t="n">
+      <c r="Z23" s="7" t="n">
         <v>103.63</v>
       </c>
-      <c r="AA23" s="6" t="n">
+      <c r="AA23" s="7" t="n">
         <v>104.24</v>
       </c>
-      <c r="AB23" s="6" t="n">
+      <c r="AB23" s="7" t="n">
         <v>104.07</v>
       </c>
-      <c r="AC23" s="6" t="n">
+      <c r="AC23" s="7" t="n">
         <v>103.92</v>
       </c>
-      <c r="AD23" s="6" t="n">
+      <c r="AD23" s="7" t="n">
         <v>103.71</v>
       </c>
-      <c r="AE23" s="6" t="n">
+      <c r="AE23" s="7" t="n">
         <v>103.58</v>
       </c>
-      <c r="AF23" s="6" t="n">
+      <c r="AF23" s="7" t="n">
         <v>103.91</v>
       </c>
-      <c r="AG23" s="6" t="n">
+      <c r="AG23" s="7" t="n">
         <v>104.5</v>
       </c>
       <c r="AH23" s="6" t="n">
@@ -2333,7 +2363,7 @@
         <v>419.3</v>
       </c>
       <c r="AJ23" s="6" t="inlineStr"/>
-      <c r="AK23" s="7" t="inlineStr"/>
+      <c r="AK23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2344,97 +2374,97 @@
       <c r="B24" s="6" t="n">
         <v>94.5</v>
       </c>
-      <c r="C24" s="6" t="n">
+      <c r="C24" s="7" t="n">
         <v>101.41</v>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="7" t="n">
         <v>101.64</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="E24" s="7" t="n">
         <v>102.16</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="F24" s="7" t="n">
         <v>102.58</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="G24" s="7" t="n">
         <v>102.74</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="H24" s="7" t="n">
         <v>103.05</v>
       </c>
-      <c r="I24" s="6" t="n">
+      <c r="I24" s="7" t="n">
         <v>103.12</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="J24" s="7" t="n">
         <v>103.12</v>
       </c>
-      <c r="K24" s="6" t="n">
+      <c r="K24" s="7" t="n">
         <v>103.72</v>
       </c>
-      <c r="L24" s="6" t="n">
+      <c r="L24" s="7" t="n">
         <v>106.07</v>
       </c>
-      <c r="M24" s="6" t="n">
+      <c r="M24" s="7" t="n">
         <v>105.31</v>
       </c>
-      <c r="N24" s="6" t="n">
+      <c r="N24" s="7" t="n">
         <v>103.62</v>
       </c>
-      <c r="O24" s="6" t="n">
+      <c r="O24" s="7" t="n">
         <v>102.91</v>
       </c>
-      <c r="P24" s="6" t="n">
+      <c r="P24" s="7" t="n">
         <v>103.32</v>
       </c>
-      <c r="Q24" s="6" t="n">
+      <c r="Q24" s="7" t="n">
         <v>103.08</v>
       </c>
-      <c r="R24" s="6" t="n">
+      <c r="R24" s="7" t="n">
         <v>103.9</v>
       </c>
-      <c r="S24" s="6" t="n">
+      <c r="S24" s="7" t="n">
         <v>103.98</v>
       </c>
-      <c r="T24" s="6" t="n">
+      <c r="T24" s="7" t="n">
         <v>103.54</v>
       </c>
-      <c r="U24" s="6" t="n">
+      <c r="U24" s="7" t="n">
         <v>104.47</v>
       </c>
-      <c r="V24" s="6" t="n">
+      <c r="V24" s="7" t="n">
         <v>104.17</v>
       </c>
-      <c r="W24" s="6" t="n">
+      <c r="W24" s="7" t="n">
         <v>104.95</v>
       </c>
-      <c r="X24" s="6" t="n">
+      <c r="X24" s="7" t="n">
         <v>105.45</v>
       </c>
-      <c r="Y24" s="6" t="n">
+      <c r="Y24" s="7" t="n">
         <v>105.52</v>
       </c>
-      <c r="Z24" s="6" t="n">
+      <c r="Z24" s="7" t="n">
         <v>105.91</v>
       </c>
-      <c r="AA24" s="6" t="n">
+      <c r="AA24" s="7" t="n">
         <v>105.18</v>
       </c>
-      <c r="AB24" s="6" t="n">
+      <c r="AB24" s="7" t="n">
         <v>105.34</v>
       </c>
-      <c r="AC24" s="6" t="n">
+      <c r="AC24" s="7" t="n">
         <v>105.46</v>
       </c>
-      <c r="AD24" s="6" t="n">
+      <c r="AD24" s="7" t="n">
         <v>105.41</v>
       </c>
-      <c r="AE24" s="6" t="n">
+      <c r="AE24" s="7" t="n">
         <v>105.26</v>
       </c>
-      <c r="AF24" s="6" t="n">
+      <c r="AF24" s="7" t="n">
         <v>105.79</v>
       </c>
-      <c r="AG24" s="6" t="n">
+      <c r="AG24" s="7" t="n">
         <v>106.08</v>
       </c>
       <c r="AH24" s="6" t="n">
@@ -2444,7 +2474,7 @@
         <v>408.72</v>
       </c>
       <c r="AJ24" s="6" t="inlineStr"/>
-      <c r="AK24" s="7" t="inlineStr"/>
+      <c r="AK24" s="8" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -2455,97 +2485,97 @@
       <c r="B25" s="6" t="n">
         <v>94.90000000000001</v>
       </c>
-      <c r="C25" s="6" t="n">
+      <c r="C25" s="7" t="n">
         <v>89.14</v>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="7" t="n">
         <v>88.89</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="E25" s="7" t="n">
         <v>89.68000000000001</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="F25" s="7" t="n">
         <v>89.27</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="G25" s="7" t="n">
         <v>89.5</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="H25" s="7" t="n">
         <v>90.97</v>
       </c>
-      <c r="I25" s="6" t="n">
+      <c r="I25" s="7" t="n">
         <v>89.84</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="J25" s="7" t="n">
         <v>89.01000000000001</v>
       </c>
-      <c r="K25" s="6" t="n">
+      <c r="K25" s="7" t="n">
         <v>92.48</v>
       </c>
-      <c r="L25" s="6" t="n">
+      <c r="L25" s="7" t="n">
         <v>95.73999999999999</v>
       </c>
-      <c r="M25" s="6" t="n">
+      <c r="M25" s="7" t="n">
         <v>93.39</v>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="N25" s="7" t="n">
         <v>91.67</v>
       </c>
-      <c r="O25" s="6" t="n">
+      <c r="O25" s="7" t="n">
         <v>90.26000000000001</v>
       </c>
-      <c r="P25" s="6" t="n">
+      <c r="P25" s="7" t="n">
         <v>90.45999999999999</v>
       </c>
-      <c r="Q25" s="6" t="n">
+      <c r="Q25" s="7" t="n">
         <v>90.36</v>
       </c>
-      <c r="R25" s="6" t="n">
+      <c r="R25" s="7" t="n">
         <v>91.18000000000001</v>
       </c>
-      <c r="S25" s="6" t="n">
+      <c r="S25" s="7" t="n">
         <v>90.94</v>
       </c>
-      <c r="T25" s="6" t="n">
+      <c r="T25" s="7" t="n">
         <v>90.26000000000001</v>
       </c>
-      <c r="U25" s="6" t="n">
+      <c r="U25" s="7" t="n">
         <v>91.06999999999999</v>
       </c>
-      <c r="V25" s="6" t="n">
+      <c r="V25" s="7" t="n">
         <v>90.27</v>
       </c>
-      <c r="W25" s="6" t="n">
+      <c r="W25" s="7" t="n">
         <v>93.14</v>
       </c>
-      <c r="X25" s="6" t="n">
+      <c r="X25" s="7" t="n">
         <v>95.72</v>
       </c>
-      <c r="Y25" s="6" t="n">
+      <c r="Y25" s="7" t="n">
         <v>95.84</v>
       </c>
-      <c r="Z25" s="6" t="n">
+      <c r="Z25" s="7" t="n">
         <v>95.25</v>
       </c>
-      <c r="AA25" s="6" t="n">
+      <c r="AA25" s="7" t="n">
         <v>94.88</v>
       </c>
-      <c r="AB25" s="6" t="n">
+      <c r="AB25" s="7" t="n">
         <v>94.68000000000001</v>
       </c>
-      <c r="AC25" s="6" t="n">
+      <c r="AC25" s="7" t="n">
         <v>95.34999999999999</v>
       </c>
-      <c r="AD25" s="6" t="n">
+      <c r="AD25" s="7" t="n">
         <v>94.42</v>
       </c>
-      <c r="AE25" s="6" t="n">
+      <c r="AE25" s="7" t="n">
         <v>95.36</v>
       </c>
-      <c r="AF25" s="6" t="n">
+      <c r="AF25" s="7" t="n">
         <v>93.76000000000001</v>
       </c>
-      <c r="AG25" s="6" t="n">
+      <c r="AG25" s="7" t="n">
         <v>92.5</v>
       </c>
       <c r="AH25" s="6" t="n">
@@ -2555,7 +2585,7 @@
         <v>439.51</v>
       </c>
       <c r="AJ25" s="6" t="inlineStr"/>
-      <c r="AK25" s="7" t="inlineStr"/>
+      <c r="AK25" s="8" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -2566,97 +2596,97 @@
       <c r="B26" s="6" t="n">
         <v>95.3</v>
       </c>
-      <c r="C26" s="6" t="n">
+      <c r="C26" s="7" t="n">
         <v>103.11</v>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="7" t="n">
         <v>102.57</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="E26" s="7" t="n">
         <v>102.42</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="F26" s="7" t="n">
         <v>102.64</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="G26" s="7" t="n">
         <v>102.87</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="H26" s="7" t="n">
         <v>103.36</v>
       </c>
-      <c r="I26" s="6" t="n">
+      <c r="I26" s="7" t="n">
         <v>102.36</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="J26" s="7" t="n">
         <v>102.6</v>
       </c>
-      <c r="K26" s="6" t="n">
+      <c r="K26" s="7" t="n">
         <v>103.14</v>
       </c>
-      <c r="L26" s="6" t="n">
+      <c r="L26" s="7" t="n">
         <v>103.19</v>
       </c>
-      <c r="M26" s="6" t="n">
+      <c r="M26" s="7" t="n">
         <v>103.63</v>
       </c>
-      <c r="N26" s="6" t="n">
+      <c r="N26" s="7" t="n">
         <v>103.47</v>
       </c>
-      <c r="O26" s="6" t="n">
+      <c r="O26" s="7" t="n">
         <v>103.23</v>
       </c>
-      <c r="P26" s="6" t="n">
+      <c r="P26" s="7" t="n">
         <v>102.84</v>
       </c>
-      <c r="Q26" s="6" t="n">
+      <c r="Q26" s="7" t="n">
         <v>102.82</v>
       </c>
-      <c r="R26" s="6" t="n">
+      <c r="R26" s="7" t="n">
         <v>103.34</v>
       </c>
-      <c r="S26" s="6" t="n">
+      <c r="S26" s="7" t="n">
         <v>103.46</v>
       </c>
-      <c r="T26" s="6" t="n">
+      <c r="T26" s="7" t="n">
         <v>102.74</v>
       </c>
-      <c r="U26" s="6" t="n">
+      <c r="U26" s="7" t="n">
         <v>103.27</v>
       </c>
-      <c r="V26" s="6" t="n">
+      <c r="V26" s="7" t="n">
         <v>103.25</v>
       </c>
-      <c r="W26" s="6" t="n">
+      <c r="W26" s="7" t="n">
         <v>103.32</v>
       </c>
-      <c r="X26" s="6" t="n">
+      <c r="X26" s="7" t="n">
         <v>103.94</v>
       </c>
-      <c r="Y26" s="6" t="n">
+      <c r="Y26" s="7" t="n">
         <v>103.06</v>
       </c>
-      <c r="Z26" s="6" t="n">
+      <c r="Z26" s="7" t="n">
         <v>103.75</v>
       </c>
-      <c r="AA26" s="6" t="n">
+      <c r="AA26" s="7" t="n">
         <v>103.18</v>
       </c>
-      <c r="AB26" s="6" t="n">
+      <c r="AB26" s="7" t="n">
         <v>103.56</v>
       </c>
-      <c r="AC26" s="6" t="n">
+      <c r="AC26" s="7" t="n">
         <v>103.35</v>
       </c>
-      <c r="AD26" s="6" t="n">
+      <c r="AD26" s="7" t="n">
         <v>103.36</v>
       </c>
-      <c r="AE26" s="6" t="n">
+      <c r="AE26" s="7" t="n">
         <v>103.43</v>
       </c>
-      <c r="AF26" s="6" t="n">
+      <c r="AF26" s="7" t="n">
         <v>104.72</v>
       </c>
-      <c r="AG26" s="6" t="n">
+      <c r="AG26" s="7" t="n">
         <v>105.59</v>
       </c>
       <c r="AH26" s="6" t="n">
@@ -2666,7 +2696,7 @@
         <v>412.36</v>
       </c>
       <c r="AJ26" s="6" t="inlineStr"/>
-      <c r="AK26" s="7" t="inlineStr"/>
+      <c r="AK26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2677,97 +2707,97 @@
       <c r="B27" s="6" t="n">
         <v>95.7</v>
       </c>
-      <c r="C27" s="6" t="n">
+      <c r="C27" s="7" t="n">
         <v>91.16</v>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="7" t="n">
         <v>91.37</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="E27" s="7" t="n">
         <v>92.98999999999999</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="F27" s="7" t="n">
         <v>93.13</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="G27" s="7" t="n">
         <v>93.72</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="H27" s="7" t="n">
         <v>94.86</v>
       </c>
-      <c r="I27" s="6" t="n">
+      <c r="I27" s="7" t="n">
         <v>93.77</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="J27" s="7" t="n">
         <v>93.08</v>
       </c>
-      <c r="K27" s="6" t="n">
+      <c r="K27" s="7" t="n">
         <v>96.44</v>
       </c>
-      <c r="L27" s="6" t="n">
+      <c r="L27" s="7" t="n">
         <v>99.08</v>
       </c>
-      <c r="M27" s="6" t="n">
+      <c r="M27" s="7" t="n">
         <v>97.33</v>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="N27" s="7" t="n">
         <v>95.83</v>
       </c>
-      <c r="O27" s="6" t="n">
+      <c r="O27" s="7" t="n">
         <v>94.39</v>
       </c>
-      <c r="P27" s="6" t="n">
+      <c r="P27" s="7" t="n">
         <v>94.2</v>
       </c>
-      <c r="Q27" s="6" t="n">
+      <c r="Q27" s="7" t="n">
         <v>93.86</v>
       </c>
-      <c r="R27" s="6" t="n">
+      <c r="R27" s="7" t="n">
         <v>94.94</v>
       </c>
-      <c r="S27" s="6" t="n">
+      <c r="S27" s="7" t="n">
         <v>94.95</v>
       </c>
-      <c r="T27" s="6" t="n">
+      <c r="T27" s="7" t="n">
         <v>93.73999999999999</v>
       </c>
-      <c r="U27" s="6" t="n">
+      <c r="U27" s="7" t="n">
         <v>95.06999999999999</v>
       </c>
-      <c r="V27" s="6" t="n">
+      <c r="V27" s="7" t="n">
         <v>94.11</v>
       </c>
-      <c r="W27" s="6" t="n">
+      <c r="W27" s="7" t="n">
         <v>96.31999999999999</v>
       </c>
-      <c r="X27" s="6" t="n">
+      <c r="X27" s="7" t="n">
         <v>99.06999999999999</v>
       </c>
-      <c r="Y27" s="6" t="n">
+      <c r="Y27" s="7" t="n">
         <v>99.26000000000001</v>
       </c>
-      <c r="Z27" s="6" t="n">
+      <c r="Z27" s="7" t="n">
         <v>99.39</v>
       </c>
-      <c r="AA27" s="6" t="n">
+      <c r="AA27" s="7" t="n">
         <v>99.06999999999999</v>
       </c>
-      <c r="AB27" s="6" t="n">
+      <c r="AB27" s="7" t="n">
         <v>99.31</v>
       </c>
-      <c r="AC27" s="6" t="n">
+      <c r="AC27" s="7" t="n">
         <v>99.2</v>
       </c>
-      <c r="AD27" s="6" t="n">
+      <c r="AD27" s="7" t="n">
         <v>99.47</v>
       </c>
-      <c r="AE27" s="6" t="n">
+      <c r="AE27" s="7" t="n">
         <v>98.97</v>
       </c>
-      <c r="AF27" s="6" t="n">
+      <c r="AF27" s="7" t="n">
         <v>97.64</v>
       </c>
-      <c r="AG27" s="6" t="n">
+      <c r="AG27" s="7" t="n">
         <v>96.20999999999999</v>
       </c>
       <c r="AH27" s="6" t="n">
@@ -2777,7 +2807,7 @@
         <v>398.86</v>
       </c>
       <c r="AJ27" s="6" t="inlineStr"/>
-      <c r="AK27" s="7" t="inlineStr"/>
+      <c r="AK27" s="8" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -2788,97 +2818,97 @@
       <c r="B28" s="6" t="n">
         <v>96.09999999999999</v>
       </c>
-      <c r="C28" s="6" t="n">
+      <c r="C28" s="9" t="n">
         <v>52.79</v>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="9" t="n">
         <v>53.24</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="E28" s="9" t="n">
         <v>53.39</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="F28" s="9" t="n">
         <v>52.91</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="G28" s="9" t="n">
         <v>52.24</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="H28" s="7" t="n">
         <v>54.92</v>
       </c>
-      <c r="I28" s="6" t="n">
+      <c r="I28" s="7" t="n">
         <v>54.52</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="J28" s="9" t="n">
         <v>53.58</v>
       </c>
-      <c r="K28" s="6" t="n">
+      <c r="K28" s="7" t="n">
         <v>54.41</v>
       </c>
-      <c r="L28" s="6" t="n">
+      <c r="L28" s="7" t="n">
         <v>75.14</v>
       </c>
-      <c r="M28" s="6" t="n">
+      <c r="M28" s="7" t="n">
         <v>97.26000000000001</v>
       </c>
-      <c r="N28" s="6" t="n">
+      <c r="N28" s="7" t="n">
         <v>95.93000000000001</v>
       </c>
-      <c r="O28" s="6" t="n">
+      <c r="O28" s="7" t="n">
         <v>95.95</v>
       </c>
-      <c r="P28" s="6" t="n">
+      <c r="P28" s="7" t="n">
         <v>71.93000000000001</v>
       </c>
-      <c r="Q28" s="6" t="n">
+      <c r="Q28" s="7" t="n">
         <v>72.12</v>
       </c>
-      <c r="R28" s="6" t="n">
+      <c r="R28" s="7" t="n">
         <v>84.53</v>
       </c>
-      <c r="S28" s="6" t="n">
+      <c r="S28" s="7" t="n">
         <v>96.76000000000001</v>
       </c>
-      <c r="T28" s="6" t="n">
+      <c r="T28" s="7" t="n">
         <v>96.43000000000001</v>
       </c>
-      <c r="U28" s="6" t="n">
+      <c r="U28" s="7" t="n">
         <v>96.91</v>
       </c>
-      <c r="V28" s="6" t="n">
+      <c r="V28" s="7" t="n">
         <v>97.02</v>
       </c>
-      <c r="W28" s="6" t="n">
+      <c r="W28" s="7" t="n">
         <v>97.68000000000001</v>
       </c>
-      <c r="X28" s="6" t="n">
+      <c r="X28" s="7" t="n">
         <v>98.02</v>
       </c>
-      <c r="Y28" s="6" t="n">
+      <c r="Y28" s="7" t="n">
         <v>97.98999999999999</v>
       </c>
-      <c r="Z28" s="6" t="n">
+      <c r="Z28" s="7" t="n">
         <v>98.39</v>
       </c>
-      <c r="AA28" s="6" t="n">
+      <c r="AA28" s="7" t="n">
         <v>97.87</v>
       </c>
-      <c r="AB28" s="6" t="n">
+      <c r="AB28" s="7" t="n">
         <v>97.86</v>
       </c>
-      <c r="AC28" s="6" t="n">
+      <c r="AC28" s="7" t="n">
         <v>97.76000000000001</v>
       </c>
-      <c r="AD28" s="6" t="n">
+      <c r="AD28" s="7" t="n">
         <v>97.93000000000001</v>
       </c>
-      <c r="AE28" s="6" t="n">
+      <c r="AE28" s="7" t="n">
         <v>98.01000000000001</v>
       </c>
-      <c r="AF28" s="6" t="n">
+      <c r="AF28" s="7" t="n">
         <v>98.28</v>
       </c>
-      <c r="AG28" s="6" t="n">
+      <c r="AG28" s="7" t="n">
         <v>98.55</v>
       </c>
       <c r="AH28" s="6" t="n">
@@ -2888,7 +2918,7 @@
         <v>546.02</v>
       </c>
       <c r="AJ28" s="6" t="inlineStr"/>
-      <c r="AK28" s="7" t="inlineStr"/>
+      <c r="AK28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -2899,97 +2929,97 @@
       <c r="B29" s="6" t="n">
         <v>96.5</v>
       </c>
-      <c r="C29" s="6" t="n">
+      <c r="C29" s="7" t="n">
         <v>95.69</v>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="7" t="n">
         <v>95.77</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="E29" s="7" t="n">
         <v>96.58</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="F29" s="7" t="n">
         <v>96.54000000000001</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="G29" s="7" t="n">
         <v>96.73</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="H29" s="7" t="n">
         <v>97.01000000000001</v>
       </c>
-      <c r="I29" s="6" t="n">
+      <c r="I29" s="7" t="n">
         <v>96.31</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="J29" s="7" t="n">
         <v>96.36</v>
       </c>
-      <c r="K29" s="6" t="n">
+      <c r="K29" s="7" t="n">
         <v>98.44</v>
       </c>
-      <c r="L29" s="6" t="n">
+      <c r="L29" s="7" t="n">
         <v>101.3</v>
       </c>
-      <c r="M29" s="6" t="n">
+      <c r="M29" s="7" t="n">
         <v>99.37</v>
       </c>
-      <c r="N29" s="6" t="n">
+      <c r="N29" s="7" t="n">
         <v>97.51000000000001</v>
       </c>
-      <c r="O29" s="6" t="n">
+      <c r="O29" s="7" t="n">
         <v>96.90000000000001</v>
       </c>
-      <c r="P29" s="6" t="n">
+      <c r="P29" s="7" t="n">
         <v>97.31999999999999</v>
       </c>
-      <c r="Q29" s="6" t="n">
+      <c r="Q29" s="7" t="n">
         <v>96.98</v>
       </c>
-      <c r="R29" s="6" t="n">
+      <c r="R29" s="7" t="n">
         <v>97.51000000000001</v>
       </c>
-      <c r="S29" s="6" t="n">
+      <c r="S29" s="7" t="n">
         <v>97.73</v>
       </c>
-      <c r="T29" s="6" t="n">
+      <c r="T29" s="7" t="n">
         <v>96.93000000000001</v>
       </c>
-      <c r="U29" s="6" t="n">
+      <c r="U29" s="7" t="n">
         <v>97.73</v>
       </c>
-      <c r="V29" s="6" t="n">
+      <c r="V29" s="7" t="n">
         <v>96.91</v>
       </c>
-      <c r="W29" s="6" t="n">
+      <c r="W29" s="7" t="n">
         <v>98.98999999999999</v>
       </c>
-      <c r="X29" s="6" t="n">
+      <c r="X29" s="7" t="n">
         <v>101.66</v>
       </c>
-      <c r="Y29" s="6" t="n">
+      <c r="Y29" s="7" t="n">
         <v>101.8</v>
       </c>
-      <c r="Z29" s="6" t="n">
+      <c r="Z29" s="7" t="n">
         <v>101.18</v>
       </c>
-      <c r="AA29" s="6" t="n">
+      <c r="AA29" s="7" t="n">
         <v>101.54</v>
       </c>
-      <c r="AB29" s="6" t="n">
+      <c r="AB29" s="7" t="n">
         <v>101.34</v>
       </c>
-      <c r="AC29" s="6" t="n">
+      <c r="AC29" s="7" t="n">
         <v>101.57</v>
       </c>
-      <c r="AD29" s="6" t="n">
+      <c r="AD29" s="7" t="n">
         <v>101.68</v>
       </c>
-      <c r="AE29" s="6" t="n">
+      <c r="AE29" s="7" t="n">
         <v>101.66</v>
       </c>
-      <c r="AF29" s="6" t="n">
+      <c r="AF29" s="7" t="n">
         <v>100.26</v>
       </c>
-      <c r="AG29" s="6" t="n">
+      <c r="AG29" s="7" t="n">
         <v>98.88</v>
       </c>
       <c r="AH29" s="6" t="n">
@@ -2999,7 +3029,7 @@
         <v>391.54</v>
       </c>
       <c r="AJ29" s="6" t="inlineStr"/>
-      <c r="AK29" s="7" t="inlineStr"/>
+      <c r="AK29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -3010,97 +3040,97 @@
       <c r="B30" s="6" t="n">
         <v>96.90000000000001</v>
       </c>
-      <c r="C30" s="6" t="n">
+      <c r="C30" s="7" t="n">
         <v>106.13</v>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="7" t="n">
         <v>105.07</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="E30" s="7" t="n">
         <v>105.17</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="F30" s="7" t="n">
         <v>104.98</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="G30" s="7" t="n">
         <v>105.09</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="H30" s="7" t="n">
         <v>105.69</v>
       </c>
-      <c r="I30" s="6" t="n">
+      <c r="I30" s="7" t="n">
         <v>105.12</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="J30" s="7" t="n">
         <v>104.79</v>
       </c>
-      <c r="K30" s="6" t="n">
+      <c r="K30" s="7" t="n">
         <v>107.12</v>
       </c>
-      <c r="L30" s="6" t="n">
+      <c r="L30" s="7" t="n">
         <v>108.92</v>
       </c>
-      <c r="M30" s="6" t="n">
+      <c r="M30" s="7" t="n">
         <v>107.68</v>
       </c>
-      <c r="N30" s="6" t="n">
+      <c r="N30" s="7" t="n">
         <v>106.08</v>
       </c>
-      <c r="O30" s="6" t="n">
+      <c r="O30" s="7" t="n">
         <v>105.24</v>
       </c>
-      <c r="P30" s="6" t="n">
+      <c r="P30" s="7" t="n">
         <v>105.14</v>
       </c>
-      <c r="Q30" s="6" t="n">
+      <c r="Q30" s="7" t="n">
         <v>105.33</v>
       </c>
-      <c r="R30" s="6" t="n">
+      <c r="R30" s="7" t="n">
         <v>105.77</v>
       </c>
-      <c r="S30" s="6" t="n">
+      <c r="S30" s="7" t="n">
         <v>105.61</v>
       </c>
-      <c r="T30" s="6" t="n">
+      <c r="T30" s="7" t="n">
         <v>105.26</v>
       </c>
-      <c r="U30" s="6" t="n">
+      <c r="U30" s="7" t="n">
         <v>105.96</v>
       </c>
-      <c r="V30" s="6" t="n">
+      <c r="V30" s="7" t="n">
         <v>105.32</v>
       </c>
-      <c r="W30" s="6" t="n">
+      <c r="W30" s="7" t="n">
         <v>107.3</v>
       </c>
-      <c r="X30" s="6" t="n">
+      <c r="X30" s="7" t="n">
         <v>108.94</v>
       </c>
-      <c r="Y30" s="6" t="n">
+      <c r="Y30" s="7" t="n">
         <v>108.86</v>
       </c>
-      <c r="Z30" s="6" t="n">
+      <c r="Z30" s="7" t="n">
         <v>109.09</v>
       </c>
-      <c r="AA30" s="6" t="n">
+      <c r="AA30" s="7" t="n">
         <v>108.56</v>
       </c>
-      <c r="AB30" s="6" t="n">
+      <c r="AB30" s="7" t="n">
         <v>108.91</v>
       </c>
-      <c r="AC30" s="6" t="n">
+      <c r="AC30" s="7" t="n">
         <v>108.65</v>
       </c>
-      <c r="AD30" s="6" t="n">
+      <c r="AD30" s="7" t="n">
         <v>108.59</v>
       </c>
-      <c r="AE30" s="6" t="n">
+      <c r="AE30" s="7" t="n">
         <v>108.64</v>
       </c>
-      <c r="AF30" s="6" t="n">
+      <c r="AF30" s="7" t="n">
         <v>107.97</v>
       </c>
-      <c r="AG30" s="6" t="n">
+      <c r="AG30" s="7" t="n">
         <v>106.94</v>
       </c>
       <c r="AH30" s="6" t="n">
@@ -3110,7 +3140,7 @@
         <v>476.01</v>
       </c>
       <c r="AJ30" s="6" t="inlineStr"/>
-      <c r="AK30" s="7" t="inlineStr"/>
+      <c r="AK30" s="8" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -3121,97 +3151,97 @@
       <c r="B31" s="6" t="n">
         <v>97.3</v>
       </c>
-      <c r="C31" s="6" t="n">
+      <c r="C31" s="9" t="n">
         <v>50.96</v>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="9" t="n">
         <v>51.09</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="E31" s="9" t="n">
         <v>51.49</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="F31" s="9" t="n">
         <v>51.17</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="G31" s="9" t="n">
         <v>50.6</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="H31" s="9" t="n">
         <v>53.72</v>
       </c>
-      <c r="I31" s="6" t="n">
+      <c r="I31" s="7" t="n">
         <v>54.82</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="J31" s="9" t="n">
         <v>51.84</v>
       </c>
-      <c r="K31" s="6" t="n">
+      <c r="K31" s="9" t="n">
         <v>51.62</v>
       </c>
-      <c r="L31" s="6" t="n">
+      <c r="L31" s="9" t="n">
         <v>50.18</v>
       </c>
-      <c r="M31" s="6" t="n">
+      <c r="M31" s="7" t="n">
         <v>54.43</v>
       </c>
-      <c r="N31" s="6" t="n">
+      <c r="N31" s="7" t="n">
         <v>58.57</v>
       </c>
-      <c r="O31" s="6" t="n">
+      <c r="O31" s="9" t="n">
         <v>53.3</v>
       </c>
-      <c r="P31" s="6" t="n">
+      <c r="P31" s="7" t="n">
         <v>55.63</v>
       </c>
-      <c r="Q31" s="6" t="n">
+      <c r="Q31" s="9" t="n">
         <v>53.83</v>
       </c>
-      <c r="R31" s="6" t="n">
+      <c r="R31" s="7" t="n">
         <v>55.09</v>
       </c>
-      <c r="S31" s="6" t="n">
+      <c r="S31" s="7" t="n">
         <v>55.61</v>
       </c>
-      <c r="T31" s="6" t="n">
+      <c r="T31" s="9" t="n">
         <v>53.61</v>
       </c>
-      <c r="U31" s="6" t="n">
+      <c r="U31" s="7" t="n">
         <v>56.99</v>
       </c>
-      <c r="V31" s="6" t="n">
+      <c r="V31" s="9" t="n">
         <v>53.82</v>
       </c>
-      <c r="W31" s="6" t="n">
+      <c r="W31" s="9" t="n">
         <v>51.9</v>
       </c>
-      <c r="X31" s="6" t="n">
+      <c r="X31" s="9" t="n">
         <v>49.27</v>
       </c>
-      <c r="Y31" s="6" t="n">
+      <c r="Y31" s="9" t="n">
         <v>49.44</v>
       </c>
-      <c r="Z31" s="6" t="n">
+      <c r="Z31" s="9" t="n">
         <v>50.36</v>
       </c>
-      <c r="AA31" s="6" t="n">
+      <c r="AA31" s="9" t="n">
         <v>49.75</v>
       </c>
-      <c r="AB31" s="6" t="n">
+      <c r="AB31" s="9" t="n">
         <v>49.7</v>
       </c>
-      <c r="AC31" s="6" t="n">
+      <c r="AC31" s="9" t="n">
         <v>49.16</v>
       </c>
-      <c r="AD31" s="6" t="n">
+      <c r="AD31" s="9" t="n">
         <v>50.04</v>
       </c>
-      <c r="AE31" s="6" t="n">
+      <c r="AE31" s="9" t="n">
         <v>49.68</v>
       </c>
-      <c r="AF31" s="6" t="n">
+      <c r="AF31" s="7" t="n">
         <v>55.52</v>
       </c>
-      <c r="AG31" s="6" t="n">
+      <c r="AG31" s="7" t="n">
         <v>61.41</v>
       </c>
       <c r="AH31" s="6" t="n">
@@ -3221,7 +3251,7 @@
         <v>703.75</v>
       </c>
       <c r="AJ31" s="6" t="inlineStr"/>
-      <c r="AK31" s="7" t="inlineStr"/>
+      <c r="AK31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -3232,97 +3262,97 @@
       <c r="B32" s="6" t="n">
         <v>97.7</v>
       </c>
-      <c r="C32" s="6" t="n">
+      <c r="C32" s="7" t="n">
         <v>87.5</v>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="7" t="n">
         <v>86.09</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="E32" s="7" t="n">
         <v>88.16</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="F32" s="7" t="n">
         <v>88.63</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="G32" s="7" t="n">
         <v>88.90000000000001</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="H32" s="7" t="n">
         <v>89.79000000000001</v>
       </c>
-      <c r="I32" s="6" t="n">
+      <c r="I32" s="7" t="n">
         <v>89.31999999999999</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="J32" s="7" t="n">
         <v>88.58</v>
       </c>
-      <c r="K32" s="6" t="n">
+      <c r="K32" s="7" t="n">
         <v>92.53</v>
       </c>
-      <c r="L32" s="6" t="n">
+      <c r="L32" s="7" t="n">
         <v>95.92</v>
       </c>
-      <c r="M32" s="6" t="n">
+      <c r="M32" s="7" t="n">
         <v>93.44</v>
       </c>
-      <c r="N32" s="6" t="n">
+      <c r="N32" s="7" t="n">
         <v>90.87</v>
       </c>
-      <c r="O32" s="6" t="n">
+      <c r="O32" s="7" t="n">
         <v>88.67</v>
       </c>
-      <c r="P32" s="6" t="n">
+      <c r="P32" s="7" t="n">
         <v>89.11</v>
       </c>
-      <c r="Q32" s="6" t="n">
+      <c r="Q32" s="7" t="n">
         <v>88.59</v>
       </c>
-      <c r="R32" s="6" t="n">
+      <c r="R32" s="7" t="n">
         <v>89.87</v>
       </c>
-      <c r="S32" s="6" t="n">
+      <c r="S32" s="7" t="n">
         <v>90.02</v>
       </c>
-      <c r="T32" s="6" t="n">
+      <c r="T32" s="7" t="n">
         <v>87.84</v>
       </c>
-      <c r="U32" s="6" t="n">
+      <c r="U32" s="7" t="n">
         <v>89.95999999999999</v>
       </c>
-      <c r="V32" s="6" t="n">
+      <c r="V32" s="7" t="n">
         <v>88.63</v>
       </c>
-      <c r="W32" s="6" t="n">
+      <c r="W32" s="7" t="n">
         <v>92.45999999999999</v>
       </c>
-      <c r="X32" s="6" t="n">
+      <c r="X32" s="7" t="n">
         <v>96.26000000000001</v>
       </c>
-      <c r="Y32" s="6" t="n">
+      <c r="Y32" s="7" t="n">
         <v>96.79000000000001</v>
       </c>
-      <c r="Z32" s="6" t="n">
+      <c r="Z32" s="7" t="n">
         <v>96.63</v>
       </c>
-      <c r="AA32" s="6" t="n">
+      <c r="AA32" s="7" t="n">
         <v>96.48</v>
       </c>
-      <c r="AB32" s="6" t="n">
+      <c r="AB32" s="7" t="n">
         <v>96.76000000000001</v>
       </c>
-      <c r="AC32" s="6" t="n">
+      <c r="AC32" s="7" t="n">
         <v>96.38</v>
       </c>
-      <c r="AD32" s="6" t="n">
+      <c r="AD32" s="7" t="n">
         <v>96.31</v>
       </c>
-      <c r="AE32" s="6" t="n">
+      <c r="AE32" s="7" t="n">
         <v>96.16</v>
       </c>
-      <c r="AF32" s="6" t="n">
+      <c r="AF32" s="7" t="n">
         <v>93.79000000000001</v>
       </c>
-      <c r="AG32" s="6" t="n">
+      <c r="AG32" s="7" t="n">
         <v>91.77</v>
       </c>
       <c r="AH32" s="6" t="n">
@@ -3332,7 +3362,7 @@
         <v>413.77</v>
       </c>
       <c r="AJ32" s="6" t="inlineStr"/>
-      <c r="AK32" s="7" t="inlineStr"/>
+      <c r="AK32" s="8" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -3343,97 +3373,97 @@
       <c r="B33" s="6" t="n">
         <v>98.09999999999999</v>
       </c>
-      <c r="C33" s="6" t="n">
+      <c r="C33" s="7" t="n">
         <v>93</v>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="7" t="n">
         <v>90.98</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="E33" s="7" t="n">
         <v>89.84</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="F33" s="7" t="n">
         <v>91.18000000000001</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="G33" s="7" t="n">
         <v>91.06999999999999</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="H33" s="7" t="n">
         <v>90.76000000000001</v>
       </c>
-      <c r="I33" s="6" t="n">
+      <c r="I33" s="7" t="n">
         <v>90.42</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="J33" s="7" t="n">
         <v>90.91</v>
       </c>
-      <c r="K33" s="6" t="n">
+      <c r="K33" s="7" t="n">
         <v>92.01000000000001</v>
       </c>
-      <c r="L33" s="6" t="n">
+      <c r="L33" s="7" t="n">
         <v>95.33</v>
       </c>
-      <c r="M33" s="6" t="n">
+      <c r="M33" s="7" t="n">
         <v>92.98</v>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="N33" s="7" t="n">
         <v>90.56</v>
       </c>
-      <c r="O33" s="6" t="n">
+      <c r="O33" s="7" t="n">
         <v>90.81999999999999</v>
       </c>
-      <c r="P33" s="6" t="n">
+      <c r="P33" s="7" t="n">
         <v>90.56</v>
       </c>
-      <c r="Q33" s="6" t="n">
+      <c r="Q33" s="7" t="n">
         <v>91.73</v>
       </c>
-      <c r="R33" s="6" t="n">
+      <c r="R33" s="7" t="n">
         <v>91.59999999999999</v>
       </c>
-      <c r="S33" s="6" t="n">
+      <c r="S33" s="7" t="n">
         <v>91.7</v>
       </c>
-      <c r="T33" s="6" t="n">
+      <c r="T33" s="7" t="n">
         <v>91.56</v>
       </c>
-      <c r="U33" s="6" t="n">
+      <c r="U33" s="7" t="n">
         <v>91.42</v>
       </c>
-      <c r="V33" s="6" t="n">
+      <c r="V33" s="7" t="n">
         <v>91.79000000000001</v>
       </c>
-      <c r="W33" s="6" t="n">
+      <c r="W33" s="7" t="n">
         <v>93.86</v>
       </c>
-      <c r="X33" s="6" t="n">
+      <c r="X33" s="7" t="n">
         <v>95.48</v>
       </c>
-      <c r="Y33" s="6" t="n">
+      <c r="Y33" s="7" t="n">
         <v>95.56</v>
       </c>
-      <c r="Z33" s="6" t="n">
+      <c r="Z33" s="7" t="n">
         <v>95.55</v>
       </c>
-      <c r="AA33" s="6" t="n">
+      <c r="AA33" s="7" t="n">
         <v>95.70999999999999</v>
       </c>
-      <c r="AB33" s="6" t="n">
+      <c r="AB33" s="7" t="n">
         <v>95.95999999999999</v>
       </c>
-      <c r="AC33" s="6" t="n">
+      <c r="AC33" s="7" t="n">
         <v>95.77</v>
       </c>
-      <c r="AD33" s="6" t="n">
+      <c r="AD33" s="7" t="n">
         <v>95.66</v>
       </c>
-      <c r="AE33" s="6" t="n">
+      <c r="AE33" s="7" t="n">
         <v>95.66</v>
       </c>
-      <c r="AF33" s="6" t="n">
+      <c r="AF33" s="7" t="n">
         <v>93.38</v>
       </c>
-      <c r="AG33" s="6" t="n">
+      <c r="AG33" s="7" t="n">
         <v>91.63</v>
       </c>
       <c r="AH33" s="6" t="n">
@@ -3443,7 +3473,7 @@
         <v>438.53</v>
       </c>
       <c r="AJ33" s="6" t="inlineStr"/>
-      <c r="AK33" s="7" t="inlineStr"/>
+      <c r="AK33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -3454,97 +3484,97 @@
       <c r="B34" s="6" t="n">
         <v>98.5</v>
       </c>
-      <c r="C34" s="6" t="n">
+      <c r="C34" s="7" t="n">
         <v>88.67</v>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D34" s="7" t="n">
         <v>87.5</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="E34" s="7" t="n">
         <v>87.81999999999999</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="F34" s="7" t="n">
         <v>87.62</v>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="G34" s="7" t="n">
         <v>87.64</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="H34" s="7" t="n">
         <v>88.52</v>
       </c>
-      <c r="I34" s="6" t="n">
+      <c r="I34" s="7" t="n">
         <v>88.34999999999999</v>
       </c>
-      <c r="J34" s="6" t="n">
+      <c r="J34" s="7" t="n">
         <v>87.61</v>
       </c>
-      <c r="K34" s="6" t="n">
+      <c r="K34" s="7" t="n">
         <v>89.45</v>
       </c>
-      <c r="L34" s="6" t="n">
+      <c r="L34" s="7" t="n">
         <v>90.98</v>
       </c>
-      <c r="M34" s="6" t="n">
+      <c r="M34" s="7" t="n">
         <v>90.31</v>
       </c>
-      <c r="N34" s="6" t="n">
+      <c r="N34" s="7" t="n">
         <v>88.88</v>
       </c>
-      <c r="O34" s="6" t="n">
+      <c r="O34" s="7" t="n">
         <v>88.42</v>
       </c>
-      <c r="P34" s="6" t="n">
+      <c r="P34" s="7" t="n">
         <v>88.13</v>
       </c>
-      <c r="Q34" s="6" t="n">
+      <c r="Q34" s="7" t="n">
         <v>88.22</v>
       </c>
-      <c r="R34" s="6" t="n">
+      <c r="R34" s="7" t="n">
         <v>88.58</v>
       </c>
-      <c r="S34" s="6" t="n">
+      <c r="S34" s="7" t="n">
         <v>88.66</v>
       </c>
-      <c r="T34" s="6" t="n">
+      <c r="T34" s="7" t="n">
         <v>88.23</v>
       </c>
-      <c r="U34" s="6" t="n">
+      <c r="U34" s="7" t="n">
         <v>88.87</v>
       </c>
-      <c r="V34" s="6" t="n">
+      <c r="V34" s="7" t="n">
         <v>88.36</v>
       </c>
-      <c r="W34" s="6" t="n">
+      <c r="W34" s="7" t="n">
         <v>89.94</v>
       </c>
-      <c r="X34" s="6" t="n">
+      <c r="X34" s="7" t="n">
         <v>91.51000000000001</v>
       </c>
-      <c r="Y34" s="6" t="n">
+      <c r="Y34" s="7" t="n">
         <v>91.56999999999999</v>
       </c>
-      <c r="Z34" s="6" t="n">
+      <c r="Z34" s="7" t="n">
         <v>91.45</v>
       </c>
-      <c r="AA34" s="6" t="n">
+      <c r="AA34" s="7" t="n">
         <v>91.41</v>
       </c>
-      <c r="AB34" s="6" t="n">
+      <c r="AB34" s="7" t="n">
         <v>91.34</v>
       </c>
-      <c r="AC34" s="6" t="n">
+      <c r="AC34" s="7" t="n">
         <v>91.48999999999999</v>
       </c>
-      <c r="AD34" s="6" t="n">
+      <c r="AD34" s="7" t="n">
         <v>91.63</v>
       </c>
-      <c r="AE34" s="6" t="n">
+      <c r="AE34" s="7" t="n">
         <v>91.52</v>
       </c>
-      <c r="AF34" s="6" t="n">
+      <c r="AF34" s="7" t="n">
         <v>91.20999999999999</v>
       </c>
-      <c r="AG34" s="6" t="n">
+      <c r="AG34" s="7" t="n">
         <v>90.66</v>
       </c>
       <c r="AH34" s="6" t="n">
@@ -3554,7 +3584,7 @@
         <v>496.73</v>
       </c>
       <c r="AJ34" s="6" t="inlineStr"/>
-      <c r="AK34" s="7" t="inlineStr"/>
+      <c r="AK34" s="8" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -3565,97 +3595,97 @@
       <c r="B35" s="6" t="n">
         <v>98.90000000000001</v>
       </c>
-      <c r="C35" s="6" t="n">
+      <c r="C35" s="7" t="n">
         <v>96.28</v>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="7" t="n">
         <v>95.2</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="E35" s="7" t="n">
         <v>93.51000000000001</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="F35" s="7" t="n">
         <v>93.5</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="G35" s="7" t="n">
         <v>93.28</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="H35" s="7" t="n">
         <v>94.70999999999999</v>
       </c>
-      <c r="I35" s="6" t="n">
+      <c r="I35" s="7" t="n">
         <v>94.20999999999999</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="J35" s="7" t="n">
         <v>93.73999999999999</v>
       </c>
-      <c r="K35" s="6" t="n">
+      <c r="K35" s="7" t="n">
         <v>97.06</v>
       </c>
-      <c r="L35" s="6" t="n">
+      <c r="L35" s="7" t="n">
         <v>99.94</v>
       </c>
-      <c r="M35" s="6" t="n">
+      <c r="M35" s="7" t="n">
         <v>97.87</v>
       </c>
-      <c r="N35" s="6" t="n">
+      <c r="N35" s="7" t="n">
         <v>95</v>
       </c>
-      <c r="O35" s="6" t="n">
+      <c r="O35" s="7" t="n">
         <v>94.31999999999999</v>
       </c>
-      <c r="P35" s="6" t="n">
+      <c r="P35" s="7" t="n">
         <v>94.08</v>
       </c>
-      <c r="Q35" s="6" t="n">
+      <c r="Q35" s="7" t="n">
         <v>94.43000000000001</v>
       </c>
-      <c r="R35" s="6" t="n">
+      <c r="R35" s="7" t="n">
         <v>94.98</v>
       </c>
-      <c r="S35" s="6" t="n">
+      <c r="S35" s="7" t="n">
         <v>95.19</v>
       </c>
-      <c r="T35" s="6" t="n">
+      <c r="T35" s="7" t="n">
         <v>94.83</v>
       </c>
-      <c r="U35" s="6" t="n">
+      <c r="U35" s="7" t="n">
         <v>95.59</v>
       </c>
-      <c r="V35" s="6" t="n">
+      <c r="V35" s="7" t="n">
         <v>94.31</v>
       </c>
-      <c r="W35" s="6" t="n">
+      <c r="W35" s="7" t="n">
         <v>96.84</v>
       </c>
-      <c r="X35" s="6" t="n">
+      <c r="X35" s="7" t="n">
         <v>99.69</v>
       </c>
-      <c r="Y35" s="6" t="n">
+      <c r="Y35" s="7" t="n">
         <v>99.31999999999999</v>
       </c>
-      <c r="Z35" s="6" t="n">
+      <c r="Z35" s="7" t="n">
         <v>99.48</v>
       </c>
-      <c r="AA35" s="6" t="n">
+      <c r="AA35" s="7" t="n">
         <v>99.34</v>
       </c>
-      <c r="AB35" s="6" t="n">
+      <c r="AB35" s="7" t="n">
         <v>99.56</v>
       </c>
-      <c r="AC35" s="6" t="n">
+      <c r="AC35" s="7" t="n">
         <v>99.34</v>
       </c>
-      <c r="AD35" s="6" t="n">
+      <c r="AD35" s="7" t="n">
         <v>99.19</v>
       </c>
-      <c r="AE35" s="6" t="n">
+      <c r="AE35" s="7" t="n">
         <v>99.31999999999999</v>
       </c>
-      <c r="AF35" s="6" t="n">
+      <c r="AF35" s="7" t="n">
         <v>97.73</v>
       </c>
-      <c r="AG35" s="6" t="n">
+      <c r="AG35" s="7" t="n">
         <v>96.22</v>
       </c>
       <c r="AH35" s="6" t="n">
@@ -3665,7 +3695,7 @@
         <v>387.7</v>
       </c>
       <c r="AJ35" s="6" t="inlineStr"/>
-      <c r="AK35" s="7" t="inlineStr"/>
+      <c r="AK35" s="8" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -3676,97 +3706,97 @@
       <c r="B36" s="6" t="n">
         <v>99.3</v>
       </c>
-      <c r="C36" s="6" t="n">
+      <c r="C36" s="7" t="n">
         <v>100.73</v>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D36" s="7" t="n">
         <v>100.51</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="E36" s="7" t="n">
         <v>100.67</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="F36" s="7" t="n">
         <v>100.09</v>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="G36" s="7" t="n">
         <v>100.42</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="H36" s="7" t="n">
         <v>101.41</v>
       </c>
-      <c r="I36" s="6" t="n">
+      <c r="I36" s="7" t="n">
         <v>101.02</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="J36" s="7" t="n">
         <v>100.88</v>
       </c>
-      <c r="K36" s="6" t="n">
+      <c r="K36" s="7" t="n">
         <v>101.19</v>
       </c>
-      <c r="L36" s="6" t="n">
+      <c r="L36" s="7" t="n">
         <v>100.89</v>
       </c>
-      <c r="M36" s="6" t="n">
+      <c r="M36" s="7" t="n">
         <v>100.48</v>
       </c>
-      <c r="N36" s="6" t="n">
+      <c r="N36" s="7" t="n">
         <v>101.38</v>
       </c>
-      <c r="O36" s="6" t="n">
+      <c r="O36" s="7" t="n">
         <v>101.37</v>
       </c>
-      <c r="P36" s="6" t="n">
+      <c r="P36" s="7" t="n">
         <v>100.68</v>
       </c>
-      <c r="Q36" s="6" t="n">
+      <c r="Q36" s="7" t="n">
         <v>101.06</v>
       </c>
-      <c r="R36" s="6" t="n">
+      <c r="R36" s="7" t="n">
         <v>100.97</v>
       </c>
-      <c r="S36" s="6" t="n">
+      <c r="S36" s="7" t="n">
         <v>100.17</v>
       </c>
-      <c r="T36" s="6" t="n">
+      <c r="T36" s="7" t="n">
         <v>101.12</v>
       </c>
-      <c r="U36" s="6" t="n">
+      <c r="U36" s="7" t="n">
         <v>101.11</v>
       </c>
-      <c r="V36" s="6" t="n">
+      <c r="V36" s="7" t="n">
         <v>101.01</v>
       </c>
-      <c r="W36" s="6" t="n">
+      <c r="W36" s="7" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="X36" s="6" t="n">
+      <c r="X36" s="7" t="n">
         <v>99.19</v>
       </c>
-      <c r="Y36" s="6" t="n">
+      <c r="Y36" s="7" t="n">
         <v>99.81999999999999</v>
       </c>
-      <c r="Z36" s="6" t="n">
+      <c r="Z36" s="7" t="n">
         <v>100.26</v>
       </c>
-      <c r="AA36" s="6" t="n">
+      <c r="AA36" s="7" t="n">
         <v>99.18000000000001</v>
       </c>
-      <c r="AB36" s="6" t="n">
+      <c r="AB36" s="7" t="n">
         <v>99.89</v>
       </c>
-      <c r="AC36" s="6" t="n">
+      <c r="AC36" s="7" t="n">
         <v>99.97</v>
       </c>
-      <c r="AD36" s="6" t="n">
+      <c r="AD36" s="7" t="n">
         <v>99.77</v>
       </c>
-      <c r="AE36" s="6" t="n">
+      <c r="AE36" s="7" t="n">
         <v>99.69</v>
       </c>
-      <c r="AF36" s="6" t="n">
+      <c r="AF36" s="7" t="n">
         <v>100.54</v>
       </c>
-      <c r="AG36" s="6" t="n">
+      <c r="AG36" s="7" t="n">
         <v>101.43</v>
       </c>
       <c r="AH36" s="6" t="n">
@@ -3776,7 +3806,7 @@
         <v>400.46</v>
       </c>
       <c r="AJ36" s="6" t="inlineStr"/>
-      <c r="AK36" s="7" t="inlineStr"/>
+      <c r="AK36" s="8" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -3787,97 +3817,97 @@
       <c r="B37" s="6" t="n">
         <v>100.1</v>
       </c>
-      <c r="C37" s="6" t="n">
+      <c r="C37" s="7" t="n">
         <v>104.58</v>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="7" t="n">
         <v>104.67</v>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="E37" s="7" t="n">
         <v>103.33</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="F37" s="7" t="n">
         <v>104.4</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="G37" s="7" t="n">
         <v>104.63</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="H37" s="7" t="n">
         <v>105.15</v>
       </c>
-      <c r="I37" s="6" t="n">
+      <c r="I37" s="7" t="n">
         <v>103.98</v>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="J37" s="7" t="n">
         <v>104.01</v>
       </c>
-      <c r="K37" s="6" t="n">
+      <c r="K37" s="7" t="n">
         <v>103.93</v>
       </c>
-      <c r="L37" s="6" t="n">
+      <c r="L37" s="7" t="n">
         <v>104.06</v>
       </c>
-      <c r="M37" s="6" t="n">
+      <c r="M37" s="7" t="n">
         <v>104.12</v>
       </c>
-      <c r="N37" s="6" t="n">
+      <c r="N37" s="7" t="n">
         <v>104.99</v>
       </c>
-      <c r="O37" s="6" t="n">
+      <c r="O37" s="7" t="n">
         <v>105.4</v>
       </c>
-      <c r="P37" s="6" t="n">
+      <c r="P37" s="7" t="n">
         <v>104.18</v>
       </c>
-      <c r="Q37" s="6" t="n">
+      <c r="Q37" s="7" t="n">
         <v>104.56</v>
       </c>
-      <c r="R37" s="6" t="n">
+      <c r="R37" s="7" t="n">
         <v>104.82</v>
       </c>
-      <c r="S37" s="6" t="n">
+      <c r="S37" s="7" t="n">
         <v>104.64</v>
       </c>
-      <c r="T37" s="6" t="n">
+      <c r="T37" s="7" t="n">
         <v>104.56</v>
       </c>
-      <c r="U37" s="6" t="n">
+      <c r="U37" s="7" t="n">
         <v>105.75</v>
       </c>
-      <c r="V37" s="6" t="n">
+      <c r="V37" s="7" t="n">
         <v>105.66</v>
       </c>
-      <c r="W37" s="6" t="n">
+      <c r="W37" s="7" t="n">
         <v>104.31</v>
       </c>
-      <c r="X37" s="6" t="n">
+      <c r="X37" s="7" t="n">
         <v>103.87</v>
       </c>
-      <c r="Y37" s="6" t="n">
+      <c r="Y37" s="7" t="n">
         <v>103.78</v>
       </c>
-      <c r="Z37" s="6" t="n">
+      <c r="Z37" s="7" t="n">
         <v>103.2</v>
       </c>
-      <c r="AA37" s="6" t="n">
+      <c r="AA37" s="7" t="n">
         <v>103.45</v>
       </c>
-      <c r="AB37" s="6" t="n">
+      <c r="AB37" s="7" t="n">
         <v>104.43</v>
       </c>
-      <c r="AC37" s="6" t="n">
+      <c r="AC37" s="7" t="n">
         <v>104.42</v>
       </c>
-      <c r="AD37" s="6" t="n">
+      <c r="AD37" s="7" t="n">
         <v>103.52</v>
       </c>
-      <c r="AE37" s="6" t="n">
+      <c r="AE37" s="7" t="n">
         <v>103.88</v>
       </c>
-      <c r="AF37" s="6" t="n">
+      <c r="AF37" s="7" t="n">
         <v>104.63</v>
       </c>
-      <c r="AG37" s="6" t="n">
+      <c r="AG37" s="7" t="n">
         <v>105.94</v>
       </c>
       <c r="AH37" s="6" t="n">
@@ -3887,7 +3917,7 @@
         <v>422.94</v>
       </c>
       <c r="AJ37" s="6" t="inlineStr"/>
-      <c r="AK37" s="7" t="inlineStr"/>
+      <c r="AK37" s="8" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -3898,97 +3928,97 @@
       <c r="B38" s="6" t="n">
         <v>100.5</v>
       </c>
-      <c r="C38" s="6" t="n">
+      <c r="C38" s="7" t="n">
         <v>85.64</v>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D38" s="7" t="n">
         <v>89.26000000000001</v>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="E38" s="7" t="n">
         <v>84.69</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="F38" s="7" t="n">
         <v>85.5</v>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="G38" s="7" t="n">
         <v>85.12</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="H38" s="7" t="n">
         <v>85.45999999999999</v>
       </c>
-      <c r="I38" s="6" t="n">
+      <c r="I38" s="7" t="n">
         <v>86.08</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="J38" s="7" t="n">
         <v>84.76000000000001</v>
       </c>
-      <c r="K38" s="6" t="n">
+      <c r="K38" s="7" t="n">
         <v>87.98</v>
       </c>
-      <c r="L38" s="6" t="n">
+      <c r="L38" s="7" t="n">
         <v>91.37</v>
       </c>
-      <c r="M38" s="6" t="n">
+      <c r="M38" s="7" t="n">
         <v>87.83</v>
       </c>
-      <c r="N38" s="6" t="n">
+      <c r="N38" s="7" t="n">
         <v>84.98</v>
       </c>
-      <c r="O38" s="6" t="n">
+      <c r="O38" s="7" t="n">
         <v>84.48999999999999</v>
       </c>
-      <c r="P38" s="6" t="n">
+      <c r="P38" s="7" t="n">
         <v>86.59</v>
       </c>
-      <c r="Q38" s="6" t="n">
+      <c r="Q38" s="7" t="n">
         <v>87.42</v>
       </c>
-      <c r="R38" s="6" t="n">
+      <c r="R38" s="7" t="n">
         <v>87.05</v>
       </c>
-      <c r="S38" s="6" t="n">
+      <c r="S38" s="7" t="n">
         <v>87.66</v>
       </c>
-      <c r="T38" s="6" t="n">
+      <c r="T38" s="7" t="n">
         <v>88.83</v>
       </c>
-      <c r="U38" s="6" t="n">
+      <c r="U38" s="7" t="n">
         <v>87.95999999999999</v>
       </c>
-      <c r="V38" s="6" t="n">
+      <c r="V38" s="7" t="n">
         <v>88.23</v>
       </c>
-      <c r="W38" s="6" t="n">
+      <c r="W38" s="7" t="n">
         <v>89.31</v>
       </c>
-      <c r="X38" s="6" t="n">
+      <c r="X38" s="7" t="n">
         <v>91.02</v>
       </c>
-      <c r="Y38" s="6" t="n">
+      <c r="Y38" s="7" t="n">
         <v>91.7</v>
       </c>
-      <c r="Z38" s="6" t="n">
+      <c r="Z38" s="7" t="n">
         <v>93.03</v>
       </c>
-      <c r="AA38" s="6" t="n">
+      <c r="AA38" s="7" t="n">
         <v>91.01000000000001</v>
       </c>
-      <c r="AB38" s="6" t="n">
+      <c r="AB38" s="7" t="n">
         <v>90.93000000000001</v>
       </c>
-      <c r="AC38" s="6" t="n">
+      <c r="AC38" s="7" t="n">
         <v>91.25</v>
       </c>
-      <c r="AD38" s="6" t="n">
+      <c r="AD38" s="7" t="n">
         <v>91.53</v>
       </c>
-      <c r="AE38" s="6" t="n">
+      <c r="AE38" s="7" t="n">
         <v>90.98999999999999</v>
       </c>
-      <c r="AF38" s="6" t="n">
+      <c r="AF38" s="7" t="n">
         <v>89.48999999999999</v>
       </c>
-      <c r="AG38" s="6" t="n">
+      <c r="AG38" s="7" t="n">
         <v>88.09</v>
       </c>
       <c r="AH38" s="6" t="n">
@@ -3998,7 +4028,7 @@
         <v>419.65</v>
       </c>
       <c r="AJ38" s="6" t="inlineStr"/>
-      <c r="AK38" s="7" t="inlineStr"/>
+      <c r="AK38" s="8" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -4009,97 +4039,97 @@
       <c r="B39" s="6" t="n">
         <v>100.9</v>
       </c>
-      <c r="C39" s="6" t="n">
+      <c r="C39" s="7" t="n">
         <v>98.81999999999999</v>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="7" t="n">
         <v>101.34</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="E39" s="7" t="n">
         <v>97.12</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="F39" s="7" t="n">
         <v>97.89</v>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="G39" s="7" t="n">
         <v>97.7</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="H39" s="7" t="n">
         <v>98.11</v>
       </c>
-      <c r="I39" s="6" t="n">
+      <c r="I39" s="7" t="n">
         <v>98.68000000000001</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="J39" s="7" t="n">
         <v>97.28</v>
       </c>
-      <c r="K39" s="6" t="n">
+      <c r="K39" s="7" t="n">
         <v>101.19</v>
       </c>
-      <c r="L39" s="6" t="n">
+      <c r="L39" s="7" t="n">
         <v>103.54</v>
       </c>
-      <c r="M39" s="6" t="n">
+      <c r="M39" s="7" t="n">
         <v>101.93</v>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="N39" s="7" t="n">
         <v>98.64</v>
       </c>
-      <c r="O39" s="6" t="n">
+      <c r="O39" s="7" t="n">
         <v>98.05</v>
       </c>
-      <c r="P39" s="6" t="n">
+      <c r="P39" s="7" t="n">
         <v>98.52</v>
       </c>
-      <c r="Q39" s="6" t="n">
+      <c r="Q39" s="7" t="n">
         <v>98.81999999999999</v>
       </c>
-      <c r="R39" s="6" t="n">
+      <c r="R39" s="7" t="n">
         <v>98.98</v>
       </c>
-      <c r="S39" s="6" t="n">
+      <c r="S39" s="7" t="n">
         <v>99.04000000000001</v>
       </c>
-      <c r="T39" s="6" t="n">
+      <c r="T39" s="7" t="n">
         <v>99.51000000000001</v>
       </c>
-      <c r="U39" s="6" t="n">
+      <c r="U39" s="7" t="n">
         <v>100.46</v>
       </c>
-      <c r="V39" s="6" t="n">
+      <c r="V39" s="7" t="n">
         <v>99.43000000000001</v>
       </c>
-      <c r="W39" s="6" t="n">
+      <c r="W39" s="7" t="n">
         <v>100.68</v>
       </c>
-      <c r="X39" s="6" t="n">
+      <c r="X39" s="7" t="n">
         <v>103.7</v>
       </c>
-      <c r="Y39" s="6" t="n">
+      <c r="Y39" s="7" t="n">
         <v>104.14</v>
       </c>
-      <c r="Z39" s="6" t="n">
+      <c r="Z39" s="7" t="n">
         <v>104.82</v>
       </c>
-      <c r="AA39" s="6" t="n">
+      <c r="AA39" s="7" t="n">
         <v>104.1</v>
       </c>
-      <c r="AB39" s="6" t="n">
+      <c r="AB39" s="7" t="n">
         <v>103.98</v>
       </c>
-      <c r="AC39" s="6" t="n">
+      <c r="AC39" s="7" t="n">
         <v>104.17</v>
       </c>
-      <c r="AD39" s="6" t="n">
+      <c r="AD39" s="7" t="n">
         <v>103.9</v>
       </c>
-      <c r="AE39" s="6" t="n">
+      <c r="AE39" s="7" t="n">
         <v>104.06</v>
       </c>
-      <c r="AF39" s="6" t="n">
+      <c r="AF39" s="7" t="n">
         <v>101.71</v>
       </c>
-      <c r="AG39" s="6" t="n">
+      <c r="AG39" s="7" t="n">
         <v>100.18</v>
       </c>
       <c r="AH39" s="6" t="n">
@@ -4109,7 +4139,7 @@
         <v>399.91</v>
       </c>
       <c r="AJ39" s="6" t="inlineStr"/>
-      <c r="AK39" s="7" t="inlineStr"/>
+      <c r="AK39" s="8" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -4120,97 +4150,97 @@
       <c r="B40" s="6" t="n">
         <v>101.3</v>
       </c>
-      <c r="C40" s="6" t="n">
+      <c r="C40" s="7" t="n">
         <v>98.51000000000001</v>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D40" s="7" t="n">
         <v>100.48</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="E40" s="7" t="n">
         <v>98.58</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="F40" s="7" t="n">
         <v>99.27</v>
       </c>
-      <c r="G40" s="6" t="n">
+      <c r="G40" s="7" t="n">
         <v>98.88</v>
       </c>
-      <c r="H40" s="6" t="n">
+      <c r="H40" s="7" t="n">
         <v>99.08</v>
       </c>
-      <c r="I40" s="6" t="n">
+      <c r="I40" s="7" t="n">
         <v>99.51000000000001</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="J40" s="7" t="n">
         <v>99.31</v>
       </c>
-      <c r="K40" s="6" t="n">
+      <c r="K40" s="7" t="n">
         <v>100.52</v>
       </c>
-      <c r="L40" s="6" t="n">
+      <c r="L40" s="7" t="n">
         <v>102.21</v>
       </c>
-      <c r="M40" s="6" t="n">
+      <c r="M40" s="7" t="n">
         <v>101.19</v>
       </c>
-      <c r="N40" s="6" t="n">
+      <c r="N40" s="7" t="n">
         <v>99.40000000000001</v>
       </c>
-      <c r="O40" s="6" t="n">
+      <c r="O40" s="7" t="n">
         <v>99.41</v>
       </c>
-      <c r="P40" s="6" t="n">
+      <c r="P40" s="7" t="n">
         <v>99.53</v>
       </c>
-      <c r="Q40" s="6" t="n">
+      <c r="Q40" s="7" t="n">
         <v>99.78</v>
       </c>
-      <c r="R40" s="6" t="n">
+      <c r="R40" s="7" t="n">
         <v>99.94</v>
       </c>
-      <c r="S40" s="6" t="n">
+      <c r="S40" s="7" t="n">
         <v>99.69</v>
       </c>
-      <c r="T40" s="6" t="n">
+      <c r="T40" s="7" t="n">
         <v>100.28</v>
       </c>
-      <c r="U40" s="6" t="n">
+      <c r="U40" s="7" t="n">
         <v>100.74</v>
       </c>
-      <c r="V40" s="6" t="n">
+      <c r="V40" s="7" t="n">
         <v>99.73</v>
       </c>
-      <c r="W40" s="6" t="n">
+      <c r="W40" s="7" t="n">
         <v>100.94</v>
       </c>
-      <c r="X40" s="6" t="n">
+      <c r="X40" s="7" t="n">
         <v>102</v>
       </c>
-      <c r="Y40" s="6" t="n">
+      <c r="Y40" s="7" t="n">
         <v>101.42</v>
       </c>
-      <c r="Z40" s="6" t="n">
+      <c r="Z40" s="7" t="n">
         <v>101.85</v>
       </c>
-      <c r="AA40" s="6" t="n">
+      <c r="AA40" s="7" t="n">
         <v>101.92</v>
       </c>
-      <c r="AB40" s="6" t="n">
+      <c r="AB40" s="7" t="n">
         <v>101.72</v>
       </c>
-      <c r="AC40" s="6" t="n">
+      <c r="AC40" s="7" t="n">
         <v>101.67</v>
       </c>
-      <c r="AD40" s="6" t="n">
+      <c r="AD40" s="7" t="n">
         <v>102.04</v>
       </c>
-      <c r="AE40" s="6" t="n">
+      <c r="AE40" s="7" t="n">
         <v>101.97</v>
       </c>
-      <c r="AF40" s="6" t="n">
+      <c r="AF40" s="7" t="n">
         <v>101.61</v>
       </c>
-      <c r="AG40" s="6" t="n">
+      <c r="AG40" s="7" t="n">
         <v>100.71</v>
       </c>
       <c r="AH40" s="6" t="n">
@@ -4220,7 +4250,7 @@
         <v>407.04</v>
       </c>
       <c r="AJ40" s="6" t="inlineStr"/>
-      <c r="AK40" s="7" t="inlineStr"/>
+      <c r="AK40" s="8" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -4231,97 +4261,97 @@
       <c r="B41" s="6" t="n">
         <v>102.1</v>
       </c>
-      <c r="C41" s="6" t="n">
+      <c r="C41" s="7" t="n">
         <v>102.57</v>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="7" t="n">
         <v>105.03</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="E41" s="7" t="n">
         <v>103.34</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="F41" s="7" t="n">
         <v>103.44</v>
       </c>
-      <c r="G41" s="6" t="n">
+      <c r="G41" s="7" t="n">
         <v>103.11</v>
       </c>
-      <c r="H41" s="6" t="n">
+      <c r="H41" s="7" t="n">
         <v>103.53</v>
       </c>
-      <c r="I41" s="6" t="n">
+      <c r="I41" s="7" t="n">
         <v>103.46</v>
       </c>
-      <c r="J41" s="6" t="n">
+      <c r="J41" s="7" t="n">
         <v>103.53</v>
       </c>
-      <c r="K41" s="6" t="n">
+      <c r="K41" s="7" t="n">
         <v>106.06</v>
       </c>
-      <c r="L41" s="6" t="n">
+      <c r="L41" s="7" t="n">
         <v>108.66</v>
       </c>
-      <c r="M41" s="6" t="n">
+      <c r="M41" s="7" t="n">
         <v>106.24</v>
       </c>
-      <c r="N41" s="6" t="n">
+      <c r="N41" s="7" t="n">
         <v>103.67</v>
       </c>
-      <c r="O41" s="6" t="n">
+      <c r="O41" s="7" t="n">
         <v>104.14</v>
       </c>
-      <c r="P41" s="6" t="n">
+      <c r="P41" s="7" t="n">
         <v>103.64</v>
       </c>
-      <c r="Q41" s="6" t="n">
+      <c r="Q41" s="7" t="n">
         <v>103.54</v>
       </c>
-      <c r="R41" s="6" t="n">
+      <c r="R41" s="7" t="n">
         <v>103.82</v>
       </c>
-      <c r="S41" s="6" t="n">
+      <c r="S41" s="7" t="n">
         <v>103.42</v>
       </c>
-      <c r="T41" s="6" t="n">
+      <c r="T41" s="7" t="n">
         <v>104.5</v>
       </c>
-      <c r="U41" s="6" t="n">
+      <c r="U41" s="7" t="n">
         <v>104.66</v>
       </c>
-      <c r="V41" s="6" t="n">
+      <c r="V41" s="7" t="n">
         <v>104.32</v>
       </c>
-      <c r="W41" s="6" t="n">
+      <c r="W41" s="7" t="n">
         <v>105.61</v>
       </c>
-      <c r="X41" s="6" t="n">
+      <c r="X41" s="7" t="n">
         <v>107.35</v>
       </c>
-      <c r="Y41" s="6" t="n">
+      <c r="Y41" s="7" t="n">
         <v>107.55</v>
       </c>
-      <c r="Z41" s="6" t="n">
+      <c r="Z41" s="7" t="n">
         <v>108.24</v>
       </c>
-      <c r="AA41" s="6" t="n">
+      <c r="AA41" s="7" t="n">
         <v>107.6</v>
       </c>
-      <c r="AB41" s="6" t="n">
+      <c r="AB41" s="7" t="n">
         <v>107.67</v>
       </c>
-      <c r="AC41" s="6" t="n">
+      <c r="AC41" s="7" t="n">
         <v>108.09</v>
       </c>
-      <c r="AD41" s="6" t="n">
+      <c r="AD41" s="7" t="n">
         <v>108.48</v>
       </c>
-      <c r="AE41" s="6" t="n">
+      <c r="AE41" s="7" t="n">
         <v>107.73</v>
       </c>
-      <c r="AF41" s="6" t="n">
+      <c r="AF41" s="7" t="n">
         <v>106.29</v>
       </c>
-      <c r="AG41" s="6" t="n">
+      <c r="AG41" s="7" t="n">
         <v>103.92</v>
       </c>
       <c r="AH41" s="6" t="n">
@@ -4331,7 +4361,7 @@
         <v>316.68</v>
       </c>
       <c r="AJ41" s="6" t="inlineStr"/>
-      <c r="AK41" s="7" t="inlineStr"/>
+      <c r="AK41" s="8" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -4342,97 +4372,97 @@
       <c r="B42" s="6" t="n">
         <v>103.7</v>
       </c>
-      <c r="C42" s="6" t="n">
+      <c r="C42" s="9" t="n">
         <v>50.32</v>
       </c>
-      <c r="D42" s="6" t="n">
+      <c r="D42" s="9" t="n">
         <v>50.59</v>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="E42" s="9" t="n">
         <v>51.34</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="F42" s="9" t="n">
         <v>51.32</v>
       </c>
-      <c r="G42" s="6" t="n">
+      <c r="G42" s="9" t="n">
         <v>50.85</v>
       </c>
-      <c r="H42" s="6" t="n">
+      <c r="H42" s="9" t="n">
         <v>52.08</v>
       </c>
-      <c r="I42" s="6" t="n">
+      <c r="I42" s="9" t="n">
         <v>53.42</v>
       </c>
-      <c r="J42" s="6" t="n">
+      <c r="J42" s="9" t="n">
         <v>51.71</v>
       </c>
-      <c r="K42" s="6" t="n">
+      <c r="K42" s="9" t="n">
         <v>52.18</v>
       </c>
-      <c r="L42" s="6" t="n">
+      <c r="L42" s="9" t="n">
         <v>50.53</v>
       </c>
-      <c r="M42" s="6" t="n">
+      <c r="M42" s="9" t="n">
         <v>53.58</v>
       </c>
-      <c r="N42" s="6" t="n">
+      <c r="N42" s="7" t="n">
         <v>56.22</v>
       </c>
-      <c r="O42" s="6" t="n">
+      <c r="O42" s="9" t="n">
         <v>52.72</v>
       </c>
-      <c r="P42" s="6" t="n">
+      <c r="P42" s="7" t="n">
         <v>54.54</v>
       </c>
-      <c r="Q42" s="6" t="n">
+      <c r="Q42" s="9" t="n">
         <v>52.73</v>
       </c>
-      <c r="R42" s="6" t="n">
+      <c r="R42" s="7" t="n">
         <v>54.53</v>
       </c>
-      <c r="S42" s="6" t="n">
+      <c r="S42" s="7" t="n">
         <v>54.02</v>
       </c>
-      <c r="T42" s="6" t="n">
+      <c r="T42" s="9" t="n">
         <v>52.69</v>
       </c>
-      <c r="U42" s="6" t="n">
+      <c r="U42" s="7" t="n">
         <v>55.21</v>
       </c>
-      <c r="V42" s="6" t="n">
+      <c r="V42" s="9" t="n">
         <v>53.4</v>
       </c>
-      <c r="W42" s="6" t="n">
+      <c r="W42" s="9" t="n">
         <v>51.93</v>
       </c>
-      <c r="X42" s="6" t="n">
+      <c r="X42" s="9" t="n">
         <v>50.58</v>
       </c>
-      <c r="Y42" s="6" t="n">
+      <c r="Y42" s="9" t="n">
         <v>50.59</v>
       </c>
-      <c r="Z42" s="6" t="n">
+      <c r="Z42" s="9" t="n">
         <v>51.81</v>
       </c>
-      <c r="AA42" s="6" t="n">
+      <c r="AA42" s="9" t="n">
         <v>50.61</v>
       </c>
-      <c r="AB42" s="6" t="n">
+      <c r="AB42" s="9" t="n">
         <v>50.29</v>
       </c>
-      <c r="AC42" s="6" t="n">
+      <c r="AC42" s="9" t="n">
         <v>50.64</v>
       </c>
-      <c r="AD42" s="6" t="n">
+      <c r="AD42" s="9" t="n">
         <v>50.85</v>
       </c>
-      <c r="AE42" s="6" t="n">
+      <c r="AE42" s="9" t="n">
         <v>50.63</v>
       </c>
-      <c r="AF42" s="6" t="n">
+      <c r="AF42" s="7" t="n">
         <v>54.85</v>
       </c>
-      <c r="AG42" s="6" t="n">
+      <c r="AG42" s="7" t="n">
         <v>59.83</v>
       </c>
       <c r="AH42" s="6" t="n">
@@ -4442,7 +4472,7 @@
         <v>504.72</v>
       </c>
       <c r="AJ42" s="6" t="inlineStr"/>
-      <c r="AK42" s="7" t="inlineStr"/>
+      <c r="AK42" s="8" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -4453,97 +4483,97 @@
       <c r="B43" s="6" t="n">
         <v>104.1</v>
       </c>
-      <c r="C43" s="6" t="n">
+      <c r="C43" s="7" t="n">
         <v>94.04000000000001</v>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" s="7" t="n">
         <v>95.83</v>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="E43" s="7" t="n">
         <v>95.92</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="F43" s="7" t="n">
         <v>96.47</v>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="G43" s="7" t="n">
         <v>95.53</v>
       </c>
-      <c r="H43" s="6" t="n">
+      <c r="H43" s="7" t="n">
         <v>96.39</v>
       </c>
-      <c r="I43" s="6" t="n">
+      <c r="I43" s="7" t="n">
         <v>96.56999999999999</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="J43" s="7" t="n">
         <v>96.41</v>
       </c>
-      <c r="K43" s="6" t="n">
+      <c r="K43" s="7" t="n">
         <v>98.69</v>
       </c>
-      <c r="L43" s="6" t="n">
+      <c r="L43" s="7" t="n">
         <v>100.37</v>
       </c>
-      <c r="M43" s="6" t="n">
+      <c r="M43" s="7" t="n">
         <v>98.08</v>
       </c>
-      <c r="N43" s="6" t="n">
+      <c r="N43" s="7" t="n">
         <v>97.19</v>
       </c>
-      <c r="O43" s="6" t="n">
+      <c r="O43" s="7" t="n">
         <v>96.73</v>
       </c>
-      <c r="P43" s="6" t="n">
+      <c r="P43" s="7" t="n">
         <v>96.40000000000001</v>
       </c>
-      <c r="Q43" s="6" t="n">
+      <c r="Q43" s="7" t="n">
         <v>95.81</v>
       </c>
-      <c r="R43" s="6" t="n">
+      <c r="R43" s="7" t="n">
         <v>97.40000000000001</v>
       </c>
-      <c r="S43" s="6" t="n">
+      <c r="S43" s="7" t="n">
         <v>97.02</v>
       </c>
-      <c r="T43" s="6" t="n">
+      <c r="T43" s="7" t="n">
         <v>97.20999999999999</v>
       </c>
-      <c r="U43" s="6" t="n">
+      <c r="U43" s="7" t="n">
         <v>98.29000000000001</v>
       </c>
-      <c r="V43" s="6" t="n">
+      <c r="V43" s="7" t="n">
         <v>96.59</v>
       </c>
-      <c r="W43" s="6" t="n">
+      <c r="W43" s="7" t="n">
         <v>98.28</v>
       </c>
-      <c r="X43" s="6" t="n">
+      <c r="X43" s="7" t="n">
         <v>99.27</v>
       </c>
-      <c r="Y43" s="6" t="n">
+      <c r="Y43" s="7" t="n">
         <v>99.29000000000001</v>
       </c>
-      <c r="Z43" s="6" t="n">
+      <c r="Z43" s="7" t="n">
         <v>100.11</v>
       </c>
-      <c r="AA43" s="6" t="n">
+      <c r="AA43" s="7" t="n">
         <v>99.68000000000001</v>
       </c>
-      <c r="AB43" s="6" t="n">
+      <c r="AB43" s="7" t="n">
         <v>99.3</v>
       </c>
-      <c r="AC43" s="6" t="n">
+      <c r="AC43" s="7" t="n">
         <v>98.88</v>
       </c>
-      <c r="AD43" s="6" t="n">
+      <c r="AD43" s="7" t="n">
         <v>99.84</v>
       </c>
-      <c r="AE43" s="6" t="n">
+      <c r="AE43" s="7" t="n">
         <v>98.58</v>
       </c>
-      <c r="AF43" s="6" t="n">
+      <c r="AF43" s="7" t="n">
         <v>98.22</v>
       </c>
-      <c r="AG43" s="6" t="n">
+      <c r="AG43" s="7" t="n">
         <v>98.54000000000001</v>
       </c>
       <c r="AH43" s="6" t="n">
@@ -4553,7 +4583,7 @@
         <v>265.12</v>
       </c>
       <c r="AJ43" s="6" t="inlineStr"/>
-      <c r="AK43" s="7" t="inlineStr"/>
+      <c r="AK43" s="8" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -4564,97 +4594,97 @@
       <c r="B44" s="6" t="n">
         <v>104.5</v>
       </c>
-      <c r="C44" s="6" t="n">
+      <c r="C44" s="7" t="n">
         <v>96.89</v>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="D44" s="7" t="n">
         <v>98.95999999999999</v>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="E44" s="7" t="n">
         <v>100.69</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="F44" s="7" t="n">
         <v>99.98999999999999</v>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="G44" s="7" t="n">
         <v>100.05</v>
       </c>
-      <c r="H44" s="6" t="n">
+      <c r="H44" s="7" t="n">
         <v>100.15</v>
       </c>
-      <c r="I44" s="6" t="n">
+      <c r="I44" s="7" t="n">
         <v>99.63</v>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="J44" s="7" t="n">
         <v>99.47</v>
       </c>
-      <c r="K44" s="6" t="n">
+      <c r="K44" s="7" t="n">
         <v>103.17</v>
       </c>
-      <c r="L44" s="6" t="n">
+      <c r="L44" s="7" t="n">
         <v>105.8</v>
       </c>
-      <c r="M44" s="6" t="n">
+      <c r="M44" s="7" t="n">
         <v>103.22</v>
       </c>
-      <c r="N44" s="6" t="n">
+      <c r="N44" s="7" t="n">
         <v>100.21</v>
       </c>
-      <c r="O44" s="6" t="n">
+      <c r="O44" s="7" t="n">
         <v>100.55</v>
       </c>
-      <c r="P44" s="6" t="n">
+      <c r="P44" s="7" t="n">
         <v>100.05</v>
       </c>
-      <c r="Q44" s="6" t="n">
+      <c r="Q44" s="7" t="n">
         <v>99.7</v>
       </c>
-      <c r="R44" s="6" t="n">
+      <c r="R44" s="7" t="n">
         <v>100.71</v>
       </c>
-      <c r="S44" s="6" t="n">
+      <c r="S44" s="7" t="n">
         <v>100.57</v>
       </c>
-      <c r="T44" s="6" t="n">
+      <c r="T44" s="7" t="n">
         <v>99.79000000000001</v>
       </c>
-      <c r="U44" s="6" t="n">
+      <c r="U44" s="7" t="n">
         <v>101.17</v>
       </c>
-      <c r="V44" s="6" t="n">
+      <c r="V44" s="7" t="n">
         <v>101.09</v>
       </c>
-      <c r="W44" s="6" t="n">
+      <c r="W44" s="7" t="n">
         <v>102.88</v>
       </c>
-      <c r="X44" s="6" t="n">
+      <c r="X44" s="7" t="n">
         <v>105.57</v>
       </c>
-      <c r="Y44" s="6" t="n">
+      <c r="Y44" s="7" t="n">
         <v>106.06</v>
       </c>
-      <c r="Z44" s="6" t="n">
+      <c r="Z44" s="7" t="n">
         <v>105.97</v>
       </c>
-      <c r="AA44" s="6" t="n">
+      <c r="AA44" s="7" t="n">
         <v>106.17</v>
       </c>
-      <c r="AB44" s="6" t="n">
+      <c r="AB44" s="7" t="n">
         <v>105.77</v>
       </c>
-      <c r="AC44" s="6" t="n">
+      <c r="AC44" s="7" t="n">
         <v>105.69</v>
       </c>
-      <c r="AD44" s="6" t="n">
+      <c r="AD44" s="7" t="n">
         <v>106.16</v>
       </c>
-      <c r="AE44" s="6" t="n">
+      <c r="AE44" s="7" t="n">
         <v>105.9</v>
       </c>
-      <c r="AF44" s="6" t="n">
+      <c r="AF44" s="7" t="n">
         <v>103.81</v>
       </c>
-      <c r="AG44" s="6" t="n">
+      <c r="AG44" s="7" t="n">
         <v>100.94</v>
       </c>
       <c r="AH44" s="6" t="n">
@@ -4664,7 +4694,7 @@
         <v>348.54</v>
       </c>
       <c r="AJ44" s="6" t="inlineStr"/>
-      <c r="AK44" s="7" t="inlineStr"/>
+      <c r="AK44" s="8" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -4675,97 +4705,97 @@
       <c r="B45" s="6" t="n">
         <v>104.9</v>
       </c>
-      <c r="C45" s="6" t="n">
+      <c r="C45" s="7" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="7" t="n">
         <v>99.70999999999999</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="E45" s="7" t="n">
         <v>100.45</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="F45" s="7" t="n">
         <v>100.85</v>
       </c>
-      <c r="G45" s="6" t="n">
+      <c r="G45" s="7" t="n">
         <v>100.75</v>
       </c>
-      <c r="H45" s="6" t="n">
+      <c r="H45" s="7" t="n">
         <v>101.45</v>
       </c>
-      <c r="I45" s="6" t="n">
+      <c r="I45" s="7" t="n">
         <v>101.65</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="J45" s="7" t="n">
         <v>100.51</v>
       </c>
-      <c r="K45" s="6" t="n">
+      <c r="K45" s="7" t="n">
         <v>101.33</v>
       </c>
-      <c r="L45" s="6" t="n">
+      <c r="L45" s="7" t="n">
         <v>101.65</v>
       </c>
-      <c r="M45" s="6" t="n">
+      <c r="M45" s="7" t="n">
         <v>101.78</v>
       </c>
-      <c r="N45" s="6" t="n">
+      <c r="N45" s="7" t="n">
         <v>102.15</v>
       </c>
-      <c r="O45" s="6" t="n">
+      <c r="O45" s="7" t="n">
         <v>101.4</v>
       </c>
-      <c r="P45" s="6" t="n">
+      <c r="P45" s="7" t="n">
         <v>101.39</v>
       </c>
-      <c r="Q45" s="6" t="n">
+      <c r="Q45" s="7" t="n">
         <v>101.01</v>
       </c>
-      <c r="R45" s="6" t="n">
+      <c r="R45" s="7" t="n">
         <v>62.75</v>
       </c>
-      <c r="S45" s="6" t="n">
+      <c r="S45" s="7" t="n">
         <v>101.98</v>
       </c>
-      <c r="T45" s="6" t="n">
+      <c r="T45" s="7" t="n">
         <v>101.33</v>
       </c>
-      <c r="U45" s="6" t="n">
+      <c r="U45" s="7" t="n">
         <v>102.57</v>
       </c>
-      <c r="V45" s="6" t="n">
+      <c r="V45" s="7" t="n">
         <v>101.05</v>
       </c>
-      <c r="W45" s="6" t="n">
+      <c r="W45" s="7" t="n">
         <v>101.24</v>
       </c>
-      <c r="X45" s="6" t="n">
+      <c r="X45" s="7" t="n">
         <v>100.69</v>
       </c>
-      <c r="Y45" s="6" t="n">
+      <c r="Y45" s="7" t="n">
         <v>100.94</v>
       </c>
-      <c r="Z45" s="6" t="n">
+      <c r="Z45" s="7" t="n">
         <v>101.27</v>
       </c>
-      <c r="AA45" s="6" t="n">
+      <c r="AA45" s="7" t="n">
         <v>100.94</v>
       </c>
-      <c r="AB45" s="6" t="n">
+      <c r="AB45" s="7" t="n">
         <v>101.06</v>
       </c>
-      <c r="AC45" s="6" t="n">
+      <c r="AC45" s="7" t="n">
         <v>101.25</v>
       </c>
-      <c r="AD45" s="6" t="n">
+      <c r="AD45" s="7" t="n">
         <v>101.16</v>
       </c>
-      <c r="AE45" s="6" t="n">
+      <c r="AE45" s="7" t="n">
         <v>101.06</v>
       </c>
-      <c r="AF45" s="6" t="n">
+      <c r="AF45" s="7" t="n">
         <v>102.18</v>
       </c>
-      <c r="AG45" s="6" t="n">
+      <c r="AG45" s="7" t="n">
         <v>104.17</v>
       </c>
       <c r="AH45" s="6" t="n">
@@ -4775,7 +4805,7 @@
         <v>456.27</v>
       </c>
       <c r="AJ45" s="6" t="inlineStr"/>
-      <c r="AK45" s="7" t="inlineStr"/>
+      <c r="AK45" s="8" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -4786,97 +4816,97 @@
       <c r="B46" s="6" t="n">
         <v>105.7</v>
       </c>
-      <c r="C46" s="6" t="n">
+      <c r="C46" s="7" t="n">
         <v>99.2</v>
       </c>
-      <c r="D46" s="6" t="n">
+      <c r="D46" s="7" t="n">
         <v>100.34</v>
       </c>
-      <c r="E46" s="6" t="n">
+      <c r="E46" s="7" t="n">
         <v>98.93000000000001</v>
       </c>
-      <c r="F46" s="6" t="n">
+      <c r="F46" s="7" t="n">
         <v>99.94</v>
       </c>
-      <c r="G46" s="6" t="n">
+      <c r="G46" s="7" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="H46" s="6" t="n">
+      <c r="H46" s="7" t="n">
         <v>99.78</v>
       </c>
-      <c r="I46" s="6" t="n">
+      <c r="I46" s="7" t="n">
         <v>100.31</v>
       </c>
-      <c r="J46" s="6" t="n">
+      <c r="J46" s="7" t="n">
         <v>100.54</v>
       </c>
-      <c r="K46" s="6" t="n">
+      <c r="K46" s="7" t="n">
         <v>100.59</v>
       </c>
-      <c r="L46" s="6" t="n">
+      <c r="L46" s="7" t="n">
         <v>101.39</v>
       </c>
-      <c r="M46" s="6" t="n">
+      <c r="M46" s="7" t="n">
         <v>101.34</v>
       </c>
-      <c r="N46" s="6" t="n">
+      <c r="N46" s="7" t="n">
         <v>100.27</v>
       </c>
-      <c r="O46" s="6" t="n">
+      <c r="O46" s="7" t="n">
         <v>99.64</v>
       </c>
-      <c r="P46" s="6" t="n">
+      <c r="P46" s="7" t="n">
         <v>100.25</v>
       </c>
-      <c r="Q46" s="6" t="n">
+      <c r="Q46" s="7" t="n">
         <v>100.02</v>
       </c>
-      <c r="R46" s="6" t="n">
+      <c r="R46" s="7" t="n">
         <v>101.94</v>
       </c>
-      <c r="S46" s="6" t="n">
+      <c r="S46" s="7" t="n">
         <v>101.76</v>
       </c>
-      <c r="T46" s="6" t="n">
+      <c r="T46" s="7" t="n">
         <v>99.89</v>
       </c>
-      <c r="U46" s="6" t="n">
+      <c r="U46" s="7" t="n">
         <v>100.34</v>
       </c>
-      <c r="V46" s="6" t="n">
+      <c r="V46" s="7" t="n">
         <v>100.52</v>
       </c>
-      <c r="W46" s="6" t="n">
+      <c r="W46" s="7" t="n">
         <v>100.96</v>
       </c>
-      <c r="X46" s="6" t="n">
+      <c r="X46" s="7" t="n">
         <v>101.15</v>
       </c>
-      <c r="Y46" s="6" t="n">
+      <c r="Y46" s="7" t="n">
         <v>101.05</v>
       </c>
-      <c r="Z46" s="6" t="n">
+      <c r="Z46" s="7" t="n">
         <v>101.21</v>
       </c>
-      <c r="AA46" s="6" t="n">
+      <c r="AA46" s="7" t="n">
         <v>101.4</v>
       </c>
-      <c r="AB46" s="6" t="n">
+      <c r="AB46" s="7" t="n">
         <v>100.88</v>
       </c>
-      <c r="AC46" s="6" t="n">
+      <c r="AC46" s="7" t="n">
         <v>101.17</v>
       </c>
-      <c r="AD46" s="6" t="n">
+      <c r="AD46" s="7" t="n">
         <v>101.41</v>
       </c>
-      <c r="AE46" s="6" t="n">
+      <c r="AE46" s="7" t="n">
         <v>101.22</v>
       </c>
-      <c r="AF46" s="6" t="n">
+      <c r="AF46" s="7" t="n">
         <v>101.94</v>
       </c>
-      <c r="AG46" s="6" t="n">
+      <c r="AG46" s="7" t="n">
         <v>102.45</v>
       </c>
       <c r="AH46" s="6" t="n">
@@ -4886,7 +4916,7 @@
         <v>420.89</v>
       </c>
       <c r="AJ46" s="6" t="inlineStr"/>
-      <c r="AK46" s="7" t="inlineStr"/>
+      <c r="AK46" s="8" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -4897,97 +4927,97 @@
       <c r="B47" s="6" t="n">
         <v>106.1</v>
       </c>
-      <c r="C47" s="6" t="n">
+      <c r="C47" s="7" t="n">
         <v>96.41</v>
       </c>
-      <c r="D47" s="6" t="n">
+      <c r="D47" s="7" t="n">
         <v>98.17</v>
       </c>
-      <c r="E47" s="6" t="n">
+      <c r="E47" s="7" t="n">
         <v>99.8</v>
       </c>
-      <c r="F47" s="6" t="n">
+      <c r="F47" s="7" t="n">
         <v>99.06</v>
       </c>
-      <c r="G47" s="6" t="n">
+      <c r="G47" s="7" t="n">
         <v>99.08</v>
       </c>
-      <c r="H47" s="6" t="n">
+      <c r="H47" s="7" t="n">
         <v>99.69</v>
       </c>
-      <c r="I47" s="6" t="n">
+      <c r="I47" s="7" t="n">
         <v>98.59</v>
       </c>
-      <c r="J47" s="6" t="n">
+      <c r="J47" s="7" t="n">
         <v>98.34999999999999</v>
       </c>
-      <c r="K47" s="6" t="n">
+      <c r="K47" s="7" t="n">
         <v>100.83</v>
       </c>
-      <c r="L47" s="6" t="n">
+      <c r="L47" s="7" t="n">
         <v>102.82</v>
       </c>
-      <c r="M47" s="6" t="n">
+      <c r="M47" s="7" t="n">
         <v>101.24</v>
       </c>
-      <c r="N47" s="6" t="n">
+      <c r="N47" s="7" t="n">
         <v>100.28</v>
       </c>
-      <c r="O47" s="6" t="n">
+      <c r="O47" s="7" t="n">
         <v>99.76000000000001</v>
       </c>
-      <c r="P47" s="6" t="n">
+      <c r="P47" s="7" t="n">
         <v>98.73</v>
       </c>
-      <c r="Q47" s="6" t="n">
+      <c r="Q47" s="7" t="n">
         <v>99.03</v>
       </c>
-      <c r="R47" s="6" t="n">
+      <c r="R47" s="7" t="n">
         <v>100.07</v>
       </c>
-      <c r="S47" s="6" t="n">
+      <c r="S47" s="7" t="n">
         <v>100.01</v>
       </c>
-      <c r="T47" s="6" t="n">
+      <c r="T47" s="7" t="n">
         <v>98.98</v>
       </c>
-      <c r="U47" s="6" t="n">
+      <c r="U47" s="7" t="n">
         <v>101.22</v>
       </c>
-      <c r="V47" s="6" t="n">
+      <c r="V47" s="7" t="n">
         <v>99.81</v>
       </c>
-      <c r="W47" s="6" t="n">
+      <c r="W47" s="7" t="n">
         <v>100.56</v>
       </c>
-      <c r="X47" s="6" t="n">
+      <c r="X47" s="7" t="n">
         <v>102.19</v>
       </c>
-      <c r="Y47" s="6" t="n">
+      <c r="Y47" s="7" t="n">
         <v>101.98</v>
       </c>
-      <c r="Z47" s="6" t="n">
+      <c r="Z47" s="7" t="n">
         <v>101.83</v>
       </c>
-      <c r="AA47" s="6" t="n">
+      <c r="AA47" s="7" t="n">
         <v>101.79</v>
       </c>
-      <c r="AB47" s="6" t="n">
+      <c r="AB47" s="7" t="n">
         <v>102.13</v>
       </c>
-      <c r="AC47" s="6" t="n">
+      <c r="AC47" s="7" t="n">
         <v>102.53</v>
       </c>
-      <c r="AD47" s="6" t="n">
+      <c r="AD47" s="7" t="n">
         <v>102.13</v>
       </c>
-      <c r="AE47" s="6" t="n">
+      <c r="AE47" s="7" t="n">
         <v>101.58</v>
       </c>
-      <c r="AF47" s="6" t="n">
+      <c r="AF47" s="7" t="n">
         <v>101.42</v>
       </c>
-      <c r="AG47" s="6" t="n">
+      <c r="AG47" s="7" t="n">
         <v>100.83</v>
       </c>
       <c r="AH47" s="6" t="n">
@@ -4997,7 +5027,7 @@
         <v>416.29</v>
       </c>
       <c r="AJ47" s="6" t="inlineStr"/>
-      <c r="AK47" s="7" t="inlineStr"/>
+      <c r="AK47" s="8" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -5008,97 +5038,97 @@
       <c r="B48" s="6" t="n">
         <v>106.5</v>
       </c>
-      <c r="C48" s="6" t="n">
+      <c r="C48" s="7" t="n">
         <v>89.23999999999999</v>
       </c>
-      <c r="D48" s="6" t="n">
+      <c r="D48" s="7" t="n">
         <v>89.87</v>
       </c>
-      <c r="E48" s="6" t="n">
+      <c r="E48" s="7" t="n">
         <v>91.44</v>
       </c>
-      <c r="F48" s="6" t="n">
+      <c r="F48" s="7" t="n">
         <v>91.03</v>
       </c>
-      <c r="G48" s="6" t="n">
+      <c r="G48" s="7" t="n">
         <v>90.90000000000001</v>
       </c>
-      <c r="H48" s="6" t="n">
+      <c r="H48" s="7" t="n">
         <v>91.18000000000001</v>
       </c>
-      <c r="I48" s="6" t="n">
+      <c r="I48" s="7" t="n">
         <v>91.34</v>
       </c>
-      <c r="J48" s="6" t="n">
+      <c r="J48" s="7" t="n">
         <v>90.97</v>
       </c>
-      <c r="K48" s="6" t="n">
+      <c r="K48" s="7" t="n">
         <v>93.91</v>
       </c>
-      <c r="L48" s="6" t="n">
+      <c r="L48" s="7" t="n">
         <v>96.01000000000001</v>
       </c>
-      <c r="M48" s="6" t="n">
+      <c r="M48" s="7" t="n">
         <v>94.14</v>
       </c>
-      <c r="N48" s="6" t="n">
+      <c r="N48" s="7" t="n">
         <v>91.38</v>
       </c>
-      <c r="O48" s="6" t="n">
+      <c r="O48" s="7" t="n">
         <v>91.3</v>
       </c>
-      <c r="P48" s="6" t="n">
+      <c r="P48" s="7" t="n">
         <v>91.44</v>
       </c>
-      <c r="Q48" s="6" t="n">
+      <c r="Q48" s="7" t="n">
         <v>91.08</v>
       </c>
-      <c r="R48" s="6" t="n">
+      <c r="R48" s="7" t="n">
         <v>92.5</v>
       </c>
-      <c r="S48" s="6" t="n">
+      <c r="S48" s="7" t="n">
         <v>91.73999999999999</v>
       </c>
-      <c r="T48" s="6" t="n">
+      <c r="T48" s="7" t="n">
         <v>90.98</v>
       </c>
-      <c r="U48" s="6" t="n">
+      <c r="U48" s="7" t="n">
         <v>91.73999999999999</v>
       </c>
-      <c r="V48" s="6" t="n">
+      <c r="V48" s="7" t="n">
         <v>92.16</v>
       </c>
-      <c r="W48" s="6" t="n">
+      <c r="W48" s="7" t="n">
         <v>94.69</v>
       </c>
-      <c r="X48" s="6" t="n">
+      <c r="X48" s="7" t="n">
         <v>96.97</v>
       </c>
-      <c r="Y48" s="6" t="n">
+      <c r="Y48" s="7" t="n">
         <v>96.66</v>
       </c>
-      <c r="Z48" s="6" t="n">
+      <c r="Z48" s="7" t="n">
         <v>96.54000000000001</v>
       </c>
-      <c r="AA48" s="6" t="n">
+      <c r="AA48" s="7" t="n">
         <v>96.87</v>
       </c>
-      <c r="AB48" s="6" t="n">
+      <c r="AB48" s="7" t="n">
         <v>96.81999999999999</v>
       </c>
-      <c r="AC48" s="6" t="n">
+      <c r="AC48" s="7" t="n">
         <v>96.98999999999999</v>
       </c>
-      <c r="AD48" s="6" t="n">
+      <c r="AD48" s="7" t="n">
         <v>96.38</v>
       </c>
-      <c r="AE48" s="6" t="n">
+      <c r="AE48" s="7" t="n">
         <v>96.38</v>
       </c>
-      <c r="AF48" s="6" t="n">
+      <c r="AF48" s="7" t="n">
         <v>94.83</v>
       </c>
-      <c r="AG48" s="6" t="n">
+      <c r="AG48" s="7" t="n">
         <v>92.87</v>
       </c>
       <c r="AH48" s="6" t="n">
@@ -5108,7 +5138,7 @@
         <v>389.74</v>
       </c>
       <c r="AJ48" s="6" t="inlineStr"/>
-      <c r="AK48" s="7" t="inlineStr"/>
+      <c r="AK48" s="8" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -5119,97 +5149,97 @@
       <c r="B49" s="6" t="n">
         <v>106.9</v>
       </c>
-      <c r="C49" s="6" t="n">
+      <c r="C49" s="7" t="n">
         <v>82.94</v>
       </c>
-      <c r="D49" s="6" t="n">
+      <c r="D49" s="7" t="n">
         <v>81.58</v>
       </c>
-      <c r="E49" s="6" t="n">
+      <c r="E49" s="7" t="n">
         <v>75.23999999999999</v>
       </c>
-      <c r="F49" s="6" t="n">
+      <c r="F49" s="7" t="n">
         <v>80.34999999999999</v>
       </c>
-      <c r="G49" s="6" t="n">
+      <c r="G49" s="7" t="n">
         <v>81.51000000000001</v>
       </c>
-      <c r="H49" s="6" t="n">
+      <c r="H49" s="7" t="n">
         <v>79.69</v>
       </c>
-      <c r="I49" s="6" t="n">
+      <c r="I49" s="7" t="n">
         <v>83.08</v>
       </c>
-      <c r="J49" s="6" t="n">
+      <c r="J49" s="7" t="n">
         <v>83.83</v>
       </c>
-      <c r="K49" s="6" t="n">
+      <c r="K49" s="7" t="n">
         <v>85.68000000000001</v>
       </c>
-      <c r="L49" s="6" t="n">
+      <c r="L49" s="7" t="n">
         <v>92.92</v>
       </c>
-      <c r="M49" s="6" t="n">
+      <c r="M49" s="7" t="n">
         <v>88.45999999999999</v>
       </c>
-      <c r="N49" s="6" t="n">
+      <c r="N49" s="7" t="n">
         <v>84.20999999999999</v>
       </c>
-      <c r="O49" s="6" t="n">
+      <c r="O49" s="7" t="n">
         <v>84.55</v>
       </c>
-      <c r="P49" s="6" t="n">
+      <c r="P49" s="7" t="n">
         <v>84.43000000000001</v>
       </c>
-      <c r="Q49" s="6" t="n">
+      <c r="Q49" s="7" t="n">
         <v>85.41</v>
       </c>
-      <c r="R49" s="6" t="n">
+      <c r="R49" s="7" t="n">
         <v>86.06</v>
       </c>
-      <c r="S49" s="6" t="n">
+      <c r="S49" s="7" t="n">
         <v>86.41</v>
       </c>
-      <c r="T49" s="6" t="n">
+      <c r="T49" s="7" t="n">
         <v>81.58</v>
       </c>
-      <c r="U49" s="6" t="n">
+      <c r="U49" s="7" t="n">
         <v>79.8</v>
       </c>
-      <c r="V49" s="6" t="n">
+      <c r="V49" s="7" t="n">
         <v>81.06</v>
       </c>
-      <c r="W49" s="6" t="n">
+      <c r="W49" s="7" t="n">
         <v>84.2</v>
       </c>
-      <c r="X49" s="6" t="n">
+      <c r="X49" s="7" t="n">
         <v>93.41</v>
       </c>
-      <c r="Y49" s="6" t="n">
+      <c r="Y49" s="7" t="n">
         <v>92.89</v>
       </c>
-      <c r="Z49" s="6" t="n">
+      <c r="Z49" s="7" t="n">
         <v>92.38</v>
       </c>
-      <c r="AA49" s="6" t="n">
+      <c r="AA49" s="7" t="n">
         <v>92.73999999999999</v>
       </c>
-      <c r="AB49" s="6" t="n">
+      <c r="AB49" s="7" t="n">
         <v>93.53</v>
       </c>
-      <c r="AC49" s="6" t="n">
+      <c r="AC49" s="7" t="n">
         <v>93.33</v>
       </c>
-      <c r="AD49" s="6" t="n">
+      <c r="AD49" s="7" t="n">
         <v>91.56999999999999</v>
       </c>
-      <c r="AE49" s="6" t="n">
+      <c r="AE49" s="7" t="n">
         <v>93.27</v>
       </c>
-      <c r="AF49" s="6" t="n">
+      <c r="AF49" s="7" t="n">
         <v>87.43000000000001</v>
       </c>
-      <c r="AG49" s="6" t="n">
+      <c r="AG49" s="7" t="n">
         <v>83.7</v>
       </c>
       <c r="AH49" s="6" t="n">
@@ -5219,7 +5249,7 @@
         <v>363.9</v>
       </c>
       <c r="AJ49" s="6" t="inlineStr"/>
-      <c r="AK49" s="7" t="inlineStr"/>
+      <c r="AK49" s="8" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -5230,97 +5260,97 @@
       <c r="B50" s="6" t="n">
         <v>107.3</v>
       </c>
-      <c r="C50" s="6" t="n">
+      <c r="C50" s="7" t="n">
         <v>97.02</v>
       </c>
-      <c r="D50" s="6" t="n">
+      <c r="D50" s="7" t="n">
         <v>97.38</v>
       </c>
-      <c r="E50" s="6" t="n">
+      <c r="E50" s="7" t="n">
         <v>100.17</v>
       </c>
-      <c r="F50" s="6" t="n">
+      <c r="F50" s="7" t="n">
         <v>100.19</v>
       </c>
-      <c r="G50" s="6" t="n">
+      <c r="G50" s="7" t="n">
         <v>99.47</v>
       </c>
-      <c r="H50" s="6" t="n">
+      <c r="H50" s="7" t="n">
         <v>99.84999999999999</v>
       </c>
-      <c r="I50" s="6" t="n">
+      <c r="I50" s="7" t="n">
         <v>100.17</v>
       </c>
-      <c r="J50" s="6" t="n">
+      <c r="J50" s="7" t="n">
         <v>99.97</v>
       </c>
-      <c r="K50" s="6" t="n">
+      <c r="K50" s="7" t="n">
         <v>101.72</v>
       </c>
-      <c r="L50" s="6" t="n">
+      <c r="L50" s="7" t="n">
         <v>103.51</v>
       </c>
-      <c r="M50" s="6" t="n">
+      <c r="M50" s="7" t="n">
         <v>102.89</v>
       </c>
-      <c r="N50" s="6" t="n">
+      <c r="N50" s="7" t="n">
         <v>101.01</v>
       </c>
-      <c r="O50" s="6" t="n">
+      <c r="O50" s="7" t="n">
         <v>100.34</v>
       </c>
-      <c r="P50" s="6" t="n">
+      <c r="P50" s="7" t="n">
         <v>100.96</v>
       </c>
-      <c r="Q50" s="6" t="n">
+      <c r="Q50" s="7" t="n">
         <v>100.27</v>
       </c>
-      <c r="R50" s="6" t="n">
+      <c r="R50" s="7" t="n">
         <v>101.63</v>
       </c>
-      <c r="S50" s="6" t="n">
+      <c r="S50" s="7" t="n">
         <v>101.48</v>
       </c>
-      <c r="T50" s="6" t="n">
+      <c r="T50" s="7" t="n">
         <v>100.31</v>
       </c>
-      <c r="U50" s="6" t="n">
+      <c r="U50" s="7" t="n">
         <v>101.41</v>
       </c>
-      <c r="V50" s="6" t="n">
+      <c r="V50" s="7" t="n">
         <v>101.11</v>
       </c>
-      <c r="W50" s="6" t="n">
+      <c r="W50" s="7" t="n">
         <v>102.63</v>
       </c>
-      <c r="X50" s="6" t="n">
+      <c r="X50" s="7" t="n">
         <v>103.98</v>
       </c>
-      <c r="Y50" s="6" t="n">
+      <c r="Y50" s="7" t="n">
         <v>103.92</v>
       </c>
-      <c r="Z50" s="6" t="n">
+      <c r="Z50" s="7" t="n">
         <v>104.27</v>
       </c>
-      <c r="AA50" s="6" t="n">
+      <c r="AA50" s="7" t="n">
         <v>103.99</v>
       </c>
-      <c r="AB50" s="6" t="n">
+      <c r="AB50" s="7" t="n">
         <v>104.23</v>
       </c>
-      <c r="AC50" s="6" t="n">
+      <c r="AC50" s="7" t="n">
         <v>103.94</v>
       </c>
-      <c r="AD50" s="6" t="n">
+      <c r="AD50" s="7" t="n">
         <v>103.89</v>
       </c>
-      <c r="AE50" s="6" t="n">
+      <c r="AE50" s="7" t="n">
         <v>103.47</v>
       </c>
-      <c r="AF50" s="6" t="n">
+      <c r="AF50" s="7" t="n">
         <v>103.17</v>
       </c>
-      <c r="AG50" s="6" t="n">
+      <c r="AG50" s="7" t="n">
         <v>102.71</v>
       </c>
       <c r="AH50" s="6" t="n">
@@ -5330,118 +5360,118 @@
         <v>310.71</v>
       </c>
       <c r="AJ50" s="6" t="inlineStr"/>
-      <c r="AK50" s="7" t="inlineStr"/>
+      <c r="AK50" s="8" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>RADIO POSITIVA FM</t>
         </is>
       </c>
-      <c r="B51" s="9" t="n">
+      <c r="B51" s="11" t="n">
         <v>107.7</v>
       </c>
-      <c r="C51" s="9" t="n">
+      <c r="C51" s="12" t="n">
         <v>76.42</v>
       </c>
-      <c r="D51" s="9" t="n">
+      <c r="D51" s="12" t="n">
         <v>76.77</v>
       </c>
-      <c r="E51" s="9" t="n">
+      <c r="E51" s="12" t="n">
         <v>81.34999999999999</v>
       </c>
-      <c r="F51" s="9" t="n">
+      <c r="F51" s="12" t="n">
         <v>79.69</v>
       </c>
-      <c r="G51" s="9" t="n">
+      <c r="G51" s="12" t="n">
         <v>79.67</v>
       </c>
-      <c r="H51" s="9" t="n">
+      <c r="H51" s="12" t="n">
         <v>79.69</v>
       </c>
-      <c r="I51" s="9" t="n">
+      <c r="I51" s="12" t="n">
         <v>79.95999999999999</v>
       </c>
-      <c r="J51" s="9" t="n">
+      <c r="J51" s="12" t="n">
         <v>79.01000000000001</v>
       </c>
-      <c r="K51" s="9" t="n">
+      <c r="K51" s="12" t="n">
         <v>82.05</v>
       </c>
-      <c r="L51" s="9" t="n">
+      <c r="L51" s="12" t="n">
         <v>84.64</v>
       </c>
-      <c r="M51" s="9" t="n">
+      <c r="M51" s="12" t="n">
         <v>81.73</v>
       </c>
-      <c r="N51" s="9" t="n">
+      <c r="N51" s="12" t="n">
         <v>79.73</v>
       </c>
-      <c r="O51" s="9" t="n">
+      <c r="O51" s="12" t="n">
         <v>78.31999999999999</v>
       </c>
-      <c r="P51" s="9" t="n">
+      <c r="P51" s="12" t="n">
         <v>79.45999999999999</v>
       </c>
-      <c r="Q51" s="9" t="n">
+      <c r="Q51" s="12" t="n">
         <v>79.41</v>
       </c>
-      <c r="R51" s="9" t="n">
+      <c r="R51" s="12" t="n">
         <v>79.73999999999999</v>
       </c>
-      <c r="S51" s="9" t="n">
+      <c r="S51" s="12" t="n">
         <v>79.73</v>
       </c>
-      <c r="T51" s="9" t="n">
+      <c r="T51" s="12" t="n">
         <v>79.68000000000001</v>
       </c>
-      <c r="U51" s="9" t="n">
+      <c r="U51" s="12" t="n">
         <v>80.61</v>
       </c>
-      <c r="V51" s="9" t="n">
+      <c r="V51" s="12" t="n">
         <v>79.16</v>
       </c>
-      <c r="W51" s="9" t="n">
+      <c r="W51" s="12" t="n">
         <v>81.95999999999999</v>
       </c>
-      <c r="X51" s="9" t="n">
+      <c r="X51" s="12" t="n">
         <v>84.26000000000001</v>
       </c>
-      <c r="Y51" s="9" t="n">
+      <c r="Y51" s="12" t="n">
         <v>83.81</v>
       </c>
-      <c r="Z51" s="9" t="n">
+      <c r="Z51" s="12" t="n">
         <v>84.69</v>
       </c>
-      <c r="AA51" s="9" t="n">
+      <c r="AA51" s="12" t="n">
         <v>84.03</v>
       </c>
-      <c r="AB51" s="9" t="n">
+      <c r="AB51" s="12" t="n">
         <v>83.94</v>
       </c>
-      <c r="AC51" s="9" t="n">
+      <c r="AC51" s="12" t="n">
         <v>83.68000000000001</v>
       </c>
-      <c r="AD51" s="9" t="n">
+      <c r="AD51" s="12" t="n">
         <v>83.81999999999999</v>
       </c>
-      <c r="AE51" s="9" t="n">
+      <c r="AE51" s="12" t="n">
         <v>84.41</v>
       </c>
-      <c r="AF51" s="9" t="n">
+      <c r="AF51" s="12" t="n">
         <v>82.03</v>
       </c>
-      <c r="AG51" s="9" t="n">
+      <c r="AG51" s="12" t="n">
         <v>79.73</v>
       </c>
-      <c r="AH51" s="9" t="n">
+      <c r="AH51" s="11" t="n">
         <v>81.06999999999999</v>
       </c>
-      <c r="AI51" s="9" t="n">
+      <c r="AI51" s="11" t="n">
         <v>264.88</v>
       </c>
-      <c r="AJ51" s="9" t="inlineStr"/>
-      <c r="AK51" s="10" t="inlineStr"/>
+      <c r="AJ51" s="11" t="inlineStr"/>
+      <c r="AK51" s="13" t="inlineStr"/>
     </row>
     <row r="52"/>
     <row r="53"/>
@@ -5490,7 +5520,7 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 27/08/2025</t>
+          <t>FECHA PRESENTACIÓN: 28/08/2025</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5646,7 @@
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK61" s="11" t="n"/>
+      <c r="AK61" s="14" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -5627,97 +5657,97 @@
       <c r="B62" s="6" t="n">
         <v>55.25</v>
       </c>
-      <c r="C62" s="6" t="n">
+      <c r="C62" s="7" t="n">
         <v>92.58</v>
       </c>
-      <c r="D62" s="6" t="n">
+      <c r="D62" s="7" t="n">
         <v>92.59999999999999</v>
       </c>
-      <c r="E62" s="6" t="n">
+      <c r="E62" s="7" t="n">
         <v>92.47</v>
       </c>
-      <c r="F62" s="6" t="n">
+      <c r="F62" s="7" t="n">
         <v>92.73</v>
       </c>
-      <c r="G62" s="6" t="n">
+      <c r="G62" s="7" t="n">
         <v>91.95</v>
       </c>
-      <c r="H62" s="6" t="n">
+      <c r="H62" s="7" t="n">
         <v>91.48</v>
       </c>
-      <c r="I62" s="6" t="n">
+      <c r="I62" s="7" t="n">
         <v>91.53</v>
       </c>
-      <c r="J62" s="6" t="n">
+      <c r="J62" s="7" t="n">
         <v>92.33</v>
       </c>
-      <c r="K62" s="6" t="n">
+      <c r="K62" s="7" t="n">
         <v>88.68000000000001</v>
       </c>
-      <c r="L62" s="6" t="n">
+      <c r="L62" s="7" t="n">
         <v>84.98</v>
       </c>
-      <c r="M62" s="6" t="n">
+      <c r="M62" s="7" t="n">
         <v>88.31999999999999</v>
       </c>
-      <c r="N62" s="6" t="n">
+      <c r="N62" s="7" t="n">
         <v>92.38</v>
       </c>
-      <c r="O62" s="6" t="n">
+      <c r="O62" s="7" t="n">
         <v>91.84999999999999</v>
       </c>
-      <c r="P62" s="6" t="n">
+      <c r="P62" s="7" t="n">
         <v>91.28</v>
       </c>
-      <c r="Q62" s="6" t="n">
+      <c r="Q62" s="7" t="n">
         <v>91.65000000000001</v>
       </c>
-      <c r="R62" s="6" t="n">
+      <c r="R62" s="7" t="n">
         <v>92.25</v>
       </c>
-      <c r="S62" s="6" t="n">
+      <c r="S62" s="7" t="n">
         <v>92.17</v>
       </c>
-      <c r="T62" s="6" t="n">
+      <c r="T62" s="7" t="n">
         <v>92.7</v>
       </c>
-      <c r="U62" s="6" t="n">
+      <c r="U62" s="7" t="n">
         <v>92.8</v>
       </c>
-      <c r="V62" s="6" t="n">
+      <c r="V62" s="7" t="n">
         <v>92.02</v>
       </c>
-      <c r="W62" s="6" t="n">
+      <c r="W62" s="7" t="n">
         <v>88.45</v>
       </c>
-      <c r="X62" s="6" t="n">
+      <c r="X62" s="7" t="n">
         <v>84.58</v>
       </c>
-      <c r="Y62" s="6" t="n">
+      <c r="Y62" s="7" t="n">
         <v>84.7</v>
       </c>
-      <c r="Z62" s="6" t="n">
+      <c r="Z62" s="7" t="n">
         <v>84.90000000000001</v>
       </c>
-      <c r="AA62" s="6" t="n">
+      <c r="AA62" s="7" t="n">
         <v>84.73</v>
       </c>
-      <c r="AB62" s="6" t="n">
+      <c r="AB62" s="7" t="n">
         <v>84.53</v>
       </c>
-      <c r="AC62" s="6" t="n">
+      <c r="AC62" s="7" t="n">
         <v>84.45</v>
       </c>
-      <c r="AD62" s="6" t="n">
+      <c r="AD62" s="7" t="n">
         <v>84.92</v>
       </c>
-      <c r="AE62" s="6" t="n">
+      <c r="AE62" s="7" t="n">
         <v>85.40000000000001</v>
       </c>
-      <c r="AF62" s="6" t="n">
+      <c r="AF62" s="7" t="n">
         <v>89.3</v>
       </c>
-      <c r="AG62" s="6" t="n">
+      <c r="AG62" s="7" t="n">
         <v>92.92</v>
       </c>
       <c r="AH62" s="6" t="n">
@@ -5725,7 +5755,7 @@
       </c>
       <c r="AI62" s="6" t="inlineStr"/>
       <c r="AJ62" s="6" t="inlineStr"/>
-      <c r="AK62" s="12" t="n"/>
+      <c r="AK62" s="15" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -5736,97 +5766,97 @@
       <c r="B63" s="6" t="n">
         <v>67.25</v>
       </c>
-      <c r="C63" s="6" t="n">
+      <c r="C63" s="7" t="n">
         <v>93.25</v>
       </c>
-      <c r="D63" s="6" t="n">
+      <c r="D63" s="7" t="n">
         <v>93.33</v>
       </c>
-      <c r="E63" s="6" t="n">
+      <c r="E63" s="7" t="n">
         <v>92.05</v>
       </c>
-      <c r="F63" s="6" t="n">
+      <c r="F63" s="7" t="n">
         <v>93.31999999999999</v>
       </c>
-      <c r="G63" s="6" t="n">
+      <c r="G63" s="7" t="n">
         <v>92.2</v>
       </c>
-      <c r="H63" s="6" t="n">
+      <c r="H63" s="7" t="n">
         <v>93.18000000000001</v>
       </c>
-      <c r="I63" s="6" t="n">
+      <c r="I63" s="7" t="n">
         <v>92.56999999999999</v>
       </c>
-      <c r="J63" s="6" t="n">
+      <c r="J63" s="7" t="n">
         <v>93.27</v>
       </c>
-      <c r="K63" s="6" t="n">
+      <c r="K63" s="7" t="n">
         <v>84.75</v>
       </c>
-      <c r="L63" s="6" t="n">
+      <c r="L63" s="7" t="n">
         <v>79.81999999999999</v>
       </c>
-      <c r="M63" s="6" t="n">
+      <c r="M63" s="7" t="n">
         <v>87.84999999999999</v>
       </c>
-      <c r="N63" s="6" t="n">
+      <c r="N63" s="7" t="n">
         <v>91.63</v>
       </c>
-      <c r="O63" s="6" t="n">
+      <c r="O63" s="7" t="n">
         <v>91.15000000000001</v>
       </c>
-      <c r="P63" s="6" t="n">
+      <c r="P63" s="7" t="n">
         <v>89.13</v>
       </c>
-      <c r="Q63" s="6" t="n">
+      <c r="Q63" s="7" t="n">
         <v>89.98</v>
       </c>
-      <c r="R63" s="6" t="n">
+      <c r="R63" s="7" t="n">
         <v>94.06999999999999</v>
       </c>
-      <c r="S63" s="6" t="n">
+      <c r="S63" s="7" t="n">
         <v>94.25</v>
       </c>
-      <c r="T63" s="6" t="n">
+      <c r="T63" s="7" t="n">
         <v>92.77</v>
       </c>
-      <c r="U63" s="6" t="n">
+      <c r="U63" s="7" t="n">
         <v>93.7</v>
       </c>
-      <c r="V63" s="6" t="n">
+      <c r="V63" s="7" t="n">
         <v>91.33</v>
       </c>
-      <c r="W63" s="6" t="n">
+      <c r="W63" s="7" t="n">
         <v>87.59999999999999</v>
       </c>
-      <c r="X63" s="6" t="n">
+      <c r="X63" s="7" t="n">
         <v>86.08</v>
       </c>
-      <c r="Y63" s="6" t="n">
+      <c r="Y63" s="7" t="n">
         <v>85.33</v>
       </c>
-      <c r="Z63" s="6" t="n">
+      <c r="Z63" s="7" t="n">
         <v>81.62</v>
       </c>
-      <c r="AA63" s="6" t="n">
+      <c r="AA63" s="7" t="n">
         <v>84.37</v>
       </c>
-      <c r="AB63" s="6" t="n">
+      <c r="AB63" s="7" t="n">
         <v>86.25</v>
       </c>
-      <c r="AC63" s="6" t="n">
+      <c r="AC63" s="7" t="n">
         <v>83.97</v>
       </c>
-      <c r="AD63" s="6" t="n">
+      <c r="AD63" s="7" t="n">
         <v>79.47</v>
       </c>
-      <c r="AE63" s="6" t="n">
+      <c r="AE63" s="7" t="n">
         <v>83.92</v>
       </c>
-      <c r="AF63" s="6" t="n">
+      <c r="AF63" s="7" t="n">
         <v>89.75</v>
       </c>
-      <c r="AG63" s="6" t="n">
+      <c r="AG63" s="7" t="n">
         <v>93.13</v>
       </c>
       <c r="AH63" s="6" t="n">
@@ -5834,7 +5864,7 @@
       </c>
       <c r="AI63" s="6" t="inlineStr"/>
       <c r="AJ63" s="6" t="inlineStr"/>
-      <c r="AK63" s="12" t="n"/>
+      <c r="AK63" s="15" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -5845,97 +5875,97 @@
       <c r="B64" s="6" t="n">
         <v>77.25</v>
       </c>
-      <c r="C64" s="6" t="n">
+      <c r="C64" s="7" t="n">
         <v>78.43000000000001</v>
       </c>
-      <c r="D64" s="6" t="n">
+      <c r="D64" s="7" t="n">
         <v>77.95</v>
       </c>
-      <c r="E64" s="6" t="n">
+      <c r="E64" s="7" t="n">
         <v>82.13</v>
       </c>
-      <c r="F64" s="6" t="n">
+      <c r="F64" s="7" t="n">
         <v>81</v>
       </c>
-      <c r="G64" s="6" t="n">
+      <c r="G64" s="7" t="n">
         <v>88.90000000000001</v>
       </c>
-      <c r="H64" s="6" t="n">
+      <c r="H64" s="7" t="n">
         <v>86.87</v>
       </c>
-      <c r="I64" s="6" t="n">
+      <c r="I64" s="7" t="n">
         <v>88.59999999999999</v>
       </c>
-      <c r="J64" s="6" t="n">
+      <c r="J64" s="7" t="n">
         <v>85.5</v>
       </c>
-      <c r="K64" s="6" t="n">
+      <c r="K64" s="7" t="n">
         <v>84.95</v>
       </c>
-      <c r="L64" s="6" t="n">
+      <c r="L64" s="7" t="n">
         <v>85.81999999999999</v>
       </c>
-      <c r="M64" s="6" t="n">
+      <c r="M64" s="7" t="n">
         <v>88.28</v>
       </c>
-      <c r="N64" s="6" t="n">
+      <c r="N64" s="7" t="n">
         <v>86.15000000000001</v>
       </c>
-      <c r="O64" s="6" t="n">
+      <c r="O64" s="7" t="n">
         <v>88.15000000000001</v>
       </c>
-      <c r="P64" s="6" t="n">
+      <c r="P64" s="7" t="n">
         <v>88.84999999999999</v>
       </c>
-      <c r="Q64" s="6" t="n">
+      <c r="Q64" s="7" t="n">
         <v>83.38</v>
       </c>
-      <c r="R64" s="6" t="n">
+      <c r="R64" s="7" t="n">
         <v>86.23</v>
       </c>
-      <c r="S64" s="6" t="n">
+      <c r="S64" s="7" t="n">
         <v>86.43000000000001</v>
       </c>
-      <c r="T64" s="6" t="n">
+      <c r="T64" s="7" t="n">
         <v>81.55</v>
       </c>
-      <c r="U64" s="6" t="n">
+      <c r="U64" s="7" t="n">
         <v>82.25</v>
       </c>
-      <c r="V64" s="6" t="n">
+      <c r="V64" s="7" t="n">
         <v>88.13</v>
       </c>
-      <c r="W64" s="6" t="n">
+      <c r="W64" s="7" t="n">
         <v>87.98</v>
       </c>
-      <c r="X64" s="6" t="n">
+      <c r="X64" s="7" t="n">
         <v>85.22</v>
       </c>
-      <c r="Y64" s="6" t="n">
+      <c r="Y64" s="7" t="n">
         <v>82.53</v>
       </c>
-      <c r="Z64" s="6" t="n">
+      <c r="Z64" s="7" t="n">
         <v>84.78</v>
       </c>
-      <c r="AA64" s="6" t="n">
+      <c r="AA64" s="7" t="n">
         <v>75.37</v>
       </c>
-      <c r="AB64" s="6" t="n">
+      <c r="AB64" s="7" t="n">
         <v>75.09999999999999</v>
       </c>
-      <c r="AC64" s="6" t="n">
+      <c r="AC64" s="7" t="n">
         <v>77.83</v>
       </c>
-      <c r="AD64" s="6" t="n">
+      <c r="AD64" s="7" t="n">
         <v>80.78</v>
       </c>
-      <c r="AE64" s="6" t="n">
+      <c r="AE64" s="7" t="n">
         <v>73.13</v>
       </c>
-      <c r="AF64" s="6" t="n">
+      <c r="AF64" s="7" t="n">
         <v>71</v>
       </c>
-      <c r="AG64" s="6" t="n">
+      <c r="AG64" s="7" t="n">
         <v>81.65000000000001</v>
       </c>
       <c r="AH64" s="6" t="n">
@@ -5943,7 +5973,7 @@
       </c>
       <c r="AI64" s="6" t="inlineStr"/>
       <c r="AJ64" s="6" t="inlineStr"/>
-      <c r="AK64" s="12" t="n"/>
+      <c r="AK64" s="15" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -5954,97 +5984,97 @@
       <c r="B65" s="6" t="n">
         <v>175.25</v>
       </c>
-      <c r="C65" s="6" t="n">
+      <c r="C65" s="7" t="n">
         <v>91.97</v>
       </c>
-      <c r="D65" s="6" t="n">
+      <c r="D65" s="7" t="n">
         <v>92.06999999999999</v>
       </c>
-      <c r="E65" s="6" t="n">
+      <c r="E65" s="7" t="n">
         <v>92.53</v>
       </c>
-      <c r="F65" s="6" t="n">
+      <c r="F65" s="7" t="n">
         <v>94.15000000000001</v>
       </c>
-      <c r="G65" s="6" t="n">
+      <c r="G65" s="7" t="n">
         <v>94.17</v>
       </c>
-      <c r="H65" s="6" t="n">
+      <c r="H65" s="7" t="n">
         <v>94.52</v>
       </c>
-      <c r="I65" s="6" t="n">
+      <c r="I65" s="7" t="n">
         <v>94.59999999999999</v>
       </c>
-      <c r="J65" s="6" t="n">
+      <c r="J65" s="7" t="n">
         <v>94.53</v>
       </c>
-      <c r="K65" s="6" t="n">
+      <c r="K65" s="7" t="n">
         <v>92.12</v>
       </c>
-      <c r="L65" s="6" t="n">
+      <c r="L65" s="7" t="n">
         <v>88.5</v>
       </c>
-      <c r="M65" s="6" t="n">
+      <c r="M65" s="7" t="n">
         <v>89.97</v>
       </c>
-      <c r="N65" s="6" t="n">
+      <c r="N65" s="7" t="n">
         <v>94.43000000000001</v>
       </c>
-      <c r="O65" s="6" t="n">
+      <c r="O65" s="7" t="n">
         <v>93.95</v>
       </c>
-      <c r="P65" s="6" t="n">
+      <c r="P65" s="7" t="n">
         <v>93.98</v>
       </c>
-      <c r="Q65" s="6" t="n">
+      <c r="Q65" s="7" t="n">
         <v>94.02</v>
       </c>
-      <c r="R65" s="6" t="n">
+      <c r="R65" s="7" t="n">
         <v>95</v>
       </c>
-      <c r="S65" s="6" t="n">
+      <c r="S65" s="7" t="n">
         <v>95.06999999999999</v>
       </c>
-      <c r="T65" s="6" t="n">
+      <c r="T65" s="7" t="n">
         <v>91.95</v>
       </c>
-      <c r="U65" s="6" t="n">
+      <c r="U65" s="7" t="n">
         <v>95.92</v>
       </c>
-      <c r="V65" s="6" t="n">
+      <c r="V65" s="7" t="n">
         <v>94.37</v>
       </c>
-      <c r="W65" s="6" t="n">
+      <c r="W65" s="7" t="n">
         <v>92.59999999999999</v>
       </c>
-      <c r="X65" s="6" t="n">
+      <c r="X65" s="7" t="n">
         <v>90.56999999999999</v>
       </c>
-      <c r="Y65" s="6" t="n">
+      <c r="Y65" s="7" t="n">
         <v>90.02</v>
       </c>
-      <c r="Z65" s="6" t="n">
+      <c r="Z65" s="7" t="n">
         <v>90.7</v>
       </c>
-      <c r="AA65" s="6" t="n">
+      <c r="AA65" s="7" t="n">
         <v>89.25</v>
       </c>
-      <c r="AB65" s="6" t="n">
+      <c r="AB65" s="7" t="n">
         <v>90.03</v>
       </c>
-      <c r="AC65" s="6" t="n">
+      <c r="AC65" s="7" t="n">
         <v>90.34999999999999</v>
       </c>
-      <c r="AD65" s="6" t="n">
+      <c r="AD65" s="7" t="n">
         <v>89.88</v>
       </c>
-      <c r="AE65" s="6" t="n">
+      <c r="AE65" s="7" t="n">
         <v>89.15000000000001</v>
       </c>
-      <c r="AF65" s="6" t="n">
+      <c r="AF65" s="7" t="n">
         <v>91.33</v>
       </c>
-      <c r="AG65" s="6" t="n">
+      <c r="AG65" s="7" t="n">
         <v>95.03</v>
       </c>
       <c r="AH65" s="6" t="n">
@@ -6052,7 +6082,7 @@
       </c>
       <c r="AI65" s="6" t="inlineStr"/>
       <c r="AJ65" s="6" t="inlineStr"/>
-      <c r="AK65" s="12" t="n"/>
+      <c r="AK65" s="15" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -6063,97 +6093,97 @@
       <c r="B66" s="6" t="n">
         <v>181.25</v>
       </c>
-      <c r="C66" s="6" t="n">
+      <c r="C66" s="7" t="n">
         <v>80.13</v>
       </c>
-      <c r="D66" s="6" t="n">
+      <c r="D66" s="7" t="n">
         <v>79.77</v>
       </c>
-      <c r="E66" s="6" t="n">
+      <c r="E66" s="7" t="n">
         <v>77.02</v>
       </c>
-      <c r="F66" s="6" t="n">
+      <c r="F66" s="7" t="n">
         <v>78.45</v>
       </c>
-      <c r="G66" s="6" t="n">
+      <c r="G66" s="7" t="n">
         <v>78.38</v>
       </c>
-      <c r="H66" s="6" t="n">
+      <c r="H66" s="7" t="n">
         <v>79.77</v>
       </c>
-      <c r="I66" s="6" t="n">
+      <c r="I66" s="7" t="n">
         <v>79.95</v>
       </c>
-      <c r="J66" s="6" t="n">
+      <c r="J66" s="7" t="n">
         <v>80.28</v>
       </c>
-      <c r="K66" s="6" t="n">
+      <c r="K66" s="7" t="n">
         <v>79.28</v>
       </c>
-      <c r="L66" s="6" t="n">
+      <c r="L66" s="7" t="n">
         <v>78.72</v>
       </c>
-      <c r="M66" s="6" t="n">
+      <c r="M66" s="7" t="n">
         <v>77.90000000000001</v>
       </c>
-      <c r="N66" s="6" t="n">
+      <c r="N66" s="7" t="n">
         <v>81.45</v>
       </c>
-      <c r="O66" s="6" t="n">
+      <c r="O66" s="7" t="n">
         <v>80.13</v>
       </c>
-      <c r="P66" s="6" t="n">
+      <c r="P66" s="7" t="n">
         <v>81</v>
       </c>
-      <c r="Q66" s="6" t="n">
+      <c r="Q66" s="7" t="n">
         <v>81.15000000000001</v>
       </c>
-      <c r="R66" s="6" t="n">
+      <c r="R66" s="7" t="n">
         <v>82.13</v>
       </c>
-      <c r="S66" s="6" t="n">
+      <c r="S66" s="7" t="n">
         <v>81.15000000000001</v>
       </c>
-      <c r="T66" s="6" t="n">
+      <c r="T66" s="7" t="n">
         <v>80.42</v>
       </c>
-      <c r="U66" s="6" t="n">
+      <c r="U66" s="7" t="n">
         <v>79.87</v>
       </c>
-      <c r="V66" s="6" t="n">
+      <c r="V66" s="7" t="n">
         <v>84.87</v>
       </c>
-      <c r="W66" s="6" t="n">
+      <c r="W66" s="7" t="n">
         <v>82.87</v>
       </c>
-      <c r="X66" s="6" t="n">
+      <c r="X66" s="7" t="n">
         <v>80.48</v>
       </c>
-      <c r="Y66" s="6" t="n">
+      <c r="Y66" s="7" t="n">
         <v>82.17</v>
       </c>
-      <c r="Z66" s="6" t="n">
+      <c r="Z66" s="7" t="n">
         <v>83.45</v>
       </c>
-      <c r="AA66" s="6" t="n">
+      <c r="AA66" s="7" t="n">
         <v>80.7</v>
       </c>
-      <c r="AB66" s="6" t="n">
+      <c r="AB66" s="7" t="n">
         <v>81.31999999999999</v>
       </c>
-      <c r="AC66" s="6" t="n">
+      <c r="AC66" s="7" t="n">
         <v>81.65000000000001</v>
       </c>
-      <c r="AD66" s="6" t="n">
+      <c r="AD66" s="7" t="n">
         <v>82.7</v>
       </c>
-      <c r="AE66" s="6" t="n">
+      <c r="AE66" s="7" t="n">
         <v>83.06999999999999</v>
       </c>
-      <c r="AF66" s="6" t="n">
+      <c r="AF66" s="7" t="n">
         <v>84.22</v>
       </c>
-      <c r="AG66" s="6" t="n">
+      <c r="AG66" s="7" t="n">
         <v>86.5</v>
       </c>
       <c r="AH66" s="6" t="n">
@@ -6161,7 +6191,7 @@
       </c>
       <c r="AI66" s="6" t="inlineStr"/>
       <c r="AJ66" s="6" t="inlineStr"/>
-      <c r="AK66" s="12" t="n"/>
+      <c r="AK66" s="15" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -6172,97 +6202,97 @@
       <c r="B67" s="6" t="n">
         <v>187.25</v>
       </c>
-      <c r="C67" s="6" t="n">
+      <c r="C67" s="7" t="n">
         <v>88</v>
       </c>
-      <c r="D67" s="6" t="n">
+      <c r="D67" s="7" t="n">
         <v>87.87</v>
       </c>
-      <c r="E67" s="6" t="n">
+      <c r="E67" s="7" t="n">
         <v>90.37</v>
       </c>
-      <c r="F67" s="6" t="n">
+      <c r="F67" s="7" t="n">
         <v>89.15000000000001</v>
       </c>
-      <c r="G67" s="6" t="n">
+      <c r="G67" s="7" t="n">
         <v>89.31999999999999</v>
       </c>
-      <c r="H67" s="6" t="n">
+      <c r="H67" s="7" t="n">
         <v>89.45</v>
       </c>
-      <c r="I67" s="6" t="n">
+      <c r="I67" s="7" t="n">
         <v>89.03</v>
       </c>
-      <c r="J67" s="6" t="n">
+      <c r="J67" s="7" t="n">
         <v>88.2</v>
       </c>
-      <c r="K67" s="6" t="n">
+      <c r="K67" s="7" t="n">
         <v>91.17</v>
       </c>
-      <c r="L67" s="6" t="n">
+      <c r="L67" s="7" t="n">
         <v>93.93000000000001</v>
       </c>
-      <c r="M67" s="6" t="n">
+      <c r="M67" s="7" t="n">
         <v>92.55</v>
       </c>
-      <c r="N67" s="6" t="n">
+      <c r="N67" s="7" t="n">
         <v>89.2</v>
       </c>
-      <c r="O67" s="6" t="n">
+      <c r="O67" s="7" t="n">
         <v>89.72</v>
       </c>
-      <c r="P67" s="6" t="n">
+      <c r="P67" s="7" t="n">
         <v>90.22</v>
       </c>
-      <c r="Q67" s="6" t="n">
+      <c r="Q67" s="7" t="n">
         <v>90.2</v>
       </c>
-      <c r="R67" s="6" t="n">
+      <c r="R67" s="7" t="n">
         <v>89.56999999999999</v>
       </c>
-      <c r="S67" s="6" t="n">
+      <c r="S67" s="7" t="n">
         <v>89.03</v>
       </c>
-      <c r="T67" s="6" t="n">
+      <c r="T67" s="7" t="n">
         <v>89.34999999999999</v>
       </c>
-      <c r="U67" s="6" t="n">
+      <c r="U67" s="7" t="n">
         <v>89.78</v>
       </c>
-      <c r="V67" s="6" t="n">
+      <c r="V67" s="7" t="n">
         <v>89.78</v>
       </c>
-      <c r="W67" s="6" t="n">
+      <c r="W67" s="7" t="n">
         <v>91.87</v>
       </c>
-      <c r="X67" s="6" t="n">
+      <c r="X67" s="7" t="n">
         <v>94.08</v>
       </c>
-      <c r="Y67" s="6" t="n">
+      <c r="Y67" s="7" t="n">
         <v>94.45</v>
       </c>
-      <c r="Z67" s="6" t="n">
+      <c r="Z67" s="7" t="n">
         <v>94.65000000000001</v>
       </c>
-      <c r="AA67" s="6" t="n">
+      <c r="AA67" s="7" t="n">
         <v>94</v>
       </c>
-      <c r="AB67" s="6" t="n">
+      <c r="AB67" s="7" t="n">
         <v>93.73</v>
       </c>
-      <c r="AC67" s="6" t="n">
+      <c r="AC67" s="7" t="n">
         <v>93.92</v>
       </c>
-      <c r="AD67" s="6" t="n">
+      <c r="AD67" s="7" t="n">
         <v>94.31999999999999</v>
       </c>
-      <c r="AE67" s="6" t="n">
+      <c r="AE67" s="7" t="n">
         <v>94.02</v>
       </c>
-      <c r="AF67" s="6" t="n">
+      <c r="AF67" s="7" t="n">
         <v>92.17</v>
       </c>
-      <c r="AG67" s="6" t="n">
+      <c r="AG67" s="7" t="n">
         <v>90.22</v>
       </c>
       <c r="AH67" s="6" t="n">
@@ -6270,7 +6300,7 @@
       </c>
       <c r="AI67" s="6" t="inlineStr"/>
       <c r="AJ67" s="6" t="inlineStr"/>
-      <c r="AK67" s="12" t="n"/>
+      <c r="AK67" s="15" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -6281,97 +6311,97 @@
       <c r="B68" s="6" t="n">
         <v>199.25</v>
       </c>
-      <c r="C68" s="6" t="n">
+      <c r="C68" s="7" t="n">
         <v>67.97</v>
       </c>
-      <c r="D68" s="6" t="n">
+      <c r="D68" s="7" t="n">
         <v>67.75</v>
       </c>
-      <c r="E68" s="6" t="n">
+      <c r="E68" s="7" t="n">
         <v>70.25</v>
       </c>
-      <c r="F68" s="6" t="n">
+      <c r="F68" s="7" t="n">
         <v>70.18000000000001</v>
       </c>
-      <c r="G68" s="6" t="n">
+      <c r="G68" s="7" t="n">
         <v>69.31999999999999</v>
       </c>
-      <c r="H68" s="6" t="n">
+      <c r="H68" s="7" t="n">
         <v>70.72</v>
       </c>
-      <c r="I68" s="6" t="n">
+      <c r="I68" s="7" t="n">
         <v>71.78</v>
       </c>
-      <c r="J68" s="6" t="n">
+      <c r="J68" s="7" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="K68" s="6" t="n">
+      <c r="K68" s="7" t="n">
         <v>68.25</v>
       </c>
-      <c r="L68" s="6" t="n">
+      <c r="L68" s="7" t="n">
         <v>65.83</v>
       </c>
-      <c r="M68" s="6" t="n">
+      <c r="M68" s="7" t="n">
         <v>67.34999999999999</v>
       </c>
-      <c r="N68" s="6" t="n">
+      <c r="N68" s="7" t="n">
         <v>72.52</v>
       </c>
-      <c r="O68" s="6" t="n">
+      <c r="O68" s="7" t="n">
         <v>71.33</v>
       </c>
-      <c r="P68" s="6" t="n">
+      <c r="P68" s="7" t="n">
         <v>72.13</v>
       </c>
-      <c r="Q68" s="6" t="n">
+      <c r="Q68" s="7" t="n">
         <v>70.43000000000001</v>
       </c>
-      <c r="R68" s="6" t="n">
+      <c r="R68" s="7" t="n">
         <v>70.83</v>
       </c>
-      <c r="S68" s="6" t="n">
+      <c r="S68" s="7" t="n">
         <v>72.3</v>
       </c>
-      <c r="T68" s="6" t="n">
+      <c r="T68" s="7" t="n">
         <v>69.37</v>
       </c>
-      <c r="U68" s="6" t="n">
+      <c r="U68" s="7" t="n">
         <v>71.59999999999999</v>
       </c>
-      <c r="V68" s="6" t="n">
+      <c r="V68" s="7" t="n">
         <v>70.43000000000001</v>
       </c>
-      <c r="W68" s="6" t="n">
+      <c r="W68" s="7" t="n">
         <v>68.2</v>
       </c>
-      <c r="X68" s="6" t="n">
+      <c r="X68" s="7" t="n">
         <v>65.47</v>
       </c>
-      <c r="Y68" s="6" t="n">
+      <c r="Y68" s="7" t="n">
         <v>64.65000000000001</v>
       </c>
-      <c r="Z68" s="6" t="n">
+      <c r="Z68" s="7" t="n">
         <v>65.03</v>
       </c>
-      <c r="AA68" s="6" t="n">
+      <c r="AA68" s="7" t="n">
         <v>64.8</v>
       </c>
-      <c r="AB68" s="6" t="n">
+      <c r="AB68" s="7" t="n">
         <v>65.42</v>
       </c>
-      <c r="AC68" s="6" t="n">
+      <c r="AC68" s="7" t="n">
         <v>65.77</v>
       </c>
-      <c r="AD68" s="6" t="n">
+      <c r="AD68" s="7" t="n">
         <v>65.05</v>
       </c>
-      <c r="AE68" s="6" t="n">
+      <c r="AE68" s="7" t="n">
         <v>66.34999999999999</v>
       </c>
-      <c r="AF68" s="6" t="n">
+      <c r="AF68" s="7" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="AG68" s="6" t="n">
+      <c r="AG68" s="7" t="n">
         <v>74.7</v>
       </c>
       <c r="AH68" s="6" t="n">
@@ -6379,7 +6409,7 @@
       </c>
       <c r="AI68" s="6" t="inlineStr"/>
       <c r="AJ68" s="6" t="inlineStr"/>
-      <c r="AK68" s="12" t="n"/>
+      <c r="AK68" s="15" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -6390,97 +6420,97 @@
       <c r="B69" s="6" t="n">
         <v>519.25</v>
       </c>
-      <c r="C69" s="6" t="n">
+      <c r="C69" s="7" t="n">
         <v>84.31999999999999</v>
       </c>
-      <c r="D69" s="6" t="n">
+      <c r="D69" s="7" t="n">
         <v>83.48</v>
       </c>
-      <c r="E69" s="6" t="n">
+      <c r="E69" s="7" t="n">
         <v>83.25</v>
       </c>
-      <c r="F69" s="6" t="n">
+      <c r="F69" s="7" t="n">
         <v>83.02</v>
       </c>
-      <c r="G69" s="6" t="n">
+      <c r="G69" s="7" t="n">
         <v>83.56999999999999</v>
       </c>
-      <c r="H69" s="6" t="n">
+      <c r="H69" s="7" t="n">
         <v>83.67</v>
       </c>
-      <c r="I69" s="6" t="n">
+      <c r="I69" s="7" t="n">
         <v>84.25</v>
       </c>
-      <c r="J69" s="6" t="n">
+      <c r="J69" s="7" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="K69" s="6" t="n">
+      <c r="K69" s="7" t="n">
         <v>81.27</v>
       </c>
-      <c r="L69" s="6" t="n">
+      <c r="L69" s="7" t="n">
         <v>79.15000000000001</v>
       </c>
-      <c r="M69" s="6" t="n">
+      <c r="M69" s="7" t="n">
         <v>82</v>
       </c>
-      <c r="N69" s="6" t="n">
+      <c r="N69" s="7" t="n">
         <v>82.68000000000001</v>
       </c>
-      <c r="O69" s="6" t="n">
+      <c r="O69" s="7" t="n">
         <v>83.15000000000001</v>
       </c>
-      <c r="P69" s="6" t="n">
+      <c r="P69" s="7" t="n">
         <v>83.65000000000001</v>
       </c>
-      <c r="Q69" s="6" t="n">
+      <c r="Q69" s="7" t="n">
         <v>83.8</v>
       </c>
-      <c r="R69" s="6" t="n">
+      <c r="R69" s="7" t="n">
         <v>83.75</v>
       </c>
-      <c r="S69" s="6" t="n">
+      <c r="S69" s="7" t="n">
         <v>83.84999999999999</v>
       </c>
-      <c r="T69" s="6" t="n">
+      <c r="T69" s="7" t="n">
         <v>83.2</v>
       </c>
-      <c r="U69" s="6" t="n">
+      <c r="U69" s="7" t="n">
         <v>83.33</v>
       </c>
-      <c r="V69" s="6" t="n">
+      <c r="V69" s="7" t="n">
         <v>83.95</v>
       </c>
-      <c r="W69" s="6" t="n">
+      <c r="W69" s="7" t="n">
         <v>82.31999999999999</v>
       </c>
-      <c r="X69" s="6" t="n">
+      <c r="X69" s="7" t="n">
         <v>78.5</v>
       </c>
-      <c r="Y69" s="6" t="n">
+      <c r="Y69" s="7" t="n">
         <v>77.97</v>
       </c>
-      <c r="Z69" s="6" t="n">
+      <c r="Z69" s="7" t="n">
         <v>75.37</v>
       </c>
-      <c r="AA69" s="6" t="n">
+      <c r="AA69" s="7" t="n">
         <v>80.13</v>
       </c>
-      <c r="AB69" s="6" t="n">
+      <c r="AB69" s="7" t="n">
         <v>79.25</v>
       </c>
-      <c r="AC69" s="6" t="n">
+      <c r="AC69" s="7" t="n">
         <v>79.8</v>
       </c>
-      <c r="AD69" s="6" t="n">
+      <c r="AD69" s="7" t="n">
         <v>77.13</v>
       </c>
-      <c r="AE69" s="6" t="n">
+      <c r="AE69" s="7" t="n">
         <v>78.34999999999999</v>
       </c>
-      <c r="AF69" s="6" t="n">
+      <c r="AF69" s="7" t="n">
         <v>81.37</v>
       </c>
-      <c r="AG69" s="6" t="n">
+      <c r="AG69" s="7" t="n">
         <v>84.68000000000001</v>
       </c>
       <c r="AH69" s="6" t="n">
@@ -6488,7 +6518,7 @@
       </c>
       <c r="AI69" s="6" t="inlineStr"/>
       <c r="AJ69" s="6" t="inlineStr"/>
-      <c r="AK69" s="12" t="n"/>
+      <c r="AK69" s="15" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -6499,97 +6529,97 @@
       <c r="B70" s="6" t="n">
         <v>531.25</v>
       </c>
-      <c r="C70" s="6" t="n">
+      <c r="C70" s="16" t="n">
         <v>28.37</v>
       </c>
-      <c r="D70" s="6" t="n">
+      <c r="D70" s="16" t="n">
         <v>29.4</v>
       </c>
-      <c r="E70" s="6" t="n">
+      <c r="E70" s="16" t="n">
         <v>27.83</v>
       </c>
-      <c r="F70" s="6" t="n">
+      <c r="F70" s="16" t="n">
         <v>28.55</v>
       </c>
-      <c r="G70" s="6" t="n">
+      <c r="G70" s="16" t="n">
         <v>28.55</v>
       </c>
-      <c r="H70" s="6" t="n">
+      <c r="H70" s="16" t="n">
         <v>27.95</v>
       </c>
-      <c r="I70" s="6" t="n">
+      <c r="I70" s="16" t="n">
         <v>28</v>
       </c>
-      <c r="J70" s="6" t="n">
+      <c r="J70" s="16" t="n">
         <v>28.12</v>
       </c>
-      <c r="K70" s="6" t="n">
+      <c r="K70" s="16" t="n">
         <v>33.42</v>
       </c>
-      <c r="L70" s="6" t="n">
+      <c r="L70" s="16" t="n">
         <v>38.92</v>
       </c>
-      <c r="M70" s="6" t="n">
+      <c r="M70" s="16" t="n">
         <v>34.12</v>
       </c>
-      <c r="N70" s="6" t="n">
+      <c r="N70" s="16" t="n">
         <v>28.75</v>
       </c>
-      <c r="O70" s="6" t="n">
+      <c r="O70" s="16" t="n">
         <v>28.63</v>
       </c>
-      <c r="P70" s="6" t="n">
+      <c r="P70" s="16" t="n">
         <v>27.68</v>
       </c>
-      <c r="Q70" s="6" t="n">
+      <c r="Q70" s="16" t="n">
         <v>28.35</v>
       </c>
-      <c r="R70" s="6" t="n">
+      <c r="R70" s="16" t="n">
         <v>27.93</v>
       </c>
-      <c r="S70" s="6" t="n">
+      <c r="S70" s="16" t="n">
         <v>28.22</v>
       </c>
-      <c r="T70" s="6" t="n">
+      <c r="T70" s="16" t="n">
         <v>29</v>
       </c>
-      <c r="U70" s="6" t="n">
+      <c r="U70" s="16" t="n">
         <v>28.68</v>
       </c>
-      <c r="V70" s="6" t="n">
+      <c r="V70" s="16" t="n">
         <v>27.77</v>
       </c>
-      <c r="W70" s="6" t="n">
+      <c r="W70" s="16" t="n">
         <v>33.18</v>
       </c>
-      <c r="X70" s="6" t="n">
+      <c r="X70" s="16" t="n">
         <v>39.05</v>
       </c>
-      <c r="Y70" s="6" t="n">
+      <c r="Y70" s="16" t="n">
         <v>39.05</v>
       </c>
-      <c r="Z70" s="6" t="n">
+      <c r="Z70" s="16" t="n">
         <v>38.88</v>
       </c>
-      <c r="AA70" s="6" t="n">
+      <c r="AA70" s="16" t="n">
         <v>38.68</v>
       </c>
-      <c r="AB70" s="6" t="n">
+      <c r="AB70" s="16" t="n">
         <v>38.78</v>
       </c>
-      <c r="AC70" s="6" t="n">
+      <c r="AC70" s="16" t="n">
         <v>39.45</v>
       </c>
-      <c r="AD70" s="6" t="n">
+      <c r="AD70" s="16" t="n">
         <v>38.48</v>
       </c>
-      <c r="AE70" s="6" t="n">
+      <c r="AE70" s="16" t="n">
         <v>39.23</v>
       </c>
-      <c r="AF70" s="6" t="n">
+      <c r="AF70" s="16" t="n">
         <v>33.83</v>
       </c>
-      <c r="AG70" s="6" t="n">
+      <c r="AG70" s="16" t="n">
         <v>28.65</v>
       </c>
       <c r="AH70" s="6" t="n">
@@ -6597,7 +6627,7 @@
       </c>
       <c r="AI70" s="6" t="inlineStr"/>
       <c r="AJ70" s="6" t="inlineStr"/>
-      <c r="AK70" s="12" t="n"/>
+      <c r="AK70" s="15" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -6608,97 +6638,97 @@
       <c r="B71" s="6" t="n">
         <v>537.25</v>
       </c>
-      <c r="C71" s="6" t="n">
+      <c r="C71" s="7" t="n">
         <v>67.88</v>
       </c>
-      <c r="D71" s="6" t="n">
+      <c r="D71" s="7" t="n">
         <v>67.90000000000001</v>
       </c>
-      <c r="E71" s="6" t="n">
+      <c r="E71" s="7" t="n">
         <v>68.84999999999999</v>
       </c>
-      <c r="F71" s="6" t="n">
+      <c r="F71" s="7" t="n">
         <v>68.3</v>
       </c>
-      <c r="G71" s="6" t="n">
+      <c r="G71" s="7" t="n">
         <v>67.59999999999999</v>
       </c>
-      <c r="H71" s="6" t="n">
+      <c r="H71" s="7" t="n">
         <v>66.7</v>
       </c>
-      <c r="I71" s="6" t="n">
+      <c r="I71" s="7" t="n">
         <v>67.18000000000001</v>
       </c>
-      <c r="J71" s="6" t="n">
+      <c r="J71" s="7" t="n">
         <v>66.09999999999999</v>
       </c>
-      <c r="K71" s="6" t="n">
+      <c r="K71" s="7" t="n">
         <v>66.88</v>
       </c>
-      <c r="L71" s="6" t="n">
+      <c r="L71" s="7" t="n">
         <v>68.42</v>
       </c>
-      <c r="M71" s="6" t="n">
+      <c r="M71" s="7" t="n">
         <v>68.22</v>
       </c>
-      <c r="N71" s="6" t="n">
+      <c r="N71" s="7" t="n">
         <v>68.06999999999999</v>
       </c>
-      <c r="O71" s="6" t="n">
+      <c r="O71" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="P71" s="6" t="n">
+      <c r="P71" s="7" t="n">
         <v>68.68000000000001</v>
       </c>
-      <c r="Q71" s="6" t="n">
+      <c r="Q71" s="7" t="n">
         <v>68.65000000000001</v>
       </c>
-      <c r="R71" s="6" t="n">
+      <c r="R71" s="7" t="n">
         <v>70.63</v>
       </c>
-      <c r="S71" s="6" t="n">
+      <c r="S71" s="7" t="n">
         <v>70.2</v>
       </c>
-      <c r="T71" s="6" t="n">
+      <c r="T71" s="7" t="n">
         <v>67.40000000000001</v>
       </c>
-      <c r="U71" s="6" t="n">
+      <c r="U71" s="7" t="n">
         <v>69.95</v>
       </c>
-      <c r="V71" s="6" t="n">
+      <c r="V71" s="7" t="n">
         <v>70.65000000000001</v>
       </c>
-      <c r="W71" s="6" t="n">
+      <c r="W71" s="7" t="n">
         <v>70.73</v>
       </c>
-      <c r="X71" s="6" t="n">
+      <c r="X71" s="7" t="n">
         <v>68.55</v>
       </c>
-      <c r="Y71" s="6" t="n">
+      <c r="Y71" s="7" t="n">
         <v>68.7</v>
       </c>
-      <c r="Z71" s="6" t="n">
+      <c r="Z71" s="7" t="n">
         <v>66.93000000000001</v>
       </c>
-      <c r="AA71" s="6" t="n">
+      <c r="AA71" s="7" t="n">
         <v>68.27</v>
       </c>
-      <c r="AB71" s="6" t="n">
+      <c r="AB71" s="7" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="AC71" s="6" t="n">
+      <c r="AC71" s="7" t="n">
         <v>69.8</v>
       </c>
-      <c r="AD71" s="6" t="n">
+      <c r="AD71" s="7" t="n">
         <v>70.15000000000001</v>
       </c>
-      <c r="AE71" s="6" t="n">
+      <c r="AE71" s="7" t="n">
         <v>69.95</v>
       </c>
-      <c r="AF71" s="6" t="n">
+      <c r="AF71" s="7" t="n">
         <v>69.75</v>
       </c>
-      <c r="AG71" s="6" t="n">
+      <c r="AG71" s="7" t="n">
         <v>72</v>
       </c>
       <c r="AH71" s="6" t="n">
@@ -6706,7 +6736,7 @@
       </c>
       <c r="AI71" s="6" t="inlineStr"/>
       <c r="AJ71" s="6" t="inlineStr"/>
-      <c r="AK71" s="12" t="n"/>
+      <c r="AK71" s="15" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -6717,97 +6747,97 @@
       <c r="B72" s="6" t="n">
         <v>543.25</v>
       </c>
-      <c r="C72" s="6" t="n">
+      <c r="C72" s="16" t="n">
         <v>30.25</v>
       </c>
-      <c r="D72" s="6" t="n">
+      <c r="D72" s="16" t="n">
         <v>28.95</v>
       </c>
-      <c r="E72" s="6" t="n">
+      <c r="E72" s="16" t="n">
         <v>29.82</v>
       </c>
-      <c r="F72" s="6" t="n">
+      <c r="F72" s="16" t="n">
         <v>30.2</v>
       </c>
-      <c r="G72" s="6" t="n">
+      <c r="G72" s="16" t="n">
         <v>30.07</v>
       </c>
-      <c r="H72" s="6" t="n">
+      <c r="H72" s="16" t="n">
         <v>29.28</v>
       </c>
-      <c r="I72" s="6" t="n">
+      <c r="I72" s="16" t="n">
         <v>29.25</v>
       </c>
-      <c r="J72" s="6" t="n">
+      <c r="J72" s="16" t="n">
         <v>30.22</v>
       </c>
-      <c r="K72" s="6" t="n">
+      <c r="K72" s="16" t="n">
         <v>35.05</v>
       </c>
-      <c r="L72" s="6" t="n">
+      <c r="L72" s="16" t="n">
         <v>39.5</v>
       </c>
-      <c r="M72" s="6" t="n">
+      <c r="M72" s="16" t="n">
         <v>34.93</v>
       </c>
-      <c r="N72" s="6" t="n">
+      <c r="N72" s="16" t="n">
         <v>31.55</v>
       </c>
-      <c r="O72" s="6" t="n">
+      <c r="O72" s="16" t="n">
         <v>29</v>
       </c>
-      <c r="P72" s="6" t="n">
+      <c r="P72" s="16" t="n">
         <v>29.75</v>
       </c>
-      <c r="Q72" s="6" t="n">
+      <c r="Q72" s="16" t="n">
         <v>29.25</v>
       </c>
-      <c r="R72" s="6" t="n">
+      <c r="R72" s="16" t="n">
         <v>30.48</v>
       </c>
-      <c r="S72" s="6" t="n">
+      <c r="S72" s="16" t="n">
         <v>30.13</v>
       </c>
-      <c r="T72" s="6" t="n">
+      <c r="T72" s="16" t="n">
         <v>29.78</v>
       </c>
-      <c r="U72" s="6" t="n">
+      <c r="U72" s="16" t="n">
         <v>33.47</v>
       </c>
-      <c r="V72" s="6" t="n">
+      <c r="V72" s="16" t="n">
         <v>29.87</v>
       </c>
-      <c r="W72" s="6" t="n">
+      <c r="W72" s="16" t="n">
         <v>34.4</v>
       </c>
-      <c r="X72" s="6" t="n">
+      <c r="X72" s="16" t="n">
         <v>38.93</v>
       </c>
-      <c r="Y72" s="6" t="n">
+      <c r="Y72" s="16" t="n">
         <v>39.37</v>
       </c>
-      <c r="Z72" s="6" t="n">
+      <c r="Z72" s="16" t="n">
         <v>39.2</v>
       </c>
-      <c r="AA72" s="6" t="n">
+      <c r="AA72" s="16" t="n">
         <v>38.98</v>
       </c>
-      <c r="AB72" s="6" t="n">
+      <c r="AB72" s="16" t="n">
         <v>40.15</v>
       </c>
-      <c r="AC72" s="6" t="n">
+      <c r="AC72" s="16" t="n">
         <v>39.25</v>
       </c>
-      <c r="AD72" s="6" t="n">
+      <c r="AD72" s="16" t="n">
         <v>39.2</v>
       </c>
-      <c r="AE72" s="6" t="n">
+      <c r="AE72" s="16" t="n">
         <v>39.17</v>
       </c>
-      <c r="AF72" s="6" t="n">
+      <c r="AF72" s="16" t="n">
         <v>34</v>
       </c>
-      <c r="AG72" s="6" t="n">
+      <c r="AG72" s="16" t="n">
         <v>30.6</v>
       </c>
       <c r="AH72" s="6" t="n">
@@ -6815,7 +6845,7 @@
       </c>
       <c r="AI72" s="6" t="inlineStr"/>
       <c r="AJ72" s="6" t="inlineStr"/>
-      <c r="AK72" s="12" t="n"/>
+      <c r="AK72" s="15" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -6826,97 +6856,97 @@
       <c r="B73" s="6" t="n">
         <v>567.25</v>
       </c>
-      <c r="C73" s="6" t="n">
+      <c r="C73" s="16" t="n">
         <v>38.72</v>
       </c>
-      <c r="D73" s="6" t="n">
+      <c r="D73" s="16" t="n">
         <v>40.58</v>
       </c>
-      <c r="E73" s="6" t="n">
+      <c r="E73" s="16" t="n">
         <v>39.1</v>
       </c>
-      <c r="F73" s="6" t="n">
+      <c r="F73" s="16" t="n">
         <v>39.9</v>
       </c>
-      <c r="G73" s="6" t="n">
+      <c r="G73" s="16" t="n">
         <v>39.67</v>
       </c>
-      <c r="H73" s="6" t="n">
+      <c r="H73" s="16" t="n">
         <v>40.1</v>
       </c>
-      <c r="I73" s="6" t="n">
+      <c r="I73" s="16" t="n">
         <v>39.85</v>
       </c>
-      <c r="J73" s="6" t="n">
+      <c r="J73" s="16" t="n">
         <v>39.65</v>
       </c>
-      <c r="K73" s="6" t="n">
+      <c r="K73" s="16" t="n">
         <v>39.85</v>
       </c>
-      <c r="L73" s="6" t="n">
+      <c r="L73" s="16" t="n">
         <v>41.55</v>
       </c>
-      <c r="M73" s="6" t="n">
+      <c r="M73" s="16" t="n">
         <v>39.78</v>
       </c>
-      <c r="N73" s="6" t="n">
+      <c r="N73" s="16" t="n">
         <v>40.37</v>
       </c>
-      <c r="O73" s="6" t="n">
+      <c r="O73" s="16" t="n">
         <v>39.98</v>
       </c>
-      <c r="P73" s="6" t="n">
+      <c r="P73" s="16" t="n">
         <v>40</v>
       </c>
-      <c r="Q73" s="6" t="n">
+      <c r="Q73" s="16" t="n">
         <v>40.37</v>
       </c>
-      <c r="R73" s="6" t="n">
+      <c r="R73" s="16" t="n">
         <v>41.43</v>
       </c>
-      <c r="S73" s="6" t="n">
+      <c r="S73" s="16" t="n">
         <v>41.08</v>
       </c>
-      <c r="T73" s="6" t="n">
+      <c r="T73" s="16" t="n">
         <v>41.43</v>
       </c>
-      <c r="U73" s="6" t="n">
+      <c r="U73" s="16" t="n">
         <v>41.27</v>
       </c>
-      <c r="V73" s="6" t="n">
+      <c r="V73" s="16" t="n">
         <v>41.17</v>
       </c>
-      <c r="W73" s="6" t="n">
+      <c r="W73" s="16" t="n">
         <v>42.6</v>
       </c>
-      <c r="X73" s="6" t="n">
+      <c r="X73" s="16" t="n">
         <v>41.62</v>
       </c>
-      <c r="Y73" s="6" t="n">
+      <c r="Y73" s="16" t="n">
         <v>40.92</v>
       </c>
-      <c r="Z73" s="6" t="n">
+      <c r="Z73" s="16" t="n">
         <v>40.37</v>
       </c>
-      <c r="AA73" s="6" t="n">
+      <c r="AA73" s="16" t="n">
         <v>41.32</v>
       </c>
-      <c r="AB73" s="6" t="n">
+      <c r="AB73" s="16" t="n">
         <v>41.38</v>
       </c>
-      <c r="AC73" s="6" t="n">
+      <c r="AC73" s="16" t="n">
         <v>41.15</v>
       </c>
-      <c r="AD73" s="6" t="n">
+      <c r="AD73" s="16" t="n">
         <v>41.08</v>
       </c>
-      <c r="AE73" s="6" t="n">
+      <c r="AE73" s="16" t="n">
         <v>41.33</v>
       </c>
-      <c r="AF73" s="6" t="n">
+      <c r="AF73" s="16" t="n">
         <v>41.33</v>
       </c>
-      <c r="AG73" s="6" t="n">
+      <c r="AG73" s="16" t="n">
         <v>41.08</v>
       </c>
       <c r="AH73" s="6" t="n">
@@ -6924,7 +6954,7 @@
       </c>
       <c r="AI73" s="6" t="inlineStr"/>
       <c r="AJ73" s="6" t="inlineStr"/>
-      <c r="AK73" s="12" t="n"/>
+      <c r="AK73" s="15" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -6935,97 +6965,97 @@
       <c r="B74" s="6" t="n">
         <v>579.25</v>
       </c>
-      <c r="C74" s="6" t="n">
+      <c r="C74" s="7" t="n">
         <v>79.78</v>
       </c>
-      <c r="D74" s="6" t="n">
+      <c r="D74" s="7" t="n">
         <v>80.72</v>
       </c>
-      <c r="E74" s="6" t="n">
+      <c r="E74" s="7" t="n">
         <v>79.93000000000001</v>
       </c>
-      <c r="F74" s="6" t="n">
+      <c r="F74" s="7" t="n">
         <v>80.12</v>
       </c>
-      <c r="G74" s="6" t="n">
+      <c r="G74" s="7" t="n">
         <v>79.88</v>
       </c>
-      <c r="H74" s="6" t="n">
+      <c r="H74" s="7" t="n">
         <v>79.08</v>
       </c>
-      <c r="I74" s="6" t="n">
+      <c r="I74" s="7" t="n">
         <v>78.75</v>
       </c>
-      <c r="J74" s="6" t="n">
+      <c r="J74" s="7" t="n">
         <v>77.95</v>
       </c>
-      <c r="K74" s="6" t="n">
+      <c r="K74" s="7" t="n">
         <v>80.68000000000001</v>
       </c>
-      <c r="L74" s="6" t="n">
+      <c r="L74" s="7" t="n">
         <v>81.78</v>
       </c>
-      <c r="M74" s="6" t="n">
+      <c r="M74" s="7" t="n">
         <v>79.17</v>
       </c>
-      <c r="N74" s="6" t="n">
+      <c r="N74" s="7" t="n">
         <v>77.7</v>
       </c>
-      <c r="O74" s="6" t="n">
+      <c r="O74" s="7" t="n">
         <v>78.22</v>
       </c>
-      <c r="P74" s="6" t="n">
+      <c r="P74" s="7" t="n">
         <v>78.63</v>
       </c>
-      <c r="Q74" s="6" t="n">
+      <c r="Q74" s="7" t="n">
         <v>80.17</v>
       </c>
-      <c r="R74" s="6" t="n">
+      <c r="R74" s="7" t="n">
         <v>81.37</v>
       </c>
-      <c r="S74" s="6" t="n">
+      <c r="S74" s="7" t="n">
         <v>81.08</v>
       </c>
-      <c r="T74" s="6" t="n">
+      <c r="T74" s="7" t="n">
         <v>80.27</v>
       </c>
-      <c r="U74" s="6" t="n">
+      <c r="U74" s="7" t="n">
         <v>81.02</v>
       </c>
-      <c r="V74" s="6" t="n">
+      <c r="V74" s="7" t="n">
         <v>81.15000000000001</v>
       </c>
-      <c r="W74" s="6" t="n">
+      <c r="W74" s="7" t="n">
         <v>80.2</v>
       </c>
-      <c r="X74" s="6" t="n">
+      <c r="X74" s="7" t="n">
         <v>80.59999999999999</v>
       </c>
-      <c r="Y74" s="6" t="n">
+      <c r="Y74" s="7" t="n">
         <v>78.77</v>
       </c>
-      <c r="Z74" s="6" t="n">
+      <c r="Z74" s="7" t="n">
         <v>82.28</v>
       </c>
-      <c r="AA74" s="6" t="n">
+      <c r="AA74" s="7" t="n">
         <v>81.15000000000001</v>
       </c>
-      <c r="AB74" s="6" t="n">
+      <c r="AB74" s="7" t="n">
         <v>80.33</v>
       </c>
-      <c r="AC74" s="6" t="n">
+      <c r="AC74" s="7" t="n">
         <v>80.15000000000001</v>
       </c>
-      <c r="AD74" s="6" t="n">
+      <c r="AD74" s="7" t="n">
         <v>83</v>
       </c>
-      <c r="AE74" s="6" t="n">
+      <c r="AE74" s="7" t="n">
         <v>79.43000000000001</v>
       </c>
-      <c r="AF74" s="6" t="n">
+      <c r="AF74" s="7" t="n">
         <v>79.03</v>
       </c>
-      <c r="AG74" s="6" t="n">
+      <c r="AG74" s="7" t="n">
         <v>81.13</v>
       </c>
       <c r="AH74" s="6" t="n">
@@ -7033,7 +7063,7 @@
       </c>
       <c r="AI74" s="6" t="inlineStr"/>
       <c r="AJ74" s="6" t="inlineStr"/>
-      <c r="AK74" s="12" t="n"/>
+      <c r="AK74" s="15" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
@@ -7044,97 +7074,97 @@
       <c r="B75" s="6" t="n">
         <v>591.25</v>
       </c>
-      <c r="C75" s="6" t="n">
+      <c r="C75" s="16" t="n">
         <v>32.83</v>
       </c>
-      <c r="D75" s="6" t="n">
+      <c r="D75" s="16" t="n">
         <v>34.15</v>
       </c>
-      <c r="E75" s="6" t="n">
+      <c r="E75" s="16" t="n">
         <v>32.67</v>
       </c>
-      <c r="F75" s="6" t="n">
+      <c r="F75" s="16" t="n">
         <v>32.47</v>
       </c>
-      <c r="G75" s="6" t="n">
+      <c r="G75" s="16" t="n">
         <v>32.32</v>
       </c>
-      <c r="H75" s="6" t="n">
+      <c r="H75" s="16" t="n">
         <v>32.23</v>
       </c>
-      <c r="I75" s="6" t="n">
+      <c r="I75" s="16" t="n">
         <v>32.47</v>
       </c>
-      <c r="J75" s="6" t="n">
+      <c r="J75" s="16" t="n">
         <v>34.17</v>
       </c>
-      <c r="K75" s="6" t="n">
+      <c r="K75" s="16" t="n">
         <v>37.27</v>
       </c>
-      <c r="L75" s="6" t="n">
+      <c r="L75" s="9" t="n">
         <v>45.08</v>
       </c>
-      <c r="M75" s="6" t="n">
+      <c r="M75" s="16" t="n">
         <v>39.83</v>
       </c>
-      <c r="N75" s="6" t="n">
+      <c r="N75" s="16" t="n">
         <v>32.48</v>
       </c>
-      <c r="O75" s="6" t="n">
+      <c r="O75" s="16" t="n">
         <v>32.45</v>
       </c>
-      <c r="P75" s="6" t="n">
+      <c r="P75" s="16" t="n">
         <v>32.08</v>
       </c>
-      <c r="Q75" s="6" t="n">
+      <c r="Q75" s="16" t="n">
         <v>31.9</v>
       </c>
-      <c r="R75" s="6" t="n">
+      <c r="R75" s="16" t="n">
         <v>31.83</v>
       </c>
-      <c r="S75" s="6" t="n">
+      <c r="S75" s="16" t="n">
         <v>32.6</v>
       </c>
-      <c r="T75" s="6" t="n">
+      <c r="T75" s="16" t="n">
         <v>34.5</v>
       </c>
-      <c r="U75" s="6" t="n">
+      <c r="U75" s="16" t="n">
         <v>31.85</v>
       </c>
-      <c r="V75" s="6" t="n">
+      <c r="V75" s="16" t="n">
         <v>32.28</v>
       </c>
-      <c r="W75" s="6" t="n">
+      <c r="W75" s="16" t="n">
         <v>37.38</v>
       </c>
-      <c r="X75" s="6" t="n">
+      <c r="X75" s="9" t="n">
         <v>43.55</v>
       </c>
-      <c r="Y75" s="6" t="n">
+      <c r="Y75" s="16" t="n">
         <v>42.93</v>
       </c>
-      <c r="Z75" s="6" t="n">
+      <c r="Z75" s="9" t="n">
         <v>43.05</v>
       </c>
-      <c r="AA75" s="6" t="n">
+      <c r="AA75" s="9" t="n">
         <v>43.25</v>
       </c>
-      <c r="AB75" s="6" t="n">
+      <c r="AB75" s="9" t="n">
         <v>43.55</v>
       </c>
-      <c r="AC75" s="6" t="n">
+      <c r="AC75" s="16" t="n">
         <v>43</v>
       </c>
-      <c r="AD75" s="6" t="n">
+      <c r="AD75" s="9" t="n">
         <v>43.15</v>
       </c>
-      <c r="AE75" s="6" t="n">
+      <c r="AE75" s="9" t="n">
         <v>43.18</v>
       </c>
-      <c r="AF75" s="6" t="n">
+      <c r="AF75" s="16" t="n">
         <v>39.02</v>
       </c>
-      <c r="AG75" s="6" t="n">
+      <c r="AG75" s="16" t="n">
         <v>32.98</v>
       </c>
       <c r="AH75" s="6" t="n">
@@ -7142,7 +7172,7 @@
       </c>
       <c r="AI75" s="6" t="inlineStr"/>
       <c r="AJ75" s="6" t="inlineStr"/>
-      <c r="AK75" s="12" t="n"/>
+      <c r="AK75" s="15" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -7153,97 +7183,97 @@
       <c r="B76" s="6" t="n">
         <v>603.25</v>
       </c>
-      <c r="C76" s="6" t="n">
+      <c r="C76" s="16" t="n">
         <v>32.45</v>
       </c>
-      <c r="D76" s="6" t="n">
+      <c r="D76" s="16" t="n">
         <v>32.73</v>
       </c>
-      <c r="E76" s="6" t="n">
+      <c r="E76" s="16" t="n">
         <v>32.25</v>
       </c>
-      <c r="F76" s="6" t="n">
+      <c r="F76" s="16" t="n">
         <v>32.4</v>
       </c>
-      <c r="G76" s="6" t="n">
+      <c r="G76" s="16" t="n">
         <v>32.48</v>
       </c>
-      <c r="H76" s="6" t="n">
+      <c r="H76" s="16" t="n">
         <v>32.68</v>
       </c>
-      <c r="I76" s="6" t="n">
+      <c r="I76" s="16" t="n">
         <v>33.48</v>
       </c>
-      <c r="J76" s="6" t="n">
+      <c r="J76" s="16" t="n">
         <v>32.9</v>
       </c>
-      <c r="K76" s="6" t="n">
+      <c r="K76" s="16" t="n">
         <v>39.47</v>
       </c>
-      <c r="L76" s="6" t="n">
+      <c r="L76" s="9" t="n">
         <v>46.07</v>
       </c>
-      <c r="M76" s="6" t="n">
+      <c r="M76" s="16" t="n">
         <v>39.98</v>
       </c>
-      <c r="N76" s="6" t="n">
+      <c r="N76" s="16" t="n">
         <v>32.65</v>
       </c>
-      <c r="O76" s="6" t="n">
+      <c r="O76" s="16" t="n">
         <v>32.73</v>
       </c>
-      <c r="P76" s="6" t="n">
+      <c r="P76" s="16" t="n">
         <v>33.17</v>
       </c>
-      <c r="Q76" s="6" t="n">
+      <c r="Q76" s="16" t="n">
         <v>32.58</v>
       </c>
-      <c r="R76" s="6" t="n">
+      <c r="R76" s="16" t="n">
         <v>32.58</v>
       </c>
-      <c r="S76" s="6" t="n">
+      <c r="S76" s="16" t="n">
         <v>33</v>
       </c>
-      <c r="T76" s="6" t="n">
+      <c r="T76" s="16" t="n">
         <v>33.23</v>
       </c>
-      <c r="U76" s="6" t="n">
+      <c r="U76" s="16" t="n">
         <v>32.78</v>
       </c>
-      <c r="V76" s="6" t="n">
+      <c r="V76" s="16" t="n">
         <v>32.85</v>
       </c>
-      <c r="W76" s="6" t="n">
+      <c r="W76" s="9" t="n">
         <v>44.6</v>
       </c>
-      <c r="X76" s="6" t="n">
+      <c r="X76" s="9" t="n">
         <v>46.48</v>
       </c>
-      <c r="Y76" s="6" t="n">
+      <c r="Y76" s="9" t="n">
         <v>46.78</v>
       </c>
-      <c r="Z76" s="6" t="n">
+      <c r="Z76" s="9" t="n">
         <v>46.05</v>
       </c>
-      <c r="AA76" s="6" t="n">
+      <c r="AA76" s="9" t="n">
         <v>46.18</v>
       </c>
-      <c r="AB76" s="6" t="n">
+      <c r="AB76" s="9" t="n">
         <v>48.7</v>
       </c>
-      <c r="AC76" s="6" t="n">
+      <c r="AC76" s="9" t="n">
         <v>47.2</v>
       </c>
-      <c r="AD76" s="6" t="n">
+      <c r="AD76" s="9" t="n">
         <v>46.2</v>
       </c>
-      <c r="AE76" s="6" t="n">
+      <c r="AE76" s="9" t="n">
         <v>46.93</v>
       </c>
-      <c r="AF76" s="6" t="n">
+      <c r="AF76" s="16" t="n">
         <v>39.97</v>
       </c>
-      <c r="AG76" s="6" t="n">
+      <c r="AG76" s="16" t="n">
         <v>33.45</v>
       </c>
       <c r="AH76" s="6" t="n">
@@ -7251,116 +7281,116 @@
       </c>
       <c r="AI76" s="6" t="inlineStr"/>
       <c r="AJ76" s="6" t="inlineStr"/>
-      <c r="AK76" s="12" t="n"/>
+      <c r="AK76" s="15" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="8" t="inlineStr">
+      <c r="A77" s="10" t="inlineStr">
         <is>
           <t>CANAL SUR - TELEVISION MUN</t>
         </is>
       </c>
-      <c r="B77" s="9" t="n">
+      <c r="B77" s="11" t="n">
         <v>621.25</v>
       </c>
-      <c r="C77" s="9" t="n">
+      <c r="C77" s="12" t="n">
         <v>75.28</v>
       </c>
-      <c r="D77" s="9" t="n">
+      <c r="D77" s="12" t="n">
         <v>75.62</v>
       </c>
-      <c r="E77" s="9" t="n">
+      <c r="E77" s="12" t="n">
         <v>69.09999999999999</v>
       </c>
-      <c r="F77" s="9" t="n">
+      <c r="F77" s="12" t="n">
         <v>70.23</v>
       </c>
-      <c r="G77" s="9" t="n">
+      <c r="G77" s="12" t="n">
         <v>70.78</v>
       </c>
-      <c r="H77" s="9" t="n">
+      <c r="H77" s="12" t="n">
         <v>69.77</v>
       </c>
-      <c r="I77" s="9" t="n">
+      <c r="I77" s="12" t="n">
         <v>70.2</v>
       </c>
-      <c r="J77" s="9" t="n">
+      <c r="J77" s="12" t="n">
         <v>68.48</v>
       </c>
-      <c r="K77" s="9" t="n">
+      <c r="K77" s="12" t="n">
         <v>83.56999999999999</v>
       </c>
-      <c r="L77" s="9" t="n">
+      <c r="L77" s="12" t="n">
         <v>99.27</v>
       </c>
-      <c r="M77" s="9" t="n">
+      <c r="M77" s="12" t="n">
         <v>84.33</v>
       </c>
-      <c r="N77" s="9" t="n">
+      <c r="N77" s="12" t="n">
         <v>69.23</v>
       </c>
-      <c r="O77" s="9" t="n">
+      <c r="O77" s="12" t="n">
         <v>68.53</v>
       </c>
-      <c r="P77" s="9" t="n">
+      <c r="P77" s="12" t="n">
         <v>70.05</v>
       </c>
-      <c r="Q77" s="9" t="n">
+      <c r="Q77" s="12" t="n">
         <v>68.92</v>
       </c>
-      <c r="R77" s="9" t="n">
+      <c r="R77" s="12" t="n">
         <v>71.08</v>
       </c>
-      <c r="S77" s="9" t="n">
+      <c r="S77" s="12" t="n">
         <v>72.17</v>
       </c>
-      <c r="T77" s="9" t="n">
+      <c r="T77" s="12" t="n">
         <v>71.13</v>
       </c>
-      <c r="U77" s="9" t="n">
+      <c r="U77" s="12" t="n">
         <v>72.59999999999999</v>
       </c>
-      <c r="V77" s="9" t="n">
+      <c r="V77" s="12" t="n">
         <v>69.81999999999999</v>
       </c>
-      <c r="W77" s="9" t="n">
+      <c r="W77" s="12" t="n">
         <v>85.8</v>
       </c>
-      <c r="X77" s="9" t="n">
+      <c r="X77" s="12" t="n">
         <v>99.72</v>
       </c>
-      <c r="Y77" s="9" t="n">
+      <c r="Y77" s="12" t="n">
         <v>99.43000000000001</v>
       </c>
-      <c r="Z77" s="9" t="n">
+      <c r="Z77" s="12" t="n">
         <v>99.73</v>
       </c>
-      <c r="AA77" s="9" t="n">
+      <c r="AA77" s="12" t="n">
         <v>99.73</v>
       </c>
-      <c r="AB77" s="9" t="n">
+      <c r="AB77" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="AC77" s="9" t="n">
+      <c r="AC77" s="12" t="n">
         <v>99.05</v>
       </c>
-      <c r="AD77" s="9" t="n">
+      <c r="AD77" s="12" t="n">
         <v>99.48</v>
       </c>
-      <c r="AE77" s="9" t="n">
+      <c r="AE77" s="12" t="n">
         <v>99.78</v>
       </c>
-      <c r="AF77" s="9" t="n">
+      <c r="AF77" s="12" t="n">
         <v>85.68000000000001</v>
       </c>
-      <c r="AG77" s="9" t="n">
+      <c r="AG77" s="12" t="n">
         <v>73.12</v>
       </c>
-      <c r="AH77" s="9" t="n">
+      <c r="AH77" s="11" t="n">
         <v>81.02</v>
       </c>
-      <c r="AI77" s="9" t="inlineStr"/>
-      <c r="AJ77" s="9" t="inlineStr"/>
-      <c r="AK77" s="13" t="n"/>
+      <c r="AI77" s="11" t="inlineStr"/>
+      <c r="AJ77" s="11" t="inlineStr"/>
+      <c r="AK77" s="17" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="33">

--- a/ReportesUnificados/loja_ReporteUnificado.xlsx
+++ b/ReportesUnificados/loja_ReporteUnificado.xlsx
@@ -30,30 +30,12 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDFECE"/>
-        <bgColor rgb="FFCDFECE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFE9F"/>
-        <bgColor rgb="FFFFFE9F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFD9BCB"/>
-        <bgColor rgb="FFFD9BCB"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="17">
@@ -171,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -191,13 +173,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -206,17 +182,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -789,7 +759,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 28/08/2025</t>
+          <t>FECHA PRESENTACIÓN: 27/08/2025</t>
         </is>
       </c>
     </row>
@@ -931,97 +901,97 @@
       <c r="B11" s="6" t="n">
         <v>88.09999999999999</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="6" t="n">
         <v>100.73</v>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="6" t="n">
         <v>100.21</v>
       </c>
-      <c r="E11" s="7" t="n">
+      <c r="E11" s="6" t="n">
         <v>99.67</v>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F11" s="6" t="n">
         <v>98.14</v>
       </c>
-      <c r="G11" s="7" t="n">
+      <c r="G11" s="6" t="n">
         <v>99.37</v>
       </c>
-      <c r="H11" s="7" t="n">
+      <c r="H11" s="6" t="n">
         <v>99.87</v>
       </c>
-      <c r="I11" s="7" t="n">
+      <c r="I11" s="6" t="n">
         <v>99.3</v>
       </c>
-      <c r="J11" s="7" t="n">
+      <c r="J11" s="6" t="n">
         <v>98.27</v>
       </c>
-      <c r="K11" s="7" t="n">
+      <c r="K11" s="6" t="n">
         <v>103.04</v>
       </c>
-      <c r="L11" s="7" t="n">
+      <c r="L11" s="6" t="n">
         <v>104.62</v>
       </c>
-      <c r="M11" s="7" t="n">
+      <c r="M11" s="6" t="n">
         <v>103.65</v>
       </c>
-      <c r="N11" s="7" t="n">
+      <c r="N11" s="6" t="n">
         <v>104.35</v>
       </c>
-      <c r="O11" s="7" t="n">
+      <c r="O11" s="6" t="n">
         <v>99.56999999999999</v>
       </c>
-      <c r="P11" s="7" t="n">
+      <c r="P11" s="6" t="n">
         <v>100.89</v>
       </c>
-      <c r="Q11" s="7" t="n">
+      <c r="Q11" s="6" t="n">
         <v>99.98999999999999</v>
       </c>
-      <c r="R11" s="7" t="n">
+      <c r="R11" s="6" t="n">
         <v>100.87</v>
       </c>
-      <c r="S11" s="7" t="n">
+      <c r="S11" s="6" t="n">
         <v>101.26</v>
       </c>
-      <c r="T11" s="7" t="n">
+      <c r="T11" s="6" t="n">
         <v>99.95999999999999</v>
       </c>
-      <c r="U11" s="7" t="n">
+      <c r="U11" s="6" t="n">
         <v>103.34</v>
       </c>
-      <c r="V11" s="7" t="n">
+      <c r="V11" s="6" t="n">
         <v>100.12</v>
       </c>
-      <c r="W11" s="7" t="n">
+      <c r="W11" s="6" t="n">
         <v>102.4</v>
       </c>
-      <c r="X11" s="7" t="n">
+      <c r="X11" s="6" t="n">
         <v>104.77</v>
       </c>
-      <c r="Y11" s="7" t="n">
+      <c r="Y11" s="6" t="n">
         <v>104.69</v>
       </c>
-      <c r="Z11" s="7" t="n">
+      <c r="Z11" s="6" t="n">
         <v>104.73</v>
       </c>
-      <c r="AA11" s="7" t="n">
+      <c r="AA11" s="6" t="n">
         <v>104.57</v>
       </c>
-      <c r="AB11" s="7" t="n">
+      <c r="AB11" s="6" t="n">
         <v>104.87</v>
       </c>
-      <c r="AC11" s="7" t="n">
+      <c r="AC11" s="6" t="n">
         <v>104.49</v>
       </c>
-      <c r="AD11" s="7" t="n">
+      <c r="AD11" s="6" t="n">
         <v>104.43</v>
       </c>
-      <c r="AE11" s="7" t="n">
+      <c r="AE11" s="6" t="n">
         <v>104.15</v>
       </c>
-      <c r="AF11" s="7" t="n">
+      <c r="AF11" s="6" t="n">
         <v>103.92</v>
       </c>
-      <c r="AG11" s="7" t="n">
+      <c r="AG11" s="6" t="n">
         <v>103.78</v>
       </c>
       <c r="AH11" s="6" t="n">
@@ -1031,7 +1001,7 @@
         <v>261.08</v>
       </c>
       <c r="AJ11" s="6" t="inlineStr"/>
-      <c r="AK11" s="8" t="inlineStr"/>
+      <c r="AK11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1042,97 +1012,97 @@
       <c r="B12" s="6" t="n">
         <v>88.5</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="6" t="n">
         <v>102.64</v>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="6" t="n">
         <v>102.54</v>
       </c>
-      <c r="E12" s="7" t="n">
+      <c r="E12" s="6" t="n">
         <v>100.03</v>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="F12" s="6" t="n">
         <v>98.68000000000001</v>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="G12" s="6" t="n">
         <v>98.81999999999999</v>
       </c>
-      <c r="H12" s="7" t="n">
+      <c r="H12" s="6" t="n">
         <v>99.39</v>
       </c>
-      <c r="I12" s="7" t="n">
+      <c r="I12" s="6" t="n">
         <v>98.18000000000001</v>
       </c>
-      <c r="J12" s="7" t="n">
+      <c r="J12" s="6" t="n">
         <v>98.54000000000001</v>
       </c>
-      <c r="K12" s="7" t="n">
+      <c r="K12" s="6" t="n">
         <v>103.48</v>
       </c>
-      <c r="L12" s="7" t="n">
+      <c r="L12" s="6" t="n">
         <v>106.07</v>
       </c>
-      <c r="M12" s="7" t="n">
+      <c r="M12" s="6" t="n">
         <v>103.61</v>
       </c>
-      <c r="N12" s="7" t="n">
+      <c r="N12" s="6" t="n">
         <v>102.12</v>
       </c>
-      <c r="O12" s="7" t="n">
+      <c r="O12" s="6" t="n">
         <v>98.91</v>
       </c>
-      <c r="P12" s="7" t="n">
+      <c r="P12" s="6" t="n">
         <v>100.43</v>
       </c>
-      <c r="Q12" s="7" t="n">
+      <c r="Q12" s="6" t="n">
         <v>99.17</v>
       </c>
-      <c r="R12" s="7" t="n">
+      <c r="R12" s="6" t="n">
         <v>100.68</v>
       </c>
-      <c r="S12" s="7" t="n">
+      <c r="S12" s="6" t="n">
         <v>100.48</v>
       </c>
-      <c r="T12" s="7" t="n">
+      <c r="T12" s="6" t="n">
         <v>100.5</v>
       </c>
-      <c r="U12" s="7" t="n">
+      <c r="U12" s="6" t="n">
         <v>102.11</v>
       </c>
-      <c r="V12" s="7" t="n">
+      <c r="V12" s="6" t="n">
         <v>99.84</v>
       </c>
-      <c r="W12" s="7" t="n">
+      <c r="W12" s="6" t="n">
         <v>102.52</v>
       </c>
-      <c r="X12" s="7" t="n">
+      <c r="X12" s="6" t="n">
         <v>105.26</v>
       </c>
-      <c r="Y12" s="7" t="n">
+      <c r="Y12" s="6" t="n">
         <v>105.26</v>
       </c>
-      <c r="Z12" s="7" t="n">
+      <c r="Z12" s="6" t="n">
         <v>105.57</v>
       </c>
-      <c r="AA12" s="7" t="n">
+      <c r="AA12" s="6" t="n">
         <v>105.29</v>
       </c>
-      <c r="AB12" s="7" t="n">
+      <c r="AB12" s="6" t="n">
         <v>104.97</v>
       </c>
-      <c r="AC12" s="7" t="n">
+      <c r="AC12" s="6" t="n">
         <v>104.81</v>
       </c>
-      <c r="AD12" s="7" t="n">
+      <c r="AD12" s="6" t="n">
         <v>105.28</v>
       </c>
-      <c r="AE12" s="7" t="n">
+      <c r="AE12" s="6" t="n">
         <v>105.18</v>
       </c>
-      <c r="AF12" s="7" t="n">
+      <c r="AF12" s="6" t="n">
         <v>103.21</v>
       </c>
-      <c r="AG12" s="7" t="n">
+      <c r="AG12" s="6" t="n">
         <v>102.45</v>
       </c>
       <c r="AH12" s="6" t="n">
@@ -1142,7 +1112,7 @@
         <v>400.33</v>
       </c>
       <c r="AJ12" s="6" t="inlineStr"/>
-      <c r="AK12" s="8" t="inlineStr"/>
+      <c r="AK12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1153,97 +1123,97 @@
       <c r="B13" s="6" t="n">
         <v>88.90000000000001</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="6" t="n">
         <v>106.04</v>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="D13" s="6" t="n">
         <v>106.46</v>
       </c>
-      <c r="E13" s="7" t="n">
+      <c r="E13" s="6" t="n">
         <v>105.83</v>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F13" s="6" t="n">
         <v>104.99</v>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="G13" s="6" t="n">
         <v>105.07</v>
       </c>
-      <c r="H13" s="7" t="n">
+      <c r="H13" s="6" t="n">
         <v>106.63</v>
       </c>
-      <c r="I13" s="7" t="n">
+      <c r="I13" s="6" t="n">
         <v>105.73</v>
       </c>
-      <c r="J13" s="7" t="n">
+      <c r="J13" s="6" t="n">
         <v>104.88</v>
       </c>
-      <c r="K13" s="7" t="n">
+      <c r="K13" s="6" t="n">
         <v>108.41</v>
       </c>
-      <c r="L13" s="7" t="n">
+      <c r="L13" s="6" t="n">
         <v>109.61</v>
       </c>
-      <c r="M13" s="7" t="n">
+      <c r="M13" s="6" t="n">
         <v>109.16</v>
       </c>
-      <c r="N13" s="7" t="n">
+      <c r="N13" s="6" t="n">
         <v>109.38</v>
       </c>
-      <c r="O13" s="7" t="n">
+      <c r="O13" s="6" t="n">
         <v>105.76</v>
       </c>
-      <c r="P13" s="7" t="n">
+      <c r="P13" s="6" t="n">
         <v>107.38</v>
       </c>
-      <c r="Q13" s="7" t="n">
+      <c r="Q13" s="6" t="n">
         <v>106.48</v>
       </c>
-      <c r="R13" s="7" t="n">
+      <c r="R13" s="6" t="n">
         <v>107.36</v>
       </c>
-      <c r="S13" s="7" t="n">
+      <c r="S13" s="6" t="n">
         <v>107.12</v>
       </c>
-      <c r="T13" s="7" t="n">
+      <c r="T13" s="6" t="n">
         <v>106.32</v>
       </c>
-      <c r="U13" s="7" t="n">
+      <c r="U13" s="6" t="n">
         <v>108.66</v>
       </c>
-      <c r="V13" s="7" t="n">
+      <c r="V13" s="6" t="n">
         <v>106.53</v>
       </c>
-      <c r="W13" s="7" t="n">
+      <c r="W13" s="6" t="n">
         <v>107.33</v>
       </c>
-      <c r="X13" s="7" t="n">
+      <c r="X13" s="6" t="n">
         <v>109.04</v>
       </c>
-      <c r="Y13" s="7" t="n">
+      <c r="Y13" s="6" t="n">
         <v>109.38</v>
       </c>
-      <c r="Z13" s="7" t="n">
+      <c r="Z13" s="6" t="n">
         <v>109.66</v>
       </c>
-      <c r="AA13" s="7" t="n">
+      <c r="AA13" s="6" t="n">
         <v>109.31</v>
       </c>
-      <c r="AB13" s="7" t="n">
+      <c r="AB13" s="6" t="n">
         <v>109.43</v>
       </c>
-      <c r="AC13" s="7" t="n">
+      <c r="AC13" s="6" t="n">
         <v>106.55</v>
       </c>
-      <c r="AD13" s="7" t="n">
+      <c r="AD13" s="6" t="n">
         <v>103.29</v>
       </c>
-      <c r="AE13" s="7" t="n">
+      <c r="AE13" s="6" t="n">
         <v>103.96</v>
       </c>
-      <c r="AF13" s="7" t="n">
+      <c r="AF13" s="6" t="n">
         <v>103.71</v>
       </c>
-      <c r="AG13" s="7" t="n">
+      <c r="AG13" s="6" t="n">
         <v>104.82</v>
       </c>
       <c r="AH13" s="6" t="n">
@@ -1253,7 +1223,7 @@
         <v>485.39</v>
       </c>
       <c r="AJ13" s="6" t="inlineStr"/>
-      <c r="AK13" s="8" t="inlineStr"/>
+      <c r="AK13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1264,97 +1234,97 @@
       <c r="B14" s="6" t="n">
         <v>89.3</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="6" t="n">
         <v>105.66</v>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D14" s="6" t="n">
         <v>107.57</v>
       </c>
-      <c r="E14" s="7" t="n">
+      <c r="E14" s="6" t="n">
         <v>107.51</v>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="F14" s="6" t="n">
         <v>106.14</v>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="G14" s="6" t="n">
         <v>106.72</v>
       </c>
-      <c r="H14" s="7" t="n">
+      <c r="H14" s="6" t="n">
         <v>108.46</v>
       </c>
-      <c r="I14" s="7" t="n">
+      <c r="I14" s="6" t="n">
         <v>107.72</v>
       </c>
-      <c r="J14" s="7" t="n">
+      <c r="J14" s="6" t="n">
         <v>106.02</v>
       </c>
-      <c r="K14" s="7" t="n">
+      <c r="K14" s="6" t="n">
         <v>110.23</v>
       </c>
-      <c r="L14" s="7" t="n">
+      <c r="L14" s="6" t="n">
         <v>111.67</v>
       </c>
-      <c r="M14" s="7" t="n">
+      <c r="M14" s="6" t="n">
         <v>111.27</v>
       </c>
-      <c r="N14" s="7" t="n">
+      <c r="N14" s="6" t="n">
         <v>111.21</v>
       </c>
-      <c r="O14" s="7" t="n">
+      <c r="O14" s="6" t="n">
         <v>108.06</v>
       </c>
-      <c r="P14" s="7" t="n">
+      <c r="P14" s="6" t="n">
         <v>109.28</v>
       </c>
-      <c r="Q14" s="7" t="n">
+      <c r="Q14" s="6" t="n">
         <v>107.56</v>
       </c>
-      <c r="R14" s="7" t="n">
+      <c r="R14" s="6" t="n">
         <v>109.17</v>
       </c>
-      <c r="S14" s="7" t="n">
+      <c r="S14" s="6" t="n">
         <v>108.37</v>
       </c>
-      <c r="T14" s="7" t="n">
+      <c r="T14" s="6" t="n">
         <v>106.98</v>
       </c>
-      <c r="U14" s="7" t="n">
+      <c r="U14" s="6" t="n">
         <v>110.21</v>
       </c>
-      <c r="V14" s="7" t="n">
+      <c r="V14" s="6" t="n">
         <v>108.43</v>
       </c>
-      <c r="W14" s="7" t="n">
+      <c r="W14" s="6" t="n">
         <v>109.52</v>
       </c>
-      <c r="X14" s="7" t="n">
+      <c r="X14" s="6" t="n">
         <v>111.48</v>
       </c>
-      <c r="Y14" s="7" t="n">
+      <c r="Y14" s="6" t="n">
         <v>111.49</v>
       </c>
-      <c r="Z14" s="7" t="n">
+      <c r="Z14" s="6" t="n">
         <v>111.6</v>
       </c>
-      <c r="AA14" s="7" t="n">
+      <c r="AA14" s="6" t="n">
         <v>111.47</v>
       </c>
-      <c r="AB14" s="7" t="n">
+      <c r="AB14" s="6" t="n">
         <v>111.8</v>
       </c>
-      <c r="AC14" s="7" t="n">
+      <c r="AC14" s="6" t="n">
         <v>111.7</v>
       </c>
-      <c r="AD14" s="7" t="n">
+      <c r="AD14" s="6" t="n">
         <v>111.21</v>
       </c>
-      <c r="AE14" s="7" t="n">
+      <c r="AE14" s="6" t="n">
         <v>111.61</v>
       </c>
-      <c r="AF14" s="7" t="n">
+      <c r="AF14" s="6" t="n">
         <v>111.38</v>
       </c>
-      <c r="AG14" s="7" t="n">
+      <c r="AG14" s="6" t="n">
         <v>111.67</v>
       </c>
       <c r="AH14" s="6" t="n">
@@ -1364,7 +1334,7 @@
         <v>372.17</v>
       </c>
       <c r="AJ14" s="6" t="inlineStr"/>
-      <c r="AK14" s="8" t="inlineStr"/>
+      <c r="AK14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1375,97 +1345,97 @@
       <c r="B15" s="6" t="n">
         <v>89.7</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="6" t="n">
         <v>101.81</v>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="D15" s="6" t="n">
         <v>101.63</v>
       </c>
-      <c r="E15" s="7" t="n">
+      <c r="E15" s="6" t="n">
         <v>101.45</v>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="F15" s="6" t="n">
         <v>100.81</v>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="G15" s="6" t="n">
         <v>100.7</v>
       </c>
-      <c r="H15" s="7" t="n">
+      <c r="H15" s="6" t="n">
         <v>102.51</v>
       </c>
-      <c r="I15" s="7" t="n">
+      <c r="I15" s="6" t="n">
         <v>101.59</v>
       </c>
-      <c r="J15" s="7" t="n">
+      <c r="J15" s="6" t="n">
         <v>100.62</v>
       </c>
-      <c r="K15" s="7" t="n">
+      <c r="K15" s="6" t="n">
         <v>104.52</v>
       </c>
-      <c r="L15" s="7" t="n">
+      <c r="L15" s="6" t="n">
         <v>105.85</v>
       </c>
-      <c r="M15" s="7" t="n">
+      <c r="M15" s="6" t="n">
         <v>104.58</v>
       </c>
-      <c r="N15" s="7" t="n">
+      <c r="N15" s="6" t="n">
         <v>104.78</v>
       </c>
-      <c r="O15" s="7" t="n">
+      <c r="O15" s="6" t="n">
         <v>101.78</v>
       </c>
-      <c r="P15" s="7" t="n">
+      <c r="P15" s="6" t="n">
         <v>102.56</v>
       </c>
-      <c r="Q15" s="7" t="n">
+      <c r="Q15" s="6" t="n">
         <v>101.9</v>
       </c>
-      <c r="R15" s="7" t="n">
+      <c r="R15" s="6" t="n">
         <v>103.48</v>
       </c>
-      <c r="S15" s="7" t="n">
+      <c r="S15" s="6" t="n">
         <v>101.89</v>
       </c>
-      <c r="T15" s="7" t="n">
+      <c r="T15" s="6" t="n">
         <v>101.72</v>
       </c>
-      <c r="U15" s="7" t="n">
+      <c r="U15" s="6" t="n">
         <v>103.71</v>
       </c>
-      <c r="V15" s="7" t="n">
+      <c r="V15" s="6" t="n">
         <v>102.37</v>
       </c>
-      <c r="W15" s="7" t="n">
+      <c r="W15" s="6" t="n">
         <v>103.49</v>
       </c>
-      <c r="X15" s="7" t="n">
+      <c r="X15" s="6" t="n">
         <v>104.3</v>
       </c>
-      <c r="Y15" s="7" t="n">
+      <c r="Y15" s="6" t="n">
         <v>104.96</v>
       </c>
-      <c r="Z15" s="7" t="n">
+      <c r="Z15" s="6" t="n">
         <v>105.19</v>
       </c>
-      <c r="AA15" s="7" t="n">
+      <c r="AA15" s="6" t="n">
         <v>104.56</v>
       </c>
-      <c r="AB15" s="7" t="n">
+      <c r="AB15" s="6" t="n">
         <v>104.47</v>
       </c>
-      <c r="AC15" s="7" t="n">
+      <c r="AC15" s="6" t="n">
         <v>104.6</v>
       </c>
-      <c r="AD15" s="7" t="n">
+      <c r="AD15" s="6" t="n">
         <v>104.82</v>
       </c>
-      <c r="AE15" s="7" t="n">
+      <c r="AE15" s="6" t="n">
         <v>104.94</v>
       </c>
-      <c r="AF15" s="7" t="n">
+      <c r="AF15" s="6" t="n">
         <v>104.81</v>
       </c>
-      <c r="AG15" s="7" t="n">
+      <c r="AG15" s="6" t="n">
         <v>105.46</v>
       </c>
       <c r="AH15" s="6" t="n">
@@ -1475,7 +1445,7 @@
         <v>388.41</v>
       </c>
       <c r="AJ15" s="6" t="inlineStr"/>
-      <c r="AK15" s="8" t="inlineStr"/>
+      <c r="AK15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1486,97 +1456,97 @@
       <c r="B16" s="6" t="n">
         <v>90.09999999999999</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="6" t="n">
         <v>81.18000000000001</v>
       </c>
-      <c r="D16" s="7" t="n">
+      <c r="D16" s="6" t="n">
         <v>81.19</v>
       </c>
-      <c r="E16" s="7" t="n">
+      <c r="E16" s="6" t="n">
         <v>82.01000000000001</v>
       </c>
-      <c r="F16" s="7" t="n">
+      <c r="F16" s="6" t="n">
         <v>81.12</v>
       </c>
-      <c r="G16" s="7" t="n">
+      <c r="G16" s="6" t="n">
         <v>82.13</v>
       </c>
-      <c r="H16" s="7" t="n">
+      <c r="H16" s="6" t="n">
         <v>83.72</v>
       </c>
-      <c r="I16" s="7" t="n">
+      <c r="I16" s="6" t="n">
         <v>83.38</v>
       </c>
-      <c r="J16" s="7" t="n">
+      <c r="J16" s="6" t="n">
         <v>81.62</v>
       </c>
-      <c r="K16" s="7" t="n">
+      <c r="K16" s="6" t="n">
         <v>82.89</v>
       </c>
-      <c r="L16" s="7" t="n">
+      <c r="L16" s="6" t="n">
         <v>84.88</v>
       </c>
-      <c r="M16" s="7" t="n">
+      <c r="M16" s="6" t="n">
         <v>86.56</v>
       </c>
-      <c r="N16" s="7" t="n">
+      <c r="N16" s="6" t="n">
         <v>85.36</v>
       </c>
-      <c r="O16" s="7" t="n">
+      <c r="O16" s="6" t="n">
         <v>83.48</v>
       </c>
-      <c r="P16" s="7" t="n">
+      <c r="P16" s="6" t="n">
         <v>83.94</v>
       </c>
-      <c r="Q16" s="7" t="n">
+      <c r="Q16" s="6" t="n">
         <v>83.54000000000001</v>
       </c>
-      <c r="R16" s="7" t="n">
+      <c r="R16" s="6" t="n">
         <v>84.23</v>
       </c>
-      <c r="S16" s="7" t="n">
+      <c r="S16" s="6" t="n">
         <v>83.56</v>
       </c>
-      <c r="T16" s="7" t="n">
+      <c r="T16" s="6" t="n">
         <v>81.23</v>
       </c>
-      <c r="U16" s="7" t="n">
+      <c r="U16" s="6" t="n">
         <v>83.98999999999999</v>
       </c>
-      <c r="V16" s="7" t="n">
+      <c r="V16" s="6" t="n">
         <v>83.53</v>
       </c>
-      <c r="W16" s="7" t="n">
+      <c r="W16" s="6" t="n">
         <v>84.95</v>
       </c>
-      <c r="X16" s="7" t="n">
+      <c r="X16" s="6" t="n">
         <v>86.98</v>
       </c>
-      <c r="Y16" s="7" t="n">
+      <c r="Y16" s="6" t="n">
         <v>87.2</v>
       </c>
-      <c r="Z16" s="7" t="n">
+      <c r="Z16" s="6" t="n">
         <v>85.37</v>
       </c>
-      <c r="AA16" s="7" t="n">
+      <c r="AA16" s="6" t="n">
         <v>87.22</v>
       </c>
-      <c r="AB16" s="7" t="n">
+      <c r="AB16" s="6" t="n">
         <v>87.34</v>
       </c>
-      <c r="AC16" s="7" t="n">
+      <c r="AC16" s="6" t="n">
         <v>87.25</v>
       </c>
-      <c r="AD16" s="7" t="n">
+      <c r="AD16" s="6" t="n">
         <v>86.56</v>
       </c>
-      <c r="AE16" s="7" t="n">
+      <c r="AE16" s="6" t="n">
         <v>87.37</v>
       </c>
-      <c r="AF16" s="7" t="n">
+      <c r="AF16" s="6" t="n">
         <v>86.66</v>
       </c>
-      <c r="AG16" s="7" t="n">
+      <c r="AG16" s="6" t="n">
         <v>87.37</v>
       </c>
       <c r="AH16" s="6" t="n">
@@ -1586,7 +1556,7 @@
         <v>444.57</v>
       </c>
       <c r="AJ16" s="6" t="inlineStr"/>
-      <c r="AK16" s="8" t="inlineStr"/>
+      <c r="AK16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1597,97 +1567,97 @@
       <c r="B17" s="6" t="n">
         <v>90.5</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="6" t="n">
         <v>86.59</v>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="D17" s="6" t="n">
         <v>86.89</v>
       </c>
-      <c r="E17" s="7" t="n">
+      <c r="E17" s="6" t="n">
         <v>87.52</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="F17" s="6" t="n">
         <v>87.31999999999999</v>
       </c>
-      <c r="G17" s="7" t="n">
+      <c r="G17" s="6" t="n">
         <v>86.2</v>
       </c>
-      <c r="H17" s="7" t="n">
+      <c r="H17" s="6" t="n">
         <v>87.95999999999999</v>
       </c>
-      <c r="I17" s="7" t="n">
+      <c r="I17" s="6" t="n">
         <v>86.48999999999999</v>
       </c>
-      <c r="J17" s="7" t="n">
+      <c r="J17" s="6" t="n">
         <v>85.58</v>
       </c>
-      <c r="K17" s="7" t="n">
+      <c r="K17" s="6" t="n">
         <v>87.87</v>
       </c>
-      <c r="L17" s="7" t="n">
+      <c r="L17" s="6" t="n">
         <v>89.41</v>
       </c>
-      <c r="M17" s="7" t="n">
+      <c r="M17" s="6" t="n">
         <v>88.76000000000001</v>
       </c>
-      <c r="N17" s="7" t="n">
+      <c r="N17" s="6" t="n">
         <v>89.28</v>
       </c>
-      <c r="O17" s="7" t="n">
+      <c r="O17" s="6" t="n">
         <v>86.09</v>
       </c>
-      <c r="P17" s="7" t="n">
+      <c r="P17" s="6" t="n">
         <v>87.20999999999999</v>
       </c>
-      <c r="Q17" s="7" t="n">
+      <c r="Q17" s="6" t="n">
         <v>86.89</v>
       </c>
-      <c r="R17" s="7" t="n">
+      <c r="R17" s="6" t="n">
         <v>87.84999999999999</v>
       </c>
-      <c r="S17" s="7" t="n">
+      <c r="S17" s="6" t="n">
         <v>87.41</v>
       </c>
-      <c r="T17" s="7" t="n">
+      <c r="T17" s="6" t="n">
         <v>87.53</v>
       </c>
-      <c r="U17" s="7" t="n">
+      <c r="U17" s="6" t="n">
         <v>88.09</v>
       </c>
-      <c r="V17" s="7" t="n">
+      <c r="V17" s="6" t="n">
         <v>86.47</v>
       </c>
-      <c r="W17" s="7" t="n">
+      <c r="W17" s="6" t="n">
         <v>88.48999999999999</v>
       </c>
-      <c r="X17" s="7" t="n">
+      <c r="X17" s="6" t="n">
         <v>90.56999999999999</v>
       </c>
-      <c r="Y17" s="7" t="n">
+      <c r="Y17" s="6" t="n">
         <v>89.93000000000001</v>
       </c>
-      <c r="Z17" s="7" t="n">
+      <c r="Z17" s="6" t="n">
         <v>89.88</v>
       </c>
-      <c r="AA17" s="7" t="n">
+      <c r="AA17" s="6" t="n">
         <v>88.79000000000001</v>
       </c>
-      <c r="AB17" s="7" t="n">
+      <c r="AB17" s="6" t="n">
         <v>88.62</v>
       </c>
-      <c r="AC17" s="7" t="n">
+      <c r="AC17" s="6" t="n">
         <v>88.70999999999999</v>
       </c>
-      <c r="AD17" s="7" t="n">
+      <c r="AD17" s="6" t="n">
         <v>88.98999999999999</v>
       </c>
-      <c r="AE17" s="7" t="n">
+      <c r="AE17" s="6" t="n">
         <v>88.67</v>
       </c>
-      <c r="AF17" s="7" t="n">
+      <c r="AF17" s="6" t="n">
         <v>88.98</v>
       </c>
-      <c r="AG17" s="7" t="n">
+      <c r="AG17" s="6" t="n">
         <v>89.48</v>
       </c>
       <c r="AH17" s="6" t="n">
@@ -1697,7 +1667,7 @@
         <v>364.81</v>
       </c>
       <c r="AJ17" s="6" t="inlineStr"/>
-      <c r="AK17" s="8" t="inlineStr"/>
+      <c r="AK17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1708,97 +1678,97 @@
       <c r="B18" s="6" t="n">
         <v>90.90000000000001</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="6" t="n">
         <v>100.28</v>
       </c>
-      <c r="D18" s="7" t="n">
+      <c r="D18" s="6" t="n">
         <v>100.14</v>
       </c>
-      <c r="E18" s="7" t="n">
+      <c r="E18" s="6" t="n">
         <v>101.43</v>
       </c>
-      <c r="F18" s="7" t="n">
+      <c r="F18" s="6" t="n">
         <v>101.02</v>
       </c>
-      <c r="G18" s="7" t="n">
+      <c r="G18" s="6" t="n">
         <v>101.46</v>
       </c>
-      <c r="H18" s="7" t="n">
+      <c r="H18" s="6" t="n">
         <v>102.67</v>
       </c>
-      <c r="I18" s="7" t="n">
+      <c r="I18" s="6" t="n">
         <v>102.67</v>
       </c>
-      <c r="J18" s="7" t="n">
+      <c r="J18" s="6" t="n">
         <v>101.48</v>
       </c>
-      <c r="K18" s="7" t="n">
+      <c r="K18" s="6" t="n">
         <v>103.87</v>
       </c>
-      <c r="L18" s="7" t="n">
+      <c r="L18" s="6" t="n">
         <v>106.03</v>
       </c>
-      <c r="M18" s="7" t="n">
+      <c r="M18" s="6" t="n">
         <v>105.71</v>
       </c>
-      <c r="N18" s="7" t="n">
+      <c r="N18" s="6" t="n">
         <v>105.21</v>
       </c>
-      <c r="O18" s="7" t="n">
+      <c r="O18" s="6" t="n">
         <v>102.61</v>
       </c>
-      <c r="P18" s="7" t="n">
+      <c r="P18" s="6" t="n">
         <v>103.77</v>
       </c>
-      <c r="Q18" s="7" t="n">
+      <c r="Q18" s="6" t="n">
         <v>102.62</v>
       </c>
-      <c r="R18" s="7" t="n">
+      <c r="R18" s="6" t="n">
         <v>103.92</v>
       </c>
-      <c r="S18" s="7" t="n">
+      <c r="S18" s="6" t="n">
         <v>103.29</v>
       </c>
-      <c r="T18" s="7" t="n">
+      <c r="T18" s="6" t="n">
         <v>101.73</v>
       </c>
-      <c r="U18" s="7" t="n">
+      <c r="U18" s="6" t="n">
         <v>103.4</v>
       </c>
-      <c r="V18" s="7" t="n">
+      <c r="V18" s="6" t="n">
         <v>102.62</v>
       </c>
-      <c r="W18" s="7" t="n">
+      <c r="W18" s="6" t="n">
         <v>104.21</v>
       </c>
-      <c r="X18" s="7" t="n">
+      <c r="X18" s="6" t="n">
         <v>105.88</v>
       </c>
-      <c r="Y18" s="7" t="n">
+      <c r="Y18" s="6" t="n">
         <v>106.01</v>
       </c>
-      <c r="Z18" s="7" t="n">
+      <c r="Z18" s="6" t="n">
         <v>106.29</v>
       </c>
-      <c r="AA18" s="7" t="n">
+      <c r="AA18" s="6" t="n">
         <v>106.23</v>
       </c>
-      <c r="AB18" s="7" t="n">
+      <c r="AB18" s="6" t="n">
         <v>106.02</v>
       </c>
-      <c r="AC18" s="7" t="n">
+      <c r="AC18" s="6" t="n">
         <v>106.35</v>
       </c>
-      <c r="AD18" s="7" t="n">
+      <c r="AD18" s="6" t="n">
         <v>106.12</v>
       </c>
-      <c r="AE18" s="7" t="n">
+      <c r="AE18" s="6" t="n">
         <v>105.89</v>
       </c>
-      <c r="AF18" s="7" t="n">
+      <c r="AF18" s="6" t="n">
         <v>106</v>
       </c>
-      <c r="AG18" s="7" t="n">
+      <c r="AG18" s="6" t="n">
         <v>106.29</v>
       </c>
       <c r="AH18" s="6" t="n">
@@ -1808,7 +1778,7 @@
         <v>415.88</v>
       </c>
       <c r="AJ18" s="6" t="inlineStr"/>
-      <c r="AK18" s="8" t="inlineStr"/>
+      <c r="AK18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1819,97 +1789,97 @@
       <c r="B19" s="6" t="n">
         <v>92.09999999999999</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="6" t="n">
         <v>97.68000000000001</v>
       </c>
-      <c r="D19" s="7" t="n">
+      <c r="D19" s="6" t="n">
         <v>100.49</v>
       </c>
-      <c r="E19" s="7" t="n">
+      <c r="E19" s="6" t="n">
         <v>101.6</v>
       </c>
-      <c r="F19" s="7" t="n">
+      <c r="F19" s="6" t="n">
         <v>101.09</v>
       </c>
-      <c r="G19" s="7" t="n">
+      <c r="G19" s="6" t="n">
         <v>102.04</v>
       </c>
-      <c r="H19" s="7" t="n">
+      <c r="H19" s="6" t="n">
         <v>103.13</v>
       </c>
-      <c r="I19" s="7" t="n">
+      <c r="I19" s="6" t="n">
         <v>103.39</v>
       </c>
-      <c r="J19" s="7" t="n">
+      <c r="J19" s="6" t="n">
         <v>101.37</v>
       </c>
-      <c r="K19" s="7" t="n">
+      <c r="K19" s="6" t="n">
         <v>104.29</v>
       </c>
-      <c r="L19" s="7" t="n">
+      <c r="L19" s="6" t="n">
         <v>106.73</v>
       </c>
-      <c r="M19" s="7" t="n">
+      <c r="M19" s="6" t="n">
         <v>105.76</v>
       </c>
-      <c r="N19" s="7" t="n">
+      <c r="N19" s="6" t="n">
         <v>104.57</v>
       </c>
-      <c r="O19" s="7" t="n">
+      <c r="O19" s="6" t="n">
         <v>102.94</v>
       </c>
-      <c r="P19" s="7" t="n">
+      <c r="P19" s="6" t="n">
         <v>103.63</v>
       </c>
-      <c r="Q19" s="7" t="n">
+      <c r="Q19" s="6" t="n">
         <v>102.59</v>
       </c>
-      <c r="R19" s="7" t="n">
+      <c r="R19" s="6" t="n">
         <v>103.54</v>
       </c>
-      <c r="S19" s="7" t="n">
+      <c r="S19" s="6" t="n">
         <v>103.07</v>
       </c>
-      <c r="T19" s="7" t="n">
+      <c r="T19" s="6" t="n">
         <v>102.02</v>
       </c>
-      <c r="U19" s="7" t="n">
+      <c r="U19" s="6" t="n">
         <v>103.72</v>
       </c>
-      <c r="V19" s="7" t="n">
+      <c r="V19" s="6" t="n">
         <v>102.81</v>
       </c>
-      <c r="W19" s="7" t="n">
+      <c r="W19" s="6" t="n">
         <v>104.56</v>
       </c>
-      <c r="X19" s="7" t="n">
+      <c r="X19" s="6" t="n">
         <v>106.92</v>
       </c>
-      <c r="Y19" s="7" t="n">
+      <c r="Y19" s="6" t="n">
         <v>107.14</v>
       </c>
-      <c r="Z19" s="7" t="n">
+      <c r="Z19" s="6" t="n">
         <v>107.26</v>
       </c>
-      <c r="AA19" s="7" t="n">
+      <c r="AA19" s="6" t="n">
         <v>107.2</v>
       </c>
-      <c r="AB19" s="7" t="n">
+      <c r="AB19" s="6" t="n">
         <v>107.29</v>
       </c>
-      <c r="AC19" s="7" t="n">
+      <c r="AC19" s="6" t="n">
         <v>107.32</v>
       </c>
-      <c r="AD19" s="7" t="n">
+      <c r="AD19" s="6" t="n">
         <v>106.9</v>
       </c>
-      <c r="AE19" s="7" t="n">
+      <c r="AE19" s="6" t="n">
         <v>106.57</v>
       </c>
-      <c r="AF19" s="7" t="n">
+      <c r="AF19" s="6" t="n">
         <v>106.03</v>
       </c>
-      <c r="AG19" s="7" t="n">
+      <c r="AG19" s="6" t="n">
         <v>105.72</v>
       </c>
       <c r="AH19" s="6" t="n">
@@ -1919,7 +1889,7 @@
         <v>418.76</v>
       </c>
       <c r="AJ19" s="6" t="inlineStr"/>
-      <c r="AK19" s="8" t="inlineStr"/>
+      <c r="AK19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -1930,97 +1900,97 @@
       <c r="B20" s="6" t="n">
         <v>92.5</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="6" t="n">
         <v>95.48999999999999</v>
       </c>
-      <c r="D20" s="7" t="n">
+      <c r="D20" s="6" t="n">
         <v>95.12</v>
       </c>
-      <c r="E20" s="7" t="n">
+      <c r="E20" s="6" t="n">
         <v>94.48999999999999</v>
       </c>
-      <c r="F20" s="7" t="n">
+      <c r="F20" s="6" t="n">
         <v>94.18000000000001</v>
       </c>
-      <c r="G20" s="7" t="n">
+      <c r="G20" s="6" t="n">
         <v>94.04000000000001</v>
       </c>
-      <c r="H20" s="7" t="n">
+      <c r="H20" s="6" t="n">
         <v>94.16</v>
       </c>
-      <c r="I20" s="7" t="n">
+      <c r="I20" s="6" t="n">
         <v>93.19</v>
       </c>
-      <c r="J20" s="7" t="n">
+      <c r="J20" s="6" t="n">
         <v>94.19</v>
       </c>
-      <c r="K20" s="7" t="n">
+      <c r="K20" s="6" t="n">
         <v>95.20999999999999</v>
       </c>
-      <c r="L20" s="7" t="n">
+      <c r="L20" s="6" t="n">
         <v>96.98</v>
       </c>
-      <c r="M20" s="7" t="n">
+      <c r="M20" s="6" t="n">
         <v>95.88</v>
       </c>
-      <c r="N20" s="7" t="n">
+      <c r="N20" s="6" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="O20" s="7" t="n">
+      <c r="O20" s="6" t="n">
         <v>93.38</v>
       </c>
-      <c r="P20" s="7" t="n">
+      <c r="P20" s="6" t="n">
         <v>92.69</v>
       </c>
-      <c r="Q20" s="7" t="n">
+      <c r="Q20" s="6" t="n">
         <v>93.16</v>
       </c>
-      <c r="R20" s="7" t="n">
+      <c r="R20" s="6" t="n">
         <v>93.67</v>
       </c>
-      <c r="S20" s="7" t="n">
+      <c r="S20" s="6" t="n">
         <v>93.63</v>
       </c>
-      <c r="T20" s="7" t="n">
+      <c r="T20" s="6" t="n">
         <v>94.48</v>
       </c>
-      <c r="U20" s="7" t="n">
+      <c r="U20" s="6" t="n">
         <v>93.19</v>
       </c>
-      <c r="V20" s="7" t="n">
+      <c r="V20" s="6" t="n">
         <v>94.34</v>
       </c>
-      <c r="W20" s="7" t="n">
+      <c r="W20" s="6" t="n">
         <v>96.26000000000001</v>
       </c>
-      <c r="X20" s="7" t="n">
+      <c r="X20" s="6" t="n">
         <v>98.88</v>
       </c>
-      <c r="Y20" s="7" t="n">
+      <c r="Y20" s="6" t="n">
         <v>98.8</v>
       </c>
-      <c r="Z20" s="7" t="n">
+      <c r="Z20" s="6" t="n">
         <v>98.48</v>
       </c>
-      <c r="AA20" s="7" t="n">
+      <c r="AA20" s="6" t="n">
         <v>98.22</v>
       </c>
-      <c r="AB20" s="7" t="n">
+      <c r="AB20" s="6" t="n">
         <v>98.26000000000001</v>
       </c>
-      <c r="AC20" s="7" t="n">
+      <c r="AC20" s="6" t="n">
         <v>98.23</v>
       </c>
-      <c r="AD20" s="7" t="n">
+      <c r="AD20" s="6" t="n">
         <v>98.13</v>
       </c>
-      <c r="AE20" s="7" t="n">
+      <c r="AE20" s="6" t="n">
         <v>98.22</v>
       </c>
-      <c r="AF20" s="7" t="n">
+      <c r="AF20" s="6" t="n">
         <v>96.83</v>
       </c>
-      <c r="AG20" s="7" t="n">
+      <c r="AG20" s="6" t="n">
         <v>94.88</v>
       </c>
       <c r="AH20" s="6" t="n">
@@ -2030,7 +2000,7 @@
         <v>400.73</v>
       </c>
       <c r="AJ20" s="6" t="inlineStr"/>
-      <c r="AK20" s="8" t="inlineStr"/>
+      <c r="AK20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2041,97 +2011,97 @@
       <c r="B21" s="6" t="n">
         <v>93.3</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="6" t="n">
         <v>93.22</v>
       </c>
-      <c r="D21" s="7" t="n">
+      <c r="D21" s="6" t="n">
         <v>93.84</v>
       </c>
-      <c r="E21" s="7" t="n">
+      <c r="E21" s="6" t="n">
         <v>94.18000000000001</v>
       </c>
-      <c r="F21" s="7" t="n">
+      <c r="F21" s="6" t="n">
         <v>93.56999999999999</v>
       </c>
-      <c r="G21" s="7" t="n">
+      <c r="G21" s="6" t="n">
         <v>94.23</v>
       </c>
-      <c r="H21" s="7" t="n">
+      <c r="H21" s="6" t="n">
         <v>94.87</v>
       </c>
-      <c r="I21" s="7" t="n">
+      <c r="I21" s="6" t="n">
         <v>94.42</v>
       </c>
-      <c r="J21" s="7" t="n">
+      <c r="J21" s="6" t="n">
         <v>93.37</v>
       </c>
-      <c r="K21" s="7" t="n">
+      <c r="K21" s="6" t="n">
         <v>97.06999999999999</v>
       </c>
-      <c r="L21" s="7" t="n">
+      <c r="L21" s="6" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="M21" s="7" t="n">
+      <c r="M21" s="6" t="n">
         <v>97.95999999999999</v>
       </c>
-      <c r="N21" s="7" t="n">
+      <c r="N21" s="6" t="n">
         <v>95.68000000000001</v>
       </c>
-      <c r="O21" s="7" t="n">
+      <c r="O21" s="6" t="n">
         <v>94.81</v>
       </c>
-      <c r="P21" s="7" t="n">
+      <c r="P21" s="6" t="n">
         <v>95.19</v>
       </c>
-      <c r="Q21" s="7" t="n">
+      <c r="Q21" s="6" t="n">
         <v>94.36</v>
       </c>
-      <c r="R21" s="7" t="n">
+      <c r="R21" s="6" t="n">
         <v>95.29000000000001</v>
       </c>
-      <c r="S21" s="7" t="n">
+      <c r="S21" s="6" t="n">
         <v>94.77</v>
       </c>
-      <c r="T21" s="7" t="n">
+      <c r="T21" s="6" t="n">
         <v>94.45</v>
       </c>
-      <c r="U21" s="7" t="n">
+      <c r="U21" s="6" t="n">
         <v>95.59</v>
       </c>
-      <c r="V21" s="7" t="n">
+      <c r="V21" s="6" t="n">
         <v>94.97</v>
       </c>
-      <c r="W21" s="7" t="n">
+      <c r="W21" s="6" t="n">
         <v>97.58</v>
       </c>
-      <c r="X21" s="7" t="n">
+      <c r="X21" s="6" t="n">
         <v>100.17</v>
       </c>
-      <c r="Y21" s="7" t="n">
+      <c r="Y21" s="6" t="n">
         <v>100.55</v>
       </c>
-      <c r="Z21" s="7" t="n">
+      <c r="Z21" s="6" t="n">
         <v>100.31</v>
       </c>
-      <c r="AA21" s="7" t="n">
+      <c r="AA21" s="6" t="n">
         <v>99.81999999999999</v>
       </c>
-      <c r="AB21" s="7" t="n">
+      <c r="AB21" s="6" t="n">
         <v>100.36</v>
       </c>
-      <c r="AC21" s="7" t="n">
+      <c r="AC21" s="6" t="n">
         <v>100.22</v>
       </c>
-      <c r="AD21" s="7" t="n">
+      <c r="AD21" s="6" t="n">
         <v>99.83</v>
       </c>
-      <c r="AE21" s="7" t="n">
+      <c r="AE21" s="6" t="n">
         <v>99.89</v>
       </c>
-      <c r="AF21" s="7" t="n">
+      <c r="AF21" s="6" t="n">
         <v>98.43000000000001</v>
       </c>
-      <c r="AG21" s="7" t="n">
+      <c r="AG21" s="6" t="n">
         <v>96.98999999999999</v>
       </c>
       <c r="AH21" s="6" t="n">
@@ -2141,7 +2111,7 @@
         <v>406.58</v>
       </c>
       <c r="AJ21" s="6" t="inlineStr"/>
-      <c r="AK21" s="8" t="inlineStr"/>
+      <c r="AK21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2152,97 +2122,97 @@
       <c r="B22" s="6" t="n">
         <v>93.7</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="6" t="n">
         <v>102.88</v>
       </c>
-      <c r="D22" s="7" t="n">
+      <c r="D22" s="6" t="n">
         <v>103.28</v>
       </c>
-      <c r="E22" s="7" t="n">
+      <c r="E22" s="6" t="n">
         <v>104.64</v>
       </c>
-      <c r="F22" s="7" t="n">
+      <c r="F22" s="6" t="n">
         <v>104.51</v>
       </c>
-      <c r="G22" s="7" t="n">
+      <c r="G22" s="6" t="n">
         <v>104.54</v>
       </c>
-      <c r="H22" s="7" t="n">
+      <c r="H22" s="6" t="n">
         <v>105.73</v>
       </c>
-      <c r="I22" s="7" t="n">
+      <c r="I22" s="6" t="n">
         <v>105.16</v>
       </c>
-      <c r="J22" s="7" t="n">
+      <c r="J22" s="6" t="n">
         <v>104.57</v>
       </c>
-      <c r="K22" s="7" t="n">
+      <c r="K22" s="6" t="n">
         <v>106.33</v>
       </c>
-      <c r="L22" s="7" t="n">
+      <c r="L22" s="6" t="n">
         <v>108.18</v>
       </c>
-      <c r="M22" s="7" t="n">
+      <c r="M22" s="6" t="n">
         <v>107.34</v>
       </c>
-      <c r="N22" s="7" t="n">
+      <c r="N22" s="6" t="n">
         <v>106.42</v>
       </c>
-      <c r="O22" s="7" t="n">
+      <c r="O22" s="6" t="n">
         <v>105.42</v>
       </c>
-      <c r="P22" s="7" t="n">
+      <c r="P22" s="6" t="n">
         <v>105.52</v>
       </c>
-      <c r="Q22" s="7" t="n">
+      <c r="Q22" s="6" t="n">
         <v>105.13</v>
       </c>
-      <c r="R22" s="7" t="n">
+      <c r="R22" s="6" t="n">
         <v>106.53</v>
       </c>
-      <c r="S22" s="7" t="n">
+      <c r="S22" s="6" t="n">
         <v>106.49</v>
       </c>
-      <c r="T22" s="7" t="n">
+      <c r="T22" s="6" t="n">
         <v>105.56</v>
       </c>
-      <c r="U22" s="7" t="n">
+      <c r="U22" s="6" t="n">
         <v>106.56</v>
       </c>
-      <c r="V22" s="7" t="n">
+      <c r="V22" s="6" t="n">
         <v>105.78</v>
       </c>
-      <c r="W22" s="7" t="n">
+      <c r="W22" s="6" t="n">
         <v>100.33</v>
       </c>
-      <c r="X22" s="7" t="n">
+      <c r="X22" s="6" t="n">
         <v>94.88</v>
       </c>
-      <c r="Y22" s="7" t="n">
+      <c r="Y22" s="6" t="n">
         <v>102.51</v>
       </c>
-      <c r="Z22" s="7" t="n">
+      <c r="Z22" s="6" t="n">
         <v>109.74</v>
       </c>
-      <c r="AA22" s="7" t="n">
+      <c r="AA22" s="6" t="n">
         <v>109.78</v>
       </c>
-      <c r="AB22" s="7" t="n">
+      <c r="AB22" s="6" t="n">
         <v>109.71</v>
       </c>
-      <c r="AC22" s="7" t="n">
+      <c r="AC22" s="6" t="n">
         <v>109.88</v>
       </c>
-      <c r="AD22" s="7" t="n">
+      <c r="AD22" s="6" t="n">
         <v>108.75</v>
       </c>
-      <c r="AE22" s="7" t="n">
+      <c r="AE22" s="6" t="n">
         <v>108.75</v>
       </c>
-      <c r="AF22" s="7" t="n">
+      <c r="AF22" s="6" t="n">
         <v>109.07</v>
       </c>
-      <c r="AG22" s="7" t="n">
+      <c r="AG22" s="6" t="n">
         <v>109.51</v>
       </c>
       <c r="AH22" s="6" t="n">
@@ -2252,7 +2222,7 @@
         <v>387.36</v>
       </c>
       <c r="AJ22" s="6" t="inlineStr"/>
-      <c r="AK22" s="8" t="inlineStr"/>
+      <c r="AK22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -2263,97 +2233,97 @@
       <c r="B23" s="6" t="n">
         <v>94.09999999999999</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="6" t="n">
         <v>101.84</v>
       </c>
-      <c r="D23" s="7" t="n">
+      <c r="D23" s="6" t="n">
         <v>102.64</v>
       </c>
-      <c r="E23" s="7" t="n">
+      <c r="E23" s="6" t="n">
         <v>102.76</v>
       </c>
-      <c r="F23" s="7" t="n">
+      <c r="F23" s="6" t="n">
         <v>102.78</v>
       </c>
-      <c r="G23" s="7" t="n">
+      <c r="G23" s="6" t="n">
         <v>102.92</v>
       </c>
-      <c r="H23" s="7" t="n">
+      <c r="H23" s="6" t="n">
         <v>103.32</v>
       </c>
-      <c r="I23" s="7" t="n">
+      <c r="I23" s="6" t="n">
         <v>103.29</v>
       </c>
-      <c r="J23" s="7" t="n">
+      <c r="J23" s="6" t="n">
         <v>102.96</v>
       </c>
-      <c r="K23" s="7" t="n">
+      <c r="K23" s="6" t="n">
         <v>103.86</v>
       </c>
-      <c r="L23" s="7" t="n">
+      <c r="L23" s="6" t="n">
         <v>105.12</v>
       </c>
-      <c r="M23" s="7" t="n">
+      <c r="M23" s="6" t="n">
         <v>104.86</v>
       </c>
-      <c r="N23" s="7" t="n">
+      <c r="N23" s="6" t="n">
         <v>104.06</v>
       </c>
-      <c r="O23" s="7" t="n">
+      <c r="O23" s="6" t="n">
         <v>100.32</v>
       </c>
-      <c r="P23" s="7" t="n">
+      <c r="P23" s="6" t="n">
         <v>100.72</v>
       </c>
-      <c r="Q23" s="7" t="n">
+      <c r="Q23" s="6" t="n">
         <v>100.56</v>
       </c>
-      <c r="R23" s="7" t="n">
+      <c r="R23" s="6" t="n">
         <v>100.99</v>
       </c>
-      <c r="S23" s="7" t="n">
+      <c r="S23" s="6" t="n">
         <v>101.06</v>
       </c>
-      <c r="T23" s="7" t="n">
+      <c r="T23" s="6" t="n">
         <v>100.81</v>
       </c>
-      <c r="U23" s="7" t="n">
+      <c r="U23" s="6" t="n">
         <v>102.33</v>
       </c>
-      <c r="V23" s="7" t="n">
+      <c r="V23" s="6" t="n">
         <v>101.98</v>
       </c>
-      <c r="W23" s="7" t="n">
+      <c r="W23" s="6" t="n">
         <v>103.28</v>
       </c>
-      <c r="X23" s="7" t="n">
+      <c r="X23" s="6" t="n">
         <v>103.92</v>
       </c>
-      <c r="Y23" s="7" t="n">
+      <c r="Y23" s="6" t="n">
         <v>104.17</v>
       </c>
-      <c r="Z23" s="7" t="n">
+      <c r="Z23" s="6" t="n">
         <v>103.63</v>
       </c>
-      <c r="AA23" s="7" t="n">
+      <c r="AA23" s="6" t="n">
         <v>104.24</v>
       </c>
-      <c r="AB23" s="7" t="n">
+      <c r="AB23" s="6" t="n">
         <v>104.07</v>
       </c>
-      <c r="AC23" s="7" t="n">
+      <c r="AC23" s="6" t="n">
         <v>103.92</v>
       </c>
-      <c r="AD23" s="7" t="n">
+      <c r="AD23" s="6" t="n">
         <v>103.71</v>
       </c>
-      <c r="AE23" s="7" t="n">
+      <c r="AE23" s="6" t="n">
         <v>103.58</v>
       </c>
-      <c r="AF23" s="7" t="n">
+      <c r="AF23" s="6" t="n">
         <v>103.91</v>
       </c>
-      <c r="AG23" s="7" t="n">
+      <c r="AG23" s="6" t="n">
         <v>104.5</v>
       </c>
       <c r="AH23" s="6" t="n">
@@ -2363,7 +2333,7 @@
         <v>419.3</v>
       </c>
       <c r="AJ23" s="6" t="inlineStr"/>
-      <c r="AK23" s="8" t="inlineStr"/>
+      <c r="AK23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2374,97 +2344,97 @@
       <c r="B24" s="6" t="n">
         <v>94.5</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="6" t="n">
         <v>101.41</v>
       </c>
-      <c r="D24" s="7" t="n">
+      <c r="D24" s="6" t="n">
         <v>101.64</v>
       </c>
-      <c r="E24" s="7" t="n">
+      <c r="E24" s="6" t="n">
         <v>102.16</v>
       </c>
-      <c r="F24" s="7" t="n">
+      <c r="F24" s="6" t="n">
         <v>102.58</v>
       </c>
-      <c r="G24" s="7" t="n">
+      <c r="G24" s="6" t="n">
         <v>102.74</v>
       </c>
-      <c r="H24" s="7" t="n">
+      <c r="H24" s="6" t="n">
         <v>103.05</v>
       </c>
-      <c r="I24" s="7" t="n">
+      <c r="I24" s="6" t="n">
         <v>103.12</v>
       </c>
-      <c r="J24" s="7" t="n">
+      <c r="J24" s="6" t="n">
         <v>103.12</v>
       </c>
-      <c r="K24" s="7" t="n">
+      <c r="K24" s="6" t="n">
         <v>103.72</v>
       </c>
-      <c r="L24" s="7" t="n">
+      <c r="L24" s="6" t="n">
         <v>106.07</v>
       </c>
-      <c r="M24" s="7" t="n">
+      <c r="M24" s="6" t="n">
         <v>105.31</v>
       </c>
-      <c r="N24" s="7" t="n">
+      <c r="N24" s="6" t="n">
         <v>103.62</v>
       </c>
-      <c r="O24" s="7" t="n">
+      <c r="O24" s="6" t="n">
         <v>102.91</v>
       </c>
-      <c r="P24" s="7" t="n">
+      <c r="P24" s="6" t="n">
         <v>103.32</v>
       </c>
-      <c r="Q24" s="7" t="n">
+      <c r="Q24" s="6" t="n">
         <v>103.08</v>
       </c>
-      <c r="R24" s="7" t="n">
+      <c r="R24" s="6" t="n">
         <v>103.9</v>
       </c>
-      <c r="S24" s="7" t="n">
+      <c r="S24" s="6" t="n">
         <v>103.98</v>
       </c>
-      <c r="T24" s="7" t="n">
+      <c r="T24" s="6" t="n">
         <v>103.54</v>
       </c>
-      <c r="U24" s="7" t="n">
+      <c r="U24" s="6" t="n">
         <v>104.47</v>
       </c>
-      <c r="V24" s="7" t="n">
+      <c r="V24" s="6" t="n">
         <v>104.17</v>
       </c>
-      <c r="W24" s="7" t="n">
+      <c r="W24" s="6" t="n">
         <v>104.95</v>
       </c>
-      <c r="X24" s="7" t="n">
+      <c r="X24" s="6" t="n">
         <v>105.45</v>
       </c>
-      <c r="Y24" s="7" t="n">
+      <c r="Y24" s="6" t="n">
         <v>105.52</v>
       </c>
-      <c r="Z24" s="7" t="n">
+      <c r="Z24" s="6" t="n">
         <v>105.91</v>
       </c>
-      <c r="AA24" s="7" t="n">
+      <c r="AA24" s="6" t="n">
         <v>105.18</v>
       </c>
-      <c r="AB24" s="7" t="n">
+      <c r="AB24" s="6" t="n">
         <v>105.34</v>
       </c>
-      <c r="AC24" s="7" t="n">
+      <c r="AC24" s="6" t="n">
         <v>105.46</v>
       </c>
-      <c r="AD24" s="7" t="n">
+      <c r="AD24" s="6" t="n">
         <v>105.41</v>
       </c>
-      <c r="AE24" s="7" t="n">
+      <c r="AE24" s="6" t="n">
         <v>105.26</v>
       </c>
-      <c r="AF24" s="7" t="n">
+      <c r="AF24" s="6" t="n">
         <v>105.79</v>
       </c>
-      <c r="AG24" s="7" t="n">
+      <c r="AG24" s="6" t="n">
         <v>106.08</v>
       </c>
       <c r="AH24" s="6" t="n">
@@ -2474,7 +2444,7 @@
         <v>408.72</v>
       </c>
       <c r="AJ24" s="6" t="inlineStr"/>
-      <c r="AK24" s="8" t="inlineStr"/>
+      <c r="AK24" s="7" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -2485,97 +2455,97 @@
       <c r="B25" s="6" t="n">
         <v>94.90000000000001</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="6" t="n">
         <v>89.14</v>
       </c>
-      <c r="D25" s="7" t="n">
+      <c r="D25" s="6" t="n">
         <v>88.89</v>
       </c>
-      <c r="E25" s="7" t="n">
+      <c r="E25" s="6" t="n">
         <v>89.68000000000001</v>
       </c>
-      <c r="F25" s="7" t="n">
+      <c r="F25" s="6" t="n">
         <v>89.27</v>
       </c>
-      <c r="G25" s="7" t="n">
+      <c r="G25" s="6" t="n">
         <v>89.5</v>
       </c>
-      <c r="H25" s="7" t="n">
+      <c r="H25" s="6" t="n">
         <v>90.97</v>
       </c>
-      <c r="I25" s="7" t="n">
+      <c r="I25" s="6" t="n">
         <v>89.84</v>
       </c>
-      <c r="J25" s="7" t="n">
+      <c r="J25" s="6" t="n">
         <v>89.01000000000001</v>
       </c>
-      <c r="K25" s="7" t="n">
+      <c r="K25" s="6" t="n">
         <v>92.48</v>
       </c>
-      <c r="L25" s="7" t="n">
+      <c r="L25" s="6" t="n">
         <v>95.73999999999999</v>
       </c>
-      <c r="M25" s="7" t="n">
+      <c r="M25" s="6" t="n">
         <v>93.39</v>
       </c>
-      <c r="N25" s="7" t="n">
+      <c r="N25" s="6" t="n">
         <v>91.67</v>
       </c>
-      <c r="O25" s="7" t="n">
+      <c r="O25" s="6" t="n">
         <v>90.26000000000001</v>
       </c>
-      <c r="P25" s="7" t="n">
+      <c r="P25" s="6" t="n">
         <v>90.45999999999999</v>
       </c>
-      <c r="Q25" s="7" t="n">
+      <c r="Q25" s="6" t="n">
         <v>90.36</v>
       </c>
-      <c r="R25" s="7" t="n">
+      <c r="R25" s="6" t="n">
         <v>91.18000000000001</v>
       </c>
-      <c r="S25" s="7" t="n">
+      <c r="S25" s="6" t="n">
         <v>90.94</v>
       </c>
-      <c r="T25" s="7" t="n">
+      <c r="T25" s="6" t="n">
         <v>90.26000000000001</v>
       </c>
-      <c r="U25" s="7" t="n">
+      <c r="U25" s="6" t="n">
         <v>91.06999999999999</v>
       </c>
-      <c r="V25" s="7" t="n">
+      <c r="V25" s="6" t="n">
         <v>90.27</v>
       </c>
-      <c r="W25" s="7" t="n">
+      <c r="W25" s="6" t="n">
         <v>93.14</v>
       </c>
-      <c r="X25" s="7" t="n">
+      <c r="X25" s="6" t="n">
         <v>95.72</v>
       </c>
-      <c r="Y25" s="7" t="n">
+      <c r="Y25" s="6" t="n">
         <v>95.84</v>
       </c>
-      <c r="Z25" s="7" t="n">
+      <c r="Z25" s="6" t="n">
         <v>95.25</v>
       </c>
-      <c r="AA25" s="7" t="n">
+      <c r="AA25" s="6" t="n">
         <v>94.88</v>
       </c>
-      <c r="AB25" s="7" t="n">
+      <c r="AB25" s="6" t="n">
         <v>94.68000000000001</v>
       </c>
-      <c r="AC25" s="7" t="n">
+      <c r="AC25" s="6" t="n">
         <v>95.34999999999999</v>
       </c>
-      <c r="AD25" s="7" t="n">
+      <c r="AD25" s="6" t="n">
         <v>94.42</v>
       </c>
-      <c r="AE25" s="7" t="n">
+      <c r="AE25" s="6" t="n">
         <v>95.36</v>
       </c>
-      <c r="AF25" s="7" t="n">
+      <c r="AF25" s="6" t="n">
         <v>93.76000000000001</v>
       </c>
-      <c r="AG25" s="7" t="n">
+      <c r="AG25" s="6" t="n">
         <v>92.5</v>
       </c>
       <c r="AH25" s="6" t="n">
@@ -2585,7 +2555,7 @@
         <v>439.51</v>
       </c>
       <c r="AJ25" s="6" t="inlineStr"/>
-      <c r="AK25" s="8" t="inlineStr"/>
+      <c r="AK25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -2596,97 +2566,97 @@
       <c r="B26" s="6" t="n">
         <v>95.3</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="6" t="n">
         <v>103.11</v>
       </c>
-      <c r="D26" s="7" t="n">
+      <c r="D26" s="6" t="n">
         <v>102.57</v>
       </c>
-      <c r="E26" s="7" t="n">
+      <c r="E26" s="6" t="n">
         <v>102.42</v>
       </c>
-      <c r="F26" s="7" t="n">
+      <c r="F26" s="6" t="n">
         <v>102.64</v>
       </c>
-      <c r="G26" s="7" t="n">
+      <c r="G26" s="6" t="n">
         <v>102.87</v>
       </c>
-      <c r="H26" s="7" t="n">
+      <c r="H26" s="6" t="n">
         <v>103.36</v>
       </c>
-      <c r="I26" s="7" t="n">
+      <c r="I26" s="6" t="n">
         <v>102.36</v>
       </c>
-      <c r="J26" s="7" t="n">
+      <c r="J26" s="6" t="n">
         <v>102.6</v>
       </c>
-      <c r="K26" s="7" t="n">
+      <c r="K26" s="6" t="n">
         <v>103.14</v>
       </c>
-      <c r="L26" s="7" t="n">
+      <c r="L26" s="6" t="n">
         <v>103.19</v>
       </c>
-      <c r="M26" s="7" t="n">
+      <c r="M26" s="6" t="n">
         <v>103.63</v>
       </c>
-      <c r="N26" s="7" t="n">
+      <c r="N26" s="6" t="n">
         <v>103.47</v>
       </c>
-      <c r="O26" s="7" t="n">
+      <c r="O26" s="6" t="n">
         <v>103.23</v>
       </c>
-      <c r="P26" s="7" t="n">
+      <c r="P26" s="6" t="n">
         <v>102.84</v>
       </c>
-      <c r="Q26" s="7" t="n">
+      <c r="Q26" s="6" t="n">
         <v>102.82</v>
       </c>
-      <c r="R26" s="7" t="n">
+      <c r="R26" s="6" t="n">
         <v>103.34</v>
       </c>
-      <c r="S26" s="7" t="n">
+      <c r="S26" s="6" t="n">
         <v>103.46</v>
       </c>
-      <c r="T26" s="7" t="n">
+      <c r="T26" s="6" t="n">
         <v>102.74</v>
       </c>
-      <c r="U26" s="7" t="n">
+      <c r="U26" s="6" t="n">
         <v>103.27</v>
       </c>
-      <c r="V26" s="7" t="n">
+      <c r="V26" s="6" t="n">
         <v>103.25</v>
       </c>
-      <c r="W26" s="7" t="n">
+      <c r="W26" s="6" t="n">
         <v>103.32</v>
       </c>
-      <c r="X26" s="7" t="n">
+      <c r="X26" s="6" t="n">
         <v>103.94</v>
       </c>
-      <c r="Y26" s="7" t="n">
+      <c r="Y26" s="6" t="n">
         <v>103.06</v>
       </c>
-      <c r="Z26" s="7" t="n">
+      <c r="Z26" s="6" t="n">
         <v>103.75</v>
       </c>
-      <c r="AA26" s="7" t="n">
+      <c r="AA26" s="6" t="n">
         <v>103.18</v>
       </c>
-      <c r="AB26" s="7" t="n">
+      <c r="AB26" s="6" t="n">
         <v>103.56</v>
       </c>
-      <c r="AC26" s="7" t="n">
+      <c r="AC26" s="6" t="n">
         <v>103.35</v>
       </c>
-      <c r="AD26" s="7" t="n">
+      <c r="AD26" s="6" t="n">
         <v>103.36</v>
       </c>
-      <c r="AE26" s="7" t="n">
+      <c r="AE26" s="6" t="n">
         <v>103.43</v>
       </c>
-      <c r="AF26" s="7" t="n">
+      <c r="AF26" s="6" t="n">
         <v>104.72</v>
       </c>
-      <c r="AG26" s="7" t="n">
+      <c r="AG26" s="6" t="n">
         <v>105.59</v>
       </c>
       <c r="AH26" s="6" t="n">
@@ -2696,7 +2666,7 @@
         <v>412.36</v>
       </c>
       <c r="AJ26" s="6" t="inlineStr"/>
-      <c r="AK26" s="8" t="inlineStr"/>
+      <c r="AK26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2707,97 +2677,97 @@
       <c r="B27" s="6" t="n">
         <v>95.7</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="6" t="n">
         <v>91.16</v>
       </c>
-      <c r="D27" s="7" t="n">
+      <c r="D27" s="6" t="n">
         <v>91.37</v>
       </c>
-      <c r="E27" s="7" t="n">
+      <c r="E27" s="6" t="n">
         <v>92.98999999999999</v>
       </c>
-      <c r="F27" s="7" t="n">
+      <c r="F27" s="6" t="n">
         <v>93.13</v>
       </c>
-      <c r="G27" s="7" t="n">
+      <c r="G27" s="6" t="n">
         <v>93.72</v>
       </c>
-      <c r="H27" s="7" t="n">
+      <c r="H27" s="6" t="n">
         <v>94.86</v>
       </c>
-      <c r="I27" s="7" t="n">
+      <c r="I27" s="6" t="n">
         <v>93.77</v>
       </c>
-      <c r="J27" s="7" t="n">
+      <c r="J27" s="6" t="n">
         <v>93.08</v>
       </c>
-      <c r="K27" s="7" t="n">
+      <c r="K27" s="6" t="n">
         <v>96.44</v>
       </c>
-      <c r="L27" s="7" t="n">
+      <c r="L27" s="6" t="n">
         <v>99.08</v>
       </c>
-      <c r="M27" s="7" t="n">
+      <c r="M27" s="6" t="n">
         <v>97.33</v>
       </c>
-      <c r="N27" s="7" t="n">
+      <c r="N27" s="6" t="n">
         <v>95.83</v>
       </c>
-      <c r="O27" s="7" t="n">
+      <c r="O27" s="6" t="n">
         <v>94.39</v>
       </c>
-      <c r="P27" s="7" t="n">
+      <c r="P27" s="6" t="n">
         <v>94.2</v>
       </c>
-      <c r="Q27" s="7" t="n">
+      <c r="Q27" s="6" t="n">
         <v>93.86</v>
       </c>
-      <c r="R27" s="7" t="n">
+      <c r="R27" s="6" t="n">
         <v>94.94</v>
       </c>
-      <c r="S27" s="7" t="n">
+      <c r="S27" s="6" t="n">
         <v>94.95</v>
       </c>
-      <c r="T27" s="7" t="n">
+      <c r="T27" s="6" t="n">
         <v>93.73999999999999</v>
       </c>
-      <c r="U27" s="7" t="n">
+      <c r="U27" s="6" t="n">
         <v>95.06999999999999</v>
       </c>
-      <c r="V27" s="7" t="n">
+      <c r="V27" s="6" t="n">
         <v>94.11</v>
       </c>
-      <c r="W27" s="7" t="n">
+      <c r="W27" s="6" t="n">
         <v>96.31999999999999</v>
       </c>
-      <c r="X27" s="7" t="n">
+      <c r="X27" s="6" t="n">
         <v>99.06999999999999</v>
       </c>
-      <c r="Y27" s="7" t="n">
+      <c r="Y27" s="6" t="n">
         <v>99.26000000000001</v>
       </c>
-      <c r="Z27" s="7" t="n">
+      <c r="Z27" s="6" t="n">
         <v>99.39</v>
       </c>
-      <c r="AA27" s="7" t="n">
+      <c r="AA27" s="6" t="n">
         <v>99.06999999999999</v>
       </c>
-      <c r="AB27" s="7" t="n">
+      <c r="AB27" s="6" t="n">
         <v>99.31</v>
       </c>
-      <c r="AC27" s="7" t="n">
+      <c r="AC27" s="6" t="n">
         <v>99.2</v>
       </c>
-      <c r="AD27" s="7" t="n">
+      <c r="AD27" s="6" t="n">
         <v>99.47</v>
       </c>
-      <c r="AE27" s="7" t="n">
+      <c r="AE27" s="6" t="n">
         <v>98.97</v>
       </c>
-      <c r="AF27" s="7" t="n">
+      <c r="AF27" s="6" t="n">
         <v>97.64</v>
       </c>
-      <c r="AG27" s="7" t="n">
+      <c r="AG27" s="6" t="n">
         <v>96.20999999999999</v>
       </c>
       <c r="AH27" s="6" t="n">
@@ -2807,7 +2777,7 @@
         <v>398.86</v>
       </c>
       <c r="AJ27" s="6" t="inlineStr"/>
-      <c r="AK27" s="8" t="inlineStr"/>
+      <c r="AK27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -2818,97 +2788,97 @@
       <c r="B28" s="6" t="n">
         <v>96.09999999999999</v>
       </c>
-      <c r="C28" s="9" t="n">
+      <c r="C28" s="6" t="n">
         <v>52.79</v>
       </c>
-      <c r="D28" s="9" t="n">
+      <c r="D28" s="6" t="n">
         <v>53.24</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="6" t="n">
         <v>53.39</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="6" t="n">
         <v>52.91</v>
       </c>
-      <c r="G28" s="9" t="n">
+      <c r="G28" s="6" t="n">
         <v>52.24</v>
       </c>
-      <c r="H28" s="7" t="n">
+      <c r="H28" s="6" t="n">
         <v>54.92</v>
       </c>
-      <c r="I28" s="7" t="n">
+      <c r="I28" s="6" t="n">
         <v>54.52</v>
       </c>
-      <c r="J28" s="9" t="n">
+      <c r="J28" s="6" t="n">
         <v>53.58</v>
       </c>
-      <c r="K28" s="7" t="n">
+      <c r="K28" s="6" t="n">
         <v>54.41</v>
       </c>
-      <c r="L28" s="7" t="n">
+      <c r="L28" s="6" t="n">
         <v>75.14</v>
       </c>
-      <c r="M28" s="7" t="n">
+      <c r="M28" s="6" t="n">
         <v>97.26000000000001</v>
       </c>
-      <c r="N28" s="7" t="n">
+      <c r="N28" s="6" t="n">
         <v>95.93000000000001</v>
       </c>
-      <c r="O28" s="7" t="n">
+      <c r="O28" s="6" t="n">
         <v>95.95</v>
       </c>
-      <c r="P28" s="7" t="n">
+      <c r="P28" s="6" t="n">
         <v>71.93000000000001</v>
       </c>
-      <c r="Q28" s="7" t="n">
+      <c r="Q28" s="6" t="n">
         <v>72.12</v>
       </c>
-      <c r="R28" s="7" t="n">
+      <c r="R28" s="6" t="n">
         <v>84.53</v>
       </c>
-      <c r="S28" s="7" t="n">
+      <c r="S28" s="6" t="n">
         <v>96.76000000000001</v>
       </c>
-      <c r="T28" s="7" t="n">
+      <c r="T28" s="6" t="n">
         <v>96.43000000000001</v>
       </c>
-      <c r="U28" s="7" t="n">
+      <c r="U28" s="6" t="n">
         <v>96.91</v>
       </c>
-      <c r="V28" s="7" t="n">
+      <c r="V28" s="6" t="n">
         <v>97.02</v>
       </c>
-      <c r="W28" s="7" t="n">
+      <c r="W28" s="6" t="n">
         <v>97.68000000000001</v>
       </c>
-      <c r="X28" s="7" t="n">
+      <c r="X28" s="6" t="n">
         <v>98.02</v>
       </c>
-      <c r="Y28" s="7" t="n">
+      <c r="Y28" s="6" t="n">
         <v>97.98999999999999</v>
       </c>
-      <c r="Z28" s="7" t="n">
+      <c r="Z28" s="6" t="n">
         <v>98.39</v>
       </c>
-      <c r="AA28" s="7" t="n">
+      <c r="AA28" s="6" t="n">
         <v>97.87</v>
       </c>
-      <c r="AB28" s="7" t="n">
+      <c r="AB28" s="6" t="n">
         <v>97.86</v>
       </c>
-      <c r="AC28" s="7" t="n">
+      <c r="AC28" s="6" t="n">
         <v>97.76000000000001</v>
       </c>
-      <c r="AD28" s="7" t="n">
+      <c r="AD28" s="6" t="n">
         <v>97.93000000000001</v>
       </c>
-      <c r="AE28" s="7" t="n">
+      <c r="AE28" s="6" t="n">
         <v>98.01000000000001</v>
       </c>
-      <c r="AF28" s="7" t="n">
+      <c r="AF28" s="6" t="n">
         <v>98.28</v>
       </c>
-      <c r="AG28" s="7" t="n">
+      <c r="AG28" s="6" t="n">
         <v>98.55</v>
       </c>
       <c r="AH28" s="6" t="n">
@@ -2918,7 +2888,7 @@
         <v>546.02</v>
       </c>
       <c r="AJ28" s="6" t="inlineStr"/>
-      <c r="AK28" s="8" t="inlineStr"/>
+      <c r="AK28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -2929,97 +2899,97 @@
       <c r="B29" s="6" t="n">
         <v>96.5</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="6" t="n">
         <v>95.69</v>
       </c>
-      <c r="D29" s="7" t="n">
+      <c r="D29" s="6" t="n">
         <v>95.77</v>
       </c>
-      <c r="E29" s="7" t="n">
+      <c r="E29" s="6" t="n">
         <v>96.58</v>
       </c>
-      <c r="F29" s="7" t="n">
+      <c r="F29" s="6" t="n">
         <v>96.54000000000001</v>
       </c>
-      <c r="G29" s="7" t="n">
+      <c r="G29" s="6" t="n">
         <v>96.73</v>
       </c>
-      <c r="H29" s="7" t="n">
+      <c r="H29" s="6" t="n">
         <v>97.01000000000001</v>
       </c>
-      <c r="I29" s="7" t="n">
+      <c r="I29" s="6" t="n">
         <v>96.31</v>
       </c>
-      <c r="J29" s="7" t="n">
+      <c r="J29" s="6" t="n">
         <v>96.36</v>
       </c>
-      <c r="K29" s="7" t="n">
+      <c r="K29" s="6" t="n">
         <v>98.44</v>
       </c>
-      <c r="L29" s="7" t="n">
+      <c r="L29" s="6" t="n">
         <v>101.3</v>
       </c>
-      <c r="M29" s="7" t="n">
+      <c r="M29" s="6" t="n">
         <v>99.37</v>
       </c>
-      <c r="N29" s="7" t="n">
+      <c r="N29" s="6" t="n">
         <v>97.51000000000001</v>
       </c>
-      <c r="O29" s="7" t="n">
+      <c r="O29" s="6" t="n">
         <v>96.90000000000001</v>
       </c>
-      <c r="P29" s="7" t="n">
+      <c r="P29" s="6" t="n">
         <v>97.31999999999999</v>
       </c>
-      <c r="Q29" s="7" t="n">
+      <c r="Q29" s="6" t="n">
         <v>96.98</v>
       </c>
-      <c r="R29" s="7" t="n">
+      <c r="R29" s="6" t="n">
         <v>97.51000000000001</v>
       </c>
-      <c r="S29" s="7" t="n">
+      <c r="S29" s="6" t="n">
         <v>97.73</v>
       </c>
-      <c r="T29" s="7" t="n">
+      <c r="T29" s="6" t="n">
         <v>96.93000000000001</v>
       </c>
-      <c r="U29" s="7" t="n">
+      <c r="U29" s="6" t="n">
         <v>97.73</v>
       </c>
-      <c r="V29" s="7" t="n">
+      <c r="V29" s="6" t="n">
         <v>96.91</v>
       </c>
-      <c r="W29" s="7" t="n">
+      <c r="W29" s="6" t="n">
         <v>98.98999999999999</v>
       </c>
-      <c r="X29" s="7" t="n">
+      <c r="X29" s="6" t="n">
         <v>101.66</v>
       </c>
-      <c r="Y29" s="7" t="n">
+      <c r="Y29" s="6" t="n">
         <v>101.8</v>
       </c>
-      <c r="Z29" s="7" t="n">
+      <c r="Z29" s="6" t="n">
         <v>101.18</v>
       </c>
-      <c r="AA29" s="7" t="n">
+      <c r="AA29" s="6" t="n">
         <v>101.54</v>
       </c>
-      <c r="AB29" s="7" t="n">
+      <c r="AB29" s="6" t="n">
         <v>101.34</v>
       </c>
-      <c r="AC29" s="7" t="n">
+      <c r="AC29" s="6" t="n">
         <v>101.57</v>
       </c>
-      <c r="AD29" s="7" t="n">
+      <c r="AD29" s="6" t="n">
         <v>101.68</v>
       </c>
-      <c r="AE29" s="7" t="n">
+      <c r="AE29" s="6" t="n">
         <v>101.66</v>
       </c>
-      <c r="AF29" s="7" t="n">
+      <c r="AF29" s="6" t="n">
         <v>100.26</v>
       </c>
-      <c r="AG29" s="7" t="n">
+      <c r="AG29" s="6" t="n">
         <v>98.88</v>
       </c>
       <c r="AH29" s="6" t="n">
@@ -3029,7 +2999,7 @@
         <v>391.54</v>
       </c>
       <c r="AJ29" s="6" t="inlineStr"/>
-      <c r="AK29" s="8" t="inlineStr"/>
+      <c r="AK29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -3040,97 +3010,97 @@
       <c r="B30" s="6" t="n">
         <v>96.90000000000001</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="6" t="n">
         <v>106.13</v>
       </c>
-      <c r="D30" s="7" t="n">
+      <c r="D30" s="6" t="n">
         <v>105.07</v>
       </c>
-      <c r="E30" s="7" t="n">
+      <c r="E30" s="6" t="n">
         <v>105.17</v>
       </c>
-      <c r="F30" s="7" t="n">
+      <c r="F30" s="6" t="n">
         <v>104.98</v>
       </c>
-      <c r="G30" s="7" t="n">
+      <c r="G30" s="6" t="n">
         <v>105.09</v>
       </c>
-      <c r="H30" s="7" t="n">
+      <c r="H30" s="6" t="n">
         <v>105.69</v>
       </c>
-      <c r="I30" s="7" t="n">
+      <c r="I30" s="6" t="n">
         <v>105.12</v>
       </c>
-      <c r="J30" s="7" t="n">
+      <c r="J30" s="6" t="n">
         <v>104.79</v>
       </c>
-      <c r="K30" s="7" t="n">
+      <c r="K30" s="6" t="n">
         <v>107.12</v>
       </c>
-      <c r="L30" s="7" t="n">
+      <c r="L30" s="6" t="n">
         <v>108.92</v>
       </c>
-      <c r="M30" s="7" t="n">
+      <c r="M30" s="6" t="n">
         <v>107.68</v>
       </c>
-      <c r="N30" s="7" t="n">
+      <c r="N30" s="6" t="n">
         <v>106.08</v>
       </c>
-      <c r="O30" s="7" t="n">
+      <c r="O30" s="6" t="n">
         <v>105.24</v>
       </c>
-      <c r="P30" s="7" t="n">
+      <c r="P30" s="6" t="n">
         <v>105.14</v>
       </c>
-      <c r="Q30" s="7" t="n">
+      <c r="Q30" s="6" t="n">
         <v>105.33</v>
       </c>
-      <c r="R30" s="7" t="n">
+      <c r="R30" s="6" t="n">
         <v>105.77</v>
       </c>
-      <c r="S30" s="7" t="n">
+      <c r="S30" s="6" t="n">
         <v>105.61</v>
       </c>
-      <c r="T30" s="7" t="n">
+      <c r="T30" s="6" t="n">
         <v>105.26</v>
       </c>
-      <c r="U30" s="7" t="n">
+      <c r="U30" s="6" t="n">
         <v>105.96</v>
       </c>
-      <c r="V30" s="7" t="n">
+      <c r="V30" s="6" t="n">
         <v>105.32</v>
       </c>
-      <c r="W30" s="7" t="n">
+      <c r="W30" s="6" t="n">
         <v>107.3</v>
       </c>
-      <c r="X30" s="7" t="n">
+      <c r="X30" s="6" t="n">
         <v>108.94</v>
       </c>
-      <c r="Y30" s="7" t="n">
+      <c r="Y30" s="6" t="n">
         <v>108.86</v>
       </c>
-      <c r="Z30" s="7" t="n">
+      <c r="Z30" s="6" t="n">
         <v>109.09</v>
       </c>
-      <c r="AA30" s="7" t="n">
+      <c r="AA30" s="6" t="n">
         <v>108.56</v>
       </c>
-      <c r="AB30" s="7" t="n">
+      <c r="AB30" s="6" t="n">
         <v>108.91</v>
       </c>
-      <c r="AC30" s="7" t="n">
+      <c r="AC30" s="6" t="n">
         <v>108.65</v>
       </c>
-      <c r="AD30" s="7" t="n">
+      <c r="AD30" s="6" t="n">
         <v>108.59</v>
       </c>
-      <c r="AE30" s="7" t="n">
+      <c r="AE30" s="6" t="n">
         <v>108.64</v>
       </c>
-      <c r="AF30" s="7" t="n">
+      <c r="AF30" s="6" t="n">
         <v>107.97</v>
       </c>
-      <c r="AG30" s="7" t="n">
+      <c r="AG30" s="6" t="n">
         <v>106.94</v>
       </c>
       <c r="AH30" s="6" t="n">
@@ -3140,7 +3110,7 @@
         <v>476.01</v>
       </c>
       <c r="AJ30" s="6" t="inlineStr"/>
-      <c r="AK30" s="8" t="inlineStr"/>
+      <c r="AK30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -3151,97 +3121,97 @@
       <c r="B31" s="6" t="n">
         <v>97.3</v>
       </c>
-      <c r="C31" s="9" t="n">
+      <c r="C31" s="6" t="n">
         <v>50.96</v>
       </c>
-      <c r="D31" s="9" t="n">
+      <c r="D31" s="6" t="n">
         <v>51.09</v>
       </c>
-      <c r="E31" s="9" t="n">
+      <c r="E31" s="6" t="n">
         <v>51.49</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F31" s="6" t="n">
         <v>51.17</v>
       </c>
-      <c r="G31" s="9" t="n">
+      <c r="G31" s="6" t="n">
         <v>50.6</v>
       </c>
-      <c r="H31" s="9" t="n">
+      <c r="H31" s="6" t="n">
         <v>53.72</v>
       </c>
-      <c r="I31" s="7" t="n">
+      <c r="I31" s="6" t="n">
         <v>54.82</v>
       </c>
-      <c r="J31" s="9" t="n">
+      <c r="J31" s="6" t="n">
         <v>51.84</v>
       </c>
-      <c r="K31" s="9" t="n">
+      <c r="K31" s="6" t="n">
         <v>51.62</v>
       </c>
-      <c r="L31" s="9" t="n">
+      <c r="L31" s="6" t="n">
         <v>50.18</v>
       </c>
-      <c r="M31" s="7" t="n">
+      <c r="M31" s="6" t="n">
         <v>54.43</v>
       </c>
-      <c r="N31" s="7" t="n">
+      <c r="N31" s="6" t="n">
         <v>58.57</v>
       </c>
-      <c r="O31" s="9" t="n">
+      <c r="O31" s="6" t="n">
         <v>53.3</v>
       </c>
-      <c r="P31" s="7" t="n">
+      <c r="P31" s="6" t="n">
         <v>55.63</v>
       </c>
-      <c r="Q31" s="9" t="n">
+      <c r="Q31" s="6" t="n">
         <v>53.83</v>
       </c>
-      <c r="R31" s="7" t="n">
+      <c r="R31" s="6" t="n">
         <v>55.09</v>
       </c>
-      <c r="S31" s="7" t="n">
+      <c r="S31" s="6" t="n">
         <v>55.61</v>
       </c>
-      <c r="T31" s="9" t="n">
+      <c r="T31" s="6" t="n">
         <v>53.61</v>
       </c>
-      <c r="U31" s="7" t="n">
+      <c r="U31" s="6" t="n">
         <v>56.99</v>
       </c>
-      <c r="V31" s="9" t="n">
+      <c r="V31" s="6" t="n">
         <v>53.82</v>
       </c>
-      <c r="W31" s="9" t="n">
+      <c r="W31" s="6" t="n">
         <v>51.9</v>
       </c>
-      <c r="X31" s="9" t="n">
+      <c r="X31" s="6" t="n">
         <v>49.27</v>
       </c>
-      <c r="Y31" s="9" t="n">
+      <c r="Y31" s="6" t="n">
         <v>49.44</v>
       </c>
-      <c r="Z31" s="9" t="n">
+      <c r="Z31" s="6" t="n">
         <v>50.36</v>
       </c>
-      <c r="AA31" s="9" t="n">
+      <c r="AA31" s="6" t="n">
         <v>49.75</v>
       </c>
-      <c r="AB31" s="9" t="n">
+      <c r="AB31" s="6" t="n">
         <v>49.7</v>
       </c>
-      <c r="AC31" s="9" t="n">
+      <c r="AC31" s="6" t="n">
         <v>49.16</v>
       </c>
-      <c r="AD31" s="9" t="n">
+      <c r="AD31" s="6" t="n">
         <v>50.04</v>
       </c>
-      <c r="AE31" s="9" t="n">
+      <c r="AE31" s="6" t="n">
         <v>49.68</v>
       </c>
-      <c r="AF31" s="7" t="n">
+      <c r="AF31" s="6" t="n">
         <v>55.52</v>
       </c>
-      <c r="AG31" s="7" t="n">
+      <c r="AG31" s="6" t="n">
         <v>61.41</v>
       </c>
       <c r="AH31" s="6" t="n">
@@ -3251,7 +3221,7 @@
         <v>703.75</v>
       </c>
       <c r="AJ31" s="6" t="inlineStr"/>
-      <c r="AK31" s="8" t="inlineStr"/>
+      <c r="AK31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -3262,97 +3232,97 @@
       <c r="B32" s="6" t="n">
         <v>97.7</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="6" t="n">
         <v>87.5</v>
       </c>
-      <c r="D32" s="7" t="n">
+      <c r="D32" s="6" t="n">
         <v>86.09</v>
       </c>
-      <c r="E32" s="7" t="n">
+      <c r="E32" s="6" t="n">
         <v>88.16</v>
       </c>
-      <c r="F32" s="7" t="n">
+      <c r="F32" s="6" t="n">
         <v>88.63</v>
       </c>
-      <c r="G32" s="7" t="n">
+      <c r="G32" s="6" t="n">
         <v>88.90000000000001</v>
       </c>
-      <c r="H32" s="7" t="n">
+      <c r="H32" s="6" t="n">
         <v>89.79000000000001</v>
       </c>
-      <c r="I32" s="7" t="n">
+      <c r="I32" s="6" t="n">
         <v>89.31999999999999</v>
       </c>
-      <c r="J32" s="7" t="n">
+      <c r="J32" s="6" t="n">
         <v>88.58</v>
       </c>
-      <c r="K32" s="7" t="n">
+      <c r="K32" s="6" t="n">
         <v>92.53</v>
       </c>
-      <c r="L32" s="7" t="n">
+      <c r="L32" s="6" t="n">
         <v>95.92</v>
       </c>
-      <c r="M32" s="7" t="n">
+      <c r="M32" s="6" t="n">
         <v>93.44</v>
       </c>
-      <c r="N32" s="7" t="n">
+      <c r="N32" s="6" t="n">
         <v>90.87</v>
       </c>
-      <c r="O32" s="7" t="n">
+      <c r="O32" s="6" t="n">
         <v>88.67</v>
       </c>
-      <c r="P32" s="7" t="n">
+      <c r="P32" s="6" t="n">
         <v>89.11</v>
       </c>
-      <c r="Q32" s="7" t="n">
+      <c r="Q32" s="6" t="n">
         <v>88.59</v>
       </c>
-      <c r="R32" s="7" t="n">
+      <c r="R32" s="6" t="n">
         <v>89.87</v>
       </c>
-      <c r="S32" s="7" t="n">
+      <c r="S32" s="6" t="n">
         <v>90.02</v>
       </c>
-      <c r="T32" s="7" t="n">
+      <c r="T32" s="6" t="n">
         <v>87.84</v>
       </c>
-      <c r="U32" s="7" t="n">
+      <c r="U32" s="6" t="n">
         <v>89.95999999999999</v>
       </c>
-      <c r="V32" s="7" t="n">
+      <c r="V32" s="6" t="n">
         <v>88.63</v>
       </c>
-      <c r="W32" s="7" t="n">
+      <c r="W32" s="6" t="n">
         <v>92.45999999999999</v>
       </c>
-      <c r="X32" s="7" t="n">
+      <c r="X32" s="6" t="n">
         <v>96.26000000000001</v>
       </c>
-      <c r="Y32" s="7" t="n">
+      <c r="Y32" s="6" t="n">
         <v>96.79000000000001</v>
       </c>
-      <c r="Z32" s="7" t="n">
+      <c r="Z32" s="6" t="n">
         <v>96.63</v>
       </c>
-      <c r="AA32" s="7" t="n">
+      <c r="AA32" s="6" t="n">
         <v>96.48</v>
       </c>
-      <c r="AB32" s="7" t="n">
+      <c r="AB32" s="6" t="n">
         <v>96.76000000000001</v>
       </c>
-      <c r="AC32" s="7" t="n">
+      <c r="AC32" s="6" t="n">
         <v>96.38</v>
       </c>
-      <c r="AD32" s="7" t="n">
+      <c r="AD32" s="6" t="n">
         <v>96.31</v>
       </c>
-      <c r="AE32" s="7" t="n">
+      <c r="AE32" s="6" t="n">
         <v>96.16</v>
       </c>
-      <c r="AF32" s="7" t="n">
+      <c r="AF32" s="6" t="n">
         <v>93.79000000000001</v>
       </c>
-      <c r="AG32" s="7" t="n">
+      <c r="AG32" s="6" t="n">
         <v>91.77</v>
       </c>
       <c r="AH32" s="6" t="n">
@@ -3362,7 +3332,7 @@
         <v>413.77</v>
       </c>
       <c r="AJ32" s="6" t="inlineStr"/>
-      <c r="AK32" s="8" t="inlineStr"/>
+      <c r="AK32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -3373,97 +3343,97 @@
       <c r="B33" s="6" t="n">
         <v>98.09999999999999</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="6" t="n">
         <v>93</v>
       </c>
-      <c r="D33" s="7" t="n">
+      <c r="D33" s="6" t="n">
         <v>90.98</v>
       </c>
-      <c r="E33" s="7" t="n">
+      <c r="E33" s="6" t="n">
         <v>89.84</v>
       </c>
-      <c r="F33" s="7" t="n">
+      <c r="F33" s="6" t="n">
         <v>91.18000000000001</v>
       </c>
-      <c r="G33" s="7" t="n">
+      <c r="G33" s="6" t="n">
         <v>91.06999999999999</v>
       </c>
-      <c r="H33" s="7" t="n">
+      <c r="H33" s="6" t="n">
         <v>90.76000000000001</v>
       </c>
-      <c r="I33" s="7" t="n">
+      <c r="I33" s="6" t="n">
         <v>90.42</v>
       </c>
-      <c r="J33" s="7" t="n">
+      <c r="J33" s="6" t="n">
         <v>90.91</v>
       </c>
-      <c r="K33" s="7" t="n">
+      <c r="K33" s="6" t="n">
         <v>92.01000000000001</v>
       </c>
-      <c r="L33" s="7" t="n">
+      <c r="L33" s="6" t="n">
         <v>95.33</v>
       </c>
-      <c r="M33" s="7" t="n">
+      <c r="M33" s="6" t="n">
         <v>92.98</v>
       </c>
-      <c r="N33" s="7" t="n">
+      <c r="N33" s="6" t="n">
         <v>90.56</v>
       </c>
-      <c r="O33" s="7" t="n">
+      <c r="O33" s="6" t="n">
         <v>90.81999999999999</v>
       </c>
-      <c r="P33" s="7" t="n">
+      <c r="P33" s="6" t="n">
         <v>90.56</v>
       </c>
-      <c r="Q33" s="7" t="n">
+      <c r="Q33" s="6" t="n">
         <v>91.73</v>
       </c>
-      <c r="R33" s="7" t="n">
+      <c r="R33" s="6" t="n">
         <v>91.59999999999999</v>
       </c>
-      <c r="S33" s="7" t="n">
+      <c r="S33" s="6" t="n">
         <v>91.7</v>
       </c>
-      <c r="T33" s="7" t="n">
+      <c r="T33" s="6" t="n">
         <v>91.56</v>
       </c>
-      <c r="U33" s="7" t="n">
+      <c r="U33" s="6" t="n">
         <v>91.42</v>
       </c>
-      <c r="V33" s="7" t="n">
+      <c r="V33" s="6" t="n">
         <v>91.79000000000001</v>
       </c>
-      <c r="W33" s="7" t="n">
+      <c r="W33" s="6" t="n">
         <v>93.86</v>
       </c>
-      <c r="X33" s="7" t="n">
+      <c r="X33" s="6" t="n">
         <v>95.48</v>
       </c>
-      <c r="Y33" s="7" t="n">
+      <c r="Y33" s="6" t="n">
         <v>95.56</v>
       </c>
-      <c r="Z33" s="7" t="n">
+      <c r="Z33" s="6" t="n">
         <v>95.55</v>
       </c>
-      <c r="AA33" s="7" t="n">
+      <c r="AA33" s="6" t="n">
         <v>95.70999999999999</v>
       </c>
-      <c r="AB33" s="7" t="n">
+      <c r="AB33" s="6" t="n">
         <v>95.95999999999999</v>
       </c>
-      <c r="AC33" s="7" t="n">
+      <c r="AC33" s="6" t="n">
         <v>95.77</v>
       </c>
-      <c r="AD33" s="7" t="n">
+      <c r="AD33" s="6" t="n">
         <v>95.66</v>
       </c>
-      <c r="AE33" s="7" t="n">
+      <c r="AE33" s="6" t="n">
         <v>95.66</v>
       </c>
-      <c r="AF33" s="7" t="n">
+      <c r="AF33" s="6" t="n">
         <v>93.38</v>
       </c>
-      <c r="AG33" s="7" t="n">
+      <c r="AG33" s="6" t="n">
         <v>91.63</v>
       </c>
       <c r="AH33" s="6" t="n">
@@ -3473,7 +3443,7 @@
         <v>438.53</v>
       </c>
       <c r="AJ33" s="6" t="inlineStr"/>
-      <c r="AK33" s="8" t="inlineStr"/>
+      <c r="AK33" s="7" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -3484,97 +3454,97 @@
       <c r="B34" s="6" t="n">
         <v>98.5</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="6" t="n">
         <v>88.67</v>
       </c>
-      <c r="D34" s="7" t="n">
+      <c r="D34" s="6" t="n">
         <v>87.5</v>
       </c>
-      <c r="E34" s="7" t="n">
+      <c r="E34" s="6" t="n">
         <v>87.81999999999999</v>
       </c>
-      <c r="F34" s="7" t="n">
+      <c r="F34" s="6" t="n">
         <v>87.62</v>
       </c>
-      <c r="G34" s="7" t="n">
+      <c r="G34" s="6" t="n">
         <v>87.64</v>
       </c>
-      <c r="H34" s="7" t="n">
+      <c r="H34" s="6" t="n">
         <v>88.52</v>
       </c>
-      <c r="I34" s="7" t="n">
+      <c r="I34" s="6" t="n">
         <v>88.34999999999999</v>
       </c>
-      <c r="J34" s="7" t="n">
+      <c r="J34" s="6" t="n">
         <v>87.61</v>
       </c>
-      <c r="K34" s="7" t="n">
+      <c r="K34" s="6" t="n">
         <v>89.45</v>
       </c>
-      <c r="L34" s="7" t="n">
+      <c r="L34" s="6" t="n">
         <v>90.98</v>
       </c>
-      <c r="M34" s="7" t="n">
+      <c r="M34" s="6" t="n">
         <v>90.31</v>
       </c>
-      <c r="N34" s="7" t="n">
+      <c r="N34" s="6" t="n">
         <v>88.88</v>
       </c>
-      <c r="O34" s="7" t="n">
+      <c r="O34" s="6" t="n">
         <v>88.42</v>
       </c>
-      <c r="P34" s="7" t="n">
+      <c r="P34" s="6" t="n">
         <v>88.13</v>
       </c>
-      <c r="Q34" s="7" t="n">
+      <c r="Q34" s="6" t="n">
         <v>88.22</v>
       </c>
-      <c r="R34" s="7" t="n">
+      <c r="R34" s="6" t="n">
         <v>88.58</v>
       </c>
-      <c r="S34" s="7" t="n">
+      <c r="S34" s="6" t="n">
         <v>88.66</v>
       </c>
-      <c r="T34" s="7" t="n">
+      <c r="T34" s="6" t="n">
         <v>88.23</v>
       </c>
-      <c r="U34" s="7" t="n">
+      <c r="U34" s="6" t="n">
         <v>88.87</v>
       </c>
-      <c r="V34" s="7" t="n">
+      <c r="V34" s="6" t="n">
         <v>88.36</v>
       </c>
-      <c r="W34" s="7" t="n">
+      <c r="W34" s="6" t="n">
         <v>89.94</v>
       </c>
-      <c r="X34" s="7" t="n">
+      <c r="X34" s="6" t="n">
         <v>91.51000000000001</v>
       </c>
-      <c r="Y34" s="7" t="n">
+      <c r="Y34" s="6" t="n">
         <v>91.56999999999999</v>
       </c>
-      <c r="Z34" s="7" t="n">
+      <c r="Z34" s="6" t="n">
         <v>91.45</v>
       </c>
-      <c r="AA34" s="7" t="n">
+      <c r="AA34" s="6" t="n">
         <v>91.41</v>
       </c>
-      <c r="AB34" s="7" t="n">
+      <c r="AB34" s="6" t="n">
         <v>91.34</v>
       </c>
-      <c r="AC34" s="7" t="n">
+      <c r="AC34" s="6" t="n">
         <v>91.48999999999999</v>
       </c>
-      <c r="AD34" s="7" t="n">
+      <c r="AD34" s="6" t="n">
         <v>91.63</v>
       </c>
-      <c r="AE34" s="7" t="n">
+      <c r="AE34" s="6" t="n">
         <v>91.52</v>
       </c>
-      <c r="AF34" s="7" t="n">
+      <c r="AF34" s="6" t="n">
         <v>91.20999999999999</v>
       </c>
-      <c r="AG34" s="7" t="n">
+      <c r="AG34" s="6" t="n">
         <v>90.66</v>
       </c>
       <c r="AH34" s="6" t="n">
@@ -3584,7 +3554,7 @@
         <v>496.73</v>
       </c>
       <c r="AJ34" s="6" t="inlineStr"/>
-      <c r="AK34" s="8" t="inlineStr"/>
+      <c r="AK34" s="7" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -3595,97 +3565,97 @@
       <c r="B35" s="6" t="n">
         <v>98.90000000000001</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="6" t="n">
         <v>96.28</v>
       </c>
-      <c r="D35" s="7" t="n">
+      <c r="D35" s="6" t="n">
         <v>95.2</v>
       </c>
-      <c r="E35" s="7" t="n">
+      <c r="E35" s="6" t="n">
         <v>93.51000000000001</v>
       </c>
-      <c r="F35" s="7" t="n">
+      <c r="F35" s="6" t="n">
         <v>93.5</v>
       </c>
-      <c r="G35" s="7" t="n">
+      <c r="G35" s="6" t="n">
         <v>93.28</v>
       </c>
-      <c r="H35" s="7" t="n">
+      <c r="H35" s="6" t="n">
         <v>94.70999999999999</v>
       </c>
-      <c r="I35" s="7" t="n">
+      <c r="I35" s="6" t="n">
         <v>94.20999999999999</v>
       </c>
-      <c r="J35" s="7" t="n">
+      <c r="J35" s="6" t="n">
         <v>93.73999999999999</v>
       </c>
-      <c r="K35" s="7" t="n">
+      <c r="K35" s="6" t="n">
         <v>97.06</v>
       </c>
-      <c r="L35" s="7" t="n">
+      <c r="L35" s="6" t="n">
         <v>99.94</v>
       </c>
-      <c r="M35" s="7" t="n">
+      <c r="M35" s="6" t="n">
         <v>97.87</v>
       </c>
-      <c r="N35" s="7" t="n">
+      <c r="N35" s="6" t="n">
         <v>95</v>
       </c>
-      <c r="O35" s="7" t="n">
+      <c r="O35" s="6" t="n">
         <v>94.31999999999999</v>
       </c>
-      <c r="P35" s="7" t="n">
+      <c r="P35" s="6" t="n">
         <v>94.08</v>
       </c>
-      <c r="Q35" s="7" t="n">
+      <c r="Q35" s="6" t="n">
         <v>94.43000000000001</v>
       </c>
-      <c r="R35" s="7" t="n">
+      <c r="R35" s="6" t="n">
         <v>94.98</v>
       </c>
-      <c r="S35" s="7" t="n">
+      <c r="S35" s="6" t="n">
         <v>95.19</v>
       </c>
-      <c r="T35" s="7" t="n">
+      <c r="T35" s="6" t="n">
         <v>94.83</v>
       </c>
-      <c r="U35" s="7" t="n">
+      <c r="U35" s="6" t="n">
         <v>95.59</v>
       </c>
-      <c r="V35" s="7" t="n">
+      <c r="V35" s="6" t="n">
         <v>94.31</v>
       </c>
-      <c r="W35" s="7" t="n">
+      <c r="W35" s="6" t="n">
         <v>96.84</v>
       </c>
-      <c r="X35" s="7" t="n">
+      <c r="X35" s="6" t="n">
         <v>99.69</v>
       </c>
-      <c r="Y35" s="7" t="n">
+      <c r="Y35" s="6" t="n">
         <v>99.31999999999999</v>
       </c>
-      <c r="Z35" s="7" t="n">
+      <c r="Z35" s="6" t="n">
         <v>99.48</v>
       </c>
-      <c r="AA35" s="7" t="n">
+      <c r="AA35" s="6" t="n">
         <v>99.34</v>
       </c>
-      <c r="AB35" s="7" t="n">
+      <c r="AB35" s="6" t="n">
         <v>99.56</v>
       </c>
-      <c r="AC35" s="7" t="n">
+      <c r="AC35" s="6" t="n">
         <v>99.34</v>
       </c>
-      <c r="AD35" s="7" t="n">
+      <c r="AD35" s="6" t="n">
         <v>99.19</v>
       </c>
-      <c r="AE35" s="7" t="n">
+      <c r="AE35" s="6" t="n">
         <v>99.31999999999999</v>
       </c>
-      <c r="AF35" s="7" t="n">
+      <c r="AF35" s="6" t="n">
         <v>97.73</v>
       </c>
-      <c r="AG35" s="7" t="n">
+      <c r="AG35" s="6" t="n">
         <v>96.22</v>
       </c>
       <c r="AH35" s="6" t="n">
@@ -3695,7 +3665,7 @@
         <v>387.7</v>
       </c>
       <c r="AJ35" s="6" t="inlineStr"/>
-      <c r="AK35" s="8" t="inlineStr"/>
+      <c r="AK35" s="7" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -3706,97 +3676,97 @@
       <c r="B36" s="6" t="n">
         <v>99.3</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="6" t="n">
         <v>100.73</v>
       </c>
-      <c r="D36" s="7" t="n">
+      <c r="D36" s="6" t="n">
         <v>100.51</v>
       </c>
-      <c r="E36" s="7" t="n">
+      <c r="E36" s="6" t="n">
         <v>100.67</v>
       </c>
-      <c r="F36" s="7" t="n">
+      <c r="F36" s="6" t="n">
         <v>100.09</v>
       </c>
-      <c r="G36" s="7" t="n">
+      <c r="G36" s="6" t="n">
         <v>100.42</v>
       </c>
-      <c r="H36" s="7" t="n">
+      <c r="H36" s="6" t="n">
         <v>101.41</v>
       </c>
-      <c r="I36" s="7" t="n">
+      <c r="I36" s="6" t="n">
         <v>101.02</v>
       </c>
-      <c r="J36" s="7" t="n">
+      <c r="J36" s="6" t="n">
         <v>100.88</v>
       </c>
-      <c r="K36" s="7" t="n">
+      <c r="K36" s="6" t="n">
         <v>101.19</v>
       </c>
-      <c r="L36" s="7" t="n">
+      <c r="L36" s="6" t="n">
         <v>100.89</v>
       </c>
-      <c r="M36" s="7" t="n">
+      <c r="M36" s="6" t="n">
         <v>100.48</v>
       </c>
-      <c r="N36" s="7" t="n">
+      <c r="N36" s="6" t="n">
         <v>101.38</v>
       </c>
-      <c r="O36" s="7" t="n">
+      <c r="O36" s="6" t="n">
         <v>101.37</v>
       </c>
-      <c r="P36" s="7" t="n">
+      <c r="P36" s="6" t="n">
         <v>100.68</v>
       </c>
-      <c r="Q36" s="7" t="n">
+      <c r="Q36" s="6" t="n">
         <v>101.06</v>
       </c>
-      <c r="R36" s="7" t="n">
+      <c r="R36" s="6" t="n">
         <v>100.97</v>
       </c>
-      <c r="S36" s="7" t="n">
+      <c r="S36" s="6" t="n">
         <v>100.17</v>
       </c>
-      <c r="T36" s="7" t="n">
+      <c r="T36" s="6" t="n">
         <v>101.12</v>
       </c>
-      <c r="U36" s="7" t="n">
+      <c r="U36" s="6" t="n">
         <v>101.11</v>
       </c>
-      <c r="V36" s="7" t="n">
+      <c r="V36" s="6" t="n">
         <v>101.01</v>
       </c>
-      <c r="W36" s="7" t="n">
+      <c r="W36" s="6" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="X36" s="7" t="n">
+      <c r="X36" s="6" t="n">
         <v>99.19</v>
       </c>
-      <c r="Y36" s="7" t="n">
+      <c r="Y36" s="6" t="n">
         <v>99.81999999999999</v>
       </c>
-      <c r="Z36" s="7" t="n">
+      <c r="Z36" s="6" t="n">
         <v>100.26</v>
       </c>
-      <c r="AA36" s="7" t="n">
+      <c r="AA36" s="6" t="n">
         <v>99.18000000000001</v>
       </c>
-      <c r="AB36" s="7" t="n">
+      <c r="AB36" s="6" t="n">
         <v>99.89</v>
       </c>
-      <c r="AC36" s="7" t="n">
+      <c r="AC36" s="6" t="n">
         <v>99.97</v>
       </c>
-      <c r="AD36" s="7" t="n">
+      <c r="AD36" s="6" t="n">
         <v>99.77</v>
       </c>
-      <c r="AE36" s="7" t="n">
+      <c r="AE36" s="6" t="n">
         <v>99.69</v>
       </c>
-      <c r="AF36" s="7" t="n">
+      <c r="AF36" s="6" t="n">
         <v>100.54</v>
       </c>
-      <c r="AG36" s="7" t="n">
+      <c r="AG36" s="6" t="n">
         <v>101.43</v>
       </c>
       <c r="AH36" s="6" t="n">
@@ -3806,7 +3776,7 @@
         <v>400.46</v>
       </c>
       <c r="AJ36" s="6" t="inlineStr"/>
-      <c r="AK36" s="8" t="inlineStr"/>
+      <c r="AK36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -3817,97 +3787,97 @@
       <c r="B37" s="6" t="n">
         <v>100.1</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="6" t="n">
         <v>104.58</v>
       </c>
-      <c r="D37" s="7" t="n">
+      <c r="D37" s="6" t="n">
         <v>104.67</v>
       </c>
-      <c r="E37" s="7" t="n">
+      <c r="E37" s="6" t="n">
         <v>103.33</v>
       </c>
-      <c r="F37" s="7" t="n">
+      <c r="F37" s="6" t="n">
         <v>104.4</v>
       </c>
-      <c r="G37" s="7" t="n">
+      <c r="G37" s="6" t="n">
         <v>104.63</v>
       </c>
-      <c r="H37" s="7" t="n">
+      <c r="H37" s="6" t="n">
         <v>105.15</v>
       </c>
-      <c r="I37" s="7" t="n">
+      <c r="I37" s="6" t="n">
         <v>103.98</v>
       </c>
-      <c r="J37" s="7" t="n">
+      <c r="J37" s="6" t="n">
         <v>104.01</v>
       </c>
-      <c r="K37" s="7" t="n">
+      <c r="K37" s="6" t="n">
         <v>103.93</v>
       </c>
-      <c r="L37" s="7" t="n">
+      <c r="L37" s="6" t="n">
         <v>104.06</v>
       </c>
-      <c r="M37" s="7" t="n">
+      <c r="M37" s="6" t="n">
         <v>104.12</v>
       </c>
-      <c r="N37" s="7" t="n">
+      <c r="N37" s="6" t="n">
         <v>104.99</v>
       </c>
-      <c r="O37" s="7" t="n">
+      <c r="O37" s="6" t="n">
         <v>105.4</v>
       </c>
-      <c r="P37" s="7" t="n">
+      <c r="P37" s="6" t="n">
         <v>104.18</v>
       </c>
-      <c r="Q37" s="7" t="n">
+      <c r="Q37" s="6" t="n">
         <v>104.56</v>
       </c>
-      <c r="R37" s="7" t="n">
+      <c r="R37" s="6" t="n">
         <v>104.82</v>
       </c>
-      <c r="S37" s="7" t="n">
+      <c r="S37" s="6" t="n">
         <v>104.64</v>
       </c>
-      <c r="T37" s="7" t="n">
+      <c r="T37" s="6" t="n">
         <v>104.56</v>
       </c>
-      <c r="U37" s="7" t="n">
+      <c r="U37" s="6" t="n">
         <v>105.75</v>
       </c>
-      <c r="V37" s="7" t="n">
+      <c r="V37" s="6" t="n">
         <v>105.66</v>
       </c>
-      <c r="W37" s="7" t="n">
+      <c r="W37" s="6" t="n">
         <v>104.31</v>
       </c>
-      <c r="X37" s="7" t="n">
+      <c r="X37" s="6" t="n">
         <v>103.87</v>
       </c>
-      <c r="Y37" s="7" t="n">
+      <c r="Y37" s="6" t="n">
         <v>103.78</v>
       </c>
-      <c r="Z37" s="7" t="n">
+      <c r="Z37" s="6" t="n">
         <v>103.2</v>
       </c>
-      <c r="AA37" s="7" t="n">
+      <c r="AA37" s="6" t="n">
         <v>103.45</v>
       </c>
-      <c r="AB37" s="7" t="n">
+      <c r="AB37" s="6" t="n">
         <v>104.43</v>
       </c>
-      <c r="AC37" s="7" t="n">
+      <c r="AC37" s="6" t="n">
         <v>104.42</v>
       </c>
-      <c r="AD37" s="7" t="n">
+      <c r="AD37" s="6" t="n">
         <v>103.52</v>
       </c>
-      <c r="AE37" s="7" t="n">
+      <c r="AE37" s="6" t="n">
         <v>103.88</v>
       </c>
-      <c r="AF37" s="7" t="n">
+      <c r="AF37" s="6" t="n">
         <v>104.63</v>
       </c>
-      <c r="AG37" s="7" t="n">
+      <c r="AG37" s="6" t="n">
         <v>105.94</v>
       </c>
       <c r="AH37" s="6" t="n">
@@ -3917,7 +3887,7 @@
         <v>422.94</v>
       </c>
       <c r="AJ37" s="6" t="inlineStr"/>
-      <c r="AK37" s="8" t="inlineStr"/>
+      <c r="AK37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -3928,97 +3898,97 @@
       <c r="B38" s="6" t="n">
         <v>100.5</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="6" t="n">
         <v>85.64</v>
       </c>
-      <c r="D38" s="7" t="n">
+      <c r="D38" s="6" t="n">
         <v>89.26000000000001</v>
       </c>
-      <c r="E38" s="7" t="n">
+      <c r="E38" s="6" t="n">
         <v>84.69</v>
       </c>
-      <c r="F38" s="7" t="n">
+      <c r="F38" s="6" t="n">
         <v>85.5</v>
       </c>
-      <c r="G38" s="7" t="n">
+      <c r="G38" s="6" t="n">
         <v>85.12</v>
       </c>
-      <c r="H38" s="7" t="n">
+      <c r="H38" s="6" t="n">
         <v>85.45999999999999</v>
       </c>
-      <c r="I38" s="7" t="n">
+      <c r="I38" s="6" t="n">
         <v>86.08</v>
       </c>
-      <c r="J38" s="7" t="n">
+      <c r="J38" s="6" t="n">
         <v>84.76000000000001</v>
       </c>
-      <c r="K38" s="7" t="n">
+      <c r="K38" s="6" t="n">
         <v>87.98</v>
       </c>
-      <c r="L38" s="7" t="n">
+      <c r="L38" s="6" t="n">
         <v>91.37</v>
       </c>
-      <c r="M38" s="7" t="n">
+      <c r="M38" s="6" t="n">
         <v>87.83</v>
       </c>
-      <c r="N38" s="7" t="n">
+      <c r="N38" s="6" t="n">
         <v>84.98</v>
       </c>
-      <c r="O38" s="7" t="n">
+      <c r="O38" s="6" t="n">
         <v>84.48999999999999</v>
       </c>
-      <c r="P38" s="7" t="n">
+      <c r="P38" s="6" t="n">
         <v>86.59</v>
       </c>
-      <c r="Q38" s="7" t="n">
+      <c r="Q38" s="6" t="n">
         <v>87.42</v>
       </c>
-      <c r="R38" s="7" t="n">
+      <c r="R38" s="6" t="n">
         <v>87.05</v>
       </c>
-      <c r="S38" s="7" t="n">
+      <c r="S38" s="6" t="n">
         <v>87.66</v>
       </c>
-      <c r="T38" s="7" t="n">
+      <c r="T38" s="6" t="n">
         <v>88.83</v>
       </c>
-      <c r="U38" s="7" t="n">
+      <c r="U38" s="6" t="n">
         <v>87.95999999999999</v>
       </c>
-      <c r="V38" s="7" t="n">
+      <c r="V38" s="6" t="n">
         <v>88.23</v>
       </c>
-      <c r="W38" s="7" t="n">
+      <c r="W38" s="6" t="n">
         <v>89.31</v>
       </c>
-      <c r="X38" s="7" t="n">
+      <c r="X38" s="6" t="n">
         <v>91.02</v>
       </c>
-      <c r="Y38" s="7" t="n">
+      <c r="Y38" s="6" t="n">
         <v>91.7</v>
       </c>
-      <c r="Z38" s="7" t="n">
+      <c r="Z38" s="6" t="n">
         <v>93.03</v>
       </c>
-      <c r="AA38" s="7" t="n">
+      <c r="AA38" s="6" t="n">
         <v>91.01000000000001</v>
       </c>
-      <c r="AB38" s="7" t="n">
+      <c r="AB38" s="6" t="n">
         <v>90.93000000000001</v>
       </c>
-      <c r="AC38" s="7" t="n">
+      <c r="AC38" s="6" t="n">
         <v>91.25</v>
       </c>
-      <c r="AD38" s="7" t="n">
+      <c r="AD38" s="6" t="n">
         <v>91.53</v>
       </c>
-      <c r="AE38" s="7" t="n">
+      <c r="AE38" s="6" t="n">
         <v>90.98999999999999</v>
       </c>
-      <c r="AF38" s="7" t="n">
+      <c r="AF38" s="6" t="n">
         <v>89.48999999999999</v>
       </c>
-      <c r="AG38" s="7" t="n">
+      <c r="AG38" s="6" t="n">
         <v>88.09</v>
       </c>
       <c r="AH38" s="6" t="n">
@@ -4028,7 +3998,7 @@
         <v>419.65</v>
       </c>
       <c r="AJ38" s="6" t="inlineStr"/>
-      <c r="AK38" s="8" t="inlineStr"/>
+      <c r="AK38" s="7" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -4039,97 +4009,97 @@
       <c r="B39" s="6" t="n">
         <v>100.9</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="6" t="n">
         <v>98.81999999999999</v>
       </c>
-      <c r="D39" s="7" t="n">
+      <c r="D39" s="6" t="n">
         <v>101.34</v>
       </c>
-      <c r="E39" s="7" t="n">
+      <c r="E39" s="6" t="n">
         <v>97.12</v>
       </c>
-      <c r="F39" s="7" t="n">
+      <c r="F39" s="6" t="n">
         <v>97.89</v>
       </c>
-      <c r="G39" s="7" t="n">
+      <c r="G39" s="6" t="n">
         <v>97.7</v>
       </c>
-      <c r="H39" s="7" t="n">
+      <c r="H39" s="6" t="n">
         <v>98.11</v>
       </c>
-      <c r="I39" s="7" t="n">
+      <c r="I39" s="6" t="n">
         <v>98.68000000000001</v>
       </c>
-      <c r="J39" s="7" t="n">
+      <c r="J39" s="6" t="n">
         <v>97.28</v>
       </c>
-      <c r="K39" s="7" t="n">
+      <c r="K39" s="6" t="n">
         <v>101.19</v>
       </c>
-      <c r="L39" s="7" t="n">
+      <c r="L39" s="6" t="n">
         <v>103.54</v>
       </c>
-      <c r="M39" s="7" t="n">
+      <c r="M39" s="6" t="n">
         <v>101.93</v>
       </c>
-      <c r="N39" s="7" t="n">
+      <c r="N39" s="6" t="n">
         <v>98.64</v>
       </c>
-      <c r="O39" s="7" t="n">
+      <c r="O39" s="6" t="n">
         <v>98.05</v>
       </c>
-      <c r="P39" s="7" t="n">
+      <c r="P39" s="6" t="n">
         <v>98.52</v>
       </c>
-      <c r="Q39" s="7" t="n">
+      <c r="Q39" s="6" t="n">
         <v>98.81999999999999</v>
       </c>
-      <c r="R39" s="7" t="n">
+      <c r="R39" s="6" t="n">
         <v>98.98</v>
       </c>
-      <c r="S39" s="7" t="n">
+      <c r="S39" s="6" t="n">
         <v>99.04000000000001</v>
       </c>
-      <c r="T39" s="7" t="n">
+      <c r="T39" s="6" t="n">
         <v>99.51000000000001</v>
       </c>
-      <c r="U39" s="7" t="n">
+      <c r="U39" s="6" t="n">
         <v>100.46</v>
       </c>
-      <c r="V39" s="7" t="n">
+      <c r="V39" s="6" t="n">
         <v>99.43000000000001</v>
       </c>
-      <c r="W39" s="7" t="n">
+      <c r="W39" s="6" t="n">
         <v>100.68</v>
       </c>
-      <c r="X39" s="7" t="n">
+      <c r="X39" s="6" t="n">
         <v>103.7</v>
       </c>
-      <c r="Y39" s="7" t="n">
+      <c r="Y39" s="6" t="n">
         <v>104.14</v>
       </c>
-      <c r="Z39" s="7" t="n">
+      <c r="Z39" s="6" t="n">
         <v>104.82</v>
       </c>
-      <c r="AA39" s="7" t="n">
+      <c r="AA39" s="6" t="n">
         <v>104.1</v>
       </c>
-      <c r="AB39" s="7" t="n">
+      <c r="AB39" s="6" t="n">
         <v>103.98</v>
       </c>
-      <c r="AC39" s="7" t="n">
+      <c r="AC39" s="6" t="n">
         <v>104.17</v>
       </c>
-      <c r="AD39" s="7" t="n">
+      <c r="AD39" s="6" t="n">
         <v>103.9</v>
       </c>
-      <c r="AE39" s="7" t="n">
+      <c r="AE39" s="6" t="n">
         <v>104.06</v>
       </c>
-      <c r="AF39" s="7" t="n">
+      <c r="AF39" s="6" t="n">
         <v>101.71</v>
       </c>
-      <c r="AG39" s="7" t="n">
+      <c r="AG39" s="6" t="n">
         <v>100.18</v>
       </c>
       <c r="AH39" s="6" t="n">
@@ -4139,7 +4109,7 @@
         <v>399.91</v>
       </c>
       <c r="AJ39" s="6" t="inlineStr"/>
-      <c r="AK39" s="8" t="inlineStr"/>
+      <c r="AK39" s="7" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -4150,97 +4120,97 @@
       <c r="B40" s="6" t="n">
         <v>101.3</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="6" t="n">
         <v>98.51000000000001</v>
       </c>
-      <c r="D40" s="7" t="n">
+      <c r="D40" s="6" t="n">
         <v>100.48</v>
       </c>
-      <c r="E40" s="7" t="n">
+      <c r="E40" s="6" t="n">
         <v>98.58</v>
       </c>
-      <c r="F40" s="7" t="n">
+      <c r="F40" s="6" t="n">
         <v>99.27</v>
       </c>
-      <c r="G40" s="7" t="n">
+      <c r="G40" s="6" t="n">
         <v>98.88</v>
       </c>
-      <c r="H40" s="7" t="n">
+      <c r="H40" s="6" t="n">
         <v>99.08</v>
       </c>
-      <c r="I40" s="7" t="n">
+      <c r="I40" s="6" t="n">
         <v>99.51000000000001</v>
       </c>
-      <c r="J40" s="7" t="n">
+      <c r="J40" s="6" t="n">
         <v>99.31</v>
       </c>
-      <c r="K40" s="7" t="n">
+      <c r="K40" s="6" t="n">
         <v>100.52</v>
       </c>
-      <c r="L40" s="7" t="n">
+      <c r="L40" s="6" t="n">
         <v>102.21</v>
       </c>
-      <c r="M40" s="7" t="n">
+      <c r="M40" s="6" t="n">
         <v>101.19</v>
       </c>
-      <c r="N40" s="7" t="n">
+      <c r="N40" s="6" t="n">
         <v>99.40000000000001</v>
       </c>
-      <c r="O40" s="7" t="n">
+      <c r="O40" s="6" t="n">
         <v>99.41</v>
       </c>
-      <c r="P40" s="7" t="n">
+      <c r="P40" s="6" t="n">
         <v>99.53</v>
       </c>
-      <c r="Q40" s="7" t="n">
+      <c r="Q40" s="6" t="n">
         <v>99.78</v>
       </c>
-      <c r="R40" s="7" t="n">
+      <c r="R40" s="6" t="n">
         <v>99.94</v>
       </c>
-      <c r="S40" s="7" t="n">
+      <c r="S40" s="6" t="n">
         <v>99.69</v>
       </c>
-      <c r="T40" s="7" t="n">
+      <c r="T40" s="6" t="n">
         <v>100.28</v>
       </c>
-      <c r="U40" s="7" t="n">
+      <c r="U40" s="6" t="n">
         <v>100.74</v>
       </c>
-      <c r="V40" s="7" t="n">
+      <c r="V40" s="6" t="n">
         <v>99.73</v>
       </c>
-      <c r="W40" s="7" t="n">
+      <c r="W40" s="6" t="n">
         <v>100.94</v>
       </c>
-      <c r="X40" s="7" t="n">
+      <c r="X40" s="6" t="n">
         <v>102</v>
       </c>
-      <c r="Y40" s="7" t="n">
+      <c r="Y40" s="6" t="n">
         <v>101.42</v>
       </c>
-      <c r="Z40" s="7" t="n">
+      <c r="Z40" s="6" t="n">
         <v>101.85</v>
       </c>
-      <c r="AA40" s="7" t="n">
+      <c r="AA40" s="6" t="n">
         <v>101.92</v>
       </c>
-      <c r="AB40" s="7" t="n">
+      <c r="AB40" s="6" t="n">
         <v>101.72</v>
       </c>
-      <c r="AC40" s="7" t="n">
+      <c r="AC40" s="6" t="n">
         <v>101.67</v>
       </c>
-      <c r="AD40" s="7" t="n">
+      <c r="AD40" s="6" t="n">
         <v>102.04</v>
       </c>
-      <c r="AE40" s="7" t="n">
+      <c r="AE40" s="6" t="n">
         <v>101.97</v>
       </c>
-      <c r="AF40" s="7" t="n">
+      <c r="AF40" s="6" t="n">
         <v>101.61</v>
       </c>
-      <c r="AG40" s="7" t="n">
+      <c r="AG40" s="6" t="n">
         <v>100.71</v>
       </c>
       <c r="AH40" s="6" t="n">
@@ -4250,7 +4220,7 @@
         <v>407.04</v>
       </c>
       <c r="AJ40" s="6" t="inlineStr"/>
-      <c r="AK40" s="8" t="inlineStr"/>
+      <c r="AK40" s="7" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -4261,97 +4231,97 @@
       <c r="B41" s="6" t="n">
         <v>102.1</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="6" t="n">
         <v>102.57</v>
       </c>
-      <c r="D41" s="7" t="n">
+      <c r="D41" s="6" t="n">
         <v>105.03</v>
       </c>
-      <c r="E41" s="7" t="n">
+      <c r="E41" s="6" t="n">
         <v>103.34</v>
       </c>
-      <c r="F41" s="7" t="n">
+      <c r="F41" s="6" t="n">
         <v>103.44</v>
       </c>
-      <c r="G41" s="7" t="n">
+      <c r="G41" s="6" t="n">
         <v>103.11</v>
       </c>
-      <c r="H41" s="7" t="n">
+      <c r="H41" s="6" t="n">
         <v>103.53</v>
       </c>
-      <c r="I41" s="7" t="n">
+      <c r="I41" s="6" t="n">
         <v>103.46</v>
       </c>
-      <c r="J41" s="7" t="n">
+      <c r="J41" s="6" t="n">
         <v>103.53</v>
       </c>
-      <c r="K41" s="7" t="n">
+      <c r="K41" s="6" t="n">
         <v>106.06</v>
       </c>
-      <c r="L41" s="7" t="n">
+      <c r="L41" s="6" t="n">
         <v>108.66</v>
       </c>
-      <c r="M41" s="7" t="n">
+      <c r="M41" s="6" t="n">
         <v>106.24</v>
       </c>
-      <c r="N41" s="7" t="n">
+      <c r="N41" s="6" t="n">
         <v>103.67</v>
       </c>
-      <c r="O41" s="7" t="n">
+      <c r="O41" s="6" t="n">
         <v>104.14</v>
       </c>
-      <c r="P41" s="7" t="n">
+      <c r="P41" s="6" t="n">
         <v>103.64</v>
       </c>
-      <c r="Q41" s="7" t="n">
+      <c r="Q41" s="6" t="n">
         <v>103.54</v>
       </c>
-      <c r="R41" s="7" t="n">
+      <c r="R41" s="6" t="n">
         <v>103.82</v>
       </c>
-      <c r="S41" s="7" t="n">
+      <c r="S41" s="6" t="n">
         <v>103.42</v>
       </c>
-      <c r="T41" s="7" t="n">
+      <c r="T41" s="6" t="n">
         <v>104.5</v>
       </c>
-      <c r="U41" s="7" t="n">
+      <c r="U41" s="6" t="n">
         <v>104.66</v>
       </c>
-      <c r="V41" s="7" t="n">
+      <c r="V41" s="6" t="n">
         <v>104.32</v>
       </c>
-      <c r="W41" s="7" t="n">
+      <c r="W41" s="6" t="n">
         <v>105.61</v>
       </c>
-      <c r="X41" s="7" t="n">
+      <c r="X41" s="6" t="n">
         <v>107.35</v>
       </c>
-      <c r="Y41" s="7" t="n">
+      <c r="Y41" s="6" t="n">
         <v>107.55</v>
       </c>
-      <c r="Z41" s="7" t="n">
+      <c r="Z41" s="6" t="n">
         <v>108.24</v>
       </c>
-      <c r="AA41" s="7" t="n">
+      <c r="AA41" s="6" t="n">
         <v>107.6</v>
       </c>
-      <c r="AB41" s="7" t="n">
+      <c r="AB41" s="6" t="n">
         <v>107.67</v>
       </c>
-      <c r="AC41" s="7" t="n">
+      <c r="AC41" s="6" t="n">
         <v>108.09</v>
       </c>
-      <c r="AD41" s="7" t="n">
+      <c r="AD41" s="6" t="n">
         <v>108.48</v>
       </c>
-      <c r="AE41" s="7" t="n">
+      <c r="AE41" s="6" t="n">
         <v>107.73</v>
       </c>
-      <c r="AF41" s="7" t="n">
+      <c r="AF41" s="6" t="n">
         <v>106.29</v>
       </c>
-      <c r="AG41" s="7" t="n">
+      <c r="AG41" s="6" t="n">
         <v>103.92</v>
       </c>
       <c r="AH41" s="6" t="n">
@@ -4361,7 +4331,7 @@
         <v>316.68</v>
       </c>
       <c r="AJ41" s="6" t="inlineStr"/>
-      <c r="AK41" s="8" t="inlineStr"/>
+      <c r="AK41" s="7" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -4372,97 +4342,97 @@
       <c r="B42" s="6" t="n">
         <v>103.7</v>
       </c>
-      <c r="C42" s="9" t="n">
+      <c r="C42" s="6" t="n">
         <v>50.32</v>
       </c>
-      <c r="D42" s="9" t="n">
+      <c r="D42" s="6" t="n">
         <v>50.59</v>
       </c>
-      <c r="E42" s="9" t="n">
+      <c r="E42" s="6" t="n">
         <v>51.34</v>
       </c>
-      <c r="F42" s="9" t="n">
+      <c r="F42" s="6" t="n">
         <v>51.32</v>
       </c>
-      <c r="G42" s="9" t="n">
+      <c r="G42" s="6" t="n">
         <v>50.85</v>
       </c>
-      <c r="H42" s="9" t="n">
+      <c r="H42" s="6" t="n">
         <v>52.08</v>
       </c>
-      <c r="I42" s="9" t="n">
+      <c r="I42" s="6" t="n">
         <v>53.42</v>
       </c>
-      <c r="J42" s="9" t="n">
+      <c r="J42" s="6" t="n">
         <v>51.71</v>
       </c>
-      <c r="K42" s="9" t="n">
+      <c r="K42" s="6" t="n">
         <v>52.18</v>
       </c>
-      <c r="L42" s="9" t="n">
+      <c r="L42" s="6" t="n">
         <v>50.53</v>
       </c>
-      <c r="M42" s="9" t="n">
+      <c r="M42" s="6" t="n">
         <v>53.58</v>
       </c>
-      <c r="N42" s="7" t="n">
+      <c r="N42" s="6" t="n">
         <v>56.22</v>
       </c>
-      <c r="O42" s="9" t="n">
+      <c r="O42" s="6" t="n">
         <v>52.72</v>
       </c>
-      <c r="P42" s="7" t="n">
+      <c r="P42" s="6" t="n">
         <v>54.54</v>
       </c>
-      <c r="Q42" s="9" t="n">
+      <c r="Q42" s="6" t="n">
         <v>52.73</v>
       </c>
-      <c r="R42" s="7" t="n">
+      <c r="R42" s="6" t="n">
         <v>54.53</v>
       </c>
-      <c r="S42" s="7" t="n">
+      <c r="S42" s="6" t="n">
         <v>54.02</v>
       </c>
-      <c r="T42" s="9" t="n">
+      <c r="T42" s="6" t="n">
         <v>52.69</v>
       </c>
-      <c r="U42" s="7" t="n">
+      <c r="U42" s="6" t="n">
         <v>55.21</v>
       </c>
-      <c r="V42" s="9" t="n">
+      <c r="V42" s="6" t="n">
         <v>53.4</v>
       </c>
-      <c r="W42" s="9" t="n">
+      <c r="W42" s="6" t="n">
         <v>51.93</v>
       </c>
-      <c r="X42" s="9" t="n">
+      <c r="X42" s="6" t="n">
         <v>50.58</v>
       </c>
-      <c r="Y42" s="9" t="n">
+      <c r="Y42" s="6" t="n">
         <v>50.59</v>
       </c>
-      <c r="Z42" s="9" t="n">
+      <c r="Z42" s="6" t="n">
         <v>51.81</v>
       </c>
-      <c r="AA42" s="9" t="n">
+      <c r="AA42" s="6" t="n">
         <v>50.61</v>
       </c>
-      <c r="AB42" s="9" t="n">
+      <c r="AB42" s="6" t="n">
         <v>50.29</v>
       </c>
-      <c r="AC42" s="9" t="n">
+      <c r="AC42" s="6" t="n">
         <v>50.64</v>
       </c>
-      <c r="AD42" s="9" t="n">
+      <c r="AD42" s="6" t="n">
         <v>50.85</v>
       </c>
-      <c r="AE42" s="9" t="n">
+      <c r="AE42" s="6" t="n">
         <v>50.63</v>
       </c>
-      <c r="AF42" s="7" t="n">
+      <c r="AF42" s="6" t="n">
         <v>54.85</v>
       </c>
-      <c r="AG42" s="7" t="n">
+      <c r="AG42" s="6" t="n">
         <v>59.83</v>
       </c>
       <c r="AH42" s="6" t="n">
@@ -4472,7 +4442,7 @@
         <v>504.72</v>
       </c>
       <c r="AJ42" s="6" t="inlineStr"/>
-      <c r="AK42" s="8" t="inlineStr"/>
+      <c r="AK42" s="7" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -4483,97 +4453,97 @@
       <c r="B43" s="6" t="n">
         <v>104.1</v>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="6" t="n">
         <v>94.04000000000001</v>
       </c>
-      <c r="D43" s="7" t="n">
+      <c r="D43" s="6" t="n">
         <v>95.83</v>
       </c>
-      <c r="E43" s="7" t="n">
+      <c r="E43" s="6" t="n">
         <v>95.92</v>
       </c>
-      <c r="F43" s="7" t="n">
+      <c r="F43" s="6" t="n">
         <v>96.47</v>
       </c>
-      <c r="G43" s="7" t="n">
+      <c r="G43" s="6" t="n">
         <v>95.53</v>
       </c>
-      <c r="H43" s="7" t="n">
+      <c r="H43" s="6" t="n">
         <v>96.39</v>
       </c>
-      <c r="I43" s="7" t="n">
+      <c r="I43" s="6" t="n">
         <v>96.56999999999999</v>
       </c>
-      <c r="J43" s="7" t="n">
+      <c r="J43" s="6" t="n">
         <v>96.41</v>
       </c>
-      <c r="K43" s="7" t="n">
+      <c r="K43" s="6" t="n">
         <v>98.69</v>
       </c>
-      <c r="L43" s="7" t="n">
+      <c r="L43" s="6" t="n">
         <v>100.37</v>
       </c>
-      <c r="M43" s="7" t="n">
+      <c r="M43" s="6" t="n">
         <v>98.08</v>
       </c>
-      <c r="N43" s="7" t="n">
+      <c r="N43" s="6" t="n">
         <v>97.19</v>
       </c>
-      <c r="O43" s="7" t="n">
+      <c r="O43" s="6" t="n">
         <v>96.73</v>
       </c>
-      <c r="P43" s="7" t="n">
+      <c r="P43" s="6" t="n">
         <v>96.40000000000001</v>
       </c>
-      <c r="Q43" s="7" t="n">
+      <c r="Q43" s="6" t="n">
         <v>95.81</v>
       </c>
-      <c r="R43" s="7" t="n">
+      <c r="R43" s="6" t="n">
         <v>97.40000000000001</v>
       </c>
-      <c r="S43" s="7" t="n">
+      <c r="S43" s="6" t="n">
         <v>97.02</v>
       </c>
-      <c r="T43" s="7" t="n">
+      <c r="T43" s="6" t="n">
         <v>97.20999999999999</v>
       </c>
-      <c r="U43" s="7" t="n">
+      <c r="U43" s="6" t="n">
         <v>98.29000000000001</v>
       </c>
-      <c r="V43" s="7" t="n">
+      <c r="V43" s="6" t="n">
         <v>96.59</v>
       </c>
-      <c r="W43" s="7" t="n">
+      <c r="W43" s="6" t="n">
         <v>98.28</v>
       </c>
-      <c r="X43" s="7" t="n">
+      <c r="X43" s="6" t="n">
         <v>99.27</v>
       </c>
-      <c r="Y43" s="7" t="n">
+      <c r="Y43" s="6" t="n">
         <v>99.29000000000001</v>
       </c>
-      <c r="Z43" s="7" t="n">
+      <c r="Z43" s="6" t="n">
         <v>100.11</v>
       </c>
-      <c r="AA43" s="7" t="n">
+      <c r="AA43" s="6" t="n">
         <v>99.68000000000001</v>
       </c>
-      <c r="AB43" s="7" t="n">
+      <c r="AB43" s="6" t="n">
         <v>99.3</v>
       </c>
-      <c r="AC43" s="7" t="n">
+      <c r="AC43" s="6" t="n">
         <v>98.88</v>
       </c>
-      <c r="AD43" s="7" t="n">
+      <c r="AD43" s="6" t="n">
         <v>99.84</v>
       </c>
-      <c r="AE43" s="7" t="n">
+      <c r="AE43" s="6" t="n">
         <v>98.58</v>
       </c>
-      <c r="AF43" s="7" t="n">
+      <c r="AF43" s="6" t="n">
         <v>98.22</v>
       </c>
-      <c r="AG43" s="7" t="n">
+      <c r="AG43" s="6" t="n">
         <v>98.54000000000001</v>
       </c>
       <c r="AH43" s="6" t="n">
@@ -4583,7 +4553,7 @@
         <v>265.12</v>
       </c>
       <c r="AJ43" s="6" t="inlineStr"/>
-      <c r="AK43" s="8" t="inlineStr"/>
+      <c r="AK43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -4594,97 +4564,97 @@
       <c r="B44" s="6" t="n">
         <v>104.5</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="6" t="n">
         <v>96.89</v>
       </c>
-      <c r="D44" s="7" t="n">
+      <c r="D44" s="6" t="n">
         <v>98.95999999999999</v>
       </c>
-      <c r="E44" s="7" t="n">
+      <c r="E44" s="6" t="n">
         <v>100.69</v>
       </c>
-      <c r="F44" s="7" t="n">
+      <c r="F44" s="6" t="n">
         <v>99.98999999999999</v>
       </c>
-      <c r="G44" s="7" t="n">
+      <c r="G44" s="6" t="n">
         <v>100.05</v>
       </c>
-      <c r="H44" s="7" t="n">
+      <c r="H44" s="6" t="n">
         <v>100.15</v>
       </c>
-      <c r="I44" s="7" t="n">
+      <c r="I44" s="6" t="n">
         <v>99.63</v>
       </c>
-      <c r="J44" s="7" t="n">
+      <c r="J44" s="6" t="n">
         <v>99.47</v>
       </c>
-      <c r="K44" s="7" t="n">
+      <c r="K44" s="6" t="n">
         <v>103.17</v>
       </c>
-      <c r="L44" s="7" t="n">
+      <c r="L44" s="6" t="n">
         <v>105.8</v>
       </c>
-      <c r="M44" s="7" t="n">
+      <c r="M44" s="6" t="n">
         <v>103.22</v>
       </c>
-      <c r="N44" s="7" t="n">
+      <c r="N44" s="6" t="n">
         <v>100.21</v>
       </c>
-      <c r="O44" s="7" t="n">
+      <c r="O44" s="6" t="n">
         <v>100.55</v>
       </c>
-      <c r="P44" s="7" t="n">
+      <c r="P44" s="6" t="n">
         <v>100.05</v>
       </c>
-      <c r="Q44" s="7" t="n">
+      <c r="Q44" s="6" t="n">
         <v>99.7</v>
       </c>
-      <c r="R44" s="7" t="n">
+      <c r="R44" s="6" t="n">
         <v>100.71</v>
       </c>
-      <c r="S44" s="7" t="n">
+      <c r="S44" s="6" t="n">
         <v>100.57</v>
       </c>
-      <c r="T44" s="7" t="n">
+      <c r="T44" s="6" t="n">
         <v>99.79000000000001</v>
       </c>
-      <c r="U44" s="7" t="n">
+      <c r="U44" s="6" t="n">
         <v>101.17</v>
       </c>
-      <c r="V44" s="7" t="n">
+      <c r="V44" s="6" t="n">
         <v>101.09</v>
       </c>
-      <c r="W44" s="7" t="n">
+      <c r="W44" s="6" t="n">
         <v>102.88</v>
       </c>
-      <c r="X44" s="7" t="n">
+      <c r="X44" s="6" t="n">
         <v>105.57</v>
       </c>
-      <c r="Y44" s="7" t="n">
+      <c r="Y44" s="6" t="n">
         <v>106.06</v>
       </c>
-      <c r="Z44" s="7" t="n">
+      <c r="Z44" s="6" t="n">
         <v>105.97</v>
       </c>
-      <c r="AA44" s="7" t="n">
+      <c r="AA44" s="6" t="n">
         <v>106.17</v>
       </c>
-      <c r="AB44" s="7" t="n">
+      <c r="AB44" s="6" t="n">
         <v>105.77</v>
       </c>
-      <c r="AC44" s="7" t="n">
+      <c r="AC44" s="6" t="n">
         <v>105.69</v>
       </c>
-      <c r="AD44" s="7" t="n">
+      <c r="AD44" s="6" t="n">
         <v>106.16</v>
       </c>
-      <c r="AE44" s="7" t="n">
+      <c r="AE44" s="6" t="n">
         <v>105.9</v>
       </c>
-      <c r="AF44" s="7" t="n">
+      <c r="AF44" s="6" t="n">
         <v>103.81</v>
       </c>
-      <c r="AG44" s="7" t="n">
+      <c r="AG44" s="6" t="n">
         <v>100.94</v>
       </c>
       <c r="AH44" s="6" t="n">
@@ -4694,7 +4664,7 @@
         <v>348.54</v>
       </c>
       <c r="AJ44" s="6" t="inlineStr"/>
-      <c r="AK44" s="8" t="inlineStr"/>
+      <c r="AK44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -4705,97 +4675,97 @@
       <c r="B45" s="6" t="n">
         <v>104.9</v>
       </c>
-      <c r="C45" s="7" t="n">
+      <c r="C45" s="6" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="D45" s="7" t="n">
+      <c r="D45" s="6" t="n">
         <v>99.70999999999999</v>
       </c>
-      <c r="E45" s="7" t="n">
+      <c r="E45" s="6" t="n">
         <v>100.45</v>
       </c>
-      <c r="F45" s="7" t="n">
+      <c r="F45" s="6" t="n">
         <v>100.85</v>
       </c>
-      <c r="G45" s="7" t="n">
+      <c r="G45" s="6" t="n">
         <v>100.75</v>
       </c>
-      <c r="H45" s="7" t="n">
+      <c r="H45" s="6" t="n">
         <v>101.45</v>
       </c>
-      <c r="I45" s="7" t="n">
+      <c r="I45" s="6" t="n">
         <v>101.65</v>
       </c>
-      <c r="J45" s="7" t="n">
+      <c r="J45" s="6" t="n">
         <v>100.51</v>
       </c>
-      <c r="K45" s="7" t="n">
+      <c r="K45" s="6" t="n">
         <v>101.33</v>
       </c>
-      <c r="L45" s="7" t="n">
+      <c r="L45" s="6" t="n">
         <v>101.65</v>
       </c>
-      <c r="M45" s="7" t="n">
+      <c r="M45" s="6" t="n">
         <v>101.78</v>
       </c>
-      <c r="N45" s="7" t="n">
+      <c r="N45" s="6" t="n">
         <v>102.15</v>
       </c>
-      <c r="O45" s="7" t="n">
+      <c r="O45" s="6" t="n">
         <v>101.4</v>
       </c>
-      <c r="P45" s="7" t="n">
+      <c r="P45" s="6" t="n">
         <v>101.39</v>
       </c>
-      <c r="Q45" s="7" t="n">
+      <c r="Q45" s="6" t="n">
         <v>101.01</v>
       </c>
-      <c r="R45" s="7" t="n">
+      <c r="R45" s="6" t="n">
         <v>62.75</v>
       </c>
-      <c r="S45" s="7" t="n">
+      <c r="S45" s="6" t="n">
         <v>101.98</v>
       </c>
-      <c r="T45" s="7" t="n">
+      <c r="T45" s="6" t="n">
         <v>101.33</v>
       </c>
-      <c r="U45" s="7" t="n">
+      <c r="U45" s="6" t="n">
         <v>102.57</v>
       </c>
-      <c r="V45" s="7" t="n">
+      <c r="V45" s="6" t="n">
         <v>101.05</v>
       </c>
-      <c r="W45" s="7" t="n">
+      <c r="W45" s="6" t="n">
         <v>101.24</v>
       </c>
-      <c r="X45" s="7" t="n">
+      <c r="X45" s="6" t="n">
         <v>100.69</v>
       </c>
-      <c r="Y45" s="7" t="n">
+      <c r="Y45" s="6" t="n">
         <v>100.94</v>
       </c>
-      <c r="Z45" s="7" t="n">
+      <c r="Z45" s="6" t="n">
         <v>101.27</v>
       </c>
-      <c r="AA45" s="7" t="n">
+      <c r="AA45" s="6" t="n">
         <v>100.94</v>
       </c>
-      <c r="AB45" s="7" t="n">
+      <c r="AB45" s="6" t="n">
         <v>101.06</v>
       </c>
-      <c r="AC45" s="7" t="n">
+      <c r="AC45" s="6" t="n">
         <v>101.25</v>
       </c>
-      <c r="AD45" s="7" t="n">
+      <c r="AD45" s="6" t="n">
         <v>101.16</v>
       </c>
-      <c r="AE45" s="7" t="n">
+      <c r="AE45" s="6" t="n">
         <v>101.06</v>
       </c>
-      <c r="AF45" s="7" t="n">
+      <c r="AF45" s="6" t="n">
         <v>102.18</v>
       </c>
-      <c r="AG45" s="7" t="n">
+      <c r="AG45" s="6" t="n">
         <v>104.17</v>
       </c>
       <c r="AH45" s="6" t="n">
@@ -4805,7 +4775,7 @@
         <v>456.27</v>
       </c>
       <c r="AJ45" s="6" t="inlineStr"/>
-      <c r="AK45" s="8" t="inlineStr"/>
+      <c r="AK45" s="7" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -4816,97 +4786,97 @@
       <c r="B46" s="6" t="n">
         <v>105.7</v>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C46" s="6" t="n">
         <v>99.2</v>
       </c>
-      <c r="D46" s="7" t="n">
+      <c r="D46" s="6" t="n">
         <v>100.34</v>
       </c>
-      <c r="E46" s="7" t="n">
+      <c r="E46" s="6" t="n">
         <v>98.93000000000001</v>
       </c>
-      <c r="F46" s="7" t="n">
+      <c r="F46" s="6" t="n">
         <v>99.94</v>
       </c>
-      <c r="G46" s="7" t="n">
+      <c r="G46" s="6" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="H46" s="7" t="n">
+      <c r="H46" s="6" t="n">
         <v>99.78</v>
       </c>
-      <c r="I46" s="7" t="n">
+      <c r="I46" s="6" t="n">
         <v>100.31</v>
       </c>
-      <c r="J46" s="7" t="n">
+      <c r="J46" s="6" t="n">
         <v>100.54</v>
       </c>
-      <c r="K46" s="7" t="n">
+      <c r="K46" s="6" t="n">
         <v>100.59</v>
       </c>
-      <c r="L46" s="7" t="n">
+      <c r="L46" s="6" t="n">
         <v>101.39</v>
       </c>
-      <c r="M46" s="7" t="n">
+      <c r="M46" s="6" t="n">
         <v>101.34</v>
       </c>
-      <c r="N46" s="7" t="n">
+      <c r="N46" s="6" t="n">
         <v>100.27</v>
       </c>
-      <c r="O46" s="7" t="n">
+      <c r="O46" s="6" t="n">
         <v>99.64</v>
       </c>
-      <c r="P46" s="7" t="n">
+      <c r="P46" s="6" t="n">
         <v>100.25</v>
       </c>
-      <c r="Q46" s="7" t="n">
+      <c r="Q46" s="6" t="n">
         <v>100.02</v>
       </c>
-      <c r="R46" s="7" t="n">
+      <c r="R46" s="6" t="n">
         <v>101.94</v>
       </c>
-      <c r="S46" s="7" t="n">
+      <c r="S46" s="6" t="n">
         <v>101.76</v>
       </c>
-      <c r="T46" s="7" t="n">
+      <c r="T46" s="6" t="n">
         <v>99.89</v>
       </c>
-      <c r="U46" s="7" t="n">
+      <c r="U46" s="6" t="n">
         <v>100.34</v>
       </c>
-      <c r="V46" s="7" t="n">
+      <c r="V46" s="6" t="n">
         <v>100.52</v>
       </c>
-      <c r="W46" s="7" t="n">
+      <c r="W46" s="6" t="n">
         <v>100.96</v>
       </c>
-      <c r="X46" s="7" t="n">
+      <c r="X46" s="6" t="n">
         <v>101.15</v>
       </c>
-      <c r="Y46" s="7" t="n">
+      <c r="Y46" s="6" t="n">
         <v>101.05</v>
       </c>
-      <c r="Z46" s="7" t="n">
+      <c r="Z46" s="6" t="n">
         <v>101.21</v>
       </c>
-      <c r="AA46" s="7" t="n">
+      <c r="AA46" s="6" t="n">
         <v>101.4</v>
       </c>
-      <c r="AB46" s="7" t="n">
+      <c r="AB46" s="6" t="n">
         <v>100.88</v>
       </c>
-      <c r="AC46" s="7" t="n">
+      <c r="AC46" s="6" t="n">
         <v>101.17</v>
       </c>
-      <c r="AD46" s="7" t="n">
+      <c r="AD46" s="6" t="n">
         <v>101.41</v>
       </c>
-      <c r="AE46" s="7" t="n">
+      <c r="AE46" s="6" t="n">
         <v>101.22</v>
       </c>
-      <c r="AF46" s="7" t="n">
+      <c r="AF46" s="6" t="n">
         <v>101.94</v>
       </c>
-      <c r="AG46" s="7" t="n">
+      <c r="AG46" s="6" t="n">
         <v>102.45</v>
       </c>
       <c r="AH46" s="6" t="n">
@@ -4916,7 +4886,7 @@
         <v>420.89</v>
       </c>
       <c r="AJ46" s="6" t="inlineStr"/>
-      <c r="AK46" s="8" t="inlineStr"/>
+      <c r="AK46" s="7" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -4927,97 +4897,97 @@
       <c r="B47" s="6" t="n">
         <v>106.1</v>
       </c>
-      <c r="C47" s="7" t="n">
+      <c r="C47" s="6" t="n">
         <v>96.41</v>
       </c>
-      <c r="D47" s="7" t="n">
+      <c r="D47" s="6" t="n">
         <v>98.17</v>
       </c>
-      <c r="E47" s="7" t="n">
+      <c r="E47" s="6" t="n">
         <v>99.8</v>
       </c>
-      <c r="F47" s="7" t="n">
+      <c r="F47" s="6" t="n">
         <v>99.06</v>
       </c>
-      <c r="G47" s="7" t="n">
+      <c r="G47" s="6" t="n">
         <v>99.08</v>
       </c>
-      <c r="H47" s="7" t="n">
+      <c r="H47" s="6" t="n">
         <v>99.69</v>
       </c>
-      <c r="I47" s="7" t="n">
+      <c r="I47" s="6" t="n">
         <v>98.59</v>
       </c>
-      <c r="J47" s="7" t="n">
+      <c r="J47" s="6" t="n">
         <v>98.34999999999999</v>
       </c>
-      <c r="K47" s="7" t="n">
+      <c r="K47" s="6" t="n">
         <v>100.83</v>
       </c>
-      <c r="L47" s="7" t="n">
+      <c r="L47" s="6" t="n">
         <v>102.82</v>
       </c>
-      <c r="M47" s="7" t="n">
+      <c r="M47" s="6" t="n">
         <v>101.24</v>
       </c>
-      <c r="N47" s="7" t="n">
+      <c r="N47" s="6" t="n">
         <v>100.28</v>
       </c>
-      <c r="O47" s="7" t="n">
+      <c r="O47" s="6" t="n">
         <v>99.76000000000001</v>
       </c>
-      <c r="P47" s="7" t="n">
+      <c r="P47" s="6" t="n">
         <v>98.73</v>
       </c>
-      <c r="Q47" s="7" t="n">
+      <c r="Q47" s="6" t="n">
         <v>99.03</v>
       </c>
-      <c r="R47" s="7" t="n">
+      <c r="R47" s="6" t="n">
         <v>100.07</v>
       </c>
-      <c r="S47" s="7" t="n">
+      <c r="S47" s="6" t="n">
         <v>100.01</v>
       </c>
-      <c r="T47" s="7" t="n">
+      <c r="T47" s="6" t="n">
         <v>98.98</v>
       </c>
-      <c r="U47" s="7" t="n">
+      <c r="U47" s="6" t="n">
         <v>101.22</v>
       </c>
-      <c r="V47" s="7" t="n">
+      <c r="V47" s="6" t="n">
         <v>99.81</v>
       </c>
-      <c r="W47" s="7" t="n">
+      <c r="W47" s="6" t="n">
         <v>100.56</v>
       </c>
-      <c r="X47" s="7" t="n">
+      <c r="X47" s="6" t="n">
         <v>102.19</v>
       </c>
-      <c r="Y47" s="7" t="n">
+      <c r="Y47" s="6" t="n">
         <v>101.98</v>
       </c>
-      <c r="Z47" s="7" t="n">
+      <c r="Z47" s="6" t="n">
         <v>101.83</v>
       </c>
-      <c r="AA47" s="7" t="n">
+      <c r="AA47" s="6" t="n">
         <v>101.79</v>
       </c>
-      <c r="AB47" s="7" t="n">
+      <c r="AB47" s="6" t="n">
         <v>102.13</v>
       </c>
-      <c r="AC47" s="7" t="n">
+      <c r="AC47" s="6" t="n">
         <v>102.53</v>
       </c>
-      <c r="AD47" s="7" t="n">
+      <c r="AD47" s="6" t="n">
         <v>102.13</v>
       </c>
-      <c r="AE47" s="7" t="n">
+      <c r="AE47" s="6" t="n">
         <v>101.58</v>
       </c>
-      <c r="AF47" s="7" t="n">
+      <c r="AF47" s="6" t="n">
         <v>101.42</v>
       </c>
-      <c r="AG47" s="7" t="n">
+      <c r="AG47" s="6" t="n">
         <v>100.83</v>
       </c>
       <c r="AH47" s="6" t="n">
@@ -5027,7 +4997,7 @@
         <v>416.29</v>
       </c>
       <c r="AJ47" s="6" t="inlineStr"/>
-      <c r="AK47" s="8" t="inlineStr"/>
+      <c r="AK47" s="7" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -5038,97 +5008,97 @@
       <c r="B48" s="6" t="n">
         <v>106.5</v>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C48" s="6" t="n">
         <v>89.23999999999999</v>
       </c>
-      <c r="D48" s="7" t="n">
+      <c r="D48" s="6" t="n">
         <v>89.87</v>
       </c>
-      <c r="E48" s="7" t="n">
+      <c r="E48" s="6" t="n">
         <v>91.44</v>
       </c>
-      <c r="F48" s="7" t="n">
+      <c r="F48" s="6" t="n">
         <v>91.03</v>
       </c>
-      <c r="G48" s="7" t="n">
+      <c r="G48" s="6" t="n">
         <v>90.90000000000001</v>
       </c>
-      <c r="H48" s="7" t="n">
+      <c r="H48" s="6" t="n">
         <v>91.18000000000001</v>
       </c>
-      <c r="I48" s="7" t="n">
+      <c r="I48" s="6" t="n">
         <v>91.34</v>
       </c>
-      <c r="J48" s="7" t="n">
+      <c r="J48" s="6" t="n">
         <v>90.97</v>
       </c>
-      <c r="K48" s="7" t="n">
+      <c r="K48" s="6" t="n">
         <v>93.91</v>
       </c>
-      <c r="L48" s="7" t="n">
+      <c r="L48" s="6" t="n">
         <v>96.01000000000001</v>
       </c>
-      <c r="M48" s="7" t="n">
+      <c r="M48" s="6" t="n">
         <v>94.14</v>
       </c>
-      <c r="N48" s="7" t="n">
+      <c r="N48" s="6" t="n">
         <v>91.38</v>
       </c>
-      <c r="O48" s="7" t="n">
+      <c r="O48" s="6" t="n">
         <v>91.3</v>
       </c>
-      <c r="P48" s="7" t="n">
+      <c r="P48" s="6" t="n">
         <v>91.44</v>
       </c>
-      <c r="Q48" s="7" t="n">
+      <c r="Q48" s="6" t="n">
         <v>91.08</v>
       </c>
-      <c r="R48" s="7" t="n">
+      <c r="R48" s="6" t="n">
         <v>92.5</v>
       </c>
-      <c r="S48" s="7" t="n">
+      <c r="S48" s="6" t="n">
         <v>91.73999999999999</v>
       </c>
-      <c r="T48" s="7" t="n">
+      <c r="T48" s="6" t="n">
         <v>90.98</v>
       </c>
-      <c r="U48" s="7" t="n">
+      <c r="U48" s="6" t="n">
         <v>91.73999999999999</v>
       </c>
-      <c r="V48" s="7" t="n">
+      <c r="V48" s="6" t="n">
         <v>92.16</v>
       </c>
-      <c r="W48" s="7" t="n">
+      <c r="W48" s="6" t="n">
         <v>94.69</v>
       </c>
-      <c r="X48" s="7" t="n">
+      <c r="X48" s="6" t="n">
         <v>96.97</v>
       </c>
-      <c r="Y48" s="7" t="n">
+      <c r="Y48" s="6" t="n">
         <v>96.66</v>
       </c>
-      <c r="Z48" s="7" t="n">
+      <c r="Z48" s="6" t="n">
         <v>96.54000000000001</v>
       </c>
-      <c r="AA48" s="7" t="n">
+      <c r="AA48" s="6" t="n">
         <v>96.87</v>
       </c>
-      <c r="AB48" s="7" t="n">
+      <c r="AB48" s="6" t="n">
         <v>96.81999999999999</v>
       </c>
-      <c r="AC48" s="7" t="n">
+      <c r="AC48" s="6" t="n">
         <v>96.98999999999999</v>
       </c>
-      <c r="AD48" s="7" t="n">
+      <c r="AD48" s="6" t="n">
         <v>96.38</v>
       </c>
-      <c r="AE48" s="7" t="n">
+      <c r="AE48" s="6" t="n">
         <v>96.38</v>
       </c>
-      <c r="AF48" s="7" t="n">
+      <c r="AF48" s="6" t="n">
         <v>94.83</v>
       </c>
-      <c r="AG48" s="7" t="n">
+      <c r="AG48" s="6" t="n">
         <v>92.87</v>
       </c>
       <c r="AH48" s="6" t="n">
@@ -5138,7 +5108,7 @@
         <v>389.74</v>
       </c>
       <c r="AJ48" s="6" t="inlineStr"/>
-      <c r="AK48" s="8" t="inlineStr"/>
+      <c r="AK48" s="7" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -5149,97 +5119,97 @@
       <c r="B49" s="6" t="n">
         <v>106.9</v>
       </c>
-      <c r="C49" s="7" t="n">
+      <c r="C49" s="6" t="n">
         <v>82.94</v>
       </c>
-      <c r="D49" s="7" t="n">
+      <c r="D49" s="6" t="n">
         <v>81.58</v>
       </c>
-      <c r="E49" s="7" t="n">
+      <c r="E49" s="6" t="n">
         <v>75.23999999999999</v>
       </c>
-      <c r="F49" s="7" t="n">
+      <c r="F49" s="6" t="n">
         <v>80.34999999999999</v>
       </c>
-      <c r="G49" s="7" t="n">
+      <c r="G49" s="6" t="n">
         <v>81.51000000000001</v>
       </c>
-      <c r="H49" s="7" t="n">
+      <c r="H49" s="6" t="n">
         <v>79.69</v>
       </c>
-      <c r="I49" s="7" t="n">
+      <c r="I49" s="6" t="n">
         <v>83.08</v>
       </c>
-      <c r="J49" s="7" t="n">
+      <c r="J49" s="6" t="n">
         <v>83.83</v>
       </c>
-      <c r="K49" s="7" t="n">
+      <c r="K49" s="6" t="n">
         <v>85.68000000000001</v>
       </c>
-      <c r="L49" s="7" t="n">
+      <c r="L49" s="6" t="n">
         <v>92.92</v>
       </c>
-      <c r="M49" s="7" t="n">
+      <c r="M49" s="6" t="n">
         <v>88.45999999999999</v>
       </c>
-      <c r="N49" s="7" t="n">
+      <c r="N49" s="6" t="n">
         <v>84.20999999999999</v>
       </c>
-      <c r="O49" s="7" t="n">
+      <c r="O49" s="6" t="n">
         <v>84.55</v>
       </c>
-      <c r="P49" s="7" t="n">
+      <c r="P49" s="6" t="n">
         <v>84.43000000000001</v>
       </c>
-      <c r="Q49" s="7" t="n">
+      <c r="Q49" s="6" t="n">
         <v>85.41</v>
       </c>
-      <c r="R49" s="7" t="n">
+      <c r="R49" s="6" t="n">
         <v>86.06</v>
       </c>
-      <c r="S49" s="7" t="n">
+      <c r="S49" s="6" t="n">
         <v>86.41</v>
       </c>
-      <c r="T49" s="7" t="n">
+      <c r="T49" s="6" t="n">
         <v>81.58</v>
       </c>
-      <c r="U49" s="7" t="n">
+      <c r="U49" s="6" t="n">
         <v>79.8</v>
       </c>
-      <c r="V49" s="7" t="n">
+      <c r="V49" s="6" t="n">
         <v>81.06</v>
       </c>
-      <c r="W49" s="7" t="n">
+      <c r="W49" s="6" t="n">
         <v>84.2</v>
       </c>
-      <c r="X49" s="7" t="n">
+      <c r="X49" s="6" t="n">
         <v>93.41</v>
       </c>
-      <c r="Y49" s="7" t="n">
+      <c r="Y49" s="6" t="n">
         <v>92.89</v>
       </c>
-      <c r="Z49" s="7" t="n">
+      <c r="Z49" s="6" t="n">
         <v>92.38</v>
       </c>
-      <c r="AA49" s="7" t="n">
+      <c r="AA49" s="6" t="n">
         <v>92.73999999999999</v>
       </c>
-      <c r="AB49" s="7" t="n">
+      <c r="AB49" s="6" t="n">
         <v>93.53</v>
       </c>
-      <c r="AC49" s="7" t="n">
+      <c r="AC49" s="6" t="n">
         <v>93.33</v>
       </c>
-      <c r="AD49" s="7" t="n">
+      <c r="AD49" s="6" t="n">
         <v>91.56999999999999</v>
       </c>
-      <c r="AE49" s="7" t="n">
+      <c r="AE49" s="6" t="n">
         <v>93.27</v>
       </c>
-      <c r="AF49" s="7" t="n">
+      <c r="AF49" s="6" t="n">
         <v>87.43000000000001</v>
       </c>
-      <c r="AG49" s="7" t="n">
+      <c r="AG49" s="6" t="n">
         <v>83.7</v>
       </c>
       <c r="AH49" s="6" t="n">
@@ -5249,7 +5219,7 @@
         <v>363.9</v>
       </c>
       <c r="AJ49" s="6" t="inlineStr"/>
-      <c r="AK49" s="8" t="inlineStr"/>
+      <c r="AK49" s="7" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -5260,97 +5230,97 @@
       <c r="B50" s="6" t="n">
         <v>107.3</v>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C50" s="6" t="n">
         <v>97.02</v>
       </c>
-      <c r="D50" s="7" t="n">
+      <c r="D50" s="6" t="n">
         <v>97.38</v>
       </c>
-      <c r="E50" s="7" t="n">
+      <c r="E50" s="6" t="n">
         <v>100.17</v>
       </c>
-      <c r="F50" s="7" t="n">
+      <c r="F50" s="6" t="n">
         <v>100.19</v>
       </c>
-      <c r="G50" s="7" t="n">
+      <c r="G50" s="6" t="n">
         <v>99.47</v>
       </c>
-      <c r="H50" s="7" t="n">
+      <c r="H50" s="6" t="n">
         <v>99.84999999999999</v>
       </c>
-      <c r="I50" s="7" t="n">
+      <c r="I50" s="6" t="n">
         <v>100.17</v>
       </c>
-      <c r="J50" s="7" t="n">
+      <c r="J50" s="6" t="n">
         <v>99.97</v>
       </c>
-      <c r="K50" s="7" t="n">
+      <c r="K50" s="6" t="n">
         <v>101.72</v>
       </c>
-      <c r="L50" s="7" t="n">
+      <c r="L50" s="6" t="n">
         <v>103.51</v>
       </c>
-      <c r="M50" s="7" t="n">
+      <c r="M50" s="6" t="n">
         <v>102.89</v>
       </c>
-      <c r="N50" s="7" t="n">
+      <c r="N50" s="6" t="n">
         <v>101.01</v>
       </c>
-      <c r="O50" s="7" t="n">
+      <c r="O50" s="6" t="n">
         <v>100.34</v>
       </c>
-      <c r="P50" s="7" t="n">
+      <c r="P50" s="6" t="n">
         <v>100.96</v>
       </c>
-      <c r="Q50" s="7" t="n">
+      <c r="Q50" s="6" t="n">
         <v>100.27</v>
       </c>
-      <c r="R50" s="7" t="n">
+      <c r="R50" s="6" t="n">
         <v>101.63</v>
       </c>
-      <c r="S50" s="7" t="n">
+      <c r="S50" s="6" t="n">
         <v>101.48</v>
       </c>
-      <c r="T50" s="7" t="n">
+      <c r="T50" s="6" t="n">
         <v>100.31</v>
       </c>
-      <c r="U50" s="7" t="n">
+      <c r="U50" s="6" t="n">
         <v>101.41</v>
       </c>
-      <c r="V50" s="7" t="n">
+      <c r="V50" s="6" t="n">
         <v>101.11</v>
       </c>
-      <c r="W50" s="7" t="n">
+      <c r="W50" s="6" t="n">
         <v>102.63</v>
       </c>
-      <c r="X50" s="7" t="n">
+      <c r="X50" s="6" t="n">
         <v>103.98</v>
       </c>
-      <c r="Y50" s="7" t="n">
+      <c r="Y50" s="6" t="n">
         <v>103.92</v>
       </c>
-      <c r="Z50" s="7" t="n">
+      <c r="Z50" s="6" t="n">
         <v>104.27</v>
       </c>
-      <c r="AA50" s="7" t="n">
+      <c r="AA50" s="6" t="n">
         <v>103.99</v>
       </c>
-      <c r="AB50" s="7" t="n">
+      <c r="AB50" s="6" t="n">
         <v>104.23</v>
       </c>
-      <c r="AC50" s="7" t="n">
+      <c r="AC50" s="6" t="n">
         <v>103.94</v>
       </c>
-      <c r="AD50" s="7" t="n">
+      <c r="AD50" s="6" t="n">
         <v>103.89</v>
       </c>
-      <c r="AE50" s="7" t="n">
+      <c r="AE50" s="6" t="n">
         <v>103.47</v>
       </c>
-      <c r="AF50" s="7" t="n">
+      <c r="AF50" s="6" t="n">
         <v>103.17</v>
       </c>
-      <c r="AG50" s="7" t="n">
+      <c r="AG50" s="6" t="n">
         <v>102.71</v>
       </c>
       <c r="AH50" s="6" t="n">
@@ -5360,118 +5330,118 @@
         <v>310.71</v>
       </c>
       <c r="AJ50" s="6" t="inlineStr"/>
-      <c r="AK50" s="8" t="inlineStr"/>
+      <c r="AK50" s="7" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="10" t="inlineStr">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>RADIO POSITIVA FM</t>
         </is>
       </c>
-      <c r="B51" s="11" t="n">
+      <c r="B51" s="9" t="n">
         <v>107.7</v>
       </c>
-      <c r="C51" s="12" t="n">
+      <c r="C51" s="9" t="n">
         <v>76.42</v>
       </c>
-      <c r="D51" s="12" t="n">
+      <c r="D51" s="9" t="n">
         <v>76.77</v>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="E51" s="9" t="n">
         <v>81.34999999999999</v>
       </c>
-      <c r="F51" s="12" t="n">
+      <c r="F51" s="9" t="n">
         <v>79.69</v>
       </c>
-      <c r="G51" s="12" t="n">
+      <c r="G51" s="9" t="n">
         <v>79.67</v>
       </c>
-      <c r="H51" s="12" t="n">
+      <c r="H51" s="9" t="n">
         <v>79.69</v>
       </c>
-      <c r="I51" s="12" t="n">
+      <c r="I51" s="9" t="n">
         <v>79.95999999999999</v>
       </c>
-      <c r="J51" s="12" t="n">
+      <c r="J51" s="9" t="n">
         <v>79.01000000000001</v>
       </c>
-      <c r="K51" s="12" t="n">
+      <c r="K51" s="9" t="n">
         <v>82.05</v>
       </c>
-      <c r="L51" s="12" t="n">
+      <c r="L51" s="9" t="n">
         <v>84.64</v>
       </c>
-      <c r="M51" s="12" t="n">
+      <c r="M51" s="9" t="n">
         <v>81.73</v>
       </c>
-      <c r="N51" s="12" t="n">
+      <c r="N51" s="9" t="n">
         <v>79.73</v>
       </c>
-      <c r="O51" s="12" t="n">
+      <c r="O51" s="9" t="n">
         <v>78.31999999999999</v>
       </c>
-      <c r="P51" s="12" t="n">
+      <c r="P51" s="9" t="n">
         <v>79.45999999999999</v>
       </c>
-      <c r="Q51" s="12" t="n">
+      <c r="Q51" s="9" t="n">
         <v>79.41</v>
       </c>
-      <c r="R51" s="12" t="n">
+      <c r="R51" s="9" t="n">
         <v>79.73999999999999</v>
       </c>
-      <c r="S51" s="12" t="n">
+      <c r="S51" s="9" t="n">
         <v>79.73</v>
       </c>
-      <c r="T51" s="12" t="n">
+      <c r="T51" s="9" t="n">
         <v>79.68000000000001</v>
       </c>
-      <c r="U51" s="12" t="n">
+      <c r="U51" s="9" t="n">
         <v>80.61</v>
       </c>
-      <c r="V51" s="12" t="n">
+      <c r="V51" s="9" t="n">
         <v>79.16</v>
       </c>
-      <c r="W51" s="12" t="n">
+      <c r="W51" s="9" t="n">
         <v>81.95999999999999</v>
       </c>
-      <c r="X51" s="12" t="n">
+      <c r="X51" s="9" t="n">
         <v>84.26000000000001</v>
       </c>
-      <c r="Y51" s="12" t="n">
+      <c r="Y51" s="9" t="n">
         <v>83.81</v>
       </c>
-      <c r="Z51" s="12" t="n">
+      <c r="Z51" s="9" t="n">
         <v>84.69</v>
       </c>
-      <c r="AA51" s="12" t="n">
+      <c r="AA51" s="9" t="n">
         <v>84.03</v>
       </c>
-      <c r="AB51" s="12" t="n">
+      <c r="AB51" s="9" t="n">
         <v>83.94</v>
       </c>
-      <c r="AC51" s="12" t="n">
+      <c r="AC51" s="9" t="n">
         <v>83.68000000000001</v>
       </c>
-      <c r="AD51" s="12" t="n">
+      <c r="AD51" s="9" t="n">
         <v>83.81999999999999</v>
       </c>
-      <c r="AE51" s="12" t="n">
+      <c r="AE51" s="9" t="n">
         <v>84.41</v>
       </c>
-      <c r="AF51" s="12" t="n">
+      <c r="AF51" s="9" t="n">
         <v>82.03</v>
       </c>
-      <c r="AG51" s="12" t="n">
+      <c r="AG51" s="9" t="n">
         <v>79.73</v>
       </c>
-      <c r="AH51" s="11" t="n">
+      <c r="AH51" s="9" t="n">
         <v>81.06999999999999</v>
       </c>
-      <c r="AI51" s="11" t="n">
+      <c r="AI51" s="9" t="n">
         <v>264.88</v>
       </c>
-      <c r="AJ51" s="11" t="inlineStr"/>
-      <c r="AK51" s="13" t="inlineStr"/>
+      <c r="AJ51" s="9" t="inlineStr"/>
+      <c r="AK51" s="10" t="inlineStr"/>
     </row>
     <row r="52"/>
     <row r="53"/>
@@ -5520,7 +5490,7 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 28/08/2025</t>
+          <t>FECHA PRESENTACIÓN: 27/08/2025</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5616,7 @@
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK61" s="14" t="n"/>
+      <c r="AK61" s="11" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -5657,97 +5627,97 @@
       <c r="B62" s="6" t="n">
         <v>55.25</v>
       </c>
-      <c r="C62" s="7" t="n">
+      <c r="C62" s="6" t="n">
         <v>92.58</v>
       </c>
-      <c r="D62" s="7" t="n">
+      <c r="D62" s="6" t="n">
         <v>92.59999999999999</v>
       </c>
-      <c r="E62" s="7" t="n">
+      <c r="E62" s="6" t="n">
         <v>92.47</v>
       </c>
-      <c r="F62" s="7" t="n">
+      <c r="F62" s="6" t="n">
         <v>92.73</v>
       </c>
-      <c r="G62" s="7" t="n">
+      <c r="G62" s="6" t="n">
         <v>91.95</v>
       </c>
-      <c r="H62" s="7" t="n">
+      <c r="H62" s="6" t="n">
         <v>91.48</v>
       </c>
-      <c r="I62" s="7" t="n">
+      <c r="I62" s="6" t="n">
         <v>91.53</v>
       </c>
-      <c r="J62" s="7" t="n">
+      <c r="J62" s="6" t="n">
         <v>92.33</v>
       </c>
-      <c r="K62" s="7" t="n">
+      <c r="K62" s="6" t="n">
         <v>88.68000000000001</v>
       </c>
-      <c r="L62" s="7" t="n">
+      <c r="L62" s="6" t="n">
         <v>84.98</v>
       </c>
-      <c r="M62" s="7" t="n">
+      <c r="M62" s="6" t="n">
         <v>88.31999999999999</v>
       </c>
-      <c r="N62" s="7" t="n">
+      <c r="N62" s="6" t="n">
         <v>92.38</v>
       </c>
-      <c r="O62" s="7" t="n">
+      <c r="O62" s="6" t="n">
         <v>91.84999999999999</v>
       </c>
-      <c r="P62" s="7" t="n">
+      <c r="P62" s="6" t="n">
         <v>91.28</v>
       </c>
-      <c r="Q62" s="7" t="n">
+      <c r="Q62" s="6" t="n">
         <v>91.65000000000001</v>
       </c>
-      <c r="R62" s="7" t="n">
+      <c r="R62" s="6" t="n">
         <v>92.25</v>
       </c>
-      <c r="S62" s="7" t="n">
+      <c r="S62" s="6" t="n">
         <v>92.17</v>
       </c>
-      <c r="T62" s="7" t="n">
+      <c r="T62" s="6" t="n">
         <v>92.7</v>
       </c>
-      <c r="U62" s="7" t="n">
+      <c r="U62" s="6" t="n">
         <v>92.8</v>
       </c>
-      <c r="V62" s="7" t="n">
+      <c r="V62" s="6" t="n">
         <v>92.02</v>
       </c>
-      <c r="W62" s="7" t="n">
+      <c r="W62" s="6" t="n">
         <v>88.45</v>
       </c>
-      <c r="X62" s="7" t="n">
+      <c r="X62" s="6" t="n">
         <v>84.58</v>
       </c>
-      <c r="Y62" s="7" t="n">
+      <c r="Y62" s="6" t="n">
         <v>84.7</v>
       </c>
-      <c r="Z62" s="7" t="n">
+      <c r="Z62" s="6" t="n">
         <v>84.90000000000001</v>
       </c>
-      <c r="AA62" s="7" t="n">
+      <c r="AA62" s="6" t="n">
         <v>84.73</v>
       </c>
-      <c r="AB62" s="7" t="n">
+      <c r="AB62" s="6" t="n">
         <v>84.53</v>
       </c>
-      <c r="AC62" s="7" t="n">
+      <c r="AC62" s="6" t="n">
         <v>84.45</v>
       </c>
-      <c r="AD62" s="7" t="n">
+      <c r="AD62" s="6" t="n">
         <v>84.92</v>
       </c>
-      <c r="AE62" s="7" t="n">
+      <c r="AE62" s="6" t="n">
         <v>85.40000000000001</v>
       </c>
-      <c r="AF62" s="7" t="n">
+      <c r="AF62" s="6" t="n">
         <v>89.3</v>
       </c>
-      <c r="AG62" s="7" t="n">
+      <c r="AG62" s="6" t="n">
         <v>92.92</v>
       </c>
       <c r="AH62" s="6" t="n">
@@ -5755,7 +5725,7 @@
       </c>
       <c r="AI62" s="6" t="inlineStr"/>
       <c r="AJ62" s="6" t="inlineStr"/>
-      <c r="AK62" s="15" t="n"/>
+      <c r="AK62" s="12" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -5766,97 +5736,97 @@
       <c r="B63" s="6" t="n">
         <v>67.25</v>
       </c>
-      <c r="C63" s="7" t="n">
+      <c r="C63" s="6" t="n">
         <v>93.25</v>
       </c>
-      <c r="D63" s="7" t="n">
+      <c r="D63" s="6" t="n">
         <v>93.33</v>
       </c>
-      <c r="E63" s="7" t="n">
+      <c r="E63" s="6" t="n">
         <v>92.05</v>
       </c>
-      <c r="F63" s="7" t="n">
+      <c r="F63" s="6" t="n">
         <v>93.31999999999999</v>
       </c>
-      <c r="G63" s="7" t="n">
+      <c r="G63" s="6" t="n">
         <v>92.2</v>
       </c>
-      <c r="H63" s="7" t="n">
+      <c r="H63" s="6" t="n">
         <v>93.18000000000001</v>
       </c>
-      <c r="I63" s="7" t="n">
+      <c r="I63" s="6" t="n">
         <v>92.56999999999999</v>
       </c>
-      <c r="J63" s="7" t="n">
+      <c r="J63" s="6" t="n">
         <v>93.27</v>
       </c>
-      <c r="K63" s="7" t="n">
+      <c r="K63" s="6" t="n">
         <v>84.75</v>
       </c>
-      <c r="L63" s="7" t="n">
+      <c r="L63" s="6" t="n">
         <v>79.81999999999999</v>
       </c>
-      <c r="M63" s="7" t="n">
+      <c r="M63" s="6" t="n">
         <v>87.84999999999999</v>
       </c>
-      <c r="N63" s="7" t="n">
+      <c r="N63" s="6" t="n">
         <v>91.63</v>
       </c>
-      <c r="O63" s="7" t="n">
+      <c r="O63" s="6" t="n">
         <v>91.15000000000001</v>
       </c>
-      <c r="P63" s="7" t="n">
+      <c r="P63" s="6" t="n">
         <v>89.13</v>
       </c>
-      <c r="Q63" s="7" t="n">
+      <c r="Q63" s="6" t="n">
         <v>89.98</v>
       </c>
-      <c r="R63" s="7" t="n">
+      <c r="R63" s="6" t="n">
         <v>94.06999999999999</v>
       </c>
-      <c r="S63" s="7" t="n">
+      <c r="S63" s="6" t="n">
         <v>94.25</v>
       </c>
-      <c r="T63" s="7" t="n">
+      <c r="T63" s="6" t="n">
         <v>92.77</v>
       </c>
-      <c r="U63" s="7" t="n">
+      <c r="U63" s="6" t="n">
         <v>93.7</v>
       </c>
-      <c r="V63" s="7" t="n">
+      <c r="V63" s="6" t="n">
         <v>91.33</v>
       </c>
-      <c r="W63" s="7" t="n">
+      <c r="W63" s="6" t="n">
         <v>87.59999999999999</v>
       </c>
-      <c r="X63" s="7" t="n">
+      <c r="X63" s="6" t="n">
         <v>86.08</v>
       </c>
-      <c r="Y63" s="7" t="n">
+      <c r="Y63" s="6" t="n">
         <v>85.33</v>
       </c>
-      <c r="Z63" s="7" t="n">
+      <c r="Z63" s="6" t="n">
         <v>81.62</v>
       </c>
-      <c r="AA63" s="7" t="n">
+      <c r="AA63" s="6" t="n">
         <v>84.37</v>
       </c>
-      <c r="AB63" s="7" t="n">
+      <c r="AB63" s="6" t="n">
         <v>86.25</v>
       </c>
-      <c r="AC63" s="7" t="n">
+      <c r="AC63" s="6" t="n">
         <v>83.97</v>
       </c>
-      <c r="AD63" s="7" t="n">
+      <c r="AD63" s="6" t="n">
         <v>79.47</v>
       </c>
-      <c r="AE63" s="7" t="n">
+      <c r="AE63" s="6" t="n">
         <v>83.92</v>
       </c>
-      <c r="AF63" s="7" t="n">
+      <c r="AF63" s="6" t="n">
         <v>89.75</v>
       </c>
-      <c r="AG63" s="7" t="n">
+      <c r="AG63" s="6" t="n">
         <v>93.13</v>
       </c>
       <c r="AH63" s="6" t="n">
@@ -5864,7 +5834,7 @@
       </c>
       <c r="AI63" s="6" t="inlineStr"/>
       <c r="AJ63" s="6" t="inlineStr"/>
-      <c r="AK63" s="15" t="n"/>
+      <c r="AK63" s="12" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -5875,97 +5845,97 @@
       <c r="B64" s="6" t="n">
         <v>77.25</v>
       </c>
-      <c r="C64" s="7" t="n">
+      <c r="C64" s="6" t="n">
         <v>78.43000000000001</v>
       </c>
-      <c r="D64" s="7" t="n">
+      <c r="D64" s="6" t="n">
         <v>77.95</v>
       </c>
-      <c r="E64" s="7" t="n">
+      <c r="E64" s="6" t="n">
         <v>82.13</v>
       </c>
-      <c r="F64" s="7" t="n">
+      <c r="F64" s="6" t="n">
         <v>81</v>
       </c>
-      <c r="G64" s="7" t="n">
+      <c r="G64" s="6" t="n">
         <v>88.90000000000001</v>
       </c>
-      <c r="H64" s="7" t="n">
+      <c r="H64" s="6" t="n">
         <v>86.87</v>
       </c>
-      <c r="I64" s="7" t="n">
+      <c r="I64" s="6" t="n">
         <v>88.59999999999999</v>
       </c>
-      <c r="J64" s="7" t="n">
+      <c r="J64" s="6" t="n">
         <v>85.5</v>
       </c>
-      <c r="K64" s="7" t="n">
+      <c r="K64" s="6" t="n">
         <v>84.95</v>
       </c>
-      <c r="L64" s="7" t="n">
+      <c r="L64" s="6" t="n">
         <v>85.81999999999999</v>
       </c>
-      <c r="M64" s="7" t="n">
+      <c r="M64" s="6" t="n">
         <v>88.28</v>
       </c>
-      <c r="N64" s="7" t="n">
+      <c r="N64" s="6" t="n">
         <v>86.15000000000001</v>
       </c>
-      <c r="O64" s="7" t="n">
+      <c r="O64" s="6" t="n">
         <v>88.15000000000001</v>
       </c>
-      <c r="P64" s="7" t="n">
+      <c r="P64" s="6" t="n">
         <v>88.84999999999999</v>
       </c>
-      <c r="Q64" s="7" t="n">
+      <c r="Q64" s="6" t="n">
         <v>83.38</v>
       </c>
-      <c r="R64" s="7" t="n">
+      <c r="R64" s="6" t="n">
         <v>86.23</v>
       </c>
-      <c r="S64" s="7" t="n">
+      <c r="S64" s="6" t="n">
         <v>86.43000000000001</v>
       </c>
-      <c r="T64" s="7" t="n">
+      <c r="T64" s="6" t="n">
         <v>81.55</v>
       </c>
-      <c r="U64" s="7" t="n">
+      <c r="U64" s="6" t="n">
         <v>82.25</v>
       </c>
-      <c r="V64" s="7" t="n">
+      <c r="V64" s="6" t="n">
         <v>88.13</v>
       </c>
-      <c r="W64" s="7" t="n">
+      <c r="W64" s="6" t="n">
         <v>87.98</v>
       </c>
-      <c r="X64" s="7" t="n">
+      <c r="X64" s="6" t="n">
         <v>85.22</v>
       </c>
-      <c r="Y64" s="7" t="n">
+      <c r="Y64" s="6" t="n">
         <v>82.53</v>
       </c>
-      <c r="Z64" s="7" t="n">
+      <c r="Z64" s="6" t="n">
         <v>84.78</v>
       </c>
-      <c r="AA64" s="7" t="n">
+      <c r="AA64" s="6" t="n">
         <v>75.37</v>
       </c>
-      <c r="AB64" s="7" t="n">
+      <c r="AB64" s="6" t="n">
         <v>75.09999999999999</v>
       </c>
-      <c r="AC64" s="7" t="n">
+      <c r="AC64" s="6" t="n">
         <v>77.83</v>
       </c>
-      <c r="AD64" s="7" t="n">
+      <c r="AD64" s="6" t="n">
         <v>80.78</v>
       </c>
-      <c r="AE64" s="7" t="n">
+      <c r="AE64" s="6" t="n">
         <v>73.13</v>
       </c>
-      <c r="AF64" s="7" t="n">
+      <c r="AF64" s="6" t="n">
         <v>71</v>
       </c>
-      <c r="AG64" s="7" t="n">
+      <c r="AG64" s="6" t="n">
         <v>81.65000000000001</v>
       </c>
       <c r="AH64" s="6" t="n">
@@ -5973,7 +5943,7 @@
       </c>
       <c r="AI64" s="6" t="inlineStr"/>
       <c r="AJ64" s="6" t="inlineStr"/>
-      <c r="AK64" s="15" t="n"/>
+      <c r="AK64" s="12" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -5984,97 +5954,97 @@
       <c r="B65" s="6" t="n">
         <v>175.25</v>
       </c>
-      <c r="C65" s="7" t="n">
+      <c r="C65" s="6" t="n">
         <v>91.97</v>
       </c>
-      <c r="D65" s="7" t="n">
+      <c r="D65" s="6" t="n">
         <v>92.06999999999999</v>
       </c>
-      <c r="E65" s="7" t="n">
+      <c r="E65" s="6" t="n">
         <v>92.53</v>
       </c>
-      <c r="F65" s="7" t="n">
+      <c r="F65" s="6" t="n">
         <v>94.15000000000001</v>
       </c>
-      <c r="G65" s="7" t="n">
+      <c r="G65" s="6" t="n">
         <v>94.17</v>
       </c>
-      <c r="H65" s="7" t="n">
+      <c r="H65" s="6" t="n">
         <v>94.52</v>
       </c>
-      <c r="I65" s="7" t="n">
+      <c r="I65" s="6" t="n">
         <v>94.59999999999999</v>
       </c>
-      <c r="J65" s="7" t="n">
+      <c r="J65" s="6" t="n">
         <v>94.53</v>
       </c>
-      <c r="K65" s="7" t="n">
+      <c r="K65" s="6" t="n">
         <v>92.12</v>
       </c>
-      <c r="L65" s="7" t="n">
+      <c r="L65" s="6" t="n">
         <v>88.5</v>
       </c>
-      <c r="M65" s="7" t="n">
+      <c r="M65" s="6" t="n">
         <v>89.97</v>
       </c>
-      <c r="N65" s="7" t="n">
+      <c r="N65" s="6" t="n">
         <v>94.43000000000001</v>
       </c>
-      <c r="O65" s="7" t="n">
+      <c r="O65" s="6" t="n">
         <v>93.95</v>
       </c>
-      <c r="P65" s="7" t="n">
+      <c r="P65" s="6" t="n">
         <v>93.98</v>
       </c>
-      <c r="Q65" s="7" t="n">
+      <c r="Q65" s="6" t="n">
         <v>94.02</v>
       </c>
-      <c r="R65" s="7" t="n">
+      <c r="R65" s="6" t="n">
         <v>95</v>
       </c>
-      <c r="S65" s="7" t="n">
+      <c r="S65" s="6" t="n">
         <v>95.06999999999999</v>
       </c>
-      <c r="T65" s="7" t="n">
+      <c r="T65" s="6" t="n">
         <v>91.95</v>
       </c>
-      <c r="U65" s="7" t="n">
+      <c r="U65" s="6" t="n">
         <v>95.92</v>
       </c>
-      <c r="V65" s="7" t="n">
+      <c r="V65" s="6" t="n">
         <v>94.37</v>
       </c>
-      <c r="W65" s="7" t="n">
+      <c r="W65" s="6" t="n">
         <v>92.59999999999999</v>
       </c>
-      <c r="X65" s="7" t="n">
+      <c r="X65" s="6" t="n">
         <v>90.56999999999999</v>
       </c>
-      <c r="Y65" s="7" t="n">
+      <c r="Y65" s="6" t="n">
         <v>90.02</v>
       </c>
-      <c r="Z65" s="7" t="n">
+      <c r="Z65" s="6" t="n">
         <v>90.7</v>
       </c>
-      <c r="AA65" s="7" t="n">
+      <c r="AA65" s="6" t="n">
         <v>89.25</v>
       </c>
-      <c r="AB65" s="7" t="n">
+      <c r="AB65" s="6" t="n">
         <v>90.03</v>
       </c>
-      <c r="AC65" s="7" t="n">
+      <c r="AC65" s="6" t="n">
         <v>90.34999999999999</v>
       </c>
-      <c r="AD65" s="7" t="n">
+      <c r="AD65" s="6" t="n">
         <v>89.88</v>
       </c>
-      <c r="AE65" s="7" t="n">
+      <c r="AE65" s="6" t="n">
         <v>89.15000000000001</v>
       </c>
-      <c r="AF65" s="7" t="n">
+      <c r="AF65" s="6" t="n">
         <v>91.33</v>
       </c>
-      <c r="AG65" s="7" t="n">
+      <c r="AG65" s="6" t="n">
         <v>95.03</v>
       </c>
       <c r="AH65" s="6" t="n">
@@ -6082,7 +6052,7 @@
       </c>
       <c r="AI65" s="6" t="inlineStr"/>
       <c r="AJ65" s="6" t="inlineStr"/>
-      <c r="AK65" s="15" t="n"/>
+      <c r="AK65" s="12" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -6093,97 +6063,97 @@
       <c r="B66" s="6" t="n">
         <v>181.25</v>
       </c>
-      <c r="C66" s="7" t="n">
+      <c r="C66" s="6" t="n">
         <v>80.13</v>
       </c>
-      <c r="D66" s="7" t="n">
+      <c r="D66" s="6" t="n">
         <v>79.77</v>
       </c>
-      <c r="E66" s="7" t="n">
+      <c r="E66" s="6" t="n">
         <v>77.02</v>
       </c>
-      <c r="F66" s="7" t="n">
+      <c r="F66" s="6" t="n">
         <v>78.45</v>
       </c>
-      <c r="G66" s="7" t="n">
+      <c r="G66" s="6" t="n">
         <v>78.38</v>
       </c>
-      <c r="H66" s="7" t="n">
+      <c r="H66" s="6" t="n">
         <v>79.77</v>
       </c>
-      <c r="I66" s="7" t="n">
+      <c r="I66" s="6" t="n">
         <v>79.95</v>
       </c>
-      <c r="J66" s="7" t="n">
+      <c r="J66" s="6" t="n">
         <v>80.28</v>
       </c>
-      <c r="K66" s="7" t="n">
+      <c r="K66" s="6" t="n">
         <v>79.28</v>
       </c>
-      <c r="L66" s="7" t="n">
+      <c r="L66" s="6" t="n">
         <v>78.72</v>
       </c>
-      <c r="M66" s="7" t="n">
+      <c r="M66" s="6" t="n">
         <v>77.90000000000001</v>
       </c>
-      <c r="N66" s="7" t="n">
+      <c r="N66" s="6" t="n">
         <v>81.45</v>
       </c>
-      <c r="O66" s="7" t="n">
+      <c r="O66" s="6" t="n">
         <v>80.13</v>
       </c>
-      <c r="P66" s="7" t="n">
+      <c r="P66" s="6" t="n">
         <v>81</v>
       </c>
-      <c r="Q66" s="7" t="n">
+      <c r="Q66" s="6" t="n">
         <v>81.15000000000001</v>
       </c>
-      <c r="R66" s="7" t="n">
+      <c r="R66" s="6" t="n">
         <v>82.13</v>
       </c>
-      <c r="S66" s="7" t="n">
+      <c r="S66" s="6" t="n">
         <v>81.15000000000001</v>
       </c>
-      <c r="T66" s="7" t="n">
+      <c r="T66" s="6" t="n">
         <v>80.42</v>
       </c>
-      <c r="U66" s="7" t="n">
+      <c r="U66" s="6" t="n">
         <v>79.87</v>
       </c>
-      <c r="V66" s="7" t="n">
+      <c r="V66" s="6" t="n">
         <v>84.87</v>
       </c>
-      <c r="W66" s="7" t="n">
+      <c r="W66" s="6" t="n">
         <v>82.87</v>
       </c>
-      <c r="X66" s="7" t="n">
+      <c r="X66" s="6" t="n">
         <v>80.48</v>
       </c>
-      <c r="Y66" s="7" t="n">
+      <c r="Y66" s="6" t="n">
         <v>82.17</v>
       </c>
-      <c r="Z66" s="7" t="n">
+      <c r="Z66" s="6" t="n">
         <v>83.45</v>
       </c>
-      <c r="AA66" s="7" t="n">
+      <c r="AA66" s="6" t="n">
         <v>80.7</v>
       </c>
-      <c r="AB66" s="7" t="n">
+      <c r="AB66" s="6" t="n">
         <v>81.31999999999999</v>
       </c>
-      <c r="AC66" s="7" t="n">
+      <c r="AC66" s="6" t="n">
         <v>81.65000000000001</v>
       </c>
-      <c r="AD66" s="7" t="n">
+      <c r="AD66" s="6" t="n">
         <v>82.7</v>
       </c>
-      <c r="AE66" s="7" t="n">
+      <c r="AE66" s="6" t="n">
         <v>83.06999999999999</v>
       </c>
-      <c r="AF66" s="7" t="n">
+      <c r="AF66" s="6" t="n">
         <v>84.22</v>
       </c>
-      <c r="AG66" s="7" t="n">
+      <c r="AG66" s="6" t="n">
         <v>86.5</v>
       </c>
       <c r="AH66" s="6" t="n">
@@ -6191,7 +6161,7 @@
       </c>
       <c r="AI66" s="6" t="inlineStr"/>
       <c r="AJ66" s="6" t="inlineStr"/>
-      <c r="AK66" s="15" t="n"/>
+      <c r="AK66" s="12" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -6202,97 +6172,97 @@
       <c r="B67" s="6" t="n">
         <v>187.25</v>
       </c>
-      <c r="C67" s="7" t="n">
+      <c r="C67" s="6" t="n">
         <v>88</v>
       </c>
-      <c r="D67" s="7" t="n">
+      <c r="D67" s="6" t="n">
         <v>87.87</v>
       </c>
-      <c r="E67" s="7" t="n">
+      <c r="E67" s="6" t="n">
         <v>90.37</v>
       </c>
-      <c r="F67" s="7" t="n">
+      <c r="F67" s="6" t="n">
         <v>89.15000000000001</v>
       </c>
-      <c r="G67" s="7" t="n">
+      <c r="G67" s="6" t="n">
         <v>89.31999999999999</v>
       </c>
-      <c r="H67" s="7" t="n">
+      <c r="H67" s="6" t="n">
         <v>89.45</v>
       </c>
-      <c r="I67" s="7" t="n">
+      <c r="I67" s="6" t="n">
         <v>89.03</v>
       </c>
-      <c r="J67" s="7" t="n">
+      <c r="J67" s="6" t="n">
         <v>88.2</v>
       </c>
-      <c r="K67" s="7" t="n">
+      <c r="K67" s="6" t="n">
         <v>91.17</v>
       </c>
-      <c r="L67" s="7" t="n">
+      <c r="L67" s="6" t="n">
         <v>93.93000000000001</v>
       </c>
-      <c r="M67" s="7" t="n">
+      <c r="M67" s="6" t="n">
         <v>92.55</v>
       </c>
-      <c r="N67" s="7" t="n">
+      <c r="N67" s="6" t="n">
         <v>89.2</v>
       </c>
-      <c r="O67" s="7" t="n">
+      <c r="O67" s="6" t="n">
         <v>89.72</v>
       </c>
-      <c r="P67" s="7" t="n">
+      <c r="P67" s="6" t="n">
         <v>90.22</v>
       </c>
-      <c r="Q67" s="7" t="n">
+      <c r="Q67" s="6" t="n">
         <v>90.2</v>
       </c>
-      <c r="R67" s="7" t="n">
+      <c r="R67" s="6" t="n">
         <v>89.56999999999999</v>
       </c>
-      <c r="S67" s="7" t="n">
+      <c r="S67" s="6" t="n">
         <v>89.03</v>
       </c>
-      <c r="T67" s="7" t="n">
+      <c r="T67" s="6" t="n">
         <v>89.34999999999999</v>
       </c>
-      <c r="U67" s="7" t="n">
+      <c r="U67" s="6" t="n">
         <v>89.78</v>
       </c>
-      <c r="V67" s="7" t="n">
+      <c r="V67" s="6" t="n">
         <v>89.78</v>
       </c>
-      <c r="W67" s="7" t="n">
+      <c r="W67" s="6" t="n">
         <v>91.87</v>
       </c>
-      <c r="X67" s="7" t="n">
+      <c r="X67" s="6" t="n">
         <v>94.08</v>
       </c>
-      <c r="Y67" s="7" t="n">
+      <c r="Y67" s="6" t="n">
         <v>94.45</v>
       </c>
-      <c r="Z67" s="7" t="n">
+      <c r="Z67" s="6" t="n">
         <v>94.65000000000001</v>
       </c>
-      <c r="AA67" s="7" t="n">
+      <c r="AA67" s="6" t="n">
         <v>94</v>
       </c>
-      <c r="AB67" s="7" t="n">
+      <c r="AB67" s="6" t="n">
         <v>93.73</v>
       </c>
-      <c r="AC67" s="7" t="n">
+      <c r="AC67" s="6" t="n">
         <v>93.92</v>
       </c>
-      <c r="AD67" s="7" t="n">
+      <c r="AD67" s="6" t="n">
         <v>94.31999999999999</v>
       </c>
-      <c r="AE67" s="7" t="n">
+      <c r="AE67" s="6" t="n">
         <v>94.02</v>
       </c>
-      <c r="AF67" s="7" t="n">
+      <c r="AF67" s="6" t="n">
         <v>92.17</v>
       </c>
-      <c r="AG67" s="7" t="n">
+      <c r="AG67" s="6" t="n">
         <v>90.22</v>
       </c>
       <c r="AH67" s="6" t="n">
@@ -6300,7 +6270,7 @@
       </c>
       <c r="AI67" s="6" t="inlineStr"/>
       <c r="AJ67" s="6" t="inlineStr"/>
-      <c r="AK67" s="15" t="n"/>
+      <c r="AK67" s="12" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -6311,97 +6281,97 @@
       <c r="B68" s="6" t="n">
         <v>199.25</v>
       </c>
-      <c r="C68" s="7" t="n">
+      <c r="C68" s="6" t="n">
         <v>67.97</v>
       </c>
-      <c r="D68" s="7" t="n">
+      <c r="D68" s="6" t="n">
         <v>67.75</v>
       </c>
-      <c r="E68" s="7" t="n">
+      <c r="E68" s="6" t="n">
         <v>70.25</v>
       </c>
-      <c r="F68" s="7" t="n">
+      <c r="F68" s="6" t="n">
         <v>70.18000000000001</v>
       </c>
-      <c r="G68" s="7" t="n">
+      <c r="G68" s="6" t="n">
         <v>69.31999999999999</v>
       </c>
-      <c r="H68" s="7" t="n">
+      <c r="H68" s="6" t="n">
         <v>70.72</v>
       </c>
-      <c r="I68" s="7" t="n">
+      <c r="I68" s="6" t="n">
         <v>71.78</v>
       </c>
-      <c r="J68" s="7" t="n">
+      <c r="J68" s="6" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="K68" s="7" t="n">
+      <c r="K68" s="6" t="n">
         <v>68.25</v>
       </c>
-      <c r="L68" s="7" t="n">
+      <c r="L68" s="6" t="n">
         <v>65.83</v>
       </c>
-      <c r="M68" s="7" t="n">
+      <c r="M68" s="6" t="n">
         <v>67.34999999999999</v>
       </c>
-      <c r="N68" s="7" t="n">
+      <c r="N68" s="6" t="n">
         <v>72.52</v>
       </c>
-      <c r="O68" s="7" t="n">
+      <c r="O68" s="6" t="n">
         <v>71.33</v>
       </c>
-      <c r="P68" s="7" t="n">
+      <c r="P68" s="6" t="n">
         <v>72.13</v>
       </c>
-      <c r="Q68" s="7" t="n">
+      <c r="Q68" s="6" t="n">
         <v>70.43000000000001</v>
       </c>
-      <c r="R68" s="7" t="n">
+      <c r="R68" s="6" t="n">
         <v>70.83</v>
       </c>
-      <c r="S68" s="7" t="n">
+      <c r="S68" s="6" t="n">
         <v>72.3</v>
       </c>
-      <c r="T68" s="7" t="n">
+      <c r="T68" s="6" t="n">
         <v>69.37</v>
       </c>
-      <c r="U68" s="7" t="n">
+      <c r="U68" s="6" t="n">
         <v>71.59999999999999</v>
       </c>
-      <c r="V68" s="7" t="n">
+      <c r="V68" s="6" t="n">
         <v>70.43000000000001</v>
       </c>
-      <c r="W68" s="7" t="n">
+      <c r="W68" s="6" t="n">
         <v>68.2</v>
       </c>
-      <c r="X68" s="7" t="n">
+      <c r="X68" s="6" t="n">
         <v>65.47</v>
       </c>
-      <c r="Y68" s="7" t="n">
+      <c r="Y68" s="6" t="n">
         <v>64.65000000000001</v>
       </c>
-      <c r="Z68" s="7" t="n">
+      <c r="Z68" s="6" t="n">
         <v>65.03</v>
       </c>
-      <c r="AA68" s="7" t="n">
+      <c r="AA68" s="6" t="n">
         <v>64.8</v>
       </c>
-      <c r="AB68" s="7" t="n">
+      <c r="AB68" s="6" t="n">
         <v>65.42</v>
       </c>
-      <c r="AC68" s="7" t="n">
+      <c r="AC68" s="6" t="n">
         <v>65.77</v>
       </c>
-      <c r="AD68" s="7" t="n">
+      <c r="AD68" s="6" t="n">
         <v>65.05</v>
       </c>
-      <c r="AE68" s="7" t="n">
+      <c r="AE68" s="6" t="n">
         <v>66.34999999999999</v>
       </c>
-      <c r="AF68" s="7" t="n">
+      <c r="AF68" s="6" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="AG68" s="7" t="n">
+      <c r="AG68" s="6" t="n">
         <v>74.7</v>
       </c>
       <c r="AH68" s="6" t="n">
@@ -6409,7 +6379,7 @@
       </c>
       <c r="AI68" s="6" t="inlineStr"/>
       <c r="AJ68" s="6" t="inlineStr"/>
-      <c r="AK68" s="15" t="n"/>
+      <c r="AK68" s="12" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -6420,97 +6390,97 @@
       <c r="B69" s="6" t="n">
         <v>519.25</v>
       </c>
-      <c r="C69" s="7" t="n">
+      <c r="C69" s="6" t="n">
         <v>84.31999999999999</v>
       </c>
-      <c r="D69" s="7" t="n">
+      <c r="D69" s="6" t="n">
         <v>83.48</v>
       </c>
-      <c r="E69" s="7" t="n">
+      <c r="E69" s="6" t="n">
         <v>83.25</v>
       </c>
-      <c r="F69" s="7" t="n">
+      <c r="F69" s="6" t="n">
         <v>83.02</v>
       </c>
-      <c r="G69" s="7" t="n">
+      <c r="G69" s="6" t="n">
         <v>83.56999999999999</v>
       </c>
-      <c r="H69" s="7" t="n">
+      <c r="H69" s="6" t="n">
         <v>83.67</v>
       </c>
-      <c r="I69" s="7" t="n">
+      <c r="I69" s="6" t="n">
         <v>84.25</v>
       </c>
-      <c r="J69" s="7" t="n">
+      <c r="J69" s="6" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="K69" s="7" t="n">
+      <c r="K69" s="6" t="n">
         <v>81.27</v>
       </c>
-      <c r="L69" s="7" t="n">
+      <c r="L69" s="6" t="n">
         <v>79.15000000000001</v>
       </c>
-      <c r="M69" s="7" t="n">
+      <c r="M69" s="6" t="n">
         <v>82</v>
       </c>
-      <c r="N69" s="7" t="n">
+      <c r="N69" s="6" t="n">
         <v>82.68000000000001</v>
       </c>
-      <c r="O69" s="7" t="n">
+      <c r="O69" s="6" t="n">
         <v>83.15000000000001</v>
       </c>
-      <c r="P69" s="7" t="n">
+      <c r="P69" s="6" t="n">
         <v>83.65000000000001</v>
       </c>
-      <c r="Q69" s="7" t="n">
+      <c r="Q69" s="6" t="n">
         <v>83.8</v>
       </c>
-      <c r="R69" s="7" t="n">
+      <c r="R69" s="6" t="n">
         <v>83.75</v>
       </c>
-      <c r="S69" s="7" t="n">
+      <c r="S69" s="6" t="n">
         <v>83.84999999999999</v>
       </c>
-      <c r="T69" s="7" t="n">
+      <c r="T69" s="6" t="n">
         <v>83.2</v>
       </c>
-      <c r="U69" s="7" t="n">
+      <c r="U69" s="6" t="n">
         <v>83.33</v>
       </c>
-      <c r="V69" s="7" t="n">
+      <c r="V69" s="6" t="n">
         <v>83.95</v>
       </c>
-      <c r="W69" s="7" t="n">
+      <c r="W69" s="6" t="n">
         <v>82.31999999999999</v>
       </c>
-      <c r="X69" s="7" t="n">
+      <c r="X69" s="6" t="n">
         <v>78.5</v>
       </c>
-      <c r="Y69" s="7" t="n">
+      <c r="Y69" s="6" t="n">
         <v>77.97</v>
       </c>
-      <c r="Z69" s="7" t="n">
+      <c r="Z69" s="6" t="n">
         <v>75.37</v>
       </c>
-      <c r="AA69" s="7" t="n">
+      <c r="AA69" s="6" t="n">
         <v>80.13</v>
       </c>
-      <c r="AB69" s="7" t="n">
+      <c r="AB69" s="6" t="n">
         <v>79.25</v>
       </c>
-      <c r="AC69" s="7" t="n">
+      <c r="AC69" s="6" t="n">
         <v>79.8</v>
       </c>
-      <c r="AD69" s="7" t="n">
+      <c r="AD69" s="6" t="n">
         <v>77.13</v>
       </c>
-      <c r="AE69" s="7" t="n">
+      <c r="AE69" s="6" t="n">
         <v>78.34999999999999</v>
       </c>
-      <c r="AF69" s="7" t="n">
+      <c r="AF69" s="6" t="n">
         <v>81.37</v>
       </c>
-      <c r="AG69" s="7" t="n">
+      <c r="AG69" s="6" t="n">
         <v>84.68000000000001</v>
       </c>
       <c r="AH69" s="6" t="n">
@@ -6518,7 +6488,7 @@
       </c>
       <c r="AI69" s="6" t="inlineStr"/>
       <c r="AJ69" s="6" t="inlineStr"/>
-      <c r="AK69" s="15" t="n"/>
+      <c r="AK69" s="12" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -6529,97 +6499,97 @@
       <c r="B70" s="6" t="n">
         <v>531.25</v>
       </c>
-      <c r="C70" s="16" t="n">
+      <c r="C70" s="6" t="n">
         <v>28.37</v>
       </c>
-      <c r="D70" s="16" t="n">
+      <c r="D70" s="6" t="n">
         <v>29.4</v>
       </c>
-      <c r="E70" s="16" t="n">
+      <c r="E70" s="6" t="n">
         <v>27.83</v>
       </c>
-      <c r="F70" s="16" t="n">
+      <c r="F70" s="6" t="n">
         <v>28.55</v>
       </c>
-      <c r="G70" s="16" t="n">
+      <c r="G70" s="6" t="n">
         <v>28.55</v>
       </c>
-      <c r="H70" s="16" t="n">
+      <c r="H70" s="6" t="n">
         <v>27.95</v>
       </c>
-      <c r="I70" s="16" t="n">
+      <c r="I70" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="J70" s="16" t="n">
+      <c r="J70" s="6" t="n">
         <v>28.12</v>
       </c>
-      <c r="K70" s="16" t="n">
+      <c r="K70" s="6" t="n">
         <v>33.42</v>
       </c>
-      <c r="L70" s="16" t="n">
+      <c r="L70" s="6" t="n">
         <v>38.92</v>
       </c>
-      <c r="M70" s="16" t="n">
+      <c r="M70" s="6" t="n">
         <v>34.12</v>
       </c>
-      <c r="N70" s="16" t="n">
+      <c r="N70" s="6" t="n">
         <v>28.75</v>
       </c>
-      <c r="O70" s="16" t="n">
+      <c r="O70" s="6" t="n">
         <v>28.63</v>
       </c>
-      <c r="P70" s="16" t="n">
+      <c r="P70" s="6" t="n">
         <v>27.68</v>
       </c>
-      <c r="Q70" s="16" t="n">
+      <c r="Q70" s="6" t="n">
         <v>28.35</v>
       </c>
-      <c r="R70" s="16" t="n">
+      <c r="R70" s="6" t="n">
         <v>27.93</v>
       </c>
-      <c r="S70" s="16" t="n">
+      <c r="S70" s="6" t="n">
         <v>28.22</v>
       </c>
-      <c r="T70" s="16" t="n">
+      <c r="T70" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="U70" s="16" t="n">
+      <c r="U70" s="6" t="n">
         <v>28.68</v>
       </c>
-      <c r="V70" s="16" t="n">
+      <c r="V70" s="6" t="n">
         <v>27.77</v>
       </c>
-      <c r="W70" s="16" t="n">
+      <c r="W70" s="6" t="n">
         <v>33.18</v>
       </c>
-      <c r="X70" s="16" t="n">
+      <c r="X70" s="6" t="n">
         <v>39.05</v>
       </c>
-      <c r="Y70" s="16" t="n">
+      <c r="Y70" s="6" t="n">
         <v>39.05</v>
       </c>
-      <c r="Z70" s="16" t="n">
+      <c r="Z70" s="6" t="n">
         <v>38.88</v>
       </c>
-      <c r="AA70" s="16" t="n">
+      <c r="AA70" s="6" t="n">
         <v>38.68</v>
       </c>
-      <c r="AB70" s="16" t="n">
+      <c r="AB70" s="6" t="n">
         <v>38.78</v>
       </c>
-      <c r="AC70" s="16" t="n">
+      <c r="AC70" s="6" t="n">
         <v>39.45</v>
       </c>
-      <c r="AD70" s="16" t="n">
+      <c r="AD70" s="6" t="n">
         <v>38.48</v>
       </c>
-      <c r="AE70" s="16" t="n">
+      <c r="AE70" s="6" t="n">
         <v>39.23</v>
       </c>
-      <c r="AF70" s="16" t="n">
+      <c r="AF70" s="6" t="n">
         <v>33.83</v>
       </c>
-      <c r="AG70" s="16" t="n">
+      <c r="AG70" s="6" t="n">
         <v>28.65</v>
       </c>
       <c r="AH70" s="6" t="n">
@@ -6627,7 +6597,7 @@
       </c>
       <c r="AI70" s="6" t="inlineStr"/>
       <c r="AJ70" s="6" t="inlineStr"/>
-      <c r="AK70" s="15" t="n"/>
+      <c r="AK70" s="12" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -6638,97 +6608,97 @@
       <c r="B71" s="6" t="n">
         <v>537.25</v>
       </c>
-      <c r="C71" s="7" t="n">
+      <c r="C71" s="6" t="n">
         <v>67.88</v>
       </c>
-      <c r="D71" s="7" t="n">
+      <c r="D71" s="6" t="n">
         <v>67.90000000000001</v>
       </c>
-      <c r="E71" s="7" t="n">
+      <c r="E71" s="6" t="n">
         <v>68.84999999999999</v>
       </c>
-      <c r="F71" s="7" t="n">
+      <c r="F71" s="6" t="n">
         <v>68.3</v>
       </c>
-      <c r="G71" s="7" t="n">
+      <c r="G71" s="6" t="n">
         <v>67.59999999999999</v>
       </c>
-      <c r="H71" s="7" t="n">
+      <c r="H71" s="6" t="n">
         <v>66.7</v>
       </c>
-      <c r="I71" s="7" t="n">
+      <c r="I71" s="6" t="n">
         <v>67.18000000000001</v>
       </c>
-      <c r="J71" s="7" t="n">
+      <c r="J71" s="6" t="n">
         <v>66.09999999999999</v>
       </c>
-      <c r="K71" s="7" t="n">
+      <c r="K71" s="6" t="n">
         <v>66.88</v>
       </c>
-      <c r="L71" s="7" t="n">
+      <c r="L71" s="6" t="n">
         <v>68.42</v>
       </c>
-      <c r="M71" s="7" t="n">
+      <c r="M71" s="6" t="n">
         <v>68.22</v>
       </c>
-      <c r="N71" s="7" t="n">
+      <c r="N71" s="6" t="n">
         <v>68.06999999999999</v>
       </c>
-      <c r="O71" s="7" t="n">
+      <c r="O71" s="6" t="n">
         <v>68</v>
       </c>
-      <c r="P71" s="7" t="n">
+      <c r="P71" s="6" t="n">
         <v>68.68000000000001</v>
       </c>
-      <c r="Q71" s="7" t="n">
+      <c r="Q71" s="6" t="n">
         <v>68.65000000000001</v>
       </c>
-      <c r="R71" s="7" t="n">
+      <c r="R71" s="6" t="n">
         <v>70.63</v>
       </c>
-      <c r="S71" s="7" t="n">
+      <c r="S71" s="6" t="n">
         <v>70.2</v>
       </c>
-      <c r="T71" s="7" t="n">
+      <c r="T71" s="6" t="n">
         <v>67.40000000000001</v>
       </c>
-      <c r="U71" s="7" t="n">
+      <c r="U71" s="6" t="n">
         <v>69.95</v>
       </c>
-      <c r="V71" s="7" t="n">
+      <c r="V71" s="6" t="n">
         <v>70.65000000000001</v>
       </c>
-      <c r="W71" s="7" t="n">
+      <c r="W71" s="6" t="n">
         <v>70.73</v>
       </c>
-      <c r="X71" s="7" t="n">
+      <c r="X71" s="6" t="n">
         <v>68.55</v>
       </c>
-      <c r="Y71" s="7" t="n">
+      <c r="Y71" s="6" t="n">
         <v>68.7</v>
       </c>
-      <c r="Z71" s="7" t="n">
+      <c r="Z71" s="6" t="n">
         <v>66.93000000000001</v>
       </c>
-      <c r="AA71" s="7" t="n">
+      <c r="AA71" s="6" t="n">
         <v>68.27</v>
       </c>
-      <c r="AB71" s="7" t="n">
+      <c r="AB71" s="6" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="AC71" s="7" t="n">
+      <c r="AC71" s="6" t="n">
         <v>69.8</v>
       </c>
-      <c r="AD71" s="7" t="n">
+      <c r="AD71" s="6" t="n">
         <v>70.15000000000001</v>
       </c>
-      <c r="AE71" s="7" t="n">
+      <c r="AE71" s="6" t="n">
         <v>69.95</v>
       </c>
-      <c r="AF71" s="7" t="n">
+      <c r="AF71" s="6" t="n">
         <v>69.75</v>
       </c>
-      <c r="AG71" s="7" t="n">
+      <c r="AG71" s="6" t="n">
         <v>72</v>
       </c>
       <c r="AH71" s="6" t="n">
@@ -6736,7 +6706,7 @@
       </c>
       <c r="AI71" s="6" t="inlineStr"/>
       <c r="AJ71" s="6" t="inlineStr"/>
-      <c r="AK71" s="15" t="n"/>
+      <c r="AK71" s="12" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -6747,97 +6717,97 @@
       <c r="B72" s="6" t="n">
         <v>543.25</v>
       </c>
-      <c r="C72" s="16" t="n">
+      <c r="C72" s="6" t="n">
         <v>30.25</v>
       </c>
-      <c r="D72" s="16" t="n">
+      <c r="D72" s="6" t="n">
         <v>28.95</v>
       </c>
-      <c r="E72" s="16" t="n">
+      <c r="E72" s="6" t="n">
         <v>29.82</v>
       </c>
-      <c r="F72" s="16" t="n">
+      <c r="F72" s="6" t="n">
         <v>30.2</v>
       </c>
-      <c r="G72" s="16" t="n">
+      <c r="G72" s="6" t="n">
         <v>30.07</v>
       </c>
-      <c r="H72" s="16" t="n">
+      <c r="H72" s="6" t="n">
         <v>29.28</v>
       </c>
-      <c r="I72" s="16" t="n">
+      <c r="I72" s="6" t="n">
         <v>29.25</v>
       </c>
-      <c r="J72" s="16" t="n">
+      <c r="J72" s="6" t="n">
         <v>30.22</v>
       </c>
-      <c r="K72" s="16" t="n">
+      <c r="K72" s="6" t="n">
         <v>35.05</v>
       </c>
-      <c r="L72" s="16" t="n">
+      <c r="L72" s="6" t="n">
         <v>39.5</v>
       </c>
-      <c r="M72" s="16" t="n">
+      <c r="M72" s="6" t="n">
         <v>34.93</v>
       </c>
-      <c r="N72" s="16" t="n">
+      <c r="N72" s="6" t="n">
         <v>31.55</v>
       </c>
-      <c r="O72" s="16" t="n">
+      <c r="O72" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="P72" s="16" t="n">
+      <c r="P72" s="6" t="n">
         <v>29.75</v>
       </c>
-      <c r="Q72" s="16" t="n">
+      <c r="Q72" s="6" t="n">
         <v>29.25</v>
       </c>
-      <c r="R72" s="16" t="n">
+      <c r="R72" s="6" t="n">
         <v>30.48</v>
       </c>
-      <c r="S72" s="16" t="n">
+      <c r="S72" s="6" t="n">
         <v>30.13</v>
       </c>
-      <c r="T72" s="16" t="n">
+      <c r="T72" s="6" t="n">
         <v>29.78</v>
       </c>
-      <c r="U72" s="16" t="n">
+      <c r="U72" s="6" t="n">
         <v>33.47</v>
       </c>
-      <c r="V72" s="16" t="n">
+      <c r="V72" s="6" t="n">
         <v>29.87</v>
       </c>
-      <c r="W72" s="16" t="n">
+      <c r="W72" s="6" t="n">
         <v>34.4</v>
       </c>
-      <c r="X72" s="16" t="n">
+      <c r="X72" s="6" t="n">
         <v>38.93</v>
       </c>
-      <c r="Y72" s="16" t="n">
+      <c r="Y72" s="6" t="n">
         <v>39.37</v>
       </c>
-      <c r="Z72" s="16" t="n">
+      <c r="Z72" s="6" t="n">
         <v>39.2</v>
       </c>
-      <c r="AA72" s="16" t="n">
+      <c r="AA72" s="6" t="n">
         <v>38.98</v>
       </c>
-      <c r="AB72" s="16" t="n">
+      <c r="AB72" s="6" t="n">
         <v>40.15</v>
       </c>
-      <c r="AC72" s="16" t="n">
+      <c r="AC72" s="6" t="n">
         <v>39.25</v>
       </c>
-      <c r="AD72" s="16" t="n">
+      <c r="AD72" s="6" t="n">
         <v>39.2</v>
       </c>
-      <c r="AE72" s="16" t="n">
+      <c r="AE72" s="6" t="n">
         <v>39.17</v>
       </c>
-      <c r="AF72" s="16" t="n">
+      <c r="AF72" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="AG72" s="16" t="n">
+      <c r="AG72" s="6" t="n">
         <v>30.6</v>
       </c>
       <c r="AH72" s="6" t="n">
@@ -6845,7 +6815,7 @@
       </c>
       <c r="AI72" s="6" t="inlineStr"/>
       <c r="AJ72" s="6" t="inlineStr"/>
-      <c r="AK72" s="15" t="n"/>
+      <c r="AK72" s="12" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -6856,97 +6826,97 @@
       <c r="B73" s="6" t="n">
         <v>567.25</v>
       </c>
-      <c r="C73" s="16" t="n">
+      <c r="C73" s="6" t="n">
         <v>38.72</v>
       </c>
-      <c r="D73" s="16" t="n">
+      <c r="D73" s="6" t="n">
         <v>40.58</v>
       </c>
-      <c r="E73" s="16" t="n">
+      <c r="E73" s="6" t="n">
         <v>39.1</v>
       </c>
-      <c r="F73" s="16" t="n">
+      <c r="F73" s="6" t="n">
         <v>39.9</v>
       </c>
-      <c r="G73" s="16" t="n">
+      <c r="G73" s="6" t="n">
         <v>39.67</v>
       </c>
-      <c r="H73" s="16" t="n">
+      <c r="H73" s="6" t="n">
         <v>40.1</v>
       </c>
-      <c r="I73" s="16" t="n">
+      <c r="I73" s="6" t="n">
         <v>39.85</v>
       </c>
-      <c r="J73" s="16" t="n">
+      <c r="J73" s="6" t="n">
         <v>39.65</v>
       </c>
-      <c r="K73" s="16" t="n">
+      <c r="K73" s="6" t="n">
         <v>39.85</v>
       </c>
-      <c r="L73" s="16" t="n">
+      <c r="L73" s="6" t="n">
         <v>41.55</v>
       </c>
-      <c r="M73" s="16" t="n">
+      <c r="M73" s="6" t="n">
         <v>39.78</v>
       </c>
-      <c r="N73" s="16" t="n">
+      <c r="N73" s="6" t="n">
         <v>40.37</v>
       </c>
-      <c r="O73" s="16" t="n">
+      <c r="O73" s="6" t="n">
         <v>39.98</v>
       </c>
-      <c r="P73" s="16" t="n">
+      <c r="P73" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="Q73" s="16" t="n">
+      <c r="Q73" s="6" t="n">
         <v>40.37</v>
       </c>
-      <c r="R73" s="16" t="n">
+      <c r="R73" s="6" t="n">
         <v>41.43</v>
       </c>
-      <c r="S73" s="16" t="n">
+      <c r="S73" s="6" t="n">
         <v>41.08</v>
       </c>
-      <c r="T73" s="16" t="n">
+      <c r="T73" s="6" t="n">
         <v>41.43</v>
       </c>
-      <c r="U73" s="16" t="n">
+      <c r="U73" s="6" t="n">
         <v>41.27</v>
       </c>
-      <c r="V73" s="16" t="n">
+      <c r="V73" s="6" t="n">
         <v>41.17</v>
       </c>
-      <c r="W73" s="16" t="n">
+      <c r="W73" s="6" t="n">
         <v>42.6</v>
       </c>
-      <c r="X73" s="16" t="n">
+      <c r="X73" s="6" t="n">
         <v>41.62</v>
       </c>
-      <c r="Y73" s="16" t="n">
+      <c r="Y73" s="6" t="n">
         <v>40.92</v>
       </c>
-      <c r="Z73" s="16" t="n">
+      <c r="Z73" s="6" t="n">
         <v>40.37</v>
       </c>
-      <c r="AA73" s="16" t="n">
+      <c r="AA73" s="6" t="n">
         <v>41.32</v>
       </c>
-      <c r="AB73" s="16" t="n">
+      <c r="AB73" s="6" t="n">
         <v>41.38</v>
       </c>
-      <c r="AC73" s="16" t="n">
+      <c r="AC73" s="6" t="n">
         <v>41.15</v>
       </c>
-      <c r="AD73" s="16" t="n">
+      <c r="AD73" s="6" t="n">
         <v>41.08</v>
       </c>
-      <c r="AE73" s="16" t="n">
+      <c r="AE73" s="6" t="n">
         <v>41.33</v>
       </c>
-      <c r="AF73" s="16" t="n">
+      <c r="AF73" s="6" t="n">
         <v>41.33</v>
       </c>
-      <c r="AG73" s="16" t="n">
+      <c r="AG73" s="6" t="n">
         <v>41.08</v>
       </c>
       <c r="AH73" s="6" t="n">
@@ -6954,7 +6924,7 @@
       </c>
       <c r="AI73" s="6" t="inlineStr"/>
       <c r="AJ73" s="6" t="inlineStr"/>
-      <c r="AK73" s="15" t="n"/>
+      <c r="AK73" s="12" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -6965,97 +6935,97 @@
       <c r="B74" s="6" t="n">
         <v>579.25</v>
       </c>
-      <c r="C74" s="7" t="n">
+      <c r="C74" s="6" t="n">
         <v>79.78</v>
       </c>
-      <c r="D74" s="7" t="n">
+      <c r="D74" s="6" t="n">
         <v>80.72</v>
       </c>
-      <c r="E74" s="7" t="n">
+      <c r="E74" s="6" t="n">
         <v>79.93000000000001</v>
       </c>
-      <c r="F74" s="7" t="n">
+      <c r="F74" s="6" t="n">
         <v>80.12</v>
       </c>
-      <c r="G74" s="7" t="n">
+      <c r="G74" s="6" t="n">
         <v>79.88</v>
       </c>
-      <c r="H74" s="7" t="n">
+      <c r="H74" s="6" t="n">
         <v>79.08</v>
       </c>
-      <c r="I74" s="7" t="n">
+      <c r="I74" s="6" t="n">
         <v>78.75</v>
       </c>
-      <c r="J74" s="7" t="n">
+      <c r="J74" s="6" t="n">
         <v>77.95</v>
       </c>
-      <c r="K74" s="7" t="n">
+      <c r="K74" s="6" t="n">
         <v>80.68000000000001</v>
       </c>
-      <c r="L74" s="7" t="n">
+      <c r="L74" s="6" t="n">
         <v>81.78</v>
       </c>
-      <c r="M74" s="7" t="n">
+      <c r="M74" s="6" t="n">
         <v>79.17</v>
       </c>
-      <c r="N74" s="7" t="n">
+      <c r="N74" s="6" t="n">
         <v>77.7</v>
       </c>
-      <c r="O74" s="7" t="n">
+      <c r="O74" s="6" t="n">
         <v>78.22</v>
       </c>
-      <c r="P74" s="7" t="n">
+      <c r="P74" s="6" t="n">
         <v>78.63</v>
       </c>
-      <c r="Q74" s="7" t="n">
+      <c r="Q74" s="6" t="n">
         <v>80.17</v>
       </c>
-      <c r="R74" s="7" t="n">
+      <c r="R74" s="6" t="n">
         <v>81.37</v>
       </c>
-      <c r="S74" s="7" t="n">
+      <c r="S74" s="6" t="n">
         <v>81.08</v>
       </c>
-      <c r="T74" s="7" t="n">
+      <c r="T74" s="6" t="n">
         <v>80.27</v>
       </c>
-      <c r="U74" s="7" t="n">
+      <c r="U74" s="6" t="n">
         <v>81.02</v>
       </c>
-      <c r="V74" s="7" t="n">
+      <c r="V74" s="6" t="n">
         <v>81.15000000000001</v>
       </c>
-      <c r="W74" s="7" t="n">
+      <c r="W74" s="6" t="n">
         <v>80.2</v>
       </c>
-      <c r="X74" s="7" t="n">
+      <c r="X74" s="6" t="n">
         <v>80.59999999999999</v>
       </c>
-      <c r="Y74" s="7" t="n">
+      <c r="Y74" s="6" t="n">
         <v>78.77</v>
       </c>
-      <c r="Z74" s="7" t="n">
+      <c r="Z74" s="6" t="n">
         <v>82.28</v>
       </c>
-      <c r="AA74" s="7" t="n">
+      <c r="AA74" s="6" t="n">
         <v>81.15000000000001</v>
       </c>
-      <c r="AB74" s="7" t="n">
+      <c r="AB74" s="6" t="n">
         <v>80.33</v>
       </c>
-      <c r="AC74" s="7" t="n">
+      <c r="AC74" s="6" t="n">
         <v>80.15000000000001</v>
       </c>
-      <c r="AD74" s="7" t="n">
+      <c r="AD74" s="6" t="n">
         <v>83</v>
       </c>
-      <c r="AE74" s="7" t="n">
+      <c r="AE74" s="6" t="n">
         <v>79.43000000000001</v>
       </c>
-      <c r="AF74" s="7" t="n">
+      <c r="AF74" s="6" t="n">
         <v>79.03</v>
       </c>
-      <c r="AG74" s="7" t="n">
+      <c r="AG74" s="6" t="n">
         <v>81.13</v>
       </c>
       <c r="AH74" s="6" t="n">
@@ -7063,7 +7033,7 @@
       </c>
       <c r="AI74" s="6" t="inlineStr"/>
       <c r="AJ74" s="6" t="inlineStr"/>
-      <c r="AK74" s="15" t="n"/>
+      <c r="AK74" s="12" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
@@ -7074,97 +7044,97 @@
       <c r="B75" s="6" t="n">
         <v>591.25</v>
       </c>
-      <c r="C75" s="16" t="n">
+      <c r="C75" s="6" t="n">
         <v>32.83</v>
       </c>
-      <c r="D75" s="16" t="n">
+      <c r="D75" s="6" t="n">
         <v>34.15</v>
       </c>
-      <c r="E75" s="16" t="n">
+      <c r="E75" s="6" t="n">
         <v>32.67</v>
       </c>
-      <c r="F75" s="16" t="n">
+      <c r="F75" s="6" t="n">
         <v>32.47</v>
       </c>
-      <c r="G75" s="16" t="n">
+      <c r="G75" s="6" t="n">
         <v>32.32</v>
       </c>
-      <c r="H75" s="16" t="n">
+      <c r="H75" s="6" t="n">
         <v>32.23</v>
       </c>
-      <c r="I75" s="16" t="n">
+      <c r="I75" s="6" t="n">
         <v>32.47</v>
       </c>
-      <c r="J75" s="16" t="n">
+      <c r="J75" s="6" t="n">
         <v>34.17</v>
       </c>
-      <c r="K75" s="16" t="n">
+      <c r="K75" s="6" t="n">
         <v>37.27</v>
       </c>
-      <c r="L75" s="9" t="n">
+      <c r="L75" s="6" t="n">
         <v>45.08</v>
       </c>
-      <c r="M75" s="16" t="n">
+      <c r="M75" s="6" t="n">
         <v>39.83</v>
       </c>
-      <c r="N75" s="16" t="n">
+      <c r="N75" s="6" t="n">
         <v>32.48</v>
       </c>
-      <c r="O75" s="16" t="n">
+      <c r="O75" s="6" t="n">
         <v>32.45</v>
       </c>
-      <c r="P75" s="16" t="n">
+      <c r="P75" s="6" t="n">
         <v>32.08</v>
       </c>
-      <c r="Q75" s="16" t="n">
+      <c r="Q75" s="6" t="n">
         <v>31.9</v>
       </c>
-      <c r="R75" s="16" t="n">
+      <c r="R75" s="6" t="n">
         <v>31.83</v>
       </c>
-      <c r="S75" s="16" t="n">
+      <c r="S75" s="6" t="n">
         <v>32.6</v>
       </c>
-      <c r="T75" s="16" t="n">
+      <c r="T75" s="6" t="n">
         <v>34.5</v>
       </c>
-      <c r="U75" s="16" t="n">
+      <c r="U75" s="6" t="n">
         <v>31.85</v>
       </c>
-      <c r="V75" s="16" t="n">
+      <c r="V75" s="6" t="n">
         <v>32.28</v>
       </c>
-      <c r="W75" s="16" t="n">
+      <c r="W75" s="6" t="n">
         <v>37.38</v>
       </c>
-      <c r="X75" s="9" t="n">
+      <c r="X75" s="6" t="n">
         <v>43.55</v>
       </c>
-      <c r="Y75" s="16" t="n">
+      <c r="Y75" s="6" t="n">
         <v>42.93</v>
       </c>
-      <c r="Z75" s="9" t="n">
+      <c r="Z75" s="6" t="n">
         <v>43.05</v>
       </c>
-      <c r="AA75" s="9" t="n">
+      <c r="AA75" s="6" t="n">
         <v>43.25</v>
       </c>
-      <c r="AB75" s="9" t="n">
+      <c r="AB75" s="6" t="n">
         <v>43.55</v>
       </c>
-      <c r="AC75" s="16" t="n">
+      <c r="AC75" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="AD75" s="9" t="n">
+      <c r="AD75" s="6" t="n">
         <v>43.15</v>
       </c>
-      <c r="AE75" s="9" t="n">
+      <c r="AE75" s="6" t="n">
         <v>43.18</v>
       </c>
-      <c r="AF75" s="16" t="n">
+      <c r="AF75" s="6" t="n">
         <v>39.02</v>
       </c>
-      <c r="AG75" s="16" t="n">
+      <c r="AG75" s="6" t="n">
         <v>32.98</v>
       </c>
       <c r="AH75" s="6" t="n">
@@ -7172,7 +7142,7 @@
       </c>
       <c r="AI75" s="6" t="inlineStr"/>
       <c r="AJ75" s="6" t="inlineStr"/>
-      <c r="AK75" s="15" t="n"/>
+      <c r="AK75" s="12" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -7183,97 +7153,97 @@
       <c r="B76" s="6" t="n">
         <v>603.25</v>
       </c>
-      <c r="C76" s="16" t="n">
+      <c r="C76" s="6" t="n">
         <v>32.45</v>
       </c>
-      <c r="D76" s="16" t="n">
+      <c r="D76" s="6" t="n">
         <v>32.73</v>
       </c>
-      <c r="E76" s="16" t="n">
+      <c r="E76" s="6" t="n">
         <v>32.25</v>
       </c>
-      <c r="F76" s="16" t="n">
+      <c r="F76" s="6" t="n">
         <v>32.4</v>
       </c>
-      <c r="G76" s="16" t="n">
+      <c r="G76" s="6" t="n">
         <v>32.48</v>
       </c>
-      <c r="H76" s="16" t="n">
+      <c r="H76" s="6" t="n">
         <v>32.68</v>
       </c>
-      <c r="I76" s="16" t="n">
+      <c r="I76" s="6" t="n">
         <v>33.48</v>
       </c>
-      <c r="J76" s="16" t="n">
+      <c r="J76" s="6" t="n">
         <v>32.9</v>
       </c>
-      <c r="K76" s="16" t="n">
+      <c r="K76" s="6" t="n">
         <v>39.47</v>
       </c>
-      <c r="L76" s="9" t="n">
+      <c r="L76" s="6" t="n">
         <v>46.07</v>
       </c>
-      <c r="M76" s="16" t="n">
+      <c r="M76" s="6" t="n">
         <v>39.98</v>
       </c>
-      <c r="N76" s="16" t="n">
+      <c r="N76" s="6" t="n">
         <v>32.65</v>
       </c>
-      <c r="O76" s="16" t="n">
+      <c r="O76" s="6" t="n">
         <v>32.73</v>
       </c>
-      <c r="P76" s="16" t="n">
+      <c r="P76" s="6" t="n">
         <v>33.17</v>
       </c>
-      <c r="Q76" s="16" t="n">
+      <c r="Q76" s="6" t="n">
         <v>32.58</v>
       </c>
-      <c r="R76" s="16" t="n">
+      <c r="R76" s="6" t="n">
         <v>32.58</v>
       </c>
-      <c r="S76" s="16" t="n">
+      <c r="S76" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="T76" s="16" t="n">
+      <c r="T76" s="6" t="n">
         <v>33.23</v>
       </c>
-      <c r="U76" s="16" t="n">
+      <c r="U76" s="6" t="n">
         <v>32.78</v>
       </c>
-      <c r="V76" s="16" t="n">
+      <c r="V76" s="6" t="n">
         <v>32.85</v>
       </c>
-      <c r="W76" s="9" t="n">
+      <c r="W76" s="6" t="n">
         <v>44.6</v>
       </c>
-      <c r="X76" s="9" t="n">
+      <c r="X76" s="6" t="n">
         <v>46.48</v>
       </c>
-      <c r="Y76" s="9" t="n">
+      <c r="Y76" s="6" t="n">
         <v>46.78</v>
       </c>
-      <c r="Z76" s="9" t="n">
+      <c r="Z76" s="6" t="n">
         <v>46.05</v>
       </c>
-      <c r="AA76" s="9" t="n">
+      <c r="AA76" s="6" t="n">
         <v>46.18</v>
       </c>
-      <c r="AB76" s="9" t="n">
+      <c r="AB76" s="6" t="n">
         <v>48.7</v>
       </c>
-      <c r="AC76" s="9" t="n">
+      <c r="AC76" s="6" t="n">
         <v>47.2</v>
       </c>
-      <c r="AD76" s="9" t="n">
+      <c r="AD76" s="6" t="n">
         <v>46.2</v>
       </c>
-      <c r="AE76" s="9" t="n">
+      <c r="AE76" s="6" t="n">
         <v>46.93</v>
       </c>
-      <c r="AF76" s="16" t="n">
+      <c r="AF76" s="6" t="n">
         <v>39.97</v>
       </c>
-      <c r="AG76" s="16" t="n">
+      <c r="AG76" s="6" t="n">
         <v>33.45</v>
       </c>
       <c r="AH76" s="6" t="n">
@@ -7281,116 +7251,116 @@
       </c>
       <c r="AI76" s="6" t="inlineStr"/>
       <c r="AJ76" s="6" t="inlineStr"/>
-      <c r="AK76" s="15" t="n"/>
+      <c r="AK76" s="12" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="10" t="inlineStr">
+      <c r="A77" s="8" t="inlineStr">
         <is>
           <t>CANAL SUR - TELEVISION MUN</t>
         </is>
       </c>
-      <c r="B77" s="11" t="n">
+      <c r="B77" s="9" t="n">
         <v>621.25</v>
       </c>
-      <c r="C77" s="12" t="n">
+      <c r="C77" s="9" t="n">
         <v>75.28</v>
       </c>
-      <c r="D77" s="12" t="n">
+      <c r="D77" s="9" t="n">
         <v>75.62</v>
       </c>
-      <c r="E77" s="12" t="n">
+      <c r="E77" s="9" t="n">
         <v>69.09999999999999</v>
       </c>
-      <c r="F77" s="12" t="n">
+      <c r="F77" s="9" t="n">
         <v>70.23</v>
       </c>
-      <c r="G77" s="12" t="n">
+      <c r="G77" s="9" t="n">
         <v>70.78</v>
       </c>
-      <c r="H77" s="12" t="n">
+      <c r="H77" s="9" t="n">
         <v>69.77</v>
       </c>
-      <c r="I77" s="12" t="n">
+      <c r="I77" s="9" t="n">
         <v>70.2</v>
       </c>
-      <c r="J77" s="12" t="n">
+      <c r="J77" s="9" t="n">
         <v>68.48</v>
       </c>
-      <c r="K77" s="12" t="n">
+      <c r="K77" s="9" t="n">
         <v>83.56999999999999</v>
       </c>
-      <c r="L77" s="12" t="n">
+      <c r="L77" s="9" t="n">
         <v>99.27</v>
       </c>
-      <c r="M77" s="12" t="n">
+      <c r="M77" s="9" t="n">
         <v>84.33</v>
       </c>
-      <c r="N77" s="12" t="n">
+      <c r="N77" s="9" t="n">
         <v>69.23</v>
       </c>
-      <c r="O77" s="12" t="n">
+      <c r="O77" s="9" t="n">
         <v>68.53</v>
       </c>
-      <c r="P77" s="12" t="n">
+      <c r="P77" s="9" t="n">
         <v>70.05</v>
       </c>
-      <c r="Q77" s="12" t="n">
+      <c r="Q77" s="9" t="n">
         <v>68.92</v>
       </c>
-      <c r="R77" s="12" t="n">
+      <c r="R77" s="9" t="n">
         <v>71.08</v>
       </c>
-      <c r="S77" s="12" t="n">
+      <c r="S77" s="9" t="n">
         <v>72.17</v>
       </c>
-      <c r="T77" s="12" t="n">
+      <c r="T77" s="9" t="n">
         <v>71.13</v>
       </c>
-      <c r="U77" s="12" t="n">
+      <c r="U77" s="9" t="n">
         <v>72.59999999999999</v>
       </c>
-      <c r="V77" s="12" t="n">
+      <c r="V77" s="9" t="n">
         <v>69.81999999999999</v>
       </c>
-      <c r="W77" s="12" t="n">
+      <c r="W77" s="9" t="n">
         <v>85.8</v>
       </c>
-      <c r="X77" s="12" t="n">
+      <c r="X77" s="9" t="n">
         <v>99.72</v>
       </c>
-      <c r="Y77" s="12" t="n">
+      <c r="Y77" s="9" t="n">
         <v>99.43000000000001</v>
       </c>
-      <c r="Z77" s="12" t="n">
+      <c r="Z77" s="9" t="n">
         <v>99.73</v>
       </c>
-      <c r="AA77" s="12" t="n">
+      <c r="AA77" s="9" t="n">
         <v>99.73</v>
       </c>
-      <c r="AB77" s="12" t="n">
+      <c r="AB77" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="AC77" s="12" t="n">
+      <c r="AC77" s="9" t="n">
         <v>99.05</v>
       </c>
-      <c r="AD77" s="12" t="n">
+      <c r="AD77" s="9" t="n">
         <v>99.48</v>
       </c>
-      <c r="AE77" s="12" t="n">
+      <c r="AE77" s="9" t="n">
         <v>99.78</v>
       </c>
-      <c r="AF77" s="12" t="n">
+      <c r="AF77" s="9" t="n">
         <v>85.68000000000001</v>
       </c>
-      <c r="AG77" s="12" t="n">
+      <c r="AG77" s="9" t="n">
         <v>73.12</v>
       </c>
-      <c r="AH77" s="11" t="n">
+      <c r="AH77" s="9" t="n">
         <v>81.02</v>
       </c>
-      <c r="AI77" s="11" t="inlineStr"/>
-      <c r="AJ77" s="11" t="inlineStr"/>
-      <c r="AK77" s="17" t="n"/>
+      <c r="AI77" s="9" t="inlineStr"/>
+      <c r="AJ77" s="9" t="inlineStr"/>
+      <c r="AK77" s="13" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="33">

--- a/ReportesUnificados/loja_ReporteUnificado.xlsx
+++ b/ReportesUnificados/loja_ReporteUnificado.xlsx
@@ -30,7 +30,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -47,6 +47,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFE9F"/>
         <bgColor rgb="FFFFFE9F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF6666"/>
+        <bgColor rgb="FFFF6666"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
     <fill>
@@ -171,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -194,6 +206,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -209,12 +227,18 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1024,14 +1048,14 @@
       <c r="AG11" s="7" t="n">
         <v>103.78</v>
       </c>
-      <c r="AH11" s="6" t="n">
+      <c r="AH11" s="8" t="n">
         <v>102.07</v>
       </c>
-      <c r="AI11" s="6" t="n">
+      <c r="AI11" s="9" t="n">
         <v>261.08</v>
       </c>
       <c r="AJ11" s="6" t="inlineStr"/>
-      <c r="AK11" s="8" t="inlineStr"/>
+      <c r="AK11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1135,14 +1159,14 @@
       <c r="AG12" s="7" t="n">
         <v>102.45</v>
       </c>
-      <c r="AH12" s="6" t="n">
+      <c r="AH12" s="8" t="n">
         <v>102.13</v>
       </c>
-      <c r="AI12" s="6" t="n">
+      <c r="AI12" s="9" t="n">
         <v>400.33</v>
       </c>
       <c r="AJ12" s="6" t="inlineStr"/>
-      <c r="AK12" s="8" t="inlineStr"/>
+      <c r="AK12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1246,14 +1270,14 @@
       <c r="AG13" s="7" t="n">
         <v>104.82</v>
       </c>
-      <c r="AH13" s="6" t="n">
+      <c r="AH13" s="8" t="n">
         <v>106.91</v>
       </c>
-      <c r="AI13" s="6" t="n">
+      <c r="AI13" s="9" t="n">
         <v>485.39</v>
       </c>
       <c r="AJ13" s="6" t="inlineStr"/>
-      <c r="AK13" s="8" t="inlineStr"/>
+      <c r="AK13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1357,14 +1381,14 @@
       <c r="AG14" s="7" t="n">
         <v>111.67</v>
       </c>
-      <c r="AH14" s="6" t="n">
+      <c r="AH14" s="8" t="n">
         <v>109.46</v>
       </c>
-      <c r="AI14" s="6" t="n">
+      <c r="AI14" s="9" t="n">
         <v>372.17</v>
       </c>
       <c r="AJ14" s="6" t="inlineStr"/>
-      <c r="AK14" s="8" t="inlineStr"/>
+      <c r="AK14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1468,14 +1492,14 @@
       <c r="AG15" s="7" t="n">
         <v>105.46</v>
       </c>
-      <c r="AH15" s="6" t="n">
+      <c r="AH15" s="8" t="n">
         <v>103.29</v>
       </c>
-      <c r="AI15" s="6" t="n">
+      <c r="AI15" s="9" t="n">
         <v>388.41</v>
       </c>
       <c r="AJ15" s="6" t="inlineStr"/>
-      <c r="AK15" s="8" t="inlineStr"/>
+      <c r="AK15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1579,14 +1603,14 @@
       <c r="AG16" s="7" t="n">
         <v>87.37</v>
       </c>
-      <c r="AH16" s="6" t="n">
+      <c r="AH16" s="8" t="n">
         <v>84.44</v>
       </c>
-      <c r="AI16" s="6" t="n">
+      <c r="AI16" s="9" t="n">
         <v>444.57</v>
       </c>
       <c r="AJ16" s="6" t="inlineStr"/>
-      <c r="AK16" s="8" t="inlineStr"/>
+      <c r="AK16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1690,14 +1714,14 @@
       <c r="AG17" s="7" t="n">
         <v>89.48</v>
       </c>
-      <c r="AH17" s="6" t="n">
+      <c r="AH17" s="8" t="n">
         <v>88.02</v>
       </c>
-      <c r="AI17" s="6" t="n">
+      <c r="AI17" s="9" t="n">
         <v>364.81</v>
       </c>
       <c r="AJ17" s="6" t="inlineStr"/>
-      <c r="AK17" s="8" t="inlineStr"/>
+      <c r="AK17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1801,14 +1825,14 @@
       <c r="AG18" s="7" t="n">
         <v>106.29</v>
       </c>
-      <c r="AH18" s="6" t="n">
+      <c r="AH18" s="8" t="n">
         <v>103.91</v>
       </c>
-      <c r="AI18" s="6" t="n">
+      <c r="AI18" s="9" t="n">
         <v>415.88</v>
       </c>
       <c r="AJ18" s="6" t="inlineStr"/>
-      <c r="AK18" s="8" t="inlineStr"/>
+      <c r="AK18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1912,14 +1936,14 @@
       <c r="AG19" s="7" t="n">
         <v>105.72</v>
       </c>
-      <c r="AH19" s="6" t="n">
+      <c r="AH19" s="8" t="n">
         <v>104.17</v>
       </c>
-      <c r="AI19" s="6" t="n">
+      <c r="AI19" s="9" t="n">
         <v>418.76</v>
       </c>
       <c r="AJ19" s="6" t="inlineStr"/>
-      <c r="AK19" s="8" t="inlineStr"/>
+      <c r="AK19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -2023,14 +2047,14 @@
       <c r="AG20" s="7" t="n">
         <v>94.88</v>
       </c>
-      <c r="AH20" s="6" t="n">
+      <c r="AH20" s="8" t="n">
         <v>95.44</v>
       </c>
-      <c r="AI20" s="6" t="n">
+      <c r="AI20" s="9" t="n">
         <v>400.73</v>
       </c>
       <c r="AJ20" s="6" t="inlineStr"/>
-      <c r="AK20" s="8" t="inlineStr"/>
+      <c r="AK20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2134,14 +2158,14 @@
       <c r="AG21" s="7" t="n">
         <v>96.98999999999999</v>
       </c>
-      <c r="AH21" s="6" t="n">
+      <c r="AH21" s="8" t="n">
         <v>96.64</v>
       </c>
-      <c r="AI21" s="6" t="n">
+      <c r="AI21" s="9" t="n">
         <v>406.58</v>
       </c>
       <c r="AJ21" s="6" t="inlineStr"/>
-      <c r="AK21" s="8" t="inlineStr"/>
+      <c r="AK21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2245,14 +2269,14 @@
       <c r="AG22" s="7" t="n">
         <v>109.51</v>
       </c>
-      <c r="AH22" s="6" t="n">
+      <c r="AH22" s="8" t="n">
         <v>105.92</v>
       </c>
-      <c r="AI22" s="6" t="n">
+      <c r="AI22" s="9" t="n">
         <v>387.36</v>
       </c>
       <c r="AJ22" s="6" t="inlineStr"/>
-      <c r="AK22" s="8" t="inlineStr"/>
+      <c r="AK22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -2356,14 +2380,14 @@
       <c r="AG23" s="7" t="n">
         <v>104.5</v>
       </c>
-      <c r="AH23" s="6" t="n">
+      <c r="AH23" s="8" t="n">
         <v>102.97</v>
       </c>
-      <c r="AI23" s="6" t="n">
+      <c r="AI23" s="9" t="n">
         <v>419.3</v>
       </c>
       <c r="AJ23" s="6" t="inlineStr"/>
-      <c r="AK23" s="8" t="inlineStr"/>
+      <c r="AK23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2467,14 +2491,14 @@
       <c r="AG24" s="7" t="n">
         <v>106.08</v>
       </c>
-      <c r="AH24" s="6" t="n">
+      <c r="AH24" s="8" t="n">
         <v>104.14</v>
       </c>
-      <c r="AI24" s="6" t="n">
+      <c r="AI24" s="9" t="n">
         <v>408.72</v>
       </c>
       <c r="AJ24" s="6" t="inlineStr"/>
-      <c r="AK24" s="8" t="inlineStr"/>
+      <c r="AK24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -2578,14 +2602,14 @@
       <c r="AG25" s="7" t="n">
         <v>92.5</v>
       </c>
-      <c r="AH25" s="6" t="n">
+      <c r="AH25" s="8" t="n">
         <v>92.11</v>
       </c>
-      <c r="AI25" s="6" t="n">
+      <c r="AI25" s="9" t="n">
         <v>439.51</v>
       </c>
       <c r="AJ25" s="6" t="inlineStr"/>
-      <c r="AK25" s="8" t="inlineStr"/>
+      <c r="AK25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -2689,14 +2713,14 @@
       <c r="AG26" s="7" t="n">
         <v>105.59</v>
       </c>
-      <c r="AH26" s="6" t="n">
+      <c r="AH26" s="8" t="n">
         <v>103.28</v>
       </c>
-      <c r="AI26" s="6" t="n">
+      <c r="AI26" s="9" t="n">
         <v>412.36</v>
       </c>
       <c r="AJ26" s="6" t="inlineStr"/>
-      <c r="AK26" s="8" t="inlineStr"/>
+      <c r="AK26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2800,14 +2824,14 @@
       <c r="AG27" s="7" t="n">
         <v>96.20999999999999</v>
       </c>
-      <c r="AH27" s="6" t="n">
+      <c r="AH27" s="8" t="n">
         <v>95.87</v>
       </c>
-      <c r="AI27" s="6" t="n">
+      <c r="AI27" s="9" t="n">
         <v>398.86</v>
       </c>
       <c r="AJ27" s="6" t="inlineStr"/>
-      <c r="AK27" s="8" t="inlineStr"/>
+      <c r="AK27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -2818,19 +2842,19 @@
       <c r="B28" s="6" t="n">
         <v>96.09999999999999</v>
       </c>
-      <c r="C28" s="9" t="n">
+      <c r="C28" s="11" t="n">
         <v>52.79</v>
       </c>
-      <c r="D28" s="9" t="n">
+      <c r="D28" s="11" t="n">
         <v>53.24</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="11" t="n">
         <v>53.39</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="11" t="n">
         <v>52.91</v>
       </c>
-      <c r="G28" s="9" t="n">
+      <c r="G28" s="11" t="n">
         <v>52.24</v>
       </c>
       <c r="H28" s="7" t="n">
@@ -2839,7 +2863,7 @@
       <c r="I28" s="7" t="n">
         <v>54.52</v>
       </c>
-      <c r="J28" s="9" t="n">
+      <c r="J28" s="11" t="n">
         <v>53.58</v>
       </c>
       <c r="K28" s="7" t="n">
@@ -2911,14 +2935,14 @@
       <c r="AG28" s="7" t="n">
         <v>98.55</v>
       </c>
-      <c r="AH28" s="6" t="n">
+      <c r="AH28" s="8" t="n">
         <v>81.95</v>
       </c>
-      <c r="AI28" s="6" t="n">
+      <c r="AI28" s="9" t="n">
         <v>546.02</v>
       </c>
       <c r="AJ28" s="6" t="inlineStr"/>
-      <c r="AK28" s="8" t="inlineStr"/>
+      <c r="AK28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -3022,14 +3046,14 @@
       <c r="AG29" s="7" t="n">
         <v>98.88</v>
       </c>
-      <c r="AH29" s="6" t="n">
+      <c r="AH29" s="8" t="n">
         <v>98.59</v>
       </c>
-      <c r="AI29" s="6" t="n">
+      <c r="AI29" s="9" t="n">
         <v>391.54</v>
       </c>
       <c r="AJ29" s="6" t="inlineStr"/>
-      <c r="AK29" s="8" t="inlineStr"/>
+      <c r="AK29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -3133,14 +3157,14 @@
       <c r="AG30" s="7" t="n">
         <v>106.94</v>
       </c>
-      <c r="AH30" s="6" t="n">
+      <c r="AH30" s="8" t="n">
         <v>106.71</v>
       </c>
-      <c r="AI30" s="6" t="n">
+      <c r="AI30" s="9" t="n">
         <v>476.01</v>
       </c>
       <c r="AJ30" s="6" t="inlineStr"/>
-      <c r="AK30" s="8" t="inlineStr"/>
+      <c r="AK30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -3151,34 +3175,34 @@
       <c r="B31" s="6" t="n">
         <v>97.3</v>
       </c>
-      <c r="C31" s="9" t="n">
+      <c r="C31" s="11" t="n">
         <v>50.96</v>
       </c>
-      <c r="D31" s="9" t="n">
+      <c r="D31" s="11" t="n">
         <v>51.09</v>
       </c>
-      <c r="E31" s="9" t="n">
+      <c r="E31" s="11" t="n">
         <v>51.49</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F31" s="11" t="n">
         <v>51.17</v>
       </c>
-      <c r="G31" s="9" t="n">
+      <c r="G31" s="11" t="n">
         <v>50.6</v>
       </c>
-      <c r="H31" s="9" t="n">
+      <c r="H31" s="11" t="n">
         <v>53.72</v>
       </c>
       <c r="I31" s="7" t="n">
         <v>54.82</v>
       </c>
-      <c r="J31" s="9" t="n">
+      <c r="J31" s="11" t="n">
         <v>51.84</v>
       </c>
-      <c r="K31" s="9" t="n">
+      <c r="K31" s="11" t="n">
         <v>51.62</v>
       </c>
-      <c r="L31" s="9" t="n">
+      <c r="L31" s="11" t="n">
         <v>50.18</v>
       </c>
       <c r="M31" s="7" t="n">
@@ -3187,13 +3211,13 @@
       <c r="N31" s="7" t="n">
         <v>58.57</v>
       </c>
-      <c r="O31" s="9" t="n">
+      <c r="O31" s="11" t="n">
         <v>53.3</v>
       </c>
       <c r="P31" s="7" t="n">
         <v>55.63</v>
       </c>
-      <c r="Q31" s="9" t="n">
+      <c r="Q31" s="11" t="n">
         <v>53.83</v>
       </c>
       <c r="R31" s="7" t="n">
@@ -3202,40 +3226,40 @@
       <c r="S31" s="7" t="n">
         <v>55.61</v>
       </c>
-      <c r="T31" s="9" t="n">
+      <c r="T31" s="11" t="n">
         <v>53.61</v>
       </c>
       <c r="U31" s="7" t="n">
         <v>56.99</v>
       </c>
-      <c r="V31" s="9" t="n">
+      <c r="V31" s="11" t="n">
         <v>53.82</v>
       </c>
-      <c r="W31" s="9" t="n">
+      <c r="W31" s="11" t="n">
         <v>51.9</v>
       </c>
-      <c r="X31" s="9" t="n">
+      <c r="X31" s="11" t="n">
         <v>49.27</v>
       </c>
-      <c r="Y31" s="9" t="n">
+      <c r="Y31" s="11" t="n">
         <v>49.44</v>
       </c>
-      <c r="Z31" s="9" t="n">
+      <c r="Z31" s="11" t="n">
         <v>50.36</v>
       </c>
-      <c r="AA31" s="9" t="n">
+      <c r="AA31" s="11" t="n">
         <v>49.75</v>
       </c>
-      <c r="AB31" s="9" t="n">
+      <c r="AB31" s="11" t="n">
         <v>49.7</v>
       </c>
-      <c r="AC31" s="9" t="n">
+      <c r="AC31" s="11" t="n">
         <v>49.16</v>
       </c>
-      <c r="AD31" s="9" t="n">
+      <c r="AD31" s="11" t="n">
         <v>50.04</v>
       </c>
-      <c r="AE31" s="9" t="n">
+      <c r="AE31" s="11" t="n">
         <v>49.68</v>
       </c>
       <c r="AF31" s="7" t="n">
@@ -3247,11 +3271,11 @@
       <c r="AH31" s="6" t="n">
         <v>52.73</v>
       </c>
-      <c r="AI31" s="6" t="n">
+      <c r="AI31" s="9" t="n">
         <v>703.75</v>
       </c>
       <c r="AJ31" s="6" t="inlineStr"/>
-      <c r="AK31" s="8" t="inlineStr"/>
+      <c r="AK31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -3355,14 +3379,14 @@
       <c r="AG32" s="7" t="n">
         <v>91.77</v>
       </c>
-      <c r="AH32" s="6" t="n">
+      <c r="AH32" s="8" t="n">
         <v>91.68000000000001</v>
       </c>
-      <c r="AI32" s="6" t="n">
+      <c r="AI32" s="9" t="n">
         <v>413.77</v>
       </c>
       <c r="AJ32" s="6" t="inlineStr"/>
-      <c r="AK32" s="8" t="inlineStr"/>
+      <c r="AK32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -3466,14 +3490,14 @@
       <c r="AG33" s="7" t="n">
         <v>91.63</v>
       </c>
-      <c r="AH33" s="6" t="n">
+      <c r="AH33" s="8" t="n">
         <v>92.72</v>
       </c>
-      <c r="AI33" s="6" t="n">
+      <c r="AI33" s="9" t="n">
         <v>438.53</v>
       </c>
       <c r="AJ33" s="6" t="inlineStr"/>
-      <c r="AK33" s="8" t="inlineStr"/>
+      <c r="AK33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -3577,14 +3601,14 @@
       <c r="AG34" s="7" t="n">
         <v>90.66</v>
       </c>
-      <c r="AH34" s="6" t="n">
+      <c r="AH34" s="8" t="n">
         <v>89.5</v>
       </c>
-      <c r="AI34" s="6" t="n">
+      <c r="AI34" s="9" t="n">
         <v>496.73</v>
       </c>
       <c r="AJ34" s="6" t="inlineStr"/>
-      <c r="AK34" s="8" t="inlineStr"/>
+      <c r="AK34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -3688,14 +3712,14 @@
       <c r="AG35" s="7" t="n">
         <v>96.22</v>
       </c>
-      <c r="AH35" s="6" t="n">
+      <c r="AH35" s="8" t="n">
         <v>96.39</v>
       </c>
-      <c r="AI35" s="6" t="n">
+      <c r="AI35" s="9" t="n">
         <v>387.7</v>
       </c>
       <c r="AJ35" s="6" t="inlineStr"/>
-      <c r="AK35" s="8" t="inlineStr"/>
+      <c r="AK35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -3799,14 +3823,14 @@
       <c r="AG36" s="7" t="n">
         <v>101.43</v>
       </c>
-      <c r="AH36" s="6" t="n">
+      <c r="AH36" s="8" t="n">
         <v>100.54</v>
       </c>
-      <c r="AI36" s="6" t="n">
+      <c r="AI36" s="9" t="n">
         <v>400.46</v>
       </c>
       <c r="AJ36" s="6" t="inlineStr"/>
-      <c r="AK36" s="8" t="inlineStr"/>
+      <c r="AK36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -3910,14 +3934,14 @@
       <c r="AG37" s="7" t="n">
         <v>105.94</v>
       </c>
-      <c r="AH37" s="6" t="n">
+      <c r="AH37" s="8" t="n">
         <v>104.41</v>
       </c>
-      <c r="AI37" s="6" t="n">
+      <c r="AI37" s="9" t="n">
         <v>422.94</v>
       </c>
       <c r="AJ37" s="6" t="inlineStr"/>
-      <c r="AK37" s="8" t="inlineStr"/>
+      <c r="AK37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -4021,14 +4045,14 @@
       <c r="AG38" s="7" t="n">
         <v>88.09</v>
       </c>
-      <c r="AH38" s="6" t="n">
+      <c r="AH38" s="8" t="n">
         <v>88.23</v>
       </c>
-      <c r="AI38" s="6" t="n">
+      <c r="AI38" s="9" t="n">
         <v>419.65</v>
       </c>
       <c r="AJ38" s="6" t="inlineStr"/>
-      <c r="AK38" s="8" t="inlineStr"/>
+      <c r="AK38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -4132,14 +4156,14 @@
       <c r="AG39" s="7" t="n">
         <v>100.18</v>
       </c>
-      <c r="AH39" s="6" t="n">
+      <c r="AH39" s="8" t="n">
         <v>100.66</v>
       </c>
-      <c r="AI39" s="6" t="n">
+      <c r="AI39" s="9" t="n">
         <v>399.91</v>
       </c>
       <c r="AJ39" s="6" t="inlineStr"/>
-      <c r="AK39" s="8" t="inlineStr"/>
+      <c r="AK39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -4243,14 +4267,14 @@
       <c r="AG40" s="7" t="n">
         <v>100.71</v>
       </c>
-      <c r="AH40" s="6" t="n">
+      <c r="AH40" s="8" t="n">
         <v>100.45</v>
       </c>
-      <c r="AI40" s="6" t="n">
+      <c r="AI40" s="9" t="n">
         <v>407.04</v>
       </c>
       <c r="AJ40" s="6" t="inlineStr"/>
-      <c r="AK40" s="8" t="inlineStr"/>
+      <c r="AK40" s="10" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -4354,14 +4378,14 @@
       <c r="AG41" s="7" t="n">
         <v>103.92</v>
       </c>
-      <c r="AH41" s="6" t="n">
+      <c r="AH41" s="8" t="n">
         <v>105.27</v>
       </c>
-      <c r="AI41" s="6" t="n">
+      <c r="AI41" s="9" t="n">
         <v>316.68</v>
       </c>
       <c r="AJ41" s="6" t="inlineStr"/>
-      <c r="AK41" s="8" t="inlineStr"/>
+      <c r="AK41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -4372,49 +4396,49 @@
       <c r="B42" s="6" t="n">
         <v>103.7</v>
       </c>
-      <c r="C42" s="9" t="n">
+      <c r="C42" s="11" t="n">
         <v>50.32</v>
       </c>
-      <c r="D42" s="9" t="n">
+      <c r="D42" s="11" t="n">
         <v>50.59</v>
       </c>
-      <c r="E42" s="9" t="n">
+      <c r="E42" s="11" t="n">
         <v>51.34</v>
       </c>
-      <c r="F42" s="9" t="n">
+      <c r="F42" s="11" t="n">
         <v>51.32</v>
       </c>
-      <c r="G42" s="9" t="n">
+      <c r="G42" s="11" t="n">
         <v>50.85</v>
       </c>
-      <c r="H42" s="9" t="n">
+      <c r="H42" s="11" t="n">
         <v>52.08</v>
       </c>
-      <c r="I42" s="9" t="n">
+      <c r="I42" s="11" t="n">
         <v>53.42</v>
       </c>
-      <c r="J42" s="9" t="n">
+      <c r="J42" s="11" t="n">
         <v>51.71</v>
       </c>
-      <c r="K42" s="9" t="n">
+      <c r="K42" s="11" t="n">
         <v>52.18</v>
       </c>
-      <c r="L42" s="9" t="n">
+      <c r="L42" s="11" t="n">
         <v>50.53</v>
       </c>
-      <c r="M42" s="9" t="n">
+      <c r="M42" s="11" t="n">
         <v>53.58</v>
       </c>
       <c r="N42" s="7" t="n">
         <v>56.22</v>
       </c>
-      <c r="O42" s="9" t="n">
+      <c r="O42" s="11" t="n">
         <v>52.72</v>
       </c>
       <c r="P42" s="7" t="n">
         <v>54.54</v>
       </c>
-      <c r="Q42" s="9" t="n">
+      <c r="Q42" s="11" t="n">
         <v>52.73</v>
       </c>
       <c r="R42" s="7" t="n">
@@ -4423,40 +4447,40 @@
       <c r="S42" s="7" t="n">
         <v>54.02</v>
       </c>
-      <c r="T42" s="9" t="n">
+      <c r="T42" s="11" t="n">
         <v>52.69</v>
       </c>
       <c r="U42" s="7" t="n">
         <v>55.21</v>
       </c>
-      <c r="V42" s="9" t="n">
+      <c r="V42" s="11" t="n">
         <v>53.4</v>
       </c>
-      <c r="W42" s="9" t="n">
+      <c r="W42" s="11" t="n">
         <v>51.93</v>
       </c>
-      <c r="X42" s="9" t="n">
+      <c r="X42" s="11" t="n">
         <v>50.58</v>
       </c>
-      <c r="Y42" s="9" t="n">
+      <c r="Y42" s="11" t="n">
         <v>50.59</v>
       </c>
-      <c r="Z42" s="9" t="n">
+      <c r="Z42" s="11" t="n">
         <v>51.81</v>
       </c>
-      <c r="AA42" s="9" t="n">
+      <c r="AA42" s="11" t="n">
         <v>50.61</v>
       </c>
-      <c r="AB42" s="9" t="n">
+      <c r="AB42" s="11" t="n">
         <v>50.29</v>
       </c>
-      <c r="AC42" s="9" t="n">
+      <c r="AC42" s="11" t="n">
         <v>50.64</v>
       </c>
-      <c r="AD42" s="9" t="n">
+      <c r="AD42" s="11" t="n">
         <v>50.85</v>
       </c>
-      <c r="AE42" s="9" t="n">
+      <c r="AE42" s="11" t="n">
         <v>50.63</v>
       </c>
       <c r="AF42" s="7" t="n">
@@ -4468,11 +4492,11 @@
       <c r="AH42" s="6" t="n">
         <v>52.47</v>
       </c>
-      <c r="AI42" s="6" t="n">
+      <c r="AI42" s="9" t="n">
         <v>504.72</v>
       </c>
       <c r="AJ42" s="6" t="inlineStr"/>
-      <c r="AK42" s="8" t="inlineStr"/>
+      <c r="AK42" s="10" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -4576,14 +4600,14 @@
       <c r="AG43" s="7" t="n">
         <v>98.54000000000001</v>
       </c>
-      <c r="AH43" s="6" t="n">
+      <c r="AH43" s="8" t="n">
         <v>97.64</v>
       </c>
-      <c r="AI43" s="6" t="n">
+      <c r="AI43" s="9" t="n">
         <v>265.12</v>
       </c>
       <c r="AJ43" s="6" t="inlineStr"/>
-      <c r="AK43" s="8" t="inlineStr"/>
+      <c r="AK43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -4687,14 +4711,14 @@
       <c r="AG44" s="7" t="n">
         <v>100.94</v>
       </c>
-      <c r="AH44" s="6" t="n">
+      <c r="AH44" s="8" t="n">
         <v>102.15</v>
       </c>
-      <c r="AI44" s="6" t="n">
+      <c r="AI44" s="9" t="n">
         <v>348.54</v>
       </c>
       <c r="AJ44" s="6" t="inlineStr"/>
-      <c r="AK44" s="8" t="inlineStr"/>
+      <c r="AK44" s="10" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -4798,14 +4822,14 @@
       <c r="AG45" s="7" t="n">
         <v>104.17</v>
       </c>
-      <c r="AH45" s="6" t="n">
+      <c r="AH45" s="8" t="n">
         <v>100.05</v>
       </c>
-      <c r="AI45" s="6" t="n">
+      <c r="AI45" s="9" t="n">
         <v>456.27</v>
       </c>
       <c r="AJ45" s="6" t="inlineStr"/>
-      <c r="AK45" s="8" t="inlineStr"/>
+      <c r="AK45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -4909,14 +4933,14 @@
       <c r="AG46" s="7" t="n">
         <v>102.45</v>
       </c>
-      <c r="AH46" s="6" t="n">
+      <c r="AH46" s="8" t="n">
         <v>100.69</v>
       </c>
-      <c r="AI46" s="6" t="n">
+      <c r="AI46" s="9" t="n">
         <v>420.89</v>
       </c>
       <c r="AJ46" s="6" t="inlineStr"/>
-      <c r="AK46" s="8" t="inlineStr"/>
+      <c r="AK46" s="10" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -5020,14 +5044,14 @@
       <c r="AG47" s="7" t="n">
         <v>100.83</v>
       </c>
-      <c r="AH47" s="6" t="n">
+      <c r="AH47" s="8" t="n">
         <v>100.35</v>
       </c>
-      <c r="AI47" s="6" t="n">
+      <c r="AI47" s="9" t="n">
         <v>416.29</v>
       </c>
       <c r="AJ47" s="6" t="inlineStr"/>
-      <c r="AK47" s="8" t="inlineStr"/>
+      <c r="AK47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -5131,14 +5155,14 @@
       <c r="AG48" s="7" t="n">
         <v>92.87</v>
       </c>
-      <c r="AH48" s="6" t="n">
+      <c r="AH48" s="8" t="n">
         <v>93.23999999999999</v>
       </c>
-      <c r="AI48" s="6" t="n">
+      <c r="AI48" s="9" t="n">
         <v>389.74</v>
       </c>
       <c r="AJ48" s="6" t="inlineStr"/>
-      <c r="AK48" s="8" t="inlineStr"/>
+      <c r="AK48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -5242,14 +5266,14 @@
       <c r="AG49" s="7" t="n">
         <v>83.7</v>
       </c>
-      <c r="AH49" s="6" t="n">
+      <c r="AH49" s="8" t="n">
         <v>86.04000000000001</v>
       </c>
-      <c r="AI49" s="6" t="n">
+      <c r="AI49" s="9" t="n">
         <v>363.9</v>
       </c>
       <c r="AJ49" s="6" t="inlineStr"/>
-      <c r="AK49" s="8" t="inlineStr"/>
+      <c r="AK49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -5353,125 +5377,125 @@
       <c r="AG50" s="7" t="n">
         <v>102.71</v>
       </c>
-      <c r="AH50" s="6" t="n">
+      <c r="AH50" s="8" t="n">
         <v>101.65</v>
       </c>
-      <c r="AI50" s="6" t="n">
+      <c r="AI50" s="9" t="n">
         <v>310.71</v>
       </c>
       <c r="AJ50" s="6" t="inlineStr"/>
-      <c r="AK50" s="8" t="inlineStr"/>
+      <c r="AK50" s="10" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="10" t="inlineStr">
+      <c r="A51" s="12" t="inlineStr">
         <is>
           <t>RADIO POSITIVA FM</t>
         </is>
       </c>
-      <c r="B51" s="11" t="n">
+      <c r="B51" s="13" t="n">
         <v>107.7</v>
       </c>
-      <c r="C51" s="12" t="n">
+      <c r="C51" s="14" t="n">
         <v>76.42</v>
       </c>
-      <c r="D51" s="12" t="n">
+      <c r="D51" s="14" t="n">
         <v>76.77</v>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="E51" s="14" t="n">
         <v>81.34999999999999</v>
       </c>
-      <c r="F51" s="12" t="n">
+      <c r="F51" s="14" t="n">
         <v>79.69</v>
       </c>
-      <c r="G51" s="12" t="n">
+      <c r="G51" s="14" t="n">
         <v>79.67</v>
       </c>
-      <c r="H51" s="12" t="n">
+      <c r="H51" s="14" t="n">
         <v>79.69</v>
       </c>
-      <c r="I51" s="12" t="n">
+      <c r="I51" s="14" t="n">
         <v>79.95999999999999</v>
       </c>
-      <c r="J51" s="12" t="n">
+      <c r="J51" s="14" t="n">
         <v>79.01000000000001</v>
       </c>
-      <c r="K51" s="12" t="n">
+      <c r="K51" s="14" t="n">
         <v>82.05</v>
       </c>
-      <c r="L51" s="12" t="n">
+      <c r="L51" s="14" t="n">
         <v>84.64</v>
       </c>
-      <c r="M51" s="12" t="n">
+      <c r="M51" s="14" t="n">
         <v>81.73</v>
       </c>
-      <c r="N51" s="12" t="n">
+      <c r="N51" s="14" t="n">
         <v>79.73</v>
       </c>
-      <c r="O51" s="12" t="n">
+      <c r="O51" s="14" t="n">
         <v>78.31999999999999</v>
       </c>
-      <c r="P51" s="12" t="n">
+      <c r="P51" s="14" t="n">
         <v>79.45999999999999</v>
       </c>
-      <c r="Q51" s="12" t="n">
+      <c r="Q51" s="14" t="n">
         <v>79.41</v>
       </c>
-      <c r="R51" s="12" t="n">
+      <c r="R51" s="14" t="n">
         <v>79.73999999999999</v>
       </c>
-      <c r="S51" s="12" t="n">
+      <c r="S51" s="14" t="n">
         <v>79.73</v>
       </c>
-      <c r="T51" s="12" t="n">
+      <c r="T51" s="14" t="n">
         <v>79.68000000000001</v>
       </c>
-      <c r="U51" s="12" t="n">
+      <c r="U51" s="14" t="n">
         <v>80.61</v>
       </c>
-      <c r="V51" s="12" t="n">
+      <c r="V51" s="14" t="n">
         <v>79.16</v>
       </c>
-      <c r="W51" s="12" t="n">
+      <c r="W51" s="14" t="n">
         <v>81.95999999999999</v>
       </c>
-      <c r="X51" s="12" t="n">
+      <c r="X51" s="14" t="n">
         <v>84.26000000000001</v>
       </c>
-      <c r="Y51" s="12" t="n">
+      <c r="Y51" s="14" t="n">
         <v>83.81</v>
       </c>
-      <c r="Z51" s="12" t="n">
+      <c r="Z51" s="14" t="n">
         <v>84.69</v>
       </c>
-      <c r="AA51" s="12" t="n">
+      <c r="AA51" s="14" t="n">
         <v>84.03</v>
       </c>
-      <c r="AB51" s="12" t="n">
+      <c r="AB51" s="14" t="n">
         <v>83.94</v>
       </c>
-      <c r="AC51" s="12" t="n">
+      <c r="AC51" s="14" t="n">
         <v>83.68000000000001</v>
       </c>
-      <c r="AD51" s="12" t="n">
+      <c r="AD51" s="14" t="n">
         <v>83.81999999999999</v>
       </c>
-      <c r="AE51" s="12" t="n">
+      <c r="AE51" s="14" t="n">
         <v>84.41</v>
       </c>
-      <c r="AF51" s="12" t="n">
+      <c r="AF51" s="14" t="n">
         <v>82.03</v>
       </c>
-      <c r="AG51" s="12" t="n">
+      <c r="AG51" s="14" t="n">
         <v>79.73</v>
       </c>
-      <c r="AH51" s="11" t="n">
+      <c r="AH51" s="15" t="n">
         <v>81.06999999999999</v>
       </c>
-      <c r="AI51" s="11" t="n">
+      <c r="AI51" s="16" t="n">
         <v>264.88</v>
       </c>
-      <c r="AJ51" s="11" t="inlineStr"/>
-      <c r="AK51" s="13" t="inlineStr"/>
+      <c r="AJ51" s="13" t="inlineStr"/>
+      <c r="AK51" s="17" t="inlineStr"/>
     </row>
     <row r="52"/>
     <row r="53"/>
@@ -5646,7 +5670,7 @@
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK61" s="14" t="n"/>
+      <c r="AK61" s="18" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -5750,12 +5774,12 @@
       <c r="AG62" s="7" t="n">
         <v>92.92</v>
       </c>
-      <c r="AH62" s="6" t="n">
+      <c r="AH62" s="8" t="n">
         <v>89.59999999999999</v>
       </c>
       <c r="AI62" s="6" t="inlineStr"/>
       <c r="AJ62" s="6" t="inlineStr"/>
-      <c r="AK62" s="15" t="n"/>
+      <c r="AK62" s="19" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -5859,12 +5883,12 @@
       <c r="AG63" s="7" t="n">
         <v>93.13</v>
       </c>
-      <c r="AH63" s="6" t="n">
+      <c r="AH63" s="8" t="n">
         <v>89.2</v>
       </c>
       <c r="AI63" s="6" t="inlineStr"/>
       <c r="AJ63" s="6" t="inlineStr"/>
-      <c r="AK63" s="15" t="n"/>
+      <c r="AK63" s="19" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -5968,12 +5992,12 @@
       <c r="AG64" s="7" t="n">
         <v>81.65000000000001</v>
       </c>
-      <c r="AH64" s="6" t="n">
+      <c r="AH64" s="8" t="n">
         <v>83.06</v>
       </c>
       <c r="AI64" s="6" t="inlineStr"/>
       <c r="AJ64" s="6" t="inlineStr"/>
-      <c r="AK64" s="15" t="n"/>
+      <c r="AK64" s="19" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -6077,12 +6101,12 @@
       <c r="AG65" s="7" t="n">
         <v>95.03</v>
       </c>
-      <c r="AH65" s="6" t="n">
+      <c r="AH65" s="8" t="n">
         <v>92.47</v>
       </c>
       <c r="AI65" s="6" t="inlineStr"/>
       <c r="AJ65" s="6" t="inlineStr"/>
-      <c r="AK65" s="15" t="n"/>
+      <c r="AK65" s="19" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -6186,12 +6210,12 @@
       <c r="AG66" s="7" t="n">
         <v>86.5</v>
       </c>
-      <c r="AH66" s="6" t="n">
+      <c r="AH66" s="8" t="n">
         <v>81</v>
       </c>
       <c r="AI66" s="6" t="inlineStr"/>
       <c r="AJ66" s="6" t="inlineStr"/>
-      <c r="AK66" s="15" t="n"/>
+      <c r="AK66" s="19" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -6295,12 +6319,12 @@
       <c r="AG67" s="7" t="n">
         <v>90.22</v>
       </c>
-      <c r="AH67" s="6" t="n">
+      <c r="AH67" s="8" t="n">
         <v>91.06999999999999</v>
       </c>
       <c r="AI67" s="6" t="inlineStr"/>
       <c r="AJ67" s="6" t="inlineStr"/>
-      <c r="AK67" s="15" t="n"/>
+      <c r="AK67" s="19" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -6404,12 +6428,12 @@
       <c r="AG68" s="7" t="n">
         <v>74.7</v>
       </c>
-      <c r="AH68" s="6" t="n">
+      <c r="AH68" s="8" t="n">
         <v>68.88</v>
       </c>
       <c r="AI68" s="6" t="inlineStr"/>
       <c r="AJ68" s="6" t="inlineStr"/>
-      <c r="AK68" s="15" t="n"/>
+      <c r="AK68" s="19" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -6513,12 +6537,12 @@
       <c r="AG69" s="7" t="n">
         <v>84.68000000000001</v>
       </c>
-      <c r="AH69" s="6" t="n">
+      <c r="AH69" s="8" t="n">
         <v>81.86</v>
       </c>
       <c r="AI69" s="6" t="inlineStr"/>
       <c r="AJ69" s="6" t="inlineStr"/>
-      <c r="AK69" s="15" t="n"/>
+      <c r="AK69" s="19" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -6529,97 +6553,97 @@
       <c r="B70" s="6" t="n">
         <v>531.25</v>
       </c>
-      <c r="C70" s="16" t="n">
+      <c r="C70" s="20" t="n">
         <v>28.37</v>
       </c>
-      <c r="D70" s="16" t="n">
+      <c r="D70" s="20" t="n">
         <v>29.4</v>
       </c>
-      <c r="E70" s="16" t="n">
+      <c r="E70" s="20" t="n">
         <v>27.83</v>
       </c>
-      <c r="F70" s="16" t="n">
+      <c r="F70" s="20" t="n">
         <v>28.55</v>
       </c>
-      <c r="G70" s="16" t="n">
+      <c r="G70" s="20" t="n">
         <v>28.55</v>
       </c>
-      <c r="H70" s="16" t="n">
+      <c r="H70" s="20" t="n">
         <v>27.95</v>
       </c>
-      <c r="I70" s="16" t="n">
+      <c r="I70" s="20" t="n">
         <v>28</v>
       </c>
-      <c r="J70" s="16" t="n">
+      <c r="J70" s="20" t="n">
         <v>28.12</v>
       </c>
-      <c r="K70" s="16" t="n">
+      <c r="K70" s="20" t="n">
         <v>33.42</v>
       </c>
-      <c r="L70" s="16" t="n">
+      <c r="L70" s="20" t="n">
         <v>38.92</v>
       </c>
-      <c r="M70" s="16" t="n">
+      <c r="M70" s="20" t="n">
         <v>34.12</v>
       </c>
-      <c r="N70" s="16" t="n">
+      <c r="N70" s="20" t="n">
         <v>28.75</v>
       </c>
-      <c r="O70" s="16" t="n">
+      <c r="O70" s="20" t="n">
         <v>28.63</v>
       </c>
-      <c r="P70" s="16" t="n">
+      <c r="P70" s="20" t="n">
         <v>27.68</v>
       </c>
-      <c r="Q70" s="16" t="n">
+      <c r="Q70" s="20" t="n">
         <v>28.35</v>
       </c>
-      <c r="R70" s="16" t="n">
+      <c r="R70" s="20" t="n">
         <v>27.93</v>
       </c>
-      <c r="S70" s="16" t="n">
+      <c r="S70" s="20" t="n">
         <v>28.22</v>
       </c>
-      <c r="T70" s="16" t="n">
+      <c r="T70" s="20" t="n">
         <v>29</v>
       </c>
-      <c r="U70" s="16" t="n">
+      <c r="U70" s="20" t="n">
         <v>28.68</v>
       </c>
-      <c r="V70" s="16" t="n">
+      <c r="V70" s="20" t="n">
         <v>27.77</v>
       </c>
-      <c r="W70" s="16" t="n">
+      <c r="W70" s="20" t="n">
         <v>33.18</v>
       </c>
-      <c r="X70" s="16" t="n">
+      <c r="X70" s="20" t="n">
         <v>39.05</v>
       </c>
-      <c r="Y70" s="16" t="n">
+      <c r="Y70" s="20" t="n">
         <v>39.05</v>
       </c>
-      <c r="Z70" s="16" t="n">
+      <c r="Z70" s="20" t="n">
         <v>38.88</v>
       </c>
-      <c r="AA70" s="16" t="n">
+      <c r="AA70" s="20" t="n">
         <v>38.68</v>
       </c>
-      <c r="AB70" s="16" t="n">
+      <c r="AB70" s="20" t="n">
         <v>38.78</v>
       </c>
-      <c r="AC70" s="16" t="n">
+      <c r="AC70" s="20" t="n">
         <v>39.45</v>
       </c>
-      <c r="AD70" s="16" t="n">
+      <c r="AD70" s="20" t="n">
         <v>38.48</v>
       </c>
-      <c r="AE70" s="16" t="n">
+      <c r="AE70" s="20" t="n">
         <v>39.23</v>
       </c>
-      <c r="AF70" s="16" t="n">
+      <c r="AF70" s="20" t="n">
         <v>33.83</v>
       </c>
-      <c r="AG70" s="16" t="n">
+      <c r="AG70" s="20" t="n">
         <v>28.65</v>
       </c>
       <c r="AH70" s="6" t="n">
@@ -6627,7 +6651,7 @@
       </c>
       <c r="AI70" s="6" t="inlineStr"/>
       <c r="AJ70" s="6" t="inlineStr"/>
-      <c r="AK70" s="15" t="n"/>
+      <c r="AK70" s="19" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -6731,12 +6755,12 @@
       <c r="AG71" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="AH71" s="6" t="n">
+      <c r="AH71" s="8" t="n">
         <v>68.69</v>
       </c>
       <c r="AI71" s="6" t="inlineStr"/>
       <c r="AJ71" s="6" t="inlineStr"/>
-      <c r="AK71" s="15" t="n"/>
+      <c r="AK71" s="19" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -6747,97 +6771,97 @@
       <c r="B72" s="6" t="n">
         <v>543.25</v>
       </c>
-      <c r="C72" s="16" t="n">
+      <c r="C72" s="20" t="n">
         <v>30.25</v>
       </c>
-      <c r="D72" s="16" t="n">
+      <c r="D72" s="20" t="n">
         <v>28.95</v>
       </c>
-      <c r="E72" s="16" t="n">
+      <c r="E72" s="20" t="n">
         <v>29.82</v>
       </c>
-      <c r="F72" s="16" t="n">
+      <c r="F72" s="20" t="n">
         <v>30.2</v>
       </c>
-      <c r="G72" s="16" t="n">
+      <c r="G72" s="20" t="n">
         <v>30.07</v>
       </c>
-      <c r="H72" s="16" t="n">
+      <c r="H72" s="20" t="n">
         <v>29.28</v>
       </c>
-      <c r="I72" s="16" t="n">
+      <c r="I72" s="20" t="n">
         <v>29.25</v>
       </c>
-      <c r="J72" s="16" t="n">
+      <c r="J72" s="20" t="n">
         <v>30.22</v>
       </c>
-      <c r="K72" s="16" t="n">
+      <c r="K72" s="20" t="n">
         <v>35.05</v>
       </c>
-      <c r="L72" s="16" t="n">
+      <c r="L72" s="20" t="n">
         <v>39.5</v>
       </c>
-      <c r="M72" s="16" t="n">
+      <c r="M72" s="20" t="n">
         <v>34.93</v>
       </c>
-      <c r="N72" s="16" t="n">
+      <c r="N72" s="20" t="n">
         <v>31.55</v>
       </c>
-      <c r="O72" s="16" t="n">
+      <c r="O72" s="20" t="n">
         <v>29</v>
       </c>
-      <c r="P72" s="16" t="n">
+      <c r="P72" s="20" t="n">
         <v>29.75</v>
       </c>
-      <c r="Q72" s="16" t="n">
+      <c r="Q72" s="20" t="n">
         <v>29.25</v>
       </c>
-      <c r="R72" s="16" t="n">
+      <c r="R72" s="20" t="n">
         <v>30.48</v>
       </c>
-      <c r="S72" s="16" t="n">
+      <c r="S72" s="20" t="n">
         <v>30.13</v>
       </c>
-      <c r="T72" s="16" t="n">
+      <c r="T72" s="20" t="n">
         <v>29.78</v>
       </c>
-      <c r="U72" s="16" t="n">
+      <c r="U72" s="20" t="n">
         <v>33.47</v>
       </c>
-      <c r="V72" s="16" t="n">
+      <c r="V72" s="20" t="n">
         <v>29.87</v>
       </c>
-      <c r="W72" s="16" t="n">
+      <c r="W72" s="20" t="n">
         <v>34.4</v>
       </c>
-      <c r="X72" s="16" t="n">
+      <c r="X72" s="20" t="n">
         <v>38.93</v>
       </c>
-      <c r="Y72" s="16" t="n">
+      <c r="Y72" s="20" t="n">
         <v>39.37</v>
       </c>
-      <c r="Z72" s="16" t="n">
+      <c r="Z72" s="20" t="n">
         <v>39.2</v>
       </c>
-      <c r="AA72" s="16" t="n">
+      <c r="AA72" s="20" t="n">
         <v>38.98</v>
       </c>
-      <c r="AB72" s="16" t="n">
+      <c r="AB72" s="20" t="n">
         <v>40.15</v>
       </c>
-      <c r="AC72" s="16" t="n">
+      <c r="AC72" s="20" t="n">
         <v>39.25</v>
       </c>
-      <c r="AD72" s="16" t="n">
+      <c r="AD72" s="20" t="n">
         <v>39.2</v>
       </c>
-      <c r="AE72" s="16" t="n">
+      <c r="AE72" s="20" t="n">
         <v>39.17</v>
       </c>
-      <c r="AF72" s="16" t="n">
+      <c r="AF72" s="20" t="n">
         <v>34</v>
       </c>
-      <c r="AG72" s="16" t="n">
+      <c r="AG72" s="20" t="n">
         <v>30.6</v>
       </c>
       <c r="AH72" s="6" t="n">
@@ -6845,7 +6869,7 @@
       </c>
       <c r="AI72" s="6" t="inlineStr"/>
       <c r="AJ72" s="6" t="inlineStr"/>
-      <c r="AK72" s="15" t="n"/>
+      <c r="AK72" s="19" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -6856,97 +6880,97 @@
       <c r="B73" s="6" t="n">
         <v>567.25</v>
       </c>
-      <c r="C73" s="16" t="n">
+      <c r="C73" s="20" t="n">
         <v>38.72</v>
       </c>
-      <c r="D73" s="16" t="n">
+      <c r="D73" s="20" t="n">
         <v>40.58</v>
       </c>
-      <c r="E73" s="16" t="n">
+      <c r="E73" s="20" t="n">
         <v>39.1</v>
       </c>
-      <c r="F73" s="16" t="n">
+      <c r="F73" s="20" t="n">
         <v>39.9</v>
       </c>
-      <c r="G73" s="16" t="n">
+      <c r="G73" s="20" t="n">
         <v>39.67</v>
       </c>
-      <c r="H73" s="16" t="n">
+      <c r="H73" s="20" t="n">
         <v>40.1</v>
       </c>
-      <c r="I73" s="16" t="n">
+      <c r="I73" s="20" t="n">
         <v>39.85</v>
       </c>
-      <c r="J73" s="16" t="n">
+      <c r="J73" s="20" t="n">
         <v>39.65</v>
       </c>
-      <c r="K73" s="16" t="n">
+      <c r="K73" s="20" t="n">
         <v>39.85</v>
       </c>
-      <c r="L73" s="16" t="n">
+      <c r="L73" s="20" t="n">
         <v>41.55</v>
       </c>
-      <c r="M73" s="16" t="n">
+      <c r="M73" s="20" t="n">
         <v>39.78</v>
       </c>
-      <c r="N73" s="16" t="n">
+      <c r="N73" s="20" t="n">
         <v>40.37</v>
       </c>
-      <c r="O73" s="16" t="n">
+      <c r="O73" s="20" t="n">
         <v>39.98</v>
       </c>
-      <c r="P73" s="16" t="n">
+      <c r="P73" s="20" t="n">
         <v>40</v>
       </c>
-      <c r="Q73" s="16" t="n">
+      <c r="Q73" s="20" t="n">
         <v>40.37</v>
       </c>
-      <c r="R73" s="16" t="n">
+      <c r="R73" s="20" t="n">
         <v>41.43</v>
       </c>
-      <c r="S73" s="16" t="n">
+      <c r="S73" s="20" t="n">
         <v>41.08</v>
       </c>
-      <c r="T73" s="16" t="n">
+      <c r="T73" s="20" t="n">
         <v>41.43</v>
       </c>
-      <c r="U73" s="16" t="n">
+      <c r="U73" s="20" t="n">
         <v>41.27</v>
       </c>
-      <c r="V73" s="16" t="n">
+      <c r="V73" s="20" t="n">
         <v>41.17</v>
       </c>
-      <c r="W73" s="16" t="n">
+      <c r="W73" s="20" t="n">
         <v>42.6</v>
       </c>
-      <c r="X73" s="16" t="n">
+      <c r="X73" s="20" t="n">
         <v>41.62</v>
       </c>
-      <c r="Y73" s="16" t="n">
+      <c r="Y73" s="20" t="n">
         <v>40.92</v>
       </c>
-      <c r="Z73" s="16" t="n">
+      <c r="Z73" s="20" t="n">
         <v>40.37</v>
       </c>
-      <c r="AA73" s="16" t="n">
+      <c r="AA73" s="20" t="n">
         <v>41.32</v>
       </c>
-      <c r="AB73" s="16" t="n">
+      <c r="AB73" s="20" t="n">
         <v>41.38</v>
       </c>
-      <c r="AC73" s="16" t="n">
+      <c r="AC73" s="20" t="n">
         <v>41.15</v>
       </c>
-      <c r="AD73" s="16" t="n">
+      <c r="AD73" s="20" t="n">
         <v>41.08</v>
       </c>
-      <c r="AE73" s="16" t="n">
+      <c r="AE73" s="20" t="n">
         <v>41.33</v>
       </c>
-      <c r="AF73" s="16" t="n">
+      <c r="AF73" s="20" t="n">
         <v>41.33</v>
       </c>
-      <c r="AG73" s="16" t="n">
+      <c r="AG73" s="20" t="n">
         <v>41.08</v>
       </c>
       <c r="AH73" s="6" t="n">
@@ -6954,7 +6978,7 @@
       </c>
       <c r="AI73" s="6" t="inlineStr"/>
       <c r="AJ73" s="6" t="inlineStr"/>
-      <c r="AK73" s="15" t="n"/>
+      <c r="AK73" s="19" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -7058,12 +7082,12 @@
       <c r="AG74" s="7" t="n">
         <v>81.13</v>
       </c>
-      <c r="AH74" s="6" t="n">
+      <c r="AH74" s="8" t="n">
         <v>80.11</v>
       </c>
       <c r="AI74" s="6" t="inlineStr"/>
       <c r="AJ74" s="6" t="inlineStr"/>
-      <c r="AK74" s="15" t="n"/>
+      <c r="AK74" s="19" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
@@ -7074,97 +7098,97 @@
       <c r="B75" s="6" t="n">
         <v>591.25</v>
       </c>
-      <c r="C75" s="16" t="n">
+      <c r="C75" s="20" t="n">
         <v>32.83</v>
       </c>
-      <c r="D75" s="16" t="n">
+      <c r="D75" s="20" t="n">
         <v>34.15</v>
       </c>
-      <c r="E75" s="16" t="n">
+      <c r="E75" s="20" t="n">
         <v>32.67</v>
       </c>
-      <c r="F75" s="16" t="n">
+      <c r="F75" s="20" t="n">
         <v>32.47</v>
       </c>
-      <c r="G75" s="16" t="n">
+      <c r="G75" s="20" t="n">
         <v>32.32</v>
       </c>
-      <c r="H75" s="16" t="n">
+      <c r="H75" s="20" t="n">
         <v>32.23</v>
       </c>
-      <c r="I75" s="16" t="n">
+      <c r="I75" s="20" t="n">
         <v>32.47</v>
       </c>
-      <c r="J75" s="16" t="n">
+      <c r="J75" s="20" t="n">
         <v>34.17</v>
       </c>
-      <c r="K75" s="16" t="n">
+      <c r="K75" s="20" t="n">
         <v>37.27</v>
       </c>
-      <c r="L75" s="9" t="n">
+      <c r="L75" s="11" t="n">
         <v>45.08</v>
       </c>
-      <c r="M75" s="16" t="n">
+      <c r="M75" s="20" t="n">
         <v>39.83</v>
       </c>
-      <c r="N75" s="16" t="n">
+      <c r="N75" s="20" t="n">
         <v>32.48</v>
       </c>
-      <c r="O75" s="16" t="n">
+      <c r="O75" s="20" t="n">
         <v>32.45</v>
       </c>
-      <c r="P75" s="16" t="n">
+      <c r="P75" s="20" t="n">
         <v>32.08</v>
       </c>
-      <c r="Q75" s="16" t="n">
+      <c r="Q75" s="20" t="n">
         <v>31.9</v>
       </c>
-      <c r="R75" s="16" t="n">
+      <c r="R75" s="20" t="n">
         <v>31.83</v>
       </c>
-      <c r="S75" s="16" t="n">
+      <c r="S75" s="20" t="n">
         <v>32.6</v>
       </c>
-      <c r="T75" s="16" t="n">
+      <c r="T75" s="20" t="n">
         <v>34.5</v>
       </c>
-      <c r="U75" s="16" t="n">
+      <c r="U75" s="20" t="n">
         <v>31.85</v>
       </c>
-      <c r="V75" s="16" t="n">
+      <c r="V75" s="20" t="n">
         <v>32.28</v>
       </c>
-      <c r="W75" s="16" t="n">
+      <c r="W75" s="20" t="n">
         <v>37.38</v>
       </c>
-      <c r="X75" s="9" t="n">
+      <c r="X75" s="11" t="n">
         <v>43.55</v>
       </c>
-      <c r="Y75" s="16" t="n">
+      <c r="Y75" s="20" t="n">
         <v>42.93</v>
       </c>
-      <c r="Z75" s="9" t="n">
+      <c r="Z75" s="11" t="n">
         <v>43.05</v>
       </c>
-      <c r="AA75" s="9" t="n">
+      <c r="AA75" s="11" t="n">
         <v>43.25</v>
       </c>
-      <c r="AB75" s="9" t="n">
+      <c r="AB75" s="11" t="n">
         <v>43.55</v>
       </c>
-      <c r="AC75" s="16" t="n">
+      <c r="AC75" s="20" t="n">
         <v>43</v>
       </c>
-      <c r="AD75" s="9" t="n">
+      <c r="AD75" s="11" t="n">
         <v>43.15</v>
       </c>
-      <c r="AE75" s="9" t="n">
+      <c r="AE75" s="11" t="n">
         <v>43.18</v>
       </c>
-      <c r="AF75" s="16" t="n">
+      <c r="AF75" s="20" t="n">
         <v>39.02</v>
       </c>
-      <c r="AG75" s="16" t="n">
+      <c r="AG75" s="20" t="n">
         <v>32.98</v>
       </c>
       <c r="AH75" s="6" t="n">
@@ -7172,7 +7196,7 @@
       </c>
       <c r="AI75" s="6" t="inlineStr"/>
       <c r="AJ75" s="6" t="inlineStr"/>
-      <c r="AK75" s="15" t="n"/>
+      <c r="AK75" s="19" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -7183,97 +7207,97 @@
       <c r="B76" s="6" t="n">
         <v>603.25</v>
       </c>
-      <c r="C76" s="16" t="n">
+      <c r="C76" s="20" t="n">
         <v>32.45</v>
       </c>
-      <c r="D76" s="16" t="n">
+      <c r="D76" s="20" t="n">
         <v>32.73</v>
       </c>
-      <c r="E76" s="16" t="n">
+      <c r="E76" s="20" t="n">
         <v>32.25</v>
       </c>
-      <c r="F76" s="16" t="n">
+      <c r="F76" s="20" t="n">
         <v>32.4</v>
       </c>
-      <c r="G76" s="16" t="n">
+      <c r="G76" s="20" t="n">
         <v>32.48</v>
       </c>
-      <c r="H76" s="16" t="n">
+      <c r="H76" s="20" t="n">
         <v>32.68</v>
       </c>
-      <c r="I76" s="16" t="n">
+      <c r="I76" s="20" t="n">
         <v>33.48</v>
       </c>
-      <c r="J76" s="16" t="n">
+      <c r="J76" s="20" t="n">
         <v>32.9</v>
       </c>
-      <c r="K76" s="16" t="n">
+      <c r="K76" s="20" t="n">
         <v>39.47</v>
       </c>
-      <c r="L76" s="9" t="n">
+      <c r="L76" s="11" t="n">
         <v>46.07</v>
       </c>
-      <c r="M76" s="16" t="n">
+      <c r="M76" s="20" t="n">
         <v>39.98</v>
       </c>
-      <c r="N76" s="16" t="n">
+      <c r="N76" s="20" t="n">
         <v>32.65</v>
       </c>
-      <c r="O76" s="16" t="n">
+      <c r="O76" s="20" t="n">
         <v>32.73</v>
       </c>
-      <c r="P76" s="16" t="n">
+      <c r="P76" s="20" t="n">
         <v>33.17</v>
       </c>
-      <c r="Q76" s="16" t="n">
+      <c r="Q76" s="20" t="n">
         <v>32.58</v>
       </c>
-      <c r="R76" s="16" t="n">
+      <c r="R76" s="20" t="n">
         <v>32.58</v>
       </c>
-      <c r="S76" s="16" t="n">
+      <c r="S76" s="20" t="n">
         <v>33</v>
       </c>
-      <c r="T76" s="16" t="n">
+      <c r="T76" s="20" t="n">
         <v>33.23</v>
       </c>
-      <c r="U76" s="16" t="n">
+      <c r="U76" s="20" t="n">
         <v>32.78</v>
       </c>
-      <c r="V76" s="16" t="n">
+      <c r="V76" s="20" t="n">
         <v>32.85</v>
       </c>
-      <c r="W76" s="9" t="n">
+      <c r="W76" s="11" t="n">
         <v>44.6</v>
       </c>
-      <c r="X76" s="9" t="n">
+      <c r="X76" s="11" t="n">
         <v>46.48</v>
       </c>
-      <c r="Y76" s="9" t="n">
+      <c r="Y76" s="11" t="n">
         <v>46.78</v>
       </c>
-      <c r="Z76" s="9" t="n">
+      <c r="Z76" s="11" t="n">
         <v>46.05</v>
       </c>
-      <c r="AA76" s="9" t="n">
+      <c r="AA76" s="11" t="n">
         <v>46.18</v>
       </c>
-      <c r="AB76" s="9" t="n">
+      <c r="AB76" s="11" t="n">
         <v>48.7</v>
       </c>
-      <c r="AC76" s="9" t="n">
+      <c r="AC76" s="11" t="n">
         <v>47.2</v>
       </c>
-      <c r="AD76" s="9" t="n">
+      <c r="AD76" s="11" t="n">
         <v>46.2</v>
       </c>
-      <c r="AE76" s="9" t="n">
+      <c r="AE76" s="11" t="n">
         <v>46.93</v>
       </c>
-      <c r="AF76" s="16" t="n">
+      <c r="AF76" s="20" t="n">
         <v>39.97</v>
       </c>
-      <c r="AG76" s="16" t="n">
+      <c r="AG76" s="20" t="n">
         <v>33.45</v>
       </c>
       <c r="AH76" s="6" t="n">
@@ -7281,116 +7305,116 @@
       </c>
       <c r="AI76" s="6" t="inlineStr"/>
       <c r="AJ76" s="6" t="inlineStr"/>
-      <c r="AK76" s="15" t="n"/>
+      <c r="AK76" s="19" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="10" t="inlineStr">
+      <c r="A77" s="12" t="inlineStr">
         <is>
           <t>CANAL SUR - TELEVISION MUN</t>
         </is>
       </c>
-      <c r="B77" s="11" t="n">
+      <c r="B77" s="13" t="n">
         <v>621.25</v>
       </c>
-      <c r="C77" s="12" t="n">
+      <c r="C77" s="14" t="n">
         <v>75.28</v>
       </c>
-      <c r="D77" s="12" t="n">
+      <c r="D77" s="14" t="n">
         <v>75.62</v>
       </c>
-      <c r="E77" s="12" t="n">
+      <c r="E77" s="14" t="n">
         <v>69.09999999999999</v>
       </c>
-      <c r="F77" s="12" t="n">
+      <c r="F77" s="14" t="n">
         <v>70.23</v>
       </c>
-      <c r="G77" s="12" t="n">
+      <c r="G77" s="14" t="n">
         <v>70.78</v>
       </c>
-      <c r="H77" s="12" t="n">
+      <c r="H77" s="14" t="n">
         <v>69.77</v>
       </c>
-      <c r="I77" s="12" t="n">
+      <c r="I77" s="14" t="n">
         <v>70.2</v>
       </c>
-      <c r="J77" s="12" t="n">
+      <c r="J77" s="14" t="n">
         <v>68.48</v>
       </c>
-      <c r="K77" s="12" t="n">
+      <c r="K77" s="14" t="n">
         <v>83.56999999999999</v>
       </c>
-      <c r="L77" s="12" t="n">
+      <c r="L77" s="14" t="n">
         <v>99.27</v>
       </c>
-      <c r="M77" s="12" t="n">
+      <c r="M77" s="14" t="n">
         <v>84.33</v>
       </c>
-      <c r="N77" s="12" t="n">
+      <c r="N77" s="14" t="n">
         <v>69.23</v>
       </c>
-      <c r="O77" s="12" t="n">
+      <c r="O77" s="14" t="n">
         <v>68.53</v>
       </c>
-      <c r="P77" s="12" t="n">
+      <c r="P77" s="14" t="n">
         <v>70.05</v>
       </c>
-      <c r="Q77" s="12" t="n">
+      <c r="Q77" s="14" t="n">
         <v>68.92</v>
       </c>
-      <c r="R77" s="12" t="n">
+      <c r="R77" s="14" t="n">
         <v>71.08</v>
       </c>
-      <c r="S77" s="12" t="n">
+      <c r="S77" s="14" t="n">
         <v>72.17</v>
       </c>
-      <c r="T77" s="12" t="n">
+      <c r="T77" s="14" t="n">
         <v>71.13</v>
       </c>
-      <c r="U77" s="12" t="n">
+      <c r="U77" s="14" t="n">
         <v>72.59999999999999</v>
       </c>
-      <c r="V77" s="12" t="n">
+      <c r="V77" s="14" t="n">
         <v>69.81999999999999</v>
       </c>
-      <c r="W77" s="12" t="n">
+      <c r="W77" s="14" t="n">
         <v>85.8</v>
       </c>
-      <c r="X77" s="12" t="n">
+      <c r="X77" s="14" t="n">
         <v>99.72</v>
       </c>
-      <c r="Y77" s="12" t="n">
+      <c r="Y77" s="14" t="n">
         <v>99.43000000000001</v>
       </c>
-      <c r="Z77" s="12" t="n">
+      <c r="Z77" s="14" t="n">
         <v>99.73</v>
       </c>
-      <c r="AA77" s="12" t="n">
+      <c r="AA77" s="14" t="n">
         <v>99.73</v>
       </c>
-      <c r="AB77" s="12" t="n">
+      <c r="AB77" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="AC77" s="12" t="n">
+      <c r="AC77" s="14" t="n">
         <v>99.05</v>
       </c>
-      <c r="AD77" s="12" t="n">
+      <c r="AD77" s="14" t="n">
         <v>99.48</v>
       </c>
-      <c r="AE77" s="12" t="n">
+      <c r="AE77" s="14" t="n">
         <v>99.78</v>
       </c>
-      <c r="AF77" s="12" t="n">
+      <c r="AF77" s="14" t="n">
         <v>85.68000000000001</v>
       </c>
-      <c r="AG77" s="12" t="n">
+      <c r="AG77" s="14" t="n">
         <v>73.12</v>
       </c>
-      <c r="AH77" s="11" t="n">
+      <c r="AH77" s="15" t="n">
         <v>81.02</v>
       </c>
-      <c r="AI77" s="11" t="inlineStr"/>
-      <c r="AJ77" s="11" t="inlineStr"/>
-      <c r="AK77" s="17" t="n"/>
+      <c r="AI77" s="13" t="inlineStr"/>
+      <c r="AJ77" s="13" t="inlineStr"/>
+      <c r="AK77" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="33">

--- a/ReportesUnificados/loja_ReporteUnificado.xlsx
+++ b/ReportesUnificados/loja_ReporteUnificado.xlsx
@@ -300,7 +300,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4762500" cy="952500"/>
@@ -323,9 +323,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>33</col>
+      <col>35</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2476500" cy="1143000"/>
@@ -373,7 +373,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>33</col>
+      <col>35</col>
       <colOff>0</colOff>
       <row>55</row>
       <rowOff>0</rowOff>

--- a/ReportesUnificados/loja_ReporteUnificado.xlsx
+++ b/ReportesUnificados/loja_ReporteUnificado.xlsx
@@ -30,12 +30,18 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFC4A2C"/>
+        <bgColor rgb="FFFC4A2C"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -171,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -191,19 +197,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -214,7 +226,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -789,7 +804,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 28/08/2025</t>
+          <t>FECHA PRESENTACIÓN: 01/09/2025</t>
         </is>
       </c>
     </row>
@@ -1027,11 +1042,11 @@
       <c r="AH11" s="6" t="n">
         <v>102.07</v>
       </c>
-      <c r="AI11" s="6" t="n">
+      <c r="AI11" s="8" t="n">
         <v>261.08</v>
       </c>
       <c r="AJ11" s="6" t="inlineStr"/>
-      <c r="AK11" s="8" t="inlineStr"/>
+      <c r="AK11" s="9" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1138,11 +1153,11 @@
       <c r="AH12" s="6" t="n">
         <v>102.13</v>
       </c>
-      <c r="AI12" s="6" t="n">
+      <c r="AI12" s="8" t="n">
         <v>400.33</v>
       </c>
       <c r="AJ12" s="6" t="inlineStr"/>
-      <c r="AK12" s="8" t="inlineStr"/>
+      <c r="AK12" s="9" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1249,11 +1264,11 @@
       <c r="AH13" s="6" t="n">
         <v>106.91</v>
       </c>
-      <c r="AI13" s="6" t="n">
+      <c r="AI13" s="8" t="n">
         <v>485.39</v>
       </c>
       <c r="AJ13" s="6" t="inlineStr"/>
-      <c r="AK13" s="8" t="inlineStr"/>
+      <c r="AK13" s="9" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1360,11 +1375,11 @@
       <c r="AH14" s="6" t="n">
         <v>109.46</v>
       </c>
-      <c r="AI14" s="6" t="n">
+      <c r="AI14" s="8" t="n">
         <v>372.17</v>
       </c>
       <c r="AJ14" s="6" t="inlineStr"/>
-      <c r="AK14" s="8" t="inlineStr"/>
+      <c r="AK14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1471,11 +1486,11 @@
       <c r="AH15" s="6" t="n">
         <v>103.29</v>
       </c>
-      <c r="AI15" s="6" t="n">
+      <c r="AI15" s="8" t="n">
         <v>388.41</v>
       </c>
       <c r="AJ15" s="6" t="inlineStr"/>
-      <c r="AK15" s="8" t="inlineStr"/>
+      <c r="AK15" s="9" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1582,11 +1597,11 @@
       <c r="AH16" s="6" t="n">
         <v>84.44</v>
       </c>
-      <c r="AI16" s="6" t="n">
+      <c r="AI16" s="8" t="n">
         <v>444.57</v>
       </c>
       <c r="AJ16" s="6" t="inlineStr"/>
-      <c r="AK16" s="8" t="inlineStr"/>
+      <c r="AK16" s="9" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1693,11 +1708,11 @@
       <c r="AH17" s="6" t="n">
         <v>88.02</v>
       </c>
-      <c r="AI17" s="6" t="n">
+      <c r="AI17" s="8" t="n">
         <v>364.81</v>
       </c>
       <c r="AJ17" s="6" t="inlineStr"/>
-      <c r="AK17" s="8" t="inlineStr"/>
+      <c r="AK17" s="9" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1804,11 +1819,11 @@
       <c r="AH18" s="6" t="n">
         <v>103.91</v>
       </c>
-      <c r="AI18" s="6" t="n">
+      <c r="AI18" s="8" t="n">
         <v>415.88</v>
       </c>
       <c r="AJ18" s="6" t="inlineStr"/>
-      <c r="AK18" s="8" t="inlineStr"/>
+      <c r="AK18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1915,11 +1930,11 @@
       <c r="AH19" s="6" t="n">
         <v>104.17</v>
       </c>
-      <c r="AI19" s="6" t="n">
+      <c r="AI19" s="8" t="n">
         <v>418.76</v>
       </c>
       <c r="AJ19" s="6" t="inlineStr"/>
-      <c r="AK19" s="8" t="inlineStr"/>
+      <c r="AK19" s="9" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -2026,11 +2041,11 @@
       <c r="AH20" s="6" t="n">
         <v>95.44</v>
       </c>
-      <c r="AI20" s="6" t="n">
+      <c r="AI20" s="8" t="n">
         <v>400.73</v>
       </c>
       <c r="AJ20" s="6" t="inlineStr"/>
-      <c r="AK20" s="8" t="inlineStr"/>
+      <c r="AK20" s="9" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2137,11 +2152,11 @@
       <c r="AH21" s="6" t="n">
         <v>96.64</v>
       </c>
-      <c r="AI21" s="6" t="n">
+      <c r="AI21" s="8" t="n">
         <v>406.58</v>
       </c>
       <c r="AJ21" s="6" t="inlineStr"/>
-      <c r="AK21" s="8" t="inlineStr"/>
+      <c r="AK21" s="9" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2248,11 +2263,11 @@
       <c r="AH22" s="6" t="n">
         <v>105.92</v>
       </c>
-      <c r="AI22" s="6" t="n">
+      <c r="AI22" s="8" t="n">
         <v>387.36</v>
       </c>
       <c r="AJ22" s="6" t="inlineStr"/>
-      <c r="AK22" s="8" t="inlineStr"/>
+      <c r="AK22" s="9" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -2359,11 +2374,11 @@
       <c r="AH23" s="6" t="n">
         <v>102.97</v>
       </c>
-      <c r="AI23" s="6" t="n">
+      <c r="AI23" s="8" t="n">
         <v>419.3</v>
       </c>
       <c r="AJ23" s="6" t="inlineStr"/>
-      <c r="AK23" s="8" t="inlineStr"/>
+      <c r="AK23" s="9" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2470,11 +2485,11 @@
       <c r="AH24" s="6" t="n">
         <v>104.14</v>
       </c>
-      <c r="AI24" s="6" t="n">
+      <c r="AI24" s="8" t="n">
         <v>408.72</v>
       </c>
       <c r="AJ24" s="6" t="inlineStr"/>
-      <c r="AK24" s="8" t="inlineStr"/>
+      <c r="AK24" s="9" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -2581,11 +2596,11 @@
       <c r="AH25" s="6" t="n">
         <v>92.11</v>
       </c>
-      <c r="AI25" s="6" t="n">
+      <c r="AI25" s="8" t="n">
         <v>439.51</v>
       </c>
       <c r="AJ25" s="6" t="inlineStr"/>
-      <c r="AK25" s="8" t="inlineStr"/>
+      <c r="AK25" s="9" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -2692,11 +2707,11 @@
       <c r="AH26" s="6" t="n">
         <v>103.28</v>
       </c>
-      <c r="AI26" s="6" t="n">
+      <c r="AI26" s="8" t="n">
         <v>412.36</v>
       </c>
       <c r="AJ26" s="6" t="inlineStr"/>
-      <c r="AK26" s="8" t="inlineStr"/>
+      <c r="AK26" s="9" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2803,11 +2818,11 @@
       <c r="AH27" s="6" t="n">
         <v>95.87</v>
       </c>
-      <c r="AI27" s="6" t="n">
+      <c r="AI27" s="8" t="n">
         <v>398.86</v>
       </c>
       <c r="AJ27" s="6" t="inlineStr"/>
-      <c r="AK27" s="8" t="inlineStr"/>
+      <c r="AK27" s="9" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -2818,19 +2833,19 @@
       <c r="B28" s="6" t="n">
         <v>96.09999999999999</v>
       </c>
-      <c r="C28" s="9" t="n">
+      <c r="C28" s="10" t="n">
         <v>52.79</v>
       </c>
-      <c r="D28" s="9" t="n">
+      <c r="D28" s="10" t="n">
         <v>53.24</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="10" t="n">
         <v>53.39</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="10" t="n">
         <v>52.91</v>
       </c>
-      <c r="G28" s="9" t="n">
+      <c r="G28" s="10" t="n">
         <v>52.24</v>
       </c>
       <c r="H28" s="7" t="n">
@@ -2839,7 +2854,7 @@
       <c r="I28" s="7" t="n">
         <v>54.52</v>
       </c>
-      <c r="J28" s="9" t="n">
+      <c r="J28" s="10" t="n">
         <v>53.58</v>
       </c>
       <c r="K28" s="7" t="n">
@@ -2914,11 +2929,11 @@
       <c r="AH28" s="6" t="n">
         <v>81.95</v>
       </c>
-      <c r="AI28" s="6" t="n">
+      <c r="AI28" s="8" t="n">
         <v>546.02</v>
       </c>
       <c r="AJ28" s="6" t="inlineStr"/>
-      <c r="AK28" s="8" t="inlineStr"/>
+      <c r="AK28" s="9" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -3025,11 +3040,11 @@
       <c r="AH29" s="6" t="n">
         <v>98.59</v>
       </c>
-      <c r="AI29" s="6" t="n">
+      <c r="AI29" s="8" t="n">
         <v>391.54</v>
       </c>
       <c r="AJ29" s="6" t="inlineStr"/>
-      <c r="AK29" s="8" t="inlineStr"/>
+      <c r="AK29" s="9" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -3136,11 +3151,11 @@
       <c r="AH30" s="6" t="n">
         <v>106.71</v>
       </c>
-      <c r="AI30" s="6" t="n">
+      <c r="AI30" s="8" t="n">
         <v>476.01</v>
       </c>
       <c r="AJ30" s="6" t="inlineStr"/>
-      <c r="AK30" s="8" t="inlineStr"/>
+      <c r="AK30" s="9" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -3151,34 +3166,34 @@
       <c r="B31" s="6" t="n">
         <v>97.3</v>
       </c>
-      <c r="C31" s="9" t="n">
+      <c r="C31" s="10" t="n">
         <v>50.96</v>
       </c>
-      <c r="D31" s="9" t="n">
+      <c r="D31" s="10" t="n">
         <v>51.09</v>
       </c>
-      <c r="E31" s="9" t="n">
+      <c r="E31" s="10" t="n">
         <v>51.49</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F31" s="10" t="n">
         <v>51.17</v>
       </c>
-      <c r="G31" s="9" t="n">
+      <c r="G31" s="10" t="n">
         <v>50.6</v>
       </c>
-      <c r="H31" s="9" t="n">
+      <c r="H31" s="10" t="n">
         <v>53.72</v>
       </c>
       <c r="I31" s="7" t="n">
         <v>54.82</v>
       </c>
-      <c r="J31" s="9" t="n">
+      <c r="J31" s="10" t="n">
         <v>51.84</v>
       </c>
-      <c r="K31" s="9" t="n">
+      <c r="K31" s="10" t="n">
         <v>51.62</v>
       </c>
-      <c r="L31" s="9" t="n">
+      <c r="L31" s="10" t="n">
         <v>50.18</v>
       </c>
       <c r="M31" s="7" t="n">
@@ -3187,13 +3202,13 @@
       <c r="N31" s="7" t="n">
         <v>58.57</v>
       </c>
-      <c r="O31" s="9" t="n">
+      <c r="O31" s="10" t="n">
         <v>53.3</v>
       </c>
       <c r="P31" s="7" t="n">
         <v>55.63</v>
       </c>
-      <c r="Q31" s="9" t="n">
+      <c r="Q31" s="10" t="n">
         <v>53.83</v>
       </c>
       <c r="R31" s="7" t="n">
@@ -3202,40 +3217,40 @@
       <c r="S31" s="7" t="n">
         <v>55.61</v>
       </c>
-      <c r="T31" s="9" t="n">
+      <c r="T31" s="10" t="n">
         <v>53.61</v>
       </c>
       <c r="U31" s="7" t="n">
         <v>56.99</v>
       </c>
-      <c r="V31" s="9" t="n">
+      <c r="V31" s="10" t="n">
         <v>53.82</v>
       </c>
-      <c r="W31" s="9" t="n">
+      <c r="W31" s="10" t="n">
         <v>51.9</v>
       </c>
-      <c r="X31" s="9" t="n">
+      <c r="X31" s="10" t="n">
         <v>49.27</v>
       </c>
-      <c r="Y31" s="9" t="n">
+      <c r="Y31" s="10" t="n">
         <v>49.44</v>
       </c>
-      <c r="Z31" s="9" t="n">
+      <c r="Z31" s="10" t="n">
         <v>50.36</v>
       </c>
-      <c r="AA31" s="9" t="n">
+      <c r="AA31" s="10" t="n">
         <v>49.75</v>
       </c>
-      <c r="AB31" s="9" t="n">
+      <c r="AB31" s="10" t="n">
         <v>49.7</v>
       </c>
-      <c r="AC31" s="9" t="n">
+      <c r="AC31" s="10" t="n">
         <v>49.16</v>
       </c>
-      <c r="AD31" s="9" t="n">
+      <c r="AD31" s="10" t="n">
         <v>50.04</v>
       </c>
-      <c r="AE31" s="9" t="n">
+      <c r="AE31" s="10" t="n">
         <v>49.68</v>
       </c>
       <c r="AF31" s="7" t="n">
@@ -3244,14 +3259,14 @@
       <c r="AG31" s="7" t="n">
         <v>61.41</v>
       </c>
-      <c r="AH31" s="6" t="n">
+      <c r="AH31" s="8" t="n">
         <v>52.73</v>
       </c>
-      <c r="AI31" s="6" t="n">
+      <c r="AI31" s="8" t="n">
         <v>703.75</v>
       </c>
       <c r="AJ31" s="6" t="inlineStr"/>
-      <c r="AK31" s="8" t="inlineStr"/>
+      <c r="AK31" s="9" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -3358,11 +3373,11 @@
       <c r="AH32" s="6" t="n">
         <v>91.68000000000001</v>
       </c>
-      <c r="AI32" s="6" t="n">
+      <c r="AI32" s="8" t="n">
         <v>413.77</v>
       </c>
       <c r="AJ32" s="6" t="inlineStr"/>
-      <c r="AK32" s="8" t="inlineStr"/>
+      <c r="AK32" s="9" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -3469,11 +3484,11 @@
       <c r="AH33" s="6" t="n">
         <v>92.72</v>
       </c>
-      <c r="AI33" s="6" t="n">
+      <c r="AI33" s="8" t="n">
         <v>438.53</v>
       </c>
       <c r="AJ33" s="6" t="inlineStr"/>
-      <c r="AK33" s="8" t="inlineStr"/>
+      <c r="AK33" s="9" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -3580,11 +3595,11 @@
       <c r="AH34" s="6" t="n">
         <v>89.5</v>
       </c>
-      <c r="AI34" s="6" t="n">
+      <c r="AI34" s="8" t="n">
         <v>496.73</v>
       </c>
       <c r="AJ34" s="6" t="inlineStr"/>
-      <c r="AK34" s="8" t="inlineStr"/>
+      <c r="AK34" s="9" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -3691,11 +3706,11 @@
       <c r="AH35" s="6" t="n">
         <v>96.39</v>
       </c>
-      <c r="AI35" s="6" t="n">
+      <c r="AI35" s="8" t="n">
         <v>387.7</v>
       </c>
       <c r="AJ35" s="6" t="inlineStr"/>
-      <c r="AK35" s="8" t="inlineStr"/>
+      <c r="AK35" s="9" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -3802,11 +3817,11 @@
       <c r="AH36" s="6" t="n">
         <v>100.54</v>
       </c>
-      <c r="AI36" s="6" t="n">
+      <c r="AI36" s="8" t="n">
         <v>400.46</v>
       </c>
       <c r="AJ36" s="6" t="inlineStr"/>
-      <c r="AK36" s="8" t="inlineStr"/>
+      <c r="AK36" s="9" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -3913,11 +3928,11 @@
       <c r="AH37" s="6" t="n">
         <v>104.41</v>
       </c>
-      <c r="AI37" s="6" t="n">
+      <c r="AI37" s="8" t="n">
         <v>422.94</v>
       </c>
       <c r="AJ37" s="6" t="inlineStr"/>
-      <c r="AK37" s="8" t="inlineStr"/>
+      <c r="AK37" s="9" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -4024,11 +4039,11 @@
       <c r="AH38" s="6" t="n">
         <v>88.23</v>
       </c>
-      <c r="AI38" s="6" t="n">
+      <c r="AI38" s="8" t="n">
         <v>419.65</v>
       </c>
       <c r="AJ38" s="6" t="inlineStr"/>
-      <c r="AK38" s="8" t="inlineStr"/>
+      <c r="AK38" s="9" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -4135,11 +4150,11 @@
       <c r="AH39" s="6" t="n">
         <v>100.66</v>
       </c>
-      <c r="AI39" s="6" t="n">
+      <c r="AI39" s="8" t="n">
         <v>399.91</v>
       </c>
       <c r="AJ39" s="6" t="inlineStr"/>
-      <c r="AK39" s="8" t="inlineStr"/>
+      <c r="AK39" s="9" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -4246,11 +4261,11 @@
       <c r="AH40" s="6" t="n">
         <v>100.45</v>
       </c>
-      <c r="AI40" s="6" t="n">
+      <c r="AI40" s="8" t="n">
         <v>407.04</v>
       </c>
       <c r="AJ40" s="6" t="inlineStr"/>
-      <c r="AK40" s="8" t="inlineStr"/>
+      <c r="AK40" s="9" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -4357,11 +4372,11 @@
       <c r="AH41" s="6" t="n">
         <v>105.27</v>
       </c>
-      <c r="AI41" s="6" t="n">
+      <c r="AI41" s="8" t="n">
         <v>316.68</v>
       </c>
       <c r="AJ41" s="6" t="inlineStr"/>
-      <c r="AK41" s="8" t="inlineStr"/>
+      <c r="AK41" s="9" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -4372,49 +4387,49 @@
       <c r="B42" s="6" t="n">
         <v>103.7</v>
       </c>
-      <c r="C42" s="9" t="n">
+      <c r="C42" s="10" t="n">
         <v>50.32</v>
       </c>
-      <c r="D42" s="9" t="n">
+      <c r="D42" s="10" t="n">
         <v>50.59</v>
       </c>
-      <c r="E42" s="9" t="n">
+      <c r="E42" s="10" t="n">
         <v>51.34</v>
       </c>
-      <c r="F42" s="9" t="n">
+      <c r="F42" s="10" t="n">
         <v>51.32</v>
       </c>
-      <c r="G42" s="9" t="n">
+      <c r="G42" s="10" t="n">
         <v>50.85</v>
       </c>
-      <c r="H42" s="9" t="n">
+      <c r="H42" s="10" t="n">
         <v>52.08</v>
       </c>
-      <c r="I42" s="9" t="n">
+      <c r="I42" s="10" t="n">
         <v>53.42</v>
       </c>
-      <c r="J42" s="9" t="n">
+      <c r="J42" s="10" t="n">
         <v>51.71</v>
       </c>
-      <c r="K42" s="9" t="n">
+      <c r="K42" s="10" t="n">
         <v>52.18</v>
       </c>
-      <c r="L42" s="9" t="n">
+      <c r="L42" s="10" t="n">
         <v>50.53</v>
       </c>
-      <c r="M42" s="9" t="n">
+      <c r="M42" s="10" t="n">
         <v>53.58</v>
       </c>
       <c r="N42" s="7" t="n">
         <v>56.22</v>
       </c>
-      <c r="O42" s="9" t="n">
+      <c r="O42" s="10" t="n">
         <v>52.72</v>
       </c>
       <c r="P42" s="7" t="n">
         <v>54.54</v>
       </c>
-      <c r="Q42" s="9" t="n">
+      <c r="Q42" s="10" t="n">
         <v>52.73</v>
       </c>
       <c r="R42" s="7" t="n">
@@ -4423,40 +4438,40 @@
       <c r="S42" s="7" t="n">
         <v>54.02</v>
       </c>
-      <c r="T42" s="9" t="n">
+      <c r="T42" s="10" t="n">
         <v>52.69</v>
       </c>
       <c r="U42" s="7" t="n">
         <v>55.21</v>
       </c>
-      <c r="V42" s="9" t="n">
+      <c r="V42" s="10" t="n">
         <v>53.4</v>
       </c>
-      <c r="W42" s="9" t="n">
+      <c r="W42" s="10" t="n">
         <v>51.93</v>
       </c>
-      <c r="X42" s="9" t="n">
+      <c r="X42" s="10" t="n">
         <v>50.58</v>
       </c>
-      <c r="Y42" s="9" t="n">
+      <c r="Y42" s="10" t="n">
         <v>50.59</v>
       </c>
-      <c r="Z42" s="9" t="n">
+      <c r="Z42" s="10" t="n">
         <v>51.81</v>
       </c>
-      <c r="AA42" s="9" t="n">
+      <c r="AA42" s="10" t="n">
         <v>50.61</v>
       </c>
-      <c r="AB42" s="9" t="n">
+      <c r="AB42" s="10" t="n">
         <v>50.29</v>
       </c>
-      <c r="AC42" s="9" t="n">
+      <c r="AC42" s="10" t="n">
         <v>50.64</v>
       </c>
-      <c r="AD42" s="9" t="n">
+      <c r="AD42" s="10" t="n">
         <v>50.85</v>
       </c>
-      <c r="AE42" s="9" t="n">
+      <c r="AE42" s="10" t="n">
         <v>50.63</v>
       </c>
       <c r="AF42" s="7" t="n">
@@ -4465,14 +4480,14 @@
       <c r="AG42" s="7" t="n">
         <v>59.83</v>
       </c>
-      <c r="AH42" s="6" t="n">
+      <c r="AH42" s="8" t="n">
         <v>52.47</v>
       </c>
-      <c r="AI42" s="6" t="n">
+      <c r="AI42" s="8" t="n">
         <v>504.72</v>
       </c>
       <c r="AJ42" s="6" t="inlineStr"/>
-      <c r="AK42" s="8" t="inlineStr"/>
+      <c r="AK42" s="9" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -4579,11 +4594,11 @@
       <c r="AH43" s="6" t="n">
         <v>97.64</v>
       </c>
-      <c r="AI43" s="6" t="n">
+      <c r="AI43" s="8" t="n">
         <v>265.12</v>
       </c>
       <c r="AJ43" s="6" t="inlineStr"/>
-      <c r="AK43" s="8" t="inlineStr"/>
+      <c r="AK43" s="9" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -4690,11 +4705,11 @@
       <c r="AH44" s="6" t="n">
         <v>102.15</v>
       </c>
-      <c r="AI44" s="6" t="n">
+      <c r="AI44" s="8" t="n">
         <v>348.54</v>
       </c>
       <c r="AJ44" s="6" t="inlineStr"/>
-      <c r="AK44" s="8" t="inlineStr"/>
+      <c r="AK44" s="9" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -4801,11 +4816,11 @@
       <c r="AH45" s="6" t="n">
         <v>100.05</v>
       </c>
-      <c r="AI45" s="6" t="n">
+      <c r="AI45" s="8" t="n">
         <v>456.27</v>
       </c>
       <c r="AJ45" s="6" t="inlineStr"/>
-      <c r="AK45" s="8" t="inlineStr"/>
+      <c r="AK45" s="9" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -4912,11 +4927,11 @@
       <c r="AH46" s="6" t="n">
         <v>100.69</v>
       </c>
-      <c r="AI46" s="6" t="n">
+      <c r="AI46" s="8" t="n">
         <v>420.89</v>
       </c>
       <c r="AJ46" s="6" t="inlineStr"/>
-      <c r="AK46" s="8" t="inlineStr"/>
+      <c r="AK46" s="9" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -5023,11 +5038,11 @@
       <c r="AH47" s="6" t="n">
         <v>100.35</v>
       </c>
-      <c r="AI47" s="6" t="n">
+      <c r="AI47" s="8" t="n">
         <v>416.29</v>
       </c>
       <c r="AJ47" s="6" t="inlineStr"/>
-      <c r="AK47" s="8" t="inlineStr"/>
+      <c r="AK47" s="9" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -5134,11 +5149,11 @@
       <c r="AH48" s="6" t="n">
         <v>93.23999999999999</v>
       </c>
-      <c r="AI48" s="6" t="n">
+      <c r="AI48" s="8" t="n">
         <v>389.74</v>
       </c>
       <c r="AJ48" s="6" t="inlineStr"/>
-      <c r="AK48" s="8" t="inlineStr"/>
+      <c r="AK48" s="9" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -5245,11 +5260,11 @@
       <c r="AH49" s="6" t="n">
         <v>86.04000000000001</v>
       </c>
-      <c r="AI49" s="6" t="n">
+      <c r="AI49" s="8" t="n">
         <v>363.9</v>
       </c>
       <c r="AJ49" s="6" t="inlineStr"/>
-      <c r="AK49" s="8" t="inlineStr"/>
+      <c r="AK49" s="9" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -5356,122 +5371,122 @@
       <c r="AH50" s="6" t="n">
         <v>101.65</v>
       </c>
-      <c r="AI50" s="6" t="n">
+      <c r="AI50" s="8" t="n">
         <v>310.71</v>
       </c>
       <c r="AJ50" s="6" t="inlineStr"/>
-      <c r="AK50" s="8" t="inlineStr"/>
+      <c r="AK50" s="9" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="10" t="inlineStr">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t>RADIO POSITIVA FM</t>
         </is>
       </c>
-      <c r="B51" s="11" t="n">
+      <c r="B51" s="12" t="n">
         <v>107.7</v>
       </c>
-      <c r="C51" s="12" t="n">
+      <c r="C51" s="13" t="n">
         <v>76.42</v>
       </c>
-      <c r="D51" s="12" t="n">
+      <c r="D51" s="13" t="n">
         <v>76.77</v>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="E51" s="13" t="n">
         <v>81.34999999999999</v>
       </c>
-      <c r="F51" s="12" t="n">
+      <c r="F51" s="13" t="n">
         <v>79.69</v>
       </c>
-      <c r="G51" s="12" t="n">
+      <c r="G51" s="13" t="n">
         <v>79.67</v>
       </c>
-      <c r="H51" s="12" t="n">
+      <c r="H51" s="13" t="n">
         <v>79.69</v>
       </c>
-      <c r="I51" s="12" t="n">
+      <c r="I51" s="13" t="n">
         <v>79.95999999999999</v>
       </c>
-      <c r="J51" s="12" t="n">
+      <c r="J51" s="13" t="n">
         <v>79.01000000000001</v>
       </c>
-      <c r="K51" s="12" t="n">
+      <c r="K51" s="13" t="n">
         <v>82.05</v>
       </c>
-      <c r="L51" s="12" t="n">
+      <c r="L51" s="13" t="n">
         <v>84.64</v>
       </c>
-      <c r="M51" s="12" t="n">
+      <c r="M51" s="13" t="n">
         <v>81.73</v>
       </c>
-      <c r="N51" s="12" t="n">
+      <c r="N51" s="13" t="n">
         <v>79.73</v>
       </c>
-      <c r="O51" s="12" t="n">
+      <c r="O51" s="13" t="n">
         <v>78.31999999999999</v>
       </c>
-      <c r="P51" s="12" t="n">
+      <c r="P51" s="13" t="n">
         <v>79.45999999999999</v>
       </c>
-      <c r="Q51" s="12" t="n">
+      <c r="Q51" s="13" t="n">
         <v>79.41</v>
       </c>
-      <c r="R51" s="12" t="n">
+      <c r="R51" s="13" t="n">
         <v>79.73999999999999</v>
       </c>
-      <c r="S51" s="12" t="n">
+      <c r="S51" s="13" t="n">
         <v>79.73</v>
       </c>
-      <c r="T51" s="12" t="n">
+      <c r="T51" s="13" t="n">
         <v>79.68000000000001</v>
       </c>
-      <c r="U51" s="12" t="n">
+      <c r="U51" s="13" t="n">
         <v>80.61</v>
       </c>
-      <c r="V51" s="12" t="n">
+      <c r="V51" s="13" t="n">
         <v>79.16</v>
       </c>
-      <c r="W51" s="12" t="n">
+      <c r="W51" s="13" t="n">
         <v>81.95999999999999</v>
       </c>
-      <c r="X51" s="12" t="n">
+      <c r="X51" s="13" t="n">
         <v>84.26000000000001</v>
       </c>
-      <c r="Y51" s="12" t="n">
+      <c r="Y51" s="13" t="n">
         <v>83.81</v>
       </c>
-      <c r="Z51" s="12" t="n">
+      <c r="Z51" s="13" t="n">
         <v>84.69</v>
       </c>
-      <c r="AA51" s="12" t="n">
+      <c r="AA51" s="13" t="n">
         <v>84.03</v>
       </c>
-      <c r="AB51" s="12" t="n">
+      <c r="AB51" s="13" t="n">
         <v>83.94</v>
       </c>
-      <c r="AC51" s="12" t="n">
+      <c r="AC51" s="13" t="n">
         <v>83.68000000000001</v>
       </c>
-      <c r="AD51" s="12" t="n">
+      <c r="AD51" s="13" t="n">
         <v>83.81999999999999</v>
       </c>
-      <c r="AE51" s="12" t="n">
+      <c r="AE51" s="13" t="n">
         <v>84.41</v>
       </c>
-      <c r="AF51" s="12" t="n">
+      <c r="AF51" s="13" t="n">
         <v>82.03</v>
       </c>
-      <c r="AG51" s="12" t="n">
+      <c r="AG51" s="13" t="n">
         <v>79.73</v>
       </c>
-      <c r="AH51" s="11" t="n">
+      <c r="AH51" s="12" t="n">
         <v>81.06999999999999</v>
       </c>
-      <c r="AI51" s="11" t="n">
+      <c r="AI51" s="14" t="n">
         <v>264.88</v>
       </c>
-      <c r="AJ51" s="11" t="inlineStr"/>
-      <c r="AK51" s="13" t="inlineStr"/>
+      <c r="AJ51" s="12" t="inlineStr"/>
+      <c r="AK51" s="15" t="inlineStr"/>
     </row>
     <row r="52"/>
     <row r="53"/>
@@ -5520,7 +5535,7 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 28/08/2025</t>
+          <t>FECHA PRESENTACIÓN: 01/09/2025</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5661,7 @@
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK61" s="14" t="n"/>
+      <c r="AK61" s="16" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -5750,12 +5765,12 @@
       <c r="AG62" s="7" t="n">
         <v>92.92</v>
       </c>
-      <c r="AH62" s="6" t="n">
+      <c r="AH62" s="7" t="n">
         <v>89.59999999999999</v>
       </c>
       <c r="AI62" s="6" t="inlineStr"/>
       <c r="AJ62" s="6" t="inlineStr"/>
-      <c r="AK62" s="15" t="n"/>
+      <c r="AK62" s="17" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -5859,12 +5874,12 @@
       <c r="AG63" s="7" t="n">
         <v>93.13</v>
       </c>
-      <c r="AH63" s="6" t="n">
+      <c r="AH63" s="7" t="n">
         <v>89.2</v>
       </c>
       <c r="AI63" s="6" t="inlineStr"/>
       <c r="AJ63" s="6" t="inlineStr"/>
-      <c r="AK63" s="15" t="n"/>
+      <c r="AK63" s="17" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -5962,18 +5977,18 @@
       <c r="AE64" s="7" t="n">
         <v>73.13</v>
       </c>
-      <c r="AF64" s="7" t="n">
+      <c r="AF64" s="10" t="n">
         <v>71</v>
       </c>
       <c r="AG64" s="7" t="n">
         <v>81.65000000000001</v>
       </c>
-      <c r="AH64" s="6" t="n">
+      <c r="AH64" s="7" t="n">
         <v>83.06</v>
       </c>
       <c r="AI64" s="6" t="inlineStr"/>
       <c r="AJ64" s="6" t="inlineStr"/>
-      <c r="AK64" s="15" t="n"/>
+      <c r="AK64" s="17" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -6077,12 +6092,12 @@
       <c r="AG65" s="7" t="n">
         <v>95.03</v>
       </c>
-      <c r="AH65" s="6" t="n">
+      <c r="AH65" s="7" t="n">
         <v>92.47</v>
       </c>
       <c r="AI65" s="6" t="inlineStr"/>
       <c r="AJ65" s="6" t="inlineStr"/>
-      <c r="AK65" s="15" t="n"/>
+      <c r="AK65" s="17" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -6186,12 +6201,12 @@
       <c r="AG66" s="7" t="n">
         <v>86.5</v>
       </c>
-      <c r="AH66" s="6" t="n">
+      <c r="AH66" s="7" t="n">
         <v>81</v>
       </c>
       <c r="AI66" s="6" t="inlineStr"/>
       <c r="AJ66" s="6" t="inlineStr"/>
-      <c r="AK66" s="15" t="n"/>
+      <c r="AK66" s="17" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -6295,12 +6310,12 @@
       <c r="AG67" s="7" t="n">
         <v>90.22</v>
       </c>
-      <c r="AH67" s="6" t="n">
+      <c r="AH67" s="7" t="n">
         <v>91.06999999999999</v>
       </c>
       <c r="AI67" s="6" t="inlineStr"/>
       <c r="AJ67" s="6" t="inlineStr"/>
-      <c r="AK67" s="15" t="n"/>
+      <c r="AK67" s="17" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -6311,37 +6326,37 @@
       <c r="B68" s="6" t="n">
         <v>199.25</v>
       </c>
-      <c r="C68" s="7" t="n">
+      <c r="C68" s="10" t="n">
         <v>67.97</v>
       </c>
-      <c r="D68" s="7" t="n">
+      <c r="D68" s="10" t="n">
         <v>67.75</v>
       </c>
-      <c r="E68" s="7" t="n">
+      <c r="E68" s="10" t="n">
         <v>70.25</v>
       </c>
-      <c r="F68" s="7" t="n">
+      <c r="F68" s="10" t="n">
         <v>70.18000000000001</v>
       </c>
-      <c r="G68" s="7" t="n">
+      <c r="G68" s="10" t="n">
         <v>69.31999999999999</v>
       </c>
-      <c r="H68" s="7" t="n">
+      <c r="H68" s="10" t="n">
         <v>70.72</v>
       </c>
       <c r="I68" s="7" t="n">
         <v>71.78</v>
       </c>
-      <c r="J68" s="7" t="n">
+      <c r="J68" s="10" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="K68" s="7" t="n">
+      <c r="K68" s="10" t="n">
         <v>68.25</v>
       </c>
-      <c r="L68" s="7" t="n">
+      <c r="L68" s="10" t="n">
         <v>65.83</v>
       </c>
-      <c r="M68" s="7" t="n">
+      <c r="M68" s="10" t="n">
         <v>67.34999999999999</v>
       </c>
       <c r="N68" s="7" t="n">
@@ -6353,63 +6368,63 @@
       <c r="P68" s="7" t="n">
         <v>72.13</v>
       </c>
-      <c r="Q68" s="7" t="n">
+      <c r="Q68" s="10" t="n">
         <v>70.43000000000001</v>
       </c>
-      <c r="R68" s="7" t="n">
+      <c r="R68" s="10" t="n">
         <v>70.83</v>
       </c>
       <c r="S68" s="7" t="n">
         <v>72.3</v>
       </c>
-      <c r="T68" s="7" t="n">
+      <c r="T68" s="10" t="n">
         <v>69.37</v>
       </c>
       <c r="U68" s="7" t="n">
         <v>71.59999999999999</v>
       </c>
-      <c r="V68" s="7" t="n">
+      <c r="V68" s="10" t="n">
         <v>70.43000000000001</v>
       </c>
-      <c r="W68" s="7" t="n">
+      <c r="W68" s="10" t="n">
         <v>68.2</v>
       </c>
-      <c r="X68" s="7" t="n">
+      <c r="X68" s="10" t="n">
         <v>65.47</v>
       </c>
-      <c r="Y68" s="7" t="n">
+      <c r="Y68" s="10" t="n">
         <v>64.65000000000001</v>
       </c>
-      <c r="Z68" s="7" t="n">
+      <c r="Z68" s="10" t="n">
         <v>65.03</v>
       </c>
-      <c r="AA68" s="7" t="n">
+      <c r="AA68" s="10" t="n">
         <v>64.8</v>
       </c>
-      <c r="AB68" s="7" t="n">
+      <c r="AB68" s="10" t="n">
         <v>65.42</v>
       </c>
-      <c r="AC68" s="7" t="n">
+      <c r="AC68" s="10" t="n">
         <v>65.77</v>
       </c>
-      <c r="AD68" s="7" t="n">
+      <c r="AD68" s="10" t="n">
         <v>65.05</v>
       </c>
-      <c r="AE68" s="7" t="n">
+      <c r="AE68" s="10" t="n">
         <v>66.34999999999999</v>
       </c>
-      <c r="AF68" s="7" t="n">
+      <c r="AF68" s="10" t="n">
         <v>69.90000000000001</v>
       </c>
       <c r="AG68" s="7" t="n">
         <v>74.7</v>
       </c>
-      <c r="AH68" s="6" t="n">
+      <c r="AH68" s="10" t="n">
         <v>68.88</v>
       </c>
       <c r="AI68" s="6" t="inlineStr"/>
       <c r="AJ68" s="6" t="inlineStr"/>
-      <c r="AK68" s="15" t="n"/>
+      <c r="AK68" s="17" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -6513,12 +6528,12 @@
       <c r="AG69" s="7" t="n">
         <v>84.68000000000001</v>
       </c>
-      <c r="AH69" s="6" t="n">
+      <c r="AH69" s="7" t="n">
         <v>81.86</v>
       </c>
       <c r="AI69" s="6" t="inlineStr"/>
       <c r="AJ69" s="6" t="inlineStr"/>
-      <c r="AK69" s="15" t="n"/>
+      <c r="AK69" s="17" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -6529,105 +6544,105 @@
       <c r="B70" s="6" t="n">
         <v>531.25</v>
       </c>
-      <c r="C70" s="16" t="n">
+      <c r="C70" s="18" t="n">
         <v>28.37</v>
       </c>
-      <c r="D70" s="16" t="n">
+      <c r="D70" s="18" t="n">
         <v>29.4</v>
       </c>
-      <c r="E70" s="16" t="n">
+      <c r="E70" s="18" t="n">
         <v>27.83</v>
       </c>
-      <c r="F70" s="16" t="n">
+      <c r="F70" s="18" t="n">
         <v>28.55</v>
       </c>
-      <c r="G70" s="16" t="n">
+      <c r="G70" s="18" t="n">
         <v>28.55</v>
       </c>
-      <c r="H70" s="16" t="n">
+      <c r="H70" s="18" t="n">
         <v>27.95</v>
       </c>
-      <c r="I70" s="16" t="n">
+      <c r="I70" s="18" t="n">
         <v>28</v>
       </c>
-      <c r="J70" s="16" t="n">
+      <c r="J70" s="18" t="n">
         <v>28.12</v>
       </c>
-      <c r="K70" s="16" t="n">
+      <c r="K70" s="18" t="n">
         <v>33.42</v>
       </c>
-      <c r="L70" s="16" t="n">
+      <c r="L70" s="18" t="n">
         <v>38.92</v>
       </c>
-      <c r="M70" s="16" t="n">
+      <c r="M70" s="18" t="n">
         <v>34.12</v>
       </c>
-      <c r="N70" s="16" t="n">
+      <c r="N70" s="18" t="n">
         <v>28.75</v>
       </c>
-      <c r="O70" s="16" t="n">
+      <c r="O70" s="18" t="n">
         <v>28.63</v>
       </c>
-      <c r="P70" s="16" t="n">
+      <c r="P70" s="18" t="n">
         <v>27.68</v>
       </c>
-      <c r="Q70" s="16" t="n">
+      <c r="Q70" s="18" t="n">
         <v>28.35</v>
       </c>
-      <c r="R70" s="16" t="n">
+      <c r="R70" s="18" t="n">
         <v>27.93</v>
       </c>
-      <c r="S70" s="16" t="n">
+      <c r="S70" s="18" t="n">
         <v>28.22</v>
       </c>
-      <c r="T70" s="16" t="n">
+      <c r="T70" s="18" t="n">
         <v>29</v>
       </c>
-      <c r="U70" s="16" t="n">
+      <c r="U70" s="18" t="n">
         <v>28.68</v>
       </c>
-      <c r="V70" s="16" t="n">
+      <c r="V70" s="18" t="n">
         <v>27.77</v>
       </c>
-      <c r="W70" s="16" t="n">
+      <c r="W70" s="18" t="n">
         <v>33.18</v>
       </c>
-      <c r="X70" s="16" t="n">
+      <c r="X70" s="18" t="n">
         <v>39.05</v>
       </c>
-      <c r="Y70" s="16" t="n">
+      <c r="Y70" s="18" t="n">
         <v>39.05</v>
       </c>
-      <c r="Z70" s="16" t="n">
+      <c r="Z70" s="18" t="n">
         <v>38.88</v>
       </c>
-      <c r="AA70" s="16" t="n">
+      <c r="AA70" s="18" t="n">
         <v>38.68</v>
       </c>
-      <c r="AB70" s="16" t="n">
+      <c r="AB70" s="18" t="n">
         <v>38.78</v>
       </c>
-      <c r="AC70" s="16" t="n">
+      <c r="AC70" s="18" t="n">
         <v>39.45</v>
       </c>
-      <c r="AD70" s="16" t="n">
+      <c r="AD70" s="18" t="n">
         <v>38.48</v>
       </c>
-      <c r="AE70" s="16" t="n">
+      <c r="AE70" s="18" t="n">
         <v>39.23</v>
       </c>
-      <c r="AF70" s="16" t="n">
+      <c r="AF70" s="18" t="n">
         <v>33.83</v>
       </c>
-      <c r="AG70" s="16" t="n">
+      <c r="AG70" s="18" t="n">
         <v>28.65</v>
       </c>
-      <c r="AH70" s="6" t="n">
+      <c r="AH70" s="8" t="n">
         <v>32.11</v>
       </c>
       <c r="AI70" s="6" t="inlineStr"/>
       <c r="AJ70" s="6" t="inlineStr"/>
-      <c r="AK70" s="15" t="n"/>
+      <c r="AK70" s="17" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -6638,105 +6653,105 @@
       <c r="B71" s="6" t="n">
         <v>537.25</v>
       </c>
-      <c r="C71" s="7" t="n">
+      <c r="C71" s="10" t="n">
         <v>67.88</v>
       </c>
-      <c r="D71" s="7" t="n">
+      <c r="D71" s="10" t="n">
         <v>67.90000000000001</v>
       </c>
-      <c r="E71" s="7" t="n">
+      <c r="E71" s="10" t="n">
         <v>68.84999999999999</v>
       </c>
-      <c r="F71" s="7" t="n">
+      <c r="F71" s="10" t="n">
         <v>68.3</v>
       </c>
-      <c r="G71" s="7" t="n">
+      <c r="G71" s="10" t="n">
         <v>67.59999999999999</v>
       </c>
-      <c r="H71" s="7" t="n">
+      <c r="H71" s="10" t="n">
         <v>66.7</v>
       </c>
-      <c r="I71" s="7" t="n">
+      <c r="I71" s="10" t="n">
         <v>67.18000000000001</v>
       </c>
-      <c r="J71" s="7" t="n">
+      <c r="J71" s="10" t="n">
         <v>66.09999999999999</v>
       </c>
-      <c r="K71" s="7" t="n">
+      <c r="K71" s="10" t="n">
         <v>66.88</v>
       </c>
-      <c r="L71" s="7" t="n">
+      <c r="L71" s="10" t="n">
         <v>68.42</v>
       </c>
-      <c r="M71" s="7" t="n">
+      <c r="M71" s="10" t="n">
         <v>68.22</v>
       </c>
-      <c r="N71" s="7" t="n">
+      <c r="N71" s="10" t="n">
         <v>68.06999999999999</v>
       </c>
-      <c r="O71" s="7" t="n">
+      <c r="O71" s="10" t="n">
         <v>68</v>
       </c>
-      <c r="P71" s="7" t="n">
+      <c r="P71" s="10" t="n">
         <v>68.68000000000001</v>
       </c>
-      <c r="Q71" s="7" t="n">
+      <c r="Q71" s="10" t="n">
         <v>68.65000000000001</v>
       </c>
-      <c r="R71" s="7" t="n">
+      <c r="R71" s="10" t="n">
         <v>70.63</v>
       </c>
-      <c r="S71" s="7" t="n">
+      <c r="S71" s="10" t="n">
         <v>70.2</v>
       </c>
-      <c r="T71" s="7" t="n">
+      <c r="T71" s="10" t="n">
         <v>67.40000000000001</v>
       </c>
-      <c r="U71" s="7" t="n">
+      <c r="U71" s="10" t="n">
         <v>69.95</v>
       </c>
-      <c r="V71" s="7" t="n">
+      <c r="V71" s="10" t="n">
         <v>70.65000000000001</v>
       </c>
-      <c r="W71" s="7" t="n">
+      <c r="W71" s="10" t="n">
         <v>70.73</v>
       </c>
-      <c r="X71" s="7" t="n">
+      <c r="X71" s="10" t="n">
         <v>68.55</v>
       </c>
-      <c r="Y71" s="7" t="n">
+      <c r="Y71" s="10" t="n">
         <v>68.7</v>
       </c>
-      <c r="Z71" s="7" t="n">
+      <c r="Z71" s="10" t="n">
         <v>66.93000000000001</v>
       </c>
-      <c r="AA71" s="7" t="n">
+      <c r="AA71" s="10" t="n">
         <v>68.27</v>
       </c>
-      <c r="AB71" s="7" t="n">
+      <c r="AB71" s="10" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="AC71" s="7" t="n">
+      <c r="AC71" s="10" t="n">
         <v>69.8</v>
       </c>
-      <c r="AD71" s="7" t="n">
+      <c r="AD71" s="10" t="n">
         <v>70.15000000000001</v>
       </c>
-      <c r="AE71" s="7" t="n">
+      <c r="AE71" s="10" t="n">
         <v>69.95</v>
       </c>
-      <c r="AF71" s="7" t="n">
+      <c r="AF71" s="10" t="n">
         <v>69.75</v>
       </c>
       <c r="AG71" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="AH71" s="6" t="n">
+      <c r="AH71" s="10" t="n">
         <v>68.69</v>
       </c>
       <c r="AI71" s="6" t="inlineStr"/>
       <c r="AJ71" s="6" t="inlineStr"/>
-      <c r="AK71" s="15" t="n"/>
+      <c r="AK71" s="17" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -6747,105 +6762,105 @@
       <c r="B72" s="6" t="n">
         <v>543.25</v>
       </c>
-      <c r="C72" s="16" t="n">
+      <c r="C72" s="18" t="n">
         <v>30.25</v>
       </c>
-      <c r="D72" s="16" t="n">
+      <c r="D72" s="18" t="n">
         <v>28.95</v>
       </c>
-      <c r="E72" s="16" t="n">
+      <c r="E72" s="18" t="n">
         <v>29.82</v>
       </c>
-      <c r="F72" s="16" t="n">
+      <c r="F72" s="18" t="n">
         <v>30.2</v>
       </c>
-      <c r="G72" s="16" t="n">
+      <c r="G72" s="18" t="n">
         <v>30.07</v>
       </c>
-      <c r="H72" s="16" t="n">
+      <c r="H72" s="18" t="n">
         <v>29.28</v>
       </c>
-      <c r="I72" s="16" t="n">
+      <c r="I72" s="18" t="n">
         <v>29.25</v>
       </c>
-      <c r="J72" s="16" t="n">
+      <c r="J72" s="18" t="n">
         <v>30.22</v>
       </c>
-      <c r="K72" s="16" t="n">
+      <c r="K72" s="18" t="n">
         <v>35.05</v>
       </c>
-      <c r="L72" s="16" t="n">
+      <c r="L72" s="18" t="n">
         <v>39.5</v>
       </c>
-      <c r="M72" s="16" t="n">
+      <c r="M72" s="18" t="n">
         <v>34.93</v>
       </c>
-      <c r="N72" s="16" t="n">
+      <c r="N72" s="18" t="n">
         <v>31.55</v>
       </c>
-      <c r="O72" s="16" t="n">
+      <c r="O72" s="18" t="n">
         <v>29</v>
       </c>
-      <c r="P72" s="16" t="n">
+      <c r="P72" s="18" t="n">
         <v>29.75</v>
       </c>
-      <c r="Q72" s="16" t="n">
+      <c r="Q72" s="18" t="n">
         <v>29.25</v>
       </c>
-      <c r="R72" s="16" t="n">
+      <c r="R72" s="18" t="n">
         <v>30.48</v>
       </c>
-      <c r="S72" s="16" t="n">
+      <c r="S72" s="18" t="n">
         <v>30.13</v>
       </c>
-      <c r="T72" s="16" t="n">
+      <c r="T72" s="18" t="n">
         <v>29.78</v>
       </c>
-      <c r="U72" s="16" t="n">
+      <c r="U72" s="18" t="n">
         <v>33.47</v>
       </c>
-      <c r="V72" s="16" t="n">
+      <c r="V72" s="18" t="n">
         <v>29.87</v>
       </c>
-      <c r="W72" s="16" t="n">
+      <c r="W72" s="18" t="n">
         <v>34.4</v>
       </c>
-      <c r="X72" s="16" t="n">
+      <c r="X72" s="18" t="n">
         <v>38.93</v>
       </c>
-      <c r="Y72" s="16" t="n">
+      <c r="Y72" s="18" t="n">
         <v>39.37</v>
       </c>
-      <c r="Z72" s="16" t="n">
+      <c r="Z72" s="18" t="n">
         <v>39.2</v>
       </c>
-      <c r="AA72" s="16" t="n">
+      <c r="AA72" s="18" t="n">
         <v>38.98</v>
       </c>
-      <c r="AB72" s="16" t="n">
+      <c r="AB72" s="18" t="n">
         <v>40.15</v>
       </c>
-      <c r="AC72" s="16" t="n">
+      <c r="AC72" s="18" t="n">
         <v>39.25</v>
       </c>
-      <c r="AD72" s="16" t="n">
+      <c r="AD72" s="18" t="n">
         <v>39.2</v>
       </c>
-      <c r="AE72" s="16" t="n">
+      <c r="AE72" s="18" t="n">
         <v>39.17</v>
       </c>
-      <c r="AF72" s="16" t="n">
+      <c r="AF72" s="18" t="n">
         <v>34</v>
       </c>
-      <c r="AG72" s="16" t="n">
+      <c r="AG72" s="18" t="n">
         <v>30.6</v>
       </c>
-      <c r="AH72" s="6" t="n">
+      <c r="AH72" s="8" t="n">
         <v>33.36</v>
       </c>
       <c r="AI72" s="6" t="inlineStr"/>
       <c r="AJ72" s="6" t="inlineStr"/>
-      <c r="AK72" s="15" t="n"/>
+      <c r="AK72" s="17" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -6856,105 +6871,105 @@
       <c r="B73" s="6" t="n">
         <v>567.25</v>
       </c>
-      <c r="C73" s="16" t="n">
+      <c r="C73" s="18" t="n">
         <v>38.72</v>
       </c>
-      <c r="D73" s="16" t="n">
+      <c r="D73" s="18" t="n">
         <v>40.58</v>
       </c>
-      <c r="E73" s="16" t="n">
+      <c r="E73" s="18" t="n">
         <v>39.1</v>
       </c>
-      <c r="F73" s="16" t="n">
+      <c r="F73" s="18" t="n">
         <v>39.9</v>
       </c>
-      <c r="G73" s="16" t="n">
+      <c r="G73" s="18" t="n">
         <v>39.67</v>
       </c>
-      <c r="H73" s="16" t="n">
+      <c r="H73" s="18" t="n">
         <v>40.1</v>
       </c>
-      <c r="I73" s="16" t="n">
+      <c r="I73" s="18" t="n">
         <v>39.85</v>
       </c>
-      <c r="J73" s="16" t="n">
+      <c r="J73" s="18" t="n">
         <v>39.65</v>
       </c>
-      <c r="K73" s="16" t="n">
+      <c r="K73" s="18" t="n">
         <v>39.85</v>
       </c>
-      <c r="L73" s="16" t="n">
+      <c r="L73" s="18" t="n">
         <v>41.55</v>
       </c>
-      <c r="M73" s="16" t="n">
+      <c r="M73" s="18" t="n">
         <v>39.78</v>
       </c>
-      <c r="N73" s="16" t="n">
+      <c r="N73" s="18" t="n">
         <v>40.37</v>
       </c>
-      <c r="O73" s="16" t="n">
+      <c r="O73" s="18" t="n">
         <v>39.98</v>
       </c>
-      <c r="P73" s="16" t="n">
+      <c r="P73" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="Q73" s="16" t="n">
+      <c r="Q73" s="18" t="n">
         <v>40.37</v>
       </c>
-      <c r="R73" s="16" t="n">
+      <c r="R73" s="18" t="n">
         <v>41.43</v>
       </c>
-      <c r="S73" s="16" t="n">
+      <c r="S73" s="18" t="n">
         <v>41.08</v>
       </c>
-      <c r="T73" s="16" t="n">
+      <c r="T73" s="18" t="n">
         <v>41.43</v>
       </c>
-      <c r="U73" s="16" t="n">
+      <c r="U73" s="18" t="n">
         <v>41.27</v>
       </c>
-      <c r="V73" s="16" t="n">
+      <c r="V73" s="18" t="n">
         <v>41.17</v>
       </c>
-      <c r="W73" s="16" t="n">
+      <c r="W73" s="18" t="n">
         <v>42.6</v>
       </c>
-      <c r="X73" s="16" t="n">
+      <c r="X73" s="18" t="n">
         <v>41.62</v>
       </c>
-      <c r="Y73" s="16" t="n">
+      <c r="Y73" s="18" t="n">
         <v>40.92</v>
       </c>
-      <c r="Z73" s="16" t="n">
+      <c r="Z73" s="18" t="n">
         <v>40.37</v>
       </c>
-      <c r="AA73" s="16" t="n">
+      <c r="AA73" s="18" t="n">
         <v>41.32</v>
       </c>
-      <c r="AB73" s="16" t="n">
+      <c r="AB73" s="18" t="n">
         <v>41.38</v>
       </c>
-      <c r="AC73" s="16" t="n">
+      <c r="AC73" s="18" t="n">
         <v>41.15</v>
       </c>
-      <c r="AD73" s="16" t="n">
+      <c r="AD73" s="18" t="n">
         <v>41.08</v>
       </c>
-      <c r="AE73" s="16" t="n">
+      <c r="AE73" s="18" t="n">
         <v>41.33</v>
       </c>
-      <c r="AF73" s="16" t="n">
+      <c r="AF73" s="18" t="n">
         <v>41.33</v>
       </c>
-      <c r="AG73" s="16" t="n">
+      <c r="AG73" s="18" t="n">
         <v>41.08</v>
       </c>
-      <c r="AH73" s="6" t="n">
+      <c r="AH73" s="8" t="n">
         <v>40.65</v>
       </c>
       <c r="AI73" s="6" t="inlineStr"/>
       <c r="AJ73" s="6" t="inlineStr"/>
-      <c r="AK73" s="15" t="n"/>
+      <c r="AK73" s="17" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -7058,12 +7073,12 @@
       <c r="AG74" s="7" t="n">
         <v>81.13</v>
       </c>
-      <c r="AH74" s="6" t="n">
+      <c r="AH74" s="7" t="n">
         <v>80.11</v>
       </c>
       <c r="AI74" s="6" t="inlineStr"/>
       <c r="AJ74" s="6" t="inlineStr"/>
-      <c r="AK74" s="15" t="n"/>
+      <c r="AK74" s="17" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
@@ -7074,105 +7089,105 @@
       <c r="B75" s="6" t="n">
         <v>591.25</v>
       </c>
-      <c r="C75" s="16" t="n">
+      <c r="C75" s="18" t="n">
         <v>32.83</v>
       </c>
-      <c r="D75" s="16" t="n">
+      <c r="D75" s="18" t="n">
         <v>34.15</v>
       </c>
-      <c r="E75" s="16" t="n">
+      <c r="E75" s="18" t="n">
         <v>32.67</v>
       </c>
-      <c r="F75" s="16" t="n">
+      <c r="F75" s="18" t="n">
         <v>32.47</v>
       </c>
-      <c r="G75" s="16" t="n">
+      <c r="G75" s="18" t="n">
         <v>32.32</v>
       </c>
-      <c r="H75" s="16" t="n">
+      <c r="H75" s="18" t="n">
         <v>32.23</v>
       </c>
-      <c r="I75" s="16" t="n">
+      <c r="I75" s="18" t="n">
         <v>32.47</v>
       </c>
-      <c r="J75" s="16" t="n">
+      <c r="J75" s="18" t="n">
         <v>34.17</v>
       </c>
-      <c r="K75" s="16" t="n">
+      <c r="K75" s="18" t="n">
         <v>37.27</v>
       </c>
-      <c r="L75" s="9" t="n">
+      <c r="L75" s="18" t="n">
         <v>45.08</v>
       </c>
-      <c r="M75" s="16" t="n">
+      <c r="M75" s="18" t="n">
         <v>39.83</v>
       </c>
-      <c r="N75" s="16" t="n">
+      <c r="N75" s="18" t="n">
         <v>32.48</v>
       </c>
-      <c r="O75" s="16" t="n">
+      <c r="O75" s="18" t="n">
         <v>32.45</v>
       </c>
-      <c r="P75" s="16" t="n">
+      <c r="P75" s="18" t="n">
         <v>32.08</v>
       </c>
-      <c r="Q75" s="16" t="n">
+      <c r="Q75" s="18" t="n">
         <v>31.9</v>
       </c>
-      <c r="R75" s="16" t="n">
+      <c r="R75" s="18" t="n">
         <v>31.83</v>
       </c>
-      <c r="S75" s="16" t="n">
+      <c r="S75" s="18" t="n">
         <v>32.6</v>
       </c>
-      <c r="T75" s="16" t="n">
+      <c r="T75" s="18" t="n">
         <v>34.5</v>
       </c>
-      <c r="U75" s="16" t="n">
+      <c r="U75" s="18" t="n">
         <v>31.85</v>
       </c>
-      <c r="V75" s="16" t="n">
+      <c r="V75" s="18" t="n">
         <v>32.28</v>
       </c>
-      <c r="W75" s="16" t="n">
+      <c r="W75" s="18" t="n">
         <v>37.38</v>
       </c>
-      <c r="X75" s="9" t="n">
+      <c r="X75" s="18" t="n">
         <v>43.55</v>
       </c>
-      <c r="Y75" s="16" t="n">
+      <c r="Y75" s="18" t="n">
         <v>42.93</v>
       </c>
-      <c r="Z75" s="9" t="n">
+      <c r="Z75" s="18" t="n">
         <v>43.05</v>
       </c>
-      <c r="AA75" s="9" t="n">
+      <c r="AA75" s="18" t="n">
         <v>43.25</v>
       </c>
-      <c r="AB75" s="9" t="n">
+      <c r="AB75" s="18" t="n">
         <v>43.55</v>
       </c>
-      <c r="AC75" s="16" t="n">
+      <c r="AC75" s="18" t="n">
         <v>43</v>
       </c>
-      <c r="AD75" s="9" t="n">
+      <c r="AD75" s="18" t="n">
         <v>43.15</v>
       </c>
-      <c r="AE75" s="9" t="n">
+      <c r="AE75" s="18" t="n">
         <v>43.18</v>
       </c>
-      <c r="AF75" s="16" t="n">
+      <c r="AF75" s="18" t="n">
         <v>39.02</v>
       </c>
-      <c r="AG75" s="16" t="n">
+      <c r="AG75" s="18" t="n">
         <v>32.98</v>
       </c>
-      <c r="AH75" s="6" t="n">
+      <c r="AH75" s="8" t="n">
         <v>36.53</v>
       </c>
       <c r="AI75" s="6" t="inlineStr"/>
       <c r="AJ75" s="6" t="inlineStr"/>
-      <c r="AK75" s="15" t="n"/>
+      <c r="AK75" s="17" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -7183,214 +7198,214 @@
       <c r="B76" s="6" t="n">
         <v>603.25</v>
       </c>
-      <c r="C76" s="16" t="n">
+      <c r="C76" s="18" t="n">
         <v>32.45</v>
       </c>
-      <c r="D76" s="16" t="n">
+      <c r="D76" s="18" t="n">
         <v>32.73</v>
       </c>
-      <c r="E76" s="16" t="n">
+      <c r="E76" s="18" t="n">
         <v>32.25</v>
       </c>
-      <c r="F76" s="16" t="n">
+      <c r="F76" s="18" t="n">
         <v>32.4</v>
       </c>
-      <c r="G76" s="16" t="n">
+      <c r="G76" s="18" t="n">
         <v>32.48</v>
       </c>
-      <c r="H76" s="16" t="n">
+      <c r="H76" s="18" t="n">
         <v>32.68</v>
       </c>
-      <c r="I76" s="16" t="n">
+      <c r="I76" s="18" t="n">
         <v>33.48</v>
       </c>
-      <c r="J76" s="16" t="n">
+      <c r="J76" s="18" t="n">
         <v>32.9</v>
       </c>
-      <c r="K76" s="16" t="n">
+      <c r="K76" s="18" t="n">
         <v>39.47</v>
       </c>
-      <c r="L76" s="9" t="n">
+      <c r="L76" s="18" t="n">
         <v>46.07</v>
       </c>
-      <c r="M76" s="16" t="n">
+      <c r="M76" s="18" t="n">
         <v>39.98</v>
       </c>
-      <c r="N76" s="16" t="n">
+      <c r="N76" s="18" t="n">
         <v>32.65</v>
       </c>
-      <c r="O76" s="16" t="n">
+      <c r="O76" s="18" t="n">
         <v>32.73</v>
       </c>
-      <c r="P76" s="16" t="n">
+      <c r="P76" s="18" t="n">
         <v>33.17</v>
       </c>
-      <c r="Q76" s="16" t="n">
+      <c r="Q76" s="18" t="n">
         <v>32.58</v>
       </c>
-      <c r="R76" s="16" t="n">
+      <c r="R76" s="18" t="n">
         <v>32.58</v>
       </c>
-      <c r="S76" s="16" t="n">
+      <c r="S76" s="18" t="n">
         <v>33</v>
       </c>
-      <c r="T76" s="16" t="n">
+      <c r="T76" s="18" t="n">
         <v>33.23</v>
       </c>
-      <c r="U76" s="16" t="n">
+      <c r="U76" s="18" t="n">
         <v>32.78</v>
       </c>
-      <c r="V76" s="16" t="n">
+      <c r="V76" s="18" t="n">
         <v>32.85</v>
       </c>
-      <c r="W76" s="9" t="n">
+      <c r="W76" s="18" t="n">
         <v>44.6</v>
       </c>
-      <c r="X76" s="9" t="n">
+      <c r="X76" s="18" t="n">
         <v>46.48</v>
       </c>
-      <c r="Y76" s="9" t="n">
+      <c r="Y76" s="18" t="n">
         <v>46.78</v>
       </c>
-      <c r="Z76" s="9" t="n">
+      <c r="Z76" s="18" t="n">
         <v>46.05</v>
       </c>
-      <c r="AA76" s="9" t="n">
+      <c r="AA76" s="18" t="n">
         <v>46.18</v>
       </c>
-      <c r="AB76" s="9" t="n">
+      <c r="AB76" s="18" t="n">
         <v>48.7</v>
       </c>
-      <c r="AC76" s="9" t="n">
+      <c r="AC76" s="18" t="n">
         <v>47.2</v>
       </c>
-      <c r="AD76" s="9" t="n">
+      <c r="AD76" s="18" t="n">
         <v>46.2</v>
       </c>
-      <c r="AE76" s="9" t="n">
+      <c r="AE76" s="18" t="n">
         <v>46.93</v>
       </c>
-      <c r="AF76" s="16" t="n">
+      <c r="AF76" s="18" t="n">
         <v>39.97</v>
       </c>
-      <c r="AG76" s="16" t="n">
+      <c r="AG76" s="18" t="n">
         <v>33.45</v>
       </c>
-      <c r="AH76" s="6" t="n">
+      <c r="AH76" s="8" t="n">
         <v>37.9</v>
       </c>
       <c r="AI76" s="6" t="inlineStr"/>
       <c r="AJ76" s="6" t="inlineStr"/>
-      <c r="AK76" s="15" t="n"/>
+      <c r="AK76" s="17" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="10" t="inlineStr">
+      <c r="A77" s="11" t="inlineStr">
         <is>
           <t>CANAL SUR - TELEVISION MUN</t>
         </is>
       </c>
-      <c r="B77" s="11" t="n">
+      <c r="B77" s="12" t="n">
         <v>621.25</v>
       </c>
-      <c r="C77" s="12" t="n">
+      <c r="C77" s="13" t="n">
         <v>75.28</v>
       </c>
-      <c r="D77" s="12" t="n">
+      <c r="D77" s="13" t="n">
         <v>75.62</v>
       </c>
-      <c r="E77" s="12" t="n">
+      <c r="E77" s="19" t="n">
         <v>69.09999999999999</v>
       </c>
-      <c r="F77" s="12" t="n">
+      <c r="F77" s="19" t="n">
         <v>70.23</v>
       </c>
-      <c r="G77" s="12" t="n">
+      <c r="G77" s="19" t="n">
         <v>70.78</v>
       </c>
-      <c r="H77" s="12" t="n">
+      <c r="H77" s="19" t="n">
         <v>69.77</v>
       </c>
-      <c r="I77" s="12" t="n">
+      <c r="I77" s="19" t="n">
         <v>70.2</v>
       </c>
-      <c r="J77" s="12" t="n">
+      <c r="J77" s="19" t="n">
         <v>68.48</v>
       </c>
-      <c r="K77" s="12" t="n">
+      <c r="K77" s="13" t="n">
         <v>83.56999999999999</v>
       </c>
-      <c r="L77" s="12" t="n">
+      <c r="L77" s="13" t="n">
         <v>99.27</v>
       </c>
-      <c r="M77" s="12" t="n">
+      <c r="M77" s="13" t="n">
         <v>84.33</v>
       </c>
-      <c r="N77" s="12" t="n">
+      <c r="N77" s="19" t="n">
         <v>69.23</v>
       </c>
-      <c r="O77" s="12" t="n">
+      <c r="O77" s="19" t="n">
         <v>68.53</v>
       </c>
-      <c r="P77" s="12" t="n">
+      <c r="P77" s="19" t="n">
         <v>70.05</v>
       </c>
-      <c r="Q77" s="12" t="n">
+      <c r="Q77" s="19" t="n">
         <v>68.92</v>
       </c>
-      <c r="R77" s="12" t="n">
+      <c r="R77" s="13" t="n">
         <v>71.08</v>
       </c>
-      <c r="S77" s="12" t="n">
+      <c r="S77" s="13" t="n">
         <v>72.17</v>
       </c>
-      <c r="T77" s="12" t="n">
+      <c r="T77" s="13" t="n">
         <v>71.13</v>
       </c>
-      <c r="U77" s="12" t="n">
+      <c r="U77" s="13" t="n">
         <v>72.59999999999999</v>
       </c>
-      <c r="V77" s="12" t="n">
+      <c r="V77" s="19" t="n">
         <v>69.81999999999999</v>
       </c>
-      <c r="W77" s="12" t="n">
+      <c r="W77" s="13" t="n">
         <v>85.8</v>
       </c>
-      <c r="X77" s="12" t="n">
+      <c r="X77" s="13" t="n">
         <v>99.72</v>
       </c>
-      <c r="Y77" s="12" t="n">
+      <c r="Y77" s="13" t="n">
         <v>99.43000000000001</v>
       </c>
-      <c r="Z77" s="12" t="n">
+      <c r="Z77" s="13" t="n">
         <v>99.73</v>
       </c>
-      <c r="AA77" s="12" t="n">
+      <c r="AA77" s="13" t="n">
         <v>99.73</v>
       </c>
-      <c r="AB77" s="12" t="n">
+      <c r="AB77" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="AC77" s="12" t="n">
+      <c r="AC77" s="13" t="n">
         <v>99.05</v>
       </c>
-      <c r="AD77" s="12" t="n">
+      <c r="AD77" s="13" t="n">
         <v>99.48</v>
       </c>
-      <c r="AE77" s="12" t="n">
+      <c r="AE77" s="13" t="n">
         <v>99.78</v>
       </c>
-      <c r="AF77" s="12" t="n">
+      <c r="AF77" s="13" t="n">
         <v>85.68000000000001</v>
       </c>
-      <c r="AG77" s="12" t="n">
+      <c r="AG77" s="13" t="n">
         <v>73.12</v>
       </c>
-      <c r="AH77" s="11" t="n">
+      <c r="AH77" s="13" t="n">
         <v>81.02</v>
       </c>
-      <c r="AI77" s="11" t="inlineStr"/>
-      <c r="AJ77" s="11" t="inlineStr"/>
-      <c r="AK77" s="17" t="n"/>
+      <c r="AI77" s="12" t="inlineStr"/>
+      <c r="AJ77" s="12" t="inlineStr"/>
+      <c r="AK77" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="33">

--- a/ReportesUnificados/loja_ReporteUnificado.xlsx
+++ b/ReportesUnificados/loja_ReporteUnificado.xlsx
@@ -39,14 +39,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFC4A2C"/>
-        <bgColor rgb="FFFC4A2C"/>
+        <fgColor rgb="FFCDFECE"/>
+        <bgColor rgb="FFCDFECE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCDFECE"/>
-        <bgColor rgb="FFCDFECE"/>
+        <fgColor rgb="FFFC4A2C"/>
+        <bgColor rgb="FFFC4A2C"/>
       </patternFill>
     </fill>
     <fill>
@@ -197,10 +197,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -215,10 +215,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -804,7 +804,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 01/09/2025</t>
+          <t>FECHA PRESENTACIÓN: 02/09/2025</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       <c r="AG11" s="7" t="n">
         <v>103.78</v>
       </c>
-      <c r="AH11" s="6" t="n">
+      <c r="AH11" s="7" t="n">
         <v>102.07</v>
       </c>
       <c r="AI11" s="8" t="n">
@@ -1150,7 +1150,7 @@
       <c r="AG12" s="7" t="n">
         <v>102.45</v>
       </c>
-      <c r="AH12" s="6" t="n">
+      <c r="AH12" s="7" t="n">
         <v>102.13</v>
       </c>
       <c r="AI12" s="8" t="n">
@@ -1261,7 +1261,7 @@
       <c r="AG13" s="7" t="n">
         <v>104.82</v>
       </c>
-      <c r="AH13" s="6" t="n">
+      <c r="AH13" s="7" t="n">
         <v>106.91</v>
       </c>
       <c r="AI13" s="8" t="n">
@@ -1372,7 +1372,7 @@
       <c r="AG14" s="7" t="n">
         <v>111.67</v>
       </c>
-      <c r="AH14" s="6" t="n">
+      <c r="AH14" s="7" t="n">
         <v>109.46</v>
       </c>
       <c r="AI14" s="8" t="n">
@@ -1483,7 +1483,7 @@
       <c r="AG15" s="7" t="n">
         <v>105.46</v>
       </c>
-      <c r="AH15" s="6" t="n">
+      <c r="AH15" s="7" t="n">
         <v>103.29</v>
       </c>
       <c r="AI15" s="8" t="n">
@@ -1594,7 +1594,7 @@
       <c r="AG16" s="7" t="n">
         <v>87.37</v>
       </c>
-      <c r="AH16" s="6" t="n">
+      <c r="AH16" s="7" t="n">
         <v>84.44</v>
       </c>
       <c r="AI16" s="8" t="n">
@@ -1705,7 +1705,7 @@
       <c r="AG17" s="7" t="n">
         <v>89.48</v>
       </c>
-      <c r="AH17" s="6" t="n">
+      <c r="AH17" s="7" t="n">
         <v>88.02</v>
       </c>
       <c r="AI17" s="8" t="n">
@@ -1816,7 +1816,7 @@
       <c r="AG18" s="7" t="n">
         <v>106.29</v>
       </c>
-      <c r="AH18" s="6" t="n">
+      <c r="AH18" s="7" t="n">
         <v>103.91</v>
       </c>
       <c r="AI18" s="8" t="n">
@@ -1927,7 +1927,7 @@
       <c r="AG19" s="7" t="n">
         <v>105.72</v>
       </c>
-      <c r="AH19" s="6" t="n">
+      <c r="AH19" s="7" t="n">
         <v>104.17</v>
       </c>
       <c r="AI19" s="8" t="n">
@@ -2038,7 +2038,7 @@
       <c r="AG20" s="7" t="n">
         <v>94.88</v>
       </c>
-      <c r="AH20" s="6" t="n">
+      <c r="AH20" s="7" t="n">
         <v>95.44</v>
       </c>
       <c r="AI20" s="8" t="n">
@@ -2149,7 +2149,7 @@
       <c r="AG21" s="7" t="n">
         <v>96.98999999999999</v>
       </c>
-      <c r="AH21" s="6" t="n">
+      <c r="AH21" s="7" t="n">
         <v>96.64</v>
       </c>
       <c r="AI21" s="8" t="n">
@@ -2260,7 +2260,7 @@
       <c r="AG22" s="7" t="n">
         <v>109.51</v>
       </c>
-      <c r="AH22" s="6" t="n">
+      <c r="AH22" s="7" t="n">
         <v>105.92</v>
       </c>
       <c r="AI22" s="8" t="n">
@@ -2371,7 +2371,7 @@
       <c r="AG23" s="7" t="n">
         <v>104.5</v>
       </c>
-      <c r="AH23" s="6" t="n">
+      <c r="AH23" s="7" t="n">
         <v>102.97</v>
       </c>
       <c r="AI23" s="8" t="n">
@@ -2482,7 +2482,7 @@
       <c r="AG24" s="7" t="n">
         <v>106.08</v>
       </c>
-      <c r="AH24" s="6" t="n">
+      <c r="AH24" s="7" t="n">
         <v>104.14</v>
       </c>
       <c r="AI24" s="8" t="n">
@@ -2593,7 +2593,7 @@
       <c r="AG25" s="7" t="n">
         <v>92.5</v>
       </c>
-      <c r="AH25" s="6" t="n">
+      <c r="AH25" s="7" t="n">
         <v>92.11</v>
       </c>
       <c r="AI25" s="8" t="n">
@@ -2704,7 +2704,7 @@
       <c r="AG26" s="7" t="n">
         <v>105.59</v>
       </c>
-      <c r="AH26" s="6" t="n">
+      <c r="AH26" s="7" t="n">
         <v>103.28</v>
       </c>
       <c r="AI26" s="8" t="n">
@@ -2815,7 +2815,7 @@
       <c r="AG27" s="7" t="n">
         <v>96.20999999999999</v>
       </c>
-      <c r="AH27" s="6" t="n">
+      <c r="AH27" s="7" t="n">
         <v>95.87</v>
       </c>
       <c r="AI27" s="8" t="n">
@@ -2926,7 +2926,7 @@
       <c r="AG28" s="7" t="n">
         <v>98.55</v>
       </c>
-      <c r="AH28" s="6" t="n">
+      <c r="AH28" s="7" t="n">
         <v>81.95</v>
       </c>
       <c r="AI28" s="8" t="n">
@@ -3037,7 +3037,7 @@
       <c r="AG29" s="7" t="n">
         <v>98.88</v>
       </c>
-      <c r="AH29" s="6" t="n">
+      <c r="AH29" s="7" t="n">
         <v>98.59</v>
       </c>
       <c r="AI29" s="8" t="n">
@@ -3148,7 +3148,7 @@
       <c r="AG30" s="7" t="n">
         <v>106.94</v>
       </c>
-      <c r="AH30" s="6" t="n">
+      <c r="AH30" s="7" t="n">
         <v>106.71</v>
       </c>
       <c r="AI30" s="8" t="n">
@@ -3259,7 +3259,7 @@
       <c r="AG31" s="7" t="n">
         <v>61.41</v>
       </c>
-      <c r="AH31" s="8" t="n">
+      <c r="AH31" s="10" t="n">
         <v>52.73</v>
       </c>
       <c r="AI31" s="8" t="n">
@@ -3370,7 +3370,7 @@
       <c r="AG32" s="7" t="n">
         <v>91.77</v>
       </c>
-      <c r="AH32" s="6" t="n">
+      <c r="AH32" s="7" t="n">
         <v>91.68000000000001</v>
       </c>
       <c r="AI32" s="8" t="n">
@@ -3481,7 +3481,7 @@
       <c r="AG33" s="7" t="n">
         <v>91.63</v>
       </c>
-      <c r="AH33" s="6" t="n">
+      <c r="AH33" s="7" t="n">
         <v>92.72</v>
       </c>
       <c r="AI33" s="8" t="n">
@@ -3592,7 +3592,7 @@
       <c r="AG34" s="7" t="n">
         <v>90.66</v>
       </c>
-      <c r="AH34" s="6" t="n">
+      <c r="AH34" s="7" t="n">
         <v>89.5</v>
       </c>
       <c r="AI34" s="8" t="n">
@@ -3703,7 +3703,7 @@
       <c r="AG35" s="7" t="n">
         <v>96.22</v>
       </c>
-      <c r="AH35" s="6" t="n">
+      <c r="AH35" s="7" t="n">
         <v>96.39</v>
       </c>
       <c r="AI35" s="8" t="n">
@@ -3814,7 +3814,7 @@
       <c r="AG36" s="7" t="n">
         <v>101.43</v>
       </c>
-      <c r="AH36" s="6" t="n">
+      <c r="AH36" s="7" t="n">
         <v>100.54</v>
       </c>
       <c r="AI36" s="8" t="n">
@@ -3925,7 +3925,7 @@
       <c r="AG37" s="7" t="n">
         <v>105.94</v>
       </c>
-      <c r="AH37" s="6" t="n">
+      <c r="AH37" s="7" t="n">
         <v>104.41</v>
       </c>
       <c r="AI37" s="8" t="n">
@@ -4036,7 +4036,7 @@
       <c r="AG38" s="7" t="n">
         <v>88.09</v>
       </c>
-      <c r="AH38" s="6" t="n">
+      <c r="AH38" s="7" t="n">
         <v>88.23</v>
       </c>
       <c r="AI38" s="8" t="n">
@@ -4147,7 +4147,7 @@
       <c r="AG39" s="7" t="n">
         <v>100.18</v>
       </c>
-      <c r="AH39" s="6" t="n">
+      <c r="AH39" s="7" t="n">
         <v>100.66</v>
       </c>
       <c r="AI39" s="8" t="n">
@@ -4258,7 +4258,7 @@
       <c r="AG40" s="7" t="n">
         <v>100.71</v>
       </c>
-      <c r="AH40" s="6" t="n">
+      <c r="AH40" s="7" t="n">
         <v>100.45</v>
       </c>
       <c r="AI40" s="8" t="n">
@@ -4369,7 +4369,7 @@
       <c r="AG41" s="7" t="n">
         <v>103.92</v>
       </c>
-      <c r="AH41" s="6" t="n">
+      <c r="AH41" s="7" t="n">
         <v>105.27</v>
       </c>
       <c r="AI41" s="8" t="n">
@@ -4480,7 +4480,7 @@
       <c r="AG42" s="7" t="n">
         <v>59.83</v>
       </c>
-      <c r="AH42" s="8" t="n">
+      <c r="AH42" s="10" t="n">
         <v>52.47</v>
       </c>
       <c r="AI42" s="8" t="n">
@@ -4591,7 +4591,7 @@
       <c r="AG43" s="7" t="n">
         <v>98.54000000000001</v>
       </c>
-      <c r="AH43" s="6" t="n">
+      <c r="AH43" s="7" t="n">
         <v>97.64</v>
       </c>
       <c r="AI43" s="8" t="n">
@@ -4702,7 +4702,7 @@
       <c r="AG44" s="7" t="n">
         <v>100.94</v>
       </c>
-      <c r="AH44" s="6" t="n">
+      <c r="AH44" s="7" t="n">
         <v>102.15</v>
       </c>
       <c r="AI44" s="8" t="n">
@@ -4813,7 +4813,7 @@
       <c r="AG45" s="7" t="n">
         <v>104.17</v>
       </c>
-      <c r="AH45" s="6" t="n">
+      <c r="AH45" s="7" t="n">
         <v>100.05</v>
       </c>
       <c r="AI45" s="8" t="n">
@@ -4924,7 +4924,7 @@
       <c r="AG46" s="7" t="n">
         <v>102.45</v>
       </c>
-      <c r="AH46" s="6" t="n">
+      <c r="AH46" s="7" t="n">
         <v>100.69</v>
       </c>
       <c r="AI46" s="8" t="n">
@@ -5035,7 +5035,7 @@
       <c r="AG47" s="7" t="n">
         <v>100.83</v>
       </c>
-      <c r="AH47" s="6" t="n">
+      <c r="AH47" s="7" t="n">
         <v>100.35</v>
       </c>
       <c r="AI47" s="8" t="n">
@@ -5146,7 +5146,7 @@
       <c r="AG48" s="7" t="n">
         <v>92.87</v>
       </c>
-      <c r="AH48" s="6" t="n">
+      <c r="AH48" s="7" t="n">
         <v>93.23999999999999</v>
       </c>
       <c r="AI48" s="8" t="n">
@@ -5257,7 +5257,7 @@
       <c r="AG49" s="7" t="n">
         <v>83.7</v>
       </c>
-      <c r="AH49" s="6" t="n">
+      <c r="AH49" s="7" t="n">
         <v>86.04000000000001</v>
       </c>
       <c r="AI49" s="8" t="n">
@@ -5368,7 +5368,7 @@
       <c r="AG50" s="7" t="n">
         <v>102.71</v>
       </c>
-      <c r="AH50" s="6" t="n">
+      <c r="AH50" s="7" t="n">
         <v>101.65</v>
       </c>
       <c r="AI50" s="8" t="n">
@@ -5479,7 +5479,7 @@
       <c r="AG51" s="13" t="n">
         <v>79.73</v>
       </c>
-      <c r="AH51" s="12" t="n">
+      <c r="AH51" s="13" t="n">
         <v>81.06999999999999</v>
       </c>
       <c r="AI51" s="14" t="n">
@@ -5535,7 +5535,7 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 01/09/2025</t>
+          <t>FECHA PRESENTACIÓN: 02/09/2025</t>
         </is>
       </c>
     </row>

--- a/ReportesUnificados/loja_ReporteUnificado.xlsx
+++ b/ReportesUnificados/loja_ReporteUnificado.xlsx
@@ -5977,7 +5977,7 @@
       <c r="AE64" s="7" t="n">
         <v>73.13</v>
       </c>
-      <c r="AF64" s="10" t="n">
+      <c r="AF64" s="7" t="n">
         <v>71</v>
       </c>
       <c r="AG64" s="7" t="n">
@@ -6637,7 +6637,7 @@
       <c r="AG70" s="18" t="n">
         <v>28.65</v>
       </c>
-      <c r="AH70" s="8" t="n">
+      <c r="AH70" s="18" t="n">
         <v>32.11</v>
       </c>
       <c r="AI70" s="6" t="inlineStr"/>
@@ -6743,7 +6743,7 @@
       <c r="AF71" s="10" t="n">
         <v>69.75</v>
       </c>
-      <c r="AG71" s="7" t="n">
+      <c r="AG71" s="10" t="n">
         <v>72</v>
       </c>
       <c r="AH71" s="10" t="n">
@@ -6855,7 +6855,7 @@
       <c r="AG72" s="18" t="n">
         <v>30.6</v>
       </c>
-      <c r="AH72" s="8" t="n">
+      <c r="AH72" s="18" t="n">
         <v>33.36</v>
       </c>
       <c r="AI72" s="6" t="inlineStr"/>
@@ -6964,7 +6964,7 @@
       <c r="AG73" s="18" t="n">
         <v>41.08</v>
       </c>
-      <c r="AH73" s="8" t="n">
+      <c r="AH73" s="18" t="n">
         <v>40.65</v>
       </c>
       <c r="AI73" s="6" t="inlineStr"/>
@@ -7182,7 +7182,7 @@
       <c r="AG75" s="18" t="n">
         <v>32.98</v>
       </c>
-      <c r="AH75" s="8" t="n">
+      <c r="AH75" s="18" t="n">
         <v>36.53</v>
       </c>
       <c r="AI75" s="6" t="inlineStr"/>
@@ -7291,7 +7291,7 @@
       <c r="AG76" s="18" t="n">
         <v>33.45</v>
       </c>
-      <c r="AH76" s="8" t="n">
+      <c r="AH76" s="18" t="n">
         <v>37.9</v>
       </c>
       <c r="AI76" s="6" t="inlineStr"/>
@@ -7352,16 +7352,16 @@
       <c r="Q77" s="19" t="n">
         <v>68.92</v>
       </c>
-      <c r="R77" s="13" t="n">
+      <c r="R77" s="19" t="n">
         <v>71.08</v>
       </c>
-      <c r="S77" s="13" t="n">
+      <c r="S77" s="19" t="n">
         <v>72.17</v>
       </c>
-      <c r="T77" s="13" t="n">
+      <c r="T77" s="19" t="n">
         <v>71.13</v>
       </c>
-      <c r="U77" s="13" t="n">
+      <c r="U77" s="19" t="n">
         <v>72.59999999999999</v>
       </c>
       <c r="V77" s="19" t="n">
@@ -7397,7 +7397,7 @@
       <c r="AF77" s="13" t="n">
         <v>85.68000000000001</v>
       </c>
-      <c r="AG77" s="13" t="n">
+      <c r="AG77" s="19" t="n">
         <v>73.12</v>
       </c>
       <c r="AH77" s="13" t="n">

--- a/ReportesUnificados/loja_ReporteUnificado.xlsx
+++ b/ReportesUnificados/loja_ReporteUnificado.xlsx
@@ -177,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -204,7 +204,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -222,12 +222,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1046,7 +1049,12 @@
         <v>261.08</v>
       </c>
       <c r="AJ11" s="6" t="inlineStr"/>
-      <c r="AK11" s="9" t="inlineStr"/>
+      <c r="AK11" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1157,7 +1165,12 @@
         <v>400.33</v>
       </c>
       <c r="AJ12" s="6" t="inlineStr"/>
-      <c r="AK12" s="9" t="inlineStr"/>
+      <c r="AK12" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1268,7 +1281,12 @@
         <v>485.39</v>
       </c>
       <c r="AJ13" s="6" t="inlineStr"/>
-      <c r="AK13" s="9" t="inlineStr"/>
+      <c r="AK13" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1379,7 +1397,12 @@
         <v>372.17</v>
       </c>
       <c r="AJ14" s="6" t="inlineStr"/>
-      <c r="AK14" s="9" t="inlineStr"/>
+      <c r="AK14" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1490,7 +1513,12 @@
         <v>388.41</v>
       </c>
       <c r="AJ15" s="6" t="inlineStr"/>
-      <c r="AK15" s="9" t="inlineStr"/>
+      <c r="AK15" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1601,7 +1629,12 @@
         <v>444.57</v>
       </c>
       <c r="AJ16" s="6" t="inlineStr"/>
-      <c r="AK16" s="9" t="inlineStr"/>
+      <c r="AK16" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1712,7 +1745,12 @@
         <v>364.81</v>
       </c>
       <c r="AJ17" s="6" t="inlineStr"/>
-      <c r="AK17" s="9" t="inlineStr"/>
+      <c r="AK17" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1823,7 +1861,12 @@
         <v>415.88</v>
       </c>
       <c r="AJ18" s="6" t="inlineStr"/>
-      <c r="AK18" s="9" t="inlineStr"/>
+      <c r="AK18" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1934,7 +1977,12 @@
         <v>418.76</v>
       </c>
       <c r="AJ19" s="6" t="inlineStr"/>
-      <c r="AK19" s="9" t="inlineStr"/>
+      <c r="AK19" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -2045,7 +2093,12 @@
         <v>400.73</v>
       </c>
       <c r="AJ20" s="6" t="inlineStr"/>
-      <c r="AK20" s="9" t="inlineStr"/>
+      <c r="AK20" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2156,7 +2209,12 @@
         <v>406.58</v>
       </c>
       <c r="AJ21" s="6" t="inlineStr"/>
-      <c r="AK21" s="9" t="inlineStr"/>
+      <c r="AK21" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2267,7 +2325,12 @@
         <v>387.36</v>
       </c>
       <c r="AJ22" s="6" t="inlineStr"/>
-      <c r="AK22" s="9" t="inlineStr"/>
+      <c r="AK22" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -2378,7 +2441,12 @@
         <v>419.3</v>
       </c>
       <c r="AJ23" s="6" t="inlineStr"/>
-      <c r="AK23" s="9" t="inlineStr"/>
+      <c r="AK23" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2489,7 +2557,12 @@
         <v>408.72</v>
       </c>
       <c r="AJ24" s="6" t="inlineStr"/>
-      <c r="AK24" s="9" t="inlineStr"/>
+      <c r="AK24" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -2600,7 +2673,12 @@
         <v>439.51</v>
       </c>
       <c r="AJ25" s="6" t="inlineStr"/>
-      <c r="AK25" s="9" t="inlineStr"/>
+      <c r="AK25" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -2711,7 +2789,12 @@
         <v>412.36</v>
       </c>
       <c r="AJ26" s="6" t="inlineStr"/>
-      <c r="AK26" s="9" t="inlineStr"/>
+      <c r="AK26" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2822,7 +2905,12 @@
         <v>398.86</v>
       </c>
       <c r="AJ27" s="6" t="inlineStr"/>
-      <c r="AK27" s="9" t="inlineStr"/>
+      <c r="AK27" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -2933,7 +3021,12 @@
         <v>546.02</v>
       </c>
       <c r="AJ28" s="6" t="inlineStr"/>
-      <c r="AK28" s="9" t="inlineStr"/>
+      <c r="AK28" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -3044,7 +3137,12 @@
         <v>391.54</v>
       </c>
       <c r="AJ29" s="6" t="inlineStr"/>
-      <c r="AK29" s="9" t="inlineStr"/>
+      <c r="AK29" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -3155,7 +3253,12 @@
         <v>476.01</v>
       </c>
       <c r="AJ30" s="6" t="inlineStr"/>
-      <c r="AK30" s="9" t="inlineStr"/>
+      <c r="AK30" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -3266,7 +3369,12 @@
         <v>703.75</v>
       </c>
       <c r="AJ31" s="6" t="inlineStr"/>
-      <c r="AK31" s="9" t="inlineStr"/>
+      <c r="AK31" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -3377,7 +3485,12 @@
         <v>413.77</v>
       </c>
       <c r="AJ32" s="6" t="inlineStr"/>
-      <c r="AK32" s="9" t="inlineStr"/>
+      <c r="AK32" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -3488,7 +3601,12 @@
         <v>438.53</v>
       </c>
       <c r="AJ33" s="6" t="inlineStr"/>
-      <c r="AK33" s="9" t="inlineStr"/>
+      <c r="AK33" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -3599,7 +3717,12 @@
         <v>496.73</v>
       </c>
       <c r="AJ34" s="6" t="inlineStr"/>
-      <c r="AK34" s="9" t="inlineStr"/>
+      <c r="AK34" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -3710,7 +3833,12 @@
         <v>387.7</v>
       </c>
       <c r="AJ35" s="6" t="inlineStr"/>
-      <c r="AK35" s="9" t="inlineStr"/>
+      <c r="AK35" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -3821,7 +3949,12 @@
         <v>400.46</v>
       </c>
       <c r="AJ36" s="6" t="inlineStr"/>
-      <c r="AK36" s="9" t="inlineStr"/>
+      <c r="AK36" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -3932,7 +4065,12 @@
         <v>422.94</v>
       </c>
       <c r="AJ37" s="6" t="inlineStr"/>
-      <c r="AK37" s="9" t="inlineStr"/>
+      <c r="AK37" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -4043,7 +4181,12 @@
         <v>419.65</v>
       </c>
       <c r="AJ38" s="6" t="inlineStr"/>
-      <c r="AK38" s="9" t="inlineStr"/>
+      <c r="AK38" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -4154,7 +4297,12 @@
         <v>399.91</v>
       </c>
       <c r="AJ39" s="6" t="inlineStr"/>
-      <c r="AK39" s="9" t="inlineStr"/>
+      <c r="AK39" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -4265,7 +4413,12 @@
         <v>407.04</v>
       </c>
       <c r="AJ40" s="6" t="inlineStr"/>
-      <c r="AK40" s="9" t="inlineStr"/>
+      <c r="AK40" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -4376,7 +4529,12 @@
         <v>316.68</v>
       </c>
       <c r="AJ41" s="6" t="inlineStr"/>
-      <c r="AK41" s="9" t="inlineStr"/>
+      <c r="AK41" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -4487,7 +4645,12 @@
         <v>504.72</v>
       </c>
       <c r="AJ42" s="6" t="inlineStr"/>
-      <c r="AK42" s="9" t="inlineStr"/>
+      <c r="AK42" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -4598,7 +4761,12 @@
         <v>265.12</v>
       </c>
       <c r="AJ43" s="6" t="inlineStr"/>
-      <c r="AK43" s="9" t="inlineStr"/>
+      <c r="AK43" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -4709,7 +4877,12 @@
         <v>348.54</v>
       </c>
       <c r="AJ44" s="6" t="inlineStr"/>
-      <c r="AK44" s="9" t="inlineStr"/>
+      <c r="AK44" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -4820,7 +4993,12 @@
         <v>456.27</v>
       </c>
       <c r="AJ45" s="6" t="inlineStr"/>
-      <c r="AK45" s="9" t="inlineStr"/>
+      <c r="AK45" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -4931,7 +5109,12 @@
         <v>420.89</v>
       </c>
       <c r="AJ46" s="6" t="inlineStr"/>
-      <c r="AK46" s="9" t="inlineStr"/>
+      <c r="AK46" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -5042,7 +5225,12 @@
         <v>416.29</v>
       </c>
       <c r="AJ47" s="6" t="inlineStr"/>
-      <c r="AK47" s="9" t="inlineStr"/>
+      <c r="AK47" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -5153,7 +5341,12 @@
         <v>389.74</v>
       </c>
       <c r="AJ48" s="6" t="inlineStr"/>
-      <c r="AK48" s="9" t="inlineStr"/>
+      <c r="AK48" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -5264,7 +5457,12 @@
         <v>363.9</v>
       </c>
       <c r="AJ49" s="6" t="inlineStr"/>
-      <c r="AK49" s="9" t="inlineStr"/>
+      <c r="AK49" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -5375,7 +5573,12 @@
         <v>310.71</v>
       </c>
       <c r="AJ50" s="6" t="inlineStr"/>
-      <c r="AK50" s="9" t="inlineStr"/>
+      <c r="AK50" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
@@ -5486,7 +5689,12 @@
         <v>264.88</v>
       </c>
       <c r="AJ51" s="12" t="inlineStr"/>
-      <c r="AK51" s="15" t="inlineStr"/>
+      <c r="AK51" s="15" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="52"/>
     <row r="53"/>
@@ -6535,7 +6743,7 @@
       <c r="AJ69" s="6" t="inlineStr"/>
       <c r="AK69" s="17" t="n"/>
     </row>
-    <row r="70">
+    <row r="70" ht="15" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
         <is>
           <t>TELERAMA</t>
@@ -6641,7 +6849,11 @@
         <v>32.11</v>
       </c>
       <c r="AI70" s="6" t="inlineStr"/>
-      <c r="AJ70" s="6" t="inlineStr"/>
+      <c r="AJ70" s="19" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
       <c r="AK70" s="17" t="n"/>
     </row>
     <row r="71">
@@ -6753,7 +6965,7 @@
       <c r="AJ71" s="6" t="inlineStr"/>
       <c r="AK71" s="17" t="n"/>
     </row>
-    <row r="72">
+    <row r="72" ht="15" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
         <is>
           <t>CANAL UNO</t>
@@ -6859,10 +7071,14 @@
         <v>33.36</v>
       </c>
       <c r="AI72" s="6" t="inlineStr"/>
-      <c r="AJ72" s="6" t="inlineStr"/>
+      <c r="AJ72" s="19" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
       <c r="AK72" s="17" t="n"/>
     </row>
-    <row r="73">
+    <row r="73" ht="15" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
         <is>
           <t>TELEATAHUALPA (RTU)</t>
@@ -6968,7 +7184,11 @@
         <v>40.65</v>
       </c>
       <c r="AI73" s="6" t="inlineStr"/>
-      <c r="AJ73" s="6" t="inlineStr"/>
+      <c r="AJ73" s="19" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
       <c r="AK73" s="17" t="n"/>
     </row>
     <row r="74">
@@ -7080,7 +7300,7 @@
       <c r="AJ74" s="6" t="inlineStr"/>
       <c r="AK74" s="17" t="n"/>
     </row>
-    <row r="75">
+    <row r="75" ht="15" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
         <is>
           <t>UCSG TELEVISION</t>
@@ -7186,10 +7406,14 @@
         <v>36.53</v>
       </c>
       <c r="AI75" s="6" t="inlineStr"/>
-      <c r="AJ75" s="6" t="inlineStr"/>
+      <c r="AJ75" s="19" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
       <c r="AK75" s="17" t="n"/>
     </row>
-    <row r="76">
+    <row r="76" ht="15" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
         <is>
           <t>OROMAR</t>
@@ -7295,7 +7519,11 @@
         <v>37.9</v>
       </c>
       <c r="AI76" s="6" t="inlineStr"/>
-      <c r="AJ76" s="6" t="inlineStr"/>
+      <c r="AJ76" s="19" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
       <c r="AK76" s="17" t="n"/>
     </row>
     <row r="77">
@@ -7313,22 +7541,22 @@
       <c r="D77" s="13" t="n">
         <v>75.62</v>
       </c>
-      <c r="E77" s="19" t="n">
+      <c r="E77" s="20" t="n">
         <v>69.09999999999999</v>
       </c>
-      <c r="F77" s="19" t="n">
+      <c r="F77" s="20" t="n">
         <v>70.23</v>
       </c>
-      <c r="G77" s="19" t="n">
+      <c r="G77" s="20" t="n">
         <v>70.78</v>
       </c>
-      <c r="H77" s="19" t="n">
+      <c r="H77" s="20" t="n">
         <v>69.77</v>
       </c>
-      <c r="I77" s="19" t="n">
+      <c r="I77" s="20" t="n">
         <v>70.2</v>
       </c>
-      <c r="J77" s="19" t="n">
+      <c r="J77" s="20" t="n">
         <v>68.48</v>
       </c>
       <c r="K77" s="13" t="n">
@@ -7340,31 +7568,31 @@
       <c r="M77" s="13" t="n">
         <v>84.33</v>
       </c>
-      <c r="N77" s="19" t="n">
+      <c r="N77" s="20" t="n">
         <v>69.23</v>
       </c>
-      <c r="O77" s="19" t="n">
+      <c r="O77" s="20" t="n">
         <v>68.53</v>
       </c>
-      <c r="P77" s="19" t="n">
+      <c r="P77" s="20" t="n">
         <v>70.05</v>
       </c>
-      <c r="Q77" s="19" t="n">
+      <c r="Q77" s="20" t="n">
         <v>68.92</v>
       </c>
-      <c r="R77" s="19" t="n">
+      <c r="R77" s="20" t="n">
         <v>71.08</v>
       </c>
-      <c r="S77" s="19" t="n">
+      <c r="S77" s="20" t="n">
         <v>72.17</v>
       </c>
-      <c r="T77" s="19" t="n">
+      <c r="T77" s="20" t="n">
         <v>71.13</v>
       </c>
-      <c r="U77" s="19" t="n">
+      <c r="U77" s="20" t="n">
         <v>72.59999999999999</v>
       </c>
-      <c r="V77" s="19" t="n">
+      <c r="V77" s="20" t="n">
         <v>69.81999999999999</v>
       </c>
       <c r="W77" s="13" t="n">
@@ -7397,7 +7625,7 @@
       <c r="AF77" s="13" t="n">
         <v>85.68000000000001</v>
       </c>
-      <c r="AG77" s="19" t="n">
+      <c r="AG77" s="20" t="n">
         <v>73.12</v>
       </c>
       <c r="AH77" s="13" t="n">
@@ -7405,7 +7633,7 @@
       </c>
       <c r="AI77" s="12" t="inlineStr"/>
       <c r="AJ77" s="12" t="inlineStr"/>
-      <c r="AK77" s="20" t="n"/>
+      <c r="AK77" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="33">

--- a/ReportesUnificados/loja_ReporteUnificado.xlsx
+++ b/ReportesUnificados/loja_ReporteUnificado.xlsx
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 02/09/2025</t>
+          <t>FECHA PRESENTACIÓN: 03/09/2025</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5743,7 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 02/09/2025</t>
+          <t>FECHA PRESENTACIÓN: 03/09/2025</t>
         </is>
       </c>
     </row>
